--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5133BB-919E-5A49-A3E6-CB9794522CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523A4904-1125-124B-9995-AA0DD874FE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="454">
   <si>
     <t>Surname</t>
   </si>
@@ -125,9 +125,6 @@
     <t>CHIROZVA</t>
   </si>
   <si>
-    <t>DUMBA</t>
-  </si>
-  <si>
     <t>HUNGWIRI</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
     <t>H250511B</t>
   </si>
   <si>
-    <t>H250726X</t>
-  </si>
-  <si>
     <t>H250497E</t>
   </si>
   <si>
@@ -341,6 +335,9 @@
     <t>H250811H</t>
   </si>
   <si>
+    <t>H240344F</t>
+  </si>
+  <si>
     <t>H250562A</t>
   </si>
   <si>
@@ -1392,13 +1389,22 @@
   </si>
   <si>
     <t>H250107X</t>
+  </si>
+  <si>
+    <t>Francis</t>
+  </si>
+  <si>
+    <t>H240009T</t>
+  </si>
+  <si>
+    <t>majoni</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -1460,6 +1466,11 @@
       <sz val="13"/>
       <color rgb="FF333333"/>
       <name val="Times"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Latin Modern Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1525,7 +1536,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1543,7 +1554,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1587,10 +1601,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M229" totalsRowShown="0">
-  <autoFilter ref="A1:M229" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M229">
-    <sortCondition ref="C1:C229"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M228" totalsRowShown="0">
+  <autoFilter ref="A1:M228" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M228">
+    <sortCondition ref="C1:C228"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -1928,7 +1942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:M229"/>
+  <dimension ref="A1:M228"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -1982,10 +1996,10 @@
         <v>15</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D2" s="4">
         <v>0.56999999999999995</v>
@@ -1998,10 +2012,10 @@
         <v>28</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D3" s="4">
         <v>0.86</v>
@@ -2014,10 +2028,10 @@
         <v>24</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D4" s="4">
         <v>0.79</v>
@@ -2026,494 +2040,493 @@
       <c r="M4" s="6"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>59</v>
+      <c r="B5" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D5" s="4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="5"/>
       <c r="M5" s="6"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>60</v>
+      <c r="A6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D6" s="4">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="H6" s="5"/>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>46</v>
+      <c r="A7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" s="4">
-        <v>0.64</v>
+        <v>0.82</v>
       </c>
       <c r="H7" s="5"/>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>67</v>
+      <c r="A8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D8" s="4">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5"/>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
         <v>71</v>
       </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
       <c r="D9" s="4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H9" s="5"/>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>69</v>
+      <c r="A10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D10" s="4">
-        <v>0.75</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="H10" s="5"/>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>44</v>
+      <c r="A11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D11" s="4">
-        <v>0.56999999999999995</v>
+        <v>0</v>
       </c>
       <c r="H11" s="5"/>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>72</v>
+      <c r="A12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" s="4">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="H12" s="5"/>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>66</v>
+      <c r="A13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D13" s="4">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="H13" s="5"/>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>56</v>
+      <c r="A14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" s="4">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="H14" s="5"/>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>64</v>
+      <c r="A15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D15" s="4">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="H15" s="5"/>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="7" t="s">
+      <c r="A16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" s="4">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="H16" s="5"/>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" s="4">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H17" s="5"/>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D18" s="4">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="H18" s="5"/>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>70</v>
+      <c r="A19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D19" s="4">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="H19" s="5"/>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>62</v>
+      <c r="A20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D20" s="4">
-        <v>0.68</v>
+        <v>0.85</v>
       </c>
       <c r="H20" s="5"/>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>50</v>
+      <c r="A21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D21" s="4">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="H21" s="5"/>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D22" s="4">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="H22" s="5"/>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>53</v>
+      <c r="A23" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D23" s="4">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="H23" s="5"/>
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>47</v>
+      <c r="A24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D24" s="4">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="H24" s="5"/>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D25" s="4">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="H25" s="5"/>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>48</v>
+      <c r="A26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D26" s="4">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="H26" s="5"/>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>52</v>
+      <c r="A27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D27" s="4">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="H27" s="5"/>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D28" s="4">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="H28" s="5"/>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>55</v>
+      <c r="A29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D29" s="4">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="H29" s="5"/>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>57</v>
+      <c r="A30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D30" s="4">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="H30" s="5"/>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>65</v>
+      <c r="A31" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="D31" s="4">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="H31" s="5"/>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>88</v>
+      <c r="A32" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D32" s="4">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="H32" s="5"/>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D33" s="4">
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="H33" s="5"/>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
+      <c r="A34" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="D34" s="4">
-        <v>0.84</v>
-      </c>
-      <c r="H34" s="5"/>
+        <v>0.65</v>
+      </c>
       <c r="M34" s="6"/>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D35" s="4">
         <v>0</v>
@@ -2523,13 +2536,13 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D36" s="4">
         <v>0.84</v>
@@ -2537,223 +2550,222 @@
       <c r="H36" s="5"/>
       <c r="M36" s="6"/>
     </row>
-    <row r="37" spans="1:13" ht="20">
-      <c r="A37" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" t="s">
-        <v>102</v>
+    <row r="37" spans="1:13">
+      <c r="A37" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="D37" s="4">
+        <v>0.66</v>
+      </c>
+      <c r="M37" s="6"/>
+    </row>
+    <row r="38" spans="1:13" ht="20">
+      <c r="A38" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="4">
         <v>0</v>
-      </c>
-      <c r="H37" s="5"/>
-      <c r="M37" s="6"/>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" t="s">
-        <v>102</v>
-      </c>
-      <c r="D38" s="4">
-        <v>0.73</v>
       </c>
       <c r="H38" s="5"/>
       <c r="M38" s="6"/>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" s="7" t="s">
+      <c r="A39" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" t="s">
         <v>101</v>
       </c>
-      <c r="C39" t="s">
-        <v>102</v>
-      </c>
       <c r="D39" s="4">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="H39" s="5"/>
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>95</v>
+      <c r="A40" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D40" s="4">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H40" s="5"/>
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="8" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D41" s="4">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="H41" s="5"/>
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="8" t="s">
         <v>97</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D42" s="4">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H42" s="5"/>
       <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D43" s="4">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="H43" s="5"/>
       <c r="M43" s="6"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>92</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D44" s="4">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="H44" s="5"/>
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>89</v>
+      <c r="A45" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D45" s="4">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="H45" s="5"/>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D46" s="12">
-        <v>0.79</v>
+      <c r="A46" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" t="s">
+        <v>101</v>
+      </c>
+      <c r="D46" s="4">
+        <v>0.67</v>
       </c>
       <c r="H46" s="5"/>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>107</v>
+      <c r="A47" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>103</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D47" s="12">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="H47" s="5"/>
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>109</v>
+      <c r="A48" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D48" s="12">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="H48" s="5"/>
       <c r="M48" s="6"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>111</v>
+      <c r="A49" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>108</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D49" s="12">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H49" s="5"/>
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>113</v>
+      <c r="A50" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D50" s="12">
         <v>0.85</v>
@@ -2762,316 +2774,317 @@
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>115</v>
+      <c r="A51" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D51" s="12">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="H51" s="5"/>
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>117</v>
+      <c r="A52" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>114</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D52" s="12">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="H52" s="5"/>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" s="12">
+        <v>0.86</v>
+      </c>
+      <c r="H53" s="5"/>
+      <c r="M53" s="6"/>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="C54" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="M54" s="6"/>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D53" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="M53" s="6"/>
-    </row>
-    <row r="54" spans="1:13">
-      <c r="A54" s="12" t="s">
+      <c r="B55" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="C55" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D55" s="12">
+        <v>0.69</v>
+      </c>
+      <c r="M55" s="6"/>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D54" s="12">
-        <v>0.69</v>
-      </c>
-      <c r="M54" s="6"/>
-    </row>
-    <row r="55" spans="1:13">
-      <c r="A55" s="12" t="s">
+      <c r="B56" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" s="12">
+      <c r="C56" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D56" s="12">
         <v>0.71</v>
-      </c>
-      <c r="M55" s="6"/>
-    </row>
-    <row r="56" spans="1:13">
-      <c r="A56" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D56" s="12">
-        <v>0.9</v>
       </c>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="12" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D57" s="12">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D58" s="12">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D59" s="12">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D60" s="12">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D61" s="12">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D62" s="12">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="12" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D63" s="12">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D64" s="12">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D65" s="12">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D66" s="12">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D67" s="12">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68" s="12">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D69" s="12">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D70" s="12">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D71" s="12">
         <v>0.84</v>
@@ -3080,103 +3093,103 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D72" s="12">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D73" s="12">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="12" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D74" s="12">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="12" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D75" s="12">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D76" s="12">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D77" s="12">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D78" s="12">
         <v>0.84</v>
@@ -3185,133 +3198,133 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D79" s="12">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D80" s="12">
-        <v>0.81</v>
+        <v>0.74</v>
       </c>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="12" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D81" s="12">
-        <v>0.71</v>
+        <v>0.81</v>
       </c>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="12" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D82" s="12">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="12" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D83" s="12">
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="12" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D84" s="12">
-        <v>0.83</v>
+        <v>0.81</v>
       </c>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D85" s="12">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D86" s="12">
+        <v>0.85</v>
+      </c>
+      <c r="M86" s="6"/>
+    </row>
+    <row r="87" spans="1:13">
+      <c r="A87" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B87" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="C87" s="12" t="s">
         <v>185</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D86" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="M86" s="6"/>
-    </row>
-    <row r="87" spans="1:13">
-      <c r="A87" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="B87" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>186</v>
       </c>
       <c r="D87" s="12">
         <v>0.75</v>
@@ -3319,1499 +3332,1499 @@
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
-      <c r="A88" s="12" t="s">
+      <c r="A88" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D88" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="M88" s="6"/>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B89" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="C89" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D89" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="M89" s="6"/>
+    </row>
+    <row r="90" spans="1:13">
+      <c r="A90" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="C88" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D88" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="M88" s="6"/>
-    </row>
-    <row r="89" spans="1:13">
-      <c r="A89" s="12" t="s">
+      <c r="B90" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="C90" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D90" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="M90" s="6"/>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="C89" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D89" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="M89" s="6"/>
-    </row>
-    <row r="90" spans="1:13">
-      <c r="A90" s="12" t="s">
+      <c r="B91" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="C91" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D91" s="12">
+        <v>0.77</v>
+      </c>
+      <c r="M91" s="6"/>
+    </row>
+    <row r="92" spans="1:13">
+      <c r="A92" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C90" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D90" s="12">
-        <v>0.77</v>
-      </c>
-      <c r="M90" s="6"/>
-    </row>
-    <row r="91" spans="1:13">
-      <c r="A91" s="12" t="s">
+      <c r="B92" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="C92" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D92" s="12">
+        <v>0.93</v>
+      </c>
+      <c r="M92" s="6"/>
+    </row>
+    <row r="93" spans="1:13">
+      <c r="A93" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="C91" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D91" s="12">
-        <v>0.93</v>
-      </c>
-      <c r="M91" s="6"/>
-    </row>
-    <row r="92" spans="1:13">
-      <c r="A92" s="12" t="s">
+      <c r="B93" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B92" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="C92" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D92" s="12">
+      <c r="C93" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D93" s="12">
         <v>0.79</v>
-      </c>
-      <c r="M92" s="6"/>
-    </row>
-    <row r="93" spans="1:13">
-      <c r="A93" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="B93" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D93" s="12">
-        <v>0.93</v>
       </c>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="12" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D94" s="12">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D95" s="12">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="12" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D96" s="12">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D97" s="12">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D98" s="12">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="12" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D99" s="12">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="12" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D100" s="12">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D101" s="12">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="12" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D102" s="12">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="12" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D103" s="12">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D104" s="12">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D105" s="12">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="12" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D106" s="12">
-        <v>0.94</v>
+        <v>0.83</v>
       </c>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D107" s="12">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="12" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D108" s="12">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D109" s="12">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D110" s="12">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B111" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="B111" s="12" t="s">
-        <v>235</v>
-      </c>
       <c r="C111" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D111" s="12">
-        <v>0.92</v>
+        <v>0.66</v>
       </c>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="12" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D112" s="12">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="12" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D113" s="12">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="12" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D114" s="12">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D115" s="12">
-        <v>0.69</v>
+        <v>0.96</v>
       </c>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="12" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D116" s="12">
-        <v>0.78</v>
+        <v>0.69</v>
       </c>
       <c r="M116" s="6"/>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D117" s="12">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M117" s="6"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="12" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D118" s="12">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="M118" s="6"/>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D119" s="12">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="M119" s="6"/>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D120" s="12">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="M120" s="6"/>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="12" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D121" s="12">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="M121" s="6"/>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D122" s="12">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="M122" s="6"/>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="12" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D123" s="12">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="M123" s="6"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="12" t="s">
-        <v>25</v>
+        <v>257</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D124" s="12">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="M124" s="6"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="12" t="s">
-        <v>261</v>
+        <v>25</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D125" s="12">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="M125" s="6"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D126" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="M126" s="6"/>
+    </row>
+    <row r="127" spans="1:13">
+      <c r="A127" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="B127" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="B126" s="12" t="s">
+      <c r="C127" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="12" t="s">
+      <c r="D127" s="12">
+        <v>0.78</v>
+      </c>
+      <c r="M127" s="6"/>
+    </row>
+    <row r="128" spans="1:13">
+      <c r="A128" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="D126" s="12">
-        <v>0.78</v>
-      </c>
-      <c r="M126" s="6"/>
-    </row>
-    <row r="127" spans="1:13">
-      <c r="A127" s="12" t="s">
+      <c r="B128" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="B127" s="12" t="s">
+      <c r="C128" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D128" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="M128" s="6"/>
+    </row>
+    <row r="129" spans="1:13">
+      <c r="A129" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="C127" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D127" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="M127" s="6"/>
-    </row>
-    <row r="128" spans="1:13">
-      <c r="A128" s="12" t="s">
+      <c r="B129" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="B128" s="12" t="s">
+      <c r="C129" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D129" s="12">
+        <v>0.93</v>
+      </c>
+      <c r="M129" s="6"/>
+    </row>
+    <row r="130" spans="1:13">
+      <c r="A130" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="C128" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D128" s="12">
-        <v>0.93</v>
-      </c>
-      <c r="M128" s="6"/>
-    </row>
-    <row r="129" spans="1:13">
-      <c r="A129" s="12" t="s">
+      <c r="B130" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="B129" s="12" t="s">
+      <c r="C130" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D130" s="12">
+        <v>0.77</v>
+      </c>
+      <c r="M130" s="6"/>
+    </row>
+    <row r="131" spans="1:13">
+      <c r="A131" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="C129" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D129" s="12">
+      <c r="B131" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D131" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="M131" s="6"/>
+    </row>
+    <row r="132" spans="1:13">
+      <c r="A132" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="B132" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D132" s="12">
+        <v>0.87</v>
+      </c>
+      <c r="M132" s="6"/>
+    </row>
+    <row r="133" spans="1:13">
+      <c r="A133" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="B133" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D133" s="12">
+        <v>0.88</v>
+      </c>
+      <c r="M133" s="6"/>
+    </row>
+    <row r="134" spans="1:13">
+      <c r="A134" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="B134" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D134" s="12">
         <v>0.77</v>
       </c>
-      <c r="M129" s="6"/>
-    </row>
-    <row r="130" spans="1:13">
-      <c r="A130" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="B130" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="C130" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D130" s="12">
+      <c r="M134" s="6"/>
+    </row>
+    <row r="135" spans="1:13">
+      <c r="A135" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="B135" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D135" s="12">
+        <v>0.86</v>
+      </c>
+      <c r="M135" s="6"/>
+    </row>
+    <row r="136" spans="1:13">
+      <c r="A136" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="B136" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D136" s="12">
+        <v>0.68</v>
+      </c>
+      <c r="M136" s="6"/>
+    </row>
+    <row r="137" spans="1:13">
+      <c r="A137" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B137" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D137" s="12">
+        <v>0.73</v>
+      </c>
+      <c r="M137" s="6"/>
+    </row>
+    <row r="138" spans="1:13">
+      <c r="A138" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="B138" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D138" s="12">
         <v>0.9</v>
       </c>
-      <c r="M130" s="6"/>
-    </row>
-    <row r="131" spans="1:13">
-      <c r="A131" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="B131" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="C131" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D131" s="12">
+      <c r="M138" s="6"/>
+    </row>
+    <row r="139" spans="1:13">
+      <c r="A139" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B139" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D139" s="12">
         <v>0.87</v>
-      </c>
-      <c r="M131" s="6"/>
-    </row>
-    <row r="132" spans="1:13">
-      <c r="A132" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="B132" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="C132" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D132" s="12">
-        <v>0.88</v>
-      </c>
-      <c r="M132" s="6"/>
-    </row>
-    <row r="133" spans="1:13">
-      <c r="A133" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="B133" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="C133" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D133" s="12">
-        <v>0.77</v>
-      </c>
-      <c r="M133" s="6"/>
-    </row>
-    <row r="134" spans="1:13">
-      <c r="A134" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="B134" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="C134" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D134" s="12">
-        <v>0.86</v>
-      </c>
-      <c r="M134" s="6"/>
-    </row>
-    <row r="135" spans="1:13">
-      <c r="A135" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="B135" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="C135" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D135" s="12">
-        <v>0.68</v>
-      </c>
-      <c r="M135" s="6"/>
-    </row>
-    <row r="136" spans="1:13">
-      <c r="A136" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B136" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="C136" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D136" s="12">
-        <v>0.73</v>
-      </c>
-      <c r="M136" s="6"/>
-    </row>
-    <row r="137" spans="1:13">
-      <c r="A137" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="B137" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="C137" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D137" s="12">
-        <v>0.9</v>
-      </c>
-      <c r="M137" s="6"/>
-    </row>
-    <row r="138" spans="1:13">
-      <c r="A138" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="B138" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="C138" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D138" s="12">
-        <v>0.87</v>
-      </c>
-      <c r="M138" s="6"/>
-    </row>
-    <row r="139" spans="1:13">
-      <c r="A139" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="B139" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="C139" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D139" s="12">
-        <v>0.94</v>
       </c>
       <c r="M139" s="6"/>
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="12" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D140" s="12">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="M140" s="6"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="12" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D141" s="12">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="M141" s="6"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="12" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D142" s="12">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="M142" s="6"/>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="12" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D143" s="12">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="M143" s="6"/>
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D144" s="12">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="M144" s="6"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="12" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D145" s="12">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="M145" s="6"/>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="12" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D146" s="12">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="M146" s="6"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D147" s="12">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="M147" s="6"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="12" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D148" s="12">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="M148" s="6"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="12" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D149" s="12">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="M149" s="6"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="12" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D150" s="12">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="M150" s="6"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="12" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D151" s="12">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="M151" s="6"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="12" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D152" s="12">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="M152" s="6"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="12" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D153" s="12">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="M153" s="6"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="12" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D154" s="12">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="M154" s="6"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="12" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D155" s="12">
-        <v>0.94</v>
+        <v>0.88</v>
       </c>
       <c r="M155" s="6"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="12" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D156" s="12">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="M156" s="6"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="12" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D157" s="12">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="M157" s="6"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="12" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D158" s="12">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="M158" s="6"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="12" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D159" s="12">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="M159" s="6"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="12" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D160" s="12">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="M160" s="6"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="12" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D161" s="12">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="M161" s="6"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="12" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D162" s="12">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="12" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D163" s="12">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="12" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D164" s="12">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D165" s="12">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="M165" s="6"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="12" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D166" s="12">
-        <v>0.69</v>
+        <v>0.86</v>
       </c>
       <c r="M166" s="6"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="12" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D167" s="12">
-        <v>0.77</v>
+        <v>0.69</v>
       </c>
       <c r="M167" s="6"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="12" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D168" s="12">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="M168" s="6"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="12" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D169" s="12">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="M169" s="6"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="12" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C170" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D170" s="12">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="12" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D171" s="12">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="M171" s="6"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="12" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D172" s="12">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="M172" s="6"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D173" s="12">
+        <v>0.61</v>
+      </c>
+      <c r="M173" s="6"/>
+    </row>
+    <row r="174" spans="1:13">
+      <c r="A174" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B174" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="B173" s="12" t="s">
+      <c r="C174" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D174" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="M174" s="6"/>
+    </row>
+    <row r="175" spans="1:13">
+      <c r="A175" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="C173" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D173" s="12">
+      <c r="B175" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D175" s="12">
+        <v>0.87</v>
+      </c>
+      <c r="M175" s="6"/>
+    </row>
+    <row r="176" spans="1:13">
+      <c r="A176" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="B176" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D176" s="12">
+        <v>0.71</v>
+      </c>
+      <c r="M176" s="6"/>
+    </row>
+    <row r="177" spans="1:13">
+      <c r="A177" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="B177" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D177" s="12">
+        <v>0.92</v>
+      </c>
+      <c r="M177" s="6"/>
+    </row>
+    <row r="178" spans="1:13">
+      <c r="A178" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="B178" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D178" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="M178" s="6"/>
+    </row>
+    <row r="179" spans="1:13">
+      <c r="A179" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="B179" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="C179" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D179" s="12">
         <v>0.75</v>
       </c>
-      <c r="M173" s="6"/>
-    </row>
-    <row r="174" spans="1:13">
-      <c r="A174" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="B174" s="13" t="s">
+      <c r="M179" s="6"/>
+    </row>
+    <row r="180" spans="1:13">
+      <c r="A180" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="B180" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="C180" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="C174" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D174" s="12">
+      <c r="D180" s="12">
         <v>0.87</v>
       </c>
-      <c r="M174" s="6"/>
-    </row>
-    <row r="175" spans="1:13">
-      <c r="A175" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="B175" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="C175" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D175" s="12">
-        <v>0.71</v>
-      </c>
-      <c r="M175" s="6"/>
-    </row>
-    <row r="176" spans="1:13">
-      <c r="A176" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="B176" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C176" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D176" s="12">
-        <v>0.92</v>
-      </c>
-      <c r="M176" s="6"/>
-    </row>
-    <row r="177" spans="1:13">
-      <c r="A177" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="B177" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="C177" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D177" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="M177" s="6"/>
-    </row>
-    <row r="178" spans="1:13">
-      <c r="A178" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="B178" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="C178" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D178" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="M178" s="6"/>
-    </row>
-    <row r="179" spans="1:13">
-      <c r="A179" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="B179" s="13" t="s">
+      <c r="M180" s="6"/>
+    </row>
+    <row r="181" spans="1:13">
+      <c r="A181" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="C179" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D179" s="12">
-        <v>0.87</v>
-      </c>
-      <c r="M179" s="6"/>
-    </row>
-    <row r="180" spans="1:13">
-      <c r="A180" s="13" t="s">
+      <c r="B181" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="B180" s="13" t="s">
+      <c r="C181" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D181" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="M181" s="6"/>
+    </row>
+    <row r="182" spans="1:13">
+      <c r="A182" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="C180" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D180" s="12">
+      <c r="B182" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D182" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="M182" s="6"/>
+    </row>
+    <row r="183" spans="1:13">
+      <c r="A183" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="B183" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D183" s="12">
+        <v>0.64</v>
+      </c>
+      <c r="M183" s="6"/>
+    </row>
+    <row r="184" spans="1:13">
+      <c r="A184" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="B184" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D184" s="12">
+        <v>0.78</v>
+      </c>
+      <c r="M184" s="6"/>
+    </row>
+    <row r="185" spans="1:13">
+      <c r="A185" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="B185" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D185" s="12">
+        <v>0.91</v>
+      </c>
+      <c r="M185" s="6"/>
+    </row>
+    <row r="186" spans="1:13">
+      <c r="A186" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="B186" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D186" s="12">
         <v>0.81</v>
       </c>
-      <c r="M180" s="6"/>
-    </row>
-    <row r="181" spans="1:13">
-      <c r="A181" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="B181" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="C181" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D181" s="12">
-        <v>0.84</v>
-      </c>
-      <c r="M181" s="6"/>
-    </row>
-    <row r="182" spans="1:13">
-      <c r="A182" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="B182" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="C182" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D182" s="12">
-        <v>0.64</v>
-      </c>
-      <c r="M182" s="6"/>
-    </row>
-    <row r="183" spans="1:13">
-      <c r="A183" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="B183" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="C183" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D183" s="12">
-        <v>0.78</v>
-      </c>
-      <c r="M183" s="6"/>
-    </row>
-    <row r="184" spans="1:13">
-      <c r="A184" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="B184" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="C184" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D184" s="12">
-        <v>0.91</v>
-      </c>
-      <c r="M184" s="6"/>
-    </row>
-    <row r="185" spans="1:13">
-      <c r="A185" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="B185" s="13" t="s">
+      <c r="M186" s="6"/>
+    </row>
+    <row r="187" spans="1:13">
+      <c r="A187" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="C185" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D185" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="M185" s="6"/>
-    </row>
-    <row r="186" spans="1:13">
-      <c r="A186" s="13" t="s">
+      <c r="B187" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="B186" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D186" s="12">
-        <v>0.84</v>
-      </c>
-      <c r="M186" s="6"/>
-    </row>
-    <row r="187" spans="1:13">
-      <c r="A187" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="B187" s="13" t="s">
-        <v>387</v>
-      </c>
       <c r="C187" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D187" s="12">
         <v>0.84</v>
@@ -4819,488 +4832,498 @@
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
-      <c r="A188" s="13" t="s">
+      <c r="A188" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="B188" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D188" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="M188" s="6"/>
+    </row>
+    <row r="189" spans="1:13">
+      <c r="A189" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="B189" s="14" t="s">
         <v>388</v>
       </c>
-      <c r="B188" s="13" t="s">
+      <c r="C189" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D189" s="12">
+        <v>0.91</v>
+      </c>
+      <c r="M189" s="6"/>
+    </row>
+    <row r="190" spans="1:13">
+      <c r="A190" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="C188" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D188" s="12">
-        <v>0.91</v>
-      </c>
-      <c r="M188" s="6"/>
-    </row>
-    <row r="189" spans="1:13">
-      <c r="A189" s="13" t="s">
+      <c r="B190" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="B189" s="13" t="s">
+      <c r="C190" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D190" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="M190" s="6"/>
+    </row>
+    <row r="191" spans="1:13">
+      <c r="A191" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="C189" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D189" s="12">
-        <v>0.83</v>
-      </c>
-      <c r="M189" s="6"/>
-    </row>
-    <row r="190" spans="1:13">
-      <c r="A190" s="13" t="s">
+      <c r="B191" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="B190" s="13" t="s">
+      <c r="C191" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D191" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="M191" s="6"/>
+    </row>
+    <row r="192" spans="1:13">
+      <c r="A192" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="C190" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D190" s="12">
-        <v>0.84</v>
-      </c>
-      <c r="M190" s="6"/>
-    </row>
-    <row r="191" spans="1:13">
-      <c r="A191" s="13" t="s">
+      <c r="B192" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="B191" s="13" t="s">
+      <c r="C192" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D192" s="12">
+        <v>0.85</v>
+      </c>
+      <c r="M192" s="6"/>
+    </row>
+    <row r="193" spans="1:13">
+      <c r="A193" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="C191" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D191" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="M191" s="6"/>
-    </row>
-    <row r="192" spans="1:13">
-      <c r="A192" s="13" t="s">
+      <c r="B193" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="B192" s="13" t="s">
+      <c r="C193" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D193" s="12">
+        <v>0.88</v>
+      </c>
+      <c r="M193" s="6"/>
+    </row>
+    <row r="194" spans="1:13">
+      <c r="A194" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="C192" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D192" s="12">
-        <v>0.88</v>
-      </c>
-      <c r="M192" s="6"/>
-    </row>
-    <row r="193" spans="1:13">
-      <c r="A193" s="13" t="s">
+      <c r="B194" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="B193" s="13" t="s">
+      <c r="C194" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D194" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="M194" s="6"/>
+    </row>
+    <row r="195" spans="1:13">
+      <c r="A195" s="14" t="s">
         <v>399</v>
       </c>
-      <c r="C193" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D193" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="M193" s="6"/>
-    </row>
-    <row r="194" spans="1:13">
-      <c r="A194" s="13" t="s">
+      <c r="B195" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="B194" s="13" t="s">
+      <c r="C195" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D195" s="12">
+        <v>0.76</v>
+      </c>
+      <c r="M195" s="6"/>
+    </row>
+    <row r="196" spans="1:13">
+      <c r="A196" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="C194" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D194" s="12">
-        <v>0.76</v>
-      </c>
-      <c r="M194" s="6"/>
-    </row>
-    <row r="195" spans="1:13">
-      <c r="A195" s="13" t="s">
+      <c r="B196" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="B195" s="13" t="s">
+      <c r="C196" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D196" s="12">
+        <v>0.59</v>
+      </c>
+      <c r="M196" s="6"/>
+    </row>
+    <row r="197" spans="1:13">
+      <c r="A197" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="C195" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D195" s="12">
-        <v>0.59</v>
-      </c>
-      <c r="M195" s="6"/>
-    </row>
-    <row r="196" spans="1:13">
-      <c r="A196" s="13" t="s">
+      <c r="B197" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="B196" s="13" t="s">
+      <c r="C197" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D197" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="M197" s="6"/>
+    </row>
+    <row r="198" spans="1:13">
+      <c r="A198" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="C196" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D196" s="12">
+      <c r="B198" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="C198" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D198" s="12">
+        <v>0.77</v>
+      </c>
+      <c r="M198" s="6"/>
+    </row>
+    <row r="199" spans="1:13">
+      <c r="A199" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="B199" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="C199" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D199" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="M199" s="6"/>
+    </row>
+    <row r="200" spans="1:13">
+      <c r="A200" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="B200" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D200" s="12">
         <v>0.79</v>
       </c>
-      <c r="M196" s="6"/>
-    </row>
-    <row r="197" spans="1:13">
-      <c r="A197" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="B197" s="13" t="s">
-        <v>407</v>
-      </c>
-      <c r="C197" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D197" s="12">
-        <v>0.77</v>
-      </c>
-      <c r="M197" s="6"/>
-    </row>
-    <row r="198" spans="1:13">
-      <c r="A198" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="B198" s="13" t="s">
-        <v>409</v>
-      </c>
-      <c r="C198" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D198" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="M198" s="6"/>
-    </row>
-    <row r="199" spans="1:13">
-      <c r="A199" s="13" t="s">
-        <v>410</v>
-      </c>
-      <c r="B199" s="13" t="s">
+      <c r="M200" s="6"/>
+    </row>
+    <row r="201" spans="1:13">
+      <c r="A201" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="C199" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D199" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="M199" s="6"/>
-    </row>
-    <row r="200" spans="1:13">
-      <c r="A200" s="13" t="s">
+      <c r="B201" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="B200" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="C200" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D200" s="12">
+      <c r="C201" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D201" s="12">
         <v>0.74</v>
-      </c>
-      <c r="M200" s="6"/>
-    </row>
-    <row r="201" spans="1:13">
-      <c r="A201" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="B201" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="C201" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D201" s="12">
-        <v>0.62</v>
       </c>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D202" s="12">
+        <v>0.62</v>
+      </c>
+      <c r="M202" s="6"/>
+    </row>
+    <row r="203" spans="1:13">
+      <c r="A203" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="B203" s="12" t="s">
         <v>416</v>
       </c>
-      <c r="B202" s="12" t="s">
+      <c r="C203" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D203" s="12">
+        <v>0.94</v>
+      </c>
+      <c r="M203" s="6"/>
+    </row>
+    <row r="204" spans="1:13">
+      <c r="A204" s="14" t="s">
         <v>417</v>
       </c>
-      <c r="C202" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D202" s="12">
-        <v>0.94</v>
-      </c>
-      <c r="M202" s="6"/>
-    </row>
-    <row r="203" spans="1:13">
-      <c r="A203" s="13" t="s">
+      <c r="B204" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="B203" s="13" t="s">
+      <c r="C204" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="C203" s="12" t="s">
+      <c r="D204" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="M204" s="6"/>
+    </row>
+    <row r="205" spans="1:13">
+      <c r="A205" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="D203" s="12">
+      <c r="B205" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="C205" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="D205" s="12">
+        <v>0.61</v>
+      </c>
+      <c r="M205" s="6"/>
+    </row>
+    <row r="206" spans="1:13">
+      <c r="A206" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="B206" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="D206" s="12">
+        <v>0.69</v>
+      </c>
+      <c r="M206" s="6"/>
+    </row>
+    <row r="207" spans="1:13">
+      <c r="A207" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="B207" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="C207" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="D207" s="12">
+        <v>0.67</v>
+      </c>
+      <c r="M207" s="6"/>
+    </row>
+    <row r="208" spans="1:13">
+      <c r="A208" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="B208" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="C208" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="D208" s="12">
+        <v>0.71</v>
+      </c>
+      <c r="M208" s="6"/>
+    </row>
+    <row r="209" spans="1:13">
+      <c r="A209" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="B209" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="D209" s="12">
+        <v>0.89</v>
+      </c>
+      <c r="M209" s="6"/>
+    </row>
+    <row r="210" spans="1:13">
+      <c r="A210" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="B210" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D210" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="M210" s="6"/>
+    </row>
+    <row r="211" spans="1:13">
+      <c r="A211" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="B211" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D211" s="12">
+        <v>0.66</v>
+      </c>
+      <c r="M211" s="6"/>
+    </row>
+    <row r="212" spans="1:13">
+      <c r="A212" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="B212" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D212" s="12">
+        <v>0.69</v>
+      </c>
+      <c r="M212" s="6"/>
+    </row>
+    <row r="213" spans="1:13">
+      <c r="A213" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="B213" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D213" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="M213" s="6"/>
+    </row>
+    <row r="214" spans="1:13">
+      <c r="A214" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B214" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D214" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="M214" s="6"/>
+    </row>
+    <row r="215" spans="1:13">
+      <c r="A215" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B215" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D215" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="M215" s="6"/>
+    </row>
+    <row r="216" spans="1:13">
+      <c r="A216" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B216" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="C216" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D216" s="12">
+        <v>0.74</v>
+      </c>
+      <c r="M216" s="6"/>
+    </row>
+    <row r="217" spans="1:13">
+      <c r="A217" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B217" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D217" s="12">
         <v>0.75</v>
       </c>
-      <c r="M203" s="6"/>
-    </row>
-    <row r="204" spans="1:13">
-      <c r="A204" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="B204" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="C204" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="D204" s="12">
-        <v>0.61</v>
-      </c>
-      <c r="M204" s="6"/>
-    </row>
-    <row r="205" spans="1:13">
-      <c r="A205" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="B205" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="C205" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="D205" s="12">
-        <v>0.69</v>
-      </c>
-      <c r="M205" s="6"/>
-    </row>
-    <row r="206" spans="1:13">
-      <c r="A206" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="B206" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="C206" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="D206" s="12">
-        <v>0.67</v>
-      </c>
-      <c r="M206" s="6"/>
-    </row>
-    <row r="207" spans="1:13">
-      <c r="A207" s="13" t="s">
-        <v>427</v>
-      </c>
-      <c r="B207" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="C207" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="D207" s="12">
-        <v>0.71</v>
-      </c>
-      <c r="M207" s="6"/>
-    </row>
-    <row r="208" spans="1:13">
-      <c r="A208" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="B208" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="C208" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="D208" s="12">
-        <v>0.89</v>
-      </c>
-      <c r="M208" s="6"/>
-    </row>
-    <row r="209" spans="1:13">
-      <c r="A209" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="B209" s="13" t="s">
+      <c r="M217" s="6"/>
+    </row>
+    <row r="218" spans="1:13">
+      <c r="A218" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B218" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="C218" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="C209" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D209" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="M209" s="6"/>
-    </row>
-    <row r="210" spans="1:13">
-      <c r="A210" s="13" t="s">
-        <v>434</v>
-      </c>
-      <c r="B210" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="C210" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D210" s="12">
-        <v>0.66</v>
-      </c>
-      <c r="M210" s="6"/>
-    </row>
-    <row r="211" spans="1:13">
-      <c r="A211" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="B211" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="C211" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D211" s="12">
-        <v>0.69</v>
-      </c>
-      <c r="M211" s="6"/>
-    </row>
-    <row r="212" spans="1:13">
-      <c r="A212" s="13" t="s">
-        <v>438</v>
-      </c>
-      <c r="B212" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="C212" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D212" s="12">
-        <v>0.83</v>
-      </c>
-      <c r="M212" s="6"/>
-    </row>
-    <row r="213" spans="1:13">
-      <c r="A213" s="13" t="s">
-        <v>440</v>
-      </c>
-      <c r="B213" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="C213" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D213" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="M213" s="6"/>
-    </row>
-    <row r="214" spans="1:13">
-      <c r="A214" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="B214" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="C214" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D214" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="M214" s="6"/>
-    </row>
-    <row r="215" spans="1:13">
-      <c r="A215" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="B215" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="C215" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D215" s="12">
-        <v>0.74</v>
-      </c>
-      <c r="M215" s="6"/>
-    </row>
-    <row r="216" spans="1:13">
-      <c r="A216" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B216" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="C216" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D216" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="M216" s="6"/>
-    </row>
-    <row r="217" spans="1:13">
-      <c r="A217" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B217" s="13" t="s">
+      <c r="D218" s="12">
+        <v>0.65</v>
+      </c>
+      <c r="M218" s="6"/>
+    </row>
+    <row r="219" spans="1:13">
+      <c r="A219" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="C217" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D217" s="12">
-        <v>0.65</v>
-      </c>
-      <c r="M217" s="6"/>
-    </row>
-    <row r="218" spans="1:13">
-      <c r="A218" s="13" t="s">
+      <c r="B219" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="B218" s="13" t="s">
+      <c r="C219" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D219" s="12">
+        <v>0.87</v>
+      </c>
+      <c r="M219" s="6"/>
+    </row>
+    <row r="220" spans="1:13">
+      <c r="A220" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="C218" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D218" s="12">
-        <v>0.87</v>
-      </c>
-      <c r="M218" s="6"/>
-    </row>
-    <row r="219" spans="1:13">
-      <c r="A219" s="13" t="s">
+      <c r="B220" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="B219" s="13" t="s">
-        <v>451</v>
-      </c>
-      <c r="C219" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D219" s="12">
+      <c r="C220" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D220" s="12">
         <v>0.7</v>
       </c>
-      <c r="M219" s="6"/>
-    </row>
-    <row r="220" spans="1:13">
-      <c r="B220" s="2"/>
-      <c r="D220" s="4"/>
       <c r="M220" s="6"/>
     </row>
     <row r="221" spans="1:13">
@@ -5314,12 +5337,12 @@
       <c r="M222" s="6"/>
     </row>
     <row r="223" spans="1:13">
-      <c r="B223" s="2"/>
+      <c r="B223" s="3"/>
       <c r="D223" s="4"/>
       <c r="M223" s="6"/>
     </row>
     <row r="224" spans="1:13">
-      <c r="B224" s="3"/>
+      <c r="B224" s="2"/>
       <c r="D224" s="4"/>
       <c r="M224" s="6"/>
     </row>
@@ -5334,7 +5357,7 @@
       <c r="M226" s="6"/>
     </row>
     <row r="227" spans="2:13">
-      <c r="B227" s="2"/>
+      <c r="B227" s="3"/>
       <c r="D227" s="4"/>
       <c r="M227" s="6"/>
     </row>
@@ -5342,11 +5365,6 @@
       <c r="B228" s="3"/>
       <c r="D228" s="4"/>
       <c r="M228" s="6"/>
-    </row>
-    <row r="229" spans="2:13">
-      <c r="B229" s="3"/>
-      <c r="D229" s="4"/>
-      <c r="M229" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523A4904-1125-124B-9995-AA0DD874FE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA1A86E-352E-2748-8938-2085262C1E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4649,6 +4649,9 @@
       <c r="D175" s="12">
         <v>0.87</v>
       </c>
+      <c r="G175">
+        <v>0.26</v>
+      </c>
       <c r="M175" s="6"/>
     </row>
     <row r="176" spans="1:13">
@@ -4664,6 +4667,9 @@
       <c r="D176" s="12">
         <v>0.71</v>
       </c>
+      <c r="G176">
+        <v>0.35</v>
+      </c>
       <c r="M176" s="6"/>
     </row>
     <row r="177" spans="1:13">
@@ -4679,6 +4685,9 @@
       <c r="D177" s="12">
         <v>0.92</v>
       </c>
+      <c r="G177">
+        <v>0.63</v>
+      </c>
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
@@ -4694,6 +4703,9 @@
       <c r="D178" s="12">
         <v>0.8</v>
       </c>
+      <c r="G178">
+        <v>0.39</v>
+      </c>
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
@@ -4709,6 +4721,9 @@
       <c r="D179" s="12">
         <v>0.75</v>
       </c>
+      <c r="G179">
+        <v>0.68</v>
+      </c>
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
@@ -4724,6 +4739,9 @@
       <c r="D180" s="12">
         <v>0.87</v>
       </c>
+      <c r="G180">
+        <v>0.42</v>
+      </c>
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13">
@@ -4739,6 +4757,9 @@
       <c r="D181" s="12">
         <v>0.81</v>
       </c>
+      <c r="G181">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13">
@@ -4754,6 +4775,9 @@
       <c r="D182" s="12">
         <v>0.84</v>
       </c>
+      <c r="G182">
+        <v>0.6</v>
+      </c>
       <c r="M182" s="6"/>
     </row>
     <row r="183" spans="1:13">
@@ -4769,6 +4793,9 @@
       <c r="D183" s="12">
         <v>0.64</v>
       </c>
+      <c r="G183">
+        <v>0.04</v>
+      </c>
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13">
@@ -4784,6 +4811,9 @@
       <c r="D184" s="12">
         <v>0.78</v>
       </c>
+      <c r="G184">
+        <v>0.54</v>
+      </c>
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13">
@@ -4799,6 +4829,9 @@
       <c r="D185" s="12">
         <v>0.91</v>
       </c>
+      <c r="G185">
+        <v>0.51</v>
+      </c>
       <c r="M185" s="6"/>
     </row>
     <row r="186" spans="1:13">
@@ -4814,6 +4847,9 @@
       <c r="D186" s="12">
         <v>0.81</v>
       </c>
+      <c r="G186">
+        <v>0.46</v>
+      </c>
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13">
@@ -4829,6 +4865,9 @@
       <c r="D187" s="12">
         <v>0.84</v>
       </c>
+      <c r="G187">
+        <v>0.67</v>
+      </c>
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
@@ -4844,6 +4883,9 @@
       <c r="D188" s="12">
         <v>0.84</v>
       </c>
+      <c r="G188">
+        <v>0.67</v>
+      </c>
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
@@ -4859,6 +4901,9 @@
       <c r="D189" s="12">
         <v>0.91</v>
       </c>
+      <c r="G189">
+        <v>0.37</v>
+      </c>
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
@@ -4874,6 +4919,9 @@
       <c r="D190" s="12">
         <v>0.83</v>
       </c>
+      <c r="G190">
+        <v>0.6</v>
+      </c>
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13">
@@ -4889,6 +4937,9 @@
       <c r="D191" s="12">
         <v>0.84</v>
       </c>
+      <c r="G191">
+        <v>0.32</v>
+      </c>
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
@@ -4904,6 +4955,9 @@
       <c r="D192" s="12">
         <v>0.85</v>
       </c>
+      <c r="G192">
+        <v>0.37</v>
+      </c>
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13">
@@ -4919,6 +4973,9 @@
       <c r="D193" s="12">
         <v>0.88</v>
       </c>
+      <c r="G193">
+        <v>0.3</v>
+      </c>
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13">
@@ -4934,6 +4991,9 @@
       <c r="D194" s="12">
         <v>0.82</v>
       </c>
+      <c r="G194">
+        <v>0.42</v>
+      </c>
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13">
@@ -4949,6 +5009,9 @@
       <c r="D195" s="12">
         <v>0.76</v>
       </c>
+      <c r="G195">
+        <v>0.39</v>
+      </c>
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13">
@@ -4964,6 +5027,9 @@
       <c r="D196" s="12">
         <v>0.59</v>
       </c>
+      <c r="G196">
+        <v>0.65</v>
+      </c>
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
@@ -4979,6 +5045,9 @@
       <c r="D197" s="12">
         <v>0.79</v>
       </c>
+      <c r="G197">
+        <v>0.44</v>
+      </c>
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
@@ -4994,6 +5063,9 @@
       <c r="D198" s="12">
         <v>0.77</v>
       </c>
+      <c r="G198">
+        <v>0.75</v>
+      </c>
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
@@ -5009,6 +5081,9 @@
       <c r="D199" s="12">
         <v>0.75</v>
       </c>
+      <c r="G199">
+        <v>0.53</v>
+      </c>
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:13">
@@ -5024,6 +5099,9 @@
       <c r="D200" s="12">
         <v>0.79</v>
       </c>
+      <c r="G200">
+        <v>0.32</v>
+      </c>
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
@@ -5039,6 +5117,9 @@
       <c r="D201" s="12">
         <v>0.74</v>
       </c>
+      <c r="G201">
+        <v>0.68</v>
+      </c>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
@@ -5054,6 +5135,9 @@
       <c r="D202" s="12">
         <v>0.62</v>
       </c>
+      <c r="G202">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M202" s="6"/>
     </row>
     <row r="203" spans="1:13">
@@ -5068,6 +5152,9 @@
       </c>
       <c r="D203" s="12">
         <v>0.94</v>
+      </c>
+      <c r="G203">
+        <v>0.65</v>
       </c>
       <c r="M203" s="6"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA1A86E-352E-2748-8938-2085262C1E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED1862B-92AF-744D-8745-4E4B1D63E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="464">
   <si>
     <t>Surname</t>
   </si>
@@ -1398,6 +1398,36 @@
   </si>
   <si>
     <t>majoni</t>
+  </si>
+  <si>
+    <t>Magaiza</t>
+  </si>
+  <si>
+    <t>H250789G</t>
+  </si>
+  <si>
+    <t>Nyamugafata</t>
+  </si>
+  <si>
+    <t>H221238E</t>
+  </si>
+  <si>
+    <t>Chimwedzi</t>
+  </si>
+  <si>
+    <t>H250360Z</t>
+  </si>
+  <si>
+    <t>Rwakuda</t>
+  </si>
+  <si>
+    <t>H250658M</t>
+  </si>
+  <si>
+    <t>Munyaradzi</t>
+  </si>
+  <si>
+    <t>H250797T</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1566,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1558,6 +1588,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4655,443 +4687,443 @@
       <c r="M175" s="6"/>
     </row>
     <row r="176" spans="1:13">
-      <c r="A176" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="B176" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="C176" s="12" t="s">
+      <c r="A176" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="B176" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="C176" t="s">
         <v>360</v>
       </c>
-      <c r="D176" s="12">
-        <v>0.71</v>
+      <c r="D176" s="4">
+        <v>0</v>
       </c>
       <c r="G176">
-        <v>0.35</v>
+        <v>0.19</v>
       </c>
       <c r="M176" s="6"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="14" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B177" s="14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C177" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D177" s="12">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="G177">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="14" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D178" s="12">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="G178">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B179" s="14" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C179" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D179" s="12">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G179">
-        <v>0.68</v>
+        <v>0.39</v>
       </c>
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="14" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C180" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D180" s="12">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="G180">
-        <v>0.42</v>
+        <v>0.68</v>
       </c>
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="14" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B181" s="14" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C181" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D181" s="12">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="G181">
-        <v>0.57999999999999996</v>
+        <v>0.42</v>
       </c>
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="14" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B182" s="14" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C182" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D182" s="12">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="G182">
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M182" s="6"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="14" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B183" s="14" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C183" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D183" s="12">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="G183">
-        <v>0.04</v>
+        <v>0.6</v>
       </c>
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="14" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B184" s="14" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C184" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D184" s="12">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="G184">
-        <v>0.54</v>
+        <v>0.04</v>
       </c>
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13">
-      <c r="A185" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="B185" s="14" t="s">
-        <v>380</v>
-      </c>
-      <c r="C185" s="12" t="s">
+      <c r="A185" t="s">
+        <v>454</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C185" t="s">
         <v>360</v>
       </c>
-      <c r="D185" s="12">
-        <v>0.91</v>
+      <c r="D185" s="4">
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="M185" s="6"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="14" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B186" s="14" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C186" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D186" s="12">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="G186">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="14" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B187" s="14" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C187" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D187" s="12">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="G187">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="14" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B188" s="14" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C188" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D188" s="12">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="G188">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="14" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B189" s="14" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C189" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D189" s="12">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="G189">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="14" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B190" s="14" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C190" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D190" s="12">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="G190">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="14" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B191" s="14" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C191" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D191" s="12">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="G191">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="14" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B192" s="14" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C192" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D192" s="12">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="G192">
-        <v>0.37</v>
+        <v>0.6</v>
       </c>
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="14" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B193" s="14" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C193" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D193" s="12">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="G193">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="14" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B194" s="14" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C194" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D194" s="12">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="G194">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13">
-      <c r="A195" s="14" t="s">
-        <v>399</v>
-      </c>
-      <c r="B195" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="C195" s="12" t="s">
+      <c r="A195" t="s">
+        <v>462</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C195" t="s">
         <v>360</v>
       </c>
-      <c r="D195" s="12">
-        <v>0.76</v>
+      <c r="D195" s="4">
+        <v>0</v>
       </c>
       <c r="G195">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="14" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B196" s="14" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C196" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D196" s="12">
-        <v>0.59</v>
+        <v>0.88</v>
       </c>
       <c r="G196">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="14" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B197" s="14" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C197" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D197" s="12">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="G197">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="14" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B198" s="14" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C198" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D198" s="12">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="G198">
-        <v>0.75</v>
+        <v>0.39</v>
       </c>
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="14" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B199" s="14" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D199" s="12">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="G199">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="14" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B200" s="14" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C200" s="12" t="s">
         <v>360</v>
@@ -5100,355 +5132,420 @@
         <v>0.79</v>
       </c>
       <c r="G200">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="14" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B201" s="14" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C201" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D201" s="12">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="G201">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
-      <c r="A202" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="B202" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="C202" s="12" t="s">
+      <c r="A202" t="s">
+        <v>456</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C202" t="s">
         <v>360</v>
       </c>
-      <c r="D202" s="12">
-        <v>0.62</v>
+      <c r="D202" s="4">
+        <v>0</v>
       </c>
       <c r="G202">
-        <v>0.56000000000000005</v>
+        <v>0.05</v>
       </c>
       <c r="M202" s="6"/>
     </row>
     <row r="203" spans="1:13">
-      <c r="A203" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="B203" s="12" t="s">
-        <v>416</v>
+      <c r="A203" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="B203" s="14" t="s">
+        <v>408</v>
       </c>
       <c r="C203" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D203" s="12">
-        <v>0.94</v>
+        <v>0.75</v>
       </c>
       <c r="G203">
-        <v>0.65</v>
+        <v>0.53</v>
       </c>
       <c r="M203" s="6"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="14" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B204" s="14" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>419</v>
+        <v>360</v>
       </c>
       <c r="D204" s="12">
-        <v>0.75</v>
+        <v>0.79</v>
+      </c>
+      <c r="G204">
+        <v>0.32</v>
       </c>
       <c r="M204" s="6"/>
     </row>
     <row r="205" spans="1:13">
-      <c r="A205" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="B205" s="14" t="s">
-        <v>421</v>
-      </c>
-      <c r="C205" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="D205" s="12">
-        <v>0.61</v>
+      <c r="A205" t="s">
+        <v>460</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C205" t="s">
+        <v>360</v>
+      </c>
+      <c r="D205" s="4">
+        <v>0</v>
+      </c>
+      <c r="G205">
+        <v>0.44</v>
       </c>
       <c r="M205" s="6"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="14" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="B206" s="14" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>419</v>
+        <v>360</v>
       </c>
       <c r="D206" s="12">
-        <v>0.69</v>
+        <v>0.74</v>
+      </c>
+      <c r="G206">
+        <v>0.68</v>
       </c>
       <c r="M206" s="6"/>
     </row>
     <row r="207" spans="1:13">
-      <c r="A207" s="14" t="s">
-        <v>424</v>
-      </c>
-      <c r="B207" s="14" t="s">
-        <v>425</v>
+      <c r="A207" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B207" s="12" t="s">
+        <v>414</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>419</v>
+        <v>360</v>
       </c>
       <c r="D207" s="12">
-        <v>0.67</v>
+        <v>0.62</v>
+      </c>
+      <c r="G207">
+        <v>0.56000000000000005</v>
       </c>
       <c r="M207" s="6"/>
     </row>
     <row r="208" spans="1:13">
-      <c r="A208" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="B208" s="14" t="s">
-        <v>427</v>
+      <c r="A208" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="B208" s="12" t="s">
+        <v>416</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>419</v>
+        <v>360</v>
       </c>
       <c r="D208" s="12">
-        <v>0.71</v>
+        <v>0.94</v>
+      </c>
+      <c r="G208">
+        <v>0.65</v>
       </c>
       <c r="M208" s="6"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="14" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B209" s="14" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="C209" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D209" s="12">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
       <c r="M209" s="6"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="14" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B210" s="14" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D210" s="12">
-        <v>0.79</v>
+        <v>0.61</v>
       </c>
       <c r="M210" s="6"/>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="14" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B211" s="14" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="C211" s="12" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D211" s="12">
-        <v>0.66</v>
+        <v>0.69</v>
       </c>
       <c r="M211" s="6"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="14" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="B212" s="14" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D212" s="12">
-        <v>0.69</v>
+        <v>0.67</v>
       </c>
       <c r="M212" s="6"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="14" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="B213" s="14" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D213" s="12">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M213" s="6"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="14" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="B214" s="14" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D214" s="12">
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
       <c r="M214" s="6"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="14" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="B215" s="14" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C215" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D215" s="12">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="M215" s="6"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="14" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="B216" s="14" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C216" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D216" s="12">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="M216" s="6"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="14" t="s">
-        <v>32</v>
+        <v>435</v>
       </c>
       <c r="B217" s="14" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="C217" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D217" s="12">
-        <v>0.75</v>
+        <v>0.69</v>
       </c>
       <c r="M217" s="6"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="14" t="s">
-        <v>32</v>
+        <v>437</v>
       </c>
       <c r="B218" s="14" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C218" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D218" s="12">
-        <v>0.65</v>
+        <v>0.83</v>
       </c>
       <c r="M218" s="6"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="14" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="B219" s="14" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C219" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D219" s="12">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="M219" s="6"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="14" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="B220" s="14" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C220" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D220" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="M220" s="6"/>
+    </row>
+    <row r="221" spans="1:13">
+      <c r="A221" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B221" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D221" s="12">
+        <v>0.74</v>
+      </c>
+      <c r="M221" s="6"/>
+    </row>
+    <row r="222" spans="1:13">
+      <c r="A222" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B222" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D222" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="M222" s="6"/>
+    </row>
+    <row r="223" spans="1:13">
+      <c r="A223" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B223" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D223" s="12">
+        <v>0.65</v>
+      </c>
+      <c r="M223" s="6"/>
+    </row>
+    <row r="224" spans="1:13">
+      <c r="A224" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="B224" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D224" s="12">
+        <v>0.87</v>
+      </c>
+      <c r="M224" s="6"/>
+    </row>
+    <row r="225" spans="1:13">
+      <c r="A225" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="B225" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="C225" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D225" s="12">
         <v>0.7</v>
       </c>
-      <c r="M220" s="6"/>
-    </row>
-    <row r="221" spans="1:13">
-      <c r="B221" s="2"/>
-      <c r="D221" s="4"/>
-      <c r="M221" s="6"/>
-    </row>
-    <row r="222" spans="1:13">
-      <c r="B222" s="2"/>
-      <c r="D222" s="4"/>
-      <c r="M222" s="6"/>
-    </row>
-    <row r="223" spans="1:13">
-      <c r="B223" s="3"/>
-      <c r="D223" s="4"/>
-      <c r="M223" s="6"/>
-    </row>
-    <row r="224" spans="1:13">
-      <c r="B224" s="2"/>
-      <c r="D224" s="4"/>
-      <c r="M224" s="6"/>
-    </row>
-    <row r="225" spans="2:13">
-      <c r="B225" s="2"/>
-      <c r="D225" s="4"/>
       <c r="M225" s="6"/>
     </row>
-    <row r="226" spans="2:13">
+    <row r="226" spans="1:13">
       <c r="B226" s="2"/>
       <c r="D226" s="4"/>
       <c r="M226" s="6"/>
     </row>
-    <row r="227" spans="2:13">
+    <row r="227" spans="1:13">
       <c r="B227" s="3"/>
       <c r="D227" s="4"/>
       <c r="M227" s="6"/>
     </row>
-    <row r="228" spans="2:13">
+    <row r="228" spans="1:13">
       <c r="B228" s="3"/>
       <c r="D228" s="4"/>
       <c r="M228" s="6"/>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED1862B-92AF-744D-8745-4E4B1D63E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7266F53D-5347-A049-B22A-8C98C3B26CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2754,6 +2754,9 @@
       <c r="D47" s="12">
         <v>0.79</v>
       </c>
+      <c r="G47">
+        <v>0.68</v>
+      </c>
       <c r="H47" s="5"/>
       <c r="M47" s="6"/>
     </row>
@@ -2786,6 +2789,9 @@
       <c r="D49" s="12">
         <v>0.9</v>
       </c>
+      <c r="G49">
+        <v>0.6</v>
+      </c>
       <c r="H49" s="5"/>
       <c r="M49" s="6"/>
     </row>
@@ -2866,6 +2872,9 @@
       <c r="D54" s="12">
         <v>0.75</v>
       </c>
+      <c r="G54">
+        <v>0.32</v>
+      </c>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
@@ -2896,6 +2905,9 @@
       <c r="D56" s="12">
         <v>0.71</v>
       </c>
+      <c r="G56">
+        <v>0.32</v>
+      </c>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
@@ -2911,6 +2923,9 @@
       <c r="D57" s="12">
         <v>0.9</v>
       </c>
+      <c r="G57">
+        <v>0.81</v>
+      </c>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
@@ -2941,6 +2956,9 @@
       <c r="D59" s="12">
         <v>0.82</v>
       </c>
+      <c r="G59">
+        <v>0.46</v>
+      </c>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
@@ -2956,6 +2974,9 @@
       <c r="D60" s="12">
         <v>0.75</v>
       </c>
+      <c r="G60">
+        <v>0.37</v>
+      </c>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
@@ -3016,6 +3037,9 @@
       <c r="D64" s="12">
         <v>0.76</v>
       </c>
+      <c r="G64">
+        <v>0.35</v>
+      </c>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
@@ -3031,6 +3055,9 @@
       <c r="D65" s="12">
         <v>0.88</v>
       </c>
+      <c r="G65">
+        <v>0.77</v>
+      </c>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
@@ -3046,6 +3073,9 @@
       <c r="D66" s="12">
         <v>0.85</v>
       </c>
+      <c r="G66">
+        <v>0.6</v>
+      </c>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
@@ -3061,6 +3091,9 @@
       <c r="D67" s="12">
         <v>0.82</v>
       </c>
+      <c r="G67">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
@@ -3076,6 +3109,9 @@
       <c r="D68" s="12">
         <v>0.78</v>
       </c>
+      <c r="G68">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
@@ -3136,6 +3172,9 @@
       <c r="D72" s="12">
         <v>0.84</v>
       </c>
+      <c r="G72">
+        <v>0.51</v>
+      </c>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
@@ -3166,6 +3205,9 @@
       <c r="D74" s="12">
         <v>0.89</v>
       </c>
+      <c r="G74">
+        <v>0.61</v>
+      </c>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
@@ -3181,6 +3223,9 @@
       <c r="D75" s="12">
         <v>0.88</v>
       </c>
+      <c r="G75">
+        <v>0.74</v>
+      </c>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
@@ -3196,6 +3241,9 @@
       <c r="D76" s="12">
         <v>0.68</v>
       </c>
+      <c r="G76">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
@@ -3211,6 +3259,9 @@
       <c r="D77" s="12">
         <v>0.78</v>
       </c>
+      <c r="G77">
+        <v>0.61</v>
+      </c>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
@@ -3226,6 +3277,9 @@
       <c r="D78" s="12">
         <v>0.84</v>
       </c>
+      <c r="G78">
+        <v>0.47</v>
+      </c>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
@@ -3241,6 +3295,9 @@
       <c r="D79" s="12">
         <v>0.84</v>
       </c>
+      <c r="G79">
+        <v>0.65</v>
+      </c>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
@@ -3286,6 +3343,9 @@
       <c r="D82" s="12">
         <v>0.71</v>
       </c>
+      <c r="G82">
+        <v>0.63</v>
+      </c>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
@@ -3300,6 +3360,9 @@
       </c>
       <c r="D83" s="12">
         <v>0.76</v>
+      </c>
+      <c r="G83">
+        <v>0.61</v>
       </c>
       <c r="M83" s="6"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7266F53D-5347-A049-B22A-8C98C3B26CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6530DCCA-7E51-FE4B-AC71-BA1DDD679F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="465">
   <si>
     <t>Surname</t>
   </si>
@@ -1428,6 +1428,9 @@
   </si>
   <si>
     <t>H250797T</t>
+  </si>
+  <si>
+    <t>H250361E</t>
   </si>
 </sst>
 </file>
@@ -2037,6 +2040,9 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="H2" s="5"/>
+      <c r="J2">
+        <v>0.48</v>
+      </c>
       <c r="M2" s="6"/>
     </row>
     <row r="3" spans="1:13">
@@ -2069,6 +2075,9 @@
         <v>0.79</v>
       </c>
       <c r="H4" s="5"/>
+      <c r="J4">
+        <v>0.48</v>
+      </c>
       <c r="M4" s="6"/>
     </row>
     <row r="5" spans="1:13">
@@ -2085,6 +2094,9 @@
         <v>0.75</v>
       </c>
       <c r="H5" s="5"/>
+      <c r="J5">
+        <v>0.48</v>
+      </c>
       <c r="M5" s="6"/>
     </row>
     <row r="6" spans="1:13">
@@ -2101,6 +2113,9 @@
         <v>0.64</v>
       </c>
       <c r="H6" s="5"/>
+      <c r="J6">
+        <v>0.48</v>
+      </c>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13">
@@ -2165,6 +2180,9 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="H10" s="5"/>
+      <c r="J10">
+        <v>0.48</v>
+      </c>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13">
@@ -2213,6 +2231,9 @@
         <v>0.79</v>
       </c>
       <c r="H13" s="5"/>
+      <c r="J13">
+        <v>0.48</v>
+      </c>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13">
@@ -2245,6 +2266,9 @@
         <v>0.74</v>
       </c>
       <c r="H15" s="5"/>
+      <c r="J15">
+        <v>0.48</v>
+      </c>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13">
@@ -2293,6 +2317,9 @@
         <v>0.72</v>
       </c>
       <c r="H18" s="5"/>
+      <c r="J18">
+        <v>0.48</v>
+      </c>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
@@ -2325,6 +2352,9 @@
         <v>0.85</v>
       </c>
       <c r="H20" s="5"/>
+      <c r="J20">
+        <v>0.48</v>
+      </c>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13">
@@ -2389,6 +2419,9 @@
         <v>0.74</v>
       </c>
       <c r="H24" s="5"/>
+      <c r="J24">
+        <v>0.48</v>
+      </c>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
@@ -2421,6 +2454,9 @@
         <v>0.85</v>
       </c>
       <c r="H26" s="5"/>
+      <c r="J26">
+        <v>0.48</v>
+      </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
@@ -2453,6 +2489,9 @@
         <v>0.77</v>
       </c>
       <c r="H28" s="5"/>
+      <c r="J28">
+        <v>0.48</v>
+      </c>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
@@ -2773,6 +2812,9 @@
       <c r="D48" s="12">
         <v>0.89</v>
       </c>
+      <c r="G48">
+        <v>0.75</v>
+      </c>
       <c r="H48" s="5"/>
       <c r="M48" s="6"/>
     </row>
@@ -2808,6 +2850,9 @@
       <c r="D50" s="12">
         <v>0.85</v>
       </c>
+      <c r="G50">
+        <v>0.54</v>
+      </c>
       <c r="H50" s="5"/>
       <c r="M50" s="6"/>
     </row>
@@ -2824,6 +2869,9 @@
       <c r="D51" s="12">
         <v>0.85</v>
       </c>
+      <c r="G51">
+        <v>0.6</v>
+      </c>
       <c r="H51" s="5"/>
       <c r="M51" s="6"/>
     </row>
@@ -2840,6 +2888,9 @@
       <c r="D52" s="12">
         <v>0.77</v>
       </c>
+      <c r="G52">
+        <v>0.33</v>
+      </c>
       <c r="H52" s="5"/>
       <c r="M52" s="6"/>
     </row>
@@ -2856,6 +2907,9 @@
       <c r="D53" s="12">
         <v>0.86</v>
       </c>
+      <c r="G53">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="H53" s="5"/>
       <c r="M53" s="6"/>
     </row>
@@ -2890,6 +2944,9 @@
       <c r="D55" s="12">
         <v>0.69</v>
       </c>
+      <c r="G55">
+        <v>0.51</v>
+      </c>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
@@ -2941,6 +2998,9 @@
       <c r="D58" s="12">
         <v>0.91</v>
       </c>
+      <c r="G58">
+        <v>0.46</v>
+      </c>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
@@ -2992,6 +3052,9 @@
       <c r="D61" s="12">
         <v>0.76</v>
       </c>
+      <c r="G61">
+        <v>0.63</v>
+      </c>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
@@ -3007,6 +3070,9 @@
       <c r="D62" s="12">
         <v>0.72</v>
       </c>
+      <c r="G62">
+        <v>0.37</v>
+      </c>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
@@ -3022,6 +3088,9 @@
       <c r="D63" s="12">
         <v>0.86</v>
       </c>
+      <c r="G63">
+        <v>0.53</v>
+      </c>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
@@ -3127,6 +3196,9 @@
       <c r="D69" s="12">
         <v>0.7</v>
       </c>
+      <c r="G69">
+        <v>0.35</v>
+      </c>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
@@ -3142,6 +3214,9 @@
       <c r="D70" s="12">
         <v>0.83</v>
       </c>
+      <c r="G70">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
@@ -3157,6 +3232,9 @@
       <c r="D71" s="12">
         <v>0.84</v>
       </c>
+      <c r="G71">
+        <v>0.77</v>
+      </c>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
@@ -3190,6 +3268,9 @@
       <c r="D73" s="12">
         <v>0.75</v>
       </c>
+      <c r="G73">
+        <v>0.05</v>
+      </c>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
@@ -3313,125 +3394,143 @@
       <c r="D80" s="12">
         <v>0.74</v>
       </c>
+      <c r="G80">
+        <v>0.39</v>
+      </c>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
-      <c r="A81" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="C81" s="12" t="s">
+      <c r="A81" t="s">
+        <v>344</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C81" t="s">
         <v>104</v>
       </c>
-      <c r="D81" s="12">
-        <v>0.81</v>
+      <c r="D81" s="4">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>0.54</v>
       </c>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>104</v>
       </c>
       <c r="D82" s="12">
-        <v>0.71</v>
+        <v>0.81</v>
       </c>
       <c r="G82">
-        <v>0.63</v>
+        <v>0.79</v>
       </c>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>104</v>
       </c>
       <c r="D83" s="12">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="G83">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>104</v>
       </c>
       <c r="D84" s="12">
-        <v>0.81</v>
+        <v>0.76</v>
+      </c>
+      <c r="G84">
+        <v>0.61</v>
       </c>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>104</v>
       </c>
       <c r="D85" s="12">
-        <v>0.83</v>
+        <v>0.81</v>
+      </c>
+      <c r="G85">
+        <v>0.25</v>
       </c>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>104</v>
       </c>
       <c r="D86" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="G86">
+        <v>0.6</v>
+      </c>
+      <c r="M86" s="6"/>
+    </row>
+    <row r="87" spans="1:13">
+      <c r="A87" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D87" s="12">
         <v>0.85</v>
       </c>
-      <c r="M86" s="6"/>
-    </row>
-    <row r="87" spans="1:13">
-      <c r="A87" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="D87" s="12">
-        <v>0.75</v>
+      <c r="G87">
+        <v>0.54</v>
       </c>
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="14" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C88" s="12" t="s">
         <v>185</v>
@@ -3443,346 +3542,346 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C89" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D89" s="12">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C90" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D90" s="12">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C91" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D91" s="12">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C92" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D92" s="12">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C93" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D93" s="12">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
-      <c r="A94" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B94" s="12" t="s">
-        <v>199</v>
+      <c r="A94" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>197</v>
       </c>
       <c r="C94" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D94" s="12">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D95" s="12">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C96" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D96" s="12">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D97" s="12">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D98" s="12">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C99" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D99" s="12">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D100" s="12">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D101" s="12">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C102" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D102" s="12">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C103" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D103" s="12">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C104" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D104" s="12">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D105" s="12">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D106" s="12">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C107" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D107" s="12">
-        <v>0.94</v>
+        <v>0.83</v>
       </c>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D108" s="12">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D109" s="12">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D110" s="12">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D111" s="12">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="M111" s="6"/>
     </row>
@@ -3791,1222 +3890,1219 @@
         <v>232</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D112" s="12">
-        <v>0.92</v>
+        <v>0.66</v>
       </c>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D113" s="12">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C114" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D114" s="12">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C115" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D115" s="12">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D116" s="12">
-        <v>0.69</v>
+        <v>0.96</v>
       </c>
       <c r="M116" s="6"/>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C117" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D117" s="12">
-        <v>0.78</v>
+        <v>0.69</v>
       </c>
       <c r="M117" s="6"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C118" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D118" s="12">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M118" s="6"/>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C119" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D119" s="12">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="M119" s="6"/>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C120" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D120" s="12">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="M120" s="6"/>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C121" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D121" s="12">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="M121" s="6"/>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C122" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D122" s="12">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="M122" s="6"/>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C123" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D123" s="12">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="M123" s="6"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D124" s="12">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="M124" s="6"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="12" t="s">
-        <v>25</v>
+        <v>257</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D125" s="12">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="M125" s="6"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="12" t="s">
-        <v>260</v>
+        <v>25</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D126" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="M126" s="6"/>
+    </row>
+    <row r="127" spans="1:13">
+      <c r="A127" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D127" s="12">
         <v>0.75</v>
-      </c>
-      <c r="M126" s="6"/>
-    </row>
-    <row r="127" spans="1:13">
-      <c r="A127" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B127" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="C127" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="D127" s="12">
-        <v>0.78</v>
       </c>
       <c r="M127" s="6"/>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="14" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B128" s="14" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D128" s="12">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="M128" s="6"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B129" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C129" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D129" s="12">
-        <v>0.93</v>
+        <v>0.81</v>
       </c>
       <c r="M129" s="6"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B130" s="14" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C130" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D130" s="12">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="M130" s="6"/>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="14" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B131" s="14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C131" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D131" s="12">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="M131" s="6"/>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C132" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D132" s="12">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="M132" s="6"/>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="14" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B133" s="14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C133" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D133" s="12">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="M133" s="6"/>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="14" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B134" s="14" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C134" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D134" s="12">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="M134" s="6"/>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B135" s="14" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C135" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D135" s="12">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="M135" s="6"/>
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="14" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B136" s="14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C136" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D136" s="12">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="M136" s="6"/>
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="14" t="s">
-        <v>117</v>
+        <v>281</v>
       </c>
       <c r="B137" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C137" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D137" s="12">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="M137" s="6"/>
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="14" t="s">
-        <v>284</v>
+        <v>117</v>
       </c>
       <c r="B138" s="14" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C138" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D138" s="12">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="M138" s="6"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="14" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B139" s="14" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C139" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D139" s="12">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="M139" s="6"/>
     </row>
     <row r="140" spans="1:13">
-      <c r="A140" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="B140" s="12" t="s">
-        <v>289</v>
+      <c r="A140" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B140" s="14" t="s">
+        <v>287</v>
       </c>
       <c r="C140" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D140" s="12">
-        <v>0.94</v>
+        <v>0.87</v>
       </c>
       <c r="M140" s="6"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C141" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D141" s="12">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="M141" s="6"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C142" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D142" s="12">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="M142" s="6"/>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C143" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D143" s="12">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="M143" s="6"/>
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D144" s="12">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="M144" s="6"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D145" s="12">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="M145" s="6"/>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C146" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D146" s="12">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="M146" s="6"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C147" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D147" s="12">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="M147" s="6"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C148" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D148" s="12">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="M148" s="6"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C149" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D149" s="12">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="M149" s="6"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C150" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D150" s="12">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="M150" s="6"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C151" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D151" s="12">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="M151" s="6"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C152" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D152" s="12">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="M152" s="6"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C153" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D153" s="12">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="M153" s="6"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C154" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D154" s="12">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="M154" s="6"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C155" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D155" s="12">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="M155" s="6"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C156" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D156" s="12">
-        <v>0.94</v>
+        <v>0.88</v>
       </c>
       <c r="M156" s="6"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C157" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D157" s="12">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="M157" s="6"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C158" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D158" s="12">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="M158" s="6"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C159" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D159" s="12">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="M159" s="6"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C160" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D160" s="12">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="M160" s="6"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C161" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D161" s="12">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="M161" s="6"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C162" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D162" s="12">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C163" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D163" s="12">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C164" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D164" s="12">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C165" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D165" s="12">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="M165" s="6"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C166" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D166" s="12">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="M166" s="6"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C167" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D167" s="12">
-        <v>0.69</v>
+        <v>0.86</v>
       </c>
       <c r="M167" s="6"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C168" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D168" s="12">
-        <v>0.77</v>
+        <v>0.69</v>
       </c>
       <c r="M168" s="6"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C169" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D169" s="12">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="M169" s="6"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C170" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D170" s="12">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C171" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D171" s="12">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="M171" s="6"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C172" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D172" s="12">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="M172" s="6"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C173" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D173" s="12">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="M173" s="6"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C174" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D174" s="12">
+        <v>0.61</v>
+      </c>
+      <c r="M174" s="6"/>
+    </row>
+    <row r="175" spans="1:13">
+      <c r="A175" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D175" s="12">
         <v>0.75</v>
       </c>
-      <c r="M174" s="6"/>
-    </row>
-    <row r="175" spans="1:13">
-      <c r="A175" s="14" t="s">
+      <c r="M175" s="6"/>
+    </row>
+    <row r="176" spans="1:13">
+      <c r="A176" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="B175" s="14" t="s">
+      <c r="B176" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="C175" s="12" t="s">
+      <c r="C176" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="D175" s="12">
+      <c r="D176" s="12">
         <v>0.87</v>
       </c>
-      <c r="G175">
+      <c r="G176">
         <v>0.26</v>
       </c>
-      <c r="M175" s="6"/>
-    </row>
-    <row r="176" spans="1:13">
-      <c r="A176" s="17" t="s">
+      <c r="M176" s="6"/>
+    </row>
+    <row r="177" spans="1:13">
+      <c r="A177" s="17" t="s">
         <v>458</v>
       </c>
-      <c r="B176" s="18" t="s">
+      <c r="B177" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C177" t="s">
         <v>360</v>
       </c>
-      <c r="D176" s="4">
+      <c r="D177" s="4">
         <v>0</v>
       </c>
-      <c r="G176">
+      <c r="G177">
         <v>0.19</v>
-      </c>
-      <c r="M176" s="6"/>
-    </row>
-    <row r="177" spans="1:13">
-      <c r="A177" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="B177" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="C177" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D177" s="12">
-        <v>0.71</v>
-      </c>
-      <c r="G177">
-        <v>0.35</v>
       </c>
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="14" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D178" s="12">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="G178">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="14" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B179" s="14" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C179" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D179" s="12">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="G179">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C180" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D180" s="12">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G180">
-        <v>0.68</v>
+        <v>0.39</v>
       </c>
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="14" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B181" s="14" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C181" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D181" s="12">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="G181">
-        <v>0.42</v>
+        <v>0.68</v>
       </c>
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="14" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B182" s="14" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C182" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D182" s="12">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="G182">
-        <v>0.57999999999999996</v>
+        <v>0.42</v>
       </c>
       <c r="M182" s="6"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="14" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B183" s="14" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C183" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D183" s="12">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="G183">
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="14" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B184" s="14" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C184" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D184" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="G184">
+        <v>0.6</v>
+      </c>
+      <c r="M184" s="6"/>
+    </row>
+    <row r="185" spans="1:13">
+      <c r="A185" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="B185" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D185" s="12">
         <v>0.64</v>
       </c>
-      <c r="G184">
+      <c r="G185">
         <v>0.04</v>
       </c>
-      <c r="M184" s="6"/>
-    </row>
-    <row r="185" spans="1:13">
-      <c r="A185" t="s">
+      <c r="M185" s="6"/>
+    </row>
+    <row r="186" spans="1:13">
+      <c r="A186" t="s">
         <v>454</v>
       </c>
-      <c r="B185" s="2" t="s">
+      <c r="B186" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C186" t="s">
         <v>360</v>
       </c>
-      <c r="D185" s="4">
+      <c r="D186" s="4">
         <v>0</v>
       </c>
-      <c r="G185">
+      <c r="G186">
         <v>0.26</v>
-      </c>
-      <c r="M185" s="6"/>
-    </row>
-    <row r="186" spans="1:13">
-      <c r="A186" s="14" t="s">
-        <v>377</v>
-      </c>
-      <c r="B186" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="C186" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D186" s="12">
-        <v>0.78</v>
-      </c>
-      <c r="G186">
-        <v>0.54</v>
       </c>
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="14" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B187" s="14" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C187" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D187" s="12">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="G187">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="14" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B188" s="14" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C188" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D188" s="12">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="G188">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="14" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B189" s="14" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C189" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D189" s="12">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="G189">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="14" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B190" s="14" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C190" s="12" t="s">
         <v>360</v>
@@ -5021,535 +5117,538 @@
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="14" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B191" s="14" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C191" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D191" s="12">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="G191">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="14" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B192" s="14" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C192" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D192" s="12">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="G192">
-        <v>0.6</v>
+        <v>0.37</v>
       </c>
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="14" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B193" s="14" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C193" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D193" s="12">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G193">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="14" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B194" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C194" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D194" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="G194">
+        <v>0.32</v>
+      </c>
+      <c r="M194" s="6"/>
+    </row>
+    <row r="195" spans="1:13">
+      <c r="A195" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="B195" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="C195" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D195" s="12">
         <v>0.85</v>
       </c>
-      <c r="G194">
+      <c r="G195">
         <v>0.37</v>
       </c>
-      <c r="M194" s="6"/>
-    </row>
-    <row r="195" spans="1:13">
-      <c r="A195" t="s">
+      <c r="M195" s="6"/>
+    </row>
+    <row r="196" spans="1:13">
+      <c r="A196" t="s">
         <v>462</v>
       </c>
-      <c r="B195" s="2" t="s">
+      <c r="B196" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="C195" t="s">
+      <c r="C196" t="s">
         <v>360</v>
       </c>
-      <c r="D195" s="4">
+      <c r="D196" s="4">
         <v>0</v>
       </c>
-      <c r="G195">
+      <c r="G196">
         <v>0.46</v>
-      </c>
-      <c r="M195" s="6"/>
-    </row>
-    <row r="196" spans="1:13">
-      <c r="A196" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="B196" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="C196" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D196" s="12">
-        <v>0.88</v>
-      </c>
-      <c r="G196">
-        <v>0.3</v>
       </c>
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="14" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B197" s="14" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C197" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D197" s="12">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="G197">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="14" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B198" s="14" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C198" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D198" s="12">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="G198">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B199" s="14" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D199" s="12">
-        <v>0.59</v>
+        <v>0.76</v>
       </c>
       <c r="G199">
-        <v>0.65</v>
+        <v>0.39</v>
       </c>
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="14" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B200" s="14" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C200" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D200" s="12">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
       <c r="G200">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="14" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B201" s="14" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C201" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D201" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="G201">
+        <v>0.44</v>
+      </c>
+      <c r="M201" s="6"/>
+    </row>
+    <row r="202" spans="1:13">
+      <c r="A202" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="B202" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D202" s="12">
         <v>0.77</v>
       </c>
-      <c r="G201">
+      <c r="G202">
         <v>0.75</v>
       </c>
-      <c r="M201" s="6"/>
-    </row>
-    <row r="202" spans="1:13">
-      <c r="A202" t="s">
+      <c r="M202" s="6"/>
+    </row>
+    <row r="203" spans="1:13">
+      <c r="A203" t="s">
         <v>456</v>
       </c>
-      <c r="B202" s="2" t="s">
+      <c r="B203" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C203" t="s">
         <v>360</v>
       </c>
-      <c r="D202" s="4">
+      <c r="D203" s="4">
         <v>0</v>
       </c>
-      <c r="G202">
+      <c r="G203">
         <v>0.05</v>
-      </c>
-      <c r="M202" s="6"/>
-    </row>
-    <row r="203" spans="1:13">
-      <c r="A203" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="B203" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="C203" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D203" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="G203">
-        <v>0.53</v>
       </c>
       <c r="M203" s="6"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B204" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C204" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D204" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="G204">
+        <v>0.53</v>
+      </c>
+      <c r="M204" s="6"/>
+    </row>
+    <row r="205" spans="1:13">
+      <c r="A205" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="B205" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C205" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D205" s="12">
         <v>0.79</v>
       </c>
-      <c r="G204">
+      <c r="G205">
         <v>0.32</v>
       </c>
-      <c r="M204" s="6"/>
-    </row>
-    <row r="205" spans="1:13">
-      <c r="A205" t="s">
+      <c r="M205" s="6"/>
+    </row>
+    <row r="206" spans="1:13">
+      <c r="A206" t="s">
         <v>460</v>
       </c>
-      <c r="B205" s="2" t="s">
+      <c r="B206" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="C205" t="s">
+      <c r="C206" t="s">
         <v>360</v>
       </c>
-      <c r="D205" s="4">
+      <c r="D206" s="4">
         <v>0</v>
       </c>
-      <c r="G205">
+      <c r="G206">
         <v>0.44</v>
       </c>
-      <c r="M205" s="6"/>
-    </row>
-    <row r="206" spans="1:13">
-      <c r="A206" s="14" t="s">
+      <c r="M206" s="6"/>
+    </row>
+    <row r="207" spans="1:13">
+      <c r="A207" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="B206" s="14" t="s">
+      <c r="B207" s="14" t="s">
         <v>412</v>
-      </c>
-      <c r="C206" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D206" s="12">
-        <v>0.74</v>
-      </c>
-      <c r="G206">
-        <v>0.68</v>
-      </c>
-      <c r="M206" s="6"/>
-    </row>
-    <row r="207" spans="1:13">
-      <c r="A207" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="B207" s="12" t="s">
-        <v>414</v>
       </c>
       <c r="C207" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D207" s="12">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="G207">
-        <v>0.56000000000000005</v>
+        <v>0.68</v>
       </c>
       <c r="M207" s="6"/>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="12" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B208" s="12" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C208" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D208" s="12">
+        <v>0.62</v>
+      </c>
+      <c r="G208">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M208" s="6"/>
+    </row>
+    <row r="209" spans="1:13">
+      <c r="A209" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="B209" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D209" s="12">
         <v>0.94</v>
       </c>
-      <c r="G208">
+      <c r="G209">
         <v>0.65</v>
-      </c>
-      <c r="M208" s="6"/>
-    </row>
-    <row r="209" spans="1:13">
-      <c r="A209" s="14" t="s">
-        <v>417</v>
-      </c>
-      <c r="B209" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="C209" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="D209" s="12">
-        <v>0.75</v>
       </c>
       <c r="M209" s="6"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="14" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B210" s="14" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C210" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D210" s="12">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="M210" s="6"/>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="14" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B211" s="14" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C211" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D211" s="12">
-        <v>0.69</v>
+        <v>0.61</v>
       </c>
       <c r="M211" s="6"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="14" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B212" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C212" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D212" s="12">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="M212" s="6"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B213" s="14" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C213" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D213" s="12">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="M213" s="6"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="14" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B214" s="14" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C214" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D214" s="12">
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
       <c r="M214" s="6"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="14" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B215" s="14" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D215" s="12">
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
       <c r="M215" s="6"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="14" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B216" s="14" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C216" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D216" s="12">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="M216" s="6"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="14" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B217" s="14" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C217" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D217" s="12">
-        <v>0.69</v>
+        <v>0.66</v>
       </c>
       <c r="M217" s="6"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="14" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B218" s="14" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C218" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D218" s="12">
-        <v>0.83</v>
+        <v>0.69</v>
       </c>
       <c r="M218" s="6"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="14" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B219" s="14" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C219" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D219" s="12">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="M219" s="6"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="14" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B220" s="14" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C220" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D220" s="12">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="M220" s="6"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="14" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B221" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C221" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D221" s="12">
-        <v>0.74</v>
+        <v>0.81</v>
       </c>
       <c r="M221" s="6"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="14" t="s">
-        <v>32</v>
+        <v>443</v>
       </c>
       <c r="B222" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C222" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D222" s="12">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="M222" s="6"/>
     </row>
@@ -5558,49 +5657,59 @@
         <v>32</v>
       </c>
       <c r="B223" s="14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C223" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D223" s="12">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="M223" s="6"/>
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="14" t="s">
-        <v>447</v>
+        <v>32</v>
       </c>
       <c r="B224" s="14" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C224" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D224" s="12">
-        <v>0.87</v>
+        <v>0.65</v>
       </c>
       <c r="M224" s="6"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="14" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B225" s="14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C225" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D225" s="12">
+        <v>0.87</v>
+      </c>
+      <c r="M225" s="6"/>
+    </row>
+    <row r="226" spans="1:13">
+      <c r="A226" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="B226" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D226" s="12">
         <v>0.7</v>
       </c>
-      <c r="M225" s="6"/>
-    </row>
-    <row r="226" spans="1:13">
-      <c r="B226" s="2"/>
-      <c r="D226" s="4"/>
       <c r="M226" s="6"/>
     </row>
     <row r="227" spans="1:13">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6530DCCA-7E51-FE4B-AC71-BA1DDD679F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED9DD2E-A313-3149-B989-A5D288F992FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="469">
   <si>
     <t>Surname</t>
   </si>
@@ -1431,6 +1431,18 @@
   </si>
   <si>
     <t>H250361E</t>
+  </si>
+  <si>
+    <t>Nyakudya</t>
+  </si>
+  <si>
+    <t>H250112E</t>
+  </si>
+  <si>
+    <t>Ntini</t>
+  </si>
+  <si>
+    <t>H250495M</t>
   </si>
 </sst>
 </file>
@@ -4138,6 +4150,9 @@
       <c r="D128" s="12">
         <v>0.78</v>
       </c>
+      <c r="G128">
+        <v>0.4</v>
+      </c>
       <c r="M128" s="6"/>
     </row>
     <row r="129" spans="1:13">
@@ -4153,6 +4168,9 @@
       <c r="D129" s="12">
         <v>0.81</v>
       </c>
+      <c r="G129">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M129" s="6"/>
     </row>
     <row r="130" spans="1:13">
@@ -4168,6 +4186,9 @@
       <c r="D130" s="12">
         <v>0.93</v>
       </c>
+      <c r="G130">
+        <v>0.63</v>
+      </c>
       <c r="M130" s="6"/>
     </row>
     <row r="131" spans="1:13">
@@ -4183,6 +4204,9 @@
       <c r="D131" s="12">
         <v>0.77</v>
       </c>
+      <c r="G131">
+        <v>0.42</v>
+      </c>
       <c r="M131" s="6"/>
     </row>
     <row r="132" spans="1:13">
@@ -4198,6 +4222,9 @@
       <c r="D132" s="12">
         <v>0.9</v>
       </c>
+      <c r="G132">
+        <v>0.39</v>
+      </c>
       <c r="M132" s="6"/>
     </row>
     <row r="133" spans="1:13">
@@ -4213,6 +4240,9 @@
       <c r="D133" s="12">
         <v>0.87</v>
       </c>
+      <c r="G133">
+        <v>0.74</v>
+      </c>
       <c r="M133" s="6"/>
     </row>
     <row r="134" spans="1:13">
@@ -4228,6 +4258,9 @@
       <c r="D134" s="12">
         <v>0.88</v>
       </c>
+      <c r="G134">
+        <v>0.39</v>
+      </c>
       <c r="M134" s="6"/>
     </row>
     <row r="135" spans="1:13">
@@ -4243,6 +4276,9 @@
       <c r="D135" s="12">
         <v>0.77</v>
       </c>
+      <c r="G135">
+        <v>0.51</v>
+      </c>
       <c r="M135" s="6"/>
     </row>
     <row r="136" spans="1:13">
@@ -4258,6 +4294,9 @@
       <c r="D136" s="12">
         <v>0.86</v>
       </c>
+      <c r="G136">
+        <v>0.42</v>
+      </c>
       <c r="M136" s="6"/>
     </row>
     <row r="137" spans="1:13">
@@ -4273,6 +4312,9 @@
       <c r="D137" s="12">
         <v>0.68</v>
       </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
       <c r="M137" s="6"/>
     </row>
     <row r="138" spans="1:13">
@@ -4288,6 +4330,9 @@
       <c r="D138" s="12">
         <v>0.73</v>
       </c>
+      <c r="G138">
+        <v>0.16</v>
+      </c>
       <c r="M138" s="6"/>
     </row>
     <row r="139" spans="1:13">
@@ -4303,6 +4348,9 @@
       <c r="D139" s="12">
         <v>0.9</v>
       </c>
+      <c r="G139">
+        <v>0.65</v>
+      </c>
       <c r="M139" s="6"/>
     </row>
     <row r="140" spans="1:13">
@@ -4318,6 +4366,9 @@
       <c r="D140" s="12">
         <v>0.87</v>
       </c>
+      <c r="G140">
+        <v>0.4</v>
+      </c>
       <c r="M140" s="6"/>
     </row>
     <row r="141" spans="1:13">
@@ -4333,6 +4384,9 @@
       <c r="D141" s="12">
         <v>0.94</v>
       </c>
+      <c r="G141">
+        <v>0.75</v>
+      </c>
       <c r="M141" s="6"/>
     </row>
     <row r="142" spans="1:13">
@@ -4348,6 +4402,9 @@
       <c r="D142" s="12">
         <v>0.91</v>
       </c>
+      <c r="G142">
+        <v>0.63</v>
+      </c>
       <c r="M142" s="6"/>
     </row>
     <row r="143" spans="1:13">
@@ -4363,6 +4420,9 @@
       <c r="D143" s="12">
         <v>0.82</v>
       </c>
+      <c r="G143">
+        <v>0.21</v>
+      </c>
       <c r="M143" s="6"/>
     </row>
     <row r="144" spans="1:13">
@@ -4378,6 +4438,9 @@
       <c r="D144" s="12">
         <v>0.79</v>
       </c>
+      <c r="G144">
+        <v>0.25</v>
+      </c>
       <c r="M144" s="6"/>
     </row>
     <row r="145" spans="1:13">
@@ -4393,6 +4456,9 @@
       <c r="D145" s="12">
         <v>0.8</v>
       </c>
+      <c r="G145">
+        <v>0.3</v>
+      </c>
       <c r="M145" s="6"/>
     </row>
     <row r="146" spans="1:13">
@@ -4408,6 +4474,9 @@
       <c r="D146" s="12">
         <v>0.83</v>
       </c>
+      <c r="G146">
+        <v>0.63</v>
+      </c>
       <c r="M146" s="6"/>
     </row>
     <row r="147" spans="1:13">
@@ -4423,6 +4492,9 @@
       <c r="D147" s="12">
         <v>0.77</v>
       </c>
+      <c r="G147">
+        <v>0.86</v>
+      </c>
       <c r="M147" s="6"/>
     </row>
     <row r="148" spans="1:13">
@@ -4438,6 +4510,9 @@
       <c r="D148" s="12">
         <v>0.88</v>
       </c>
+      <c r="G148">
+        <v>0.47</v>
+      </c>
       <c r="M148" s="6"/>
     </row>
     <row r="149" spans="1:13">
@@ -4453,6 +4528,9 @@
       <c r="D149" s="12">
         <v>0.9</v>
       </c>
+      <c r="G149">
+        <v>0.49</v>
+      </c>
       <c r="M149" s="6"/>
     </row>
     <row r="150" spans="1:13">
@@ -4468,6 +4546,9 @@
       <c r="D150" s="12">
         <v>0.77</v>
       </c>
+      <c r="G150">
+        <v>0.44</v>
+      </c>
       <c r="M150" s="6"/>
     </row>
     <row r="151" spans="1:13">
@@ -4483,6 +4564,9 @@
       <c r="D151" s="12">
         <v>0.79</v>
       </c>
+      <c r="G151">
+        <v>0.65</v>
+      </c>
       <c r="M151" s="6"/>
     </row>
     <row r="152" spans="1:13">
@@ -4498,6 +4582,9 @@
       <c r="D152" s="12">
         <v>0.84</v>
       </c>
+      <c r="G152">
+        <v>0.6</v>
+      </c>
       <c r="M152" s="6"/>
     </row>
     <row r="153" spans="1:13">
@@ -4513,6 +4600,9 @@
       <c r="D153" s="12">
         <v>0.88</v>
       </c>
+      <c r="G153">
+        <v>0.46</v>
+      </c>
       <c r="M153" s="6"/>
     </row>
     <row r="154" spans="1:13">
@@ -4528,6 +4618,9 @@
       <c r="D154" s="12">
         <v>0.8</v>
       </c>
+      <c r="G154">
+        <v>0.42</v>
+      </c>
       <c r="M154" s="6"/>
     </row>
     <row r="155" spans="1:13">
@@ -4543,6 +4636,9 @@
       <c r="D155" s="12">
         <v>0.66</v>
       </c>
+      <c r="G155">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M155" s="6"/>
     </row>
     <row r="156" spans="1:13">
@@ -4558,6 +4654,9 @@
       <c r="D156" s="12">
         <v>0.88</v>
       </c>
+      <c r="G156">
+        <v>0.68</v>
+      </c>
       <c r="M156" s="6"/>
     </row>
     <row r="157" spans="1:13">
@@ -4573,6 +4672,9 @@
       <c r="D157" s="12">
         <v>0.94</v>
       </c>
+      <c r="G157">
+        <v>0.51</v>
+      </c>
       <c r="M157" s="6"/>
     </row>
     <row r="158" spans="1:13">
@@ -4588,6 +4690,9 @@
       <c r="D158" s="12">
         <v>0.95</v>
       </c>
+      <c r="G158">
+        <v>0.33</v>
+      </c>
       <c r="M158" s="6"/>
     </row>
     <row r="159" spans="1:13">
@@ -4603,6 +4708,9 @@
       <c r="D159" s="12">
         <v>0.79</v>
       </c>
+      <c r="G159">
+        <v>0.18</v>
+      </c>
       <c r="M159" s="6"/>
     </row>
     <row r="160" spans="1:13">
@@ -4618,6 +4726,9 @@
       <c r="D160" s="12">
         <v>0.9</v>
       </c>
+      <c r="G160">
+        <v>0.47</v>
+      </c>
       <c r="M160" s="6"/>
     </row>
     <row r="161" spans="1:13">
@@ -4633,6 +4744,9 @@
       <c r="D161" s="12">
         <v>0.82</v>
       </c>
+      <c r="G161">
+        <v>0.63</v>
+      </c>
       <c r="M161" s="6"/>
     </row>
     <row r="162" spans="1:13">
@@ -4648,6 +4762,9 @@
       <c r="D162" s="12">
         <v>0.75</v>
       </c>
+      <c r="G162">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13">
@@ -4663,6 +4780,9 @@
       <c r="D163" s="12">
         <v>0.8</v>
       </c>
+      <c r="G163">
+        <v>0.54</v>
+      </c>
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13">
@@ -4678,6 +4798,9 @@
       <c r="D164" s="12">
         <v>0.85</v>
       </c>
+      <c r="G164">
+        <v>0.3</v>
+      </c>
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13">
@@ -4693,6 +4816,9 @@
       <c r="D165" s="12">
         <v>0.82</v>
       </c>
+      <c r="G165">
+        <v>0.25</v>
+      </c>
       <c r="M165" s="6"/>
     </row>
     <row r="166" spans="1:13">
@@ -4708,1018 +4834,1074 @@
       <c r="D166" s="12">
         <v>0.9</v>
       </c>
+      <c r="G166">
+        <v>0.39</v>
+      </c>
       <c r="M166" s="6"/>
     </row>
     <row r="167" spans="1:13">
-      <c r="A167" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="B167" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="C167" s="12" t="s">
+      <c r="A167" t="s">
+        <v>467</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C167" t="s">
         <v>264</v>
       </c>
-      <c r="D167" s="12">
-        <v>0.86</v>
+      <c r="D167" s="4">
+        <v>0</v>
+      </c>
+      <c r="G167">
+        <v>0.35</v>
       </c>
       <c r="M167" s="6"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C168" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D168" s="12">
-        <v>0.69</v>
+        <v>0.86</v>
+      </c>
+      <c r="G168">
+        <v>0.35</v>
       </c>
       <c r="M168" s="6"/>
     </row>
     <row r="169" spans="1:13">
-      <c r="A169" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="B169" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="C169" s="12" t="s">
+      <c r="A169" t="s">
+        <v>465</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C169" t="s">
         <v>264</v>
       </c>
-      <c r="D169" s="12">
-        <v>0.77</v>
+      <c r="D169" s="4">
+        <v>0</v>
+      </c>
+      <c r="G169">
+        <v>0.33</v>
       </c>
       <c r="M169" s="6"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="12" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C170" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D170" s="12">
-        <v>0.73</v>
+        <v>0.69</v>
+      </c>
+      <c r="G170">
+        <v>0.12</v>
       </c>
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="12" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C171" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D171" s="12">
-        <v>0.86</v>
+        <v>0.77</v>
+      </c>
+      <c r="G171">
+        <v>0.46</v>
       </c>
       <c r="M171" s="6"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="12" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C172" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D172" s="12">
-        <v>0.68</v>
+        <v>0.73</v>
+      </c>
+      <c r="G172">
+        <v>0.19</v>
       </c>
       <c r="M172" s="6"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="12" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C173" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D173" s="12">
-        <v>0.82</v>
+        <v>0.86</v>
+      </c>
+      <c r="G173">
+        <v>0.42</v>
       </c>
       <c r="M173" s="6"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="12" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C174" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D174" s="12">
+        <v>0.68</v>
+      </c>
+      <c r="G174">
         <v>0.61</v>
       </c>
       <c r="M174" s="6"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="12" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C175" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D175" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="G175">
+        <v>0.53</v>
+      </c>
+      <c r="M175" s="6"/>
+    </row>
+    <row r="176" spans="1:13">
+      <c r="A176" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D176" s="12">
+        <v>0.61</v>
+      </c>
+      <c r="G176">
+        <v>0.35</v>
+      </c>
+      <c r="M176" s="6"/>
+    </row>
+    <row r="177" spans="1:13">
+      <c r="A177" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D177" s="12">
         <v>0.75</v>
       </c>
-      <c r="M175" s="6"/>
-    </row>
-    <row r="176" spans="1:13">
-      <c r="A176" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="B176" s="14" t="s">
-        <v>359</v>
-      </c>
-      <c r="C176" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D176" s="12">
-        <v>0.87</v>
-      </c>
-      <c r="G176">
-        <v>0.26</v>
-      </c>
-      <c r="M176" s="6"/>
-    </row>
-    <row r="177" spans="1:13">
-      <c r="A177" s="17" t="s">
-        <v>458</v>
-      </c>
-      <c r="B177" s="18" t="s">
-        <v>459</v>
-      </c>
-      <c r="C177" t="s">
-        <v>360</v>
-      </c>
-      <c r="D177" s="4">
-        <v>0</v>
-      </c>
       <c r="G177">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="14" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D178" s="12">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="G178">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
-      <c r="A179" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="B179" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="C179" s="12" t="s">
+      <c r="A179" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="B179" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="C179" t="s">
         <v>360</v>
       </c>
-      <c r="D179" s="12">
-        <v>0.92</v>
+      <c r="D179" s="4">
+        <v>0</v>
       </c>
       <c r="G179">
-        <v>0.63</v>
+        <v>0.19</v>
       </c>
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="14" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C180" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D180" s="12">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="G180">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="14" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B181" s="14" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C181" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D181" s="12">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="G181">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="14" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B182" s="14" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C182" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D182" s="12">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="G182">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="M182" s="6"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="14" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B183" s="14" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C183" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D183" s="12">
-        <v>0.81</v>
+        <v>0.75</v>
       </c>
       <c r="G183">
-        <v>0.57999999999999996</v>
+        <v>0.68</v>
       </c>
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="14" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B184" s="14" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C184" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D184" s="12">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="G184">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="14" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B185" s="14" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C185" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D185" s="12">
-        <v>0.64</v>
+        <v>0.81</v>
       </c>
       <c r="G185">
-        <v>0.04</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M185" s="6"/>
     </row>
     <row r="186" spans="1:13">
-      <c r="A186" t="s">
-        <v>454</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C186" t="s">
+      <c r="A186" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="B186" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="C186" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="D186" s="4">
-        <v>0</v>
+      <c r="D186" s="12">
+        <v>0.84</v>
       </c>
       <c r="G186">
-        <v>0.26</v>
+        <v>0.6</v>
       </c>
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="14" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B187" s="14" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C187" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D187" s="12">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="G187">
-        <v>0.54</v>
+        <v>0.04</v>
       </c>
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
-      <c r="A188" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="B188" s="14" t="s">
-        <v>380</v>
-      </c>
-      <c r="C188" s="12" t="s">
+      <c r="A188" t="s">
+        <v>454</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C188" t="s">
         <v>360</v>
       </c>
-      <c r="D188" s="12">
-        <v>0.91</v>
+      <c r="D188" s="4">
+        <v>0</v>
       </c>
       <c r="G188">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="14" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B189" s="14" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C189" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D189" s="12">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="G189">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="14" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B190" s="14" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C190" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D190" s="12">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="G190">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="14" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B191" s="14" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C191" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D191" s="12">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="G191">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="14" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B192" s="14" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C192" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D192" s="12">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="G192">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="14" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B193" s="14" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C193" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D193" s="12">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="G193">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="14" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B194" s="14" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C194" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D194" s="12">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="G194">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="14" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B195" s="14" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C195" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D195" s="12">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="G195">
-        <v>0.37</v>
+        <v>0.6</v>
       </c>
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13">
-      <c r="A196" t="s">
-        <v>462</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C196" t="s">
+      <c r="A196" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="B196" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="C196" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="D196" s="4">
-        <v>0</v>
+      <c r="D196" s="12">
+        <v>0.84</v>
       </c>
       <c r="G196">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="14" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B197" s="14" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C197" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D197" s="12">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="G197">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
-      <c r="A198" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="B198" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="C198" s="12" t="s">
+      <c r="A198" t="s">
+        <v>462</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C198" t="s">
         <v>360</v>
       </c>
-      <c r="D198" s="12">
-        <v>0.82</v>
+      <c r="D198" s="4">
+        <v>0</v>
       </c>
       <c r="G198">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="14" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B199" s="14" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D199" s="12">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="G199">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="14" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B200" s="14" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C200" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D200" s="12">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="G200">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="14" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B201" s="14" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C201" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D201" s="12">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="G201">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="14" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B202" s="14" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C202" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D202" s="12">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
       <c r="G202">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="M202" s="6"/>
     </row>
     <row r="203" spans="1:13">
-      <c r="A203" t="s">
-        <v>456</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C203" t="s">
+      <c r="A203" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="B203" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="C203" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="D203" s="4">
-        <v>0</v>
+      <c r="D203" s="12">
+        <v>0.79</v>
       </c>
       <c r="G203">
-        <v>0.05</v>
+        <v>0.44</v>
       </c>
       <c r="M203" s="6"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="14" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B204" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C204" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D204" s="12">
+        <v>0.77</v>
+      </c>
+      <c r="G204">
         <v>0.75</v>
       </c>
-      <c r="G204">
+      <c r="M204" s="6"/>
+    </row>
+    <row r="205" spans="1:13">
+      <c r="A205" t="s">
+        <v>456</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C205" t="s">
+        <v>360</v>
+      </c>
+      <c r="D205" s="4">
+        <v>0</v>
+      </c>
+      <c r="G205">
+        <v>0.05</v>
+      </c>
+      <c r="M205" s="6"/>
+    </row>
+    <row r="206" spans="1:13">
+      <c r="A206" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="B206" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D206" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="G206">
         <v>0.53</v>
-      </c>
-      <c r="M204" s="6"/>
-    </row>
-    <row r="205" spans="1:13">
-      <c r="A205" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="B205" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="C205" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D205" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="G205">
-        <v>0.32</v>
-      </c>
-      <c r="M205" s="6"/>
-    </row>
-    <row r="206" spans="1:13">
-      <c r="A206" t="s">
-        <v>460</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C206" t="s">
-        <v>360</v>
-      </c>
-      <c r="D206" s="4">
-        <v>0</v>
-      </c>
-      <c r="G206">
-        <v>0.44</v>
       </c>
       <c r="M206" s="6"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="14" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B207" s="14" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C207" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D207" s="12">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="G207">
-        <v>0.68</v>
+        <v>0.32</v>
       </c>
       <c r="M207" s="6"/>
     </row>
     <row r="208" spans="1:13">
-      <c r="A208" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="B208" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="C208" s="12" t="s">
+      <c r="A208" t="s">
+        <v>460</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C208" t="s">
         <v>360</v>
       </c>
-      <c r="D208" s="12">
-        <v>0.62</v>
+      <c r="D208" s="4">
+        <v>0</v>
       </c>
       <c r="G208">
-        <v>0.56000000000000005</v>
+        <v>0.44</v>
       </c>
       <c r="M208" s="6"/>
     </row>
     <row r="209" spans="1:13">
-      <c r="A209" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="B209" s="12" t="s">
-        <v>416</v>
+      <c r="A209" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="B209" s="14" t="s">
+        <v>412</v>
       </c>
       <c r="C209" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D209" s="12">
+        <v>0.74</v>
+      </c>
+      <c r="G209">
+        <v>0.68</v>
+      </c>
+      <c r="M209" s="6"/>
+    </row>
+    <row r="210" spans="1:13">
+      <c r="A210" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B210" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D210" s="12">
+        <v>0.62</v>
+      </c>
+      <c r="G210">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M210" s="6"/>
+    </row>
+    <row r="211" spans="1:13">
+      <c r="A211" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D211" s="12">
         <v>0.94</v>
       </c>
-      <c r="G209">
+      <c r="G211">
         <v>0.65</v>
-      </c>
-      <c r="M209" s="6"/>
-    </row>
-    <row r="210" spans="1:13">
-      <c r="A210" s="14" t="s">
-        <v>417</v>
-      </c>
-      <c r="B210" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="C210" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="D210" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="M210" s="6"/>
-    </row>
-    <row r="211" spans="1:13">
-      <c r="A211" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="B211" s="14" t="s">
-        <v>421</v>
-      </c>
-      <c r="C211" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="D211" s="12">
-        <v>0.61</v>
       </c>
       <c r="M211" s="6"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="14" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B212" s="14" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C212" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D212" s="12">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="M212" s="6"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="14" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B213" s="14" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C213" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D213" s="12">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="M213" s="6"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="14" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B214" s="14" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C214" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D214" s="12">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="M214" s="6"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="14" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B215" s="14" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C215" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D215" s="12">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="M215" s="6"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="14" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B216" s="14" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D216" s="12">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="M216" s="6"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="14" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B217" s="14" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D217" s="12">
-        <v>0.66</v>
+        <v>0.89</v>
       </c>
       <c r="M217" s="6"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="14" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B218" s="14" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C218" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D218" s="12">
-        <v>0.69</v>
+        <v>0.79</v>
       </c>
       <c r="M218" s="6"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="14" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B219" s="14" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C219" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D219" s="12">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="M219" s="6"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="14" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B220" s="14" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C220" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D220" s="12">
-        <v>0.79</v>
+        <v>0.69</v>
       </c>
       <c r="M220" s="6"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="14" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B221" s="14" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C221" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D221" s="12">
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="M221" s="6"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="14" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B222" s="14" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C222" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D222" s="12">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="M222" s="6"/>
     </row>
     <row r="223" spans="1:13">
       <c r="A223" s="14" t="s">
-        <v>32</v>
+        <v>441</v>
       </c>
       <c r="B223" s="14" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C223" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D223" s="12">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="M223" s="6"/>
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="14" t="s">
-        <v>32</v>
+        <v>443</v>
       </c>
       <c r="B224" s="14" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C224" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D224" s="12">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="M224" s="6"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="14" t="s">
-        <v>447</v>
+        <v>32</v>
       </c>
       <c r="B225" s="14" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C225" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D225" s="12">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="M225" s="6"/>
     </row>
     <row r="226" spans="1:13">
       <c r="A226" s="14" t="s">
-        <v>449</v>
+        <v>32</v>
       </c>
       <c r="B226" s="14" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C226" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D226" s="12">
+        <v>0.65</v>
+      </c>
+      <c r="M226" s="6"/>
+    </row>
+    <row r="227" spans="1:13">
+      <c r="A227" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="B227" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D227" s="12">
+        <v>0.87</v>
+      </c>
+      <c r="M227" s="6"/>
+    </row>
+    <row r="228" spans="1:13">
+      <c r="A228" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="B228" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D228" s="12">
         <v>0.7</v>
       </c>
-      <c r="M226" s="6"/>
-    </row>
-    <row r="227" spans="1:13">
-      <c r="B227" s="3"/>
-      <c r="D227" s="4"/>
-      <c r="M227" s="6"/>
-    </row>
-    <row r="228" spans="1:13">
-      <c r="B228" s="3"/>
-      <c r="D228" s="4"/>
       <c r="M228" s="6"/>
     </row>
   </sheetData>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED9DD2E-A313-3149-B989-A5D288F992FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD060AD-9BC0-1C43-8899-9D71B1F8C74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="488">
   <si>
     <t>Surname</t>
   </si>
@@ -1443,6 +1443,63 @@
   </si>
   <si>
     <t>H250495M</t>
+  </si>
+  <si>
+    <t>Magondo</t>
+  </si>
+  <si>
+    <t>H250547B</t>
+  </si>
+  <si>
+    <t>H250282N</t>
+  </si>
+  <si>
+    <t>Chadzingwa</t>
+  </si>
+  <si>
+    <t>H250704C</t>
+  </si>
+  <si>
+    <t>Mutsiwa</t>
+  </si>
+  <si>
+    <t>H250713C</t>
+  </si>
+  <si>
+    <t>Maera</t>
+  </si>
+  <si>
+    <t>H230448V</t>
+  </si>
+  <si>
+    <t>Ndongwe</t>
+  </si>
+  <si>
+    <t>H230835V</t>
+  </si>
+  <si>
+    <t>Mayterah</t>
+  </si>
+  <si>
+    <t>H240144N</t>
+  </si>
+  <si>
+    <t>Kanyama</t>
+  </si>
+  <si>
+    <t>Munzvangi</t>
+  </si>
+  <si>
+    <t>H250319B</t>
+  </si>
+  <si>
+    <t>H250794W</t>
+  </si>
+  <si>
+    <t>Chigwada</t>
+  </si>
+  <si>
+    <t>H250391C</t>
   </si>
 </sst>
 </file>
@@ -1581,7 +1638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1599,12 +1656,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1648,8 +1702,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M228" totalsRowShown="0">
-  <autoFilter ref="A1:M228" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M238" totalsRowShown="0">
+  <autoFilter ref="A1:M238" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M228">
     <sortCondition ref="C1:C228"/>
   </sortState>
@@ -1989,7 +2043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:M228"/>
+  <dimension ref="A1:M238"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -2587,13 +2641,13 @@
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="15" t="s">
         <v>452</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="14" t="s">
         <v>101</v>
       </c>
       <c r="D34" s="4">
@@ -2634,13 +2688,13 @@
       <c r="M36" s="6"/>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="15" t="s">
         <v>453</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="14" t="s">
         <v>101</v>
       </c>
       <c r="D37" s="4">
@@ -2793,10 +2847,10 @@
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="12" t="s">
         <v>103</v>
       </c>
       <c r="C47" s="12" t="s">
@@ -2812,10 +2866,10 @@
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="12" t="s">
         <v>106</v>
       </c>
       <c r="C48" s="12" t="s">
@@ -2831,10 +2885,10 @@
       <c r="M48" s="6"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C49" s="12" t="s">
@@ -2850,10 +2904,10 @@
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="12" t="s">
         <v>110</v>
       </c>
       <c r="C50" s="12" t="s">
@@ -2869,10 +2923,10 @@
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="12" t="s">
         <v>112</v>
       </c>
       <c r="C51" s="12" t="s">
@@ -2888,10 +2942,10 @@
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="12" t="s">
         <v>114</v>
       </c>
       <c r="C52" s="12" t="s">
@@ -2907,10 +2961,10 @@
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="12" t="s">
         <v>116</v>
       </c>
       <c r="C53" s="12" t="s">
@@ -2926,10 +2980,10 @@
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="12" t="s">
         <v>118</v>
       </c>
       <c r="C54" s="12" t="s">
@@ -2944,10 +2998,10 @@
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="12" t="s">
         <v>120</v>
       </c>
       <c r="C55" s="12" t="s">
@@ -2962,10 +3016,10 @@
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="12" t="s">
         <v>122</v>
       </c>
       <c r="C56" s="12" t="s">
@@ -3538,10 +3592,10 @@
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="B88" s="14" t="s">
+      <c r="B88" s="12" t="s">
         <v>184</v>
       </c>
       <c r="C88" s="12" t="s">
@@ -3550,13 +3604,16 @@
       <c r="D88" s="12">
         <v>0.75</v>
       </c>
+      <c r="G88">
+        <v>0.68</v>
+      </c>
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
-      <c r="A89" s="14" t="s">
+      <c r="A89" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="B89" s="14" t="s">
+      <c r="B89" s="12" t="s">
         <v>187</v>
       </c>
       <c r="C89" s="12" t="s">
@@ -3565,13 +3622,16 @@
       <c r="D89" s="12">
         <v>0.75</v>
       </c>
+      <c r="G89">
+        <v>0.6</v>
+      </c>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="B90" s="12" t="s">
         <v>189</v>
       </c>
       <c r="C90" s="12" t="s">
@@ -3580,13 +3640,16 @@
       <c r="D90" s="12">
         <v>0.82</v>
       </c>
+      <c r="G90">
+        <v>0.47</v>
+      </c>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
-      <c r="A91" s="14" t="s">
+      <c r="A91" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="B91" s="14" t="s">
+      <c r="B91" s="12" t="s">
         <v>191</v>
       </c>
       <c r="C91" s="12" t="s">
@@ -3595,13 +3658,16 @@
       <c r="D91" s="12">
         <v>0.75</v>
       </c>
+      <c r="G91">
+        <v>0.65</v>
+      </c>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
-      <c r="A92" s="14" t="s">
+      <c r="A92" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B92" s="14" t="s">
+      <c r="B92" s="12" t="s">
         <v>193</v>
       </c>
       <c r="C92" s="12" t="s">
@@ -3610,13 +3676,16 @@
       <c r="D92" s="12">
         <v>0.77</v>
       </c>
+      <c r="G92">
+        <v>0.42</v>
+      </c>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
-      <c r="A93" s="14" t="s">
+      <c r="A93" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="12" t="s">
         <v>195</v>
       </c>
       <c r="C93" s="12" t="s">
@@ -3625,13 +3694,16 @@
       <c r="D93" s="12">
         <v>0.93</v>
       </c>
+      <c r="G93">
+        <v>0.79</v>
+      </c>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
-      <c r="A94" s="14" t="s">
+      <c r="A94" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="B94" s="12" t="s">
         <v>197</v>
       </c>
       <c r="C94" s="12" t="s">
@@ -3639,6 +3711,9 @@
       </c>
       <c r="D94" s="12">
         <v>0.79</v>
+      </c>
+      <c r="G94">
+        <v>0.46</v>
       </c>
       <c r="M94" s="6"/>
     </row>
@@ -3655,6 +3730,9 @@
       <c r="D95" s="12">
         <v>0.93</v>
       </c>
+      <c r="G95">
+        <v>0.72</v>
+      </c>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
@@ -3670,6 +3748,9 @@
       <c r="D96" s="12">
         <v>0.83</v>
       </c>
+      <c r="G96">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
@@ -3685,6 +3766,9 @@
       <c r="D97" s="12">
         <v>0.9</v>
       </c>
+      <c r="G97">
+        <v>0.4</v>
+      </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
@@ -3700,6 +3784,9 @@
       <c r="D98" s="12">
         <v>0.83</v>
       </c>
+      <c r="G98">
+        <v>0.44</v>
+      </c>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
@@ -3715,6 +3802,9 @@
       <c r="D99" s="12">
         <v>0.85</v>
       </c>
+      <c r="G99">
+        <v>0.51</v>
+      </c>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
@@ -3730,6 +3820,9 @@
       <c r="D100" s="12">
         <v>0.89</v>
       </c>
+      <c r="G100">
+        <v>0.49</v>
+      </c>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
@@ -3745,6 +3838,9 @@
       <c r="D101" s="12">
         <v>0.85</v>
       </c>
+      <c r="G101">
+        <v>0.54</v>
+      </c>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
@@ -3760,6 +3856,9 @@
       <c r="D102" s="12">
         <v>0.86</v>
       </c>
+      <c r="G102">
+        <v>0.4</v>
+      </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
@@ -3775,6 +3874,9 @@
       <c r="D103" s="12">
         <v>0.79</v>
       </c>
+      <c r="G103">
+        <v>0.44</v>
+      </c>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
@@ -3790,6 +3892,9 @@
       <c r="D104" s="12">
         <v>0.76</v>
       </c>
+      <c r="G104">
+        <v>0.39</v>
+      </c>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
@@ -3805,6 +3910,9 @@
       <c r="D105" s="12">
         <v>0.84</v>
       </c>
+      <c r="G105">
+        <v>0.75</v>
+      </c>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
@@ -3820,6 +3928,9 @@
       <c r="D106" s="12">
         <v>0.82</v>
       </c>
+      <c r="G106">
+        <v>0.61</v>
+      </c>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
@@ -3835,6 +3946,9 @@
       <c r="D107" s="12">
         <v>0.83</v>
       </c>
+      <c r="G107">
+        <v>0.26</v>
+      </c>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
@@ -3850,6 +3964,9 @@
       <c r="D108" s="12">
         <v>0.94</v>
       </c>
+      <c r="G108">
+        <v>0.46</v>
+      </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
@@ -3865,6 +3982,9 @@
       <c r="D109" s="12">
         <v>0.9</v>
       </c>
+      <c r="G109">
+        <v>0.42</v>
+      </c>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
@@ -3880,6 +4000,9 @@
       <c r="D110" s="12">
         <v>0.75</v>
       </c>
+      <c r="G110">
+        <v>0.39</v>
+      </c>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
@@ -3895,6 +4018,9 @@
       <c r="D111" s="12">
         <v>0.9</v>
       </c>
+      <c r="G111">
+        <v>0.46</v>
+      </c>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
@@ -3910,6 +4036,9 @@
       <c r="D112" s="12">
         <v>0.66</v>
       </c>
+      <c r="G112">
+        <v>0.63</v>
+      </c>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
@@ -3925,6 +4054,9 @@
       <c r="D113" s="12">
         <v>0.92</v>
       </c>
+      <c r="G113">
+        <v>0.44</v>
+      </c>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
@@ -3940,6 +4072,9 @@
       <c r="D114" s="12">
         <v>0.82</v>
       </c>
+      <c r="G114">
+        <v>0.54</v>
+      </c>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
@@ -3955,6 +4090,9 @@
       <c r="D115" s="12">
         <v>0.8</v>
       </c>
+      <c r="G115">
+        <v>0.26</v>
+      </c>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">
@@ -3970,6 +4108,9 @@
       <c r="D116" s="12">
         <v>0.96</v>
       </c>
+      <c r="G116">
+        <v>0.26</v>
+      </c>
       <c r="M116" s="6"/>
     </row>
     <row r="117" spans="1:13">
@@ -3985,6 +4126,9 @@
       <c r="D117" s="12">
         <v>0.69</v>
       </c>
+      <c r="G117">
+        <v>0.26</v>
+      </c>
       <c r="M117" s="6"/>
     </row>
     <row r="118" spans="1:13">
@@ -4000,6 +4144,9 @@
       <c r="D118" s="12">
         <v>0.78</v>
       </c>
+      <c r="G118">
+        <v>0.09</v>
+      </c>
       <c r="M118" s="6"/>
     </row>
     <row r="119" spans="1:13">
@@ -4015,6 +4162,9 @@
       <c r="D119" s="12">
         <v>0.75</v>
       </c>
+      <c r="G119">
+        <v>0.49</v>
+      </c>
       <c r="M119" s="6"/>
     </row>
     <row r="120" spans="1:13">
@@ -4030,6 +4180,9 @@
       <c r="D120" s="12">
         <v>0.67</v>
       </c>
+      <c r="G120">
+        <v>0.74</v>
+      </c>
       <c r="M120" s="6"/>
     </row>
     <row r="121" spans="1:13">
@@ -4045,6 +4198,9 @@
       <c r="D121" s="12">
         <v>0.84</v>
       </c>
+      <c r="G121">
+        <v>0.26</v>
+      </c>
       <c r="M121" s="6"/>
     </row>
     <row r="122" spans="1:13">
@@ -4060,6 +4216,9 @@
       <c r="D122" s="12">
         <v>0.73</v>
       </c>
+      <c r="G122">
+        <v>0.32</v>
+      </c>
       <c r="M122" s="6"/>
     </row>
     <row r="123" spans="1:13">
@@ -4075,6 +4234,9 @@
       <c r="D123" s="12">
         <v>0.83</v>
       </c>
+      <c r="G123">
+        <v>0.11</v>
+      </c>
       <c r="M123" s="6"/>
     </row>
     <row r="124" spans="1:13">
@@ -4090,6 +4252,9 @@
       <c r="D124" s="12">
         <v>0.95</v>
       </c>
+      <c r="G124">
+        <v>0.65</v>
+      </c>
       <c r="M124" s="6"/>
     </row>
     <row r="125" spans="1:13">
@@ -4105,6 +4270,9 @@
       <c r="D125" s="12">
         <v>0.72</v>
       </c>
+      <c r="G125">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="M125" s="6"/>
     </row>
     <row r="126" spans="1:13">
@@ -4120,6 +4288,9 @@
       <c r="D126" s="12">
         <v>0.83</v>
       </c>
+      <c r="G126">
+        <v>0.47</v>
+      </c>
       <c r="M126" s="6"/>
     </row>
     <row r="127" spans="1:13">
@@ -4135,13 +4306,16 @@
       <c r="D127" s="12">
         <v>0.75</v>
       </c>
+      <c r="G127">
+        <v>0.35</v>
+      </c>
       <c r="M127" s="6"/>
     </row>
     <row r="128" spans="1:13">
-      <c r="A128" s="14" t="s">
+      <c r="A128" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="B128" s="14" t="s">
+      <c r="B128" s="12" t="s">
         <v>263</v>
       </c>
       <c r="C128" s="12" t="s">
@@ -4156,10 +4330,10 @@
       <c r="M128" s="6"/>
     </row>
     <row r="129" spans="1:13">
-      <c r="A129" s="14" t="s">
+      <c r="A129" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="B129" s="14" t="s">
+      <c r="B129" s="12" t="s">
         <v>266</v>
       </c>
       <c r="C129" s="12" t="s">
@@ -4174,10 +4348,10 @@
       <c r="M129" s="6"/>
     </row>
     <row r="130" spans="1:13">
-      <c r="A130" s="14" t="s">
+      <c r="A130" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="B130" s="14" t="s">
+      <c r="B130" s="12" t="s">
         <v>268</v>
       </c>
       <c r="C130" s="12" t="s">
@@ -4192,10 +4366,10 @@
       <c r="M130" s="6"/>
     </row>
     <row r="131" spans="1:13">
-      <c r="A131" s="14" t="s">
+      <c r="A131" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="B131" s="14" t="s">
+      <c r="B131" s="12" t="s">
         <v>270</v>
       </c>
       <c r="C131" s="12" t="s">
@@ -4210,10 +4384,10 @@
       <c r="M131" s="6"/>
     </row>
     <row r="132" spans="1:13">
-      <c r="A132" s="14" t="s">
+      <c r="A132" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="B132" s="14" t="s">
+      <c r="B132" s="12" t="s">
         <v>272</v>
       </c>
       <c r="C132" s="12" t="s">
@@ -4228,10 +4402,10 @@
       <c r="M132" s="6"/>
     </row>
     <row r="133" spans="1:13">
-      <c r="A133" s="14" t="s">
+      <c r="A133" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="B133" s="14" t="s">
+      <c r="B133" s="12" t="s">
         <v>274</v>
       </c>
       <c r="C133" s="12" t="s">
@@ -4246,10 +4420,10 @@
       <c r="M133" s="6"/>
     </row>
     <row r="134" spans="1:13">
-      <c r="A134" s="14" t="s">
+      <c r="A134" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="B134" s="14" t="s">
+      <c r="B134" s="12" t="s">
         <v>276</v>
       </c>
       <c r="C134" s="12" t="s">
@@ -4264,10 +4438,10 @@
       <c r="M134" s="6"/>
     </row>
     <row r="135" spans="1:13">
-      <c r="A135" s="14" t="s">
+      <c r="A135" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="B135" s="14" t="s">
+      <c r="B135" s="12" t="s">
         <v>278</v>
       </c>
       <c r="C135" s="12" t="s">
@@ -4282,10 +4456,10 @@
       <c r="M135" s="6"/>
     </row>
     <row r="136" spans="1:13">
-      <c r="A136" s="14" t="s">
+      <c r="A136" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B136" s="14" t="s">
+      <c r="B136" s="12" t="s">
         <v>280</v>
       </c>
       <c r="C136" s="12" t="s">
@@ -4300,10 +4474,10 @@
       <c r="M136" s="6"/>
     </row>
     <row r="137" spans="1:13">
-      <c r="A137" s="14" t="s">
+      <c r="A137" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="B137" s="14" t="s">
+      <c r="B137" s="12" t="s">
         <v>282</v>
       </c>
       <c r="C137" s="12" t="s">
@@ -4318,10 +4492,10 @@
       <c r="M137" s="6"/>
     </row>
     <row r="138" spans="1:13">
-      <c r="A138" s="14" t="s">
+      <c r="A138" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B138" s="14" t="s">
+      <c r="B138" s="12" t="s">
         <v>283</v>
       </c>
       <c r="C138" s="12" t="s">
@@ -4336,10 +4510,10 @@
       <c r="M138" s="6"/>
     </row>
     <row r="139" spans="1:13">
-      <c r="A139" s="14" t="s">
+      <c r="A139" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="B139" s="14" t="s">
+      <c r="B139" s="12" t="s">
         <v>285</v>
       </c>
       <c r="C139" s="12" t="s">
@@ -4354,10 +4528,10 @@
       <c r="M139" s="6"/>
     </row>
     <row r="140" spans="1:13">
-      <c r="A140" s="14" t="s">
+      <c r="A140" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="B140" s="14" t="s">
+      <c r="B140" s="12" t="s">
         <v>287</v>
       </c>
       <c r="C140" s="12" t="s">
@@ -5038,10 +5212,10 @@
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
-      <c r="A178" s="14" t="s">
+      <c r="A178" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="B178" s="14" t="s">
+      <c r="B178" s="12" t="s">
         <v>359</v>
       </c>
       <c r="C178" s="12" t="s">
@@ -5056,10 +5230,10 @@
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
-      <c r="A179" s="17" t="s">
+      <c r="A179" t="s">
         <v>458</v>
       </c>
-      <c r="B179" s="18" t="s">
+      <c r="B179" s="3" t="s">
         <v>459</v>
       </c>
       <c r="C179" t="s">
@@ -5074,10 +5248,10 @@
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
-      <c r="A180" s="14" t="s">
+      <c r="A180" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="B180" s="14" t="s">
+      <c r="B180" s="12" t="s">
         <v>362</v>
       </c>
       <c r="C180" s="12" t="s">
@@ -5092,10 +5266,10 @@
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13">
-      <c r="A181" s="14" t="s">
+      <c r="A181" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="B181" s="14" t="s">
+      <c r="B181" s="12" t="s">
         <v>364</v>
       </c>
       <c r="C181" s="12" t="s">
@@ -5110,10 +5284,10 @@
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13">
-      <c r="A182" s="14" t="s">
+      <c r="A182" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="B182" s="14" t="s">
+      <c r="B182" s="12" t="s">
         <v>366</v>
       </c>
       <c r="C182" s="12" t="s">
@@ -5128,10 +5302,10 @@
       <c r="M182" s="6"/>
     </row>
     <row r="183" spans="1:13">
-      <c r="A183" s="14" t="s">
+      <c r="A183" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="B183" s="14" t="s">
+      <c r="B183" s="12" t="s">
         <v>368</v>
       </c>
       <c r="C183" s="12" t="s">
@@ -5146,10 +5320,10 @@
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13">
-      <c r="A184" s="14" t="s">
+      <c r="A184" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="B184" s="14" t="s">
+      <c r="B184" s="12" t="s">
         <v>370</v>
       </c>
       <c r="C184" s="12" t="s">
@@ -5164,10 +5338,10 @@
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13">
-      <c r="A185" s="14" t="s">
+      <c r="A185" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="B185" s="14" t="s">
+      <c r="B185" s="12" t="s">
         <v>372</v>
       </c>
       <c r="C185" s="12" t="s">
@@ -5182,10 +5356,10 @@
       <c r="M185" s="6"/>
     </row>
     <row r="186" spans="1:13">
-      <c r="A186" s="14" t="s">
+      <c r="A186" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="B186" s="14" t="s">
+      <c r="B186" s="12" t="s">
         <v>374</v>
       </c>
       <c r="C186" s="12" t="s">
@@ -5200,10 +5374,10 @@
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13">
-      <c r="A187" s="14" t="s">
+      <c r="A187" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="B187" s="14" t="s">
+      <c r="B187" s="12" t="s">
         <v>376</v>
       </c>
       <c r="C187" s="12" t="s">
@@ -5236,10 +5410,10 @@
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
-      <c r="A189" s="14" t="s">
+      <c r="A189" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="B189" s="14" t="s">
+      <c r="B189" s="12" t="s">
         <v>378</v>
       </c>
       <c r="C189" s="12" t="s">
@@ -5254,10 +5428,10 @@
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
-      <c r="A190" s="14" t="s">
+      <c r="A190" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="B190" s="14" t="s">
+      <c r="B190" s="12" t="s">
         <v>380</v>
       </c>
       <c r="C190" s="12" t="s">
@@ -5272,10 +5446,10 @@
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13">
-      <c r="A191" s="14" t="s">
+      <c r="A191" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="B191" s="14" t="s">
+      <c r="B191" s="12" t="s">
         <v>382</v>
       </c>
       <c r="C191" s="12" t="s">
@@ -5290,10 +5464,10 @@
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
-      <c r="A192" s="14" t="s">
+      <c r="A192" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="B192" s="14" t="s">
+      <c r="B192" s="12" t="s">
         <v>384</v>
       </c>
       <c r="C192" s="12" t="s">
@@ -5308,10 +5482,10 @@
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13">
-      <c r="A193" s="14" t="s">
+      <c r="A193" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="B193" s="14" t="s">
+      <c r="B193" s="12" t="s">
         <v>386</v>
       </c>
       <c r="C193" s="12" t="s">
@@ -5326,10 +5500,10 @@
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13">
-      <c r="A194" s="14" t="s">
+      <c r="A194" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="B194" s="14" t="s">
+      <c r="B194" s="12" t="s">
         <v>388</v>
       </c>
       <c r="C194" s="12" t="s">
@@ -5344,10 +5518,10 @@
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13">
-      <c r="A195" s="14" t="s">
+      <c r="A195" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B195" s="14" t="s">
+      <c r="B195" s="12" t="s">
         <v>390</v>
       </c>
       <c r="C195" s="12" t="s">
@@ -5362,10 +5536,10 @@
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13">
-      <c r="A196" s="14" t="s">
+      <c r="A196" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="B196" s="14" t="s">
+      <c r="B196" s="12" t="s">
         <v>392</v>
       </c>
       <c r="C196" s="12" t="s">
@@ -5380,10 +5554,10 @@
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
-      <c r="A197" s="14" t="s">
+      <c r="A197" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="B197" s="14" t="s">
+      <c r="B197" s="12" t="s">
         <v>394</v>
       </c>
       <c r="C197" s="12" t="s">
@@ -5416,10 +5590,10 @@
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
-      <c r="A199" s="14" t="s">
+      <c r="A199" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="B199" s="14" t="s">
+      <c r="B199" s="12" t="s">
         <v>396</v>
       </c>
       <c r="C199" s="12" t="s">
@@ -5434,10 +5608,10 @@
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:13">
-      <c r="A200" s="14" t="s">
+      <c r="A200" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="B200" s="14" t="s">
+      <c r="B200" s="12" t="s">
         <v>398</v>
       </c>
       <c r="C200" s="12" t="s">
@@ -5452,10 +5626,10 @@
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
-      <c r="A201" s="14" t="s">
+      <c r="A201" s="12" t="s">
         <v>399</v>
       </c>
-      <c r="B201" s="14" t="s">
+      <c r="B201" s="12" t="s">
         <v>400</v>
       </c>
       <c r="C201" s="12" t="s">
@@ -5470,10 +5644,10 @@
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
-      <c r="A202" s="14" t="s">
+      <c r="A202" s="12" t="s">
         <v>401</v>
       </c>
-      <c r="B202" s="14" t="s">
+      <c r="B202" s="12" t="s">
         <v>402</v>
       </c>
       <c r="C202" s="12" t="s">
@@ -5488,10 +5662,10 @@
       <c r="M202" s="6"/>
     </row>
     <row r="203" spans="1:13">
-      <c r="A203" s="14" t="s">
+      <c r="A203" s="12" t="s">
         <v>403</v>
       </c>
-      <c r="B203" s="14" t="s">
+      <c r="B203" s="12" t="s">
         <v>404</v>
       </c>
       <c r="C203" s="12" t="s">
@@ -5506,10 +5680,10 @@
       <c r="M203" s="6"/>
     </row>
     <row r="204" spans="1:13">
-      <c r="A204" s="14" t="s">
+      <c r="A204" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="B204" s="14" t="s">
+      <c r="B204" s="12" t="s">
         <v>406</v>
       </c>
       <c r="C204" s="12" t="s">
@@ -5542,10 +5716,10 @@
       <c r="M205" s="6"/>
     </row>
     <row r="206" spans="1:13">
-      <c r="A206" s="14" t="s">
+      <c r="A206" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="B206" s="14" t="s">
+      <c r="B206" s="12" t="s">
         <v>408</v>
       </c>
       <c r="C206" s="12" t="s">
@@ -5560,10 +5734,10 @@
       <c r="M206" s="6"/>
     </row>
     <row r="207" spans="1:13">
-      <c r="A207" s="14" t="s">
+      <c r="A207" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="B207" s="14" t="s">
+      <c r="B207" s="12" t="s">
         <v>410</v>
       </c>
       <c r="C207" s="12" t="s">
@@ -5596,10 +5770,10 @@
       <c r="M208" s="6"/>
     </row>
     <row r="209" spans="1:13">
-      <c r="A209" s="14" t="s">
+      <c r="A209" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="B209" s="14" t="s">
+      <c r="B209" s="12" t="s">
         <v>412</v>
       </c>
       <c r="C209" s="12" t="s">
@@ -5650,10 +5824,10 @@
       <c r="M211" s="6"/>
     </row>
     <row r="212" spans="1:13">
-      <c r="A212" s="14" t="s">
+      <c r="A212" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="B212" s="14" t="s">
+      <c r="B212" s="12" t="s">
         <v>418</v>
       </c>
       <c r="C212" s="12" t="s">
@@ -5662,13 +5836,16 @@
       <c r="D212" s="12">
         <v>0.75</v>
       </c>
+      <c r="G212">
+        <v>0.79</v>
+      </c>
       <c r="M212" s="6"/>
     </row>
     <row r="213" spans="1:13">
-      <c r="A213" s="14" t="s">
+      <c r="A213" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="B213" s="14" t="s">
+      <c r="B213" s="12" t="s">
         <v>421</v>
       </c>
       <c r="C213" s="12" t="s">
@@ -5677,13 +5854,16 @@
       <c r="D213" s="12">
         <v>0.61</v>
       </c>
+      <c r="G213">
+        <v>0.32</v>
+      </c>
       <c r="M213" s="6"/>
     </row>
     <row r="214" spans="1:13">
-      <c r="A214" s="14" t="s">
+      <c r="A214" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="B214" s="14" t="s">
+      <c r="B214" s="12" t="s">
         <v>423</v>
       </c>
       <c r="C214" s="12" t="s">
@@ -5692,13 +5872,16 @@
       <c r="D214" s="12">
         <v>0.69</v>
       </c>
+      <c r="G214">
+        <v>0.54</v>
+      </c>
       <c r="M214" s="6"/>
     </row>
     <row r="215" spans="1:13">
-      <c r="A215" s="14" t="s">
+      <c r="A215" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="B215" s="14" t="s">
+      <c r="B215" s="12" t="s">
         <v>425</v>
       </c>
       <c r="C215" s="12" t="s">
@@ -5707,13 +5890,16 @@
       <c r="D215" s="12">
         <v>0.67</v>
       </c>
+      <c r="G215">
+        <v>0.11</v>
+      </c>
       <c r="M215" s="6"/>
     </row>
     <row r="216" spans="1:13">
-      <c r="A216" s="14" t="s">
+      <c r="A216" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="B216" s="14" t="s">
+      <c r="B216" s="12" t="s">
         <v>427</v>
       </c>
       <c r="C216" s="12" t="s">
@@ -5722,13 +5908,16 @@
       <c r="D216" s="12">
         <v>0.71</v>
       </c>
+      <c r="G216">
+        <v>0.54</v>
+      </c>
       <c r="M216" s="6"/>
     </row>
     <row r="217" spans="1:13">
-      <c r="A217" s="14" t="s">
+      <c r="A217" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="B217" s="14" t="s">
+      <c r="B217" s="12" t="s">
         <v>429</v>
       </c>
       <c r="C217" s="12" t="s">
@@ -5737,13 +5926,16 @@
       <c r="D217" s="12">
         <v>0.89</v>
       </c>
+      <c r="G217">
+        <v>0.61</v>
+      </c>
       <c r="M217" s="6"/>
     </row>
     <row r="218" spans="1:13">
-      <c r="A218" s="14" t="s">
+      <c r="A218" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="B218" s="14" t="s">
+      <c r="B218" s="12" t="s">
         <v>431</v>
       </c>
       <c r="C218" s="12" t="s">
@@ -5752,13 +5944,16 @@
       <c r="D218" s="12">
         <v>0.79</v>
       </c>
+      <c r="G218">
+        <v>0.26</v>
+      </c>
       <c r="M218" s="6"/>
     </row>
     <row r="219" spans="1:13">
-      <c r="A219" s="14" t="s">
+      <c r="A219" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="B219" s="14" t="s">
+      <c r="B219" s="12" t="s">
         <v>434</v>
       </c>
       <c r="C219" s="12" t="s">
@@ -5767,13 +5962,16 @@
       <c r="D219" s="12">
         <v>0.66</v>
       </c>
+      <c r="G219">
+        <v>0.16</v>
+      </c>
       <c r="M219" s="6"/>
     </row>
     <row r="220" spans="1:13">
-      <c r="A220" s="14" t="s">
+      <c r="A220" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="B220" s="14" t="s">
+      <c r="B220" s="12" t="s">
         <v>436</v>
       </c>
       <c r="C220" s="12" t="s">
@@ -5782,13 +5980,16 @@
       <c r="D220" s="12">
         <v>0.69</v>
       </c>
+      <c r="G220">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="M220" s="6"/>
     </row>
     <row r="221" spans="1:13">
-      <c r="A221" s="14" t="s">
+      <c r="A221" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="B221" s="14" t="s">
+      <c r="B221" s="12" t="s">
         <v>438</v>
       </c>
       <c r="C221" s="12" t="s">
@@ -5797,13 +5998,16 @@
       <c r="D221" s="12">
         <v>0.83</v>
       </c>
+      <c r="G221">
+        <v>0.63</v>
+      </c>
       <c r="M221" s="6"/>
     </row>
     <row r="222" spans="1:13">
-      <c r="A222" s="14" t="s">
+      <c r="A222" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="B222" s="14" t="s">
+      <c r="B222" s="12" t="s">
         <v>440</v>
       </c>
       <c r="C222" s="12" t="s">
@@ -5812,13 +6016,16 @@
       <c r="D222" s="12">
         <v>0.79</v>
       </c>
+      <c r="G222">
+        <v>0.26</v>
+      </c>
       <c r="M222" s="6"/>
     </row>
     <row r="223" spans="1:13">
-      <c r="A223" s="14" t="s">
+      <c r="A223" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="B223" s="14" t="s">
+      <c r="B223" s="12" t="s">
         <v>442</v>
       </c>
       <c r="C223" s="12" t="s">
@@ -5827,13 +6034,16 @@
       <c r="D223" s="12">
         <v>0.81</v>
       </c>
+      <c r="G223">
+        <v>0.67</v>
+      </c>
       <c r="M223" s="6"/>
     </row>
     <row r="224" spans="1:13">
-      <c r="A224" s="14" t="s">
+      <c r="A224" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="B224" s="14" t="s">
+      <c r="B224" s="12" t="s">
         <v>444</v>
       </c>
       <c r="C224" s="12" t="s">
@@ -5842,13 +6052,16 @@
       <c r="D224" s="12">
         <v>0.74</v>
       </c>
+      <c r="G224">
+        <v>0.37</v>
+      </c>
       <c r="M224" s="6"/>
     </row>
     <row r="225" spans="1:13">
-      <c r="A225" s="14" t="s">
+      <c r="A225" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B225" s="14" t="s">
+      <c r="B225" s="12" t="s">
         <v>445</v>
       </c>
       <c r="C225" s="12" t="s">
@@ -5857,13 +6070,16 @@
       <c r="D225" s="12">
         <v>0.75</v>
       </c>
+      <c r="G225">
+        <v>0.44</v>
+      </c>
       <c r="M225" s="6"/>
     </row>
     <row r="226" spans="1:13">
-      <c r="A226" s="14" t="s">
+      <c r="A226" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B226" s="14" t="s">
+      <c r="B226" s="12" t="s">
         <v>446</v>
       </c>
       <c r="C226" s="12" t="s">
@@ -5872,13 +6088,16 @@
       <c r="D226" s="12">
         <v>0.65</v>
       </c>
+      <c r="G226">
+        <v>0.63</v>
+      </c>
       <c r="M226" s="6"/>
     </row>
     <row r="227" spans="1:13">
-      <c r="A227" s="14" t="s">
+      <c r="A227" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="B227" s="14" t="s">
+      <c r="B227" s="12" t="s">
         <v>448</v>
       </c>
       <c r="C227" s="12" t="s">
@@ -5887,13 +6106,16 @@
       <c r="D227" s="12">
         <v>0.87</v>
       </c>
+      <c r="G227">
+        <v>0.47</v>
+      </c>
       <c r="M227" s="6"/>
     </row>
     <row r="228" spans="1:13">
-      <c r="A228" s="14" t="s">
+      <c r="A228" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="B228" s="14" t="s">
+      <c r="B228" s="12" t="s">
         <v>450</v>
       </c>
       <c r="C228" s="12" t="s">
@@ -5902,7 +6124,180 @@
       <c r="D228" s="12">
         <v>0.7</v>
       </c>
+      <c r="G228">
+        <v>0.19</v>
+      </c>
       <c r="M228" s="6"/>
+    </row>
+    <row r="229" spans="1:13">
+      <c r="A229" t="s">
+        <v>469</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C229" t="s">
+        <v>432</v>
+      </c>
+      <c r="D229" s="4">
+        <v>0</v>
+      </c>
+      <c r="G229">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13">
+      <c r="A230" t="s">
+        <v>177</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C230" t="s">
+        <v>432</v>
+      </c>
+      <c r="D230" s="4">
+        <v>0</v>
+      </c>
+      <c r="G230">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13">
+      <c r="A231" t="s">
+        <v>472</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C231" t="s">
+        <v>432</v>
+      </c>
+      <c r="D231" s="4">
+        <v>0</v>
+      </c>
+      <c r="G231">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13">
+      <c r="A232" t="s">
+        <v>474</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C232" t="s">
+        <v>432</v>
+      </c>
+      <c r="D232" s="4">
+        <v>0</v>
+      </c>
+      <c r="G232">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13">
+      <c r="A233" t="s">
+        <v>476</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C233" t="s">
+        <v>432</v>
+      </c>
+      <c r="D233" s="4">
+        <v>0</v>
+      </c>
+      <c r="G233">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13">
+      <c r="A234" t="s">
+        <v>478</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C234" t="s">
+        <v>432</v>
+      </c>
+      <c r="D234" s="4">
+        <v>0</v>
+      </c>
+      <c r="G234">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13">
+      <c r="A235" t="s">
+        <v>480</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C235" t="s">
+        <v>432</v>
+      </c>
+      <c r="D235" s="4">
+        <v>0</v>
+      </c>
+      <c r="G235">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13">
+      <c r="A236" t="s">
+        <v>482</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C236" t="s">
+        <v>185</v>
+      </c>
+      <c r="D236" s="4">
+        <v>0</v>
+      </c>
+      <c r="G236">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13">
+      <c r="A237" t="s">
+        <v>483</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C237" t="s">
+        <v>185</v>
+      </c>
+      <c r="D237" s="4">
+        <v>0</v>
+      </c>
+      <c r="G237">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13">
+      <c r="A238" t="s">
+        <v>486</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C238" t="s">
+        <v>185</v>
+      </c>
+      <c r="D238" s="4">
+        <v>0</v>
+      </c>
+      <c r="G238">
+        <v>7.0000000000000007E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD060AD-9BC0-1C43-8899-9D71B1F8C74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B04B915-CFE3-7742-ABA3-7DF858030984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1638,7 +1638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1659,6 +1659,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1704,8 +1712,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M238" totalsRowShown="0">
   <autoFilter ref="A1:M238" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M228">
-    <sortCondition ref="C1:C228"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M238">
+    <sortCondition ref="C1:C238"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -2847,10 +2855,10 @@
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="18" t="s">
         <v>103</v>
       </c>
       <c r="C47" s="12" t="s">
@@ -2866,10 +2874,10 @@
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="18" t="s">
         <v>106</v>
       </c>
       <c r="C48" s="12" t="s">
@@ -2885,10 +2893,10 @@
       <c r="M48" s="6"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="18" t="s">
         <v>108</v>
       </c>
       <c r="C49" s="12" t="s">
@@ -2904,10 +2912,10 @@
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="18" t="s">
         <v>110</v>
       </c>
       <c r="C50" s="12" t="s">
@@ -2923,10 +2931,10 @@
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="18" t="s">
         <v>112</v>
       </c>
       <c r="C51" s="12" t="s">
@@ -2942,10 +2950,10 @@
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="18" t="s">
         <v>114</v>
       </c>
       <c r="C52" s="12" t="s">
@@ -2961,10 +2969,10 @@
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="18" t="s">
         <v>116</v>
       </c>
       <c r="C53" s="12" t="s">
@@ -2980,10 +2988,10 @@
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="18" t="s">
         <v>118</v>
       </c>
       <c r="C54" s="12" t="s">
@@ -2998,10 +3006,10 @@
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="18" t="s">
         <v>120</v>
       </c>
       <c r="C55" s="12" t="s">
@@ -3016,10 +3024,10 @@
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="18" t="s">
         <v>122</v>
       </c>
       <c r="C56" s="12" t="s">
@@ -3592,10 +3600,10 @@
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
-      <c r="A88" s="12" t="s">
+      <c r="A88" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="18" t="s">
         <v>184</v>
       </c>
       <c r="C88" s="12" t="s">
@@ -3610,10 +3618,10 @@
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
-      <c r="A89" s="12" t="s">
+      <c r="A89" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="18" t="s">
         <v>187</v>
       </c>
       <c r="C89" s="12" t="s">
@@ -3628,389 +3636,389 @@
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
-      <c r="A90" s="12" t="s">
+      <c r="A90" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="B90" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="C90" t="s">
+        <v>185</v>
+      </c>
+      <c r="D90" s="4">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M90" s="16"/>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B91" s="18" t="s">
         <v>189</v>
-      </c>
-      <c r="C90" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="D90" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="G90">
-        <v>0.47</v>
-      </c>
-      <c r="M90" s="6"/>
-    </row>
-    <row r="91" spans="1:13">
-      <c r="A91" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B91" s="12" t="s">
-        <v>191</v>
       </c>
       <c r="C91" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D91" s="12">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="G91">
-        <v>0.65</v>
+        <v>0.47</v>
       </c>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
-      <c r="A92" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="B92" s="12" t="s">
-        <v>193</v>
+      <c r="A92" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>191</v>
       </c>
       <c r="C92" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D92" s="12">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="G92">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
-      <c r="A93" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="B93" s="12" t="s">
-        <v>195</v>
+      <c r="A93" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>193</v>
       </c>
       <c r="C93" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D93" s="12">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
       <c r="G93">
-        <v>0.79</v>
+        <v>0.42</v>
       </c>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
-      <c r="A94" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B94" s="12" t="s">
-        <v>197</v>
+      <c r="A94" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>195</v>
       </c>
       <c r="C94" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D94" s="12">
+        <v>0.93</v>
+      </c>
+      <c r="G94">
         <v>0.79</v>
       </c>
-      <c r="G94">
-        <v>0.46</v>
-      </c>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
-      <c r="A95" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B95" s="12" t="s">
-        <v>199</v>
+      <c r="A95" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>197</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D95" s="12">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="G95">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C96" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D96" s="12">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="G96">
-        <v>0.28000000000000003</v>
+        <v>0.72</v>
       </c>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D97" s="12">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="G97">
-        <v>0.4</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D98" s="12">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="G98">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C99" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D99" s="12">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="G99">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D100" s="12">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="G100">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D101" s="12">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="G101">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C102" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D102" s="12">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="G102">
-        <v>0.4</v>
+        <v>0.54</v>
       </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
-      <c r="A103" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="B103" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="C103" s="12" t="s">
+      <c r="A103" t="s">
+        <v>482</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C103" t="s">
         <v>185</v>
       </c>
-      <c r="D103" s="12">
-        <v>0.79</v>
+      <c r="D103" s="4">
+        <v>0</v>
       </c>
       <c r="G103">
-        <v>0.44</v>
-      </c>
-      <c r="M103" s="6"/>
+        <v>0.51</v>
+      </c>
+      <c r="M103" s="16"/>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C104" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D104" s="12">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="G104">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="12" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D105" s="12">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="G105">
-        <v>0.75</v>
+        <v>0.44</v>
       </c>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="12" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D106" s="12">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="G106">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="12" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C107" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D107" s="12">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="G107">
-        <v>0.26</v>
+        <v>0.75</v>
       </c>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="12" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D108" s="12">
-        <v>0.94</v>
+        <v>0.82</v>
       </c>
       <c r="G108">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="12" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D109" s="12">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="G109">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D110" s="12">
-        <v>0.75</v>
+        <v>0.94</v>
       </c>
       <c r="G110">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="12" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>185</v>
@@ -4019,268 +4027,268 @@
         <v>0.9</v>
       </c>
       <c r="G111">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="12" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D112" s="12">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="G112">
-        <v>0.63</v>
+        <v>0.39</v>
       </c>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D113" s="12">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G113">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C114" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D114" s="12">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="G114">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="12" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C115" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D115" s="12">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="G115">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="12" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D116" s="12">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="G116">
-        <v>0.26</v>
+        <v>0.54</v>
       </c>
       <c r="M116" s="6"/>
     </row>
     <row r="117" spans="1:13">
-      <c r="A117" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="B117" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="C117" s="12" t="s">
+      <c r="A117" t="s">
+        <v>483</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C117" t="s">
         <v>185</v>
       </c>
-      <c r="D117" s="12">
-        <v>0.69</v>
+      <c r="D117" s="4">
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>0.26</v>
-      </c>
-      <c r="M117" s="6"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M117" s="16"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="12" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C118" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D118" s="12">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="G118">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="M118" s="6"/>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="12" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C119" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D119" s="12">
-        <v>0.75</v>
+        <v>0.96</v>
       </c>
       <c r="G119">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="M119" s="6"/>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="12" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C120" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D120" s="12">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="G120">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="M120" s="6"/>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="12" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C121" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D121" s="12">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="G121">
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="M121" s="6"/>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="12" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C122" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D122" s="12">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G122">
-        <v>0.32</v>
+        <v>0.49</v>
       </c>
       <c r="M122" s="6"/>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="12" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C123" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D123" s="12">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="G123">
-        <v>0.11</v>
+        <v>0.74</v>
       </c>
       <c r="M123" s="6"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="12" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D124" s="12">
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="G124">
-        <v>0.65</v>
+        <v>0.26</v>
       </c>
       <c r="M124" s="6"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="12" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D125" s="12">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="G125">
-        <v>0.28000000000000003</v>
+        <v>0.32</v>
       </c>
       <c r="M125" s="6"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="12" t="s">
-        <v>25</v>
+        <v>253</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>185</v>
@@ -4289,430 +4297,430 @@
         <v>0.83</v>
       </c>
       <c r="G126">
-        <v>0.47</v>
+        <v>0.11</v>
       </c>
       <c r="M126" s="6"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="12" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C127" s="12" t="s">
         <v>185</v>
       </c>
       <c r="D127" s="12">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="G127">
-        <v>0.35</v>
+        <v>0.65</v>
       </c>
       <c r="M127" s="6"/>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="12" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="D128" s="12">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="G128">
-        <v>0.4</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M128" s="6"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="12" t="s">
-        <v>265</v>
+        <v>25</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="D129" s="12">
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="G129">
-        <v>0.56000000000000005</v>
+        <v>0.47</v>
       </c>
       <c r="M129" s="6"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="12" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="D130" s="12">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="G130">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="M130" s="6"/>
     </row>
     <row r="131" spans="1:13">
-      <c r="A131" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="B131" s="12" t="s">
-        <v>270</v>
+      <c r="A131" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B131" s="18" t="s">
+        <v>263</v>
       </c>
       <c r="C131" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D131" s="12">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="G131">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="M131" s="6"/>
     </row>
     <row r="132" spans="1:13">
-      <c r="A132" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="B132" s="12" t="s">
-        <v>272</v>
+      <c r="A132" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B132" s="18" t="s">
+        <v>266</v>
       </c>
       <c r="C132" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D132" s="12">
-        <v>0.9</v>
+        <v>0.81</v>
       </c>
       <c r="G132">
-        <v>0.39</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M132" s="6"/>
     </row>
     <row r="133" spans="1:13">
-      <c r="A133" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="B133" s="12" t="s">
-        <v>274</v>
+      <c r="A133" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B133" s="18" t="s">
+        <v>268</v>
       </c>
       <c r="C133" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D133" s="12">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="G133">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="M133" s="6"/>
     </row>
     <row r="134" spans="1:13">
-      <c r="A134" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="B134" s="12" t="s">
-        <v>276</v>
+      <c r="A134" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="B134" s="18" t="s">
+        <v>270</v>
       </c>
       <c r="C134" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D134" s="12">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="G134">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="M134" s="6"/>
     </row>
     <row r="135" spans="1:13">
-      <c r="A135" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="B135" s="12" t="s">
-        <v>278</v>
+      <c r="A135" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="B135" s="18" t="s">
+        <v>272</v>
       </c>
       <c r="C135" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D135" s="12">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="G135">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="M135" s="6"/>
     </row>
     <row r="136" spans="1:13">
-      <c r="A136" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B136" s="12" t="s">
-        <v>280</v>
+      <c r="A136" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B136" s="18" t="s">
+        <v>274</v>
       </c>
       <c r="C136" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D136" s="12">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="G136">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="M136" s="6"/>
     </row>
     <row r="137" spans="1:13">
-      <c r="A137" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="B137" s="12" t="s">
-        <v>282</v>
+      <c r="A137" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B137" s="18" t="s">
+        <v>276</v>
       </c>
       <c r="C137" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D137" s="12">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="G137">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="M137" s="6"/>
     </row>
     <row r="138" spans="1:13">
-      <c r="A138" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B138" s="12" t="s">
-        <v>283</v>
+      <c r="A138" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="B138" s="18" t="s">
+        <v>278</v>
       </c>
       <c r="C138" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D138" s="12">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="G138">
-        <v>0.16</v>
+        <v>0.51</v>
       </c>
       <c r="M138" s="6"/>
     </row>
     <row r="139" spans="1:13">
-      <c r="A139" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="B139" s="12" t="s">
-        <v>285</v>
+      <c r="A139" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B139" s="18" t="s">
+        <v>280</v>
       </c>
       <c r="C139" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D139" s="12">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="G139">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="M139" s="6"/>
     </row>
     <row r="140" spans="1:13">
-      <c r="A140" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="B140" s="12" t="s">
-        <v>287</v>
+      <c r="A140" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="B140" s="18" t="s">
+        <v>282</v>
       </c>
       <c r="C140" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D140" s="12">
-        <v>0.87</v>
+        <v>0.68</v>
       </c>
       <c r="G140">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M140" s="6"/>
     </row>
     <row r="141" spans="1:13">
-      <c r="A141" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="B141" s="12" t="s">
-        <v>289</v>
+      <c r="A141" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B141" s="18" t="s">
+        <v>283</v>
       </c>
       <c r="C141" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D141" s="12">
-        <v>0.94</v>
+        <v>0.73</v>
       </c>
       <c r="G141">
-        <v>0.75</v>
+        <v>0.16</v>
       </c>
       <c r="M141" s="6"/>
     </row>
     <row r="142" spans="1:13">
-      <c r="A142" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B142" s="12" t="s">
-        <v>291</v>
+      <c r="A142" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="B142" s="18" t="s">
+        <v>285</v>
       </c>
       <c r="C142" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D142" s="12">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G142">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="M142" s="6"/>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="12" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C143" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D143" s="12">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="G143">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="M143" s="6"/>
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="12" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D144" s="12">
-        <v>0.79</v>
+        <v>0.94</v>
       </c>
       <c r="G144">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="M144" s="6"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="12" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D145" s="12">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="G145">
-        <v>0.3</v>
+        <v>0.63</v>
       </c>
       <c r="M145" s="6"/>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="12" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C146" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D146" s="12">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="G146">
-        <v>0.63</v>
+        <v>0.21</v>
       </c>
       <c r="M146" s="6"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="12" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C147" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D147" s="12">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="G147">
-        <v>0.86</v>
+        <v>0.25</v>
       </c>
       <c r="M147" s="6"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="12" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C148" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D148" s="12">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="G148">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="M148" s="6"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C149" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D149" s="12">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="G149">
-        <v>0.49</v>
+        <v>0.63</v>
       </c>
       <c r="M149" s="6"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="12" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C150" s="12" t="s">
         <v>264</v>
@@ -4721,106 +4729,106 @@
         <v>0.77</v>
       </c>
       <c r="G150">
-        <v>0.44</v>
+        <v>0.86</v>
       </c>
       <c r="M150" s="6"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="12" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C151" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D151" s="12">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="G151">
-        <v>0.65</v>
+        <v>0.47</v>
       </c>
       <c r="M151" s="6"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="12" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C152" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D152" s="12">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="G152">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="M152" s="6"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="12" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C153" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D153" s="12">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="G153">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="M153" s="6"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="12" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C154" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D154" s="12">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="G154">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="M154" s="6"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="12" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C155" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D155" s="12">
-        <v>0.66</v>
+        <v>0.84</v>
       </c>
       <c r="G155">
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="M155" s="6"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="12" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C156" s="12" t="s">
         <v>264</v>
@@ -4829,718 +4837,718 @@
         <v>0.88</v>
       </c>
       <c r="G156">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="M156" s="6"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="12" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C157" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D157" s="12">
-        <v>0.94</v>
+        <v>0.8</v>
       </c>
       <c r="G157">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="M157" s="6"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="12" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C158" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D158" s="12">
-        <v>0.95</v>
+        <v>0.66</v>
       </c>
       <c r="G158">
-        <v>0.33</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M158" s="6"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="12" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C159" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D159" s="12">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="G159">
-        <v>0.18</v>
+        <v>0.68</v>
       </c>
       <c r="M159" s="6"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="12" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C160" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D160" s="12">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="G160">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="M160" s="6"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="12" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C161" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D161" s="12">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="G161">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="M161" s="6"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="12" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C162" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D162" s="12">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="G162">
-        <v>0.56000000000000005</v>
+        <v>0.18</v>
       </c>
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="12" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C163" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D163" s="12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G163">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="12" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C164" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D164" s="12">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="G164">
-        <v>0.3</v>
+        <v>0.63</v>
       </c>
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="12" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C165" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D165" s="12">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="G165">
-        <v>0.25</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M165" s="6"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="12" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C166" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D166" s="12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G166">
-        <v>0.39</v>
+        <v>0.54</v>
       </c>
       <c r="M166" s="6"/>
     </row>
     <row r="167" spans="1:13">
-      <c r="A167" t="s">
-        <v>467</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C167" t="s">
+      <c r="A167" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="B167" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="C167" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="D167" s="4">
-        <v>0</v>
+      <c r="D167" s="12">
+        <v>0.85</v>
       </c>
       <c r="G167">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="M167" s="6"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="12" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C168" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D168" s="12">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="G168">
+        <v>0.25</v>
+      </c>
+      <c r="M168" s="6"/>
+    </row>
+    <row r="169" spans="1:13">
+      <c r="A169" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D169" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="G169">
+        <v>0.39</v>
+      </c>
+      <c r="M169" s="6"/>
+    </row>
+    <row r="170" spans="1:13">
+      <c r="A170" t="s">
+        <v>467</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C170" t="s">
+        <v>264</v>
+      </c>
+      <c r="D170" s="4">
+        <v>0</v>
+      </c>
+      <c r="G170">
         <v>0.35</v>
-      </c>
-      <c r="M168" s="6"/>
-    </row>
-    <row r="169" spans="1:13">
-      <c r="A169" t="s">
-        <v>465</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="C169" t="s">
-        <v>264</v>
-      </c>
-      <c r="D169" s="4">
-        <v>0</v>
-      </c>
-      <c r="G169">
-        <v>0.33</v>
-      </c>
-      <c r="M169" s="6"/>
-    </row>
-    <row r="170" spans="1:13">
-      <c r="A170" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="B170" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="C170" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="D170" s="12">
-        <v>0.69</v>
-      </c>
-      <c r="G170">
-        <v>0.12</v>
       </c>
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="12" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C171" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D171" s="12">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="G171">
-        <v>0.46</v>
+        <v>0.35</v>
       </c>
       <c r="M171" s="6"/>
     </row>
     <row r="172" spans="1:13">
-      <c r="A172" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B172" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="C172" s="12" t="s">
+      <c r="A172" t="s">
+        <v>465</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C172" t="s">
         <v>264</v>
       </c>
-      <c r="D172" s="12">
-        <v>0.73</v>
+      <c r="D172" s="4">
+        <v>0</v>
       </c>
       <c r="G172">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="M172" s="6"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="12" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C173" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D173" s="12">
-        <v>0.86</v>
+        <v>0.69</v>
       </c>
       <c r="G173">
-        <v>0.42</v>
+        <v>0.12</v>
       </c>
       <c r="M173" s="6"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="12" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C174" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D174" s="12">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="G174">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="M174" s="6"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="12" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C175" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D175" s="12">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="G175">
-        <v>0.53</v>
+        <v>0.19</v>
       </c>
       <c r="M175" s="6"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="12" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C176" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D176" s="12">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="G176">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="M176" s="6"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="12" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C177" s="12" t="s">
         <v>264</v>
       </c>
       <c r="D177" s="12">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="G177">
-        <v>0.32</v>
+        <v>0.61</v>
       </c>
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="12" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>360</v>
+        <v>264</v>
       </c>
       <c r="D178" s="12">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="G178">
-        <v>0.26</v>
+        <v>0.53</v>
       </c>
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
-      <c r="A179" t="s">
-        <v>458</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C179" t="s">
-        <v>360</v>
-      </c>
-      <c r="D179" s="4">
-        <v>0</v>
+      <c r="A179" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B179" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C179" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D179" s="12">
+        <v>0.61</v>
       </c>
       <c r="G179">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="12" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>360</v>
+        <v>264</v>
       </c>
       <c r="D180" s="12">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G180">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13">
-      <c r="A181" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="B181" s="12" t="s">
-        <v>364</v>
+      <c r="A181" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="B181" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="C181" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D181" s="12">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="G181">
-        <v>0.63</v>
+        <v>0.26</v>
       </c>
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13">
-      <c r="A182" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B182" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="C182" s="12" t="s">
+      <c r="A182" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="B182" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="C182" t="s">
         <v>360</v>
       </c>
-      <c r="D182" s="12">
-        <v>0.8</v>
+      <c r="D182" s="4">
+        <v>0</v>
       </c>
       <c r="G182">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="M182" s="6"/>
     </row>
     <row r="183" spans="1:13">
-      <c r="A183" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="B183" s="12" t="s">
-        <v>368</v>
+      <c r="A183" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="B183" s="18" t="s">
+        <v>362</v>
       </c>
       <c r="C183" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D183" s="12">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="G183">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="12" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C184" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D184" s="12">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="G184">
-        <v>0.42</v>
+        <v>0.63</v>
       </c>
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="12" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="B185" s="12" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C185" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D185" s="12">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="G185">
-        <v>0.57999999999999996</v>
+        <v>0.39</v>
       </c>
       <c r="M185" s="6"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="12" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C186" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D186" s="12">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="G186">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="12" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C187" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D187" s="12">
-        <v>0.64</v>
+        <v>0.87</v>
       </c>
       <c r="G187">
-        <v>0.04</v>
+        <v>0.42</v>
       </c>
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
-      <c r="A188" t="s">
-        <v>454</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C188" t="s">
+      <c r="A188" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B188" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C188" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="D188" s="4">
-        <v>0</v>
+      <c r="D188" s="12">
+        <v>0.81</v>
       </c>
       <c r="G188">
-        <v>0.26</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="12" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B189" s="12" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C189" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D189" s="12">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="G189">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="12" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B190" s="12" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C190" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D190" s="12">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="G190">
-        <v>0.51</v>
+        <v>0.04</v>
       </c>
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13">
-      <c r="A191" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="B191" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="C191" s="12" t="s">
+      <c r="A191" t="s">
+        <v>454</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C191" t="s">
         <v>360</v>
       </c>
-      <c r="D191" s="12">
-        <v>0.81</v>
+      <c r="D191" s="4">
+        <v>0</v>
       </c>
       <c r="G191">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="12" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C192" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D192" s="12">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="G192">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="12" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B193" s="12" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C193" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D193" s="12">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="G193">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="12" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B194" s="12" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C194" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D194" s="12">
-        <v>0.91</v>
+        <v>0.81</v>
       </c>
       <c r="G194">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="12" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B195" s="12" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C195" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D195" s="12">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="G195">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="12" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C196" s="12" t="s">
         <v>360</v>
@@ -5549,22 +5557,22 @@
         <v>0.84</v>
       </c>
       <c r="G196">
-        <v>0.32</v>
+        <v>0.67</v>
       </c>
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="12" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B197" s="12" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C197" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D197" s="12">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="G197">
         <v>0.37</v>
@@ -5572,191 +5580,191 @@
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
-      <c r="A198" t="s">
-        <v>462</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C198" t="s">
+      <c r="A198" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B198" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="C198" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="D198" s="4">
-        <v>0</v>
+      <c r="D198" s="12">
+        <v>0.83</v>
       </c>
       <c r="G198">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="12" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B199" s="12" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D199" s="12">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="G199">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="12" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C200" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D200" s="12">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="G200">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
-      <c r="A201" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="B201" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="C201" s="12" t="s">
+      <c r="A201" t="s">
+        <v>462</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C201" t="s">
         <v>360</v>
       </c>
-      <c r="D201" s="12">
-        <v>0.76</v>
+      <c r="D201" s="4">
+        <v>0</v>
       </c>
       <c r="G201">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="12" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B202" s="12" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C202" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D202" s="12">
-        <v>0.59</v>
+        <v>0.88</v>
       </c>
       <c r="G202">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="M202" s="6"/>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="12" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B203" s="12" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C203" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D203" s="12">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="G203">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="M203" s="6"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="12" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B204" s="12" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C204" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D204" s="12">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="G204">
-        <v>0.75</v>
+        <v>0.39</v>
       </c>
       <c r="M204" s="6"/>
     </row>
     <row r="205" spans="1:13">
-      <c r="A205" t="s">
-        <v>456</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C205" t="s">
+      <c r="A205" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B205" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="C205" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="D205" s="4">
-        <v>0</v>
+      <c r="D205" s="12">
+        <v>0.59</v>
       </c>
       <c r="G205">
-        <v>0.05</v>
+        <v>0.65</v>
       </c>
       <c r="M205" s="6"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="12" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B206" s="12" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D206" s="12">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="G206">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="M206" s="6"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="12" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B207" s="12" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C207" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D207" s="12">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="G207">
-        <v>0.32</v>
+        <v>0.75</v>
       </c>
       <c r="M207" s="6"/>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C208" t="s">
         <v>360</v>
@@ -5765,250 +5773,250 @@
         <v>0</v>
       </c>
       <c r="G208">
-        <v>0.44</v>
+        <v>0.05</v>
       </c>
       <c r="M208" s="6"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="12" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B209" s="12" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C209" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D209" s="12">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="G209">
-        <v>0.68</v>
+        <v>0.53</v>
       </c>
       <c r="M209" s="6"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="12" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B210" s="12" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C210" s="12" t="s">
         <v>360</v>
       </c>
       <c r="D210" s="12">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="G210">
-        <v>0.56000000000000005</v>
+        <v>0.32</v>
       </c>
       <c r="M210" s="6"/>
     </row>
     <row r="211" spans="1:13">
-      <c r="A211" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="B211" s="12" t="s">
-        <v>416</v>
-      </c>
-      <c r="C211" s="12" t="s">
+      <c r="A211" t="s">
+        <v>460</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C211" t="s">
         <v>360</v>
       </c>
-      <c r="D211" s="12">
-        <v>0.94</v>
+      <c r="D211" s="4">
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>0.65</v>
+        <v>0.44</v>
       </c>
       <c r="M211" s="6"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="12" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B212" s="12" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>419</v>
+        <v>360</v>
       </c>
       <c r="D212" s="12">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="G212">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="M212" s="6"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="12" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B213" s="12" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>419</v>
+        <v>360</v>
       </c>
       <c r="D213" s="12">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="G213">
-        <v>0.32</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M213" s="6"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="12" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="B214" s="12" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>419</v>
+        <v>360</v>
       </c>
       <c r="D214" s="12">
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="G214">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="M214" s="6"/>
     </row>
     <row r="215" spans="1:13">
-      <c r="A215" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="B215" s="12" t="s">
-        <v>425</v>
+      <c r="A215" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="B215" s="18" t="s">
+        <v>418</v>
       </c>
       <c r="C215" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D215" s="12">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="G215">
-        <v>0.11</v>
+        <v>0.79</v>
       </c>
       <c r="M215" s="6"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="12" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B216" s="12" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C216" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D216" s="12">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="G216">
-        <v>0.54</v>
+        <v>0.32</v>
       </c>
       <c r="M216" s="6"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="12" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B217" s="12" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C217" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D217" s="12">
-        <v>0.89</v>
+        <v>0.69</v>
       </c>
       <c r="G217">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="M217" s="6"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="12" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B218" s="12" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D218" s="12">
-        <v>0.79</v>
+        <v>0.67</v>
       </c>
       <c r="G218">
-        <v>0.26</v>
+        <v>0.11</v>
       </c>
       <c r="M218" s="6"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="12" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B219" s="12" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D219" s="12">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="G219">
-        <v>0.16</v>
+        <v>0.54</v>
       </c>
       <c r="M219" s="6"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="12" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B220" s="12" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C220" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="D220" s="12">
+        <v>0.89</v>
+      </c>
+      <c r="G220">
+        <v>0.61</v>
+      </c>
+      <c r="M220" s="6"/>
+    </row>
+    <row r="221" spans="1:13">
+      <c r="A221" s="19" t="s">
+        <v>472</v>
+      </c>
+      <c r="B221" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="C221" t="s">
         <v>432</v>
       </c>
-      <c r="D220" s="12">
-        <v>0.69</v>
-      </c>
-      <c r="G220">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="M220" s="6"/>
-    </row>
-    <row r="221" spans="1:13">
-      <c r="A221" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="B221" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="C221" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="D221" s="12">
-        <v>0.83</v>
+      <c r="D221" s="4">
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>0.63</v>
-      </c>
-      <c r="M221" s="6"/>
+        <v>0.33</v>
+      </c>
+      <c r="M221" s="16"/>
     </row>
     <row r="222" spans="1:13">
-      <c r="A222" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="B222" s="12" t="s">
-        <v>440</v>
+      <c r="A222" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="B222" s="18" t="s">
+        <v>431</v>
       </c>
       <c r="C222" s="12" t="s">
         <v>432</v>
@@ -6022,153 +6030,155 @@
       <c r="M222" s="6"/>
     </row>
     <row r="223" spans="1:13">
-      <c r="A223" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="B223" s="12" t="s">
-        <v>442</v>
+      <c r="A223" s="18" t="s">
+        <v>433</v>
+      </c>
+      <c r="B223" s="18" t="s">
+        <v>434</v>
       </c>
       <c r="C223" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D223" s="12">
-        <v>0.81</v>
+        <v>0.66</v>
       </c>
       <c r="G223">
-        <v>0.67</v>
+        <v>0.16</v>
       </c>
       <c r="M223" s="6"/>
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="12" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="B224" s="12" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C224" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D224" s="12">
-        <v>0.74</v>
+        <v>0.69</v>
       </c>
       <c r="G224">
-        <v>0.37</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M224" s="6"/>
     </row>
     <row r="225" spans="1:13">
-      <c r="A225" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B225" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="C225" s="12" t="s">
+      <c r="A225" t="s">
+        <v>476</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C225" t="s">
         <v>432</v>
       </c>
-      <c r="D225" s="12">
-        <v>0.75</v>
+      <c r="D225" s="4">
+        <v>0</v>
       </c>
       <c r="G225">
-        <v>0.44</v>
-      </c>
-      <c r="M225" s="6"/>
+        <v>0.16</v>
+      </c>
+      <c r="M225" s="16"/>
     </row>
     <row r="226" spans="1:13">
-      <c r="A226" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B226" s="12" t="s">
-        <v>446</v>
-      </c>
-      <c r="C226" s="12" t="s">
+      <c r="A226" t="s">
+        <v>469</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C226" t="s">
         <v>432</v>
       </c>
-      <c r="D226" s="12">
-        <v>0.65</v>
+      <c r="D226" s="4">
+        <v>0</v>
       </c>
       <c r="G226">
-        <v>0.63</v>
-      </c>
-      <c r="M226" s="6"/>
+        <v>0.26</v>
+      </c>
+      <c r="M226" s="16"/>
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="12" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="B227" s="12" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C227" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D227" s="12">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="G227">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="M227" s="6"/>
     </row>
     <row r="228" spans="1:13">
       <c r="A228" s="12" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="B228" s="12" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C228" s="12" t="s">
         <v>432</v>
       </c>
       <c r="D228" s="12">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="G228">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="M228" s="6"/>
     </row>
     <row r="229" spans="1:13">
-      <c r="A229" t="s">
-        <v>469</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="C229" t="s">
+      <c r="A229" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="B229" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="C229" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="D229" s="4">
-        <v>0</v>
+      <c r="D229" s="12">
+        <v>0.81</v>
       </c>
       <c r="G229">
-        <v>0.26</v>
-      </c>
+        <v>0.67</v>
+      </c>
+      <c r="M229" s="17"/>
     </row>
     <row r="230" spans="1:13">
-      <c r="A230" t="s">
-        <v>177</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C230" t="s">
+      <c r="A230" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="B230" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="C230" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="D230" s="4">
-        <v>0</v>
+      <c r="D230" s="12">
+        <v>0.74</v>
       </c>
       <c r="G230">
-        <v>0.49</v>
-      </c>
+        <v>0.37</v>
+      </c>
+      <c r="M230" s="17"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C231" t="s">
         <v>432</v>
@@ -6177,49 +6187,52 @@
         <v>0</v>
       </c>
       <c r="G231">
-        <v>0.33</v>
-      </c>
+        <v>0.35</v>
+      </c>
+      <c r="M231" s="19"/>
     </row>
     <row r="232" spans="1:13">
-      <c r="A232" t="s">
-        <v>474</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="C232" t="s">
+      <c r="A232" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B232" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="C232" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="D232" s="4">
-        <v>0</v>
+      <c r="D232" s="12">
+        <v>0.75</v>
       </c>
       <c r="G232">
-        <v>0.54</v>
-      </c>
+        <v>0.44</v>
+      </c>
+      <c r="M232" s="17"/>
     </row>
     <row r="233" spans="1:13">
-      <c r="A233" t="s">
-        <v>476</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="C233" t="s">
+      <c r="A233" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B233" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="C233" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="D233" s="4">
-        <v>0</v>
+      <c r="D233" s="12">
+        <v>0.65</v>
       </c>
       <c r="G233">
-        <v>0.16</v>
-      </c>
+        <v>0.63</v>
+      </c>
+      <c r="M233" s="17"/>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C234" t="s">
         <v>432</v>
@@ -6228,15 +6241,16 @@
         <v>0</v>
       </c>
       <c r="G234">
-        <v>0.42</v>
-      </c>
+        <v>0.54</v>
+      </c>
+      <c r="M234" s="19"/>
     </row>
     <row r="235" spans="1:13">
       <c r="A235" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C235" t="s">
         <v>432</v>
@@ -6245,59 +6259,63 @@
         <v>0</v>
       </c>
       <c r="G235">
-        <v>0.35</v>
-      </c>
+        <v>0.42</v>
+      </c>
+      <c r="M235" s="19"/>
     </row>
     <row r="236" spans="1:13">
       <c r="A236" t="s">
-        <v>482</v>
+        <v>177</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="C236" t="s">
-        <v>185</v>
+        <v>432</v>
       </c>
       <c r="D236" s="4">
         <v>0</v>
       </c>
       <c r="G236">
-        <v>0.51</v>
-      </c>
+        <v>0.49</v>
+      </c>
+      <c r="M236" s="19"/>
     </row>
     <row r="237" spans="1:13">
-      <c r="A237" t="s">
-        <v>483</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C237" t="s">
-        <v>185</v>
-      </c>
-      <c r="D237" s="4">
-        <v>0</v>
+      <c r="A237" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="B237" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D237" s="12">
+        <v>0.87</v>
       </c>
       <c r="G237">
-        <v>0.14000000000000001</v>
-      </c>
+        <v>0.47</v>
+      </c>
+      <c r="M237" s="17"/>
     </row>
     <row r="238" spans="1:13">
-      <c r="A238" t="s">
-        <v>486</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="C238" t="s">
-        <v>185</v>
-      </c>
-      <c r="D238" s="4">
-        <v>0</v>
+      <c r="A238" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="B238" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="C238" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D238" s="12">
+        <v>0.7</v>
       </c>
       <c r="G238">
-        <v>7.0000000000000007E-2</v>
-      </c>
+        <v>0.19</v>
+      </c>
+      <c r="M238" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B04B915-CFE3-7742-ABA3-7DF858030984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40CA324-4176-F748-9BC3-746BEA0EB90C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -278,9 +278,6 @@
     <t>NIKISI</t>
   </si>
   <si>
-    <t>CHINYAMA</t>
-  </si>
-  <si>
     <t>SITOTOMBE</t>
   </si>
   <si>
@@ -386,9 +383,6 @@
     <t>DONDO</t>
   </si>
   <si>
-    <t>H50348J</t>
-  </si>
-  <si>
     <t>Dube</t>
   </si>
   <si>
@@ -1500,6 +1494,12 @@
   </si>
   <si>
     <t>H250391C</t>
+  </si>
+  <si>
+    <t>H250348J</t>
+  </si>
+  <si>
+    <t>CHIYAMA</t>
   </si>
 </sst>
 </file>
@@ -2133,6 +2133,9 @@
         <v>0.86</v>
       </c>
       <c r="H3" s="5"/>
+      <c r="J3">
+        <v>0.68</v>
+      </c>
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13">
@@ -2206,6 +2209,9 @@
         <v>0.82</v>
       </c>
       <c r="H7" s="5"/>
+      <c r="J7">
+        <v>0.48</v>
+      </c>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
@@ -2222,6 +2228,9 @@
         <v>0</v>
       </c>
       <c r="H8" s="5"/>
+      <c r="J8">
+        <v>0.8</v>
+      </c>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
@@ -2238,6 +2247,9 @@
         <v>0.75</v>
       </c>
       <c r="H9" s="5"/>
+      <c r="J9">
+        <v>0.68</v>
+      </c>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
@@ -2273,6 +2285,9 @@
         <v>0</v>
       </c>
       <c r="H11" s="5"/>
+      <c r="J11">
+        <v>0</v>
+      </c>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13">
@@ -2289,6 +2304,9 @@
         <v>0.76</v>
       </c>
       <c r="H12" s="5"/>
+      <c r="J12">
+        <v>0.48</v>
+      </c>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13">
@@ -2324,6 +2342,9 @@
         <v>0.75</v>
       </c>
       <c r="H14" s="5"/>
+      <c r="J14">
+        <v>0.48</v>
+      </c>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13">
@@ -2359,6 +2380,9 @@
         <v>0.75</v>
       </c>
       <c r="H16" s="5"/>
+      <c r="J16">
+        <v>0.68</v>
+      </c>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
@@ -2375,6 +2399,9 @@
         <v>0</v>
       </c>
       <c r="H17" s="5"/>
+      <c r="J17">
+        <v>0.48</v>
+      </c>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13">
@@ -2410,6 +2437,9 @@
         <v>0.68</v>
       </c>
       <c r="H19" s="5"/>
+      <c r="J19">
+        <v>0.48</v>
+      </c>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
@@ -2445,6 +2475,9 @@
         <v>0.78</v>
       </c>
       <c r="H21" s="5"/>
+      <c r="J21">
+        <v>0.68</v>
+      </c>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
@@ -2461,6 +2494,9 @@
         <v>0.82</v>
       </c>
       <c r="H22" s="5"/>
+      <c r="J22">
+        <v>0.68</v>
+      </c>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
@@ -2477,6 +2513,9 @@
         <v>0.7</v>
       </c>
       <c r="H23" s="5"/>
+      <c r="J23">
+        <v>0.68</v>
+      </c>
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
@@ -2512,6 +2551,9 @@
         <v>0.67</v>
       </c>
       <c r="H25" s="5"/>
+      <c r="J25">
+        <v>0.8</v>
+      </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
@@ -2547,6 +2589,9 @@
         <v>0.83</v>
       </c>
       <c r="H27" s="5"/>
+      <c r="J27">
+        <v>0.8</v>
+      </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
@@ -2582,6 +2627,9 @@
         <v>0</v>
       </c>
       <c r="H29" s="5"/>
+      <c r="J29">
+        <v>0.8</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -2598,6 +2646,9 @@
         <v>0.86</v>
       </c>
       <c r="H30" s="5"/>
+      <c r="J30">
+        <v>0.48</v>
+      </c>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
@@ -2605,78 +2656,93 @@
         <v>72</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D31" s="4">
         <v>0.79</v>
       </c>
       <c r="H31" s="5"/>
+      <c r="J31">
+        <v>0.24</v>
+      </c>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="7" t="s">
-        <v>80</v>
+        <v>487</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D32" s="4">
         <v>0.81</v>
       </c>
       <c r="H32" s="5"/>
+      <c r="J32">
+        <v>0.8</v>
+      </c>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D33" s="4">
         <v>0.84</v>
       </c>
       <c r="H33" s="5"/>
+      <c r="J33">
+        <v>0.8</v>
+      </c>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="15" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D34" s="4">
         <v>0.65</v>
       </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
       <c r="M34" s="6"/>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D35" s="4">
         <v>0</v>
       </c>
       <c r="H35" s="5"/>
+      <c r="J35">
+        <v>0</v>
+      </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
@@ -2684,29 +2750,35 @@
         <v>74</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D36" s="4">
         <v>0.84</v>
       </c>
       <c r="H36" s="5"/>
+      <c r="J36">
+        <v>0.24</v>
+      </c>
       <c r="M36" s="6"/>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="15" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D37" s="4">
         <v>0.66</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
       </c>
       <c r="M37" s="6"/>
     </row>
@@ -2715,15 +2787,18 @@
         <v>77</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D38" s="4">
         <v>0</v>
       </c>
       <c r="H38" s="5"/>
+      <c r="J38">
+        <v>0</v>
+      </c>
       <c r="M38" s="6"/>
     </row>
     <row r="39" spans="1:13">
@@ -2731,31 +2806,37 @@
         <v>75</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D39" s="4">
         <v>0.73</v>
       </c>
       <c r="H39" s="5"/>
+      <c r="J39">
+        <v>0.8</v>
+      </c>
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" t="s">
         <v>100</v>
-      </c>
-      <c r="C40" t="s">
-        <v>101</v>
       </c>
       <c r="D40" s="4">
         <v>0.75</v>
       </c>
       <c r="H40" s="5"/>
+      <c r="J40">
+        <v>0.8</v>
+      </c>
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13">
@@ -2763,47 +2844,56 @@
         <v>79</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D41" s="4">
         <v>0.77</v>
       </c>
       <c r="H41" s="5"/>
+      <c r="J41">
+        <v>0.24</v>
+      </c>
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D42" s="4">
         <v>0.7</v>
       </c>
       <c r="H42" s="5"/>
+      <c r="J42">
+        <v>0.24</v>
+      </c>
       <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D43" s="4">
         <v>0.64</v>
       </c>
       <c r="H43" s="5"/>
+      <c r="J43">
+        <v>0.8</v>
+      </c>
       <c r="M43" s="6"/>
     </row>
     <row r="44" spans="1:13">
@@ -2811,15 +2901,18 @@
         <v>78</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D44" s="4">
         <v>0.77</v>
       </c>
       <c r="H44" s="5"/>
+      <c r="J44">
+        <v>0.24</v>
+      </c>
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
@@ -2827,15 +2920,18 @@
         <v>76</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D45" s="4">
         <v>0.91</v>
       </c>
       <c r="H45" s="5"/>
+      <c r="J45">
+        <v>0.24</v>
+      </c>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
@@ -2843,26 +2939,29 @@
         <v>73</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D46" s="4">
         <v>0.67</v>
       </c>
       <c r="H46" s="5"/>
+      <c r="J46">
+        <v>0.8</v>
+      </c>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="C47" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>104</v>
       </c>
       <c r="D47" s="12">
         <v>0.79</v>
@@ -2875,13 +2974,13 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B48" s="18" t="s">
-        <v>106</v>
-      </c>
       <c r="C48" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D48" s="12">
         <v>0.89</v>
@@ -2894,13 +2993,13 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B49" s="18" t="s">
-        <v>108</v>
-      </c>
       <c r="C49" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D49" s="12">
         <v>0.9</v>
@@ -2913,13 +3012,13 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B50" s="18" t="s">
-        <v>110</v>
-      </c>
       <c r="C50" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D50" s="12">
         <v>0.85</v>
@@ -2932,13 +3031,13 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="B51" s="18" t="s">
-        <v>112</v>
-      </c>
       <c r="C51" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D51" s="12">
         <v>0.85</v>
@@ -2951,13 +3050,13 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B52" s="18" t="s">
-        <v>114</v>
-      </c>
       <c r="C52" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D52" s="12">
         <v>0.77</v>
@@ -2970,13 +3069,13 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>116</v>
+        <v>486</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D53" s="12">
         <v>0.86</v>
@@ -2989,13 +3088,13 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D54" s="12">
         <v>0.75</v>
@@ -3007,13 +3106,13 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D55" s="12">
         <v>0.69</v>
@@ -3025,13 +3124,13 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D56" s="12">
         <v>0.71</v>
@@ -3043,13 +3142,13 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D57" s="12">
         <v>0.9</v>
@@ -3061,13 +3160,13 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D58" s="12">
         <v>0.91</v>
@@ -3079,13 +3178,13 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D59" s="12">
         <v>0.82</v>
@@ -3097,13 +3196,13 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D60" s="12">
         <v>0.75</v>
@@ -3115,13 +3214,13 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61" s="12">
         <v>0.76</v>
@@ -3133,13 +3232,13 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D62" s="12">
         <v>0.72</v>
@@ -3151,13 +3250,13 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D63" s="12">
         <v>0.86</v>
@@ -3169,13 +3268,13 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" s="12">
         <v>0.76</v>
@@ -3187,13 +3286,13 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D65" s="12">
         <v>0.88</v>
@@ -3205,13 +3304,13 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D66" s="12">
         <v>0.85</v>
@@ -3223,13 +3322,13 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D67" s="12">
         <v>0.82</v>
@@ -3241,13 +3340,13 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D68" s="12">
         <v>0.78</v>
@@ -3259,13 +3358,13 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D69" s="12">
         <v>0.7</v>
@@ -3277,13 +3376,13 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D70" s="12">
         <v>0.83</v>
@@ -3295,13 +3394,13 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D71" s="12">
         <v>0.84</v>
@@ -3313,13 +3412,13 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D72" s="12">
         <v>0.84</v>
@@ -3331,13 +3430,13 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D73" s="12">
         <v>0.75</v>
@@ -3349,13 +3448,13 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D74" s="12">
         <v>0.89</v>
@@ -3367,13 +3466,13 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D75" s="12">
         <v>0.88</v>
@@ -3385,13 +3484,13 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D76" s="12">
         <v>0.68</v>
@@ -3403,13 +3502,13 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D77" s="12">
         <v>0.78</v>
@@ -3421,13 +3520,13 @@
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D78" s="12">
         <v>0.84</v>
@@ -3439,13 +3538,13 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D79" s="12">
         <v>0.84</v>
@@ -3457,13 +3556,13 @@
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D80" s="12">
         <v>0.74</v>
@@ -3475,13 +3574,13 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C81" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D81" s="4">
         <v>0</v>
@@ -3493,13 +3592,13 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D82" s="12">
         <v>0.81</v>
@@ -3511,13 +3610,13 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D83" s="12">
         <v>0.71</v>
@@ -3529,13 +3628,13 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D84" s="12">
         <v>0.76</v>
@@ -3547,13 +3646,13 @@
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D85" s="12">
         <v>0.81</v>
@@ -3565,13 +3664,13 @@
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D86" s="12">
         <v>0.83</v>
@@ -3583,13 +3682,13 @@
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D87" s="12">
         <v>0.85</v>
@@ -3601,13 +3700,13 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C88" s="12" t="s">
         <v>183</v>
-      </c>
-      <c r="B88" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>185</v>
       </c>
       <c r="D88" s="12">
         <v>0.75</v>
@@ -3619,13 +3718,13 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="18" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D89" s="12">
         <v>0.75</v>
@@ -3637,13 +3736,13 @@
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="19" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B90" s="20" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C90" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D90" s="4">
         <v>0</v>
@@ -3655,13 +3754,13 @@
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D91" s="12">
         <v>0.82</v>
@@ -3673,13 +3772,13 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="18" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B92" s="18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D92" s="12">
         <v>0.75</v>
@@ -3691,13 +3790,13 @@
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="18" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D93" s="12">
         <v>0.77</v>
@@ -3709,13 +3808,13 @@
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="18" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B94" s="18" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D94" s="12">
         <v>0.93</v>
@@ -3727,13 +3826,13 @@
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D95" s="12">
         <v>0.79</v>
@@ -3745,13 +3844,13 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D96" s="12">
         <v>0.93</v>
@@ -3763,13 +3862,13 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D97" s="12">
         <v>0.83</v>
@@ -3781,13 +3880,13 @@
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D98" s="12">
         <v>0.9</v>
@@ -3799,13 +3898,13 @@
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D99" s="12">
         <v>0.83</v>
@@ -3817,13 +3916,13 @@
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D100" s="12">
         <v>0.85</v>
@@ -3835,13 +3934,13 @@
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D101" s="12">
         <v>0.89</v>
@@ -3853,13 +3952,13 @@
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D102" s="12">
         <v>0.85</v>
@@ -3871,13 +3970,13 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" t="s">
+        <v>480</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>484</v>
-      </c>
       <c r="C103" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D103" s="4">
         <v>0</v>
@@ -3889,13 +3988,13 @@
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D104" s="12">
         <v>0.86</v>
@@ -3907,13 +4006,13 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D105" s="12">
         <v>0.79</v>
@@ -3925,13 +4024,13 @@
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D106" s="12">
         <v>0.76</v>
@@ -3943,13 +4042,13 @@
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D107" s="12">
         <v>0.84</v>
@@ -3961,13 +4060,13 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D108" s="12">
         <v>0.82</v>
@@ -3979,13 +4078,13 @@
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D109" s="12">
         <v>0.83</v>
@@ -3997,13 +4096,13 @@
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D110" s="12">
         <v>0.94</v>
@@ -4015,13 +4114,13 @@
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D111" s="12">
         <v>0.9</v>
@@ -4033,13 +4132,13 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D112" s="12">
         <v>0.75</v>
@@ -4051,13 +4150,13 @@
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D113" s="12">
         <v>0.9</v>
@@ -4069,13 +4168,13 @@
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D114" s="12">
         <v>0.66</v>
@@ -4087,13 +4186,13 @@
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B115" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="B115" s="12" t="s">
-        <v>234</v>
-      </c>
       <c r="C115" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D115" s="12">
         <v>0.92</v>
@@ -4105,13 +4204,13 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D116" s="12">
         <v>0.82</v>
@@ -4123,13 +4222,13 @@
     </row>
     <row r="117" spans="1:13">
       <c r="A117" t="s">
+        <v>481</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>485</v>
-      </c>
       <c r="C117" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D117" s="4">
         <v>0</v>
@@ -4141,13 +4240,13 @@
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D118" s="12">
         <v>0.8</v>
@@ -4159,13 +4258,13 @@
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D119" s="12">
         <v>0.96</v>
@@ -4177,13 +4276,13 @@
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D120" s="12">
         <v>0.69</v>
@@ -4195,13 +4294,13 @@
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D121" s="12">
         <v>0.78</v>
@@ -4213,13 +4312,13 @@
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D122" s="12">
         <v>0.75</v>
@@ -4231,13 +4330,13 @@
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D123" s="12">
         <v>0.67</v>
@@ -4249,13 +4348,13 @@
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D124" s="12">
         <v>0.84</v>
@@ -4267,13 +4366,13 @@
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D125" s="12">
         <v>0.73</v>
@@ -4285,13 +4384,13 @@
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D126" s="12">
         <v>0.83</v>
@@ -4303,13 +4402,13 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D127" s="12">
         <v>0.95</v>
@@ -4321,13 +4420,13 @@
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D128" s="12">
         <v>0.72</v>
@@ -4342,10 +4441,10 @@
         <v>25</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D129" s="12">
         <v>0.83</v>
@@ -4357,13 +4456,13 @@
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D130" s="12">
         <v>0.75</v>
@@ -4375,13 +4474,13 @@
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B131" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="C131" s="12" t="s">
         <v>262</v>
-      </c>
-      <c r="B131" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="C131" s="12" t="s">
-        <v>264</v>
       </c>
       <c r="D131" s="12">
         <v>0.78</v>
@@ -4393,13 +4492,13 @@
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="18" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B132" s="18" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D132" s="12">
         <v>0.81</v>
@@ -4411,13 +4510,13 @@
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B133" s="18" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D133" s="12">
         <v>0.93</v>
@@ -4429,13 +4528,13 @@
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="18" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B134" s="18" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D134" s="12">
         <v>0.77</v>
@@ -4447,13 +4546,13 @@
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="18" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D135" s="12">
         <v>0.9</v>
@@ -4465,13 +4564,13 @@
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="18" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B136" s="18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D136" s="12">
         <v>0.87</v>
@@ -4483,13 +4582,13 @@
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="18" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D137" s="12">
         <v>0.88</v>
@@ -4501,13 +4600,13 @@
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B138" s="18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D138" s="12">
         <v>0.77</v>
@@ -4519,13 +4618,13 @@
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="18" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D139" s="12">
         <v>0.86</v>
@@ -4537,13 +4636,13 @@
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="18" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B140" s="18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D140" s="12">
         <v>0.68</v>
@@ -4555,13 +4654,13 @@
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D141" s="12">
         <v>0.73</v>
@@ -4573,13 +4672,13 @@
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="18" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B142" s="18" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D142" s="12">
         <v>0.9</v>
@@ -4591,13 +4690,13 @@
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D143" s="12">
         <v>0.87</v>
@@ -4609,13 +4708,13 @@
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D144" s="12">
         <v>0.94</v>
@@ -4627,13 +4726,13 @@
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D145" s="12">
         <v>0.91</v>
@@ -4645,13 +4744,13 @@
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D146" s="12">
         <v>0.82</v>
@@ -4663,13 +4762,13 @@
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D147" s="12">
         <v>0.79</v>
@@ -4681,13 +4780,13 @@
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D148" s="12">
         <v>0.8</v>
@@ -4699,13 +4798,13 @@
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D149" s="12">
         <v>0.83</v>
@@ -4717,13 +4816,13 @@
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D150" s="12">
         <v>0.77</v>
@@ -4735,13 +4834,13 @@
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D151" s="12">
         <v>0.88</v>
@@ -4753,13 +4852,13 @@
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D152" s="12">
         <v>0.9</v>
@@ -4771,13 +4870,13 @@
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D153" s="12">
         <v>0.77</v>
@@ -4789,13 +4888,13 @@
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D154" s="12">
         <v>0.79</v>
@@ -4807,13 +4906,13 @@
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D155" s="12">
         <v>0.84</v>
@@ -4825,13 +4924,13 @@
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D156" s="12">
         <v>0.88</v>
@@ -4843,13 +4942,13 @@
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D157" s="12">
         <v>0.8</v>
@@ -4861,13 +4960,13 @@
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D158" s="12">
         <v>0.66</v>
@@ -4879,13 +4978,13 @@
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D159" s="12">
         <v>0.88</v>
@@ -4897,13 +4996,13 @@
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D160" s="12">
         <v>0.94</v>
@@ -4915,13 +5014,13 @@
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D161" s="12">
         <v>0.95</v>
@@ -4933,13 +5032,13 @@
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D162" s="12">
         <v>0.79</v>
@@ -4951,13 +5050,13 @@
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D163" s="12">
         <v>0.9</v>
@@ -4969,13 +5068,13 @@
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D164" s="12">
         <v>0.82</v>
@@ -4987,13 +5086,13 @@
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D165" s="12">
         <v>0.75</v>
@@ -5005,13 +5104,13 @@
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D166" s="12">
         <v>0.8</v>
@@ -5023,13 +5122,13 @@
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D167" s="12">
         <v>0.85</v>
@@ -5041,13 +5140,13 @@
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D168" s="12">
         <v>0.82</v>
@@ -5059,13 +5158,13 @@
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D169" s="12">
         <v>0.9</v>
@@ -5077,13 +5176,13 @@
     </row>
     <row r="170" spans="1:13">
       <c r="A170" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C170" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D170" s="4">
         <v>0</v>
@@ -5095,13 +5194,13 @@
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D171" s="12">
         <v>0.86</v>
@@ -5113,13 +5212,13 @@
     </row>
     <row r="172" spans="1:13">
       <c r="A172" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C172" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D172" s="4">
         <v>0</v>
@@ -5131,13 +5230,13 @@
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C173" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D173" s="12">
         <v>0.69</v>
@@ -5149,13 +5248,13 @@
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D174" s="12">
         <v>0.77</v>
@@ -5167,13 +5266,13 @@
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D175" s="12">
         <v>0.73</v>
@@ -5185,13 +5284,13 @@
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D176" s="12">
         <v>0.86</v>
@@ -5203,13 +5302,13 @@
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D177" s="12">
         <v>0.68</v>
@@ -5221,13 +5320,13 @@
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D178" s="12">
         <v>0.82</v>
@@ -5239,13 +5338,13 @@
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D179" s="12">
         <v>0.61</v>
@@ -5257,13 +5356,13 @@
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D180" s="12">
         <v>0.75</v>
@@ -5275,13 +5374,13 @@
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="B181" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="C181" s="12" t="s">
         <v>358</v>
-      </c>
-      <c r="B181" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="C181" s="12" t="s">
-        <v>360</v>
       </c>
       <c r="D181" s="12">
         <v>0.87</v>
@@ -5293,13 +5392,13 @@
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B182" s="21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C182" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D182" s="4">
         <v>0</v>
@@ -5311,13 +5410,13 @@
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="18" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B183" s="18" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D183" s="12">
         <v>0.71</v>
@@ -5329,13 +5428,13 @@
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D184" s="12">
         <v>0.92</v>
@@ -5347,13 +5446,13 @@
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B185" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D185" s="12">
         <v>0.8</v>
@@ -5365,13 +5464,13 @@
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="12" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D186" s="12">
         <v>0.75</v>
@@ -5383,13 +5482,13 @@
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="12" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D187" s="12">
         <v>0.87</v>
@@ -5401,13 +5500,13 @@
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B188" s="12" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D188" s="12">
         <v>0.81</v>
@@ -5419,13 +5518,13 @@
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="12" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B189" s="12" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D189" s="12">
         <v>0.84</v>
@@ -5437,13 +5536,13 @@
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="12" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B190" s="12" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D190" s="12">
         <v>0.64</v>
@@ -5455,13 +5554,13 @@
     </row>
     <row r="191" spans="1:13">
       <c r="A191" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C191" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D191" s="4">
         <v>0</v>
@@ -5473,13 +5572,13 @@
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D192" s="12">
         <v>0.78</v>
@@ -5491,13 +5590,13 @@
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="12" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B193" s="12" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D193" s="12">
         <v>0.91</v>
@@ -5509,13 +5608,13 @@
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="12" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B194" s="12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D194" s="12">
         <v>0.81</v>
@@ -5527,13 +5626,13 @@
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B195" s="12" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D195" s="12">
         <v>0.84</v>
@@ -5545,13 +5644,13 @@
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="12" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C196" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D196" s="12">
         <v>0.84</v>
@@ -5563,13 +5662,13 @@
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B197" s="12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D197" s="12">
         <v>0.91</v>
@@ -5581,13 +5680,13 @@
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B198" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C198" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D198" s="12">
         <v>0.83</v>
@@ -5599,13 +5698,13 @@
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="12" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B199" s="12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D199" s="12">
         <v>0.84</v>
@@ -5617,13 +5716,13 @@
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="12" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D200" s="12">
         <v>0.85</v>
@@ -5635,13 +5734,13 @@
     </row>
     <row r="201" spans="1:13">
       <c r="A201" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C201" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D201" s="4">
         <v>0</v>
@@ -5653,13 +5752,13 @@
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B202" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D202" s="12">
         <v>0.88</v>
@@ -5671,13 +5770,13 @@
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B203" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D203" s="12">
         <v>0.82</v>
@@ -5689,13 +5788,13 @@
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B204" s="12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D204" s="12">
         <v>0.76</v>
@@ -5707,13 +5806,13 @@
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B205" s="12" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D205" s="12">
         <v>0.59</v>
@@ -5725,13 +5824,13 @@
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="12" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B206" s="12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D206" s="12">
         <v>0.79</v>
@@ -5743,13 +5842,13 @@
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B207" s="12" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D207" s="12">
         <v>0.77</v>
@@ -5761,13 +5860,13 @@
     </row>
     <row r="208" spans="1:13">
       <c r="A208" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C208" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D208" s="4">
         <v>0</v>
@@ -5779,13 +5878,13 @@
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="12" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B209" s="12" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D209" s="12">
         <v>0.75</v>
@@ -5797,13 +5896,13 @@
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B210" s="12" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D210" s="12">
         <v>0.79</v>
@@ -5815,13 +5914,13 @@
     </row>
     <row r="211" spans="1:13">
       <c r="A211" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C211" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D211" s="4">
         <v>0</v>
@@ -5833,13 +5932,13 @@
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="12" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B212" s="12" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D212" s="12">
         <v>0.74</v>
@@ -5851,13 +5950,13 @@
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B213" s="12" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D213" s="12">
         <v>0.62</v>
@@ -5869,13 +5968,13 @@
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="12" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B214" s="12" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D214" s="12">
         <v>0.94</v>
@@ -5887,13 +5986,13 @@
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="B215" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="C215" s="12" t="s">
         <v>417</v>
-      </c>
-      <c r="B215" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="C215" s="12" t="s">
-        <v>419</v>
       </c>
       <c r="D215" s="12">
         <v>0.75</v>
@@ -5905,13 +6004,13 @@
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B216" s="12" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D216" s="12">
         <v>0.61</v>
@@ -5923,13 +6022,13 @@
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="12" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B217" s="12" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D217" s="12">
         <v>0.69</v>
@@ -5941,13 +6040,13 @@
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B218" s="12" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D218" s="12">
         <v>0.67</v>
@@ -5959,13 +6058,13 @@
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="12" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B219" s="12" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D219" s="12">
         <v>0.71</v>
@@ -5977,13 +6076,13 @@
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B220" s="12" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D220" s="12">
         <v>0.89</v>
@@ -5995,13 +6094,13 @@
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="19" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B221" s="20" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C221" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D221" s="4">
         <v>0</v>
@@ -6013,13 +6112,13 @@
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="B222" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="C222" s="12" t="s">
         <v>430</v>
-      </c>
-      <c r="B222" s="18" t="s">
-        <v>431</v>
-      </c>
-      <c r="C222" s="12" t="s">
-        <v>432</v>
       </c>
       <c r="D222" s="12">
         <v>0.79</v>
@@ -6031,13 +6130,13 @@
     </row>
     <row r="223" spans="1:13">
       <c r="A223" s="18" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B223" s="18" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D223" s="12">
         <v>0.66</v>
@@ -6049,13 +6148,13 @@
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="12" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B224" s="12" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D224" s="12">
         <v>0.69</v>
@@ -6067,13 +6166,13 @@
     </row>
     <row r="225" spans="1:13">
       <c r="A225" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C225" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D225" s="4">
         <v>0</v>
@@ -6085,13 +6184,13 @@
     </row>
     <row r="226" spans="1:13">
       <c r="A226" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C226" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D226" s="4">
         <v>0</v>
@@ -6103,13 +6202,13 @@
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B227" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C227" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D227" s="12">
         <v>0.83</v>
@@ -6121,13 +6220,13 @@
     </row>
     <row r="228" spans="1:13">
       <c r="A228" s="12" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B228" s="12" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D228" s="12">
         <v>0.79</v>
@@ -6139,13 +6238,13 @@
     </row>
     <row r="229" spans="1:13">
       <c r="A229" s="12" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B229" s="12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C229" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D229" s="12">
         <v>0.81</v>
@@ -6157,13 +6256,13 @@
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B230" s="12" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C230" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D230" s="12">
         <v>0.74</v>
@@ -6175,13 +6274,13 @@
     </row>
     <row r="231" spans="1:13">
       <c r="A231" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C231" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D231" s="4">
         <v>0</v>
@@ -6196,10 +6295,10 @@
         <v>32</v>
       </c>
       <c r="B232" s="12" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C232" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D232" s="12">
         <v>0.75</v>
@@ -6214,10 +6313,10 @@
         <v>32</v>
       </c>
       <c r="B233" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C233" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D233" s="12">
         <v>0.65</v>
@@ -6229,13 +6328,13 @@
     </row>
     <row r="234" spans="1:13">
       <c r="A234" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C234" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D234" s="4">
         <v>0</v>
@@ -6247,13 +6346,13 @@
     </row>
     <row r="235" spans="1:13">
       <c r="A235" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C235" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D235" s="4">
         <v>0</v>
@@ -6265,13 +6364,13 @@
     </row>
     <row r="236" spans="1:13">
       <c r="A236" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C236" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D236" s="4">
         <v>0</v>
@@ -6283,13 +6382,13 @@
     </row>
     <row r="237" spans="1:13">
       <c r="A237" s="12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B237" s="12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C237" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D237" s="12">
         <v>0.87</v>
@@ -6301,13 +6400,13 @@
     </row>
     <row r="238" spans="1:13">
       <c r="A238" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B238" s="12" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C238" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D238" s="12">
         <v>0.7</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40CA324-4176-F748-9BC3-746BEA0EB90C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0342B17-4241-0145-B69D-88C09BD8DB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2398,6 +2398,9 @@
       <c r="D17" s="4">
         <v>0</v>
       </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
       <c r="H17" s="5"/>
       <c r="J17">
         <v>0.48</v>
@@ -2417,6 +2420,9 @@
       <c r="D18" s="4">
         <v>0.72</v>
       </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
       <c r="H18" s="5"/>
       <c r="J18">
         <v>0.48</v>
@@ -2739,6 +2745,9 @@
       <c r="D35" s="4">
         <v>0</v>
       </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
       <c r="H35" s="5"/>
       <c r="J35">
         <v>0</v>
@@ -3008,6 +3017,9 @@
         <v>0.6</v>
       </c>
       <c r="H49" s="5"/>
+      <c r="J49">
+        <v>0.92</v>
+      </c>
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
@@ -3102,6 +3114,9 @@
       <c r="G54">
         <v>0.32</v>
       </c>
+      <c r="J54">
+        <v>0.92</v>
+      </c>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
@@ -3156,6 +3171,9 @@
       <c r="G57">
         <v>0.81</v>
       </c>
+      <c r="J57">
+        <v>0.92</v>
+      </c>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
@@ -3336,6 +3354,9 @@
       <c r="G67">
         <v>0.56000000000000005</v>
       </c>
+      <c r="J67">
+        <v>0.92</v>
+      </c>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
@@ -3480,6 +3501,9 @@
       <c r="G75">
         <v>0.74</v>
       </c>
+      <c r="J75">
+        <v>0.92</v>
+      </c>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
@@ -3515,6 +3539,9 @@
       </c>
       <c r="G77">
         <v>0.61</v>
+      </c>
+      <c r="J77">
+        <v>0.92</v>
       </c>
       <c r="M77" s="6"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0342B17-4241-0145-B69D-88C09BD8DB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88749F8E-8E0B-E44D-A9D0-ABFF7A52BE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3039,6 +3039,9 @@
         <v>0.54</v>
       </c>
       <c r="H50" s="5"/>
+      <c r="J50">
+        <v>0.83</v>
+      </c>
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
@@ -3096,6 +3099,9 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H53" s="5"/>
+      <c r="J53">
+        <v>0.83</v>
+      </c>
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
@@ -3192,6 +3198,9 @@
       <c r="G58">
         <v>0.46</v>
       </c>
+      <c r="J58">
+        <v>0.83</v>
+      </c>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
@@ -3228,6 +3237,9 @@
       <c r="G60">
         <v>0.37</v>
       </c>
+      <c r="J60">
+        <v>0.83</v>
+      </c>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
@@ -3318,6 +3330,9 @@
       <c r="G65">
         <v>0.77</v>
       </c>
+      <c r="J65">
+        <v>0.83</v>
+      </c>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
@@ -3428,6 +3443,9 @@
       </c>
       <c r="G71">
         <v>0.77</v>
+      </c>
+      <c r="J71">
+        <v>0.83</v>
       </c>
       <c r="M71" s="6"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88749F8E-8E0B-E44D-A9D0-ABFF7A52BE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A859BCF7-8351-F143-A166-AA6E99873C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2303,6 +2303,9 @@
       <c r="D12" s="4">
         <v>0.76</v>
       </c>
+      <c r="G12">
+        <v>0.16</v>
+      </c>
       <c r="H12" s="5"/>
       <c r="J12">
         <v>0.48</v>
@@ -2341,6 +2344,9 @@
       <c r="D14" s="4">
         <v>0.75</v>
       </c>
+      <c r="G14">
+        <v>0.44</v>
+      </c>
       <c r="H14" s="5"/>
       <c r="J14">
         <v>0.48</v>
@@ -2480,6 +2486,9 @@
       <c r="D21" s="4">
         <v>0.78</v>
       </c>
+      <c r="G21">
+        <v>0.65</v>
+      </c>
       <c r="H21" s="5"/>
       <c r="J21">
         <v>0.68</v>
@@ -2537,6 +2546,9 @@
       <c r="D24" s="4">
         <v>0.74</v>
       </c>
+      <c r="G24">
+        <v>0.67</v>
+      </c>
       <c r="H24" s="5"/>
       <c r="J24">
         <v>0.48</v>
@@ -2556,6 +2568,9 @@
       <c r="D25" s="4">
         <v>0.67</v>
       </c>
+      <c r="G25">
+        <v>0.61</v>
+      </c>
       <c r="H25" s="5"/>
       <c r="J25">
         <v>0.8</v>
@@ -2631,6 +2646,9 @@
       </c>
       <c r="D29" s="4">
         <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0.75</v>
       </c>
       <c r="H29" s="5"/>
       <c r="J29">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A859BCF7-8351-F143-A166-AA6E99873C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E12D619-C8BE-D249-8C26-B52CB40CAE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2113,6 +2113,9 @@
       <c r="D2" s="4">
         <v>0.56999999999999995</v>
       </c>
+      <c r="G2">
+        <v>0.79</v>
+      </c>
       <c r="H2" s="5"/>
       <c r="J2">
         <v>0.48</v>
@@ -2170,6 +2173,9 @@
       <c r="D5" s="4">
         <v>0.75</v>
       </c>
+      <c r="G5">
+        <v>0.54</v>
+      </c>
       <c r="H5" s="5"/>
       <c r="J5">
         <v>0.48</v>
@@ -2227,6 +2233,9 @@
       <c r="D8" s="4">
         <v>0</v>
       </c>
+      <c r="G8">
+        <v>0.11</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="J8">
         <v>0.8</v>
@@ -2427,7 +2436,7 @@
         <v>0.72</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="H18" s="5"/>
       <c r="J18">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E12D619-C8BE-D249-8C26-B52CB40CAE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6400264E-C825-964B-9EFF-CD067A3EAD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="492">
   <si>
     <t>Surname</t>
   </si>
@@ -1500,6 +1500,18 @@
   </si>
   <si>
     <t>CHIYAMA</t>
+  </si>
+  <si>
+    <t>Munyanyiri</t>
+  </si>
+  <si>
+    <t>H240094P</t>
+  </si>
+  <si>
+    <t>Nyambuya</t>
+  </si>
+  <si>
+    <t>H240460T</t>
   </si>
 </sst>
 </file>
@@ -1638,7 +1650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1659,6 +1671,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1710,10 +1725,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M238" totalsRowShown="0">
-  <autoFilter ref="A1:M238" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M238">
-    <sortCondition ref="C1:C238"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M240" totalsRowShown="0">
+  <autoFilter ref="A1:M240" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M240">
+    <sortCondition ref="C1:C240"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -2051,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:M238"/>
+  <dimension ref="A1:M240"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -2135,6 +2150,9 @@
       <c r="D3" s="4">
         <v>0.86</v>
       </c>
+      <c r="G3">
+        <v>0.39</v>
+      </c>
       <c r="H3" s="5"/>
       <c r="J3">
         <v>0.68</v>
@@ -2154,6 +2172,9 @@
       <c r="D4" s="4">
         <v>0.79</v>
       </c>
+      <c r="G4">
+        <v>0.39</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="J4">
         <v>0.48</v>
@@ -2195,6 +2216,9 @@
       <c r="D6" s="4">
         <v>0.64</v>
       </c>
+      <c r="G6">
+        <v>0.53</v>
+      </c>
       <c r="H6" s="5"/>
       <c r="J6">
         <v>0.48</v>
@@ -2214,6 +2238,9 @@
       <c r="D7" s="4">
         <v>0.82</v>
       </c>
+      <c r="G7">
+        <v>0.42</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="J7">
         <v>0.48</v>
@@ -2255,6 +2282,9 @@
       <c r="D9" s="4">
         <v>0.75</v>
       </c>
+      <c r="G9">
+        <v>0.47</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="J9">
         <v>0.68</v>
@@ -2274,6 +2304,9 @@
       <c r="D10" s="4">
         <v>0.56999999999999995</v>
       </c>
+      <c r="G10">
+        <v>0.54</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="J10">
         <v>0.48</v>
@@ -2599,6 +2632,9 @@
       <c r="D26" s="4">
         <v>0.85</v>
       </c>
+      <c r="G26">
+        <v>0.53</v>
+      </c>
       <c r="H26" s="5"/>
       <c r="J26">
         <v>0.48</v>
@@ -2637,6 +2673,9 @@
       <c r="D28" s="4">
         <v>0.77</v>
       </c>
+      <c r="G28">
+        <v>0.63</v>
+      </c>
       <c r="H28" s="5"/>
       <c r="J28">
         <v>0.48</v>
@@ -2678,6 +2717,9 @@
       <c r="D30" s="4">
         <v>0.86</v>
       </c>
+      <c r="G30">
+        <v>0.35</v>
+      </c>
       <c r="H30" s="5"/>
       <c r="J30">
         <v>0.48</v>
@@ -2705,16 +2747,16 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="7" t="s">
-        <v>487</v>
+        <v>83</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
         <v>100</v>
       </c>
       <c r="D32" s="4">
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="H32" s="5"/>
       <c r="J32">
@@ -2724,16 +2766,16 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="7" t="s">
-        <v>83</v>
+        <v>487</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
         <v>100</v>
       </c>
       <c r="D33" s="4">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="H33" s="5"/>
       <c r="J33">
@@ -2838,36 +2880,35 @@
       <c r="M38" s="6"/>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>88</v>
+      <c r="A39" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>489</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
       </c>
       <c r="D39" s="4">
-        <v>0.73</v>
-      </c>
-      <c r="H39" s="5"/>
-      <c r="J39">
-        <v>0.8</v>
-      </c>
-      <c r="M39" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0.52</v>
+      </c>
+      <c r="M39" s="19"/>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>99</v>
+      <c r="A40" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="C40" t="s">
         <v>100</v>
       </c>
       <c r="D40" s="4">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="H40" s="5"/>
       <c r="J40">
@@ -2876,36 +2917,36 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>92</v>
+      <c r="A41" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="C41" t="s">
         <v>100</v>
       </c>
       <c r="D41" s="4">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H41" s="5"/>
       <c r="J41">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C42" t="s">
         <v>100</v>
       </c>
       <c r="D42" s="4">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="H42" s="5"/>
       <c r="J42">
@@ -2914,355 +2955,359 @@
       <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>94</v>
+      <c r="A43" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>96</v>
       </c>
       <c r="C43" t="s">
         <v>100</v>
       </c>
       <c r="D43" s="4">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H43" s="5"/>
       <c r="J43">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="M43" s="6"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>91</v>
+      <c r="A44" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>491</v>
       </c>
       <c r="C44" t="s">
         <v>100</v>
       </c>
       <c r="D44" s="4">
-        <v>0.77</v>
-      </c>
-      <c r="H44" s="5"/>
-      <c r="J44">
-        <v>0.24</v>
-      </c>
-      <c r="M44" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0.54</v>
+      </c>
+      <c r="M44" s="19"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>89</v>
+      <c r="A45" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C45" t="s">
         <v>100</v>
       </c>
       <c r="D45" s="4">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="H45" s="5"/>
       <c r="J45">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>86</v>
+      <c r="A46" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="C46" t="s">
         <v>100</v>
       </c>
       <c r="D46" s="4">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="H46" s="5"/>
       <c r="J46">
+        <v>0.24</v>
+      </c>
+      <c r="M46" s="6"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="4">
+        <v>0.91</v>
+      </c>
+      <c r="G47">
+        <v>0.54</v>
+      </c>
+      <c r="H47" s="5"/>
+      <c r="J47">
+        <v>0.24</v>
+      </c>
+      <c r="M47" s="6"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="G48">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H48" s="5"/>
+      <c r="J48">
         <v>0.8</v>
       </c>
-      <c r="M46" s="6"/>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="18" t="s">
+      <c r="M48" s="6"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B49" s="21" t="s">
         <v>102</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D47" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="G47">
-        <v>0.68</v>
-      </c>
-      <c r="H47" s="5"/>
-      <c r="M47" s="6"/>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D48" s="12">
-        <v>0.89</v>
-      </c>
-      <c r="G48">
-        <v>0.75</v>
-      </c>
-      <c r="H48" s="5"/>
-      <c r="M48" s="6"/>
-    </row>
-    <row r="49" spans="1:13">
-      <c r="A49" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>107</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D49" s="12">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="G49">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="H49" s="5"/>
-      <c r="J49">
-        <v>0.92</v>
-      </c>
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>109</v>
+      <c r="A50" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>105</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D50" s="12">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="G50">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="H50" s="5"/>
-      <c r="J50">
-        <v>0.83</v>
-      </c>
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="B51" s="18" t="s">
-        <v>111</v>
+      <c r="A51" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D51" s="12">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G51">
         <v>0.6</v>
       </c>
       <c r="H51" s="5"/>
+      <c r="J51">
+        <v>0.92</v>
+      </c>
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="B52" s="18" t="s">
-        <v>113</v>
+      <c r="A52" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>109</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D52" s="12">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="G52">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="H52" s="5"/>
+      <c r="J52">
+        <v>0.83</v>
+      </c>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>486</v>
+      <c r="A53" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>111</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D53" s="12">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="G53">
-        <v>0.56000000000000005</v>
+        <v>0.6</v>
       </c>
       <c r="H53" s="5"/>
-      <c r="J53">
-        <v>0.83</v>
-      </c>
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>116</v>
+      <c r="A54" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>113</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D54" s="12">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="G54">
-        <v>0.32</v>
-      </c>
-      <c r="J54">
-        <v>0.92</v>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="H54" s="5"/>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>118</v>
+      <c r="A55" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>486</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D55" s="12">
-        <v>0.69</v>
+        <v>0.86</v>
       </c>
       <c r="G55">
-        <v>0.51</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H55" s="5"/>
+      <c r="J55">
+        <v>0.83</v>
       </c>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>120</v>
+      <c r="A56" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>116</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D56" s="12">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G56">
         <v>0.32</v>
       </c>
+      <c r="J56">
+        <v>0.92</v>
+      </c>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>122</v>
+      <c r="A57" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>118</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D57" s="12">
-        <v>0.9</v>
+        <v>0.69</v>
       </c>
       <c r="G57">
-        <v>0.81</v>
-      </c>
-      <c r="J57">
-        <v>0.92</v>
+        <v>0.51</v>
       </c>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>124</v>
+      <c r="A58" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>120</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D58" s="12">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="G58">
-        <v>0.46</v>
-      </c>
-      <c r="J58">
-        <v>0.83</v>
+        <v>0.32</v>
       </c>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D59" s="12">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="G59">
-        <v>0.46</v>
+        <v>0.81</v>
+      </c>
+      <c r="J59">
+        <v>0.92</v>
       </c>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D60" s="12">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="G60">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="J60">
         <v>0.83</v>
@@ -3271,319 +3316,319 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D61" s="12">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="G61">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C62" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D62" s="12">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="G62">
         <v>0.37</v>
       </c>
+      <c r="J62">
+        <v>0.83</v>
+      </c>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D63" s="12">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="G63">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D64" s="12">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="G64">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D65" s="12">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="G65">
-        <v>0.77</v>
-      </c>
-      <c r="J65">
-        <v>0.83</v>
+        <v>0.53</v>
       </c>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D66" s="12">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="G66">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="12" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D67" s="12">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="G67">
-        <v>0.56000000000000005</v>
+        <v>0.77</v>
       </c>
       <c r="J67">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="12" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D68" s="12">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="G68">
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="12" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D69" s="12">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="G69">
-        <v>0.35</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J69">
+        <v>0.92</v>
       </c>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C70" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D70" s="12">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="G70">
-        <v>0.28000000000000003</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D71" s="12">
-        <v>0.84</v>
+        <v>0.7</v>
       </c>
       <c r="G71">
-        <v>0.77</v>
-      </c>
-      <c r="J71">
-        <v>0.83</v>
+        <v>0.35</v>
       </c>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="12" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D72" s="12">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G72">
-        <v>0.51</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="12" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D73" s="12">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="G73">
-        <v>0.05</v>
+        <v>0.77</v>
+      </c>
+      <c r="J73">
+        <v>0.83</v>
       </c>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="12" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C74" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D74" s="12">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="G74">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D75" s="12">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="G75">
-        <v>0.74</v>
-      </c>
-      <c r="J75">
-        <v>0.92</v>
+        <v>0.05</v>
       </c>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C76" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D76" s="12">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="G76">
-        <v>0.57999999999999996</v>
+        <v>0.61</v>
       </c>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="12" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D77" s="12">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="G77">
-        <v>0.61</v>
+        <v>0.74</v>
       </c>
       <c r="J77">
         <v>0.92</v>
@@ -3592,334 +3637,337 @@
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D78" s="12">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="G78">
-        <v>0.47</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D79" s="12">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="G79">
-        <v>0.65</v>
+        <v>0.61</v>
+      </c>
+      <c r="J79">
+        <v>0.92</v>
       </c>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D80" s="12">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="G80">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
-      <c r="A81" t="s">
-        <v>342</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C81" t="s">
+      <c r="A81" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C81" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D81" s="4">
-        <v>0</v>
+      <c r="D81" s="12">
+        <v>0.84</v>
       </c>
       <c r="G81">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D82" s="12">
-        <v>0.81</v>
+        <v>0.74</v>
       </c>
       <c r="G82">
-        <v>0.79</v>
+        <v>0.39</v>
       </c>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
-      <c r="A83" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="C83" s="12" t="s">
+      <c r="A83" t="s">
+        <v>342</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C83" t="s">
         <v>103</v>
       </c>
-      <c r="D83" s="12">
-        <v>0.71</v>
+      <c r="D83" s="4">
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D84" s="12">
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
       <c r="G84">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D85" s="12">
-        <v>0.81</v>
+        <v>0.71</v>
       </c>
       <c r="G85">
-        <v>0.25</v>
+        <v>0.63</v>
       </c>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D86" s="12">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="G86">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="M86" s="6"/>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C87" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D87" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="G87">
+        <v>0.25</v>
+      </c>
+      <c r="M87" s="6"/>
+    </row>
+    <row r="88" spans="1:13">
+      <c r="A88" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D88" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="G88">
+        <v>0.6</v>
+      </c>
+      <c r="M88" s="6"/>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D89" s="12">
         <v>0.85</v>
       </c>
-      <c r="G87">
+      <c r="G89">
         <v>0.54</v>
       </c>
-      <c r="M87" s="6"/>
-    </row>
-    <row r="88" spans="1:13">
-      <c r="A88" s="18" t="s">
+      <c r="M89" s="6"/>
+    </row>
+    <row r="90" spans="1:13">
+      <c r="A90" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="B88" s="18" t="s">
+      <c r="B90" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="C90" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="D88" s="12">
+      <c r="D90" s="12">
         <v>0.75</v>
       </c>
-      <c r="G88">
+      <c r="G90">
         <v>0.68</v>
       </c>
-      <c r="M88" s="6"/>
-    </row>
-    <row r="89" spans="1:13">
-      <c r="A89" s="18" t="s">
+      <c r="M90" s="6"/>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="B89" s="18" t="s">
+      <c r="B91" s="21" t="s">
         <v>185</v>
-      </c>
-      <c r="C89" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D89" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="G89">
-        <v>0.6</v>
-      </c>
-      <c r="M89" s="6"/>
-    </row>
-    <row r="90" spans="1:13">
-      <c r="A90" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="B90" s="20" t="s">
-        <v>485</v>
-      </c>
-      <c r="C90" t="s">
-        <v>183</v>
-      </c>
-      <c r="D90" s="4">
-        <v>0</v>
-      </c>
-      <c r="G90">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="M90" s="16"/>
-    </row>
-    <row r="91" spans="1:13">
-      <c r="A91" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="B91" s="18" t="s">
-        <v>187</v>
       </c>
       <c r="C91" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D91" s="12">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="G91">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
-      <c r="A92" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="B92" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="C92" s="12" t="s">
+      <c r="A92" s="22" t="s">
+        <v>484</v>
+      </c>
+      <c r="B92" s="23" t="s">
+        <v>485</v>
+      </c>
+      <c r="C92" t="s">
         <v>183</v>
       </c>
-      <c r="D92" s="12">
-        <v>0.75</v>
+      <c r="D92" s="4">
+        <v>0</v>
       </c>
       <c r="G92">
-        <v>0.65</v>
-      </c>
-      <c r="M92" s="6"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M92" s="19"/>
     </row>
     <row r="93" spans="1:13">
-      <c r="A93" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="B93" s="18" t="s">
-        <v>191</v>
+      <c r="A93" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B93" s="21" t="s">
+        <v>187</v>
       </c>
       <c r="C93" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D93" s="12">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="G93">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
-      <c r="A94" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="B94" s="18" t="s">
-        <v>193</v>
+      <c r="A94" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>189</v>
       </c>
       <c r="C94" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D94" s="12">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="G94">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
-      <c r="A95" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="B95" s="18" t="s">
-        <v>195</v>
+      <c r="A95" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B95" s="21" t="s">
+        <v>191</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D95" s="12">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="G95">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
-      <c r="A96" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B96" s="12" t="s">
-        <v>197</v>
+      <c r="A96" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B96" s="21" t="s">
+        <v>193</v>
       </c>
       <c r="C96" s="12" t="s">
         <v>183</v>
@@ -3928,52 +3976,52 @@
         <v>0.93</v>
       </c>
       <c r="G96">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
-      <c r="A97" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B97" s="12" t="s">
-        <v>199</v>
+      <c r="A97" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>195</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D97" s="12">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="G97">
-        <v>0.28000000000000003</v>
+        <v>0.46</v>
       </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="12" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D98" s="12">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="G98">
-        <v>0.4</v>
+        <v>0.72</v>
       </c>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C99" s="12" t="s">
         <v>183</v>
@@ -3982,52 +4030,52 @@
         <v>0.83</v>
       </c>
       <c r="G99">
-        <v>0.44</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D100" s="12">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G100">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="12" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D101" s="12">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="G101">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="12" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C102" s="12" t="s">
         <v>183</v>
@@ -4036,196 +4084,196 @@
         <v>0.85</v>
       </c>
       <c r="G102">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
-      <c r="A103" t="s">
-        <v>480</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="C103" t="s">
+      <c r="A103" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C103" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="D103" s="4">
-        <v>0</v>
+      <c r="D103" s="12">
+        <v>0.89</v>
       </c>
       <c r="G103">
-        <v>0.51</v>
-      </c>
-      <c r="M103" s="16"/>
+        <v>0.49</v>
+      </c>
+      <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C104" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D104" s="12">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="G104">
-        <v>0.4</v>
+        <v>0.54</v>
       </c>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
-      <c r="A105" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="B105" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="C105" s="12" t="s">
+      <c r="A105" t="s">
+        <v>480</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C105" t="s">
         <v>183</v>
       </c>
-      <c r="D105" s="12">
-        <v>0.79</v>
+      <c r="D105" s="4">
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>0.44</v>
-      </c>
-      <c r="M105" s="6"/>
+        <v>0.51</v>
+      </c>
+      <c r="M105" s="19"/>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="12" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D106" s="12">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="G106">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C107" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D107" s="12">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="G107">
-        <v>0.75</v>
+        <v>0.44</v>
       </c>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="12" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D108" s="12">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="G108">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="12" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D109" s="12">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="G109">
-        <v>0.26</v>
+        <v>0.75</v>
       </c>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="12" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D110" s="12">
-        <v>0.94</v>
+        <v>0.82</v>
       </c>
       <c r="G110">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="12" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D111" s="12">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="G111">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="12" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D112" s="12">
-        <v>0.75</v>
+        <v>0.94</v>
       </c>
       <c r="G112">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>183</v>
@@ -4234,130 +4282,130 @@
         <v>0.9</v>
       </c>
       <c r="G113">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="12" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C114" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D114" s="12">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="G114">
-        <v>0.63</v>
+        <v>0.39</v>
       </c>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C115" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D115" s="12">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G115">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D116" s="12">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="G116">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="M116" s="6"/>
     </row>
     <row r="117" spans="1:13">
-      <c r="A117" t="s">
-        <v>481</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="A117" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C117" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="D117" s="4">
-        <v>0</v>
+      <c r="D117" s="12">
+        <v>0.92</v>
       </c>
       <c r="G117">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="M117" s="16"/>
+        <v>0.44</v>
+      </c>
+      <c r="M117" s="6"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C118" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D118" s="12">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G118">
-        <v>0.26</v>
+        <v>0.54</v>
       </c>
       <c r="M118" s="6"/>
     </row>
     <row r="119" spans="1:13">
-      <c r="A119" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="B119" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="C119" s="12" t="s">
+      <c r="A119" t="s">
+        <v>481</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C119" t="s">
         <v>183</v>
       </c>
-      <c r="D119" s="12">
-        <v>0.96</v>
+      <c r="D119" s="4">
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>0.26</v>
-      </c>
-      <c r="M119" s="6"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M119" s="19"/>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="12" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C120" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D120" s="12">
-        <v>0.69</v>
+        <v>0.8</v>
       </c>
       <c r="G120">
         <v>0.26</v>
@@ -4366,304 +4414,304 @@
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="12" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C121" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D121" s="12">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="G121">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="M121" s="6"/>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="12" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C122" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D122" s="12">
-        <v>0.75</v>
+        <v>0.69</v>
       </c>
       <c r="G122">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="M122" s="6"/>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="12" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C123" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D123" s="12">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="G123">
-        <v>0.74</v>
+        <v>0.09</v>
       </c>
       <c r="M123" s="6"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="12" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D124" s="12">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="G124">
-        <v>0.26</v>
+        <v>0.49</v>
       </c>
       <c r="M124" s="6"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="12" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D125" s="12">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="G125">
-        <v>0.32</v>
+        <v>0.74</v>
       </c>
       <c r="M125" s="6"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="12" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D126" s="12">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="G126">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="M126" s="6"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="12" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C127" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D127" s="12">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="G127">
-        <v>0.65</v>
+        <v>0.32</v>
       </c>
       <c r="M127" s="6"/>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="12" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D128" s="12">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="G128">
-        <v>0.28000000000000003</v>
+        <v>0.11</v>
       </c>
       <c r="M128" s="6"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="12" t="s">
-        <v>25</v>
+        <v>253</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C129" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D129" s="12">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="G129">
-        <v>0.47</v>
+        <v>0.65</v>
       </c>
       <c r="M129" s="6"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="12" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C130" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D130" s="12">
+        <v>0.72</v>
+      </c>
+      <c r="G130">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M130" s="6"/>
+    </row>
+    <row r="131" spans="1:13">
+      <c r="A131" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B131" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D131" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="G131">
+        <v>0.47</v>
+      </c>
+      <c r="M131" s="6"/>
+    </row>
+    <row r="132" spans="1:13">
+      <c r="A132" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B132" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D132" s="12">
         <v>0.75</v>
       </c>
-      <c r="G130">
+      <c r="G132">
         <v>0.35</v>
       </c>
-      <c r="M130" s="6"/>
-    </row>
-    <row r="131" spans="1:13">
-      <c r="A131" s="18" t="s">
+      <c r="M132" s="6"/>
+    </row>
+    <row r="133" spans="1:13">
+      <c r="A133" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="B131" s="18" t="s">
+      <c r="B133" s="21" t="s">
         <v>261</v>
-      </c>
-      <c r="C131" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="D131" s="12">
-        <v>0.78</v>
-      </c>
-      <c r="G131">
-        <v>0.4</v>
-      </c>
-      <c r="M131" s="6"/>
-    </row>
-    <row r="132" spans="1:13">
-      <c r="A132" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="B132" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="C132" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="D132" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="G132">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M132" s="6"/>
-    </row>
-    <row r="133" spans="1:13">
-      <c r="A133" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="B133" s="18" t="s">
-        <v>266</v>
       </c>
       <c r="C133" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D133" s="12">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="G133">
-        <v>0.63</v>
+        <v>0.4</v>
       </c>
       <c r="M133" s="6"/>
     </row>
     <row r="134" spans="1:13">
-      <c r="A134" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="B134" s="18" t="s">
-        <v>268</v>
+      <c r="A134" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="B134" s="21" t="s">
+        <v>264</v>
       </c>
       <c r="C134" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D134" s="12">
-        <v>0.77</v>
+        <v>0.81</v>
       </c>
       <c r="G134">
-        <v>0.42</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M134" s="6"/>
     </row>
     <row r="135" spans="1:13">
-      <c r="A135" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="B135" s="18" t="s">
-        <v>270</v>
+      <c r="A135" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="B135" s="21" t="s">
+        <v>266</v>
       </c>
       <c r="C135" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D135" s="12">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="G135">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="M135" s="6"/>
     </row>
     <row r="136" spans="1:13">
-      <c r="A136" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="B136" s="18" t="s">
-        <v>272</v>
+      <c r="A136" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="B136" s="21" t="s">
+        <v>268</v>
       </c>
       <c r="C136" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D136" s="12">
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
       <c r="G136">
-        <v>0.74</v>
+        <v>0.42</v>
       </c>
       <c r="M136" s="6"/>
     </row>
     <row r="137" spans="1:13">
-      <c r="A137" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="B137" s="18" t="s">
-        <v>274</v>
+      <c r="A137" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B137" s="21" t="s">
+        <v>270</v>
       </c>
       <c r="C137" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D137" s="12">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="G137">
         <v>0.39</v>
@@ -4671,623 +4719,623 @@
       <c r="M137" s="6"/>
     </row>
     <row r="138" spans="1:13">
-      <c r="A138" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="B138" s="18" t="s">
-        <v>276</v>
+      <c r="A138" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="B138" s="21" t="s">
+        <v>272</v>
       </c>
       <c r="C138" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D138" s="12">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="G138">
-        <v>0.51</v>
+        <v>0.74</v>
       </c>
       <c r="M138" s="6"/>
     </row>
     <row r="139" spans="1:13">
-      <c r="A139" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="B139" s="18" t="s">
-        <v>278</v>
+      <c r="A139" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="B139" s="21" t="s">
+        <v>274</v>
       </c>
       <c r="C139" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D139" s="12">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="G139">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="M139" s="6"/>
     </row>
     <row r="140" spans="1:13">
-      <c r="A140" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="B140" s="18" t="s">
-        <v>280</v>
+      <c r="A140" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="B140" s="21" t="s">
+        <v>276</v>
       </c>
       <c r="C140" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D140" s="12">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="G140">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="M140" s="6"/>
     </row>
     <row r="141" spans="1:13">
-      <c r="A141" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B141" s="18" t="s">
-        <v>281</v>
+      <c r="A141" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="B141" s="21" t="s">
+        <v>278</v>
       </c>
       <c r="C141" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D141" s="12">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="G141">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="M141" s="6"/>
     </row>
     <row r="142" spans="1:13">
-      <c r="A142" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="B142" s="18" t="s">
-        <v>283</v>
+      <c r="A142" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B142" s="21" t="s">
+        <v>280</v>
       </c>
       <c r="C142" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D142" s="12">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="G142">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="M142" s="6"/>
     </row>
     <row r="143" spans="1:13">
-      <c r="A143" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="B143" s="12" t="s">
-        <v>285</v>
+      <c r="A143" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B143" s="21" t="s">
+        <v>281</v>
       </c>
       <c r="C143" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D143" s="12">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="G143">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="M143" s="6"/>
     </row>
     <row r="144" spans="1:13">
-      <c r="A144" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="B144" s="12" t="s">
-        <v>287</v>
+      <c r="A144" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="B144" s="21" t="s">
+        <v>283</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D144" s="12">
-        <v>0.94</v>
+        <v>0.9</v>
       </c>
       <c r="G144">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="M144" s="6"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="12" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D145" s="12">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="G145">
-        <v>0.63</v>
+        <v>0.4</v>
       </c>
       <c r="M145" s="6"/>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="12" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C146" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D146" s="12">
-        <v>0.82</v>
+        <v>0.94</v>
       </c>
       <c r="G146">
-        <v>0.21</v>
+        <v>0.75</v>
       </c>
       <c r="M146" s="6"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="12" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C147" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D147" s="12">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="G147">
-        <v>0.25</v>
+        <v>0.63</v>
       </c>
       <c r="M147" s="6"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="12" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C148" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D148" s="12">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G148">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="M148" s="6"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="12" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C149" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D149" s="12">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="G149">
-        <v>0.63</v>
+        <v>0.25</v>
       </c>
       <c r="M149" s="6"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="12" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C150" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D150" s="12">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="G150">
-        <v>0.86</v>
+        <v>0.3</v>
       </c>
       <c r="M150" s="6"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="12" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C151" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D151" s="12">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="G151">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="M151" s="6"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="12" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C152" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D152" s="12">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="G152">
-        <v>0.49</v>
+        <v>0.86</v>
       </c>
       <c r="M152" s="6"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="12" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C153" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D153" s="12">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="G153">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="M153" s="6"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="12" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C154" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D154" s="12">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="G154">
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="M154" s="6"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="12" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C155" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D155" s="12">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="G155">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="M155" s="6"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="12" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C156" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D156" s="12">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="G156">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="M156" s="6"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="12" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C157" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D157" s="12">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="G157">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="M157" s="6"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="12" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C158" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D158" s="12">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="G158">
-        <v>0.57999999999999996</v>
+        <v>0.46</v>
       </c>
       <c r="M158" s="6"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="12" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C159" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D159" s="12">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="G159">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="M159" s="6"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="12" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C160" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D160" s="12">
-        <v>0.94</v>
+        <v>0.66</v>
       </c>
       <c r="G160">
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M160" s="6"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="12" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C161" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D161" s="12">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="G161">
-        <v>0.33</v>
+        <v>0.68</v>
       </c>
       <c r="M161" s="6"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="12" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C162" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D162" s="12">
-        <v>0.79</v>
+        <v>0.94</v>
       </c>
       <c r="G162">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="12" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C163" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D163" s="12">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G163">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="12" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C164" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D164" s="12">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="G164">
-        <v>0.63</v>
+        <v>0.18</v>
       </c>
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="12" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C165" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D165" s="12">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="G165">
-        <v>0.56000000000000005</v>
+        <v>0.47</v>
       </c>
       <c r="M165" s="6"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="12" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C166" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D166" s="12">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G166">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="M166" s="6"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="12" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C167" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D167" s="12">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="G167">
-        <v>0.3</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M167" s="6"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="12" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C168" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D168" s="12">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="G168">
-        <v>0.25</v>
+        <v>0.54</v>
       </c>
       <c r="M168" s="6"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="12" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C169" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D169" s="12">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G169">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="M169" s="6"/>
     </row>
     <row r="170" spans="1:13">
-      <c r="A170" t="s">
-        <v>465</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="C170" t="s">
+      <c r="A170" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="C170" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="D170" s="4">
-        <v>0</v>
+      <c r="D170" s="12">
+        <v>0.82</v>
       </c>
       <c r="G170">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C171" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D171" s="12">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="G171">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="M171" s="6"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C172" t="s">
         <v>262</v>
@@ -5296,850 +5344,850 @@
         <v>0</v>
       </c>
       <c r="G172">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="M172" s="6"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C173" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D173" s="12">
-        <v>0.69</v>
+        <v>0.86</v>
       </c>
       <c r="G173">
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="M173" s="6"/>
     </row>
     <row r="174" spans="1:13">
-      <c r="A174" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="B174" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="C174" s="12" t="s">
+      <c r="A174" t="s">
+        <v>463</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C174" t="s">
         <v>262</v>
       </c>
-      <c r="D174" s="12">
-        <v>0.77</v>
+      <c r="D174" s="4">
+        <v>0</v>
       </c>
       <c r="G174">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="M174" s="6"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="12" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C175" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D175" s="12">
-        <v>0.73</v>
+        <v>0.69</v>
       </c>
       <c r="G175">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="M175" s="6"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="12" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C176" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D176" s="12">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="G176">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="M176" s="6"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="12" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C177" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D177" s="12">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="G177">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="12" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D178" s="12">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="G178">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="12" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C179" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D179" s="12">
+        <v>0.68</v>
+      </c>
+      <c r="G179">
         <v>0.61</v>
-      </c>
-      <c r="G179">
-        <v>0.35</v>
       </c>
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="12" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C180" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D180" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="G180">
+        <v>0.53</v>
+      </c>
+      <c r="M180" s="6"/>
+    </row>
+    <row r="181" spans="1:13">
+      <c r="A181" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="B181" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C181" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D181" s="12">
+        <v>0.61</v>
+      </c>
+      <c r="G181">
+        <v>0.35</v>
+      </c>
+      <c r="M181" s="6"/>
+    </row>
+    <row r="182" spans="1:13">
+      <c r="A182" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B182" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D182" s="12">
         <v>0.75</v>
       </c>
-      <c r="G180">
+      <c r="G182">
         <v>0.32</v>
       </c>
-      <c r="M180" s="6"/>
-    </row>
-    <row r="181" spans="1:13">
-      <c r="A181" s="18" t="s">
+      <c r="M182" s="6"/>
+    </row>
+    <row r="183" spans="1:13">
+      <c r="A183" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="B181" s="18" t="s">
+      <c r="B183" s="21" t="s">
         <v>357</v>
-      </c>
-      <c r="C181" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D181" s="12">
-        <v>0.87</v>
-      </c>
-      <c r="G181">
-        <v>0.26</v>
-      </c>
-      <c r="M181" s="6"/>
-    </row>
-    <row r="182" spans="1:13">
-      <c r="A182" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="B182" s="21" t="s">
-        <v>457</v>
-      </c>
-      <c r="C182" t="s">
-        <v>358</v>
-      </c>
-      <c r="D182" s="4">
-        <v>0</v>
-      </c>
-      <c r="G182">
-        <v>0.19</v>
-      </c>
-      <c r="M182" s="6"/>
-    </row>
-    <row r="183" spans="1:13">
-      <c r="A183" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="B183" s="18" t="s">
-        <v>360</v>
       </c>
       <c r="C183" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D183" s="12">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="G183">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13">
-      <c r="A184" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="B184" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="C184" s="12" t="s">
+      <c r="A184" s="22" t="s">
+        <v>456</v>
+      </c>
+      <c r="B184" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="C184" t="s">
         <v>358</v>
       </c>
-      <c r="D184" s="12">
-        <v>0.92</v>
+      <c r="D184" s="4">
+        <v>0</v>
       </c>
       <c r="G184">
-        <v>0.63</v>
+        <v>0.19</v>
       </c>
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13">
-      <c r="A185" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="B185" s="12" t="s">
-        <v>364</v>
+      <c r="A185" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="B185" s="21" t="s">
+        <v>360</v>
       </c>
       <c r="C185" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D185" s="12">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="G185">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="M185" s="6"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="12" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C186" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D186" s="12">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="G186">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="12" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C187" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D187" s="12">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="G187">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="12" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B188" s="12" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C188" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D188" s="12">
-        <v>0.81</v>
+        <v>0.75</v>
       </c>
       <c r="G188">
-        <v>0.57999999999999996</v>
+        <v>0.68</v>
       </c>
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="12" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B189" s="12" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C189" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D189" s="12">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="G189">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="12" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B190" s="12" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C190" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D190" s="12">
-        <v>0.64</v>
+        <v>0.81</v>
       </c>
       <c r="G190">
-        <v>0.04</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13">
-      <c r="A191" t="s">
-        <v>452</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C191" t="s">
+      <c r="A191" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C191" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="D191" s="4">
-        <v>0</v>
+      <c r="D191" s="12">
+        <v>0.84</v>
       </c>
       <c r="G191">
-        <v>0.26</v>
+        <v>0.6</v>
       </c>
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="12" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C192" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D192" s="12">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="G192">
-        <v>0.54</v>
+        <v>0.04</v>
       </c>
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13">
-      <c r="A193" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="B193" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="C193" s="12" t="s">
+      <c r="A193" t="s">
+        <v>452</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C193" t="s">
         <v>358</v>
       </c>
-      <c r="D193" s="12">
-        <v>0.91</v>
+      <c r="D193" s="4">
+        <v>0</v>
       </c>
       <c r="G193">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="12" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B194" s="12" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C194" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D194" s="12">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="G194">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="12" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B195" s="12" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C195" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D195" s="12">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="G195">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="12" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C196" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D196" s="12">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="G196">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="12" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B197" s="12" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C197" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D197" s="12">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="G197">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="12" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B198" s="12" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C198" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D198" s="12">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="G198">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="12" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B199" s="12" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D199" s="12">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="G199">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="12" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C200" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D200" s="12">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="G200">
-        <v>0.37</v>
+        <v>0.6</v>
       </c>
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
-      <c r="A201" t="s">
-        <v>460</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C201" t="s">
+      <c r="A201" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B201" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="C201" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="D201" s="4">
-        <v>0</v>
+      <c r="D201" s="12">
+        <v>0.84</v>
       </c>
       <c r="G201">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="12" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B202" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C202" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D202" s="12">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="G202">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="M202" s="6"/>
     </row>
     <row r="203" spans="1:13">
-      <c r="A203" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="B203" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="C203" s="12" t="s">
+      <c r="A203" t="s">
+        <v>460</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C203" t="s">
         <v>358</v>
       </c>
-      <c r="D203" s="12">
-        <v>0.82</v>
+      <c r="D203" s="4">
+        <v>0</v>
       </c>
       <c r="G203">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="M203" s="6"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="12" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B204" s="12" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C204" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D204" s="12">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="G204">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="M204" s="6"/>
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="12" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B205" s="12" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C205" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D205" s="12">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="G205">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="M205" s="6"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="12" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B206" s="12" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D206" s="12">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="G206">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="M206" s="6"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="12" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B207" s="12" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C207" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D207" s="12">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
       <c r="G207">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="M207" s="6"/>
     </row>
     <row r="208" spans="1:13">
-      <c r="A208" t="s">
-        <v>454</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C208" t="s">
+      <c r="A208" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B208" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="C208" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="D208" s="4">
-        <v>0</v>
+      <c r="D208" s="12">
+        <v>0.79</v>
       </c>
       <c r="G208">
-        <v>0.05</v>
+        <v>0.44</v>
       </c>
       <c r="M208" s="6"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B209" s="12" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C209" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D209" s="12">
+        <v>0.77</v>
+      </c>
+      <c r="G209">
         <v>0.75</v>
       </c>
-      <c r="G209">
+      <c r="M209" s="6"/>
+    </row>
+    <row r="210" spans="1:13">
+      <c r="A210" t="s">
+        <v>454</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C210" t="s">
+        <v>358</v>
+      </c>
+      <c r="D210" s="4">
+        <v>0</v>
+      </c>
+      <c r="G210">
+        <v>0.05</v>
+      </c>
+      <c r="M210" s="6"/>
+    </row>
+    <row r="211" spans="1:13">
+      <c r="A211" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D211" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="G211">
         <v>0.53</v>
-      </c>
-      <c r="M209" s="6"/>
-    </row>
-    <row r="210" spans="1:13">
-      <c r="A210" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="B210" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="C210" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D210" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="G210">
-        <v>0.32</v>
-      </c>
-      <c r="M210" s="6"/>
-    </row>
-    <row r="211" spans="1:13">
-      <c r="A211" t="s">
-        <v>458</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C211" t="s">
-        <v>358</v>
-      </c>
-      <c r="D211" s="4">
-        <v>0</v>
-      </c>
-      <c r="G211">
-        <v>0.44</v>
       </c>
       <c r="M211" s="6"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B212" s="12" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C212" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D212" s="12">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="G212">
-        <v>0.68</v>
+        <v>0.32</v>
       </c>
       <c r="M212" s="6"/>
     </row>
     <row r="213" spans="1:13">
-      <c r="A213" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="B213" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="C213" s="12" t="s">
+      <c r="A213" t="s">
+        <v>458</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C213" t="s">
         <v>358</v>
       </c>
-      <c r="D213" s="12">
-        <v>0.62</v>
+      <c r="D213" s="4">
+        <v>0</v>
       </c>
       <c r="G213">
-        <v>0.56000000000000005</v>
+        <v>0.44</v>
       </c>
       <c r="M213" s="6"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="12" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B214" s="12" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C214" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D214" s="12">
-        <v>0.94</v>
+        <v>0.74</v>
       </c>
       <c r="G214">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="M214" s="6"/>
     </row>
     <row r="215" spans="1:13">
-      <c r="A215" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="B215" s="18" t="s">
-        <v>416</v>
+      <c r="A215" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B215" s="12" t="s">
+        <v>412</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>417</v>
+        <v>358</v>
       </c>
       <c r="D215" s="12">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="G215">
-        <v>0.79</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M215" s="6"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="12" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B216" s="12" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>417</v>
+        <v>358</v>
       </c>
       <c r="D216" s="12">
-        <v>0.61</v>
+        <v>0.94</v>
       </c>
       <c r="G216">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="M216" s="6"/>
     </row>
     <row r="217" spans="1:13">
-      <c r="A217" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="B217" s="12" t="s">
-        <v>421</v>
+      <c r="A217" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="B217" s="21" t="s">
+        <v>416</v>
       </c>
       <c r="C217" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D217" s="12">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="G217">
-        <v>0.54</v>
+        <v>0.79</v>
       </c>
       <c r="M217" s="6"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="12" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B218" s="12" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C218" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D218" s="12">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="G218">
-        <v>0.11</v>
+        <v>0.32</v>
       </c>
       <c r="M218" s="6"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="12" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B219" s="12" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C219" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D219" s="12">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="G219">
         <v>0.54</v>
@@ -6148,298 +6196,298 @@
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="12" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B220" s="12" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C220" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D220" s="12">
+        <v>0.67</v>
+      </c>
+      <c r="G220">
+        <v>0.11</v>
+      </c>
+      <c r="M220" s="6"/>
+    </row>
+    <row r="221" spans="1:13">
+      <c r="A221" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="D221" s="12">
+        <v>0.71</v>
+      </c>
+      <c r="G221">
+        <v>0.54</v>
+      </c>
+      <c r="M221" s="6"/>
+    </row>
+    <row r="222" spans="1:13">
+      <c r="A222" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="B222" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="D222" s="12">
         <v>0.89</v>
       </c>
-      <c r="G220">
+      <c r="G222">
         <v>0.61</v>
       </c>
-      <c r="M220" s="6"/>
-    </row>
-    <row r="221" spans="1:13">
-      <c r="A221" s="19" t="s">
+      <c r="M222" s="6"/>
+    </row>
+    <row r="223" spans="1:13">
+      <c r="A223" s="22" t="s">
         <v>470</v>
       </c>
-      <c r="B221" s="20" t="s">
+      <c r="B223" s="23" t="s">
         <v>471</v>
       </c>
-      <c r="C221" t="s">
+      <c r="C223" t="s">
         <v>430</v>
       </c>
-      <c r="D221" s="4">
+      <c r="D223" s="4">
         <v>0</v>
       </c>
-      <c r="G221">
+      <c r="G223">
         <v>0.33</v>
       </c>
-      <c r="M221" s="16"/>
-    </row>
-    <row r="222" spans="1:13">
-      <c r="A222" s="18" t="s">
+      <c r="M223" s="19"/>
+    </row>
+    <row r="224" spans="1:13">
+      <c r="A224" s="21" t="s">
         <v>428</v>
       </c>
-      <c r="B222" s="18" t="s">
+      <c r="B224" s="21" t="s">
         <v>429</v>
-      </c>
-      <c r="C222" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D222" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="G222">
-        <v>0.26</v>
-      </c>
-      <c r="M222" s="6"/>
-    </row>
-    <row r="223" spans="1:13">
-      <c r="A223" s="18" t="s">
-        <v>431</v>
-      </c>
-      <c r="B223" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="C223" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D223" s="12">
-        <v>0.66</v>
-      </c>
-      <c r="G223">
-        <v>0.16</v>
-      </c>
-      <c r="M223" s="6"/>
-    </row>
-    <row r="224" spans="1:13">
-      <c r="A224" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="B224" s="12" t="s">
-        <v>434</v>
       </c>
       <c r="C224" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D224" s="12">
-        <v>0.69</v>
+        <v>0.79</v>
       </c>
       <c r="G224">
-        <v>0.28000000000000003</v>
+        <v>0.26</v>
       </c>
       <c r="M224" s="6"/>
     </row>
     <row r="225" spans="1:13">
-      <c r="A225" t="s">
-        <v>474</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="C225" t="s">
+      <c r="A225" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="B225" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="C225" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="D225" s="4">
-        <v>0</v>
+      <c r="D225" s="12">
+        <v>0.66</v>
       </c>
       <c r="G225">
         <v>0.16</v>
       </c>
-      <c r="M225" s="16"/>
+      <c r="M225" s="6"/>
     </row>
     <row r="226" spans="1:13">
-      <c r="A226" t="s">
+      <c r="A226" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="B226" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D226" s="12">
+        <v>0.69</v>
+      </c>
+      <c r="G226">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M226" s="6"/>
+    </row>
+    <row r="227" spans="1:13">
+      <c r="A227" t="s">
+        <v>474</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C227" t="s">
+        <v>430</v>
+      </c>
+      <c r="D227" s="4">
+        <v>0</v>
+      </c>
+      <c r="G227">
+        <v>0.16</v>
+      </c>
+      <c r="M227" s="19"/>
+    </row>
+    <row r="228" spans="1:13">
+      <c r="A228" t="s">
         <v>467</v>
       </c>
-      <c r="B226" s="2" t="s">
+      <c r="B228" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="C226" t="s">
+      <c r="C228" t="s">
         <v>430</v>
       </c>
-      <c r="D226" s="4">
+      <c r="D228" s="4">
         <v>0</v>
-      </c>
-      <c r="G226">
-        <v>0.26</v>
-      </c>
-      <c r="M226" s="16"/>
-    </row>
-    <row r="227" spans="1:13">
-      <c r="A227" s="12" t="s">
-        <v>435</v>
-      </c>
-      <c r="B227" s="12" t="s">
-        <v>436</v>
-      </c>
-      <c r="C227" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D227" s="12">
-        <v>0.83</v>
-      </c>
-      <c r="G227">
-        <v>0.63</v>
-      </c>
-      <c r="M227" s="6"/>
-    </row>
-    <row r="228" spans="1:13">
-      <c r="A228" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="B228" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="C228" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D228" s="12">
-        <v>0.79</v>
       </c>
       <c r="G228">
         <v>0.26</v>
       </c>
-      <c r="M228" s="6"/>
+      <c r="M228" s="19"/>
     </row>
     <row r="229" spans="1:13">
       <c r="A229" s="12" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B229" s="12" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C229" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D229" s="12">
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="G229">
-        <v>0.67</v>
-      </c>
-      <c r="M229" s="17"/>
+        <v>0.63</v>
+      </c>
+      <c r="M229" s="20"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="12" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B230" s="12" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C230" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D230" s="12">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="G230">
-        <v>0.37</v>
-      </c>
-      <c r="M230" s="17"/>
+        <v>0.26</v>
+      </c>
+      <c r="M230" s="20"/>
     </row>
     <row r="231" spans="1:13">
-      <c r="A231" t="s">
-        <v>478</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="C231" t="s">
+      <c r="A231" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B231" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="C231" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="D231" s="4">
-        <v>0</v>
+      <c r="D231" s="12">
+        <v>0.81</v>
       </c>
       <c r="G231">
-        <v>0.35</v>
-      </c>
-      <c r="M231" s="19"/>
+        <v>0.67</v>
+      </c>
+      <c r="M231" s="20"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" s="12" t="s">
-        <v>32</v>
+        <v>441</v>
       </c>
       <c r="B232" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D232" s="12">
+        <v>0.74</v>
+      </c>
+      <c r="G232">
+        <v>0.37</v>
+      </c>
+      <c r="M232" s="20"/>
+    </row>
+    <row r="233" spans="1:13">
+      <c r="A233" t="s">
+        <v>478</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C233" t="s">
+        <v>430</v>
+      </c>
+      <c r="D233" s="4">
+        <v>0</v>
+      </c>
+      <c r="G233">
+        <v>0.35</v>
+      </c>
+      <c r="M233" s="22"/>
+    </row>
+    <row r="234" spans="1:13">
+      <c r="A234" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B234" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D234" s="12">
         <v>0.75</v>
       </c>
-      <c r="G232">
+      <c r="G234">
         <v>0.44</v>
       </c>
-      <c r="M232" s="17"/>
-    </row>
-    <row r="233" spans="1:13">
-      <c r="A233" s="12" t="s">
+      <c r="M234" s="20"/>
+    </row>
+    <row r="235" spans="1:13">
+      <c r="A235" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B233" s="12" t="s">
+      <c r="B235" s="12" t="s">
         <v>444</v>
       </c>
-      <c r="C233" s="12" t="s">
+      <c r="C235" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="D233" s="12">
+      <c r="D235" s="12">
         <v>0.65</v>
       </c>
-      <c r="G233">
+      <c r="G235">
         <v>0.63</v>
       </c>
-      <c r="M233" s="17"/>
-    </row>
-    <row r="234" spans="1:13">
-      <c r="A234" t="s">
-        <v>472</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C234" t="s">
-        <v>430</v>
-      </c>
-      <c r="D234" s="4">
-        <v>0</v>
-      </c>
-      <c r="G234">
-        <v>0.54</v>
-      </c>
-      <c r="M234" s="19"/>
-    </row>
-    <row r="235" spans="1:13">
-      <c r="A235" t="s">
-        <v>476</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="C235" t="s">
-        <v>430</v>
-      </c>
-      <c r="D235" s="4">
-        <v>0</v>
-      </c>
-      <c r="G235">
-        <v>0.42</v>
-      </c>
-      <c r="M235" s="19"/>
+      <c r="M235" s="20"/>
     </row>
     <row r="236" spans="1:13">
       <c r="A236" t="s">
-        <v>175</v>
+        <v>472</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C236" t="s">
         <v>430</v>
@@ -6448,45 +6496,81 @@
         <v>0</v>
       </c>
       <c r="G236">
+        <v>0.54</v>
+      </c>
+      <c r="M236" s="22"/>
+    </row>
+    <row r="237" spans="1:13">
+      <c r="A237" t="s">
+        <v>476</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C237" t="s">
+        <v>430</v>
+      </c>
+      <c r="D237" s="4">
+        <v>0</v>
+      </c>
+      <c r="G237">
+        <v>0.42</v>
+      </c>
+      <c r="M237" s="22"/>
+    </row>
+    <row r="238" spans="1:13">
+      <c r="A238" t="s">
+        <v>175</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C238" t="s">
+        <v>430</v>
+      </c>
+      <c r="D238" s="4">
+        <v>0</v>
+      </c>
+      <c r="G238">
         <v>0.49</v>
       </c>
-      <c r="M236" s="19"/>
-    </row>
-    <row r="237" spans="1:13">
-      <c r="A237" s="12" t="s">
+      <c r="M238" s="22"/>
+    </row>
+    <row r="239" spans="1:13">
+      <c r="A239" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="B237" s="12" t="s">
+      <c r="B239" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="C237" s="12" t="s">
+      <c r="C239" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="D237" s="12">
+      <c r="D239" s="12">
         <v>0.87</v>
       </c>
-      <c r="G237">
+      <c r="G239">
         <v>0.47</v>
       </c>
-      <c r="M237" s="17"/>
-    </row>
-    <row r="238" spans="1:13">
-      <c r="A238" s="12" t="s">
+      <c r="M239" s="20"/>
+    </row>
+    <row r="240" spans="1:13">
+      <c r="A240" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="B238" s="12" t="s">
+      <c r="B240" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="C238" s="12" t="s">
+      <c r="C240" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="D238" s="12">
+      <c r="D240" s="12">
         <v>0.7</v>
       </c>
-      <c r="G238">
+      <c r="G240">
         <v>0.19</v>
       </c>
-      <c r="M238" s="17"/>
+      <c r="M240" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6400264E-C825-964B-9EFF-CD067A3EAD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D0B8F1-2593-AA46-9399-E9DCD5FFC5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="495">
   <si>
     <t>Surname</t>
   </si>
@@ -1512,6 +1512,15 @@
   </si>
   <si>
     <t>H240460T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>Mujee</t>
+  </si>
+  <si>
+    <t>H240044A</t>
   </si>
 </sst>
 </file>
@@ -1668,9 +1677,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1725,10 +1734,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M240" totalsRowShown="0">
-  <autoFilter ref="A1:M240" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M240">
-    <sortCondition ref="C1:C240"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M241" totalsRowShown="0">
+  <autoFilter ref="A1:M241" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M241">
+    <sortCondition ref="C1:C241"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -2066,7 +2075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:M240"/>
+  <dimension ref="A1:M241"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -2304,8 +2313,8 @@
       <c r="D10" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="G10">
-        <v>0.54</v>
+      <c r="G10" t="s">
+        <v>492</v>
       </c>
       <c r="H10" s="5"/>
       <c r="J10">
@@ -2427,6 +2436,9 @@
       <c r="D16" s="4">
         <v>0.75</v>
       </c>
+      <c r="G16">
+        <v>0.67</v>
+      </c>
       <c r="H16" s="5"/>
       <c r="J16">
         <v>0.68</v>
@@ -2490,6 +2502,9 @@
       <c r="D19" s="4">
         <v>0.68</v>
       </c>
+      <c r="G19">
+        <v>0.44</v>
+      </c>
       <c r="H19" s="5"/>
       <c r="J19">
         <v>0.48</v>
@@ -2497,58 +2512,57 @@
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>49</v>
+      <c r="A20" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>494</v>
       </c>
       <c r="C20" t="s">
         <v>71</v>
       </c>
       <c r="D20" s="4">
-        <v>0.85</v>
-      </c>
-      <c r="H20" s="5"/>
-      <c r="J20">
-        <v>0.48</v>
-      </c>
-      <c r="M20" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0.53</v>
+      </c>
+      <c r="M20" s="19"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>48</v>
+      <c r="A21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="C21" t="s">
         <v>71</v>
       </c>
       <c r="D21" s="4">
-        <v>0.78</v>
-      </c>
-      <c r="G21">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="H21" s="5"/>
       <c r="J21">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
         <v>71</v>
       </c>
       <c r="D22" s="4">
-        <v>0.82</v>
+        <v>0.78</v>
+      </c>
+      <c r="G22">
+        <v>0.65</v>
       </c>
       <c r="H22" s="5"/>
       <c r="J22">
@@ -2557,17 +2571,17 @@
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>46</v>
+      <c r="A23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="C23" t="s">
         <v>71</v>
       </c>
       <c r="D23" s="4">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="H23" s="5"/>
       <c r="J23">
@@ -2576,206 +2590,212 @@
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>50</v>
+      <c r="A24" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="C24" t="s">
         <v>71</v>
       </c>
       <c r="D24" s="4">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="G24">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H24" s="5"/>
       <c r="J24">
-        <v>0.48</v>
+        <v>0.68</v>
       </c>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
         <v>71</v>
       </c>
       <c r="D25" s="4">
+        <v>0.74</v>
+      </c>
+      <c r="G25">
         <v>0.67</v>
-      </c>
-      <c r="G25">
-        <v>0.61</v>
       </c>
       <c r="H25" s="5"/>
       <c r="J25">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>51</v>
+      <c r="A26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C26" t="s">
         <v>71</v>
       </c>
       <c r="D26" s="4">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="G26">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="H26" s="5"/>
       <c r="J26">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>42</v>
+      <c r="A27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="C27" t="s">
         <v>71</v>
       </c>
       <c r="D27" s="4">
-        <v>0.83</v>
+        <v>0.85</v>
+      </c>
+      <c r="G27">
+        <v>0.53</v>
       </c>
       <c r="H27" s="5"/>
       <c r="J27">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
         <v>71</v>
       </c>
       <c r="D28" s="4">
-        <v>0.77</v>
-      </c>
-      <c r="G28">
-        <v>0.63</v>
+        <v>0.83</v>
       </c>
       <c r="H28" s="5"/>
       <c r="J28">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>56</v>
+      <c r="A29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="C29" t="s">
         <v>71</v>
       </c>
       <c r="D29" s="4">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="G29">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="H29" s="5"/>
       <c r="J29">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>63</v>
+      <c r="A30" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="C30" t="s">
         <v>71</v>
       </c>
       <c r="D30" s="4">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>0.35</v>
+        <v>0.75</v>
       </c>
       <c r="H30" s="5"/>
       <c r="J30">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>85</v>
+      <c r="A31" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="D31" s="4">
-        <v>0.79</v>
+        <v>0.86</v>
+      </c>
+      <c r="G31">
+        <v>0.35</v>
       </c>
       <c r="H31" s="5"/>
       <c r="J31">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>97</v>
+      <c r="A32" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="C32" t="s">
         <v>100</v>
       </c>
       <c r="D32" s="4">
-        <v>0.84</v>
+        <v>0.79</v>
+      </c>
+      <c r="G32">
+        <v>0.6</v>
       </c>
       <c r="H32" s="5"/>
       <c r="J32">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="7" t="s">
-        <v>487</v>
+        <v>83</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
         <v>100</v>
       </c>
       <c r="D33" s="4">
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="H33" s="5"/>
       <c r="J33">
@@ -2784,107 +2804,107 @@
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0.81</v>
+      </c>
+      <c r="H34" s="5"/>
+      <c r="J34">
+        <v>0.8</v>
+      </c>
+      <c r="M34" s="6"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B35" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C35" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D35" s="4">
         <v>0.65</v>
       </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="M34" s="6"/>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" s="4">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35" s="5"/>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>87</v>
+      <c r="A36" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
       </c>
       <c r="D36" s="4">
-        <v>0.84</v>
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
       </c>
       <c r="H36" s="5"/>
       <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="M36" s="6"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="H37" s="5"/>
+      <c r="J37">
         <v>0.24</v>
       </c>
-      <c r="M36" s="6"/>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="A37" s="15" t="s">
+      <c r="M37" s="6"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="14" t="s">
         <v>451</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B38" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C38" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D38" s="4">
         <v>0.66</v>
       </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="M37" s="6"/>
-    </row>
-    <row r="38" spans="1:13" ht="20">
-      <c r="A38" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" s="4">
-        <v>0</v>
-      </c>
-      <c r="H38" s="5"/>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="M38" s="6"/>
     </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="16" t="s">
-        <v>488</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>489</v>
+    <row r="39" spans="1:13" ht="20">
+      <c r="A39" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -2892,42 +2912,42 @@
       <c r="D39" s="4">
         <v>0</v>
       </c>
-      <c r="G39">
-        <v>0.52</v>
-      </c>
-      <c r="M39" s="19"/>
+      <c r="H39" s="5"/>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>88</v>
+      <c r="A40" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>489</v>
       </c>
       <c r="C40" t="s">
         <v>100</v>
       </c>
       <c r="D40" s="4">
-        <v>0.73</v>
-      </c>
-      <c r="H40" s="5"/>
-      <c r="J40">
-        <v>0.8</v>
-      </c>
-      <c r="M40" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0.52</v>
+      </c>
+      <c r="M40" s="19"/>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>99</v>
+      <c r="A41" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="C41" t="s">
         <v>100</v>
       </c>
       <c r="D41" s="4">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="H41" s="5"/>
       <c r="J41">
@@ -2936,36 +2956,36 @@
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>92</v>
+      <c r="A42" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="C42" t="s">
         <v>100</v>
       </c>
       <c r="D42" s="4">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H42" s="5"/>
       <c r="J42">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
         <v>100</v>
       </c>
       <c r="D43" s="4">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="H43" s="5"/>
       <c r="J43">
@@ -2974,76 +2994,76 @@
       <c r="M43" s="6"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="16" t="s">
-        <v>490</v>
-      </c>
-      <c r="B44" s="18" t="s">
-        <v>491</v>
+      <c r="A44" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>96</v>
       </c>
       <c r="C44" t="s">
         <v>100</v>
       </c>
       <c r="D44" s="4">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0.54</v>
-      </c>
-      <c r="M44" s="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="H44" s="5"/>
+      <c r="J44">
+        <v>0.24</v>
+      </c>
+      <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>94</v>
+      <c r="A45" s="22" t="s">
+        <v>490</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>491</v>
       </c>
       <c r="C45" t="s">
         <v>100</v>
       </c>
       <c r="D45" s="4">
-        <v>0.64</v>
-      </c>
-      <c r="H45" s="5"/>
-      <c r="J45">
-        <v>0.8</v>
-      </c>
-      <c r="M45" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0.54</v>
+      </c>
+      <c r="M45" s="19"/>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
         <v>100</v>
       </c>
       <c r="D46" s="4">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="H46" s="5"/>
       <c r="J46">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>89</v>
+      <c r="A47" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="C47" t="s">
         <v>100</v>
       </c>
       <c r="D47" s="4">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="G47">
-        <v>0.54</v>
+        <v>0.44</v>
       </c>
       <c r="H47" s="5"/>
       <c r="J47">
@@ -3052,115 +3072,115 @@
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>86</v>
+      <c r="A48" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>89</v>
       </c>
       <c r="C48" t="s">
         <v>100</v>
       </c>
       <c r="D48" s="4">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="G48">
-        <v>0.56000000000000005</v>
+        <v>0.54</v>
       </c>
       <c r="H48" s="5"/>
       <c r="J48">
+        <v>0.24</v>
+      </c>
+      <c r="M48" s="6"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="G49">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H49" s="5"/>
+      <c r="J49">
         <v>0.8</v>
       </c>
-      <c r="M48" s="6"/>
-    </row>
-    <row r="49" spans="1:13">
-      <c r="A49" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B49" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="G49">
-        <v>0.68</v>
-      </c>
-      <c r="H49" s="5"/>
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="21" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D50" s="12">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="G50">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="H50" s="5"/>
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D51" s="12">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="G51">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H51" s="5"/>
-      <c r="J51">
-        <v>0.92</v>
-      </c>
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D52" s="12">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G52">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="H52" s="5"/>
       <c r="J52">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>103</v>
@@ -3169,403 +3189,404 @@
         <v>0.85</v>
       </c>
       <c r="G53">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="H53" s="5"/>
+      <c r="J53">
+        <v>0.83</v>
+      </c>
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D54" s="12">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="G54">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="H54" s="5"/>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>486</v>
+        <v>113</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D55" s="12">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="G55">
-        <v>0.56000000000000005</v>
+        <v>0.33</v>
       </c>
       <c r="H55" s="5"/>
-      <c r="J55">
-        <v>0.83</v>
-      </c>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>116</v>
+        <v>486</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D56" s="12">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="G56">
-        <v>0.32</v>
-      </c>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H56" s="5"/>
       <c r="J56">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D57" s="12">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="G57">
-        <v>0.51</v>
+        <v>0.32</v>
+      </c>
+      <c r="J57">
+        <v>0.92</v>
       </c>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D58" s="12">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="G58">
-        <v>0.32</v>
+        <v>0.51</v>
       </c>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>122</v>
+      <c r="A59" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>120</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D59" s="12">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="G59">
-        <v>0.81</v>
-      </c>
-      <c r="J59">
-        <v>0.92</v>
+        <v>0.32</v>
       </c>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D60" s="12">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G60">
-        <v>0.46</v>
+        <v>0.81</v>
       </c>
       <c r="J60">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D61" s="12">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="G61">
         <v>0.46</v>
       </c>
+      <c r="J61">
+        <v>0.83</v>
+      </c>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C62" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D62" s="12">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="G62">
-        <v>0.37</v>
-      </c>
-      <c r="J62">
-        <v>0.83</v>
+        <v>0.46</v>
       </c>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D63" s="12">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="G63">
-        <v>0.63</v>
+        <v>0.37</v>
+      </c>
+      <c r="J63">
+        <v>0.83</v>
       </c>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D64" s="12">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="G64">
-        <v>0.37</v>
+        <v>0.63</v>
       </c>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D65" s="12">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="G65">
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D66" s="12">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="G66">
-        <v>0.35</v>
+        <v>0.53</v>
       </c>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D67" s="12">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="G67">
-        <v>0.77</v>
-      </c>
-      <c r="J67">
-        <v>0.83</v>
+        <v>0.35</v>
       </c>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D68" s="12">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="G68">
-        <v>0.6</v>
+        <v>0.77</v>
+      </c>
+      <c r="J68">
+        <v>0.83</v>
       </c>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>142</v>
+      <c r="A69" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>140</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D69" s="12">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="G69">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="J69">
-        <v>0.92</v>
+        <v>0.6</v>
       </c>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>144</v>
+      <c r="A70" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>142</v>
       </c>
       <c r="C70" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D70" s="12">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G70">
-        <v>0.57999999999999996</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J70">
+        <v>0.92</v>
       </c>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D71" s="12">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="G71">
-        <v>0.35</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D72" s="12">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="G72">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D73" s="12">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G73">
-        <v>0.77</v>
-      </c>
-      <c r="J73">
-        <v>0.83</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C74" s="12" t="s">
         <v>103</v>
@@ -3574,130 +3595,133 @@
         <v>0.84</v>
       </c>
       <c r="G74">
-        <v>0.51</v>
+        <v>0.77</v>
+      </c>
+      <c r="J74">
+        <v>0.83</v>
       </c>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D75" s="12">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="G75">
-        <v>0.05</v>
+        <v>0.51</v>
       </c>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C76" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D76" s="12">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
       <c r="G76">
-        <v>0.61</v>
+        <v>0.05</v>
       </c>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D77" s="12">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G77">
-        <v>0.74</v>
-      </c>
-      <c r="J77">
-        <v>0.92</v>
+        <v>0.61</v>
       </c>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D78" s="12">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="G78">
-        <v>0.57999999999999996</v>
+        <v>0.74</v>
+      </c>
+      <c r="J78">
+        <v>0.92</v>
       </c>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D79" s="12">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="G79">
-        <v>0.61</v>
-      </c>
-      <c r="J79">
-        <v>0.92</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D80" s="12">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="G80">
-        <v>0.47</v>
+        <v>0.61</v>
+      </c>
+      <c r="J80">
+        <v>0.92</v>
       </c>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>103</v>
@@ -3706,178 +3730,178 @@
         <v>0.84</v>
       </c>
       <c r="G81">
-        <v>0.65</v>
+        <v>0.47</v>
       </c>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D82" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="G82">
+        <v>0.65</v>
+      </c>
+      <c r="M82" s="6"/>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D83" s="12">
         <v>0.74</v>
       </c>
-      <c r="G82">
+      <c r="G83">
         <v>0.39</v>
       </c>
-      <c r="M82" s="6"/>
-    </row>
-    <row r="83" spans="1:13">
-      <c r="A83" t="s">
+      <c r="M83" s="6"/>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" t="s">
         <v>342</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B84" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C84" t="s">
         <v>103</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D84" s="4">
         <v>0</v>
       </c>
-      <c r="G83">
+      <c r="G84">
         <v>0.54</v>
-      </c>
-      <c r="M83" s="6"/>
-    </row>
-    <row r="84" spans="1:13">
-      <c r="A84" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="B84" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D84" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="G84">
-        <v>0.79</v>
       </c>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D85" s="12">
-        <v>0.71</v>
+        <v>0.81</v>
       </c>
       <c r="G85">
-        <v>0.63</v>
+        <v>0.79</v>
       </c>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D86" s="12">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="G86">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="M86" s="6"/>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C87" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D87" s="12">
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
       <c r="G87">
-        <v>0.25</v>
+        <v>0.61</v>
       </c>
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
-      <c r="A88" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="B88" s="12" t="s">
-        <v>178</v>
+      <c r="A88" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B88" s="21" t="s">
+        <v>176</v>
       </c>
       <c r="C88" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D88" s="12">
-        <v>0.83</v>
+        <v>0.81</v>
       </c>
       <c r="G88">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C89" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D89" s="12">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="G89">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="21" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="D90" s="12">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="G90">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="21" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C91" s="12" t="s">
         <v>183</v>
@@ -3886,457 +3910,457 @@
         <v>0.75</v>
       </c>
       <c r="G91">
+        <v>0.68</v>
+      </c>
+      <c r="M91" s="6"/>
+    </row>
+    <row r="92" spans="1:13">
+      <c r="A92" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B92" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D92" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="G92">
         <v>0.6</v>
       </c>
-      <c r="M91" s="6"/>
-    </row>
-    <row r="92" spans="1:13">
-      <c r="A92" s="22" t="s">
+      <c r="M92" s="6"/>
+    </row>
+    <row r="93" spans="1:13">
+      <c r="A93" s="22" t="s">
         <v>484</v>
       </c>
-      <c r="B92" s="23" t="s">
+      <c r="B93" s="23" t="s">
         <v>485</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C93" t="s">
         <v>183</v>
       </c>
-      <c r="D92" s="4">
+      <c r="D93" s="4">
         <v>0</v>
       </c>
-      <c r="G92">
+      <c r="G93">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M92" s="19"/>
-    </row>
-    <row r="93" spans="1:13">
-      <c r="A93" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="B93" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D93" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="G93">
-        <v>0.47</v>
-      </c>
-      <c r="M93" s="6"/>
+      <c r="M93" s="19"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C94" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D94" s="12">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="G94">
-        <v>0.65</v>
+        <v>0.47</v>
       </c>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D95" s="12">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="G95">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C96" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D96" s="12">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
       <c r="G96">
-        <v>0.79</v>
+        <v>0.42</v>
       </c>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="21" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D97" s="12">
+        <v>0.93</v>
+      </c>
+      <c r="G97">
         <v>0.79</v>
       </c>
-      <c r="G97">
-        <v>0.46</v>
-      </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
-      <c r="A98" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B98" s="12" t="s">
-        <v>197</v>
+      <c r="A98" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="B98" s="21" t="s">
+        <v>195</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D98" s="12">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="G98">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C99" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D99" s="12">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="G99">
-        <v>0.28000000000000003</v>
+        <v>0.72</v>
       </c>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
-      <c r="A100" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="B100" s="12" t="s">
-        <v>201</v>
+      <c r="A100" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" s="21" t="s">
+        <v>199</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D100" s="12">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="G100">
-        <v>0.4</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D101" s="12">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="G101">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C102" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D102" s="12">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="G102">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
-      <c r="A103" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="B103" s="12" t="s">
-        <v>207</v>
+      <c r="A103" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" s="21" t="s">
+        <v>205</v>
       </c>
       <c r="C103" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D103" s="12">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="G103">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
-      <c r="A104" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B104" s="12" t="s">
-        <v>209</v>
+      <c r="A104" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="B104" s="21" t="s">
+        <v>207</v>
       </c>
       <c r="C104" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D104" s="12">
+        <v>0.89</v>
+      </c>
+      <c r="G104">
+        <v>0.49</v>
+      </c>
+      <c r="M104" s="6"/>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="A105" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D105" s="12">
         <v>0.85</v>
       </c>
-      <c r="G104">
+      <c r="G105">
         <v>0.54</v>
       </c>
-      <c r="M104" s="6"/>
-    </row>
-    <row r="105" spans="1:13">
-      <c r="A105" t="s">
+      <c r="M105" s="6"/>
+    </row>
+    <row r="106" spans="1:13">
+      <c r="A106" t="s">
         <v>480</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B106" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C106" t="s">
         <v>183</v>
       </c>
-      <c r="D105" s="4">
+      <c r="D106" s="4">
         <v>0</v>
       </c>
-      <c r="G105">
+      <c r="G106">
         <v>0.51</v>
       </c>
-      <c r="M105" s="19"/>
-    </row>
-    <row r="106" spans="1:13">
-      <c r="A106" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B106" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D106" s="12">
-        <v>0.86</v>
-      </c>
-      <c r="G106">
-        <v>0.4</v>
-      </c>
-      <c r="M106" s="6"/>
+      <c r="M106" s="19"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C107" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D107" s="12">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="G107">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D108" s="12">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="G108">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
-      <c r="A109" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="B109" s="12" t="s">
-        <v>217</v>
+      <c r="A109" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="B109" s="21" t="s">
+        <v>215</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D109" s="12">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="G109">
-        <v>0.75</v>
+        <v>0.39</v>
       </c>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D110" s="12">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="G110">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D111" s="12">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="G111">
-        <v>0.26</v>
+        <v>0.61</v>
       </c>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D112" s="12">
-        <v>0.94</v>
+        <v>0.83</v>
       </c>
       <c r="G112">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D113" s="12">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="G113">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C114" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D114" s="12">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="G114">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C115" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D115" s="12">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G115">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D116" s="12">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="G116">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="M116" s="6"/>
     </row>
@@ -4345,85 +4369,85 @@
         <v>230</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C117" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D117" s="12">
-        <v>0.92</v>
+        <v>0.66</v>
       </c>
       <c r="G117">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
       <c r="M117" s="6"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C118" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D118" s="12">
+        <v>0.92</v>
+      </c>
+      <c r="G118">
+        <v>0.44</v>
+      </c>
+      <c r="M118" s="6"/>
+    </row>
+    <row r="119" spans="1:13">
+      <c r="A119" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B119" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D119" s="12">
         <v>0.82</v>
       </c>
-      <c r="G118">
+      <c r="G119">
         <v>0.54</v>
       </c>
-      <c r="M118" s="6"/>
-    </row>
-    <row r="119" spans="1:13">
-      <c r="A119" t="s">
+      <c r="M119" s="6"/>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120" t="s">
         <v>481</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B120" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C120" t="s">
         <v>183</v>
       </c>
-      <c r="D119" s="4">
+      <c r="D120" s="4">
         <v>0</v>
       </c>
-      <c r="G119">
+      <c r="G120">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M119" s="19"/>
-    </row>
-    <row r="120" spans="1:13">
-      <c r="A120" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="B120" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="C120" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D120" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="G120">
-        <v>0.26</v>
-      </c>
-      <c r="M120" s="6"/>
+      <c r="M120" s="19"/>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C121" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D121" s="12">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="G121">
         <v>0.26</v>
@@ -4432,16 +4456,16 @@
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C122" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D122" s="12">
-        <v>0.69</v>
+        <v>0.96</v>
       </c>
       <c r="G122">
         <v>0.26</v>
@@ -4450,916 +4474,916 @@
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C123" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D123" s="12">
-        <v>0.78</v>
+        <v>0.69</v>
       </c>
       <c r="G123">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="M123" s="6"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D124" s="12">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="G124">
-        <v>0.49</v>
+        <v>0.09</v>
       </c>
       <c r="M124" s="6"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D125" s="12">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="G125">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
       <c r="M125" s="6"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D126" s="12">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="G126">
-        <v>0.26</v>
+        <v>0.74</v>
       </c>
       <c r="M126" s="6"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C127" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D127" s="12">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="G127">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="M127" s="6"/>
     </row>
     <row r="128" spans="1:13">
-      <c r="A128" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="B128" s="12" t="s">
-        <v>252</v>
+      <c r="A128" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B128" s="21" t="s">
+        <v>250</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D128" s="12">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="G128">
-        <v>0.11</v>
+        <v>0.32</v>
       </c>
       <c r="M128" s="6"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C129" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D129" s="12">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="G129">
-        <v>0.65</v>
+        <v>0.11</v>
       </c>
       <c r="M129" s="6"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C130" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D130" s="12">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="G130">
-        <v>0.28000000000000003</v>
+        <v>0.65</v>
       </c>
       <c r="M130" s="6"/>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="12" t="s">
-        <v>25</v>
+        <v>255</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C131" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D131" s="12">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="G131">
-        <v>0.47</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M131" s="6"/>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="12" t="s">
-        <v>258</v>
+        <v>25</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C132" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D132" s="12">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="G132">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="M132" s="6"/>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>262</v>
+        <v>183</v>
       </c>
       <c r="D133" s="12">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="G133">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="M133" s="6"/>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="21" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C134" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D134" s="12">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="G134">
-        <v>0.56000000000000005</v>
+        <v>0.4</v>
       </c>
       <c r="M134" s="6"/>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="21" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C135" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D135" s="12">
-        <v>0.93</v>
+        <v>0.81</v>
       </c>
       <c r="G135">
-        <v>0.63</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M135" s="6"/>
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="21" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B136" s="21" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C136" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D136" s="12">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="G136">
-        <v>0.42</v>
+        <v>0.63</v>
       </c>
       <c r="M136" s="6"/>
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="21" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B137" s="21" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C137" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D137" s="12">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="G137">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="M137" s="6"/>
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="21" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B138" s="21" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C138" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D138" s="12">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="G138">
-        <v>0.74</v>
+        <v>0.39</v>
       </c>
       <c r="M138" s="6"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="21" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B139" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C139" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D139" s="12">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="G139">
-        <v>0.39</v>
+        <v>0.74</v>
       </c>
       <c r="M139" s="6"/>
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="21" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B140" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C140" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D140" s="12">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="G140">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="M140" s="6"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B141" s="21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C141" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D141" s="12">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="G141">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="M141" s="6"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B142" s="21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C142" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D142" s="12">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="M142" s="6"/>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="21" t="s">
-        <v>115</v>
+        <v>279</v>
       </c>
       <c r="B143" s="21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C143" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D143" s="12">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="G143">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="M143" s="6"/>
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="21" t="s">
-        <v>282</v>
+        <v>115</v>
       </c>
       <c r="B144" s="21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D144" s="12">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="G144">
-        <v>0.65</v>
+        <v>0.16</v>
       </c>
       <c r="M144" s="6"/>
     </row>
     <row r="145" spans="1:13">
-      <c r="A145" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="B145" s="12" t="s">
-        <v>285</v>
+      <c r="A145" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="B145" s="21" t="s">
+        <v>283</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D145" s="12">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="G145">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="M145" s="6"/>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C146" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D146" s="12">
-        <v>0.94</v>
+        <v>0.87</v>
       </c>
       <c r="G146">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="M146" s="6"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C147" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D147" s="12">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="G147">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="M147" s="6"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C148" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D148" s="12">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="G148">
-        <v>0.21</v>
+        <v>0.63</v>
       </c>
       <c r="M148" s="6"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C149" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D149" s="12">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="G149">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="M149" s="6"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C150" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D150" s="12">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="G150">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="M150" s="6"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C151" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D151" s="12">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="G151">
-        <v>0.63</v>
+        <v>0.3</v>
       </c>
       <c r="M151" s="6"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C152" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D152" s="12">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="G152">
-        <v>0.86</v>
+        <v>0.63</v>
       </c>
       <c r="M152" s="6"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C153" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D153" s="12">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="G153">
-        <v>0.47</v>
+        <v>0.86</v>
       </c>
       <c r="M153" s="6"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C154" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D154" s="12">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="G154">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="M154" s="6"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C155" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D155" s="12">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="G155">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="M155" s="6"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C156" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D156" s="12">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="G156">
-        <v>0.65</v>
+        <v>0.44</v>
       </c>
       <c r="M156" s="6"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C157" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D157" s="12">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="G157">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="M157" s="6"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C158" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D158" s="12">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="G158">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="M158" s="6"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C159" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D159" s="12">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="G159">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="M159" s="6"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C160" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D160" s="12">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="G160">
-        <v>0.57999999999999996</v>
+        <v>0.42</v>
       </c>
       <c r="M160" s="6"/>
     </row>
     <row r="161" spans="1:13">
-      <c r="A161" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="B161" s="12" t="s">
-        <v>317</v>
+      <c r="A161" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="B161" s="21" t="s">
+        <v>315</v>
       </c>
       <c r="C161" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D161" s="12">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="G161">
-        <v>0.68</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M161" s="6"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C162" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D162" s="12">
-        <v>0.94</v>
+        <v>0.88</v>
       </c>
       <c r="G162">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C163" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D163" s="12">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="G163">
-        <v>0.33</v>
+        <v>0.51</v>
       </c>
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C164" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D164" s="12">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="G164">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C165" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D165" s="12">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="G165">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="M165" s="6"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C166" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D166" s="12">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="G166">
-        <v>0.63</v>
+        <v>0.47</v>
       </c>
       <c r="M166" s="6"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C167" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D167" s="12">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="G167">
-        <v>0.56000000000000005</v>
+        <v>0.63</v>
       </c>
       <c r="M167" s="6"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C168" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D168" s="12">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="G168">
-        <v>0.54</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M168" s="6"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C169" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D169" s="12">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G169">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="M169" s="6"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C170" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D170" s="12">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="G170">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C171" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D171" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="G171">
+        <v>0.25</v>
+      </c>
+      <c r="M171" s="6"/>
+    </row>
+    <row r="172" spans="1:13">
+      <c r="A172" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B172" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D172" s="12">
         <v>0.9</v>
       </c>
-      <c r="G171">
+      <c r="G172">
         <v>0.39</v>
       </c>
-      <c r="M171" s="6"/>
-    </row>
-    <row r="172" spans="1:13">
-      <c r="A172" t="s">
+      <c r="M172" s="6"/>
+    </row>
+    <row r="173" spans="1:13">
+      <c r="A173" t="s">
         <v>465</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="B173" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C173" t="s">
         <v>262</v>
       </c>
-      <c r="D172" s="4">
+      <c r="D173" s="4">
         <v>0</v>
-      </c>
-      <c r="G172">
-        <v>0.35</v>
-      </c>
-      <c r="M172" s="6"/>
-    </row>
-    <row r="173" spans="1:13">
-      <c r="A173" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="B173" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="C173" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="D173" s="12">
-        <v>0.86</v>
       </c>
       <c r="G173">
         <v>0.35</v>
@@ -5367,443 +5391,443 @@
       <c r="M173" s="6"/>
     </row>
     <row r="174" spans="1:13">
-      <c r="A174" t="s">
+      <c r="A174" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D174" s="12">
+        <v>0.86</v>
+      </c>
+      <c r="G174">
+        <v>0.35</v>
+      </c>
+      <c r="M174" s="6"/>
+    </row>
+    <row r="175" spans="1:13">
+      <c r="A175" s="22" t="s">
         <v>463</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="B175" s="24" t="s">
         <v>464</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C175" t="s">
         <v>262</v>
       </c>
-      <c r="D174" s="4">
+      <c r="D175" s="4">
         <v>0</v>
       </c>
-      <c r="G174">
+      <c r="G175">
         <v>0.33</v>
-      </c>
-      <c r="M174" s="6"/>
-    </row>
-    <row r="175" spans="1:13">
-      <c r="A175" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="B175" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="C175" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="D175" s="12">
-        <v>0.69</v>
-      </c>
-      <c r="G175">
-        <v>0.12</v>
       </c>
       <c r="M175" s="6"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C176" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D176" s="12">
-        <v>0.77</v>
+        <v>0.69</v>
       </c>
       <c r="G176">
-        <v>0.46</v>
+        <v>0.12</v>
       </c>
       <c r="M176" s="6"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C177" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D177" s="12">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="G177">
-        <v>0.19</v>
+        <v>0.46</v>
       </c>
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
-      <c r="A178" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B178" s="12" t="s">
-        <v>347</v>
+      <c r="A178" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="B178" s="21" t="s">
+        <v>345</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D178" s="12">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="G178">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C179" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D179" s="12">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="G179">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C180" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D180" s="12">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="G180">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B181" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C181" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D181" s="12">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="G181">
-        <v>0.35</v>
+        <v>0.53</v>
       </c>
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C182" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D182" s="12">
+        <v>0.61</v>
+      </c>
+      <c r="G182">
+        <v>0.35</v>
+      </c>
+      <c r="M182" s="6"/>
+    </row>
+    <row r="183" spans="1:13">
+      <c r="A183" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D183" s="12">
         <v>0.75</v>
       </c>
-      <c r="G182">
+      <c r="G183">
         <v>0.32</v>
       </c>
-      <c r="M182" s="6"/>
-    </row>
-    <row r="183" spans="1:13">
-      <c r="A183" s="21" t="s">
+      <c r="M183" s="6"/>
+    </row>
+    <row r="184" spans="1:13">
+      <c r="A184" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="B183" s="21" t="s">
+      <c r="B184" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="C183" s="12" t="s">
+      <c r="C184" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="D183" s="12">
+      <c r="D184" s="12">
         <v>0.87</v>
       </c>
-      <c r="G183">
+      <c r="G184">
         <v>0.26</v>
       </c>
-      <c r="M183" s="6"/>
-    </row>
-    <row r="184" spans="1:13">
-      <c r="A184" s="22" t="s">
+      <c r="M184" s="6"/>
+    </row>
+    <row r="185" spans="1:13">
+      <c r="A185" s="22" t="s">
         <v>456</v>
       </c>
-      <c r="B184" s="24" t="s">
+      <c r="B185" s="24" t="s">
         <v>457</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C185" t="s">
         <v>358</v>
       </c>
-      <c r="D184" s="4">
+      <c r="D185" s="4">
         <v>0</v>
       </c>
-      <c r="G184">
+      <c r="G185">
         <v>0.19</v>
       </c>
-      <c r="M184" s="6"/>
-    </row>
-    <row r="185" spans="1:13">
-      <c r="A185" s="21" t="s">
+      <c r="M185" s="6"/>
+    </row>
+    <row r="186" spans="1:13">
+      <c r="A186" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="B185" s="21" t="s">
+      <c r="B186" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="C185" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D185" s="12">
-        <v>0.71</v>
-      </c>
-      <c r="G185">
-        <v>0.35</v>
-      </c>
-      <c r="M185" s="6"/>
-    </row>
-    <row r="186" spans="1:13">
-      <c r="A186" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="B186" s="12" t="s">
-        <v>362</v>
       </c>
       <c r="C186" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D186" s="12">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="G186">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C187" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D187" s="12">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="G187">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B188" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C188" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D188" s="12">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G188">
-        <v>0.68</v>
+        <v>0.39</v>
       </c>
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="12" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B189" s="12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C189" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D189" s="12">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="G189">
-        <v>0.42</v>
+        <v>0.68</v>
       </c>
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
-      <c r="A190" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="B190" s="12" t="s">
-        <v>370</v>
+      <c r="A190" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="B190" s="21" t="s">
+        <v>368</v>
       </c>
       <c r="C190" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D190" s="12">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="G190">
-        <v>0.57999999999999996</v>
+        <v>0.42</v>
       </c>
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B191" s="12" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C191" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D191" s="12">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="G191">
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="12" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C192" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D192" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="G192">
+        <v>0.6</v>
+      </c>
+      <c r="M192" s="6"/>
+    </row>
+    <row r="193" spans="1:13">
+      <c r="A193" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="C193" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D193" s="12">
         <v>0.64</v>
       </c>
-      <c r="G192">
+      <c r="G193">
         <v>0.04</v>
       </c>
-      <c r="M192" s="6"/>
-    </row>
-    <row r="193" spans="1:13">
-      <c r="A193" t="s">
+      <c r="M193" s="6"/>
+    </row>
+    <row r="194" spans="1:13">
+      <c r="A194" t="s">
         <v>452</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="B194" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C194" t="s">
         <v>358</v>
       </c>
-      <c r="D193" s="4">
+      <c r="D194" s="4">
         <v>0</v>
       </c>
-      <c r="G193">
+      <c r="G194">
         <v>0.26</v>
-      </c>
-      <c r="M193" s="6"/>
-    </row>
-    <row r="194" spans="1:13">
-      <c r="A194" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="B194" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="C194" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D194" s="12">
-        <v>0.78</v>
-      </c>
-      <c r="G194">
-        <v>0.54</v>
       </c>
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B195" s="12" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C195" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D195" s="12">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="G195">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="12" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C196" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D196" s="12">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="G196">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="12" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B197" s="12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C197" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D197" s="12">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="G197">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B198" s="12" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C198" s="12" t="s">
         <v>358</v>
@@ -5818,532 +5842,532 @@
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="12" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B199" s="12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D199" s="12">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="G199">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C200" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D200" s="12">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="G200">
-        <v>0.6</v>
+        <v>0.37</v>
       </c>
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B201" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C201" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D201" s="12">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G201">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="12" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B202" s="12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C202" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D202" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="G202">
+        <v>0.32</v>
+      </c>
+      <c r="M202" s="6"/>
+    </row>
+    <row r="203" spans="1:13">
+      <c r="A203" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="B203" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="C203" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D203" s="12">
         <v>0.85</v>
       </c>
-      <c r="G202">
+      <c r="G203">
         <v>0.37</v>
       </c>
-      <c r="M202" s="6"/>
-    </row>
-    <row r="203" spans="1:13">
-      <c r="A203" t="s">
+      <c r="M203" s="6"/>
+    </row>
+    <row r="204" spans="1:13">
+      <c r="A204" t="s">
         <v>460</v>
       </c>
-      <c r="B203" s="2" t="s">
+      <c r="B204" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="C203" t="s">
+      <c r="C204" t="s">
         <v>358</v>
       </c>
-      <c r="D203" s="4">
+      <c r="D204" s="4">
         <v>0</v>
       </c>
-      <c r="G203">
+      <c r="G204">
         <v>0.46</v>
-      </c>
-      <c r="M203" s="6"/>
-    </row>
-    <row r="204" spans="1:13">
-      <c r="A204" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="B204" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="C204" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D204" s="12">
-        <v>0.88</v>
-      </c>
-      <c r="G204">
-        <v>0.3</v>
       </c>
       <c r="M204" s="6"/>
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B205" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C205" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D205" s="12">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="G205">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="M205" s="6"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B206" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D206" s="12">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="G206">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="M206" s="6"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B207" s="12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C207" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D207" s="12">
-        <v>0.59</v>
+        <v>0.76</v>
       </c>
       <c r="G207">
-        <v>0.65</v>
+        <v>0.39</v>
       </c>
       <c r="M207" s="6"/>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B208" s="12" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C208" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D208" s="12">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
       <c r="G208">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="M208" s="6"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="12" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B209" s="12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C209" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D209" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="G209">
+        <v>0.44</v>
+      </c>
+      <c r="M209" s="6"/>
+    </row>
+    <row r="210" spans="1:13">
+      <c r="A210" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="B210" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D210" s="12">
         <v>0.77</v>
       </c>
-      <c r="G209">
+      <c r="G210">
         <v>0.75</v>
       </c>
-      <c r="M209" s="6"/>
-    </row>
-    <row r="210" spans="1:13">
-      <c r="A210" t="s">
+      <c r="M210" s="6"/>
+    </row>
+    <row r="211" spans="1:13">
+      <c r="A211" s="22" t="s">
         <v>454</v>
       </c>
-      <c r="B210" s="2" t="s">
+      <c r="B211" s="23" t="s">
         <v>455</v>
       </c>
-      <c r="C210" t="s">
+      <c r="C211" t="s">
         <v>358</v>
       </c>
-      <c r="D210" s="4">
+      <c r="D211" s="4">
         <v>0</v>
       </c>
-      <c r="G210">
+      <c r="G211">
         <v>0.05</v>
-      </c>
-      <c r="M210" s="6"/>
-    </row>
-    <row r="211" spans="1:13">
-      <c r="A211" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="B211" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="C211" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D211" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="G211">
-        <v>0.53</v>
       </c>
       <c r="M211" s="6"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="12" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B212" s="12" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C212" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D212" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="G212">
+        <v>0.53</v>
+      </c>
+      <c r="M212" s="6"/>
+    </row>
+    <row r="213" spans="1:13">
+      <c r="A213" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D213" s="12">
         <v>0.79</v>
       </c>
-      <c r="G212">
+      <c r="G213">
         <v>0.32</v>
       </c>
-      <c r="M212" s="6"/>
-    </row>
-    <row r="213" spans="1:13">
-      <c r="A213" t="s">
+      <c r="M213" s="6"/>
+    </row>
+    <row r="214" spans="1:13">
+      <c r="A214" t="s">
         <v>458</v>
       </c>
-      <c r="B213" s="2" t="s">
+      <c r="B214" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C214" t="s">
         <v>358</v>
       </c>
-      <c r="D213" s="4">
+      <c r="D214" s="4">
         <v>0</v>
       </c>
-      <c r="G213">
+      <c r="G214">
         <v>0.44</v>
-      </c>
-      <c r="M213" s="6"/>
-    </row>
-    <row r="214" spans="1:13">
-      <c r="A214" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="B214" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="C214" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D214" s="12">
-        <v>0.74</v>
-      </c>
-      <c r="G214">
-        <v>0.68</v>
       </c>
       <c r="M214" s="6"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="12" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B215" s="12" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C215" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D215" s="12">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="G215">
-        <v>0.56000000000000005</v>
+        <v>0.68</v>
       </c>
       <c r="M215" s="6"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B216" s="12" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C216" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D216" s="12">
-        <v>0.94</v>
+        <v>0.62</v>
       </c>
       <c r="G216">
-        <v>0.65</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M216" s="6"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="B217" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D217" s="12">
+        <v>0.94</v>
+      </c>
+      <c r="G217">
+        <v>0.65</v>
+      </c>
+      <c r="M217" s="6"/>
+    </row>
+    <row r="218" spans="1:13">
+      <c r="A218" s="21" t="s">
         <v>415</v>
       </c>
-      <c r="B217" s="21" t="s">
+      <c r="B218" s="21" t="s">
         <v>416</v>
-      </c>
-      <c r="C217" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="D217" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="G217">
-        <v>0.79</v>
-      </c>
-      <c r="M217" s="6"/>
-    </row>
-    <row r="218" spans="1:13">
-      <c r="A218" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="B218" s="12" t="s">
-        <v>419</v>
       </c>
       <c r="C218" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D218" s="12">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="G218">
-        <v>0.32</v>
+        <v>0.79</v>
       </c>
       <c r="M218" s="6"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B219" s="12" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C219" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D219" s="12">
-        <v>0.69</v>
+        <v>0.61</v>
       </c>
       <c r="G219">
-        <v>0.54</v>
+        <v>0.32</v>
       </c>
       <c r="M219" s="6"/>
     </row>
     <row r="220" spans="1:13">
-      <c r="A220" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="B220" s="12" t="s">
-        <v>423</v>
+      <c r="A220" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="B220" s="21" t="s">
+        <v>421</v>
       </c>
       <c r="C220" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D220" s="12">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="G220">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="M220" s="6"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B221" s="12" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C221" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D221" s="12">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="G221">
-        <v>0.54</v>
+        <v>0.11</v>
       </c>
       <c r="M221" s="6"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="12" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B222" s="12" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C222" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D222" s="12">
+        <v>0.71</v>
+      </c>
+      <c r="G222">
+        <v>0.54</v>
+      </c>
+      <c r="M222" s="6"/>
+    </row>
+    <row r="223" spans="1:13">
+      <c r="A223" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="B223" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="D223" s="12">
         <v>0.89</v>
       </c>
-      <c r="G222">
+      <c r="G223">
         <v>0.61</v>
       </c>
-      <c r="M222" s="6"/>
-    </row>
-    <row r="223" spans="1:13">
-      <c r="A223" s="22" t="s">
+      <c r="M223" s="6"/>
+    </row>
+    <row r="224" spans="1:13">
+      <c r="A224" s="22" t="s">
         <v>470</v>
       </c>
-      <c r="B223" s="23" t="s">
+      <c r="B224" s="23" t="s">
         <v>471</v>
       </c>
-      <c r="C223" t="s">
+      <c r="C224" t="s">
         <v>430</v>
       </c>
-      <c r="D223" s="4">
+      <c r="D224" s="4">
         <v>0</v>
       </c>
-      <c r="G223">
+      <c r="G224">
         <v>0.33</v>
       </c>
-      <c r="M223" s="19"/>
-    </row>
-    <row r="224" spans="1:13">
-      <c r="A224" s="21" t="s">
-        <v>428</v>
-      </c>
-      <c r="B224" s="21" t="s">
-        <v>429</v>
-      </c>
-      <c r="C224" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D224" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="G224">
-        <v>0.26</v>
-      </c>
-      <c r="M224" s="6"/>
+      <c r="M224" s="19"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="21" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B225" s="21" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C225" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D225" s="12">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="G225">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="M225" s="6"/>
     </row>
     <row r="226" spans="1:13">
-      <c r="A226" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="B226" s="12" t="s">
-        <v>434</v>
+      <c r="A226" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="B226" s="21" t="s">
+        <v>432</v>
       </c>
       <c r="C226" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D226" s="12">
+        <v>0.66</v>
+      </c>
+      <c r="G226">
+        <v>0.16</v>
+      </c>
+      <c r="M226" s="6"/>
+    </row>
+    <row r="227" spans="1:13">
+      <c r="A227" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="B227" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D227" s="12">
         <v>0.69</v>
       </c>
-      <c r="G226">
+      <c r="G227">
         <v>0.28000000000000003</v>
       </c>
-      <c r="M226" s="6"/>
-    </row>
-    <row r="227" spans="1:13">
-      <c r="A227" t="s">
+      <c r="M227" s="6"/>
+    </row>
+    <row r="228" spans="1:13">
+      <c r="A228" s="22" t="s">
         <v>474</v>
       </c>
-      <c r="B227" s="2" t="s">
+      <c r="B228" s="23" t="s">
         <v>475</v>
-      </c>
-      <c r="C227" t="s">
-        <v>430</v>
-      </c>
-      <c r="D227" s="4">
-        <v>0</v>
-      </c>
-      <c r="G227">
-        <v>0.16</v>
-      </c>
-      <c r="M227" s="19"/>
-    </row>
-    <row r="228" spans="1:13">
-      <c r="A228" t="s">
-        <v>467</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="C228" t="s">
         <v>430</v>
@@ -6352,160 +6376,160 @@
         <v>0</v>
       </c>
       <c r="G228">
+        <v>0.16</v>
+      </c>
+      <c r="M228" s="19"/>
+    </row>
+    <row r="229" spans="1:13">
+      <c r="A229" t="s">
+        <v>467</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C229" t="s">
+        <v>430</v>
+      </c>
+      <c r="D229" s="4">
+        <v>0</v>
+      </c>
+      <c r="G229">
         <v>0.26</v>
       </c>
-      <c r="M228" s="19"/>
-    </row>
-    <row r="229" spans="1:13">
-      <c r="A229" s="12" t="s">
-        <v>435</v>
-      </c>
-      <c r="B229" s="12" t="s">
-        <v>436</v>
-      </c>
-      <c r="C229" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D229" s="12">
-        <v>0.83</v>
-      </c>
-      <c r="G229">
-        <v>0.63</v>
-      </c>
-      <c r="M229" s="20"/>
+      <c r="M229" s="22"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B230" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C230" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D230" s="12">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="G230">
-        <v>0.26</v>
+        <v>0.63</v>
       </c>
       <c r="M230" s="20"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="12" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B231" s="12" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C231" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D231" s="12">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="G231">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="M231" s="20"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" s="12" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B232" s="12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D232" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="G232">
+        <v>0.67</v>
+      </c>
+      <c r="M232" s="20"/>
+    </row>
+    <row r="233" spans="1:13">
+      <c r="A233" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B233" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D233" s="12">
         <v>0.74</v>
       </c>
-      <c r="G232">
+      <c r="G233">
         <v>0.37</v>
       </c>
-      <c r="M232" s="20"/>
-    </row>
-    <row r="233" spans="1:13">
-      <c r="A233" t="s">
+      <c r="M233" s="20"/>
+    </row>
+    <row r="234" spans="1:13">
+      <c r="A234" s="22" t="s">
         <v>478</v>
       </c>
-      <c r="B233" s="2" t="s">
+      <c r="B234" s="23" t="s">
         <v>479</v>
       </c>
-      <c r="C233" t="s">
+      <c r="C234" t="s">
         <v>430</v>
       </c>
-      <c r="D233" s="4">
+      <c r="D234" s="4">
         <v>0</v>
       </c>
-      <c r="G233">
+      <c r="G234">
         <v>0.35</v>
       </c>
-      <c r="M233" s="22"/>
-    </row>
-    <row r="234" spans="1:13">
-      <c r="A234" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B234" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="C234" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D234" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="G234">
-        <v>0.44</v>
-      </c>
-      <c r="M234" s="20"/>
+      <c r="M234" s="22"/>
     </row>
     <row r="235" spans="1:13">
       <c r="A235" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B235" s="12" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C235" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D235" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="G235">
+        <v>0.44</v>
+      </c>
+      <c r="M235" s="20"/>
+    </row>
+    <row r="236" spans="1:13">
+      <c r="A236" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B236" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="C236" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D236" s="12">
         <v>0.65</v>
       </c>
-      <c r="G235">
+      <c r="G236">
         <v>0.63</v>
       </c>
-      <c r="M235" s="20"/>
-    </row>
-    <row r="236" spans="1:13">
-      <c r="A236" t="s">
-        <v>472</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C236" t="s">
-        <v>430</v>
-      </c>
-      <c r="D236" s="4">
-        <v>0</v>
-      </c>
-      <c r="G236">
-        <v>0.54</v>
-      </c>
-      <c r="M236" s="22"/>
+      <c r="M236" s="20"/>
     </row>
     <row r="237" spans="1:13">
       <c r="A237" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C237" t="s">
         <v>430</v>
@@ -6514,16 +6538,16 @@
         <v>0</v>
       </c>
       <c r="G237">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="M237" s="22"/>
     </row>
     <row r="238" spans="1:13">
-      <c r="A238" t="s">
-        <v>175</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>469</v>
+      <c r="A238" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="B238" s="23" t="s">
+        <v>477</v>
       </c>
       <c r="C238" t="s">
         <v>430</v>
@@ -6532,45 +6556,63 @@
         <v>0</v>
       </c>
       <c r="G238">
+        <v>0.42</v>
+      </c>
+      <c r="M238" s="22"/>
+    </row>
+    <row r="239" spans="1:13">
+      <c r="A239" t="s">
+        <v>175</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C239" t="s">
+        <v>430</v>
+      </c>
+      <c r="D239" s="4">
+        <v>0</v>
+      </c>
+      <c r="G239">
         <v>0.49</v>
       </c>
-      <c r="M238" s="22"/>
-    </row>
-    <row r="239" spans="1:13">
-      <c r="A239" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="B239" s="12" t="s">
-        <v>446</v>
-      </c>
-      <c r="C239" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D239" s="12">
-        <v>0.87</v>
-      </c>
-      <c r="G239">
-        <v>0.47</v>
-      </c>
-      <c r="M239" s="20"/>
+      <c r="M239" s="22"/>
     </row>
     <row r="240" spans="1:13">
       <c r="A240" s="12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B240" s="12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C240" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D240" s="12">
+        <v>0.87</v>
+      </c>
+      <c r="G240">
+        <v>0.47</v>
+      </c>
+      <c r="M240" s="20"/>
+    </row>
+    <row r="241" spans="1:13">
+      <c r="A241" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="B241" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="C241" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D241" s="12">
         <v>0.7</v>
       </c>
-      <c r="G240">
+      <c r="G241">
         <v>0.19</v>
       </c>
-      <c r="M240" s="20"/>
+      <c r="M241" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D0B8F1-2593-AA46-9399-E9DCD5FFC5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4A1F71-466D-FD48-8E3B-343FBD2724EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="497">
   <si>
     <t>Surname</t>
   </si>
@@ -1521,6 +1521,12 @@
   </si>
   <si>
     <t>H240044A</t>
+  </si>
+  <si>
+    <t>Simango</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -1659,7 +1665,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1679,17 +1685,20 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1734,10 +1743,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M241" totalsRowShown="0">
-  <autoFilter ref="A1:M241" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M241">
-    <sortCondition ref="C1:C241"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M242" totalsRowShown="0">
+  <autoFilter ref="A1:M242" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M242">
+    <sortCondition ref="C1:C242"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -2075,7 +2084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:M241"/>
+  <dimension ref="A1:M242"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -2376,6 +2385,9 @@
       <c r="D13" s="4">
         <v>0.79</v>
       </c>
+      <c r="G13">
+        <v>0.44</v>
+      </c>
       <c r="H13" s="5"/>
       <c r="J13">
         <v>0.48</v>
@@ -2542,6 +2554,9 @@
       <c r="D21" s="4">
         <v>0.85</v>
       </c>
+      <c r="G21">
+        <v>0.54</v>
+      </c>
       <c r="H21" s="5"/>
       <c r="J21">
         <v>0.48</v>
@@ -2583,6 +2598,9 @@
       <c r="D23" s="4">
         <v>0.82</v>
       </c>
+      <c r="G23">
+        <v>0.33</v>
+      </c>
       <c r="H23" s="5"/>
       <c r="J23">
         <v>0.68</v>
@@ -2690,6 +2708,9 @@
       <c r="D28" s="4">
         <v>0.83</v>
       </c>
+      <c r="G28">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="H28" s="5"/>
       <c r="J28">
         <v>0.8</v>
@@ -2797,6 +2818,9 @@
       <c r="D33" s="4">
         <v>0.84</v>
       </c>
+      <c r="G33">
+        <v>0.47</v>
+      </c>
       <c r="H33" s="5"/>
       <c r="J33">
         <v>0.8</v>
@@ -2816,6 +2840,9 @@
       <c r="D34" s="4">
         <v>0.81</v>
       </c>
+      <c r="G34">
+        <v>0.54</v>
+      </c>
       <c r="H34" s="5"/>
       <c r="J34">
         <v>0.8</v>
@@ -2835,6 +2862,9 @@
       <c r="D35" s="4">
         <v>0.65</v>
       </c>
+      <c r="G35">
+        <v>0.16</v>
+      </c>
       <c r="J35">
         <v>0</v>
       </c>
@@ -2987,6 +3017,9 @@
       <c r="D43" s="4">
         <v>0.77</v>
       </c>
+      <c r="G43">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="H43" s="5"/>
       <c r="J43">
         <v>0.24</v>
@@ -3013,10 +3046,10 @@
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="22" t="s">
+      <c r="A45" t="s">
         <v>490</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="2" t="s">
         <v>491</v>
       </c>
       <c r="C45" t="s">
@@ -3031,61 +3064,60 @@
       <c r="M45" s="19"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>94</v>
+      <c r="A46" t="s">
+        <v>495</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>496</v>
       </c>
       <c r="C46" t="s">
         <v>100</v>
       </c>
       <c r="D46" s="4">
-        <v>0.64</v>
-      </c>
-      <c r="H46" s="5"/>
-      <c r="J46">
-        <v>0.8</v>
-      </c>
-      <c r="M46" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0.65</v>
+      </c>
+      <c r="M46" s="19"/>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
         <v>100</v>
       </c>
       <c r="D47" s="4">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="G47">
         <v>0.44</v>
       </c>
       <c r="H47" s="5"/>
       <c r="J47">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>89</v>
+      <c r="A48" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="C48" t="s">
         <v>100</v>
       </c>
       <c r="D48" s="4">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="G48">
-        <v>0.54</v>
+        <v>0.44</v>
       </c>
       <c r="H48" s="5"/>
       <c r="J48">
@@ -3095,114 +3127,114 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C49" t="s">
         <v>100</v>
       </c>
       <c r="D49" s="4">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="G49">
-        <v>0.56000000000000005</v>
+        <v>0.54</v>
       </c>
       <c r="H49" s="5"/>
       <c r="J49">
+        <v>0.24</v>
+      </c>
+      <c r="M49" s="6"/>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="G50">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H50" s="5"/>
+      <c r="J50">
         <v>0.8</v>
       </c>
-      <c r="M49" s="6"/>
-    </row>
-    <row r="50" spans="1:13">
-      <c r="A50" s="21" t="s">
+      <c r="M50" s="6"/>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="B51" s="24" t="s">
         <v>102</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="G50">
-        <v>0.68</v>
-      </c>
-      <c r="H50" s="5"/>
-      <c r="M50" s="6"/>
-    </row>
-    <row r="51" spans="1:13">
-      <c r="A51" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>105</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D51" s="12">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="G51">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="H51" s="5"/>
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>107</v>
+      <c r="A52" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="24" t="s">
+        <v>105</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D52" s="12">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="G52">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H52" s="5"/>
-      <c r="J52">
-        <v>0.92</v>
-      </c>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>109</v>
+      <c r="A53" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="24" t="s">
+        <v>107</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D53" s="12">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G53">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="H53" s="5"/>
       <c r="J53">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B54" s="21" t="s">
-        <v>111</v>
+      <c r="A54" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>109</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>103</v>
@@ -3211,403 +3243,404 @@
         <v>0.85</v>
       </c>
       <c r="G54">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="H54" s="5"/>
+      <c r="J54">
+        <v>0.83</v>
+      </c>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>113</v>
+      <c r="A55" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D55" s="12">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="G55">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="H55" s="5"/>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>486</v>
+      <c r="A56" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>113</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D56" s="12">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="G56">
-        <v>0.56000000000000005</v>
+        <v>0.33</v>
       </c>
       <c r="H56" s="5"/>
-      <c r="J56">
-        <v>0.83</v>
-      </c>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>116</v>
+      <c r="A57" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="24" t="s">
+        <v>486</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D57" s="12">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="G57">
-        <v>0.32</v>
-      </c>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H57" s="5"/>
       <c r="J57">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B58" s="21" t="s">
-        <v>118</v>
+      <c r="A58" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D58" s="12">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="G58">
-        <v>0.51</v>
+        <v>0.32</v>
+      </c>
+      <c r="J58">
+        <v>0.92</v>
       </c>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="B59" s="21" t="s">
-        <v>120</v>
+      <c r="A59" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" s="24" t="s">
+        <v>118</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D59" s="12">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="G59">
-        <v>0.32</v>
+        <v>0.51</v>
       </c>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>122</v>
+      <c r="A60" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>120</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D60" s="12">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="G60">
-        <v>0.81</v>
-      </c>
-      <c r="J60">
-        <v>0.92</v>
+        <v>0.32</v>
       </c>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D61" s="12">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G61">
-        <v>0.46</v>
+        <v>0.81</v>
       </c>
       <c r="J61">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C62" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D62" s="12">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="G62">
         <v>0.46</v>
       </c>
+      <c r="J62">
+        <v>0.83</v>
+      </c>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D63" s="12">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="G63">
-        <v>0.37</v>
-      </c>
-      <c r="J63">
-        <v>0.83</v>
+        <v>0.46</v>
       </c>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D64" s="12">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="G64">
-        <v>0.63</v>
+        <v>0.37</v>
+      </c>
+      <c r="J64">
+        <v>0.83</v>
       </c>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D65" s="12">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="G65">
-        <v>0.37</v>
+        <v>0.63</v>
       </c>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D66" s="12">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="G66">
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D67" s="12">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="G67">
-        <v>0.35</v>
+        <v>0.53</v>
       </c>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D68" s="12">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="G68">
-        <v>0.77</v>
-      </c>
-      <c r="J68">
-        <v>0.83</v>
+        <v>0.35</v>
       </c>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="B69" s="21" t="s">
-        <v>140</v>
+      <c r="A69" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D69" s="12">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="G69">
-        <v>0.6</v>
+        <v>0.77</v>
+      </c>
+      <c r="J69">
+        <v>0.83</v>
       </c>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="B70" s="21" t="s">
-        <v>142</v>
+      <c r="A70" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>140</v>
       </c>
       <c r="C70" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D70" s="12">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="G70">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="J70">
-        <v>0.92</v>
+        <v>0.6</v>
       </c>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D71" s="12">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G71">
-        <v>0.57999999999999996</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J71">
+        <v>0.92</v>
       </c>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D72" s="12">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="G72">
-        <v>0.35</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D73" s="12">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="G73">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C74" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D74" s="12">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G74">
-        <v>0.77</v>
-      </c>
-      <c r="J74">
-        <v>0.83</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>103</v>
@@ -3616,130 +3649,133 @@
         <v>0.84</v>
       </c>
       <c r="G75">
-        <v>0.51</v>
+        <v>0.77</v>
+      </c>
+      <c r="J75">
+        <v>0.83</v>
       </c>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C76" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D76" s="12">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="G76">
-        <v>0.05</v>
+        <v>0.51</v>
       </c>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D77" s="12">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
       <c r="G77">
-        <v>0.61</v>
+        <v>0.05</v>
       </c>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D78" s="12">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G78">
-        <v>0.74</v>
-      </c>
-      <c r="J78">
-        <v>0.92</v>
+        <v>0.61</v>
       </c>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D79" s="12">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="G79">
-        <v>0.57999999999999996</v>
+        <v>0.74</v>
+      </c>
+      <c r="J79">
+        <v>0.92</v>
       </c>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D80" s="12">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="G80">
-        <v>0.61</v>
-      </c>
-      <c r="J80">
-        <v>0.92</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D81" s="12">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="G81">
-        <v>0.47</v>
+        <v>0.61</v>
+      </c>
+      <c r="J81">
+        <v>0.92</v>
       </c>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>103</v>
@@ -3748,178 +3784,178 @@
         <v>0.84</v>
       </c>
       <c r="G82">
-        <v>0.65</v>
+        <v>0.47</v>
       </c>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D83" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="G83">
+        <v>0.65</v>
+      </c>
+      <c r="M83" s="6"/>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D84" s="12">
         <v>0.74</v>
       </c>
-      <c r="G83">
+      <c r="G84">
         <v>0.39</v>
       </c>
-      <c r="M83" s="6"/>
-    </row>
-    <row r="84" spans="1:13">
-      <c r="A84" t="s">
+      <c r="M84" s="6"/>
+    </row>
+    <row r="85" spans="1:13">
+      <c r="A85" t="s">
         <v>342</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C85" t="s">
         <v>103</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D85" s="4">
         <v>0</v>
       </c>
-      <c r="G84">
+      <c r="G85">
         <v>0.54</v>
-      </c>
-      <c r="M84" s="6"/>
-    </row>
-    <row r="85" spans="1:13">
-      <c r="A85" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D85" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="G85">
-        <v>0.79</v>
       </c>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D86" s="12">
-        <v>0.71</v>
+        <v>0.81</v>
       </c>
       <c r="G86">
-        <v>0.63</v>
+        <v>0.79</v>
       </c>
       <c r="M86" s="6"/>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C87" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D87" s="12">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="G87">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
-      <c r="A88" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="B88" s="21" t="s">
-        <v>176</v>
+      <c r="A88" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="C88" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D88" s="12">
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
       <c r="G88">
-        <v>0.25</v>
+        <v>0.61</v>
       </c>
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C89" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D89" s="12">
-        <v>0.83</v>
+        <v>0.81</v>
       </c>
       <c r="G89">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
-      <c r="A90" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="B90" s="21" t="s">
-        <v>180</v>
+      <c r="A90" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>178</v>
       </c>
       <c r="C90" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D90" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="G90">
+        <v>0.6</v>
+      </c>
+      <c r="M90" s="6"/>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D91" s="12">
         <v>0.85</v>
       </c>
-      <c r="G90">
+      <c r="G91">
         <v>0.54</v>
       </c>
-      <c r="M90" s="6"/>
-    </row>
-    <row r="91" spans="1:13">
-      <c r="A91" s="21" t="s">
+      <c r="M91" s="6"/>
+    </row>
+    <row r="92" spans="1:13">
+      <c r="A92" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="B91" s="21" t="s">
+      <c r="B92" s="24" t="s">
         <v>182</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D91" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="G91">
-        <v>0.68</v>
-      </c>
-      <c r="M91" s="6"/>
-    </row>
-    <row r="92" spans="1:13">
-      <c r="A92" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="B92" s="21" t="s">
-        <v>185</v>
       </c>
       <c r="C92" s="12" t="s">
         <v>183</v>
@@ -3928,457 +3964,457 @@
         <v>0.75</v>
       </c>
       <c r="G92">
+        <v>0.68</v>
+      </c>
+      <c r="M92" s="6"/>
+    </row>
+    <row r="93" spans="1:13">
+      <c r="A93" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D93" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="G93">
         <v>0.6</v>
       </c>
-      <c r="M92" s="6"/>
-    </row>
-    <row r="93" spans="1:13">
-      <c r="A93" s="22" t="s">
-        <v>484</v>
-      </c>
-      <c r="B93" s="23" t="s">
-        <v>485</v>
-      </c>
-      <c r="C93" t="s">
-        <v>183</v>
-      </c>
-      <c r="D93" s="4">
-        <v>0</v>
-      </c>
-      <c r="G93">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="M93" s="19"/>
+      <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="B94" s="22" t="s">
+        <v>485</v>
+      </c>
+      <c r="C94" t="s">
+        <v>183</v>
+      </c>
+      <c r="D94" s="4">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M94" s="19"/>
+    </row>
+    <row r="95" spans="1:13">
+      <c r="A95" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="B94" s="21" t="s">
+      <c r="B95" s="24" t="s">
         <v>187</v>
-      </c>
-      <c r="C94" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D94" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="G94">
-        <v>0.47</v>
-      </c>
-      <c r="M94" s="6"/>
-    </row>
-    <row r="95" spans="1:13">
-      <c r="A95" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="B95" s="21" t="s">
-        <v>189</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D95" s="12">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="G95">
-        <v>0.65</v>
+        <v>0.47</v>
       </c>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
-      <c r="A96" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="B96" s="21" t="s">
-        <v>191</v>
+      <c r="A96" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="B96" s="24" t="s">
+        <v>189</v>
       </c>
       <c r="C96" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D96" s="12">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="G96">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
-      <c r="A97" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="B97" s="21" t="s">
-        <v>193</v>
+      <c r="A97" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="B97" s="24" t="s">
+        <v>191</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D97" s="12">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
       <c r="G97">
-        <v>0.79</v>
+        <v>0.42</v>
       </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
-      <c r="A98" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B98" s="21" t="s">
-        <v>195</v>
+      <c r="A98" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="B98" s="24" t="s">
+        <v>193</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D98" s="12">
+        <v>0.93</v>
+      </c>
+      <c r="G98">
         <v>0.79</v>
       </c>
-      <c r="G98">
-        <v>0.46</v>
-      </c>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
-      <c r="A99" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B99" s="12" t="s">
-        <v>197</v>
+      <c r="A99" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="B99" s="24" t="s">
+        <v>195</v>
       </c>
       <c r="C99" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D99" s="12">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="G99">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
-      <c r="A100" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="B100" s="21" t="s">
-        <v>199</v>
+      <c r="A100" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D100" s="12">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="G100">
-        <v>0.28000000000000003</v>
+        <v>0.72</v>
       </c>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D101" s="12">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="G101">
-        <v>0.4</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C102" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D102" s="12">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="G102">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
-      <c r="A103" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="B103" s="21" t="s">
-        <v>205</v>
+      <c r="A103" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>203</v>
       </c>
       <c r="C103" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D103" s="12">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="G103">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
-      <c r="A104" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="B104" s="21" t="s">
-        <v>207</v>
+      <c r="A104" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="C104" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D104" s="12">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="G104">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
-      <c r="A105" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="B105" s="21" t="s">
-        <v>209</v>
+      <c r="A105" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D105" s="12">
+        <v>0.89</v>
+      </c>
+      <c r="G105">
+        <v>0.49</v>
+      </c>
+      <c r="M105" s="6"/>
+    </row>
+    <row r="106" spans="1:13">
+      <c r="A106" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D106" s="12">
         <v>0.85</v>
       </c>
-      <c r="G105">
+      <c r="G106">
         <v>0.54</v>
       </c>
-      <c r="M105" s="6"/>
-    </row>
-    <row r="106" spans="1:13">
-      <c r="A106" t="s">
+      <c r="M106" s="6"/>
+    </row>
+    <row r="107" spans="1:13">
+      <c r="A107" t="s">
         <v>480</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B107" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C107" t="s">
         <v>183</v>
       </c>
-      <c r="D106" s="4">
+      <c r="D107" s="4">
         <v>0</v>
       </c>
-      <c r="G106">
+      <c r="G107">
         <v>0.51</v>
       </c>
-      <c r="M106" s="19"/>
-    </row>
-    <row r="107" spans="1:13">
-      <c r="A107" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B107" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="C107" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D107" s="12">
-        <v>0.86</v>
-      </c>
-      <c r="G107">
-        <v>0.4</v>
-      </c>
-      <c r="M107" s="6"/>
+      <c r="M107" s="19"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D108" s="12">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="G108">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
-      <c r="A109" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="B109" s="21" t="s">
-        <v>215</v>
+      <c r="A109" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D109" s="12">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="G109">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D110" s="12">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="G110">
-        <v>0.75</v>
+        <v>0.39</v>
       </c>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D111" s="12">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="G111">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D112" s="12">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="G112">
-        <v>0.26</v>
+        <v>0.61</v>
       </c>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D113" s="12">
-        <v>0.94</v>
+        <v>0.83</v>
       </c>
       <c r="G113">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C114" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D114" s="12">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="G114">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C115" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D115" s="12">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="G115">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D116" s="12">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G116">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="M116" s="6"/>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C117" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D117" s="12">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="G117">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="M117" s="6"/>
     </row>
@@ -4387,85 +4423,85 @@
         <v>230</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C118" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D118" s="12">
-        <v>0.92</v>
+        <v>0.66</v>
       </c>
       <c r="G118">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
       <c r="M118" s="6"/>
     </row>
     <row r="119" spans="1:13">
-      <c r="A119" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="B119" s="21" t="s">
-        <v>234</v>
+      <c r="A119" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>232</v>
       </c>
       <c r="C119" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D119" s="12">
+        <v>0.92</v>
+      </c>
+      <c r="G119">
+        <v>0.44</v>
+      </c>
+      <c r="M119" s="6"/>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D120" s="12">
         <v>0.82</v>
       </c>
-      <c r="G119">
+      <c r="G120">
         <v>0.54</v>
       </c>
-      <c r="M119" s="6"/>
-    </row>
-    <row r="120" spans="1:13">
-      <c r="A120" t="s">
+      <c r="M120" s="6"/>
+    </row>
+    <row r="121" spans="1:13">
+      <c r="A121" t="s">
         <v>481</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B121" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C121" t="s">
         <v>183</v>
       </c>
-      <c r="D120" s="4">
+      <c r="D121" s="4">
         <v>0</v>
       </c>
-      <c r="G120">
+      <c r="G121">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M120" s="19"/>
-    </row>
-    <row r="121" spans="1:13">
-      <c r="A121" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="B121" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="C121" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D121" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="G121">
-        <v>0.26</v>
-      </c>
-      <c r="M121" s="6"/>
+      <c r="M121" s="19"/>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C122" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D122" s="12">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="G122">
         <v>0.26</v>
@@ -4474,16 +4510,16 @@
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C123" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D123" s="12">
-        <v>0.69</v>
+        <v>0.96</v>
       </c>
       <c r="G123">
         <v>0.26</v>
@@ -4492,916 +4528,916 @@
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D124" s="12">
-        <v>0.78</v>
+        <v>0.69</v>
       </c>
       <c r="G124">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="M124" s="6"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D125" s="12">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="G125">
-        <v>0.49</v>
+        <v>0.09</v>
       </c>
       <c r="M125" s="6"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D126" s="12">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="G126">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
       <c r="M126" s="6"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C127" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D127" s="12">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="G127">
-        <v>0.26</v>
+        <v>0.74</v>
       </c>
       <c r="M127" s="6"/>
     </row>
     <row r="128" spans="1:13">
-      <c r="A128" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="B128" s="21" t="s">
-        <v>250</v>
+      <c r="A128" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>248</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D128" s="12">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="G128">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="M128" s="6"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C129" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D129" s="12">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="G129">
-        <v>0.11</v>
+        <v>0.32</v>
       </c>
       <c r="M129" s="6"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C130" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D130" s="12">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="G130">
-        <v>0.65</v>
+        <v>0.11</v>
       </c>
       <c r="M130" s="6"/>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C131" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D131" s="12">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="G131">
-        <v>0.28000000000000003</v>
+        <v>0.65</v>
       </c>
       <c r="M131" s="6"/>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="12" t="s">
-        <v>25</v>
+        <v>255</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C132" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D132" s="12">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="G132">
-        <v>0.47</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M132" s="6"/>
     </row>
     <row r="133" spans="1:13">
-      <c r="A133" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="B133" s="21" t="s">
-        <v>259</v>
+      <c r="A133" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B133" s="12" t="s">
+        <v>257</v>
       </c>
       <c r="C133" s="12" t="s">
         <v>183</v>
       </c>
       <c r="D133" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="G133">
+        <v>0.47</v>
+      </c>
+      <c r="M133" s="6"/>
+    </row>
+    <row r="134" spans="1:13">
+      <c r="A134" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D134" s="12">
         <v>0.75</v>
       </c>
-      <c r="G133">
+      <c r="G134">
         <v>0.35</v>
       </c>
-      <c r="M133" s="6"/>
-    </row>
-    <row r="134" spans="1:13">
-      <c r="A134" s="21" t="s">
+      <c r="M134" s="6"/>
+    </row>
+    <row r="135" spans="1:13">
+      <c r="A135" s="24" t="s">
         <v>260</v>
       </c>
-      <c r="B134" s="21" t="s">
+      <c r="B135" s="24" t="s">
         <v>261</v>
-      </c>
-      <c r="C134" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="D134" s="12">
-        <v>0.78</v>
-      </c>
-      <c r="G134">
-        <v>0.4</v>
-      </c>
-      <c r="M134" s="6"/>
-    </row>
-    <row r="135" spans="1:13">
-      <c r="A135" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="B135" s="21" t="s">
-        <v>264</v>
       </c>
       <c r="C135" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D135" s="12">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="G135">
-        <v>0.56000000000000005</v>
+        <v>0.4</v>
       </c>
       <c r="M135" s="6"/>
     </row>
     <row r="136" spans="1:13">
-      <c r="A136" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="B136" s="21" t="s">
-        <v>266</v>
+      <c r="A136" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="B136" s="24" t="s">
+        <v>264</v>
       </c>
       <c r="C136" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D136" s="12">
-        <v>0.93</v>
+        <v>0.81</v>
       </c>
       <c r="G136">
-        <v>0.63</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M136" s="6"/>
     </row>
     <row r="137" spans="1:13">
-      <c r="A137" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="B137" s="21" t="s">
-        <v>268</v>
+      <c r="A137" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="B137" s="24" t="s">
+        <v>266</v>
       </c>
       <c r="C137" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D137" s="12">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="G137">
-        <v>0.42</v>
+        <v>0.63</v>
       </c>
       <c r="M137" s="6"/>
     </row>
     <row r="138" spans="1:13">
-      <c r="A138" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="B138" s="21" t="s">
-        <v>270</v>
+      <c r="A138" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="B138" s="24" t="s">
+        <v>268</v>
       </c>
       <c r="C138" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D138" s="12">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="G138">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="M138" s="6"/>
     </row>
     <row r="139" spans="1:13">
-      <c r="A139" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="B139" s="21" t="s">
-        <v>272</v>
+      <c r="A139" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="B139" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="C139" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D139" s="12">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="G139">
-        <v>0.74</v>
+        <v>0.39</v>
       </c>
       <c r="M139" s="6"/>
     </row>
     <row r="140" spans="1:13">
-      <c r="A140" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="B140" s="21" t="s">
-        <v>274</v>
+      <c r="A140" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="B140" s="24" t="s">
+        <v>272</v>
       </c>
       <c r="C140" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D140" s="12">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="G140">
-        <v>0.39</v>
+        <v>0.74</v>
       </c>
       <c r="M140" s="6"/>
     </row>
     <row r="141" spans="1:13">
-      <c r="A141" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="B141" s="21" t="s">
-        <v>276</v>
+      <c r="A141" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="B141" s="24" t="s">
+        <v>274</v>
       </c>
       <c r="C141" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D141" s="12">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="G141">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="M141" s="6"/>
     </row>
     <row r="142" spans="1:13">
-      <c r="A142" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="B142" s="21" t="s">
-        <v>278</v>
+      <c r="A142" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="B142" s="24" t="s">
+        <v>276</v>
       </c>
       <c r="C142" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D142" s="12">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="G142">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="M142" s="6"/>
     </row>
     <row r="143" spans="1:13">
-      <c r="A143" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B143" s="21" t="s">
-        <v>280</v>
+      <c r="A143" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="B143" s="24" t="s">
+        <v>278</v>
       </c>
       <c r="C143" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D143" s="12">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="M143" s="6"/>
     </row>
     <row r="144" spans="1:13">
-      <c r="A144" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B144" s="21" t="s">
-        <v>281</v>
+      <c r="A144" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="B144" s="24" t="s">
+        <v>280</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D144" s="12">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="G144">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="M144" s="6"/>
     </row>
     <row r="145" spans="1:13">
-      <c r="A145" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="B145" s="21" t="s">
-        <v>283</v>
+      <c r="A145" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B145" s="24" t="s">
+        <v>281</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D145" s="12">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="G145">
-        <v>0.65</v>
+        <v>0.16</v>
       </c>
       <c r="M145" s="6"/>
     </row>
     <row r="146" spans="1:13">
-      <c r="A146" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="B146" s="12" t="s">
-        <v>285</v>
+      <c r="A146" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="B146" s="24" t="s">
+        <v>283</v>
       </c>
       <c r="C146" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D146" s="12">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="G146">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="M146" s="6"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C147" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D147" s="12">
-        <v>0.94</v>
+        <v>0.87</v>
       </c>
       <c r="G147">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="M147" s="6"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C148" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D148" s="12">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="G148">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="M148" s="6"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C149" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D149" s="12">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="G149">
-        <v>0.21</v>
+        <v>0.63</v>
       </c>
       <c r="M149" s="6"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C150" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D150" s="12">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="G150">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="M150" s="6"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C151" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D151" s="12">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="G151">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="M151" s="6"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C152" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D152" s="12">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="G152">
-        <v>0.63</v>
+        <v>0.3</v>
       </c>
       <c r="M152" s="6"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C153" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D153" s="12">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="G153">
-        <v>0.86</v>
+        <v>0.63</v>
       </c>
       <c r="M153" s="6"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C154" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D154" s="12">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="G154">
-        <v>0.47</v>
+        <v>0.86</v>
       </c>
       <c r="M154" s="6"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C155" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D155" s="12">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="G155">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="M155" s="6"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C156" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D156" s="12">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="G156">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="M156" s="6"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C157" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D157" s="12">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="G157">
-        <v>0.65</v>
+        <v>0.44</v>
       </c>
       <c r="M157" s="6"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C158" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D158" s="12">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="G158">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="M158" s="6"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C159" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D159" s="12">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="G159">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="M159" s="6"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C160" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D160" s="12">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="G160">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="M160" s="6"/>
     </row>
     <row r="161" spans="1:13">
-      <c r="A161" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="B161" s="21" t="s">
-        <v>315</v>
+      <c r="A161" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>313</v>
       </c>
       <c r="C161" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D161" s="12">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="G161">
-        <v>0.57999999999999996</v>
+        <v>0.42</v>
       </c>
       <c r="M161" s="6"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C162" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D162" s="12">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="G162">
-        <v>0.68</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C163" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D163" s="12">
-        <v>0.94</v>
+        <v>0.88</v>
       </c>
       <c r="G163">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C164" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D164" s="12">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="G164">
-        <v>0.33</v>
+        <v>0.51</v>
       </c>
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C165" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D165" s="12">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="G165">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="M165" s="6"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C166" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D166" s="12">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="G166">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="M166" s="6"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C167" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D167" s="12">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="G167">
-        <v>0.63</v>
+        <v>0.47</v>
       </c>
       <c r="M167" s="6"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C168" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D168" s="12">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="G168">
-        <v>0.56000000000000005</v>
+        <v>0.63</v>
       </c>
       <c r="M168" s="6"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C169" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D169" s="12">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="G169">
-        <v>0.54</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M169" s="6"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C170" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D170" s="12">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G170">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C171" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D171" s="12">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="G171">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="M171" s="6"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C172" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D172" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="G172">
+        <v>0.25</v>
+      </c>
+      <c r="M172" s="6"/>
+    </row>
+    <row r="173" spans="1:13">
+      <c r="A173" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D173" s="12">
         <v>0.9</v>
       </c>
-      <c r="G172">
+      <c r="G173">
         <v>0.39</v>
       </c>
-      <c r="M172" s="6"/>
-    </row>
-    <row r="173" spans="1:13">
-      <c r="A173" t="s">
+      <c r="M173" s="6"/>
+    </row>
+    <row r="174" spans="1:13">
+      <c r="A174" t="s">
         <v>465</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B174" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C174" t="s">
         <v>262</v>
       </c>
-      <c r="D173" s="4">
+      <c r="D174" s="4">
         <v>0</v>
-      </c>
-      <c r="G173">
-        <v>0.35</v>
-      </c>
-      <c r="M173" s="6"/>
-    </row>
-    <row r="174" spans="1:13">
-      <c r="A174" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="B174" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="C174" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="D174" s="12">
-        <v>0.86</v>
       </c>
       <c r="G174">
         <v>0.35</v>
@@ -5409,443 +5445,443 @@
       <c r="M174" s="6"/>
     </row>
     <row r="175" spans="1:13">
-      <c r="A175" s="22" t="s">
+      <c r="A175" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D175" s="12">
+        <v>0.86</v>
+      </c>
+      <c r="G175">
+        <v>0.35</v>
+      </c>
+      <c r="M175" s="6"/>
+    </row>
+    <row r="176" spans="1:13">
+      <c r="A176" t="s">
         <v>463</v>
       </c>
-      <c r="B175" s="24" t="s">
+      <c r="B176" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C176" t="s">
         <v>262</v>
       </c>
-      <c r="D175" s="4">
+      <c r="D176" s="4">
         <v>0</v>
       </c>
-      <c r="G175">
+      <c r="G176">
         <v>0.33</v>
-      </c>
-      <c r="M175" s="6"/>
-    </row>
-    <row r="176" spans="1:13">
-      <c r="A176" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="B176" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="C176" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="D176" s="12">
-        <v>0.69</v>
-      </c>
-      <c r="G176">
-        <v>0.12</v>
       </c>
       <c r="M176" s="6"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C177" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D177" s="12">
-        <v>0.77</v>
+        <v>0.69</v>
       </c>
       <c r="G177">
-        <v>0.46</v>
+        <v>0.12</v>
       </c>
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
-      <c r="A178" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="B178" s="21" t="s">
-        <v>345</v>
+      <c r="A178" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>343</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D178" s="12">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="G178">
-        <v>0.19</v>
+        <v>0.46</v>
       </c>
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C179" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D179" s="12">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="G179">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C180" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D180" s="12">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="G180">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B181" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C181" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D181" s="12">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="G181">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C182" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D182" s="12">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="G182">
-        <v>0.35</v>
+        <v>0.53</v>
       </c>
       <c r="M182" s="6"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B183" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C183" s="12" t="s">
         <v>262</v>
       </c>
       <c r="D183" s="12">
+        <v>0.61</v>
+      </c>
+      <c r="G183">
+        <v>0.35</v>
+      </c>
+      <c r="M183" s="6"/>
+    </row>
+    <row r="184" spans="1:13">
+      <c r="A184" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B184" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D184" s="12">
         <v>0.75</v>
       </c>
-      <c r="G183">
+      <c r="G184">
         <v>0.32</v>
       </c>
-      <c r="M183" s="6"/>
-    </row>
-    <row r="184" spans="1:13">
-      <c r="A184" s="21" t="s">
+      <c r="M184" s="6"/>
+    </row>
+    <row r="185" spans="1:13">
+      <c r="A185" s="24" t="s">
         <v>356</v>
       </c>
-      <c r="B184" s="21" t="s">
+      <c r="B185" s="24" t="s">
         <v>357</v>
       </c>
-      <c r="C184" s="12" t="s">
+      <c r="C185" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="D184" s="12">
+      <c r="D185" s="12">
         <v>0.87</v>
       </c>
-      <c r="G184">
+      <c r="G185">
         <v>0.26</v>
-      </c>
-      <c r="M184" s="6"/>
-    </row>
-    <row r="185" spans="1:13">
-      <c r="A185" s="22" t="s">
-        <v>456</v>
-      </c>
-      <c r="B185" s="24" t="s">
-        <v>457</v>
-      </c>
-      <c r="C185" t="s">
-        <v>358</v>
-      </c>
-      <c r="D185" s="4">
-        <v>0</v>
-      </c>
-      <c r="G185">
-        <v>0.19</v>
       </c>
       <c r="M185" s="6"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="B186" s="25" t="s">
+        <v>457</v>
+      </c>
+      <c r="C186" t="s">
+        <v>358</v>
+      </c>
+      <c r="D186" s="4">
+        <v>0</v>
+      </c>
+      <c r="G186">
+        <v>0.19</v>
+      </c>
+      <c r="M186" s="6"/>
+    </row>
+    <row r="187" spans="1:13">
+      <c r="A187" s="24" t="s">
         <v>359</v>
       </c>
-      <c r="B186" s="21" t="s">
+      <c r="B187" s="24" t="s">
         <v>360</v>
-      </c>
-      <c r="C186" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D186" s="12">
-        <v>0.71</v>
-      </c>
-      <c r="G186">
-        <v>0.35</v>
-      </c>
-      <c r="M186" s="6"/>
-    </row>
-    <row r="187" spans="1:13">
-      <c r="A187" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="B187" s="12" t="s">
-        <v>362</v>
       </c>
       <c r="C187" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D187" s="12">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="G187">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B188" s="12" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C188" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D188" s="12">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="G188">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B189" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C189" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D189" s="12">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G189">
-        <v>0.68</v>
+        <v>0.39</v>
       </c>
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
-      <c r="A190" s="21" t="s">
-        <v>367</v>
-      </c>
-      <c r="B190" s="21" t="s">
-        <v>368</v>
+      <c r="A190" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>366</v>
       </c>
       <c r="C190" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D190" s="12">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="G190">
-        <v>0.42</v>
+        <v>0.68</v>
       </c>
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="12" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B191" s="12" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C191" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D191" s="12">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="G191">
-        <v>0.57999999999999996</v>
+        <v>0.42</v>
       </c>
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C192" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D192" s="12">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="G192">
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="12" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B193" s="12" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C193" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D193" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="G193">
+        <v>0.6</v>
+      </c>
+      <c r="M193" s="6"/>
+    </row>
+    <row r="194" spans="1:13">
+      <c r="A194" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B194" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="C194" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D194" s="12">
         <v>0.64</v>
       </c>
-      <c r="G193">
+      <c r="G194">
         <v>0.04</v>
       </c>
-      <c r="M193" s="6"/>
-    </row>
-    <row r="194" spans="1:13">
-      <c r="A194" t="s">
+      <c r="M194" s="6"/>
+    </row>
+    <row r="195" spans="1:13">
+      <c r="A195" t="s">
         <v>452</v>
       </c>
-      <c r="B194" s="2" t="s">
+      <c r="B195" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C195" t="s">
         <v>358</v>
       </c>
-      <c r="D194" s="4">
+      <c r="D195" s="4">
         <v>0</v>
       </c>
-      <c r="G194">
+      <c r="G195">
         <v>0.26</v>
-      </c>
-      <c r="M194" s="6"/>
-    </row>
-    <row r="195" spans="1:13">
-      <c r="A195" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="B195" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="C195" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D195" s="12">
-        <v>0.78</v>
-      </c>
-      <c r="G195">
-        <v>0.54</v>
       </c>
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C196" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D196" s="12">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="G196">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="12" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B197" s="12" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C197" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D197" s="12">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="G197">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="12" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B198" s="12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C198" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D198" s="12">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="G198">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B199" s="12" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>358</v>
@@ -5860,532 +5896,532 @@
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="12" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C200" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D200" s="12">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="G200">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B201" s="12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C201" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D201" s="12">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="G201">
-        <v>0.6</v>
+        <v>0.37</v>
       </c>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B202" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C202" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D202" s="12">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G202">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="M202" s="6"/>
     </row>
     <row r="203" spans="1:13">
-      <c r="A203" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="B203" s="21" t="s">
-        <v>392</v>
+      <c r="A203" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>390</v>
       </c>
       <c r="C203" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D203" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="G203">
+        <v>0.32</v>
+      </c>
+      <c r="M203" s="6"/>
+    </row>
+    <row r="204" spans="1:13">
+      <c r="A204" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="B204" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D204" s="12">
         <v>0.85</v>
       </c>
-      <c r="G203">
+      <c r="G204">
         <v>0.37</v>
       </c>
-      <c r="M203" s="6"/>
-    </row>
-    <row r="204" spans="1:13">
-      <c r="A204" t="s">
+      <c r="M204" s="6"/>
+    </row>
+    <row r="205" spans="1:13">
+      <c r="A205" t="s">
         <v>460</v>
       </c>
-      <c r="B204" s="2" t="s">
+      <c r="B205" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C205" t="s">
         <v>358</v>
       </c>
-      <c r="D204" s="4">
+      <c r="D205" s="4">
         <v>0</v>
       </c>
-      <c r="G204">
+      <c r="G205">
         <v>0.46</v>
-      </c>
-      <c r="M204" s="6"/>
-    </row>
-    <row r="205" spans="1:13">
-      <c r="A205" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="B205" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="C205" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D205" s="12">
-        <v>0.88</v>
-      </c>
-      <c r="G205">
-        <v>0.3</v>
       </c>
       <c r="M205" s="6"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B206" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D206" s="12">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="G206">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="M206" s="6"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B207" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C207" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D207" s="12">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="G207">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="M207" s="6"/>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B208" s="12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C208" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D208" s="12">
-        <v>0.59</v>
+        <v>0.76</v>
       </c>
       <c r="G208">
-        <v>0.65</v>
+        <v>0.39</v>
       </c>
       <c r="M208" s="6"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B209" s="12" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C209" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D209" s="12">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
       <c r="G209">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="M209" s="6"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="12" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B210" s="12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C210" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D210" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="G210">
+        <v>0.44</v>
+      </c>
+      <c r="M210" s="6"/>
+    </row>
+    <row r="211" spans="1:13">
+      <c r="A211" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D211" s="12">
         <v>0.77</v>
       </c>
-      <c r="G210">
+      <c r="G211">
         <v>0.75</v>
       </c>
-      <c r="M210" s="6"/>
-    </row>
-    <row r="211" spans="1:13">
-      <c r="A211" s="22" t="s">
+      <c r="M211" s="6"/>
+    </row>
+    <row r="212" spans="1:13">
+      <c r="A212" t="s">
         <v>454</v>
       </c>
-      <c r="B211" s="23" t="s">
+      <c r="B212" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="C211" t="s">
+      <c r="C212" t="s">
         <v>358</v>
       </c>
-      <c r="D211" s="4">
+      <c r="D212" s="4">
         <v>0</v>
       </c>
-      <c r="G211">
+      <c r="G212">
         <v>0.05</v>
-      </c>
-      <c r="M211" s="6"/>
-    </row>
-    <row r="212" spans="1:13">
-      <c r="A212" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="B212" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="C212" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D212" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="G212">
-        <v>0.53</v>
       </c>
       <c r="M212" s="6"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="12" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B213" s="12" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C213" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D213" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="G213">
+        <v>0.53</v>
+      </c>
+      <c r="M213" s="6"/>
+    </row>
+    <row r="214" spans="1:13">
+      <c r="A214" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="B214" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D214" s="12">
         <v>0.79</v>
       </c>
-      <c r="G213">
+      <c r="G214">
         <v>0.32</v>
       </c>
-      <c r="M213" s="6"/>
-    </row>
-    <row r="214" spans="1:13">
-      <c r="A214" t="s">
+      <c r="M214" s="6"/>
+    </row>
+    <row r="215" spans="1:13">
+      <c r="A215" t="s">
         <v>458</v>
       </c>
-      <c r="B214" s="2" t="s">
+      <c r="B215" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C214" t="s">
+      <c r="C215" t="s">
         <v>358</v>
       </c>
-      <c r="D214" s="4">
+      <c r="D215" s="4">
         <v>0</v>
       </c>
-      <c r="G214">
+      <c r="G215">
         <v>0.44</v>
-      </c>
-      <c r="M214" s="6"/>
-    </row>
-    <row r="215" spans="1:13">
-      <c r="A215" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="B215" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="C215" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D215" s="12">
-        <v>0.74</v>
-      </c>
-      <c r="G215">
-        <v>0.68</v>
       </c>
       <c r="M215" s="6"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="12" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B216" s="12" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C216" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D216" s="12">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="G216">
-        <v>0.56000000000000005</v>
+        <v>0.68</v>
       </c>
       <c r="M216" s="6"/>
     </row>
     <row r="217" spans="1:13">
-      <c r="A217" s="21" t="s">
-        <v>413</v>
-      </c>
-      <c r="B217" s="21" t="s">
-        <v>414</v>
+      <c r="A217" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B217" s="12" t="s">
+        <v>412</v>
       </c>
       <c r="C217" s="12" t="s">
         <v>358</v>
       </c>
       <c r="D217" s="12">
+        <v>0.62</v>
+      </c>
+      <c r="G217">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M217" s="6"/>
+    </row>
+    <row r="218" spans="1:13">
+      <c r="A218" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B218" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="C218" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D218" s="12">
         <v>0.94</v>
       </c>
-      <c r="G217">
+      <c r="G218">
         <v>0.65</v>
       </c>
-      <c r="M217" s="6"/>
-    </row>
-    <row r="218" spans="1:13">
-      <c r="A218" s="21" t="s">
+      <c r="M218" s="6"/>
+    </row>
+    <row r="219" spans="1:13">
+      <c r="A219" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="B218" s="21" t="s">
+      <c r="B219" s="24" t="s">
         <v>416</v>
-      </c>
-      <c r="C218" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="D218" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="G218">
-        <v>0.79</v>
-      </c>
-      <c r="M218" s="6"/>
-    </row>
-    <row r="219" spans="1:13">
-      <c r="A219" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="B219" s="12" t="s">
-        <v>419</v>
       </c>
       <c r="C219" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D219" s="12">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="G219">
-        <v>0.32</v>
+        <v>0.79</v>
       </c>
       <c r="M219" s="6"/>
     </row>
     <row r="220" spans="1:13">
-      <c r="A220" s="21" t="s">
-        <v>420</v>
-      </c>
-      <c r="B220" s="21" t="s">
-        <v>421</v>
+      <c r="A220" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="B220" s="12" t="s">
+        <v>419</v>
       </c>
       <c r="C220" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D220" s="12">
-        <v>0.69</v>
+        <v>0.61</v>
       </c>
       <c r="G220">
-        <v>0.54</v>
+        <v>0.32</v>
       </c>
       <c r="M220" s="6"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="12" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B221" s="12" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C221" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D221" s="12">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="G221">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="M221" s="6"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B222" s="12" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C222" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D222" s="12">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="G222">
-        <v>0.54</v>
+        <v>0.11</v>
       </c>
       <c r="M222" s="6"/>
     </row>
     <row r="223" spans="1:13">
       <c r="A223" s="12" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B223" s="12" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C223" s="12" t="s">
         <v>417</v>
       </c>
       <c r="D223" s="12">
+        <v>0.71</v>
+      </c>
+      <c r="G223">
+        <v>0.54</v>
+      </c>
+      <c r="M223" s="6"/>
+    </row>
+    <row r="224" spans="1:13">
+      <c r="A224" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="B224" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="D224" s="12">
         <v>0.89</v>
       </c>
-      <c r="G223">
+      <c r="G224">
         <v>0.61</v>
       </c>
-      <c r="M223" s="6"/>
-    </row>
-    <row r="224" spans="1:13">
-      <c r="A224" s="22" t="s">
-        <v>470</v>
-      </c>
-      <c r="B224" s="23" t="s">
-        <v>471</v>
-      </c>
-      <c r="C224" t="s">
-        <v>430</v>
-      </c>
-      <c r="D224" s="4">
-        <v>0</v>
-      </c>
-      <c r="G224">
-        <v>0.33</v>
-      </c>
-      <c r="M224" s="19"/>
+      <c r="M224" s="6"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="B225" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="C225" t="s">
+        <v>430</v>
+      </c>
+      <c r="D225" s="4">
+        <v>0</v>
+      </c>
+      <c r="G225">
+        <v>0.33</v>
+      </c>
+      <c r="M225" s="19"/>
+    </row>
+    <row r="226" spans="1:13">
+      <c r="A226" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="B225" s="21" t="s">
+      <c r="B226" s="24" t="s">
         <v>429</v>
-      </c>
-      <c r="C225" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D225" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="G225">
-        <v>0.26</v>
-      </c>
-      <c r="M225" s="6"/>
-    </row>
-    <row r="226" spans="1:13">
-      <c r="A226" s="21" t="s">
-        <v>431</v>
-      </c>
-      <c r="B226" s="21" t="s">
-        <v>432</v>
       </c>
       <c r="C226" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D226" s="12">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="G226">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="M226" s="6"/>
     </row>
     <row r="227" spans="1:13">
-      <c r="A227" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="B227" s="12" t="s">
-        <v>434</v>
+      <c r="A227" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="B227" s="24" t="s">
+        <v>432</v>
       </c>
       <c r="C227" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D227" s="12">
+        <v>0.66</v>
+      </c>
+      <c r="G227">
+        <v>0.16</v>
+      </c>
+      <c r="M227" s="6"/>
+    </row>
+    <row r="228" spans="1:13">
+      <c r="A228" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="B228" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D228" s="12">
         <v>0.69</v>
       </c>
-      <c r="G227">
+      <c r="G228">
         <v>0.28000000000000003</v>
       </c>
-      <c r="M227" s="6"/>
-    </row>
-    <row r="228" spans="1:13">
-      <c r="A228" s="22" t="s">
-        <v>474</v>
-      </c>
-      <c r="B228" s="23" t="s">
-        <v>475</v>
-      </c>
-      <c r="C228" t="s">
-        <v>430</v>
-      </c>
-      <c r="D228" s="4">
-        <v>0</v>
-      </c>
-      <c r="G228">
-        <v>0.16</v>
-      </c>
-      <c r="M228" s="19"/>
+      <c r="M228" s="6"/>
     </row>
     <row r="229" spans="1:13">
       <c r="A229" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C229" t="s">
         <v>430</v>
@@ -6394,160 +6430,160 @@
         <v>0</v>
       </c>
       <c r="G229">
+        <v>0.16</v>
+      </c>
+      <c r="M229" s="21"/>
+    </row>
+    <row r="230" spans="1:13">
+      <c r="A230" t="s">
+        <v>467</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C230" t="s">
+        <v>430</v>
+      </c>
+      <c r="D230" s="4">
+        <v>0</v>
+      </c>
+      <c r="G230">
         <v>0.26</v>
       </c>
-      <c r="M229" s="22"/>
-    </row>
-    <row r="230" spans="1:13">
-      <c r="A230" s="12" t="s">
-        <v>435</v>
-      </c>
-      <c r="B230" s="12" t="s">
-        <v>436</v>
-      </c>
-      <c r="C230" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D230" s="12">
-        <v>0.83</v>
-      </c>
-      <c r="G230">
-        <v>0.63</v>
-      </c>
-      <c r="M230" s="20"/>
+      <c r="M230" s="21"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B231" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C231" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D231" s="12">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="G231">
-        <v>0.26</v>
-      </c>
-      <c r="M231" s="20"/>
+        <v>0.63</v>
+      </c>
+      <c r="M231" s="23"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" s="12" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B232" s="12" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D232" s="12">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="G232">
-        <v>0.67</v>
-      </c>
-      <c r="M232" s="20"/>
+        <v>0.26</v>
+      </c>
+      <c r="M232" s="23"/>
     </row>
     <row r="233" spans="1:13">
-      <c r="A233" s="21" t="s">
-        <v>441</v>
-      </c>
-      <c r="B233" s="21" t="s">
-        <v>442</v>
+      <c r="A233" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B233" s="12" t="s">
+        <v>440</v>
       </c>
       <c r="C233" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D233" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="G233">
+        <v>0.67</v>
+      </c>
+      <c r="M233" s="23"/>
+    </row>
+    <row r="234" spans="1:13">
+      <c r="A234" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="B234" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D234" s="12">
         <v>0.74</v>
       </c>
-      <c r="G233">
+      <c r="G234">
         <v>0.37</v>
       </c>
-      <c r="M233" s="20"/>
-    </row>
-    <row r="234" spans="1:13">
-      <c r="A234" s="22" t="s">
+      <c r="M234" s="23"/>
+    </row>
+    <row r="235" spans="1:13">
+      <c r="A235" t="s">
         <v>478</v>
       </c>
-      <c r="B234" s="23" t="s">
+      <c r="B235" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C235" t="s">
         <v>430</v>
       </c>
-      <c r="D234" s="4">
+      <c r="D235" s="4">
         <v>0</v>
       </c>
-      <c r="G234">
+      <c r="G235">
         <v>0.35</v>
       </c>
-      <c r="M234" s="22"/>
-    </row>
-    <row r="235" spans="1:13">
-      <c r="A235" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B235" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="C235" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D235" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="G235">
-        <v>0.44</v>
-      </c>
-      <c r="M235" s="20"/>
+      <c r="M235" s="21"/>
     </row>
     <row r="236" spans="1:13">
       <c r="A236" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B236" s="12" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C236" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D236" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="G236">
+        <v>0.44</v>
+      </c>
+      <c r="M236" s="23"/>
+    </row>
+    <row r="237" spans="1:13">
+      <c r="A237" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B237" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D237" s="12">
         <v>0.65</v>
       </c>
-      <c r="G236">
+      <c r="G237">
         <v>0.63</v>
       </c>
-      <c r="M236" s="20"/>
-    </row>
-    <row r="237" spans="1:13">
-      <c r="A237" t="s">
+      <c r="M237" s="23"/>
+    </row>
+    <row r="238" spans="1:13">
+      <c r="A238" t="s">
         <v>472</v>
       </c>
-      <c r="B237" s="2" t="s">
+      <c r="B238" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="C237" t="s">
-        <v>430</v>
-      </c>
-      <c r="D237" s="4">
-        <v>0</v>
-      </c>
-      <c r="G237">
-        <v>0.54</v>
-      </c>
-      <c r="M237" s="22"/>
-    </row>
-    <row r="238" spans="1:13">
-      <c r="A238" s="22" t="s">
-        <v>476</v>
-      </c>
-      <c r="B238" s="23" t="s">
-        <v>477</v>
       </c>
       <c r="C238" t="s">
         <v>430</v>
@@ -6556,16 +6592,16 @@
         <v>0</v>
       </c>
       <c r="G238">
-        <v>0.42</v>
-      </c>
-      <c r="M238" s="22"/>
+        <v>0.54</v>
+      </c>
+      <c r="M238" s="21"/>
     </row>
     <row r="239" spans="1:13">
       <c r="A239" t="s">
-        <v>175</v>
+        <v>476</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C239" t="s">
         <v>430</v>
@@ -6574,45 +6610,62 @@
         <v>0</v>
       </c>
       <c r="G239">
+        <v>0.42</v>
+      </c>
+      <c r="M239" s="21"/>
+    </row>
+    <row r="240" spans="1:13">
+      <c r="A240" t="s">
+        <v>175</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C240" t="s">
+        <v>430</v>
+      </c>
+      <c r="D240" s="4">
+        <v>0</v>
+      </c>
+      <c r="G240">
         <v>0.49</v>
       </c>
-      <c r="M239" s="22"/>
-    </row>
-    <row r="240" spans="1:13">
-      <c r="A240" s="12" t="s">
+    </row>
+    <row r="241" spans="1:13">
+      <c r="A241" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="B240" s="12" t="s">
+      <c r="B241" s="12" t="s">
         <v>446</v>
-      </c>
-      <c r="C240" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D240" s="12">
-        <v>0.87</v>
-      </c>
-      <c r="G240">
-        <v>0.47</v>
-      </c>
-      <c r="M240" s="20"/>
-    </row>
-    <row r="241" spans="1:13">
-      <c r="A241" s="21" t="s">
-        <v>447</v>
-      </c>
-      <c r="B241" s="21" t="s">
-        <v>448</v>
       </c>
       <c r="C241" s="12" t="s">
         <v>430</v>
       </c>
       <c r="D241" s="12">
+        <v>0.87</v>
+      </c>
+      <c r="G241">
+        <v>0.47</v>
+      </c>
+      <c r="M241" s="20"/>
+    </row>
+    <row r="242" spans="1:13">
+      <c r="A242" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="B242" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="C242" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D242" s="12">
         <v>0.7</v>
       </c>
-      <c r="G241">
+      <c r="G242">
         <v>0.19</v>
       </c>
-      <c r="M241" s="20"/>
+      <c r="M242" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5683A84E-5B9B-8341-A8C9-79BE39FF52E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429EB6A9-1DB0-2046-935F-AF91BDE323A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1661,7 +1661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1688,13 +1688,6 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2417,7 +2410,9 @@
       <c r="D14" s="4">
         <v>0.74</v>
       </c>
-      <c r="H14"/>
+      <c r="H14">
+        <v>0.4</v>
+      </c>
       <c r="I14" s="5"/>
       <c r="L14">
         <v>0.48</v>
@@ -2874,7 +2869,9 @@
       <c r="D35" s="4">
         <v>0.84</v>
       </c>
-      <c r="H35"/>
+      <c r="H35">
+        <v>0.42</v>
+      </c>
       <c r="I35" s="5"/>
       <c r="L35">
         <v>0.24</v>
@@ -2894,7 +2891,9 @@
       <c r="D36" s="4">
         <v>0.66</v>
       </c>
-      <c r="H36"/>
+      <c r="H36">
+        <v>0.47</v>
+      </c>
       <c r="I36" s="4"/>
       <c r="L36">
         <v>0</v>
@@ -2914,7 +2913,9 @@
       <c r="D37" s="4">
         <v>0</v>
       </c>
-      <c r="H37"/>
+      <c r="H37">
+        <v>0.77</v>
+      </c>
       <c r="I37" s="5"/>
       <c r="L37">
         <v>0</v>
@@ -2953,7 +2954,9 @@
       <c r="D39" s="4">
         <v>0.73</v>
       </c>
-      <c r="H39"/>
+      <c r="H39">
+        <v>0.6</v>
+      </c>
       <c r="I39" s="5"/>
       <c r="L39">
         <v>0.8</v>
@@ -2973,7 +2976,9 @@
       <c r="D40" s="4">
         <v>0.75</v>
       </c>
-      <c r="H40"/>
+      <c r="H40">
+        <v>0.47</v>
+      </c>
       <c r="I40" s="5"/>
       <c r="L40">
         <v>0.8</v>
@@ -3015,7 +3020,9 @@
       <c r="D42" s="4">
         <v>0.7</v>
       </c>
-      <c r="H42"/>
+      <c r="H42">
+        <v>0.33</v>
+      </c>
       <c r="I42" s="5"/>
       <c r="L42">
         <v>0.24</v>
@@ -3149,10 +3156,10 @@
       <c r="P48" s="6"/>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="B49" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="11" t="s">
@@ -3168,10 +3175,10 @@
       <c r="P49" s="6"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="23" t="s">
+      <c r="A50" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="23" t="s">
+      <c r="B50" s="11" t="s">
         <v>98</v>
       </c>
       <c r="C50" s="11" t="s">
@@ -3187,10 +3194,10 @@
       <c r="P50" s="6"/>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="11" t="s">
         <v>100</v>
       </c>
       <c r="C51" s="11" t="s">
@@ -3209,10 +3216,10 @@
       <c r="P51" s="6"/>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="23" t="s">
+      <c r="A52" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="B52" s="23" t="s">
+      <c r="B52" s="11" t="s">
         <v>102</v>
       </c>
       <c r="C52" s="11" t="s">
@@ -3231,10 +3238,10 @@
       <c r="P52" s="6"/>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="23" t="s">
+      <c r="A53" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="11" t="s">
         <v>104</v>
       </c>
       <c r="C53" s="11" t="s">
@@ -3250,10 +3257,10 @@
       <c r="P53" s="6"/>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="11" t="s">
         <v>106</v>
       </c>
       <c r="C54" s="11" t="s">
@@ -3269,10 +3276,10 @@
       <c r="P54" s="6"/>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="11" t="s">
         <v>479</v>
       </c>
       <c r="C55" s="11" t="s">
@@ -3291,10 +3298,10 @@
       <c r="P55" s="6"/>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="B56" s="11" t="s">
         <v>109</v>
       </c>
       <c r="C56" s="11" t="s">
@@ -3313,10 +3320,10 @@
       <c r="P56" s="6"/>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="23" t="s">
+      <c r="A57" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B57" s="23" t="s">
+      <c r="B57" s="11" t="s">
         <v>111</v>
       </c>
       <c r="C57" s="11" t="s">
@@ -3332,10 +3339,10 @@
       <c r="P57" s="6"/>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B58" s="23" t="s">
+      <c r="B58" s="11" t="s">
         <v>113</v>
       </c>
       <c r="C58" s="11" t="s">
@@ -3964,10 +3971,10 @@
       <c r="P89" s="6"/>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="23" t="s">
+      <c r="A90" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="B90" s="23" t="s">
+      <c r="B90" s="11" t="s">
         <v>175</v>
       </c>
       <c r="C90" s="11" t="s">
@@ -3983,10 +3990,10 @@
       <c r="P90" s="6"/>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="23" t="s">
+      <c r="A91" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="B91" s="23" t="s">
+      <c r="B91" s="11" t="s">
         <v>178</v>
       </c>
       <c r="C91" s="11" t="s">
@@ -4002,10 +4009,10 @@
       <c r="P91" s="6"/>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" s="20" t="s">
+      <c r="A92" t="s">
         <v>477</v>
       </c>
-      <c r="B92" s="21" t="s">
+      <c r="B92" s="2" t="s">
         <v>478</v>
       </c>
       <c r="C92" t="s">
@@ -4021,10 +4028,10 @@
       <c r="P92" s="18"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="23" t="s">
+      <c r="A93" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="B93" s="23" t="s">
+      <c r="B93" s="11" t="s">
         <v>180</v>
       </c>
       <c r="C93" s="11" t="s">
@@ -4040,10 +4047,10 @@
       <c r="P93" s="6"/>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="23" t="s">
+      <c r="A94" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B94" s="23" t="s">
+      <c r="B94" s="11" t="s">
         <v>182</v>
       </c>
       <c r="C94" s="11" t="s">
@@ -4059,10 +4066,10 @@
       <c r="P94" s="6"/>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="23" t="s">
+      <c r="A95" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="B95" s="23" t="s">
+      <c r="B95" s="11" t="s">
         <v>184</v>
       </c>
       <c r="C95" s="11" t="s">
@@ -4078,10 +4085,10 @@
       <c r="P95" s="6"/>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="23" t="s">
+      <c r="A96" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="B96" s="23" t="s">
+      <c r="B96" s="11" t="s">
         <v>186</v>
       </c>
       <c r="C96" s="11" t="s">
@@ -4097,10 +4104,10 @@
       <c r="P96" s="6"/>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="23" t="s">
+      <c r="A97" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B97" s="23" t="s">
+      <c r="B97" s="11" t="s">
         <v>188</v>
       </c>
       <c r="C97" s="11" t="s">
@@ -4781,10 +4788,10 @@
       <c r="P132" s="6"/>
     </row>
     <row r="133" spans="1:16">
-      <c r="A133" s="23" t="s">
+      <c r="A133" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="B133" s="23" t="s">
+      <c r="B133" s="11" t="s">
         <v>254</v>
       </c>
       <c r="C133" s="11" t="s">
@@ -4800,10 +4807,10 @@
       <c r="P133" s="6"/>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="23" t="s">
+      <c r="A134" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="B134" s="23" t="s">
+      <c r="B134" s="11" t="s">
         <v>257</v>
       </c>
       <c r="C134" s="11" t="s">
@@ -4819,10 +4826,10 @@
       <c r="P134" s="6"/>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" s="23" t="s">
+      <c r="A135" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="B135" s="23" t="s">
+      <c r="B135" s="11" t="s">
         <v>259</v>
       </c>
       <c r="C135" s="11" t="s">
@@ -4838,10 +4845,10 @@
       <c r="P135" s="6"/>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="23" t="s">
+      <c r="A136" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="B136" s="23" t="s">
+      <c r="B136" s="11" t="s">
         <v>261</v>
       </c>
       <c r="C136" s="11" t="s">
@@ -4857,10 +4864,10 @@
       <c r="P136" s="6"/>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="23" t="s">
+      <c r="A137" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="B137" s="23" t="s">
+      <c r="B137" s="11" t="s">
         <v>263</v>
       </c>
       <c r="C137" s="11" t="s">
@@ -4876,10 +4883,10 @@
       <c r="P137" s="6"/>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="23" t="s">
+      <c r="A138" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="B138" s="23" t="s">
+      <c r="B138" s="11" t="s">
         <v>265</v>
       </c>
       <c r="C138" s="11" t="s">
@@ -4895,10 +4902,10 @@
       <c r="P138" s="6"/>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="23" t="s">
+      <c r="A139" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="B139" s="23" t="s">
+      <c r="B139" s="11" t="s">
         <v>267</v>
       </c>
       <c r="C139" s="11" t="s">
@@ -4914,10 +4921,10 @@
       <c r="P139" s="6"/>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" s="23" t="s">
+      <c r="A140" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B140" s="23" t="s">
+      <c r="B140" s="11" t="s">
         <v>269</v>
       </c>
       <c r="C140" s="11" t="s">
@@ -4933,10 +4940,10 @@
       <c r="P140" s="6"/>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="23" t="s">
+      <c r="A141" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="B141" s="23" t="s">
+      <c r="B141" s="11" t="s">
         <v>271</v>
       </c>
       <c r="C141" s="11" t="s">
@@ -4952,10 +4959,10 @@
       <c r="P141" s="6"/>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="23" t="s">
+      <c r="A142" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="B142" s="23" t="s">
+      <c r="B142" s="11" t="s">
         <v>273</v>
       </c>
       <c r="C142" s="11" t="s">
@@ -4971,10 +4978,10 @@
       <c r="P142" s="6"/>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="23" t="s">
+      <c r="A143" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B143" s="23" t="s">
+      <c r="B143" s="11" t="s">
         <v>274</v>
       </c>
       <c r="C143" s="11" t="s">
@@ -4990,10 +4997,10 @@
       <c r="P143" s="6"/>
     </row>
     <row r="144" spans="1:16">
-      <c r="A144" s="23" t="s">
+      <c r="A144" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B144" s="23" t="s">
+      <c r="B144" s="11" t="s">
         <v>276</v>
       </c>
       <c r="C144" s="11" t="s">
@@ -5731,10 +5738,10 @@
       <c r="P182" s="6"/>
     </row>
     <row r="183" spans="1:16">
-      <c r="A183" s="23" t="s">
+      <c r="A183" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B183" s="23" t="s">
+      <c r="B183" s="11" t="s">
         <v>350</v>
       </c>
       <c r="C183" s="11" t="s">
@@ -5750,10 +5757,10 @@
       <c r="P183" s="6"/>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" s="20" t="s">
+      <c r="A184" t="s">
         <v>449</v>
       </c>
-      <c r="B184" s="24" t="s">
+      <c r="B184" s="3" t="s">
         <v>450</v>
       </c>
       <c r="C184" t="s">
@@ -5769,10 +5776,10 @@
       <c r="P184" s="6"/>
     </row>
     <row r="185" spans="1:16">
-      <c r="A185" s="23" t="s">
+      <c r="A185" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="B185" s="23" t="s">
+      <c r="B185" s="11" t="s">
         <v>353</v>
       </c>
       <c r="C185" s="11" t="s">
@@ -6377,10 +6384,10 @@
       <c r="P216" s="6"/>
     </row>
     <row r="217" spans="1:16">
-      <c r="A217" s="23" t="s">
+      <c r="A217" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="B217" s="23" t="s">
+      <c r="B217" s="11" t="s">
         <v>409</v>
       </c>
       <c r="C217" s="11" t="s">
@@ -6491,10 +6498,10 @@
       <c r="P222" s="6"/>
     </row>
     <row r="223" spans="1:16">
-      <c r="A223" s="20" t="s">
+      <c r="A223" t="s">
         <v>463</v>
       </c>
-      <c r="B223" s="21" t="s">
+      <c r="B223" s="2" t="s">
         <v>464</v>
       </c>
       <c r="C223" t="s">
@@ -6510,10 +6517,10 @@
       <c r="P223" s="18"/>
     </row>
     <row r="224" spans="1:16">
-      <c r="A224" s="23" t="s">
+      <c r="A224" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="B224" s="23" t="s">
+      <c r="B224" s="11" t="s">
         <v>422</v>
       </c>
       <c r="C224" s="11" t="s">
@@ -6529,10 +6536,10 @@
       <c r="P224" s="6"/>
     </row>
     <row r="225" spans="1:16">
-      <c r="A225" s="23" t="s">
+      <c r="A225" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="B225" s="23" t="s">
+      <c r="B225" s="11" t="s">
         <v>425</v>
       </c>
       <c r="C225" s="11" t="s">
@@ -6583,7 +6590,6 @@
         <v>0.16</v>
       </c>
       <c r="I227" s="4"/>
-      <c r="P227" s="20"/>
     </row>
     <row r="228" spans="1:16">
       <c r="A228" t="s">
@@ -6602,7 +6608,6 @@
         <v>0.26</v>
       </c>
       <c r="I228" s="4"/>
-      <c r="P228" s="20"/>
     </row>
     <row r="229" spans="1:16">
       <c r="A229" s="11" t="s">
@@ -6621,7 +6626,7 @@
         <v>0.63</v>
       </c>
       <c r="I229" s="4"/>
-      <c r="P229" s="22"/>
+      <c r="P229" s="19"/>
     </row>
     <row r="230" spans="1:16">
       <c r="A230" s="11" t="s">
@@ -6640,7 +6645,7 @@
         <v>0.26</v>
       </c>
       <c r="I230" s="4"/>
-      <c r="P230" s="22"/>
+      <c r="P230" s="19"/>
     </row>
     <row r="231" spans="1:16">
       <c r="A231" s="11" t="s">
@@ -6659,7 +6664,7 @@
         <v>0.67</v>
       </c>
       <c r="I231" s="4"/>
-      <c r="P231" s="22"/>
+      <c r="P231" s="19"/>
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="11" t="s">
@@ -6678,7 +6683,7 @@
         <v>0.37</v>
       </c>
       <c r="I232" s="4"/>
-      <c r="P232" s="22"/>
+      <c r="P232" s="19"/>
     </row>
     <row r="233" spans="1:16">
       <c r="A233" t="s">
@@ -6697,7 +6702,6 @@
         <v>0.35</v>
       </c>
       <c r="I233" s="4"/>
-      <c r="P233" s="20"/>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" s="11" t="s">
@@ -6716,7 +6720,7 @@
         <v>0.44</v>
       </c>
       <c r="I234" s="4"/>
-      <c r="P234" s="22"/>
+      <c r="P234" s="19"/>
     </row>
     <row r="235" spans="1:16">
       <c r="A235" s="11" t="s">
@@ -6735,7 +6739,7 @@
         <v>0.63</v>
       </c>
       <c r="I235" s="4"/>
-      <c r="P235" s="22"/>
+      <c r="P235" s="19"/>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" t="s">
@@ -6754,7 +6758,6 @@
         <v>0.54</v>
       </c>
       <c r="I236" s="4"/>
-      <c r="P236" s="20"/>
     </row>
     <row r="237" spans="1:16">
       <c r="A237" t="s">
@@ -6773,7 +6776,6 @@
         <v>0.42</v>
       </c>
       <c r="I237" s="4"/>
-      <c r="P237" s="20"/>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" t="s">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429EB6A9-1DB0-2046-935F-AF91BDE323A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE39990-032B-5147-BB58-22B5AA25D7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -53,15 +53,6 @@
     <t>AS_1</t>
   </si>
   <si>
-    <t>Test_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_3 </t>
-  </si>
-  <si>
     <t xml:space="preserve">AS_2 </t>
   </si>
   <si>
@@ -1508,9 +1499,6 @@
     <t>H</t>
   </si>
   <si>
-    <t>Test_4</t>
-  </si>
-  <si>
     <t>AS_4</t>
   </si>
   <si>
@@ -1524,6 +1512,18 @@
   </si>
   <si>
     <t>Q_4</t>
+  </si>
+  <si>
+    <t>T_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T_2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T_3 </t>
+  </si>
+  <si>
+    <t>T_4</t>
   </si>
 </sst>
 </file>
@@ -1744,10 +1744,10 @@
     <tableColumn id="5" xr3:uid="{4A2A2B68-EF30-7742-9921-AE9C8CB19994}" name="Q_2"/>
     <tableColumn id="6" xr3:uid="{F4845CBF-1A2D-6F4D-8189-BDA9FF51FC40}" name="Q_3"/>
     <tableColumn id="14" xr3:uid="{EB0128D0-EDEA-7E4E-BB55-3B322034409A}" name="Q_4"/>
-    <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="Test_1"/>
-    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="Test_2 " dataDxfId="0"/>
-    <tableColumn id="9" xr3:uid="{AF37A560-C5F8-4E49-A224-CE84A49E046A}" name="Test_3 "/>
-    <tableColumn id="15" xr3:uid="{2B895D50-2C68-B148-81D6-7366E82004E7}" name="Test_4"/>
+    <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="T_1"/>
+    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="T_2 " dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{AF37A560-C5F8-4E49-A224-CE84A49E046A}" name="T_3 "/>
+    <tableColumn id="15" xr3:uid="{2B895D50-2C68-B148-81D6-7366E82004E7}" name="T_4"/>
     <tableColumn id="10" xr3:uid="{E7DCE493-9761-F446-9017-EFE5CA173E6F}" name="AS_1"/>
     <tableColumn id="11" xr3:uid="{22CC7E9A-51CA-274B-9C92-B1E8F88F4324}" name="AS_2 "/>
     <tableColumn id="12" xr3:uid="{912F9A7A-D63B-9A42-91A4-38F3D4DCB1F9}" name="AS_3"/>
@@ -2094,40 +2094,40 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E1" t="s">
+        <v>489</v>
+      </c>
+      <c r="F1" t="s">
+        <v>490</v>
+      </c>
+      <c r="G1" t="s">
+        <v>491</v>
+      </c>
+      <c r="H1" t="s">
         <v>492</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>494</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>495</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>490</v>
       </c>
       <c r="L1" t="s">
         <v>4</v>
       </c>
       <c r="M1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="P1" t="s">
         <v>2</v>
@@ -2135,16 +2135,19 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D2" s="4">
         <v>0.56999999999999995</v>
+      </c>
+      <c r="E2">
+        <v>0.99</v>
       </c>
       <c r="H2">
         <v>0.79</v>
@@ -2157,16 +2160,19 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D3" s="4">
         <v>0.86</v>
+      </c>
+      <c r="E3">
+        <v>0.94</v>
       </c>
       <c r="H3">
         <v>0.39</v>
@@ -2179,16 +2185,19 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D4" s="4">
         <v>0.79</v>
+      </c>
+      <c r="E4">
+        <v>0.94</v>
       </c>
       <c r="H4">
         <v>0.39</v>
@@ -2201,16 +2210,19 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D5" s="4">
         <v>0.75</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0.54</v>
@@ -2223,16 +2235,19 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D6" s="4">
         <v>0.64</v>
+      </c>
+      <c r="E6">
+        <v>0.91</v>
       </c>
       <c r="H6">
         <v>0.53</v>
@@ -2245,16 +2260,19 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D7" s="4">
         <v>0.82</v>
+      </c>
+      <c r="E7">
+        <v>0.94</v>
       </c>
       <c r="H7">
         <v>0.42</v>
@@ -2267,15 +2285,18 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>0</v>
       </c>
       <c r="H8">
@@ -2289,16 +2310,19 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
         <v>63</v>
-      </c>
-      <c r="C9" t="s">
-        <v>66</v>
       </c>
       <c r="D9" s="4">
         <v>0.75</v>
+      </c>
+      <c r="E9">
+        <v>0.93</v>
       </c>
       <c r="H9">
         <v>0.47</v>
@@ -2311,19 +2335,22 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D10" s="4">
         <v>0.56999999999999995</v>
       </c>
+      <c r="E10">
+        <v>0.9</v>
+      </c>
       <c r="H10" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I10" s="5"/>
       <c r="L10">
@@ -2333,16 +2360,19 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D11" s="4">
         <v>0.76</v>
+      </c>
+      <c r="E11">
+        <v>0.95</v>
       </c>
       <c r="H11">
         <v>0.16</v>
@@ -2355,16 +2385,19 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D12" s="4">
         <v>0.79</v>
+      </c>
+      <c r="E12">
+        <v>0.7</v>
       </c>
       <c r="H12">
         <v>0.44</v>
@@ -2377,16 +2410,19 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D13" s="4">
         <v>0.75</v>
+      </c>
+      <c r="E13">
+        <v>0.94</v>
       </c>
       <c r="H13">
         <v>0.44</v>
@@ -2399,16 +2435,19 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D14" s="4">
         <v>0.74</v>
+      </c>
+      <c r="E14">
+        <v>0.82</v>
       </c>
       <c r="H14">
         <v>0.4</v>
@@ -2421,16 +2460,19 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D15" s="4">
         <v>0.75</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
       </c>
       <c r="H15">
         <v>0.67</v>
@@ -2443,16 +2485,19 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D16" s="4">
         <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0.9</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2465,16 +2510,19 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D17" s="4">
         <v>0.72</v>
+      </c>
+      <c r="E17">
+        <v>0.8</v>
       </c>
       <c r="H17">
         <v>0.37</v>
@@ -2487,16 +2535,19 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D18" s="4">
         <v>0.68</v>
+      </c>
+      <c r="E18">
+        <v>0.93</v>
       </c>
       <c r="H18">
         <v>0.44</v>
@@ -2509,17 +2560,20 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="15" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D19" s="4">
         <v>0</v>
       </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
       <c r="H19">
         <v>0.53</v>
       </c>
@@ -2528,16 +2582,19 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D20" s="4">
         <v>0.85</v>
+      </c>
+      <c r="E20">
+        <v>0.92</v>
       </c>
       <c r="H20">
         <v>0.54</v>
@@ -2550,16 +2607,19 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D21" s="4">
         <v>0.78</v>
+      </c>
+      <c r="E21">
+        <v>0.92</v>
       </c>
       <c r="H21">
         <v>0.65</v>
@@ -2572,16 +2632,19 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D22" s="4">
         <v>0.82</v>
+      </c>
+      <c r="E22">
+        <v>0.92</v>
       </c>
       <c r="H22">
         <v>0.33</v>
@@ -2594,16 +2657,19 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D23" s="4">
         <v>0.7</v>
+      </c>
+      <c r="E23">
+        <v>0.93</v>
       </c>
       <c r="H23">
         <v>0.68</v>
@@ -2616,16 +2682,19 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D24" s="4">
         <v>0.74</v>
+      </c>
+      <c r="E24">
+        <v>0.93</v>
       </c>
       <c r="H24">
         <v>0.67</v>
@@ -2638,16 +2707,19 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D25" s="4">
         <v>0.67</v>
+      </c>
+      <c r="E25">
+        <v>0.9</v>
       </c>
       <c r="H25">
         <v>0.61</v>
@@ -2660,16 +2732,19 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D26" s="4">
         <v>0.85</v>
+      </c>
+      <c r="E26">
+        <v>0.95</v>
       </c>
       <c r="H26">
         <v>0.53</v>
@@ -2682,16 +2757,19 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D27" s="4">
         <v>0.83</v>
+      </c>
+      <c r="E27">
+        <v>0.94</v>
       </c>
       <c r="H27">
         <v>0.57999999999999996</v>
@@ -2704,16 +2782,19 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D28" s="4">
         <v>0.77</v>
+      </c>
+      <c r="E28">
+        <v>0.93</v>
       </c>
       <c r="H28">
         <v>0.63</v>
@@ -2726,16 +2807,19 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D29" s="4">
         <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0.91</v>
       </c>
       <c r="H29">
         <v>0.75</v>
@@ -2748,16 +2832,19 @@
     </row>
     <row r="30" spans="1:16">
       <c r="A30" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D30" s="4">
         <v>0.86</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
       </c>
       <c r="H30">
         <v>0.35</v>
@@ -2770,16 +2857,19 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D31" s="4">
         <v>0.79</v>
+      </c>
+      <c r="E31">
+        <v>0.82</v>
       </c>
       <c r="H31">
         <v>0.6</v>
@@ -2792,16 +2882,19 @@
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s">
         <v>90</v>
-      </c>
-      <c r="C32" t="s">
-        <v>93</v>
       </c>
       <c r="D32" s="4">
         <v>0.84</v>
+      </c>
+      <c r="E32">
+        <v>0.86</v>
       </c>
       <c r="H32">
         <v>0.47</v>
@@ -2814,16 +2907,19 @@
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="7" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D33" s="4">
         <v>0.81</v>
+      </c>
+      <c r="E33">
+        <v>0.85</v>
       </c>
       <c r="H33">
         <v>0.54</v>
@@ -2836,16 +2932,19 @@
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="13" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D34" s="4">
         <v>0.65</v>
+      </c>
+      <c r="E34">
+        <v>0.9</v>
       </c>
       <c r="H34">
         <v>0.16</v>
@@ -2858,16 +2957,19 @@
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D35" s="4">
         <v>0.84</v>
+      </c>
+      <c r="E35">
+        <v>0.99</v>
       </c>
       <c r="H35">
         <v>0.42</v>
@@ -2880,16 +2982,19 @@
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="13" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D36" s="4">
         <v>0.66</v>
+      </c>
+      <c r="E36">
+        <v>0.74</v>
       </c>
       <c r="H36">
         <v>0.47</v>
@@ -2902,15 +3007,18 @@
     </row>
     <row r="37" spans="1:16" ht="20">
       <c r="A37" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D37" s="4">
+        <v>0</v>
+      </c>
+      <c r="E37">
         <v>0</v>
       </c>
       <c r="H37">
@@ -2924,17 +3032,20 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="15" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D38" s="4">
         <v>0</v>
       </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
       <c r="H38">
         <v>0.52</v>
       </c>
@@ -2943,16 +3054,19 @@
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C39" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D39" s="4">
         <v>0.73</v>
+      </c>
+      <c r="E39">
+        <v>0.95</v>
       </c>
       <c r="H39">
         <v>0.6</v>
@@ -2965,16 +3079,19 @@
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D40" s="4">
         <v>0.75</v>
+      </c>
+      <c r="E40">
+        <v>0.94</v>
       </c>
       <c r="H40">
         <v>0.47</v>
@@ -2987,16 +3104,19 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D41" s="4">
         <v>0.77</v>
+      </c>
+      <c r="E41">
+        <v>0.89</v>
       </c>
       <c r="H41">
         <v>0.57999999999999996</v>
@@ -3009,16 +3129,19 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C42" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D42" s="4">
         <v>0.7</v>
+      </c>
+      <c r="E42">
+        <v>0.93</v>
       </c>
       <c r="H42">
         <v>0.33</v>
@@ -3031,17 +3154,20 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C43" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D43" s="4">
         <v>0</v>
       </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
       <c r="H43">
         <v>0.54</v>
       </c>
@@ -3050,17 +3176,20 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C44" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D44" s="4">
         <v>0</v>
       </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
       <c r="H44">
         <v>0.65</v>
       </c>
@@ -3069,16 +3198,19 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D45" s="4">
         <v>0.64</v>
+      </c>
+      <c r="E45">
+        <v>0.82</v>
       </c>
       <c r="H45">
         <v>0.44</v>
@@ -3091,16 +3223,19 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D46" s="4">
         <v>0.77</v>
+      </c>
+      <c r="E46">
+        <v>0.89</v>
       </c>
       <c r="H46">
         <v>0.44</v>
@@ -3113,16 +3248,19 @@
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C47" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D47" s="4">
         <v>0.91</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
       </c>
       <c r="H47">
         <v>0.54</v>
@@ -3135,16 +3273,19 @@
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D48" s="4">
         <v>0.67</v>
+      </c>
+      <c r="E48">
+        <v>0.97</v>
       </c>
       <c r="H48">
         <v>0.56000000000000005</v>
@@ -3157,17 +3298,20 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D49" s="11">
         <v>0.79</v>
       </c>
+      <c r="E49">
+        <v>0.98</v>
+      </c>
       <c r="H49">
         <v>0.68</v>
       </c>
@@ -3176,17 +3320,20 @@
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D50" s="11">
         <v>0.89</v>
       </c>
+      <c r="E50">
+        <v>0.91</v>
+      </c>
       <c r="H50">
         <v>0.75</v>
       </c>
@@ -3195,16 +3342,19 @@
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D51" s="11">
         <v>0.9</v>
+      </c>
+      <c r="E51">
+        <v>0.94</v>
       </c>
       <c r="H51">
         <v>0.6</v>
@@ -3217,16 +3367,19 @@
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D52" s="11">
         <v>0.85</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
       </c>
       <c r="H52">
         <v>0.54</v>
@@ -3239,17 +3392,20 @@
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D53" s="11">
         <v>0.85</v>
       </c>
+      <c r="E53">
+        <v>0.98</v>
+      </c>
       <c r="H53">
         <v>0.6</v>
       </c>
@@ -3258,17 +3414,20 @@
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D54" s="11">
         <v>0.77</v>
       </c>
+      <c r="E54">
+        <v>0.88</v>
+      </c>
       <c r="H54">
         <v>0.33</v>
       </c>
@@ -3277,16 +3436,19 @@
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D55" s="11">
         <v>0.86</v>
+      </c>
+      <c r="E55">
+        <v>0.97</v>
       </c>
       <c r="H55">
         <v>0.56000000000000005</v>
@@ -3299,16 +3461,19 @@
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D56" s="11">
         <v>0.75</v>
+      </c>
+      <c r="E56">
+        <v>0.98</v>
       </c>
       <c r="H56">
         <v>0.32</v>
@@ -3321,17 +3486,20 @@
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D57" s="11">
         <v>0.69</v>
       </c>
+      <c r="E57">
+        <v>0.97</v>
+      </c>
       <c r="H57">
         <v>0.51</v>
       </c>
@@ -3340,17 +3508,20 @@
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D58" s="11">
         <v>0.71</v>
       </c>
+      <c r="E58">
+        <v>0.91</v>
+      </c>
       <c r="H58">
         <v>0.32</v>
       </c>
@@ -3359,16 +3530,19 @@
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D59" s="11">
         <v>0.9</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
       </c>
       <c r="H59">
         <v>0.81</v>
@@ -3381,16 +3555,19 @@
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D60" s="11">
         <v>0.91</v>
+      </c>
+      <c r="E60">
+        <v>0.98</v>
       </c>
       <c r="H60">
         <v>0.46</v>
@@ -3403,17 +3580,20 @@
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D61" s="11">
         <v>0.82</v>
       </c>
+      <c r="E61">
+        <v>0.88</v>
+      </c>
       <c r="H61">
         <v>0.46</v>
       </c>
@@ -3422,16 +3602,19 @@
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D62" s="11">
         <v>0.75</v>
+      </c>
+      <c r="E62">
+        <v>0.91</v>
       </c>
       <c r="H62">
         <v>0.37</v>
@@ -3444,17 +3627,20 @@
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D63" s="11">
         <v>0.76</v>
       </c>
+      <c r="E63">
+        <v>0.92</v>
+      </c>
       <c r="H63">
         <v>0.63</v>
       </c>
@@ -3463,17 +3649,20 @@
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D64" s="11">
         <v>0.72</v>
       </c>
+      <c r="E64">
+        <v>0.99</v>
+      </c>
       <c r="H64">
         <v>0.37</v>
       </c>
@@ -3482,17 +3671,20 @@
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D65" s="11">
         <v>0.86</v>
       </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
       <c r="H65">
         <v>0.53</v>
       </c>
@@ -3501,17 +3693,20 @@
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D66" s="11">
         <v>0.76</v>
       </c>
+      <c r="E66">
+        <v>0.78</v>
+      </c>
       <c r="H66">
         <v>0.35</v>
       </c>
@@ -3520,16 +3715,19 @@
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D67" s="11">
         <v>0.88</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
       </c>
       <c r="H67">
         <v>0.77</v>
@@ -3542,17 +3740,20 @@
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D68" s="11">
         <v>0.85</v>
       </c>
+      <c r="E68">
+        <v>0.97</v>
+      </c>
       <c r="H68">
         <v>0.6</v>
       </c>
@@ -3561,16 +3762,19 @@
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D69" s="11">
         <v>0.82</v>
+      </c>
+      <c r="E69">
+        <v>0.98</v>
       </c>
       <c r="H69">
         <v>0.56000000000000005</v>
@@ -3583,17 +3787,20 @@
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D70" s="11">
         <v>0.78</v>
       </c>
+      <c r="E70">
+        <v>0.87</v>
+      </c>
       <c r="H70">
         <v>0.57999999999999996</v>
       </c>
@@ -3602,17 +3809,20 @@
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D71" s="11">
         <v>0.7</v>
       </c>
+      <c r="E71">
+        <v>0.91</v>
+      </c>
       <c r="H71">
         <v>0.35</v>
       </c>
@@ -3621,17 +3831,20 @@
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D72" s="11">
         <v>0.83</v>
       </c>
+      <c r="E72">
+        <v>0.89</v>
+      </c>
       <c r="H72">
         <v>0.28000000000000003</v>
       </c>
@@ -3640,16 +3853,19 @@
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D73" s="11">
         <v>0.84</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
       </c>
       <c r="H73">
         <v>0.77</v>
@@ -3662,17 +3878,20 @@
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D74" s="11">
         <v>0.84</v>
       </c>
+      <c r="E74">
+        <v>0.98</v>
+      </c>
       <c r="H74">
         <v>0.51</v>
       </c>
@@ -3681,17 +3900,20 @@
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D75" s="11">
         <v>0.75</v>
       </c>
+      <c r="E75">
+        <v>0.96</v>
+      </c>
       <c r="H75">
         <v>0.05</v>
       </c>
@@ -3700,17 +3922,20 @@
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D76" s="11">
         <v>0.89</v>
       </c>
+      <c r="E76">
+        <v>0.99</v>
+      </c>
       <c r="H76">
         <v>0.61</v>
       </c>
@@ -3719,16 +3944,19 @@
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D77" s="11">
         <v>0.88</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
       </c>
       <c r="H77">
         <v>0.74</v>
@@ -3741,17 +3969,20 @@
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D78" s="11">
         <v>0.68</v>
       </c>
+      <c r="E78">
+        <v>0.92</v>
+      </c>
       <c r="H78">
         <v>0.57999999999999996</v>
       </c>
@@ -3760,16 +3991,19 @@
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D79" s="11">
         <v>0.78</v>
+      </c>
+      <c r="E79">
+        <v>0.93</v>
       </c>
       <c r="H79">
         <v>0.61</v>
@@ -3782,17 +4016,20 @@
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D80" s="11">
         <v>0.84</v>
       </c>
+      <c r="E80">
+        <v>0.94</v>
+      </c>
       <c r="H80">
         <v>0.47</v>
       </c>
@@ -3801,17 +4038,20 @@
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D81" s="11">
         <v>0.84</v>
       </c>
+      <c r="E81">
+        <v>0.87</v>
+      </c>
       <c r="H81">
         <v>0.65</v>
       </c>
@@ -3820,17 +4060,20 @@
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D82" s="11">
         <v>0.74</v>
       </c>
+      <c r="E82">
+        <v>0.98</v>
+      </c>
       <c r="H82">
         <v>0.39</v>
       </c>
@@ -3839,17 +4082,20 @@
     </row>
     <row r="83" spans="1:16">
       <c r="A83" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C83" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D83" s="4">
         <v>0</v>
       </c>
+      <c r="E83">
+        <v>0.97</v>
+      </c>
       <c r="H83">
         <v>0.54</v>
       </c>
@@ -3858,17 +4104,20 @@
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="11" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D84" s="11">
         <v>0.81</v>
       </c>
+      <c r="E84">
+        <v>0.93</v>
+      </c>
       <c r="H84">
         <v>0.79</v>
       </c>
@@ -3877,17 +4126,20 @@
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D85" s="11">
         <v>0.71</v>
       </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
       <c r="H85">
         <v>0.63</v>
       </c>
@@ -3896,17 +4148,20 @@
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D86" s="11">
         <v>0.76</v>
       </c>
+      <c r="E86">
+        <v>0.89</v>
+      </c>
       <c r="H86">
         <v>0.61</v>
       </c>
@@ -3915,17 +4170,20 @@
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D87" s="11">
         <v>0.81</v>
       </c>
+      <c r="E87">
+        <v>0.82</v>
+      </c>
       <c r="H87">
         <v>0.25</v>
       </c>
@@ -3934,17 +4192,20 @@
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D88" s="11">
         <v>0.83</v>
       </c>
+      <c r="E88">
+        <v>0.98</v>
+      </c>
       <c r="H88">
         <v>0.6</v>
       </c>
@@ -3953,17 +4214,20 @@
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D89" s="11">
         <v>0.85</v>
       </c>
+      <c r="E89">
+        <v>0.96</v>
+      </c>
       <c r="H89">
         <v>0.54</v>
       </c>
@@ -3972,17 +4236,20 @@
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D90" s="11">
         <v>0.75</v>
       </c>
+      <c r="E90">
+        <v>0.97</v>
+      </c>
       <c r="H90">
         <v>0.68</v>
       </c>
@@ -3991,17 +4258,20 @@
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D91" s="11">
         <v>0.75</v>
       </c>
+      <c r="E91">
+        <v>0.86</v>
+      </c>
       <c r="H91">
         <v>0.6</v>
       </c>
@@ -4010,17 +4280,20 @@
     </row>
     <row r="92" spans="1:16">
       <c r="A92" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C92" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D92" s="4">
         <v>0</v>
       </c>
+      <c r="E92">
+        <v>0.53</v>
+      </c>
       <c r="H92">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -4029,17 +4302,20 @@
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D93" s="11">
         <v>0.82</v>
       </c>
+      <c r="E93">
+        <v>0.99</v>
+      </c>
       <c r="H93">
         <v>0.47</v>
       </c>
@@ -4048,17 +4324,20 @@
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D94" s="11">
         <v>0.75</v>
       </c>
+      <c r="E94">
+        <v>0.91</v>
+      </c>
       <c r="H94">
         <v>0.65</v>
       </c>
@@ -4067,17 +4346,20 @@
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="11" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D95" s="11">
         <v>0.77</v>
       </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
       <c r="H95">
         <v>0.42</v>
       </c>
@@ -4086,17 +4368,20 @@
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D96" s="11">
         <v>0.93</v>
       </c>
+      <c r="E96">
+        <v>0.9</v>
+      </c>
       <c r="H96">
         <v>0.79</v>
       </c>
@@ -4105,17 +4390,20 @@
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="11" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D97" s="11">
         <v>0.79</v>
       </c>
+      <c r="E97">
+        <v>0.98</v>
+      </c>
       <c r="H97">
         <v>0.46</v>
       </c>
@@ -4124,17 +4412,20 @@
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D98" s="11">
         <v>0.93</v>
       </c>
+      <c r="E98">
+        <v>0.96</v>
+      </c>
       <c r="H98">
         <v>0.72</v>
       </c>
@@ -4143,17 +4434,20 @@
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D99" s="11">
         <v>0.83</v>
       </c>
+      <c r="E99">
+        <v>0.96</v>
+      </c>
       <c r="H99">
         <v>0.28000000000000003</v>
       </c>
@@ -4162,17 +4456,20 @@
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D100" s="11">
         <v>0.9</v>
       </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
       <c r="H100">
         <v>0.4</v>
       </c>
@@ -4181,17 +4478,20 @@
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D101" s="11">
         <v>0.83</v>
       </c>
+      <c r="E101">
+        <v>0.91</v>
+      </c>
       <c r="H101">
         <v>0.44</v>
       </c>
@@ -4200,17 +4500,20 @@
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="11" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D102" s="11">
         <v>0.85</v>
       </c>
+      <c r="E102">
+        <v>0.99</v>
+      </c>
       <c r="H102">
         <v>0.51</v>
       </c>
@@ -4219,17 +4522,20 @@
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D103" s="11">
         <v>0.89</v>
       </c>
+      <c r="E103">
+        <v>0.8</v>
+      </c>
       <c r="H103">
         <v>0.49</v>
       </c>
@@ -4238,17 +4544,20 @@
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="11" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D104" s="11">
         <v>0.85</v>
       </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
       <c r="H104">
         <v>0.54</v>
       </c>
@@ -4257,17 +4566,20 @@
     </row>
     <row r="105" spans="1:16">
       <c r="A105" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C105" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D105" s="4">
         <v>0</v>
       </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
       <c r="H105">
         <v>0.51</v>
       </c>
@@ -4276,17 +4588,20 @@
     </row>
     <row r="106" spans="1:16">
       <c r="A106" s="11" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D106" s="11">
         <v>0.86</v>
       </c>
+      <c r="E106">
+        <v>0.94</v>
+      </c>
       <c r="H106">
         <v>0.4</v>
       </c>
@@ -4295,17 +4610,20 @@
     </row>
     <row r="107" spans="1:16">
       <c r="A107" s="11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D107" s="11">
         <v>0.79</v>
       </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
       <c r="H107">
         <v>0.44</v>
       </c>
@@ -4314,17 +4632,20 @@
     </row>
     <row r="108" spans="1:16">
       <c r="A108" s="11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D108" s="11">
         <v>0.76</v>
       </c>
+      <c r="E108">
+        <v>0.91</v>
+      </c>
       <c r="H108">
         <v>0.39</v>
       </c>
@@ -4333,17 +4654,20 @@
     </row>
     <row r="109" spans="1:16">
       <c r="A109" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D109" s="11">
         <v>0.84</v>
       </c>
+      <c r="E109">
+        <v>0.89</v>
+      </c>
       <c r="H109">
         <v>0.75</v>
       </c>
@@ -4352,17 +4676,20 @@
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="11" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D110" s="11">
         <v>0.82</v>
       </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
       <c r="H110">
         <v>0.61</v>
       </c>
@@ -4371,17 +4698,20 @@
     </row>
     <row r="111" spans="1:16">
       <c r="A111" s="11" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D111" s="11">
         <v>0.83</v>
       </c>
+      <c r="E111">
+        <v>0.94</v>
+      </c>
       <c r="H111">
         <v>0.26</v>
       </c>
@@ -4390,17 +4720,20 @@
     </row>
     <row r="112" spans="1:16">
       <c r="A112" s="11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D112" s="11">
         <v>0.94</v>
       </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
       <c r="H112">
         <v>0.46</v>
       </c>
@@ -4409,17 +4742,20 @@
     </row>
     <row r="113" spans="1:16">
       <c r="A113" s="11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D113" s="11">
         <v>0.9</v>
       </c>
+      <c r="E113">
+        <v>0.91</v>
+      </c>
       <c r="H113">
         <v>0.42</v>
       </c>
@@ -4428,17 +4764,20 @@
     </row>
     <row r="114" spans="1:16">
       <c r="A114" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D114" s="11">
         <v>0.75</v>
       </c>
+      <c r="E114">
+        <v>0.91</v>
+      </c>
       <c r="H114">
         <v>0.39</v>
       </c>
@@ -4447,17 +4786,20 @@
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D115" s="11">
         <v>0.9</v>
       </c>
+      <c r="E115">
+        <v>0.87</v>
+      </c>
       <c r="H115">
         <v>0.46</v>
       </c>
@@ -4466,17 +4808,20 @@
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D116" s="11">
         <v>0.66</v>
       </c>
+      <c r="E116">
+        <v>0.84</v>
+      </c>
       <c r="H116">
         <v>0.63</v>
       </c>
@@ -4485,17 +4830,20 @@
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D117" s="11">
         <v>0.92</v>
       </c>
+      <c r="E117">
+        <v>0.9</v>
+      </c>
       <c r="H117">
         <v>0.44</v>
       </c>
@@ -4504,17 +4852,20 @@
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D118" s="11">
         <v>0.82</v>
       </c>
+      <c r="E118">
+        <v>0.9</v>
+      </c>
       <c r="H118">
         <v>0.54</v>
       </c>
@@ -4523,17 +4874,20 @@
     </row>
     <row r="119" spans="1:16">
       <c r="A119" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C119" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D119" s="4">
         <v>0</v>
       </c>
+      <c r="E119">
+        <v>0.9</v>
+      </c>
       <c r="H119">
         <v>0.14000000000000001</v>
       </c>
@@ -4542,17 +4896,20 @@
     </row>
     <row r="120" spans="1:16">
       <c r="A120" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D120" s="11">
         <v>0.8</v>
       </c>
+      <c r="E120">
+        <v>0.97</v>
+      </c>
       <c r="H120">
         <v>0.26</v>
       </c>
@@ -4561,17 +4918,20 @@
     </row>
     <row r="121" spans="1:16">
       <c r="A121" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D121" s="11">
         <v>0.96</v>
       </c>
+      <c r="E121">
+        <v>0.96</v>
+      </c>
       <c r="H121">
         <v>0.26</v>
       </c>
@@ -4580,17 +4940,20 @@
     </row>
     <row r="122" spans="1:16">
       <c r="A122" s="11" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D122" s="11">
         <v>0.69</v>
       </c>
+      <c r="E122">
+        <v>0.5</v>
+      </c>
       <c r="H122">
         <v>0.26</v>
       </c>
@@ -4599,17 +4962,20 @@
     </row>
     <row r="123" spans="1:16">
       <c r="A123" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D123" s="11">
         <v>0.78</v>
       </c>
+      <c r="E123">
+        <v>0.96</v>
+      </c>
       <c r="H123">
         <v>0.09</v>
       </c>
@@ -4618,17 +4984,20 @@
     </row>
     <row r="124" spans="1:16">
       <c r="A124" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D124" s="11">
         <v>0.75</v>
       </c>
+      <c r="E124">
+        <v>0.99</v>
+      </c>
       <c r="H124">
         <v>0.49</v>
       </c>
@@ -4637,17 +5006,20 @@
     </row>
     <row r="125" spans="1:16">
       <c r="A125" s="11" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D125" s="11">
         <v>0.67</v>
       </c>
+      <c r="E125">
+        <v>0.98</v>
+      </c>
       <c r="H125">
         <v>0.74</v>
       </c>
@@ -4656,17 +5028,20 @@
     </row>
     <row r="126" spans="1:16">
       <c r="A126" s="11" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D126" s="11">
         <v>0.84</v>
       </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
       <c r="H126">
         <v>0.26</v>
       </c>
@@ -4675,17 +5050,20 @@
     </row>
     <row r="127" spans="1:16">
       <c r="A127" s="11" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D127" s="11">
         <v>0.73</v>
       </c>
+      <c r="E127">
+        <v>0.99</v>
+      </c>
       <c r="H127">
         <v>0.32</v>
       </c>
@@ -4694,17 +5072,20 @@
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="11" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D128" s="11">
         <v>0.83</v>
       </c>
+      <c r="E128">
+        <v>0.92</v>
+      </c>
       <c r="H128">
         <v>0.11</v>
       </c>
@@ -4713,17 +5094,20 @@
     </row>
     <row r="129" spans="1:16">
       <c r="A129" s="11" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D129" s="11">
         <v>0.95</v>
       </c>
+      <c r="E129">
+        <v>0.96</v>
+      </c>
       <c r="H129">
         <v>0.65</v>
       </c>
@@ -4732,17 +5116,20 @@
     </row>
     <row r="130" spans="1:16">
       <c r="A130" s="11" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D130" s="11">
         <v>0.72</v>
       </c>
+      <c r="E130">
+        <v>0.99</v>
+      </c>
       <c r="H130">
         <v>0.28000000000000003</v>
       </c>
@@ -4751,17 +5138,20 @@
     </row>
     <row r="131" spans="1:16">
       <c r="A131" s="11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D131" s="11">
         <v>0.83</v>
       </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
       <c r="H131">
         <v>0.47</v>
       </c>
@@ -4770,17 +5160,20 @@
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D132" s="11">
         <v>0.75</v>
       </c>
+      <c r="E132">
+        <v>0.86</v>
+      </c>
       <c r="H132">
         <v>0.35</v>
       </c>
@@ -4789,17 +5182,20 @@
     </row>
     <row r="133" spans="1:16">
       <c r="A133" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D133" s="11">
         <v>0.78</v>
       </c>
+      <c r="E133">
+        <v>0.98</v>
+      </c>
       <c r="H133">
         <v>0.4</v>
       </c>
@@ -4808,17 +5204,20 @@
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D134" s="11">
         <v>0.81</v>
       </c>
+      <c r="E134">
+        <v>0.97</v>
+      </c>
       <c r="H134">
         <v>0.56000000000000005</v>
       </c>
@@ -4827,17 +5226,20 @@
     </row>
     <row r="135" spans="1:16">
       <c r="A135" s="11" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D135" s="11">
         <v>0.93</v>
       </c>
+      <c r="E135">
+        <v>0.99</v>
+      </c>
       <c r="H135">
         <v>0.63</v>
       </c>
@@ -4846,17 +5248,20 @@
     </row>
     <row r="136" spans="1:16">
       <c r="A136" s="11" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D136" s="11">
         <v>0.77</v>
       </c>
+      <c r="E136">
+        <v>0.93</v>
+      </c>
       <c r="H136">
         <v>0.42</v>
       </c>
@@ -4865,17 +5270,20 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D137" s="11">
         <v>0.9</v>
       </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
       <c r="H137">
         <v>0.39</v>
       </c>
@@ -4884,17 +5292,20 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" s="11" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D138" s="11">
         <v>0.87</v>
       </c>
+      <c r="E138">
+        <v>0.98</v>
+      </c>
       <c r="H138">
         <v>0.74</v>
       </c>
@@ -4903,17 +5314,20 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" s="11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D139" s="11">
         <v>0.88</v>
       </c>
+      <c r="E139">
+        <v>0.96</v>
+      </c>
       <c r="H139">
         <v>0.39</v>
       </c>
@@ -4922,17 +5336,20 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" s="11" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D140" s="11">
         <v>0.77</v>
       </c>
+      <c r="E140">
+        <v>0.92</v>
+      </c>
       <c r="H140">
         <v>0.51</v>
       </c>
@@ -4941,17 +5358,20 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" s="11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D141" s="11">
         <v>0.86</v>
       </c>
+      <c r="E141">
+        <v>0.82</v>
+      </c>
       <c r="H141">
         <v>0.42</v>
       </c>
@@ -4960,17 +5380,20 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" s="11" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D142" s="11">
         <v>0.68</v>
       </c>
+      <c r="E142">
+        <v>0.93</v>
+      </c>
       <c r="H142">
         <v>0</v>
       </c>
@@ -4979,17 +5402,20 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D143" s="11">
         <v>0.73</v>
       </c>
+      <c r="E143">
+        <v>0.92</v>
+      </c>
       <c r="H143">
         <v>0.16</v>
       </c>
@@ -4998,17 +5424,20 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" s="11" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D144" s="11">
         <v>0.9</v>
       </c>
+      <c r="E144">
+        <v>0.91</v>
+      </c>
       <c r="H144">
         <v>0.65</v>
       </c>
@@ -5017,17 +5446,20 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" s="11" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D145" s="11">
         <v>0.87</v>
       </c>
+      <c r="E145">
+        <v>1</v>
+      </c>
       <c r="H145">
         <v>0.4</v>
       </c>
@@ -5036,17 +5468,20 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" s="11" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D146" s="11">
         <v>0.94</v>
       </c>
+      <c r="E146">
+        <v>0.99</v>
+      </c>
       <c r="H146">
         <v>0.75</v>
       </c>
@@ -5055,17 +5490,20 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147" s="11" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D147" s="11">
         <v>0.91</v>
       </c>
+      <c r="E147">
+        <v>1</v>
+      </c>
       <c r="H147">
         <v>0.63</v>
       </c>
@@ -5074,17 +5512,20 @@
     </row>
     <row r="148" spans="1:16">
       <c r="A148" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D148" s="11">
         <v>0.82</v>
       </c>
+      <c r="E148">
+        <v>0.93</v>
+      </c>
       <c r="H148">
         <v>0.21</v>
       </c>
@@ -5093,17 +5534,20 @@
     </row>
     <row r="149" spans="1:16">
       <c r="A149" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D149" s="11">
         <v>0.79</v>
       </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
       <c r="H149">
         <v>0.25</v>
       </c>
@@ -5112,17 +5556,20 @@
     </row>
     <row r="150" spans="1:16">
       <c r="A150" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D150" s="11">
         <v>0.8</v>
       </c>
+      <c r="E150">
+        <v>0.94</v>
+      </c>
       <c r="H150">
         <v>0.3</v>
       </c>
@@ -5131,17 +5578,20 @@
     </row>
     <row r="151" spans="1:16">
       <c r="A151" s="11" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D151" s="11">
         <v>0.83</v>
       </c>
+      <c r="E151">
+        <v>0.91</v>
+      </c>
       <c r="H151">
         <v>0.63</v>
       </c>
@@ -5150,17 +5600,20 @@
     </row>
     <row r="152" spans="1:16">
       <c r="A152" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D152" s="11">
         <v>0.77</v>
       </c>
+      <c r="E152">
+        <v>0.97</v>
+      </c>
       <c r="H152">
         <v>0.86</v>
       </c>
@@ -5169,17 +5622,20 @@
     </row>
     <row r="153" spans="1:16">
       <c r="A153" s="11" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D153" s="11">
         <v>0.88</v>
       </c>
+      <c r="E153">
+        <v>0.81</v>
+      </c>
       <c r="H153">
         <v>0.47</v>
       </c>
@@ -5188,17 +5644,20 @@
     </row>
     <row r="154" spans="1:16">
       <c r="A154" s="11" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D154" s="11">
         <v>0.9</v>
       </c>
+      <c r="E154">
+        <v>0.94</v>
+      </c>
       <c r="H154">
         <v>0.49</v>
       </c>
@@ -5207,17 +5666,20 @@
     </row>
     <row r="155" spans="1:16">
       <c r="A155" s="11" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D155" s="11">
         <v>0.77</v>
       </c>
+      <c r="E155">
+        <v>0.97</v>
+      </c>
       <c r="H155">
         <v>0.44</v>
       </c>
@@ -5226,17 +5688,20 @@
     </row>
     <row r="156" spans="1:16">
       <c r="A156" s="11" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D156" s="11">
         <v>0.79</v>
       </c>
+      <c r="E156">
+        <v>0.89</v>
+      </c>
       <c r="H156">
         <v>0.65</v>
       </c>
@@ -5245,17 +5710,20 @@
     </row>
     <row r="157" spans="1:16">
       <c r="A157" s="11" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D157" s="11">
         <v>0.84</v>
       </c>
+      <c r="E157">
+        <v>0.99</v>
+      </c>
       <c r="H157">
         <v>0.6</v>
       </c>
@@ -5264,17 +5732,20 @@
     </row>
     <row r="158" spans="1:16">
       <c r="A158" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D158" s="11">
         <v>0.88</v>
       </c>
+      <c r="E158">
+        <v>0.86</v>
+      </c>
       <c r="H158">
         <v>0.46</v>
       </c>
@@ -5283,17 +5754,20 @@
     </row>
     <row r="159" spans="1:16">
       <c r="A159" s="11" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D159" s="11">
         <v>0.8</v>
       </c>
+      <c r="E159">
+        <v>0.99</v>
+      </c>
       <c r="H159">
         <v>0.42</v>
       </c>
@@ -5302,17 +5776,20 @@
     </row>
     <row r="160" spans="1:16">
       <c r="A160" s="11" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D160" s="11">
         <v>0.66</v>
       </c>
+      <c r="E160">
+        <v>0.97</v>
+      </c>
       <c r="H160">
         <v>0.57999999999999996</v>
       </c>
@@ -5321,17 +5798,20 @@
     </row>
     <row r="161" spans="1:16">
       <c r="A161" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D161" s="11">
         <v>0.88</v>
       </c>
+      <c r="E161">
+        <v>0.92</v>
+      </c>
       <c r="H161">
         <v>0.68</v>
       </c>
@@ -5340,17 +5820,20 @@
     </row>
     <row r="162" spans="1:16">
       <c r="A162" s="11" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D162" s="11">
         <v>0.94</v>
       </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
       <c r="H162">
         <v>0.51</v>
       </c>
@@ -5359,17 +5842,20 @@
     </row>
     <row r="163" spans="1:16">
       <c r="A163" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D163" s="11">
         <v>0.95</v>
       </c>
+      <c r="E163">
+        <v>0.98</v>
+      </c>
       <c r="H163">
         <v>0.33</v>
       </c>
@@ -5378,17 +5864,20 @@
     </row>
     <row r="164" spans="1:16">
       <c r="A164" s="11" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D164" s="11">
         <v>0.79</v>
       </c>
+      <c r="E164">
+        <v>0.97</v>
+      </c>
       <c r="H164">
         <v>0.18</v>
       </c>
@@ -5397,17 +5886,20 @@
     </row>
     <row r="165" spans="1:16">
       <c r="A165" s="11" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D165" s="11">
         <v>0.9</v>
       </c>
+      <c r="E165">
+        <v>0.87</v>
+      </c>
       <c r="H165">
         <v>0.47</v>
       </c>
@@ -5416,17 +5908,20 @@
     </row>
     <row r="166" spans="1:16">
       <c r="A166" s="11" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D166" s="11">
         <v>0.82</v>
       </c>
+      <c r="E166">
+        <v>0.97</v>
+      </c>
       <c r="H166">
         <v>0.63</v>
       </c>
@@ -5435,17 +5930,20 @@
     </row>
     <row r="167" spans="1:16">
       <c r="A167" s="11" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D167" s="11">
         <v>0.75</v>
       </c>
+      <c r="E167">
+        <v>0.98</v>
+      </c>
       <c r="H167">
         <v>0.56000000000000005</v>
       </c>
@@ -5454,17 +5952,20 @@
     </row>
     <row r="168" spans="1:16">
       <c r="A168" s="11" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D168" s="11">
         <v>0.8</v>
       </c>
+      <c r="E168">
+        <v>0.96</v>
+      </c>
       <c r="H168">
         <v>0.54</v>
       </c>
@@ -5473,17 +5974,20 @@
     </row>
     <row r="169" spans="1:16">
       <c r="A169" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D169" s="11">
         <v>0.85</v>
       </c>
+      <c r="E169">
+        <v>0.99</v>
+      </c>
       <c r="H169">
         <v>0.3</v>
       </c>
@@ -5492,17 +5996,20 @@
     </row>
     <row r="170" spans="1:16">
       <c r="A170" s="11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D170" s="11">
         <v>0.82</v>
       </c>
+      <c r="E170">
+        <v>0.98</v>
+      </c>
       <c r="H170">
         <v>0.25</v>
       </c>
@@ -5511,17 +6018,20 @@
     </row>
     <row r="171" spans="1:16">
       <c r="A171" s="11" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D171" s="11">
         <v>0.9</v>
       </c>
+      <c r="E171">
+        <v>1</v>
+      </c>
       <c r="H171">
         <v>0.39</v>
       </c>
@@ -5530,17 +6040,20 @@
     </row>
     <row r="172" spans="1:16">
       <c r="A172" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C172" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D172" s="4">
         <v>0</v>
       </c>
+      <c r="E172">
+        <v>0.87</v>
+      </c>
       <c r="H172">
         <v>0.35</v>
       </c>
@@ -5549,17 +6062,20 @@
     </row>
     <row r="173" spans="1:16">
       <c r="A173" s="11" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B173" s="11" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D173" s="11">
         <v>0.86</v>
       </c>
+      <c r="E173">
+        <v>0.93</v>
+      </c>
       <c r="H173">
         <v>0.35</v>
       </c>
@@ -5568,17 +6084,20 @@
     </row>
     <row r="174" spans="1:16">
       <c r="A174" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C174" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D174" s="4">
         <v>0</v>
       </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
       <c r="H174">
         <v>0.33</v>
       </c>
@@ -5587,17 +6106,20 @@
     </row>
     <row r="175" spans="1:16">
       <c r="A175" s="11" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B175" s="11" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D175" s="11">
         <v>0.69</v>
       </c>
+      <c r="E175">
+        <v>0.89</v>
+      </c>
       <c r="H175">
         <v>0.12</v>
       </c>
@@ -5606,17 +6128,20 @@
     </row>
     <row r="176" spans="1:16">
       <c r="A176" s="11" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B176" s="11" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D176" s="11">
         <v>0.77</v>
       </c>
+      <c r="E176">
+        <v>0.97</v>
+      </c>
       <c r="H176">
         <v>0.46</v>
       </c>
@@ -5625,17 +6150,20 @@
     </row>
     <row r="177" spans="1:16">
       <c r="A177" s="11" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B177" s="11" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D177" s="11">
         <v>0.73</v>
       </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
       <c r="H177">
         <v>0.19</v>
       </c>
@@ -5644,17 +6172,20 @@
     </row>
     <row r="178" spans="1:16">
       <c r="A178" s="11" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D178" s="11">
         <v>0.86</v>
       </c>
+      <c r="E178">
+        <v>0.99</v>
+      </c>
       <c r="H178">
         <v>0.42</v>
       </c>
@@ -5663,17 +6194,20 @@
     </row>
     <row r="179" spans="1:16">
       <c r="A179" s="11" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B179" s="11" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D179" s="11">
         <v>0.68</v>
       </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
       <c r="H179">
         <v>0.61</v>
       </c>
@@ -5682,17 +6216,20 @@
     </row>
     <row r="180" spans="1:16">
       <c r="A180" s="11" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D180" s="11">
         <v>0.82</v>
       </c>
+      <c r="E180">
+        <v>0.91</v>
+      </c>
       <c r="H180">
         <v>0.53</v>
       </c>
@@ -5701,17 +6238,20 @@
     </row>
     <row r="181" spans="1:16">
       <c r="A181" s="11" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D181" s="11">
         <v>0.61</v>
       </c>
+      <c r="E181">
+        <v>0.98</v>
+      </c>
       <c r="H181">
         <v>0.35</v>
       </c>
@@ -5720,17 +6260,20 @@
     </row>
     <row r="182" spans="1:16">
       <c r="A182" s="11" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D182" s="11">
         <v>0.75</v>
       </c>
+      <c r="E182">
+        <v>0.89</v>
+      </c>
       <c r="H182">
         <v>0.32</v>
       </c>
@@ -5739,17 +6282,20 @@
     </row>
     <row r="183" spans="1:16">
       <c r="A183" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B183" s="11" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D183" s="11">
         <v>0.87</v>
       </c>
+      <c r="E183">
+        <v>0.97</v>
+      </c>
       <c r="H183">
         <v>0.26</v>
       </c>
@@ -5758,17 +6304,20 @@
     </row>
     <row r="184" spans="1:16">
       <c r="A184" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C184" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D184" s="4">
         <v>0</v>
       </c>
+      <c r="E184">
+        <v>0.98</v>
+      </c>
       <c r="H184">
         <v>0.19</v>
       </c>
@@ -5777,17 +6326,20 @@
     </row>
     <row r="185" spans="1:16">
       <c r="A185" s="11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B185" s="11" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D185" s="11">
         <v>0.71</v>
       </c>
+      <c r="E185">
+        <v>0.97</v>
+      </c>
       <c r="H185">
         <v>0.35</v>
       </c>
@@ -5796,17 +6348,20 @@
     </row>
     <row r="186" spans="1:16">
       <c r="A186" s="11" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D186" s="11">
         <v>0.92</v>
       </c>
+      <c r="E186">
+        <v>0.97</v>
+      </c>
       <c r="H186">
         <v>0.63</v>
       </c>
@@ -5815,17 +6370,20 @@
     </row>
     <row r="187" spans="1:16">
       <c r="A187" s="11" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D187" s="11">
         <v>0.8</v>
       </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
       <c r="H187">
         <v>0.39</v>
       </c>
@@ -5834,17 +6392,20 @@
     </row>
     <row r="188" spans="1:16">
       <c r="A188" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D188" s="11">
         <v>0.75</v>
       </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
       <c r="H188">
         <v>0.68</v>
       </c>
@@ -5853,17 +6414,20 @@
     </row>
     <row r="189" spans="1:16">
       <c r="A189" s="11" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D189" s="11">
         <v>0.87</v>
       </c>
+      <c r="E189">
+        <v>0.96</v>
+      </c>
       <c r="H189">
         <v>0.42</v>
       </c>
@@ -5872,17 +6436,20 @@
     </row>
     <row r="190" spans="1:16">
       <c r="A190" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D190" s="11">
         <v>0.81</v>
       </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
       <c r="H190">
         <v>0.57999999999999996</v>
       </c>
@@ -5891,17 +6458,20 @@
     </row>
     <row r="191" spans="1:16">
       <c r="A191" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D191" s="11">
         <v>0.84</v>
       </c>
+      <c r="E191">
+        <v>0.98</v>
+      </c>
       <c r="H191">
         <v>0.6</v>
       </c>
@@ -5910,17 +6480,20 @@
     </row>
     <row r="192" spans="1:16">
       <c r="A192" s="11" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D192" s="11">
         <v>0.64</v>
       </c>
+      <c r="E192">
+        <v>0.96</v>
+      </c>
       <c r="H192">
         <v>0.04</v>
       </c>
@@ -5929,17 +6502,20 @@
     </row>
     <row r="193" spans="1:16">
       <c r="A193" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C193" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D193" s="4">
         <v>0</v>
       </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
       <c r="H193">
         <v>0.26</v>
       </c>
@@ -5948,17 +6524,20 @@
     </row>
     <row r="194" spans="1:16">
       <c r="A194" s="11" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D194" s="11">
         <v>0.78</v>
       </c>
+      <c r="E194">
+        <v>0.97</v>
+      </c>
       <c r="H194">
         <v>0.54</v>
       </c>
@@ -5967,17 +6546,20 @@
     </row>
     <row r="195" spans="1:16">
       <c r="A195" s="11" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B195" s="11" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D195" s="11">
         <v>0.91</v>
       </c>
+      <c r="E195">
+        <v>0.94</v>
+      </c>
       <c r="H195">
         <v>0.51</v>
       </c>
@@ -5986,17 +6568,20 @@
     </row>
     <row r="196" spans="1:16">
       <c r="A196" s="11" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D196" s="11">
         <v>0.81</v>
       </c>
+      <c r="E196">
+        <v>0.98</v>
+      </c>
       <c r="H196">
         <v>0.46</v>
       </c>
@@ -6005,17 +6590,20 @@
     </row>
     <row r="197" spans="1:16">
       <c r="A197" s="11" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B197" s="11" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D197" s="11">
         <v>0.84</v>
       </c>
+      <c r="E197">
+        <v>0.99</v>
+      </c>
       <c r="H197">
         <v>0.67</v>
       </c>
@@ -6024,17 +6612,20 @@
     </row>
     <row r="198" spans="1:16">
       <c r="A198" s="11" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D198" s="11">
         <v>0.84</v>
       </c>
+      <c r="E198">
+        <v>1</v>
+      </c>
       <c r="H198">
         <v>0.67</v>
       </c>
@@ -6043,17 +6634,20 @@
     </row>
     <row r="199" spans="1:16">
       <c r="A199" s="11" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D199" s="11">
         <v>0.91</v>
       </c>
+      <c r="E199">
+        <v>0.93</v>
+      </c>
       <c r="H199">
         <v>0.37</v>
       </c>
@@ -6062,17 +6656,20 @@
     </row>
     <row r="200" spans="1:16">
       <c r="A200" s="11" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B200" s="11" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D200" s="11">
         <v>0.83</v>
       </c>
+      <c r="E200">
+        <v>0.98</v>
+      </c>
       <c r="H200">
         <v>0.6</v>
       </c>
@@ -6081,17 +6678,20 @@
     </row>
     <row r="201" spans="1:16">
       <c r="A201" s="11" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D201" s="11">
         <v>0.84</v>
       </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
       <c r="H201">
         <v>0.32</v>
       </c>
@@ -6100,17 +6700,20 @@
     </row>
     <row r="202" spans="1:16">
       <c r="A202" s="11" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D202" s="11">
         <v>0.85</v>
       </c>
+      <c r="E202">
+        <v>0.99</v>
+      </c>
       <c r="H202">
         <v>0.37</v>
       </c>
@@ -6119,17 +6722,20 @@
     </row>
     <row r="203" spans="1:16">
       <c r="A203" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C203" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D203" s="4">
         <v>0</v>
       </c>
+      <c r="E203">
+        <v>1</v>
+      </c>
       <c r="H203">
         <v>0.46</v>
       </c>
@@ -6138,17 +6744,20 @@
     </row>
     <row r="204" spans="1:16">
       <c r="A204" s="11" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B204" s="11" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D204" s="11">
         <v>0.88</v>
       </c>
+      <c r="E204">
+        <v>0.82</v>
+      </c>
       <c r="H204">
         <v>0.3</v>
       </c>
@@ -6157,17 +6766,20 @@
     </row>
     <row r="205" spans="1:16">
       <c r="A205" s="11" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D205" s="11">
         <v>0.82</v>
       </c>
+      <c r="E205">
+        <v>0.97</v>
+      </c>
       <c r="H205">
         <v>0.42</v>
       </c>
@@ -6176,17 +6788,20 @@
     </row>
     <row r="206" spans="1:16">
       <c r="A206" s="11" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D206" s="11">
         <v>0.76</v>
       </c>
+      <c r="E206">
+        <v>0.93</v>
+      </c>
       <c r="H206">
         <v>0.39</v>
       </c>
@@ -6195,17 +6810,20 @@
     </row>
     <row r="207" spans="1:16">
       <c r="A207" s="11" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B207" s="11" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D207" s="11">
         <v>0.59</v>
       </c>
+      <c r="E207">
+        <v>0.93</v>
+      </c>
       <c r="H207">
         <v>0.65</v>
       </c>
@@ -6214,17 +6832,20 @@
     </row>
     <row r="208" spans="1:16">
       <c r="A208" s="11" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D208" s="11">
         <v>0.79</v>
       </c>
+      <c r="E208">
+        <v>0.93</v>
+      </c>
       <c r="H208">
         <v>0.44</v>
       </c>
@@ -6233,17 +6854,20 @@
     </row>
     <row r="209" spans="1:16">
       <c r="A209" s="11" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D209" s="11">
         <v>0.77</v>
       </c>
+      <c r="E209">
+        <v>0.98</v>
+      </c>
       <c r="H209">
         <v>0.75</v>
       </c>
@@ -6252,17 +6876,20 @@
     </row>
     <row r="210" spans="1:16">
       <c r="A210" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C210" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D210" s="4">
         <v>0</v>
       </c>
+      <c r="E210">
+        <v>0.8</v>
+      </c>
       <c r="H210">
         <v>0.05</v>
       </c>
@@ -6271,17 +6898,20 @@
     </row>
     <row r="211" spans="1:16">
       <c r="A211" s="11" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C211" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D211" s="11">
         <v>0.75</v>
       </c>
+      <c r="E211">
+        <v>0.98</v>
+      </c>
       <c r="H211">
         <v>0.53</v>
       </c>
@@ -6290,17 +6920,20 @@
     </row>
     <row r="212" spans="1:16">
       <c r="A212" s="11" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C212" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D212" s="11">
         <v>0.79</v>
       </c>
+      <c r="E212">
+        <v>0.92</v>
+      </c>
       <c r="H212">
         <v>0.32</v>
       </c>
@@ -6309,17 +6942,20 @@
     </row>
     <row r="213" spans="1:16">
       <c r="A213" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C213" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D213" s="4">
         <v>0</v>
       </c>
+      <c r="E213">
+        <v>0.97</v>
+      </c>
       <c r="H213">
         <v>0.44</v>
       </c>
@@ -6328,17 +6964,20 @@
     </row>
     <row r="214" spans="1:16">
       <c r="A214" s="11" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B214" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C214" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D214" s="11">
         <v>0.74</v>
       </c>
+      <c r="E214">
+        <v>1</v>
+      </c>
       <c r="H214">
         <v>0.68</v>
       </c>
@@ -6347,17 +6986,20 @@
     </row>
     <row r="215" spans="1:16">
       <c r="A215" s="11" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B215" s="11" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C215" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D215" s="11">
         <v>0.62</v>
       </c>
+      <c r="E215">
+        <v>0.92</v>
+      </c>
       <c r="H215">
         <v>0.56000000000000005</v>
       </c>
@@ -6366,17 +7008,20 @@
     </row>
     <row r="216" spans="1:16">
       <c r="A216" s="11" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C216" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D216" s="11">
         <v>0.94</v>
       </c>
+      <c r="E216">
+        <v>0.99</v>
+      </c>
       <c r="H216">
         <v>0.65</v>
       </c>
@@ -6385,17 +7030,20 @@
     </row>
     <row r="217" spans="1:16">
       <c r="A217" s="11" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B217" s="11" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C217" s="11" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D217" s="11">
         <v>0.75</v>
       </c>
+      <c r="E217">
+        <v>0.9</v>
+      </c>
       <c r="H217">
         <v>0.79</v>
       </c>
@@ -6404,17 +7052,20 @@
     </row>
     <row r="218" spans="1:16">
       <c r="A218" s="11" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B218" s="11" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C218" s="11" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D218" s="11">
         <v>0.61</v>
       </c>
+      <c r="E218">
+        <v>0.91</v>
+      </c>
       <c r="H218">
         <v>0.32</v>
       </c>
@@ -6423,17 +7074,20 @@
     </row>
     <row r="219" spans="1:16">
       <c r="A219" s="11" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D219" s="11">
         <v>0.69</v>
       </c>
+      <c r="E219">
+        <v>0.79</v>
+      </c>
       <c r="H219">
         <v>0.54</v>
       </c>
@@ -6442,17 +7096,20 @@
     </row>
     <row r="220" spans="1:16">
       <c r="A220" s="11" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B220" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D220" s="11">
         <v>0.67</v>
       </c>
+      <c r="E220">
+        <v>0.97</v>
+      </c>
       <c r="H220">
         <v>0.11</v>
       </c>
@@ -6461,17 +7118,20 @@
     </row>
     <row r="221" spans="1:16">
       <c r="A221" s="11" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B221" s="11" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C221" s="11" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D221" s="11">
         <v>0.71</v>
       </c>
+      <c r="E221">
+        <v>0.98</v>
+      </c>
       <c r="H221">
         <v>0.54</v>
       </c>
@@ -6480,17 +7140,20 @@
     </row>
     <row r="222" spans="1:16">
       <c r="A222" s="11" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B222" s="11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C222" s="11" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D222" s="11">
         <v>0.89</v>
       </c>
+      <c r="E222">
+        <v>0.97</v>
+      </c>
       <c r="H222">
         <v>0.61</v>
       </c>
@@ -6499,17 +7162,20 @@
     </row>
     <row r="223" spans="1:16">
       <c r="A223" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C223" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D223" s="4">
         <v>0</v>
       </c>
+      <c r="E223">
+        <v>0.88</v>
+      </c>
       <c r="H223">
         <v>0.33</v>
       </c>
@@ -6518,17 +7184,20 @@
     </row>
     <row r="224" spans="1:16">
       <c r="A224" s="11" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B224" s="11" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C224" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D224" s="11">
         <v>0.79</v>
       </c>
+      <c r="E224">
+        <v>0.89</v>
+      </c>
       <c r="H224">
         <v>0.26</v>
       </c>
@@ -6537,17 +7206,20 @@
     </row>
     <row r="225" spans="1:16">
       <c r="A225" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B225" s="11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C225" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D225" s="11">
         <v>0.66</v>
       </c>
+      <c r="E225">
+        <v>0.87</v>
+      </c>
       <c r="H225">
         <v>0.16</v>
       </c>
@@ -6556,17 +7228,20 @@
     </row>
     <row r="226" spans="1:16">
       <c r="A226" s="11" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B226" s="11" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C226" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D226" s="11">
         <v>0.69</v>
       </c>
+      <c r="E226">
+        <v>0.88</v>
+      </c>
       <c r="H226">
         <v>0.28000000000000003</v>
       </c>
@@ -6575,17 +7250,20 @@
     </row>
     <row r="227" spans="1:16">
       <c r="A227" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C227" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D227" s="4">
         <v>0</v>
       </c>
+      <c r="E227">
+        <v>0.98</v>
+      </c>
       <c r="H227">
         <v>0.16</v>
       </c>
@@ -6593,17 +7271,20 @@
     </row>
     <row r="228" spans="1:16">
       <c r="A228" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C228" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D228" s="4">
         <v>0</v>
       </c>
+      <c r="E228">
+        <v>0.94</v>
+      </c>
       <c r="H228">
         <v>0.26</v>
       </c>
@@ -6611,17 +7292,20 @@
     </row>
     <row r="229" spans="1:16">
       <c r="A229" s="11" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B229" s="11" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C229" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D229" s="11">
         <v>0.83</v>
       </c>
+      <c r="E229">
+        <v>0.9</v>
+      </c>
       <c r="H229">
         <v>0.63</v>
       </c>
@@ -6630,17 +7314,20 @@
     </row>
     <row r="230" spans="1:16">
       <c r="A230" s="11" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B230" s="11" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C230" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D230" s="11">
         <v>0.79</v>
       </c>
+      <c r="E230">
+        <v>0.99</v>
+      </c>
       <c r="H230">
         <v>0.26</v>
       </c>
@@ -6649,17 +7336,20 @@
     </row>
     <row r="231" spans="1:16">
       <c r="A231" s="11" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B231" s="11" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C231" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D231" s="11">
         <v>0.81</v>
       </c>
+      <c r="E231">
+        <v>0.92</v>
+      </c>
       <c r="H231">
         <v>0.67</v>
       </c>
@@ -6668,17 +7358,20 @@
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="11" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B232" s="11" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C232" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D232" s="11">
         <v>0.74</v>
       </c>
+      <c r="E232">
+        <v>0.94</v>
+      </c>
       <c r="H232">
         <v>0.37</v>
       </c>
@@ -6687,17 +7380,20 @@
     </row>
     <row r="233" spans="1:16">
       <c r="A233" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C233" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D233" s="4">
         <v>0</v>
       </c>
+      <c r="E233">
+        <v>0.91</v>
+      </c>
       <c r="H233">
         <v>0.35</v>
       </c>
@@ -6705,17 +7401,20 @@
     </row>
     <row r="234" spans="1:16">
       <c r="A234" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B234" s="11" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C234" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D234" s="11">
         <v>0.75</v>
       </c>
+      <c r="E234">
+        <v>1</v>
+      </c>
       <c r="H234">
         <v>0.44</v>
       </c>
@@ -6724,17 +7423,20 @@
     </row>
     <row r="235" spans="1:16">
       <c r="A235" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B235" s="11" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C235" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D235" s="11">
         <v>0.65</v>
       </c>
+      <c r="E235">
+        <v>1</v>
+      </c>
       <c r="H235">
         <v>0.63</v>
       </c>
@@ -6743,17 +7445,20 @@
     </row>
     <row r="236" spans="1:16">
       <c r="A236" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C236" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D236" s="4">
         <v>0</v>
       </c>
+      <c r="E236">
+        <v>0.9</v>
+      </c>
       <c r="H236">
         <v>0.54</v>
       </c>
@@ -6761,17 +7466,20 @@
     </row>
     <row r="237" spans="1:16">
       <c r="A237" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C237" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D237" s="4">
         <v>0</v>
       </c>
+      <c r="E237">
+        <v>0.9</v>
+      </c>
       <c r="H237">
         <v>0.42</v>
       </c>
@@ -6779,17 +7487,20 @@
     </row>
     <row r="238" spans="1:16">
       <c r="A238" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C238" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D238" s="4">
         <v>0</v>
       </c>
+      <c r="E238">
+        <v>1</v>
+      </c>
       <c r="H238">
         <v>0.49</v>
       </c>
@@ -6797,17 +7508,20 @@
     </row>
     <row r="239" spans="1:16">
       <c r="A239" s="11" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B239" s="11" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C239" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D239" s="11">
         <v>0.87</v>
       </c>
+      <c r="E239">
+        <v>0.84</v>
+      </c>
       <c r="H239">
         <v>0.47</v>
       </c>
@@ -6816,16 +7530,19 @@
     </row>
     <row r="240" spans="1:16">
       <c r="A240" s="11" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B240" s="11" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C240" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D240" s="11">
         <v>0.7</v>
+      </c>
+      <c r="E240">
+        <v>0.89</v>
       </c>
       <c r="H240">
         <v>0.19</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE39990-032B-5147-BB58-22B5AA25D7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E85635-7746-6143-911C-92B52909E763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3338,6 +3338,9 @@
         <v>0.75</v>
       </c>
       <c r="I50" s="5"/>
+      <c r="L50">
+        <v>0.63</v>
+      </c>
       <c r="P50" s="6"/>
     </row>
     <row r="51" spans="1:16">
@@ -3379,7 +3382,7 @@
         <v>0.85</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="H52">
         <v>0.54</v>
@@ -3410,6 +3413,9 @@
         <v>0.6</v>
       </c>
       <c r="I53" s="5"/>
+      <c r="L53">
+        <v>0.79</v>
+      </c>
       <c r="P53" s="6"/>
     </row>
     <row r="54" spans="1:16">
@@ -3432,6 +3438,9 @@
         <v>0.33</v>
       </c>
       <c r="I54" s="5"/>
+      <c r="L54">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P54" s="6"/>
     </row>
     <row r="55" spans="1:16">
@@ -3504,6 +3513,9 @@
         <v>0.51</v>
       </c>
       <c r="I57" s="4"/>
+      <c r="L57">
+        <v>0.37</v>
+      </c>
       <c r="P57" s="6"/>
     </row>
     <row r="58" spans="1:16">
@@ -3598,6 +3610,9 @@
         <v>0.46</v>
       </c>
       <c r="I61" s="4"/>
+      <c r="L61">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P61" s="6"/>
     </row>
     <row r="62" spans="1:16">
@@ -3645,6 +3660,9 @@
         <v>0.63</v>
       </c>
       <c r="I63" s="4"/>
+      <c r="L63">
+        <v>0.63</v>
+      </c>
       <c r="P63" s="6"/>
     </row>
     <row r="64" spans="1:16">
@@ -3667,6 +3685,9 @@
         <v>0.37</v>
       </c>
       <c r="I64" s="4"/>
+      <c r="L64">
+        <v>0.37</v>
+      </c>
       <c r="P64" s="6"/>
     </row>
     <row r="65" spans="1:16">
@@ -3689,6 +3710,9 @@
         <v>0.53</v>
       </c>
       <c r="I65" s="4"/>
+      <c r="L65">
+        <v>0.79</v>
+      </c>
       <c r="P65" s="6"/>
     </row>
     <row r="66" spans="1:16">
@@ -3711,6 +3735,9 @@
         <v>0.35</v>
       </c>
       <c r="I66" s="4"/>
+      <c r="L66">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P66" s="6"/>
     </row>
     <row r="67" spans="1:16">
@@ -3758,6 +3785,9 @@
         <v>0.6</v>
       </c>
       <c r="I68" s="4"/>
+      <c r="L68">
+        <v>0.79</v>
+      </c>
       <c r="P68" s="6"/>
     </row>
     <row r="69" spans="1:16">
@@ -3805,6 +3835,9 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="I70" s="4"/>
+      <c r="L70">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P70" s="6"/>
     </row>
     <row r="71" spans="1:16">
@@ -3827,6 +3860,9 @@
         <v>0.35</v>
       </c>
       <c r="I71" s="4"/>
+      <c r="L71">
+        <v>0.37</v>
+      </c>
       <c r="P71" s="6"/>
     </row>
     <row r="72" spans="1:16">
@@ -3849,6 +3885,9 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="I72" s="4"/>
+      <c r="L72">
+        <v>0.79</v>
+      </c>
       <c r="P72" s="6"/>
     </row>
     <row r="73" spans="1:16">
@@ -3940,6 +3979,9 @@
         <v>0.61</v>
       </c>
       <c r="I76" s="4"/>
+      <c r="L76">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P76" s="6"/>
     </row>
     <row r="77" spans="1:16">
@@ -4034,6 +4076,9 @@
         <v>0.47</v>
       </c>
       <c r="I80" s="4"/>
+      <c r="L80">
+        <v>0.63</v>
+      </c>
       <c r="P80" s="6"/>
     </row>
     <row r="81" spans="1:16">
@@ -4056,6 +4101,9 @@
         <v>0.65</v>
       </c>
       <c r="I81" s="4"/>
+      <c r="L81">
+        <v>0.37</v>
+      </c>
       <c r="P81" s="6"/>
     </row>
     <row r="82" spans="1:16">
@@ -4078,6 +4126,9 @@
         <v>0.39</v>
       </c>
       <c r="I82" s="4"/>
+      <c r="L82">
+        <v>0.37</v>
+      </c>
       <c r="P82" s="6"/>
     </row>
     <row r="83" spans="1:16">
@@ -4100,6 +4151,9 @@
         <v>0.54</v>
       </c>
       <c r="I83" s="4"/>
+      <c r="L83">
+        <v>0.63</v>
+      </c>
       <c r="P83" s="6"/>
     </row>
     <row r="84" spans="1:16">
@@ -4122,6 +4176,9 @@
         <v>0.79</v>
       </c>
       <c r="I84" s="4"/>
+      <c r="L84">
+        <v>0.79</v>
+      </c>
       <c r="P84" s="6"/>
     </row>
     <row r="85" spans="1:16">
@@ -4144,6 +4201,9 @@
         <v>0.63</v>
       </c>
       <c r="I85" s="4"/>
+      <c r="L85">
+        <v>0.63</v>
+      </c>
       <c r="P85" s="6"/>
     </row>
     <row r="86" spans="1:16">
@@ -4166,6 +4226,9 @@
         <v>0.61</v>
       </c>
       <c r="I86" s="4"/>
+      <c r="L86">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P86" s="6"/>
     </row>
     <row r="87" spans="1:16">
@@ -4210,6 +4273,9 @@
         <v>0.6</v>
       </c>
       <c r="I88" s="4"/>
+      <c r="L88">
+        <v>0.79</v>
+      </c>
       <c r="P88" s="6"/>
     </row>
     <row r="89" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E85635-7746-6143-911C-92B52909E763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81216F93-6E6E-314A-989A-24BF904A7814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2150,7 +2150,7 @@
         <v>0.99</v>
       </c>
       <c r="H2">
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
       <c r="I2" s="5"/>
       <c r="L2">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81216F93-6E6E-314A-989A-24BF904A7814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4AFABB-721E-FB44-BDDC-60821C54F4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2527,7 +2527,9 @@
       <c r="H17">
         <v>0.37</v>
       </c>
-      <c r="I17" s="5"/>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
       <c r="L17">
         <v>0.48</v>
       </c>
@@ -2577,7 +2579,9 @@
       <c r="H19">
         <v>0.53</v>
       </c>
-      <c r="I19" s="4"/>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
       <c r="P19" s="18"/>
     </row>
     <row r="20" spans="1:16">
@@ -2599,7 +2603,9 @@
       <c r="H20">
         <v>0.54</v>
       </c>
-      <c r="I20" s="5"/>
+      <c r="I20" s="5">
+        <v>0</v>
+      </c>
       <c r="L20">
         <v>0.48</v>
       </c>
@@ -2849,7 +2855,9 @@
       <c r="H30">
         <v>0.35</v>
       </c>
-      <c r="I30" s="5"/>
+      <c r="I30" s="5">
+        <v>0</v>
+      </c>
       <c r="L30">
         <v>0.48</v>
       </c>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4AFABB-721E-FB44-BDDC-60821C54F4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3643E72E-2D31-FC42-AD22-7E0C60D9C0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="497">
   <si>
     <t>Surname</t>
   </si>
@@ -1524,6 +1524,9 @@
   </si>
   <si>
     <t>T_4</t>
+  </si>
+  <si>
+    <t>]</t>
   </si>
 </sst>
 </file>
@@ -2152,7 +2155,9 @@
       <c r="H2">
         <v>0.89</v>
       </c>
-      <c r="I2" s="5"/>
+      <c r="I2" s="5">
+        <v>0.7</v>
+      </c>
       <c r="L2">
         <v>0.48</v>
       </c>
@@ -2177,7 +2182,9 @@
       <c r="H3">
         <v>0.39</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="5">
+        <v>0.22</v>
+      </c>
       <c r="L3">
         <v>0.68</v>
       </c>
@@ -2202,7 +2209,9 @@
       <c r="H4">
         <v>0.39</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="5">
+        <v>0.31</v>
+      </c>
       <c r="L4">
         <v>0.48</v>
       </c>
@@ -2227,7 +2236,9 @@
       <c r="H5">
         <v>0.54</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="5">
+        <v>0.16</v>
+      </c>
       <c r="L5">
         <v>0.48</v>
       </c>
@@ -2277,7 +2288,9 @@
       <c r="H7">
         <v>0.42</v>
       </c>
-      <c r="I7" s="5"/>
+      <c r="I7" s="5">
+        <v>0.25</v>
+      </c>
       <c r="L7">
         <v>0.48</v>
       </c>
@@ -2327,7 +2340,9 @@
       <c r="H9">
         <v>0.47</v>
       </c>
-      <c r="I9" s="5"/>
+      <c r="I9" s="5">
+        <v>0.18</v>
+      </c>
       <c r="L9">
         <v>0.68</v>
       </c>
@@ -2452,7 +2467,9 @@
       <c r="H14">
         <v>0.4</v>
       </c>
-      <c r="I14" s="5"/>
+      <c r="I14" s="5">
+        <v>0.22</v>
+      </c>
       <c r="L14">
         <v>0.48</v>
       </c>
@@ -2502,7 +2519,9 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="5"/>
+      <c r="I16" s="5">
+        <v>0.16</v>
+      </c>
       <c r="L16">
         <v>0.48</v>
       </c>
@@ -2554,7 +2573,9 @@
       <c r="H18">
         <v>0.44</v>
       </c>
-      <c r="I18" s="5"/>
+      <c r="I18" s="5">
+        <v>0.03</v>
+      </c>
       <c r="L18">
         <v>0.48</v>
       </c>
@@ -2655,7 +2676,9 @@
       <c r="H22">
         <v>0.33</v>
       </c>
-      <c r="I22" s="5"/>
+      <c r="I22" s="5">
+        <v>0.16</v>
+      </c>
       <c r="L22">
         <v>0.68</v>
       </c>
@@ -2755,7 +2778,9 @@
       <c r="H26">
         <v>0.53</v>
       </c>
-      <c r="I26" s="5"/>
+      <c r="I26" s="5">
+        <v>0.46</v>
+      </c>
       <c r="L26">
         <v>0.48</v>
       </c>
@@ -2780,7 +2805,9 @@
       <c r="H27">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I27" s="5"/>
+      <c r="I27" s="5" t="s">
+        <v>496</v>
+      </c>
       <c r="L27">
         <v>0.8</v>
       </c>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3643E72E-2D31-FC42-AD22-7E0C60D9C0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BD23E0-08AC-E24B-92E3-8260C2E2218E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="496">
   <si>
     <t>Surname</t>
   </si>
@@ -1524,9 +1524,6 @@
   </si>
   <si>
     <t>T_4</t>
-  </si>
-  <si>
-    <t>]</t>
   </si>
 </sst>
 </file>
@@ -2263,7 +2260,9 @@
       <c r="H6">
         <v>0.53</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5">
+        <v>0.25</v>
+      </c>
       <c r="L6">
         <v>0.48</v>
       </c>
@@ -2315,7 +2314,9 @@
       <c r="H8">
         <v>0.11</v>
       </c>
-      <c r="I8" s="5"/>
+      <c r="I8" s="5">
+        <v>0.21</v>
+      </c>
       <c r="L8">
         <v>0.8</v>
       </c>
@@ -2367,7 +2368,9 @@
       <c r="H10" t="s">
         <v>482</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="5">
+        <v>0.48</v>
+      </c>
       <c r="L10">
         <v>0.48</v>
       </c>
@@ -2392,7 +2395,9 @@
       <c r="H11">
         <v>0.16</v>
       </c>
-      <c r="I11" s="5"/>
+      <c r="I11" s="5">
+        <v>0.31</v>
+      </c>
       <c r="L11">
         <v>0.48</v>
       </c>
@@ -2417,7 +2422,9 @@
       <c r="H12">
         <v>0.44</v>
       </c>
-      <c r="I12" s="5"/>
+      <c r="I12" s="5">
+        <v>0.33</v>
+      </c>
       <c r="L12">
         <v>0.48</v>
       </c>
@@ -2442,7 +2449,9 @@
       <c r="H13">
         <v>0.44</v>
       </c>
-      <c r="I13" s="5"/>
+      <c r="I13" s="5">
+        <v>0.3</v>
+      </c>
       <c r="L13">
         <v>0.48</v>
       </c>
@@ -2494,7 +2503,9 @@
       <c r="H15">
         <v>0.67</v>
       </c>
-      <c r="I15" s="5"/>
+      <c r="I15" s="5">
+        <v>0.51</v>
+      </c>
       <c r="L15">
         <v>0.68</v>
       </c>
@@ -2651,7 +2662,9 @@
       <c r="H21">
         <v>0.65</v>
       </c>
-      <c r="I21" s="5"/>
+      <c r="I21" s="5">
+        <v>0.3</v>
+      </c>
       <c r="L21">
         <v>0.68</v>
       </c>
@@ -2703,7 +2716,9 @@
       <c r="H23">
         <v>0.68</v>
       </c>
-      <c r="I23" s="5"/>
+      <c r="I23" s="5">
+        <v>0.22</v>
+      </c>
       <c r="L23">
         <v>0.68</v>
       </c>
@@ -2728,7 +2743,9 @@
       <c r="H24">
         <v>0.67</v>
       </c>
-      <c r="I24" s="5"/>
+      <c r="I24" s="5">
+        <v>0.1</v>
+      </c>
       <c r="L24">
         <v>0.48</v>
       </c>
@@ -2753,7 +2770,9 @@
       <c r="H25">
         <v>0.61</v>
       </c>
-      <c r="I25" s="5"/>
+      <c r="I25" s="5">
+        <v>0.37</v>
+      </c>
       <c r="L25">
         <v>0.8</v>
       </c>
@@ -2805,8 +2824,8 @@
       <c r="H27">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>496</v>
+      <c r="I27" s="5">
+        <v>0.37</v>
       </c>
       <c r="L27">
         <v>0.8</v>
@@ -2832,7 +2851,9 @@
       <c r="H28">
         <v>0.63</v>
       </c>
-      <c r="I28" s="5"/>
+      <c r="I28" s="5">
+        <v>0.34</v>
+      </c>
       <c r="L28">
         <v>0.48</v>
       </c>
@@ -2857,7 +2878,9 @@
       <c r="H29">
         <v>0.75</v>
       </c>
-      <c r="I29" s="5"/>
+      <c r="I29" s="5">
+        <v>0.63</v>
+      </c>
       <c r="L29">
         <v>0.8</v>
       </c>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BD23E0-08AC-E24B-92E3-8260C2E2218E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0F1425-5CB7-0B4A-BA84-3D2C9E853808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1496,9 +1496,6 @@
     <t>Simango</t>
   </si>
   <si>
-    <t>H</t>
-  </si>
-  <si>
     <t>AS_4</t>
   </si>
   <si>
@@ -1524,6 +1521,9 @@
   </si>
   <si>
     <t>T_4</t>
+  </si>
+  <si>
+    <t>H240284Z</t>
   </si>
 </sst>
 </file>
@@ -2094,28 +2094,28 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E1" t="s">
         <v>488</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>489</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>490</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>491</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" t="s">
         <v>493</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>494</v>
-      </c>
-      <c r="K1" t="s">
-        <v>495</v>
       </c>
       <c r="L1" t="s">
         <v>4</v>
@@ -2127,7 +2127,7 @@
         <v>6</v>
       </c>
       <c r="O1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P1" t="s">
         <v>2</v>
@@ -2932,7 +2932,9 @@
       <c r="H31">
         <v>0.6</v>
       </c>
-      <c r="I31" s="5"/>
+      <c r="I31" s="5">
+        <v>0.45</v>
+      </c>
       <c r="L31">
         <v>0.24</v>
       </c>
@@ -2957,7 +2959,9 @@
       <c r="H32">
         <v>0.47</v>
       </c>
-      <c r="I32" s="5"/>
+      <c r="I32" s="5">
+        <v>0.3</v>
+      </c>
       <c r="L32">
         <v>0.8</v>
       </c>
@@ -2982,7 +2986,9 @@
       <c r="H33">
         <v>0.54</v>
       </c>
-      <c r="I33" s="5"/>
+      <c r="I33" s="5">
+        <v>0.31</v>
+      </c>
       <c r="L33">
         <v>0.8</v>
       </c>
@@ -3007,7 +3013,9 @@
       <c r="H34">
         <v>0.16</v>
       </c>
-      <c r="I34" s="4"/>
+      <c r="I34" s="4">
+        <v>0.12</v>
+      </c>
       <c r="L34">
         <v>0</v>
       </c>
@@ -3032,7 +3040,9 @@
       <c r="H35">
         <v>0.42</v>
       </c>
-      <c r="I35" s="5"/>
+      <c r="I35" s="5">
+        <v>0.61</v>
+      </c>
       <c r="L35">
         <v>0.24</v>
       </c>
@@ -3057,7 +3067,9 @@
       <c r="H36">
         <v>0.47</v>
       </c>
-      <c r="I36" s="4"/>
+      <c r="I36" s="4">
+        <v>0.25</v>
+      </c>
       <c r="L36">
         <v>0</v>
       </c>
@@ -3204,7 +3216,9 @@
       <c r="H42">
         <v>0.33</v>
       </c>
-      <c r="I42" s="5"/>
+      <c r="I42" s="5">
+        <v>0.19</v>
+      </c>
       <c r="L42">
         <v>0.24</v>
       </c>
@@ -3237,7 +3251,7 @@
         <v>485</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="C44" t="s">
         <v>90</v>
@@ -3251,7 +3265,9 @@
       <c r="H44">
         <v>0.65</v>
       </c>
-      <c r="I44" s="4"/>
+      <c r="I44" s="4">
+        <v>0.18</v>
+      </c>
       <c r="P44" s="18"/>
     </row>
     <row r="45" spans="1:16">
@@ -3348,7 +3364,9 @@
       <c r="H48">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I48" s="5"/>
+      <c r="I48" s="5">
+        <v>0.54</v>
+      </c>
       <c r="L48">
         <v>0.8</v>
       </c>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0F1425-5CB7-0B4A-BA84-3D2C9E853808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EDAE17-3CCA-024E-8C06-F8CE8DA5DDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3094,7 +3094,9 @@
       <c r="H37">
         <v>0.77</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I37" s="5">
+        <v>0.27</v>
+      </c>
       <c r="L37">
         <v>0</v>
       </c>
@@ -3119,7 +3121,9 @@
       <c r="H38">
         <v>0.52</v>
       </c>
-      <c r="I38" s="4"/>
+      <c r="I38" s="4">
+        <v>0.24</v>
+      </c>
       <c r="P38" s="18"/>
     </row>
     <row r="39" spans="1:16">
@@ -3141,7 +3145,9 @@
       <c r="H39">
         <v>0.6</v>
       </c>
-      <c r="I39" s="5"/>
+      <c r="I39" s="5">
+        <v>0.49</v>
+      </c>
       <c r="L39">
         <v>0.8</v>
       </c>
@@ -3166,7 +3172,9 @@
       <c r="H40">
         <v>0.47</v>
       </c>
-      <c r="I40" s="5"/>
+      <c r="I40" s="5">
+        <v>0.22</v>
+      </c>
       <c r="L40">
         <v>0.8</v>
       </c>
@@ -3191,7 +3199,9 @@
       <c r="H41">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I41" s="5"/>
+      <c r="I41" s="5">
+        <v>0.31</v>
+      </c>
       <c r="L41">
         <v>0.24</v>
       </c>
@@ -3243,7 +3253,9 @@
       <c r="H43">
         <v>0.54</v>
       </c>
-      <c r="I43" s="4"/>
+      <c r="I43" s="4">
+        <v>0.51</v>
+      </c>
       <c r="P43" s="18"/>
     </row>
     <row r="44" spans="1:16">
@@ -3289,7 +3301,9 @@
       <c r="H45">
         <v>0.44</v>
       </c>
-      <c r="I45" s="5"/>
+      <c r="I45" s="5">
+        <v>0.39</v>
+      </c>
       <c r="L45">
         <v>0.8</v>
       </c>
@@ -3314,7 +3328,9 @@
       <c r="H46">
         <v>0.44</v>
       </c>
-      <c r="I46" s="5"/>
+      <c r="I46" s="5">
+        <v>0.27</v>
+      </c>
       <c r="L46">
         <v>0.24</v>
       </c>
@@ -3339,7 +3355,9 @@
       <c r="H47">
         <v>0.54</v>
       </c>
-      <c r="I47" s="5"/>
+      <c r="I47" s="5">
+        <v>0.15</v>
+      </c>
       <c r="L47">
         <v>0.24</v>
       </c>
@@ -3463,7 +3481,9 @@
       <c r="H52">
         <v>0.54</v>
       </c>
-      <c r="I52" s="5"/>
+      <c r="I52" s="5">
+        <v>0.48</v>
+      </c>
       <c r="L52">
         <v>0.83</v>
       </c>
@@ -3563,7 +3583,9 @@
       <c r="H56">
         <v>0.32</v>
       </c>
-      <c r="I56" s="4"/>
+      <c r="I56" s="4">
+        <v>0.64</v>
+      </c>
       <c r="L56">
         <v>0.92</v>
       </c>
@@ -3613,7 +3635,9 @@
       <c r="H58">
         <v>0.32</v>
       </c>
-      <c r="I58" s="4"/>
+      <c r="I58" s="4">
+        <v>0.34</v>
+      </c>
       <c r="P58" s="6"/>
     </row>
     <row r="59" spans="1:16">
@@ -3710,7 +3734,9 @@
       <c r="H62">
         <v>0.37</v>
       </c>
-      <c r="I62" s="4"/>
+      <c r="I62" s="4">
+        <v>0.49</v>
+      </c>
       <c r="L62">
         <v>0.83</v>
       </c>
@@ -3785,7 +3811,9 @@
       <c r="H65">
         <v>0.53</v>
       </c>
-      <c r="I65" s="4"/>
+      <c r="I65" s="4">
+        <v>0.67</v>
+      </c>
       <c r="L65">
         <v>0.79</v>
       </c>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EDAE17-3CCA-024E-8C06-F8CE8DA5DDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0D396A-E8A5-9443-A6AE-13259B40BDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3409,7 +3409,9 @@
       <c r="H49">
         <v>0.68</v>
       </c>
-      <c r="I49" s="5"/>
+      <c r="I49" s="5">
+        <v>0.79</v>
+      </c>
       <c r="P49" s="6"/>
     </row>
     <row r="50" spans="1:16">
@@ -3431,7 +3433,9 @@
       <c r="H50">
         <v>0.75</v>
       </c>
-      <c r="I50" s="5"/>
+      <c r="I50" s="5">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="L50">
         <v>0.63</v>
       </c>
@@ -3508,7 +3512,9 @@
       <c r="H53">
         <v>0.6</v>
       </c>
-      <c r="I53" s="5"/>
+      <c r="I53" s="5">
+        <v>0.51</v>
+      </c>
       <c r="L53">
         <v>0.79</v>
       </c>
@@ -3533,7 +3539,9 @@
       <c r="H54">
         <v>0.33</v>
       </c>
-      <c r="I54" s="5"/>
+      <c r="I54" s="5">
+        <v>0.4</v>
+      </c>
       <c r="L54">
         <v>0.55000000000000004</v>
       </c>
@@ -3659,7 +3667,9 @@
       <c r="H59">
         <v>0.81</v>
       </c>
-      <c r="I59" s="4"/>
+      <c r="I59" s="4">
+        <v>0.66</v>
+      </c>
       <c r="L59">
         <v>0.92</v>
       </c>
@@ -3709,7 +3719,9 @@
       <c r="H61">
         <v>0.46</v>
       </c>
-      <c r="I61" s="4"/>
+      <c r="I61" s="4">
+        <v>0.45</v>
+      </c>
       <c r="L61">
         <v>0.55000000000000004</v>
       </c>
@@ -3761,7 +3773,9 @@
       <c r="H63">
         <v>0.63</v>
       </c>
-      <c r="I63" s="4"/>
+      <c r="I63" s="4">
+        <v>0.61</v>
+      </c>
       <c r="L63">
         <v>0.63</v>
       </c>
@@ -3786,7 +3800,9 @@
       <c r="H64">
         <v>0.37</v>
       </c>
-      <c r="I64" s="4"/>
+      <c r="I64" s="4">
+        <v>0.15</v>
+      </c>
       <c r="L64">
         <v>0.37</v>
       </c>
@@ -4107,7 +4123,9 @@
       <c r="H77">
         <v>0.74</v>
       </c>
-      <c r="I77" s="4"/>
+      <c r="I77" s="4">
+        <v>0.84</v>
+      </c>
       <c r="L77">
         <v>0.92</v>
       </c>
@@ -4229,7 +4247,9 @@
       <c r="H82">
         <v>0.39</v>
       </c>
-      <c r="I82" s="4"/>
+      <c r="I82" s="4">
+        <v>0.36</v>
+      </c>
       <c r="L82">
         <v>0.37</v>
       </c>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0D396A-E8A5-9443-A6AE-13259B40BDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEF49C7-2494-7640-91FE-B78EB0820059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3460,7 +3460,9 @@
       <c r="H51">
         <v>0.6</v>
       </c>
-      <c r="I51" s="5"/>
+      <c r="I51" s="5">
+        <v>0.46</v>
+      </c>
       <c r="L51">
         <v>0.92</v>
       </c>
@@ -3566,7 +3568,9 @@
       <c r="H55">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I55" s="5"/>
+      <c r="I55" s="5">
+        <v>0.52</v>
+      </c>
       <c r="L55">
         <v>0.83</v>
       </c>
@@ -3618,7 +3622,9 @@
       <c r="H57">
         <v>0.51</v>
       </c>
-      <c r="I57" s="4"/>
+      <c r="I57" s="4">
+        <v>0.25</v>
+      </c>
       <c r="L57">
         <v>0.37</v>
       </c>
@@ -3694,7 +3700,9 @@
       <c r="H60">
         <v>0.46</v>
       </c>
-      <c r="I60" s="4"/>
+      <c r="I60" s="4">
+        <v>0.39</v>
+      </c>
       <c r="L60">
         <v>0.83</v>
       </c>
@@ -3854,7 +3862,9 @@
       <c r="H66">
         <v>0.35</v>
       </c>
-      <c r="I66" s="4"/>
+      <c r="I66" s="4">
+        <v>0.25</v>
+      </c>
       <c r="L66">
         <v>0.55000000000000004</v>
       </c>
@@ -4685,7 +4695,9 @@
       <c r="H101">
         <v>0.44</v>
       </c>
-      <c r="I101" s="4"/>
+      <c r="I101" s="4">
+        <v>0.37</v>
+      </c>
       <c r="P101" s="6"/>
     </row>
     <row r="102" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEF49C7-2494-7640-91FE-B78EB0820059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18517FA0-C92B-3949-96ED-0A7DCC893729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="495">
   <si>
     <t>Surname</t>
   </si>
@@ -1482,9 +1482,6 @@
   </si>
   <si>
     <t>H240460T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   </t>
   </si>
   <si>
     <t>Mujee</t>
@@ -2094,28 +2091,28 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E1" t="s">
         <v>487</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>488</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>489</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>490</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" t="s">
         <v>492</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>493</v>
-      </c>
-      <c r="K1" t="s">
-        <v>494</v>
       </c>
       <c r="L1" t="s">
         <v>4</v>
@@ -2127,7 +2124,7 @@
         <v>6</v>
       </c>
       <c r="O1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P1" t="s">
         <v>2</v>
@@ -2365,8 +2362,8 @@
       <c r="E10">
         <v>0.9</v>
       </c>
-      <c r="H10" t="s">
-        <v>482</v>
+      <c r="H10">
+        <v>0.54</v>
       </c>
       <c r="I10" s="5">
         <v>0.48</v>
@@ -2594,10 +2591,10 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>483</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>484</v>
       </c>
       <c r="C19" t="s">
         <v>63</v>
@@ -3260,10 +3257,10 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C44" t="s">
         <v>90</v>
@@ -3889,7 +3886,9 @@
       <c r="H67">
         <v>0.77</v>
       </c>
-      <c r="I67" s="4"/>
+      <c r="I67" s="4">
+        <v>0.7</v>
+      </c>
       <c r="L67">
         <v>0.83</v>
       </c>
@@ -4014,7 +4013,9 @@
       <c r="H72">
         <v>0.28000000000000003</v>
       </c>
-      <c r="I72" s="4"/>
+      <c r="I72" s="4">
+        <v>0.36</v>
+      </c>
       <c r="L72">
         <v>0.79</v>
       </c>
@@ -4039,7 +4040,9 @@
       <c r="H73">
         <v>0.77</v>
       </c>
-      <c r="I73" s="4"/>
+      <c r="I73" s="4">
+        <v>0.66</v>
+      </c>
       <c r="L73">
         <v>0.83</v>
       </c>
@@ -4108,7 +4111,9 @@
       <c r="H76">
         <v>0.61</v>
       </c>
-      <c r="I76" s="4"/>
+      <c r="I76" s="4">
+        <v>0.63</v>
+      </c>
       <c r="L76">
         <v>0.55000000000000004</v>
       </c>
@@ -4431,7 +4436,9 @@
       <c r="H89">
         <v>0.54</v>
       </c>
-      <c r="I89" s="4"/>
+      <c r="I89" s="4">
+        <v>0.34</v>
+      </c>
       <c r="P89" s="6"/>
     </row>
     <row r="90" spans="1:16">
@@ -4741,7 +4748,9 @@
       <c r="H103">
         <v>0.49</v>
       </c>
-      <c r="I103" s="4"/>
+      <c r="I103" s="4">
+        <v>0.27</v>
+      </c>
       <c r="P103" s="6"/>
     </row>
     <row r="104" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18517FA0-C92B-3949-96ED-0A7DCC893729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CAB15A-F43F-AE42-B427-B628822D8A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4314,7 +4314,9 @@
       <c r="H84">
         <v>0.79</v>
       </c>
-      <c r="I84" s="4"/>
+      <c r="I84" s="4">
+        <v>0.6</v>
+      </c>
       <c r="L84">
         <v>0.79</v>
       </c>
@@ -4364,7 +4366,9 @@
       <c r="H86">
         <v>0.61</v>
       </c>
-      <c r="I86" s="4"/>
+      <c r="I86" s="4">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="L86">
         <v>0.55000000000000004</v>
       </c>
@@ -5278,7 +5282,9 @@
       <c r="H127">
         <v>0.32</v>
       </c>
-      <c r="I127" s="4"/>
+      <c r="I127" s="4">
+        <v>0.24</v>
+      </c>
       <c r="P127" s="6"/>
     </row>
     <row r="128" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CAB15A-F43F-AE42-B427-B628822D8A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F72692-5B55-7B4F-A73D-B4EC1D83D7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3485,7 +3485,7 @@
         <v>0.54</v>
       </c>
       <c r="I52" s="5">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="L52">
         <v>0.83</v>
@@ -3938,7 +3938,9 @@
       <c r="H69">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I69" s="4"/>
+      <c r="I69" s="4">
+        <v>0.6</v>
+      </c>
       <c r="L69">
         <v>0.92</v>
       </c>
@@ -4067,7 +4069,9 @@
       <c r="H74">
         <v>0.51</v>
       </c>
-      <c r="I74" s="4"/>
+      <c r="I74" s="4">
+        <v>0.34</v>
+      </c>
       <c r="P74" s="6"/>
     </row>
     <row r="75" spans="1:16">
@@ -4464,7 +4468,9 @@
       <c r="H90">
         <v>0.68</v>
       </c>
-      <c r="I90" s="4"/>
+      <c r="I90" s="4">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P90" s="6"/>
     </row>
     <row r="91" spans="1:16">
@@ -4842,7 +4848,9 @@
       <c r="H107">
         <v>0.44</v>
       </c>
-      <c r="I107" s="4"/>
+      <c r="I107" s="4">
+        <v>0.1</v>
+      </c>
       <c r="P107" s="6"/>
     </row>
     <row r="108" spans="1:16">
@@ -5018,7 +5026,9 @@
       <c r="H115">
         <v>0.46</v>
       </c>
-      <c r="I115" s="4"/>
+      <c r="I115" s="4">
+        <v>0.4</v>
+      </c>
       <c r="P115" s="6"/>
     </row>
     <row r="116" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F72692-5B55-7B4F-A73D-B4EC1D83D7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD2DF56-5427-5E48-8470-50FD2A6BF35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3913,7 +3913,9 @@
       <c r="H68">
         <v>0.6</v>
       </c>
-      <c r="I68" s="4"/>
+      <c r="I68" s="4">
+        <v>0.39</v>
+      </c>
       <c r="L68">
         <v>0.79</v>
       </c>
@@ -3965,7 +3967,9 @@
       <c r="H70">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I70" s="4"/>
+      <c r="I70" s="4">
+        <v>0.24</v>
+      </c>
       <c r="L70">
         <v>0.55000000000000004</v>
       </c>
@@ -3990,7 +3994,9 @@
       <c r="H71">
         <v>0.35</v>
       </c>
-      <c r="I71" s="4"/>
+      <c r="I71" s="4">
+        <v>0.45</v>
+      </c>
       <c r="L71">
         <v>0.37</v>
       </c>
@@ -4093,7 +4099,9 @@
       <c r="H75">
         <v>0.05</v>
       </c>
-      <c r="I75" s="4"/>
+      <c r="I75" s="4">
+        <v>0.18</v>
+      </c>
       <c r="P75" s="6"/>
     </row>
     <row r="76" spans="1:16">
@@ -4169,7 +4177,9 @@
       <c r="H78">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I78" s="4"/>
+      <c r="I78" s="4">
+        <v>0.18</v>
+      </c>
       <c r="P78" s="6"/>
     </row>
     <row r="79" spans="1:16">
@@ -4191,7 +4201,9 @@
       <c r="H79">
         <v>0.61</v>
       </c>
-      <c r="I79" s="4"/>
+      <c r="I79" s="4">
+        <v>0.63</v>
+      </c>
       <c r="L79">
         <v>0.92</v>
       </c>
@@ -4216,7 +4228,9 @@
       <c r="H80">
         <v>0.47</v>
       </c>
-      <c r="I80" s="4"/>
+      <c r="I80" s="4">
+        <v>0.46</v>
+      </c>
       <c r="L80">
         <v>0.63</v>
       </c>
@@ -4241,7 +4255,9 @@
       <c r="H81">
         <v>0.65</v>
       </c>
-      <c r="I81" s="4"/>
+      <c r="I81" s="4">
+        <v>0.72</v>
+      </c>
       <c r="L81">
         <v>0.37</v>
       </c>
@@ -4293,7 +4309,9 @@
       <c r="H83">
         <v>0.54</v>
       </c>
-      <c r="I83" s="4"/>
+      <c r="I83" s="4">
+        <v>0.46</v>
+      </c>
       <c r="L83">
         <v>0.63</v>
       </c>
@@ -4345,7 +4363,9 @@
       <c r="H85">
         <v>0.63</v>
       </c>
-      <c r="I85" s="4"/>
+      <c r="I85" s="4">
+        <v>0.33</v>
+      </c>
       <c r="L85">
         <v>0.63</v>
       </c>
@@ -4397,7 +4417,9 @@
       <c r="H87">
         <v>0.25</v>
       </c>
-      <c r="I87" s="4"/>
+      <c r="I87" s="4">
+        <v>0.18</v>
+      </c>
       <c r="P87" s="6"/>
     </row>
     <row r="88" spans="1:16">
@@ -4419,7 +4441,9 @@
       <c r="H88">
         <v>0.6</v>
       </c>
-      <c r="I88" s="4"/>
+      <c r="I88" s="4">
+        <v>0.39</v>
+      </c>
       <c r="L88">
         <v>0.79</v>
       </c>
@@ -4736,7 +4760,9 @@
       <c r="H102">
         <v>0.51</v>
       </c>
-      <c r="I102" s="4"/>
+      <c r="I102" s="4">
+        <v>0.69</v>
+      </c>
       <c r="P102" s="6"/>
     </row>
     <row r="103" spans="1:16">
@@ -4782,7 +4808,9 @@
       <c r="H104">
         <v>0.54</v>
       </c>
-      <c r="I104" s="4"/>
+      <c r="I104" s="4">
+        <v>0.3</v>
+      </c>
       <c r="P104" s="6"/>
     </row>
     <row r="105" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD2DF56-5427-5E48-8470-50FD2A6BF35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99F7B1B-F643-2E4D-BF9B-FCEF5B7A85E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="497">
   <si>
     <t>Surname</t>
   </si>
@@ -1521,6 +1521,12 @@
   </si>
   <si>
     <t>H240284Z</t>
+  </si>
+  <si>
+    <t>Gama</t>
+  </si>
+  <si>
+    <t>H250784X</t>
   </si>
 </sst>
 </file>
@@ -1658,7 +1664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1685,6 +1691,13 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1728,10 +1741,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:P240" totalsRowShown="0">
-  <autoFilter ref="A1:P240" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P240">
-    <sortCondition ref="C1:C240"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:P241" totalsRowShown="0">
+  <autoFilter ref="A1:P241" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P241">
+    <sortCondition ref="C1:C241"/>
   </sortState>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -2072,7 +2085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:P240"/>
+  <dimension ref="A1:P241"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -3388,10 +3401,10 @@
       <c r="P48" s="6"/>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="23" t="s">
         <v>92</v>
       </c>
       <c r="C49" s="11" t="s">
@@ -3412,10 +3425,10 @@
       <c r="P49" s="6"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="23" t="s">
         <v>95</v>
       </c>
       <c r="C50" s="11" t="s">
@@ -3439,10 +3452,10 @@
       <c r="P50" s="6"/>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="23" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="11" t="s">
@@ -3466,10 +3479,10 @@
       <c r="P51" s="6"/>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="23" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="11" t="s">
@@ -3493,10 +3506,10 @@
       <c r="P52" s="6"/>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="23" t="s">
         <v>101</v>
       </c>
       <c r="C53" s="11" t="s">
@@ -3520,10 +3533,10 @@
       <c r="P53" s="6"/>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="23" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="11" t="s">
@@ -3547,10 +3560,10 @@
       <c r="P54" s="6"/>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="23" t="s">
         <v>476</v>
       </c>
       <c r="C55" s="11" t="s">
@@ -3574,10 +3587,10 @@
       <c r="P55" s="6"/>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="23" t="s">
         <v>106</v>
       </c>
       <c r="C56" s="11" t="s">
@@ -3601,10 +3614,10 @@
       <c r="P56" s="6"/>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="23" t="s">
         <v>108</v>
       </c>
       <c r="C57" s="11" t="s">
@@ -4474,10 +4487,10 @@
       <c r="P89" s="6"/>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="23" t="s">
         <v>172</v>
       </c>
       <c r="C90" s="11" t="s">
@@ -4498,10 +4511,10 @@
       <c r="P90" s="6"/>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="11" t="s">
+      <c r="A91" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="23" t="s">
         <v>175</v>
       </c>
       <c r="C91" s="11" t="s">
@@ -4516,14 +4529,16 @@
       <c r="H91">
         <v>0.6</v>
       </c>
-      <c r="I91" s="4"/>
+      <c r="I91" s="4">
+        <v>0.76</v>
+      </c>
       <c r="P91" s="6"/>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" t="s">
+      <c r="A92" s="20" t="s">
         <v>474</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="21" t="s">
         <v>475</v>
       </c>
       <c r="C92" t="s">
@@ -4542,10 +4557,10 @@
       <c r="P92" s="18"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="11" t="s">
+      <c r="A93" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="23" t="s">
         <v>177</v>
       </c>
       <c r="C93" s="11" t="s">
@@ -4564,10 +4579,10 @@
       <c r="P93" s="6"/>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="11" t="s">
+      <c r="A94" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="23" t="s">
         <v>179</v>
       </c>
       <c r="C94" s="11" t="s">
@@ -4582,14 +4597,16 @@
       <c r="H94">
         <v>0.65</v>
       </c>
-      <c r="I94" s="4"/>
+      <c r="I94" s="4">
+        <v>0.84</v>
+      </c>
       <c r="P94" s="6"/>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="11" t="s">
+      <c r="A95" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="23" t="s">
         <v>181</v>
       </c>
       <c r="C95" s="11" t="s">
@@ -4604,14 +4621,16 @@
       <c r="H95">
         <v>0.42</v>
       </c>
-      <c r="I95" s="4"/>
+      <c r="I95" s="4">
+        <v>0.31</v>
+      </c>
       <c r="P95" s="6"/>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="23" t="s">
         <v>183</v>
       </c>
       <c r="C96" s="11" t="s">
@@ -4626,14 +4645,16 @@
       <c r="H96">
         <v>0.79</v>
       </c>
-      <c r="I96" s="4"/>
+      <c r="I96" s="4">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="P96" s="6"/>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="11" t="s">
+      <c r="A97" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="23" t="s">
         <v>185</v>
       </c>
       <c r="C97" s="11" t="s">
@@ -4648,437 +4669,442 @@
       <c r="H97">
         <v>0.46</v>
       </c>
-      <c r="I97" s="4"/>
+      <c r="I97" s="4">
+        <v>0.31</v>
+      </c>
       <c r="P97" s="6"/>
     </row>
     <row r="98" spans="1:16">
-      <c r="A98" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="C98" s="11" t="s">
+      <c r="A98" t="s">
+        <v>495</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C98" t="s">
         <v>173</v>
       </c>
-      <c r="D98" s="11">
-        <v>0.93</v>
-      </c>
-      <c r="E98">
-        <v>0.96</v>
-      </c>
-      <c r="H98">
-        <v>0.72</v>
-      </c>
-      <c r="I98" s="4"/>
-      <c r="P98" s="6"/>
+      <c r="D98" s="4"/>
+      <c r="H98" s="4">
+        <v>0</v>
+      </c>
+      <c r="I98" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="P98" s="18"/>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C99" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D99" s="11">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="E99">
         <v>0.96</v>
       </c>
       <c r="H99">
-        <v>0.28000000000000003</v>
+        <v>0.72</v>
       </c>
       <c r="I99" s="4"/>
       <c r="P99" s="6"/>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D100" s="11">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="E100">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H100">
-        <v>0.4</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I100" s="4"/>
       <c r="P100" s="6"/>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C101" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D101" s="11">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="E101">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H101">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="I101" s="4">
-        <v>0.37</v>
+        <v>0.48</v>
       </c>
       <c r="P101" s="6"/>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D102" s="11">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="E102">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="H102">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="I102" s="4">
-        <v>0.69</v>
+        <v>0.37</v>
       </c>
       <c r="P102" s="6"/>
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D103" s="11">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="E103">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="H103">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="I103" s="4">
-        <v>0.27</v>
+        <v>0.69</v>
       </c>
       <c r="P103" s="6"/>
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D104" s="11">
+        <v>0.89</v>
+      </c>
+      <c r="E104">
+        <v>0.8</v>
+      </c>
+      <c r="H104">
+        <v>0.49</v>
+      </c>
+      <c r="I104" s="4">
+        <v>0.27</v>
+      </c>
+      <c r="P104" s="6"/>
+    </row>
+    <row r="105" spans="1:16">
+      <c r="A105" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D105" s="11">
         <v>0.85</v>
-      </c>
-      <c r="E104">
-        <v>1</v>
-      </c>
-      <c r="H104">
-        <v>0.54</v>
-      </c>
-      <c r="I104" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="P104" s="6"/>
-    </row>
-    <row r="105" spans="1:16">
-      <c r="A105" t="s">
-        <v>470</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C105" t="s">
-        <v>173</v>
-      </c>
-      <c r="D105" s="4">
-        <v>0</v>
       </c>
       <c r="E105">
         <v>1</v>
       </c>
       <c r="H105">
+        <v>0.54</v>
+      </c>
+      <c r="I105" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="P105" s="6"/>
+    </row>
+    <row r="106" spans="1:16">
+      <c r="A106" t="s">
+        <v>470</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C106" t="s">
+        <v>173</v>
+      </c>
+      <c r="D106" s="4">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="H106">
         <v>0.51</v>
       </c>
-      <c r="I105" s="4"/>
-      <c r="P105" s="18"/>
-    </row>
-    <row r="106" spans="1:16">
-      <c r="A106" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B106" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D106" s="11">
-        <v>0.86</v>
-      </c>
-      <c r="E106">
-        <v>0.94</v>
-      </c>
-      <c r="H106">
-        <v>0.4</v>
-      </c>
-      <c r="I106" s="4"/>
-      <c r="P106" s="6"/>
+      <c r="I106" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="P106" s="18"/>
     </row>
     <row r="107" spans="1:16">
       <c r="A107" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C107" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D107" s="11">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="E107">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="H107">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="I107" s="4">
-        <v>0.1</v>
+        <v>0.37</v>
       </c>
       <c r="P107" s="6"/>
     </row>
     <row r="108" spans="1:16">
       <c r="A108" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D108" s="11">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="E108">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H108">
-        <v>0.39</v>
-      </c>
-      <c r="I108" s="4"/>
+        <v>0.44</v>
+      </c>
+      <c r="I108" s="4">
+        <v>0.1</v>
+      </c>
       <c r="P108" s="6"/>
     </row>
     <row r="109" spans="1:16">
       <c r="A109" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C109" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D109" s="11">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="E109">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="H109">
-        <v>0.75</v>
+        <v>0.39</v>
       </c>
       <c r="I109" s="4"/>
       <c r="P109" s="6"/>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D110" s="11">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="E110">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="H110">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="I110" s="4"/>
       <c r="P110" s="6"/>
     </row>
     <row r="111" spans="1:16">
       <c r="A111" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C111" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D111" s="11">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="E111">
-        <v>0.94</v>
+        <v>1</v>
       </c>
       <c r="H111">
-        <v>0.26</v>
+        <v>0.61</v>
       </c>
       <c r="I111" s="4"/>
       <c r="P111" s="6"/>
     </row>
     <row r="112" spans="1:16">
       <c r="A112" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D112" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="E112">
         <v>0.94</v>
       </c>
-      <c r="E112">
-        <v>1</v>
-      </c>
       <c r="H112">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="I112" s="4"/>
       <c r="P112" s="6"/>
     </row>
     <row r="113" spans="1:16">
       <c r="A113" s="11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C113" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D113" s="11">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="E113">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H113">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="I113" s="4"/>
       <c r="P113" s="6"/>
     </row>
     <row r="114" spans="1:16">
       <c r="A114" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C114" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D114" s="11">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="E114">
         <v>0.91</v>
       </c>
       <c r="H114">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I114" s="4"/>
       <c r="P114" s="6"/>
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C115" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D115" s="11">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="E115">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="H115">
-        <v>0.46</v>
-      </c>
-      <c r="I115" s="4">
-        <v>0.4</v>
-      </c>
+        <v>0.39</v>
+      </c>
+      <c r="I115" s="4"/>
       <c r="P115" s="6"/>
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C116" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D116" s="11">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="E116">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="H116">
-        <v>0.63</v>
-      </c>
-      <c r="I116" s="4"/>
+        <v>0.46</v>
+      </c>
+      <c r="I116" s="4">
+        <v>0.4</v>
+      </c>
       <c r="P116" s="6"/>
     </row>
     <row r="117" spans="1:16">
@@ -5086,104 +5112,104 @@
         <v>220</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C117" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D117" s="11">
-        <v>0.92</v>
+        <v>0.66</v>
       </c>
       <c r="E117">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="H117">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
       <c r="I117" s="4"/>
       <c r="P117" s="6"/>
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C118" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D118" s="11">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="E118">
         <v>0.9</v>
       </c>
       <c r="H118">
-        <v>0.54</v>
+        <v>0.44</v>
       </c>
       <c r="I118" s="4"/>
       <c r="P118" s="6"/>
     </row>
     <row r="119" spans="1:16">
-      <c r="A119" t="s">
-        <v>471</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="A119" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="C119" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D119" s="4">
-        <v>0</v>
+      <c r="D119" s="11">
+        <v>0.82</v>
       </c>
       <c r="E119">
         <v>0.9</v>
       </c>
       <c r="H119">
+        <v>0.54</v>
+      </c>
+      <c r="I119" s="4"/>
+      <c r="P119" s="6"/>
+    </row>
+    <row r="120" spans="1:16">
+      <c r="A120" t="s">
+        <v>471</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C120" t="s">
+        <v>173</v>
+      </c>
+      <c r="D120" s="4">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0.9</v>
+      </c>
+      <c r="H120">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I119" s="4"/>
-      <c r="P119" s="18"/>
-    </row>
-    <row r="120" spans="1:16">
-      <c r="A120" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B120" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D120" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="E120">
-        <v>0.97</v>
-      </c>
-      <c r="H120">
-        <v>0.26</v>
-      </c>
       <c r="I120" s="4"/>
-      <c r="P120" s="6"/>
+      <c r="P120" s="18"/>
     </row>
     <row r="121" spans="1:16">
       <c r="A121" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C121" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D121" s="11">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="E121">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="H121">
         <v>0.26</v>
@@ -5193,19 +5219,19 @@
     </row>
     <row r="122" spans="1:16">
       <c r="A122" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C122" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D122" s="11">
-        <v>0.69</v>
+        <v>0.96</v>
       </c>
       <c r="E122">
-        <v>0.5</v>
+        <v>0.96</v>
       </c>
       <c r="H122">
         <v>0.26</v>
@@ -5215,1121 +5241,1123 @@
     </row>
     <row r="123" spans="1:16">
       <c r="A123" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C123" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D123" s="11">
-        <v>0.78</v>
+        <v>0.69</v>
       </c>
       <c r="E123">
-        <v>0.96</v>
+        <v>0.5</v>
       </c>
       <c r="H123">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="I123" s="4"/>
       <c r="P123" s="6"/>
     </row>
     <row r="124" spans="1:16">
       <c r="A124" s="11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C124" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D124" s="11">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="E124">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="H124">
-        <v>0.49</v>
+        <v>0.09</v>
       </c>
       <c r="I124" s="4"/>
       <c r="P124" s="6"/>
     </row>
     <row r="125" spans="1:16">
       <c r="A125" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C125" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D125" s="11">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="E125">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H125">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
       <c r="I125" s="4"/>
       <c r="P125" s="6"/>
     </row>
     <row r="126" spans="1:16">
       <c r="A126" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C126" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D126" s="11">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="E126">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H126">
-        <v>0.26</v>
+        <v>0.74</v>
       </c>
       <c r="I126" s="4"/>
       <c r="P126" s="6"/>
     </row>
     <row r="127" spans="1:16">
       <c r="A127" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C127" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D127" s="11">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="E127">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H127">
-        <v>0.32</v>
-      </c>
-      <c r="I127" s="4">
-        <v>0.24</v>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="I127" s="4"/>
       <c r="P127" s="6"/>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C128" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D128" s="11">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="E128">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="H128">
-        <v>0.11</v>
-      </c>
-      <c r="I128" s="4"/>
+        <v>0.32</v>
+      </c>
+      <c r="I128" s="4">
+        <v>0.24</v>
+      </c>
       <c r="P128" s="6"/>
     </row>
     <row r="129" spans="1:16">
       <c r="A129" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C129" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D129" s="11">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="E129">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="H129">
-        <v>0.65</v>
+        <v>0.11</v>
       </c>
       <c r="I129" s="4"/>
       <c r="P129" s="6"/>
     </row>
     <row r="130" spans="1:16">
       <c r="A130" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C130" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D130" s="11">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="E130">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="H130">
-        <v>0.28000000000000003</v>
+        <v>0.65</v>
       </c>
       <c r="I130" s="4"/>
       <c r="P130" s="6"/>
     </row>
     <row r="131" spans="1:16">
       <c r="A131" s="11" t="s">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C131" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D131" s="11">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="E131">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H131">
-        <v>0.47</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I131" s="4"/>
       <c r="P131" s="6"/>
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="11" t="s">
-        <v>248</v>
+        <v>19</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C132" s="11" t="s">
         <v>173</v>
       </c>
       <c r="D132" s="11">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="E132">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="H132">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I132" s="4"/>
       <c r="P132" s="6"/>
     </row>
     <row r="133" spans="1:16">
       <c r="A133" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>252</v>
+        <v>173</v>
       </c>
       <c r="D133" s="11">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="E133">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="H133">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="I133" s="4"/>
       <c r="P133" s="6"/>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="B134" s="11" t="s">
-        <v>254</v>
+      <c r="A134" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="B134" s="23" t="s">
+        <v>251</v>
       </c>
       <c r="C134" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D134" s="11">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="E134">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H134">
-        <v>0.56000000000000005</v>
+        <v>0.4</v>
       </c>
       <c r="I134" s="4"/>
       <c r="P134" s="6"/>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B135" s="11" t="s">
-        <v>256</v>
+      <c r="A135" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="B135" s="23" t="s">
+        <v>254</v>
       </c>
       <c r="C135" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D135" s="11">
-        <v>0.93</v>
+        <v>0.81</v>
       </c>
       <c r="E135">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H135">
-        <v>0.63</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I135" s="4"/>
       <c r="P135" s="6"/>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B136" s="11" t="s">
-        <v>258</v>
+      <c r="A136" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B136" s="23" t="s">
+        <v>256</v>
       </c>
       <c r="C136" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D136" s="11">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="E136">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="H136">
-        <v>0.42</v>
+        <v>0.63</v>
       </c>
       <c r="I136" s="4"/>
       <c r="P136" s="6"/>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B137" s="11" t="s">
-        <v>260</v>
+      <c r="A137" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="B137" s="23" t="s">
+        <v>258</v>
       </c>
       <c r="C137" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D137" s="11">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="E137">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="H137">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I137" s="4"/>
       <c r="P137" s="6"/>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="B138" s="11" t="s">
-        <v>262</v>
+      <c r="A138" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="B138" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="C138" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D138" s="11">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="E138">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H138">
-        <v>0.74</v>
+        <v>0.39</v>
       </c>
       <c r="I138" s="4"/>
       <c r="P138" s="6"/>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="B139" s="11" t="s">
-        <v>264</v>
+      <c r="A139" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="B139" s="23" t="s">
+        <v>262</v>
       </c>
       <c r="C139" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D139" s="11">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="E139">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H139">
-        <v>0.39</v>
+        <v>0.74</v>
       </c>
       <c r="I139" s="4"/>
       <c r="P139" s="6"/>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B140" s="11" t="s">
-        <v>266</v>
+      <c r="A140" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="B140" s="23" t="s">
+        <v>264</v>
       </c>
       <c r="C140" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D140" s="11">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="E140">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H140">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="I140" s="4"/>
       <c r="P140" s="6"/>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B141" s="11" t="s">
-        <v>268</v>
+      <c r="A141" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="B141" s="23" t="s">
+        <v>266</v>
       </c>
       <c r="C141" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D141" s="11">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="E141">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="H141">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="I141" s="4"/>
       <c r="P141" s="6"/>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B142" s="11" t="s">
-        <v>270</v>
+      <c r="A142" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="B142" s="23" t="s">
+        <v>268</v>
       </c>
       <c r="C142" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D142" s="11">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="E142">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="I142" s="4"/>
       <c r="P142" s="6"/>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B143" s="11" t="s">
-        <v>271</v>
+      <c r="A143" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="B143" s="23" t="s">
+        <v>270</v>
       </c>
       <c r="C143" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D143" s="11">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="E143">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H143">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="I143" s="4"/>
       <c r="P143" s="6"/>
     </row>
     <row r="144" spans="1:16">
-      <c r="A144" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B144" s="11" t="s">
-        <v>273</v>
+      <c r="A144" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B144" s="23" t="s">
+        <v>271</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D144" s="11">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="E144">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H144">
-        <v>0.65</v>
-      </c>
-      <c r="I144" s="4"/>
+        <v>0.16</v>
+      </c>
+      <c r="I144" s="4">
+        <v>0</v>
+      </c>
       <c r="P144" s="6"/>
     </row>
     <row r="145" spans="1:16">
       <c r="A145" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D145" s="11">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="E145">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="H145">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="I145" s="4"/>
       <c r="P145" s="6"/>
     </row>
     <row r="146" spans="1:16">
       <c r="A146" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D146" s="11">
-        <v>0.94</v>
+        <v>0.87</v>
       </c>
       <c r="E146">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H146">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="I146" s="4"/>
       <c r="P146" s="6"/>
     </row>
     <row r="147" spans="1:16">
       <c r="A147" s="11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C147" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D147" s="11">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="E147">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H147">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="I147" s="4"/>
       <c r="P147" s="6"/>
     </row>
     <row r="148" spans="1:16">
       <c r="A148" s="11" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D148" s="11">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="E148">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="H148">
-        <v>0.21</v>
+        <v>0.63</v>
       </c>
       <c r="I148" s="4"/>
       <c r="P148" s="6"/>
     </row>
     <row r="149" spans="1:16">
       <c r="A149" s="11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C149" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D149" s="11">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="H149">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="I149" s="4"/>
       <c r="P149" s="6"/>
     </row>
     <row r="150" spans="1:16">
       <c r="A150" s="11" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C150" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D150" s="11">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="E150">
-        <v>0.94</v>
+        <v>0</v>
       </c>
       <c r="H150">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I150" s="4"/>
       <c r="P150" s="6"/>
     </row>
     <row r="151" spans="1:16">
       <c r="A151" s="11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C151" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D151" s="11">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="E151">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="H151">
-        <v>0.63</v>
+        <v>0.3</v>
       </c>
       <c r="I151" s="4"/>
       <c r="P151" s="6"/>
     </row>
     <row r="152" spans="1:16">
       <c r="A152" s="11" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C152" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D152" s="11">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="E152">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="H152">
-        <v>0.86</v>
+        <v>0.63</v>
       </c>
       <c r="I152" s="4"/>
       <c r="P152" s="6"/>
     </row>
     <row r="153" spans="1:16">
       <c r="A153" s="11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C153" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D153" s="11">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="E153">
-        <v>0.81</v>
+        <v>0.97</v>
       </c>
       <c r="H153">
-        <v>0.47</v>
+        <v>0.86</v>
       </c>
       <c r="I153" s="4"/>
       <c r="P153" s="6"/>
     </row>
     <row r="154" spans="1:16">
       <c r="A154" s="11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C154" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D154" s="11">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="E154">
-        <v>0.94</v>
+        <v>0.81</v>
       </c>
       <c r="H154">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="I154" s="4"/>
       <c r="P154" s="6"/>
     </row>
     <row r="155" spans="1:16">
       <c r="A155" s="11" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C155" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D155" s="11">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="E155">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="H155">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="I155" s="4"/>
       <c r="P155" s="6"/>
     </row>
     <row r="156" spans="1:16">
       <c r="A156" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C156" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D156" s="11">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="E156">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="H156">
-        <v>0.65</v>
+        <v>0.44</v>
       </c>
       <c r="I156" s="4"/>
       <c r="P156" s="6"/>
     </row>
     <row r="157" spans="1:16">
       <c r="A157" s="11" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C157" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D157" s="11">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="E157">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
       <c r="H157">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="I157" s="4"/>
       <c r="P157" s="6"/>
     </row>
     <row r="158" spans="1:16">
       <c r="A158" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C158" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D158" s="11">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="E158">
-        <v>0.86</v>
+        <v>0.99</v>
       </c>
       <c r="H158">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="I158" s="4"/>
       <c r="P158" s="6"/>
     </row>
     <row r="159" spans="1:16">
       <c r="A159" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C159" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D159" s="11">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="E159">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="H159">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="I159" s="4"/>
       <c r="P159" s="6"/>
     </row>
     <row r="160" spans="1:16">
       <c r="A160" s="11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C160" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D160" s="11">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="E160">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="H160">
-        <v>0.57999999999999996</v>
+        <v>0.42</v>
       </c>
       <c r="I160" s="4"/>
       <c r="P160" s="6"/>
     </row>
     <row r="161" spans="1:16">
       <c r="A161" s="11" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C161" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D161" s="11">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="E161">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="H161">
-        <v>0.68</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I161" s="4"/>
       <c r="P161" s="6"/>
     </row>
     <row r="162" spans="1:16">
       <c r="A162" s="11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C162" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D162" s="11">
-        <v>0.94</v>
+        <v>0.88</v>
       </c>
       <c r="E162">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="H162">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="I162" s="4"/>
       <c r="P162" s="6"/>
     </row>
     <row r="163" spans="1:16">
       <c r="A163" s="11" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D163" s="11">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="E163">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H163">
-        <v>0.33</v>
+        <v>0.51</v>
       </c>
       <c r="I163" s="4"/>
       <c r="P163" s="6"/>
     </row>
     <row r="164" spans="1:16">
       <c r="A164" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C164" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D164" s="11">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="E164">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H164">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="I164" s="4"/>
       <c r="P164" s="6"/>
     </row>
     <row r="165" spans="1:16">
       <c r="A165" s="11" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C165" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D165" s="11">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="E165">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="H165">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="I165" s="4"/>
       <c r="P165" s="6"/>
     </row>
     <row r="166" spans="1:16">
       <c r="A166" s="11" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C166" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D166" s="11">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="E166">
-        <v>0.97</v>
+        <v>0.87</v>
       </c>
       <c r="H166">
-        <v>0.63</v>
+        <v>0.47</v>
       </c>
       <c r="I166" s="4"/>
       <c r="P166" s="6"/>
     </row>
     <row r="167" spans="1:16">
       <c r="A167" s="11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C167" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D167" s="11">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="E167">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="H167">
-        <v>0.56000000000000005</v>
+        <v>0.63</v>
       </c>
       <c r="I167" s="4"/>
       <c r="P167" s="6"/>
     </row>
     <row r="168" spans="1:16">
       <c r="A168" s="11" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C168" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D168" s="11">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E168">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H168">
-        <v>0.54</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I168" s="4"/>
       <c r="P168" s="6"/>
     </row>
     <row r="169" spans="1:16">
       <c r="A169" s="11" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D169" s="11">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E169">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="H169">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="I169" s="4"/>
       <c r="P169" s="6"/>
     </row>
     <row r="170" spans="1:16">
       <c r="A170" s="11" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D170" s="11">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="E170">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H170">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I170" s="4"/>
       <c r="P170" s="6"/>
     </row>
     <row r="171" spans="1:16">
       <c r="A171" s="11" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C171" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D171" s="11">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="E171">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H171">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="I171" s="4"/>
       <c r="P171" s="6"/>
     </row>
     <row r="172" spans="1:16">
-      <c r="A172" t="s">
-        <v>455</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="C172" t="s">
+      <c r="A172" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="C172" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="D172" s="4">
-        <v>0</v>
+      <c r="D172" s="11">
+        <v>0.9</v>
       </c>
       <c r="E172">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="H172">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="I172" s="4"/>
       <c r="P172" s="6"/>
     </row>
     <row r="173" spans="1:16">
-      <c r="A173" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="B173" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="C173" s="11" t="s">
+      <c r="A173" t="s">
+        <v>455</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C173" t="s">
         <v>252</v>
       </c>
-      <c r="D173" s="11">
-        <v>0.86</v>
+      <c r="D173" s="4">
+        <v>0</v>
       </c>
       <c r="E173">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="H173">
         <v>0.35</v>
@@ -6338,539 +6366,541 @@
       <c r="P173" s="6"/>
     </row>
     <row r="174" spans="1:16">
-      <c r="A174" t="s">
-        <v>453</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="C174" t="s">
+      <c r="A174" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="B174" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C174" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="D174" s="4">
-        <v>0</v>
+      <c r="D174" s="11">
+        <v>0.86</v>
       </c>
       <c r="E174">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="H174">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="I174" s="4"/>
       <c r="P174" s="6"/>
     </row>
     <row r="175" spans="1:16">
-      <c r="A175" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B175" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="C175" s="11" t="s">
+      <c r="A175" t="s">
+        <v>453</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C175" t="s">
         <v>252</v>
       </c>
-      <c r="D175" s="11">
-        <v>0.69</v>
+      <c r="D175" s="4">
+        <v>0</v>
       </c>
       <c r="E175">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="H175">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="I175" s="4"/>
       <c r="P175" s="6"/>
     </row>
     <row r="176" spans="1:16">
       <c r="A176" s="11" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B176" s="11" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C176" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D176" s="11">
-        <v>0.77</v>
+        <v>0.69</v>
       </c>
       <c r="E176">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="H176">
-        <v>0.46</v>
+        <v>0.12</v>
       </c>
       <c r="I176" s="4"/>
       <c r="P176" s="6"/>
     </row>
     <row r="177" spans="1:16">
       <c r="A177" s="11" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B177" s="11" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C177" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D177" s="11">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="H177">
-        <v>0.19</v>
+        <v>0.46</v>
       </c>
       <c r="I177" s="4"/>
       <c r="P177" s="6"/>
     </row>
     <row r="178" spans="1:16">
       <c r="A178" s="11" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C178" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D178" s="11">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="E178">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="H178">
-        <v>0.42</v>
-      </c>
-      <c r="I178" s="4"/>
+        <v>0.19</v>
+      </c>
+      <c r="I178" s="4">
+        <v>0</v>
+      </c>
       <c r="P178" s="6"/>
     </row>
     <row r="179" spans="1:16">
       <c r="A179" s="11" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B179" s="11" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C179" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D179" s="11">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="E179">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H179">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="I179" s="4"/>
       <c r="P179" s="6"/>
     </row>
     <row r="180" spans="1:16">
       <c r="A180" s="11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C180" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D180" s="11">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="E180">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H180">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="I180" s="4"/>
       <c r="P180" s="6"/>
     </row>
     <row r="181" spans="1:16">
       <c r="A181" s="11" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C181" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D181" s="11">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="E181">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="H181">
-        <v>0.35</v>
+        <v>0.53</v>
       </c>
       <c r="I181" s="4"/>
       <c r="P181" s="6"/>
     </row>
     <row r="182" spans="1:16">
       <c r="A182" s="11" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C182" s="11" t="s">
         <v>252</v>
       </c>
       <c r="D182" s="11">
-        <v>0.75</v>
+        <v>0.61</v>
       </c>
       <c r="E182">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="H182">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="I182" s="4"/>
       <c r="P182" s="6"/>
     </row>
     <row r="183" spans="1:16">
       <c r="A183" s="11" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B183" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>348</v>
+        <v>252</v>
       </c>
       <c r="D183" s="11">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="E183">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="H183">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I183" s="4"/>
       <c r="P183" s="6"/>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" t="s">
-        <v>446</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="C184" t="s">
+      <c r="A184" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="B184" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="C184" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="D184" s="4">
-        <v>0</v>
+      <c r="D184" s="11">
+        <v>0.87</v>
       </c>
       <c r="E184">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="H184">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="I184" s="4"/>
       <c r="P184" s="6"/>
     </row>
     <row r="185" spans="1:16">
-      <c r="A185" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="B185" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="C185" s="11" t="s">
+      <c r="A185" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="B185" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="C185" t="s">
         <v>348</v>
       </c>
-      <c r="D185" s="11">
-        <v>0.71</v>
+      <c r="D185" s="4">
+        <v>0</v>
       </c>
       <c r="E185">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H185">
-        <v>0.35</v>
+        <v>0.19</v>
       </c>
       <c r="I185" s="4"/>
       <c r="P185" s="6"/>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="B186" s="11" t="s">
-        <v>352</v>
+      <c r="A186" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="B186" s="23" t="s">
+        <v>350</v>
       </c>
       <c r="C186" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D186" s="11">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="E186">
         <v>0.97</v>
       </c>
       <c r="H186">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="I186" s="4"/>
       <c r="P186" s="6"/>
     </row>
     <row r="187" spans="1:16">
       <c r="A187" s="11" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C187" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D187" s="11">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="E187">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H187">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="I187" s="4"/>
       <c r="P187" s="6"/>
     </row>
     <row r="188" spans="1:16">
       <c r="A188" s="11" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C188" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D188" s="11">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E188">
         <v>1</v>
       </c>
       <c r="H188">
-        <v>0.68</v>
+        <v>0.39</v>
       </c>
       <c r="I188" s="4"/>
       <c r="P188" s="6"/>
     </row>
     <row r="189" spans="1:16">
       <c r="A189" s="11" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C189" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D189" s="11">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="E189">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="H189">
-        <v>0.42</v>
+        <v>0.68</v>
       </c>
       <c r="I189" s="4"/>
       <c r="P189" s="6"/>
     </row>
     <row r="190" spans="1:16">
       <c r="A190" s="11" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C190" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D190" s="11">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="E190">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H190">
-        <v>0.57999999999999996</v>
+        <v>0.42</v>
       </c>
       <c r="I190" s="4"/>
       <c r="P190" s="6"/>
     </row>
     <row r="191" spans="1:16">
       <c r="A191" s="11" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C191" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D191" s="11">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="E191">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H191">
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I191" s="4"/>
       <c r="P191" s="6"/>
     </row>
     <row r="192" spans="1:16">
       <c r="A192" s="11" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C192" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D192" s="11">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="E192">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H192">
-        <v>0.04</v>
+        <v>0.6</v>
       </c>
       <c r="I192" s="4"/>
       <c r="P192" s="6"/>
     </row>
     <row r="193" spans="1:16">
-      <c r="A193" t="s">
-        <v>442</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C193" t="s">
+      <c r="A193" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B193" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="C193" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="D193" s="4">
-        <v>0</v>
+      <c r="D193" s="11">
+        <v>0.64</v>
       </c>
       <c r="E193">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H193">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="I193" s="4"/>
       <c r="P193" s="6"/>
     </row>
     <row r="194" spans="1:16">
-      <c r="A194" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="B194" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="C194" s="11" t="s">
+      <c r="A194" t="s">
+        <v>442</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C194" t="s">
         <v>348</v>
       </c>
-      <c r="D194" s="11">
-        <v>0.78</v>
+      <c r="D194" s="4">
+        <v>0</v>
       </c>
       <c r="E194">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H194">
-        <v>0.54</v>
+        <v>0.26</v>
       </c>
       <c r="I194" s="4"/>
       <c r="P194" s="6"/>
     </row>
     <row r="195" spans="1:16">
       <c r="A195" s="11" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B195" s="11" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C195" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D195" s="11">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="E195">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="H195">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="I195" s="4"/>
       <c r="P195" s="6"/>
     </row>
     <row r="196" spans="1:16">
       <c r="A196" s="11" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C196" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D196" s="11">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="E196">
-        <v>0.98</v>
+        <v>0.94</v>
       </c>
       <c r="H196">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="I196" s="4"/>
       <c r="P196" s="6"/>
     </row>
     <row r="197" spans="1:16">
       <c r="A197" s="11" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B197" s="11" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C197" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D197" s="11">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="E197">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="H197">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="I197" s="4"/>
       <c r="P197" s="6"/>
     </row>
     <row r="198" spans="1:16">
       <c r="A198" s="11" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C198" s="11" t="s">
         <v>348</v>
@@ -6879,7 +6909,7 @@
         <v>0.84</v>
       </c>
       <c r="E198">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H198">
         <v>0.67</v>
@@ -6889,647 +6919,648 @@
     </row>
     <row r="199" spans="1:16">
       <c r="A199" s="11" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C199" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D199" s="11">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="E199">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="H199">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="I199" s="4"/>
       <c r="P199" s="6"/>
     </row>
     <row r="200" spans="1:16">
       <c r="A200" s="11" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B200" s="11" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C200" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D200" s="11">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="E200">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H200">
-        <v>0.6</v>
+        <v>0.37</v>
       </c>
       <c r="I200" s="4"/>
       <c r="P200" s="6"/>
     </row>
     <row r="201" spans="1:16">
       <c r="A201" s="11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C201" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D201" s="11">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="E201">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H201">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="I201" s="4"/>
       <c r="P201" s="6"/>
     </row>
     <row r="202" spans="1:16">
       <c r="A202" s="11" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C202" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D202" s="11">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="E202">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H202">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="I202" s="4"/>
       <c r="P202" s="6"/>
     </row>
     <row r="203" spans="1:16">
-      <c r="A203" t="s">
-        <v>450</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C203" t="s">
+      <c r="A203" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="B203" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="C203" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="D203" s="4">
-        <v>0</v>
+      <c r="D203" s="11">
+        <v>0.85</v>
       </c>
       <c r="E203">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H203">
-        <v>0.46</v>
+        <v>0.37</v>
       </c>
       <c r="I203" s="4"/>
       <c r="P203" s="6"/>
     </row>
     <row r="204" spans="1:16">
-      <c r="A204" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="B204" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="C204" s="11" t="s">
+      <c r="A204" t="s">
+        <v>450</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C204" t="s">
         <v>348</v>
       </c>
-      <c r="D204" s="11">
-        <v>0.88</v>
+      <c r="D204" s="4">
+        <v>0</v>
       </c>
       <c r="E204">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="H204">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="I204" s="4"/>
       <c r="P204" s="6"/>
     </row>
     <row r="205" spans="1:16">
       <c r="A205" s="11" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C205" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D205" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="E205">
         <v>0.82</v>
       </c>
-      <c r="E205">
-        <v>0.97</v>
-      </c>
       <c r="H205">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="I205" s="4"/>
       <c r="P205" s="6"/>
     </row>
     <row r="206" spans="1:16">
       <c r="A206" s="11" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D206" s="11">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="E206">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="H206">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I206" s="4"/>
       <c r="P206" s="6"/>
     </row>
     <row r="207" spans="1:16">
       <c r="A207" s="11" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B207" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D207" s="11">
-        <v>0.59</v>
+        <v>0.76</v>
       </c>
       <c r="E207">
         <v>0.93</v>
       </c>
       <c r="H207">
-        <v>0.65</v>
+        <v>0.39</v>
       </c>
       <c r="I207" s="4"/>
       <c r="P207" s="6"/>
     </row>
     <row r="208" spans="1:16">
       <c r="A208" s="11" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D208" s="11">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
       <c r="E208">
         <v>0.93</v>
       </c>
       <c r="H208">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="I208" s="4"/>
       <c r="P208" s="6"/>
     </row>
     <row r="209" spans="1:16">
       <c r="A209" s="11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C209" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D209" s="11">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="E209">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H209">
-        <v>0.75</v>
+        <v>0.44</v>
       </c>
       <c r="I209" s="4"/>
       <c r="P209" s="6"/>
     </row>
     <row r="210" spans="1:16">
-      <c r="A210" t="s">
-        <v>444</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C210" t="s">
+      <c r="A210" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="B210" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="C210" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="D210" s="4">
-        <v>0</v>
+      <c r="D210" s="11">
+        <v>0.77</v>
       </c>
       <c r="E210">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="H210">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="I210" s="4"/>
       <c r="P210" s="6"/>
     </row>
     <row r="211" spans="1:16">
-      <c r="A211" s="11" t="s">
-        <v>395</v>
-      </c>
-      <c r="B211" s="11" t="s">
-        <v>396</v>
-      </c>
-      <c r="C211" s="11" t="s">
+      <c r="A211" t="s">
+        <v>444</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C211" t="s">
         <v>348</v>
       </c>
-      <c r="D211" s="11">
-        <v>0.75</v>
+      <c r="D211" s="4">
+        <v>0</v>
       </c>
       <c r="E211">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="H211">
-        <v>0.53</v>
+        <v>0.05</v>
       </c>
       <c r="I211" s="4"/>
       <c r="P211" s="6"/>
     </row>
     <row r="212" spans="1:16">
       <c r="A212" s="11" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C212" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D212" s="11">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="E212">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="H212">
-        <v>0.32</v>
+        <v>0.53</v>
       </c>
       <c r="I212" s="4"/>
       <c r="P212" s="6"/>
     </row>
     <row r="213" spans="1:16">
-      <c r="A213" t="s">
-        <v>448</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C213" t="s">
+      <c r="A213" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="B213" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="C213" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="D213" s="4">
-        <v>0</v>
+      <c r="D213" s="11">
+        <v>0.79</v>
       </c>
       <c r="E213">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="H213">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="I213" s="4"/>
       <c r="P213" s="6"/>
     </row>
     <row r="214" spans="1:16">
-      <c r="A214" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B214" s="11" t="s">
-        <v>400</v>
-      </c>
-      <c r="C214" s="11" t="s">
+      <c r="A214" t="s">
+        <v>448</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C214" t="s">
         <v>348</v>
       </c>
-      <c r="D214" s="11">
-        <v>0.74</v>
+      <c r="D214" s="4">
+        <v>0</v>
       </c>
       <c r="E214">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H214">
-        <v>0.68</v>
+        <v>0.44</v>
       </c>
       <c r="I214" s="4"/>
       <c r="P214" s="6"/>
     </row>
     <row r="215" spans="1:16">
       <c r="A215" s="11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B215" s="11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C215" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D215" s="11">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="E215">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="H215">
-        <v>0.56000000000000005</v>
+        <v>0.68</v>
       </c>
       <c r="I215" s="4"/>
       <c r="P215" s="6"/>
     </row>
     <row r="216" spans="1:16">
       <c r="A216" s="11" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C216" s="11" t="s">
         <v>348</v>
       </c>
       <c r="D216" s="11">
-        <v>0.94</v>
+        <v>0.62</v>
       </c>
       <c r="E216">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="H216">
-        <v>0.65</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I216" s="4"/>
       <c r="P216" s="6"/>
     </row>
     <row r="217" spans="1:16">
       <c r="A217" s="11" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B217" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C217" s="11" t="s">
-        <v>407</v>
+        <v>348</v>
       </c>
       <c r="D217" s="11">
-        <v>0.75</v>
+        <v>0.94</v>
       </c>
       <c r="E217">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="H217">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="I217" s="4"/>
       <c r="P217" s="6"/>
     </row>
     <row r="218" spans="1:16">
-      <c r="A218" s="11" t="s">
-        <v>408</v>
-      </c>
-      <c r="B218" s="11" t="s">
-        <v>409</v>
+      <c r="A218" s="23" t="s">
+        <v>405</v>
+      </c>
+      <c r="B218" s="23" t="s">
+        <v>406</v>
       </c>
       <c r="C218" s="11" t="s">
         <v>407</v>
       </c>
       <c r="D218" s="11">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="E218">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="H218">
-        <v>0.32</v>
+        <v>0.79</v>
       </c>
       <c r="I218" s="4"/>
       <c r="P218" s="6"/>
     </row>
     <row r="219" spans="1:16">
       <c r="A219" s="11" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C219" s="11" t="s">
         <v>407</v>
       </c>
       <c r="D219" s="11">
-        <v>0.69</v>
+        <v>0.61</v>
       </c>
       <c r="E219">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="H219">
-        <v>0.54</v>
+        <v>0.32</v>
       </c>
       <c r="I219" s="4"/>
       <c r="P219" s="6"/>
     </row>
     <row r="220" spans="1:16">
       <c r="A220" s="11" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B220" s="11" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C220" s="11" t="s">
         <v>407</v>
       </c>
       <c r="D220" s="11">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="E220">
-        <v>0.97</v>
+        <v>0.79</v>
       </c>
       <c r="H220">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="I220" s="4"/>
       <c r="P220" s="6"/>
     </row>
     <row r="221" spans="1:16">
       <c r="A221" s="11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B221" s="11" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C221" s="11" t="s">
         <v>407</v>
       </c>
       <c r="D221" s="11">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="E221">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="H221">
-        <v>0.54</v>
+        <v>0.11</v>
       </c>
       <c r="I221" s="4"/>
       <c r="P221" s="6"/>
     </row>
     <row r="222" spans="1:16">
       <c r="A222" s="11" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B222" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C222" s="11" t="s">
         <v>407</v>
       </c>
       <c r="D222" s="11">
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
       <c r="E222">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H222">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="I222" s="4"/>
       <c r="P222" s="6"/>
     </row>
     <row r="223" spans="1:16">
-      <c r="A223" t="s">
+      <c r="A223" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="B223" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="C223" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="D223" s="11">
+        <v>0.89</v>
+      </c>
+      <c r="E223">
+        <v>0.97</v>
+      </c>
+      <c r="H223">
+        <v>0.61</v>
+      </c>
+      <c r="I223" s="4"/>
+      <c r="P223" s="6"/>
+    </row>
+    <row r="224" spans="1:16">
+      <c r="A224" s="20" t="s">
         <v>460</v>
       </c>
-      <c r="B223" s="2" t="s">
+      <c r="B224" s="21" t="s">
         <v>461</v>
       </c>
-      <c r="C223" t="s">
+      <c r="C224" t="s">
         <v>420</v>
       </c>
-      <c r="D223" s="4">
+      <c r="D224" s="4">
         <v>0</v>
       </c>
-      <c r="E223">
+      <c r="E224">
         <v>0.88</v>
       </c>
-      <c r="H223">
+      <c r="H224">
         <v>0.33</v>
       </c>
-      <c r="I223" s="4"/>
-      <c r="P223" s="18"/>
-    </row>
-    <row r="224" spans="1:16">
-      <c r="A224" s="11" t="s">
+      <c r="I224" s="4"/>
+      <c r="P224" s="18"/>
+    </row>
+    <row r="225" spans="1:16">
+      <c r="A225" s="23" t="s">
         <v>418</v>
       </c>
-      <c r="B224" s="11" t="s">
+      <c r="B225" s="23" t="s">
         <v>419</v>
-      </c>
-      <c r="C224" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="D224" s="11">
-        <v>0.79</v>
-      </c>
-      <c r="E224">
-        <v>0.89</v>
-      </c>
-      <c r="H224">
-        <v>0.26</v>
-      </c>
-      <c r="I224" s="4"/>
-      <c r="P224" s="6"/>
-    </row>
-    <row r="225" spans="1:16">
-      <c r="A225" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="B225" s="11" t="s">
-        <v>422</v>
       </c>
       <c r="C225" s="11" t="s">
         <v>420</v>
       </c>
       <c r="D225" s="11">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="E225">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="H225">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="I225" s="4"/>
       <c r="P225" s="6"/>
     </row>
     <row r="226" spans="1:16">
-      <c r="A226" s="11" t="s">
-        <v>423</v>
-      </c>
-      <c r="B226" s="11" t="s">
-        <v>424</v>
+      <c r="A226" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="B226" s="23" t="s">
+        <v>422</v>
       </c>
       <c r="C226" s="11" t="s">
         <v>420</v>
       </c>
       <c r="D226" s="11">
-        <v>0.69</v>
+        <v>0.66</v>
       </c>
       <c r="E226">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="H226">
-        <v>0.28000000000000003</v>
+        <v>0.16</v>
       </c>
       <c r="I226" s="4"/>
       <c r="P226" s="6"/>
     </row>
     <row r="227" spans="1:16">
-      <c r="A227" t="s">
-        <v>464</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="C227" t="s">
+      <c r="A227" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="B227" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="C227" s="11" t="s">
         <v>420</v>
       </c>
-      <c r="D227" s="4">
-        <v>0</v>
+      <c r="D227" s="11">
+        <v>0.69</v>
       </c>
       <c r="E227">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="H227">
-        <v>0.16</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I227" s="4"/>
+      <c r="P227" s="22"/>
     </row>
     <row r="228" spans="1:16">
       <c r="A228" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C228" t="s">
         <v>420</v>
@@ -7538,193 +7569,196 @@
         <v>0</v>
       </c>
       <c r="E228">
+        <v>0.98</v>
+      </c>
+      <c r="H228">
+        <v>0.16</v>
+      </c>
+      <c r="I228" s="4"/>
+      <c r="P228" s="20"/>
+    </row>
+    <row r="229" spans="1:16">
+      <c r="A229" t="s">
+        <v>457</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C229" t="s">
+        <v>420</v>
+      </c>
+      <c r="D229" s="4">
+        <v>0</v>
+      </c>
+      <c r="E229">
         <v>0.94</v>
       </c>
-      <c r="H228">
+      <c r="H229">
         <v>0.26</v>
       </c>
-      <c r="I228" s="4"/>
-    </row>
-    <row r="229" spans="1:16">
-      <c r="A229" s="11" t="s">
-        <v>425</v>
-      </c>
-      <c r="B229" s="11" t="s">
-        <v>426</v>
-      </c>
-      <c r="C229" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="D229" s="11">
-        <v>0.83</v>
-      </c>
-      <c r="E229">
-        <v>0.9</v>
-      </c>
-      <c r="H229">
-        <v>0.63</v>
-      </c>
       <c r="I229" s="4"/>
-      <c r="P229" s="19"/>
+      <c r="P229" s="20"/>
     </row>
     <row r="230" spans="1:16">
       <c r="A230" s="11" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B230" s="11" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C230" s="11" t="s">
         <v>420</v>
       </c>
       <c r="D230" s="11">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="E230">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="H230">
-        <v>0.26</v>
+        <v>0.63</v>
       </c>
       <c r="I230" s="4"/>
-      <c r="P230" s="19"/>
+      <c r="P230" s="22"/>
     </row>
     <row r="231" spans="1:16">
       <c r="A231" s="11" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B231" s="11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C231" s="11" t="s">
         <v>420</v>
       </c>
       <c r="D231" s="11">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="E231">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="H231">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="I231" s="4"/>
-      <c r="P231" s="19"/>
+      <c r="P231" s="22"/>
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="11" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B232" s="11" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C232" s="11" t="s">
         <v>420</v>
       </c>
       <c r="D232" s="11">
+        <v>0.81</v>
+      </c>
+      <c r="E232">
+        <v>0.92</v>
+      </c>
+      <c r="H232">
+        <v>0.67</v>
+      </c>
+      <c r="I232" s="4"/>
+      <c r="P232" s="22"/>
+    </row>
+    <row r="233" spans="1:16">
+      <c r="A233" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="B233" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C233" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="D233" s="11">
         <v>0.74</v>
       </c>
-      <c r="E232">
+      <c r="E233">
         <v>0.94</v>
       </c>
-      <c r="H232">
+      <c r="H233">
         <v>0.37</v>
       </c>
-      <c r="I232" s="4"/>
-      <c r="P232" s="19"/>
-    </row>
-    <row r="233" spans="1:16">
-      <c r="A233" t="s">
+      <c r="I233" s="4"/>
+      <c r="P233" s="22"/>
+    </row>
+    <row r="234" spans="1:16">
+      <c r="A234" t="s">
         <v>468</v>
       </c>
-      <c r="B233" s="2" t="s">
+      <c r="B234" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="C233" t="s">
+      <c r="C234" t="s">
         <v>420</v>
       </c>
-      <c r="D233" s="4">
+      <c r="D234" s="4">
         <v>0</v>
       </c>
-      <c r="E233">
+      <c r="E234">
         <v>0.91</v>
       </c>
-      <c r="H233">
+      <c r="H234">
         <v>0.35</v>
       </c>
-      <c r="I233" s="4"/>
-    </row>
-    <row r="234" spans="1:16">
-      <c r="A234" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B234" s="11" t="s">
-        <v>433</v>
-      </c>
-      <c r="C234" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="D234" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="E234">
-        <v>1</v>
-      </c>
-      <c r="H234">
-        <v>0.44</v>
-      </c>
       <c r="I234" s="4"/>
-      <c r="P234" s="19"/>
+      <c r="P234" s="20"/>
     </row>
     <row r="235" spans="1:16">
       <c r="A235" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B235" s="11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C235" s="11" t="s">
         <v>420</v>
       </c>
       <c r="D235" s="11">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="E235">
         <v>1</v>
       </c>
       <c r="H235">
+        <v>0.44</v>
+      </c>
+      <c r="I235" s="4"/>
+      <c r="P235" s="22"/>
+    </row>
+    <row r="236" spans="1:16">
+      <c r="A236" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B236" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="C236" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="D236" s="11">
+        <v>0.65</v>
+      </c>
+      <c r="E236">
+        <v>1</v>
+      </c>
+      <c r="H236">
         <v>0.63</v>
       </c>
-      <c r="I235" s="4"/>
-      <c r="P235" s="19"/>
-    </row>
-    <row r="236" spans="1:16">
-      <c r="A236" t="s">
-        <v>462</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C236" t="s">
-        <v>420</v>
-      </c>
-      <c r="D236" s="4">
-        <v>0</v>
-      </c>
-      <c r="E236">
-        <v>0.9</v>
-      </c>
-      <c r="H236">
-        <v>0.54</v>
-      </c>
       <c r="I236" s="4"/>
+      <c r="P236" s="22"/>
     </row>
     <row r="237" spans="1:16">
       <c r="A237" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C237" t="s">
         <v>420</v>
@@ -7736,16 +7770,17 @@
         <v>0.9</v>
       </c>
       <c r="H237">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="I237" s="4"/>
+      <c r="P237" s="20"/>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" t="s">
-        <v>165</v>
+        <v>466</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C238" t="s">
         <v>420</v>
@@ -7754,56 +7789,78 @@
         <v>0</v>
       </c>
       <c r="E238">
+        <v>0.9</v>
+      </c>
+      <c r="H238">
+        <v>0.42</v>
+      </c>
+      <c r="I238" s="4"/>
+      <c r="P238" s="20"/>
+    </row>
+    <row r="239" spans="1:16">
+      <c r="A239" t="s">
+        <v>165</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C239" t="s">
+        <v>420</v>
+      </c>
+      <c r="D239" s="4">
+        <v>0</v>
+      </c>
+      <c r="E239">
         <v>1</v>
       </c>
-      <c r="H238">
+      <c r="H239">
         <v>0.49</v>
       </c>
-      <c r="I238" s="4"/>
-    </row>
-    <row r="239" spans="1:16">
-      <c r="A239" s="11" t="s">
-        <v>435</v>
-      </c>
-      <c r="B239" s="11" t="s">
-        <v>436</v>
-      </c>
-      <c r="C239" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="D239" s="11">
-        <v>0.87</v>
-      </c>
-      <c r="E239">
-        <v>0.84</v>
-      </c>
-      <c r="H239">
-        <v>0.47</v>
-      </c>
       <c r="I239" s="4"/>
-      <c r="P239" s="19"/>
     </row>
     <row r="240" spans="1:16">
       <c r="A240" s="11" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B240" s="11" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C240" s="11" t="s">
         <v>420</v>
       </c>
       <c r="D240" s="11">
-        <v>0.7</v>
+        <v>0.87</v>
       </c>
       <c r="E240">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="H240">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="I240" s="4"/>
       <c r="P240" s="19"/>
+    </row>
+    <row r="241" spans="1:16">
+      <c r="A241" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="B241" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="C241" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="D241" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="E241">
+        <v>0.89</v>
+      </c>
+      <c r="H241">
+        <v>0.19</v>
+      </c>
+      <c r="I241" s="4"/>
+      <c r="P241" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99F7B1B-F643-2E4D-BF9B-FCEF5B7A85E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C5B1E7-BE34-1F49-A99F-C76C0CAC241C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2163,7 +2163,7 @@
         <v>0.89</v>
       </c>
       <c r="I2" s="5">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="L2">
         <v>0.48</v>
@@ -7354,7 +7354,9 @@
       <c r="H218">
         <v>0.79</v>
       </c>
-      <c r="I218" s="4"/>
+      <c r="I218" s="4">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="P218" s="6"/>
     </row>
     <row r="219" spans="1:16">
@@ -7376,7 +7378,9 @@
       <c r="H219">
         <v>0.32</v>
       </c>
-      <c r="I219" s="4"/>
+      <c r="I219" s="4">
+        <v>0.1</v>
+      </c>
       <c r="P219" s="6"/>
     </row>
     <row r="220" spans="1:16">
@@ -7398,7 +7402,9 @@
       <c r="H220">
         <v>0.54</v>
       </c>
-      <c r="I220" s="4"/>
+      <c r="I220" s="4">
+        <v>0.43</v>
+      </c>
       <c r="P220" s="6"/>
     </row>
     <row r="221" spans="1:16">
@@ -7420,7 +7426,9 @@
       <c r="H221">
         <v>0.11</v>
       </c>
-      <c r="I221" s="4"/>
+      <c r="I221" s="4">
+        <v>0.21</v>
+      </c>
       <c r="P221" s="6"/>
     </row>
     <row r="222" spans="1:16">
@@ -7442,7 +7450,9 @@
       <c r="H222">
         <v>0.54</v>
       </c>
-      <c r="I222" s="4"/>
+      <c r="I222" s="4">
+        <v>0.7</v>
+      </c>
       <c r="P222" s="6"/>
     </row>
     <row r="223" spans="1:16">
@@ -7464,7 +7474,9 @@
       <c r="H223">
         <v>0.61</v>
       </c>
-      <c r="I223" s="4"/>
+      <c r="I223" s="4">
+        <v>0.34</v>
+      </c>
       <c r="P223" s="6"/>
     </row>
     <row r="224" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C5B1E7-BE34-1F49-A99F-C76C0CAC241C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F12CE0-0B5E-7448-A004-0E9357918B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4948,7 +4948,9 @@
       <c r="H109">
         <v>0.39</v>
       </c>
-      <c r="I109" s="4"/>
+      <c r="I109" s="4">
+        <v>0.31</v>
+      </c>
       <c r="P109" s="6"/>
     </row>
     <row r="110" spans="1:16">
@@ -5036,7 +5038,9 @@
       <c r="H113">
         <v>0.46</v>
       </c>
-      <c r="I113" s="4"/>
+      <c r="I113" s="4">
+        <v>0.46</v>
+      </c>
       <c r="P113" s="6"/>
     </row>
     <row r="114" spans="1:16">
@@ -5148,7 +5152,9 @@
       <c r="H118">
         <v>0.44</v>
       </c>
-      <c r="I118" s="4"/>
+      <c r="I118" s="4">
+        <v>0.84</v>
+      </c>
       <c r="P118" s="6"/>
     </row>
     <row r="119" spans="1:16">
@@ -5192,7 +5198,9 @@
       <c r="H120">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I120" s="4"/>
+      <c r="I120" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="P120" s="18"/>
     </row>
     <row r="121" spans="1:16">
@@ -5236,7 +5244,9 @@
       <c r="H122">
         <v>0.26</v>
       </c>
-      <c r="I122" s="4"/>
+      <c r="I122" s="4">
+        <v>0.75</v>
+      </c>
       <c r="P122" s="6"/>
     </row>
     <row r="123" spans="1:16">
@@ -5258,7 +5268,9 @@
       <c r="H123">
         <v>0.26</v>
       </c>
-      <c r="I123" s="4"/>
+      <c r="I123" s="4">
+        <v>0.69</v>
+      </c>
       <c r="P123" s="6"/>
     </row>
     <row r="124" spans="1:16">
@@ -5302,7 +5314,9 @@
       <c r="H125">
         <v>0.49</v>
       </c>
-      <c r="I125" s="4"/>
+      <c r="I125" s="4">
+        <v>0.42</v>
+      </c>
       <c r="P125" s="6"/>
     </row>
     <row r="126" spans="1:16">
@@ -5436,7 +5450,9 @@
       <c r="H131">
         <v>0.28000000000000003</v>
       </c>
-      <c r="I131" s="4"/>
+      <c r="I131" s="4">
+        <v>0.64</v>
+      </c>
       <c r="P131" s="6"/>
     </row>
     <row r="132" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F12CE0-0B5E-7448-A004-0E9357918B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C8A8F8-BC0D-D445-BA8D-D9E1F04B59F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="960" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="260" yWindow="960" windowWidth="35680" windowHeight="19280" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -1664,7 +1663,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1691,13 +1690,6 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3401,10 +3393,10 @@
       <c r="P48" s="6"/>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="B49" s="11" t="s">
         <v>92</v>
       </c>
       <c r="C49" s="11" t="s">
@@ -3425,10 +3417,10 @@
       <c r="P49" s="6"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="23" t="s">
+      <c r="A50" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="23" t="s">
+      <c r="B50" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C50" s="11" t="s">
@@ -3452,10 +3444,10 @@
       <c r="P50" s="6"/>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="11" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="11" t="s">
@@ -3479,10 +3471,10 @@
       <c r="P51" s="6"/>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="23" t="s">
+      <c r="A52" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="23" t="s">
+      <c r="B52" s="11" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="11" t="s">
@@ -3506,10 +3498,10 @@
       <c r="P52" s="6"/>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="23" t="s">
+      <c r="A53" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C53" s="11" t="s">
@@ -3533,10 +3525,10 @@
       <c r="P53" s="6"/>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="11" t="s">
@@ -3560,10 +3552,10 @@
       <c r="P54" s="6"/>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="11" t="s">
         <v>476</v>
       </c>
       <c r="C55" s="11" t="s">
@@ -3587,10 +3579,10 @@
       <c r="P55" s="6"/>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="B56" s="11" t="s">
         <v>106</v>
       </c>
       <c r="C56" s="11" t="s">
@@ -3614,10 +3606,10 @@
       <c r="P56" s="6"/>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="23" t="s">
+      <c r="A57" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B57" s="23" t="s">
+      <c r="B57" s="11" t="s">
         <v>108</v>
       </c>
       <c r="C57" s="11" t="s">
@@ -4487,10 +4479,10 @@
       <c r="P89" s="6"/>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="23" t="s">
+      <c r="A90" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="B90" s="23" t="s">
+      <c r="B90" s="11" t="s">
         <v>172</v>
       </c>
       <c r="C90" s="11" t="s">
@@ -4511,10 +4503,10 @@
       <c r="P90" s="6"/>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="23" t="s">
+      <c r="A91" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="B91" s="23" t="s">
+      <c r="B91" s="11" t="s">
         <v>175</v>
       </c>
       <c r="C91" s="11" t="s">
@@ -4535,10 +4527,10 @@
       <c r="P91" s="6"/>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" s="20" t="s">
+      <c r="A92" t="s">
         <v>474</v>
       </c>
-      <c r="B92" s="21" t="s">
+      <c r="B92" s="2" t="s">
         <v>475</v>
       </c>
       <c r="C92" t="s">
@@ -4557,10 +4549,10 @@
       <c r="P92" s="18"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="23" t="s">
+      <c r="A93" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="B93" s="23" t="s">
+      <c r="B93" s="11" t="s">
         <v>177</v>
       </c>
       <c r="C93" s="11" t="s">
@@ -4579,10 +4571,10 @@
       <c r="P93" s="6"/>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="23" t="s">
+      <c r="A94" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B94" s="23" t="s">
+      <c r="B94" s="11" t="s">
         <v>179</v>
       </c>
       <c r="C94" s="11" t="s">
@@ -4603,10 +4595,10 @@
       <c r="P94" s="6"/>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="23" t="s">
+      <c r="A95" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B95" s="23" t="s">
+      <c r="B95" s="11" t="s">
         <v>181</v>
       </c>
       <c r="C95" s="11" t="s">
@@ -4627,10 +4619,10 @@
       <c r="P95" s="6"/>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="23" t="s">
+      <c r="A96" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B96" s="23" t="s">
+      <c r="B96" s="11" t="s">
         <v>183</v>
       </c>
       <c r="C96" s="11" t="s">
@@ -4651,10 +4643,10 @@
       <c r="P96" s="6"/>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="23" t="s">
+      <c r="A97" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="B97" s="23" t="s">
+      <c r="B97" s="11" t="s">
         <v>185</v>
       </c>
       <c r="C97" s="11" t="s">
@@ -4972,7 +4964,9 @@
       <c r="H110">
         <v>0.75</v>
       </c>
-      <c r="I110" s="4"/>
+      <c r="I110" s="4">
+        <v>0.66</v>
+      </c>
       <c r="P110" s="6"/>
     </row>
     <row r="111" spans="1:16">
@@ -5016,7 +5010,9 @@
       <c r="H112">
         <v>0.26</v>
       </c>
-      <c r="I112" s="4"/>
+      <c r="I112" s="4">
+        <v>0.67</v>
+      </c>
       <c r="P112" s="6"/>
     </row>
     <row r="113" spans="1:16">
@@ -5338,7 +5334,9 @@
       <c r="H126">
         <v>0.74</v>
       </c>
-      <c r="I126" s="4"/>
+      <c r="I126" s="4">
+        <v>0.78</v>
+      </c>
       <c r="P126" s="6"/>
     </row>
     <row r="127" spans="1:16">
@@ -5360,7 +5358,9 @@
       <c r="H127">
         <v>0.26</v>
       </c>
-      <c r="I127" s="4"/>
+      <c r="I127" s="4">
+        <v>0.36</v>
+      </c>
       <c r="P127" s="6"/>
     </row>
     <row r="128" spans="1:16">
@@ -5406,7 +5406,9 @@
       <c r="H129">
         <v>0.11</v>
       </c>
-      <c r="I129" s="4"/>
+      <c r="I129" s="4">
+        <v>0.13</v>
+      </c>
       <c r="P129" s="6"/>
     </row>
     <row r="130" spans="1:16">
@@ -5474,7 +5476,9 @@
       <c r="H132">
         <v>0.47</v>
       </c>
-      <c r="I132" s="4"/>
+      <c r="I132" s="4">
+        <v>0.39</v>
+      </c>
       <c r="P132" s="6"/>
     </row>
     <row r="133" spans="1:16">
@@ -5500,10 +5504,10 @@
       <c r="P133" s="6"/>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="23" t="s">
+      <c r="A134" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="B134" s="23" t="s">
+      <c r="B134" s="11" t="s">
         <v>251</v>
       </c>
       <c r="C134" s="11" t="s">
@@ -5522,10 +5526,10 @@
       <c r="P134" s="6"/>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" s="23" t="s">
+      <c r="A135" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="B135" s="23" t="s">
+      <c r="B135" s="11" t="s">
         <v>254</v>
       </c>
       <c r="C135" s="11" t="s">
@@ -5544,10 +5548,10 @@
       <c r="P135" s="6"/>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="23" t="s">
+      <c r="A136" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="B136" s="23" t="s">
+      <c r="B136" s="11" t="s">
         <v>256</v>
       </c>
       <c r="C136" s="11" t="s">
@@ -5566,10 +5570,10 @@
       <c r="P136" s="6"/>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="23" t="s">
+      <c r="A137" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B137" s="23" t="s">
+      <c r="B137" s="11" t="s">
         <v>258</v>
       </c>
       <c r="C137" s="11" t="s">
@@ -5588,10 +5592,10 @@
       <c r="P137" s="6"/>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="23" t="s">
+      <c r="A138" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="B138" s="23" t="s">
+      <c r="B138" s="11" t="s">
         <v>260</v>
       </c>
       <c r="C138" s="11" t="s">
@@ -5610,10 +5614,10 @@
       <c r="P138" s="6"/>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="23" t="s">
+      <c r="A139" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="B139" s="23" t="s">
+      <c r="B139" s="11" t="s">
         <v>262</v>
       </c>
       <c r="C139" s="11" t="s">
@@ -5632,10 +5636,10 @@
       <c r="P139" s="6"/>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" s="23" t="s">
+      <c r="A140" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="B140" s="23" t="s">
+      <c r="B140" s="11" t="s">
         <v>264</v>
       </c>
       <c r="C140" s="11" t="s">
@@ -5654,10 +5658,10 @@
       <c r="P140" s="6"/>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="23" t="s">
+      <c r="A141" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="B141" s="23" t="s">
+      <c r="B141" s="11" t="s">
         <v>266</v>
       </c>
       <c r="C141" s="11" t="s">
@@ -5676,10 +5680,10 @@
       <c r="P141" s="6"/>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="23" t="s">
+      <c r="A142" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="B142" s="23" t="s">
+      <c r="B142" s="11" t="s">
         <v>268</v>
       </c>
       <c r="C142" s="11" t="s">
@@ -5698,10 +5702,10 @@
       <c r="P142" s="6"/>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="23" t="s">
+      <c r="A143" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="B143" s="23" t="s">
+      <c r="B143" s="11" t="s">
         <v>270</v>
       </c>
       <c r="C143" s="11" t="s">
@@ -5720,10 +5724,10 @@
       <c r="P143" s="6"/>
     </row>
     <row r="144" spans="1:16">
-      <c r="A144" s="23" t="s">
+      <c r="A144" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B144" s="23" t="s">
+      <c r="B144" s="11" t="s">
         <v>271</v>
       </c>
       <c r="C144" s="11" t="s">
@@ -5784,7 +5788,9 @@
       <c r="H146">
         <v>0.4</v>
       </c>
-      <c r="I146" s="4"/>
+      <c r="I146" s="4">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P146" s="6"/>
     </row>
     <row r="147" spans="1:16">
@@ -6092,7 +6098,9 @@
       <c r="H160">
         <v>0.42</v>
       </c>
-      <c r="I160" s="4"/>
+      <c r="I160" s="4">
+        <v>0.31</v>
+      </c>
       <c r="P160" s="6"/>
     </row>
     <row r="161" spans="1:16">
@@ -6604,10 +6612,10 @@
       <c r="P183" s="6"/>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" s="23" t="s">
+      <c r="A184" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="B184" s="23" t="s">
+      <c r="B184" s="11" t="s">
         <v>347</v>
       </c>
       <c r="C184" s="11" t="s">
@@ -6626,10 +6634,10 @@
       <c r="P184" s="6"/>
     </row>
     <row r="185" spans="1:16">
-      <c r="A185" s="20" t="s">
+      <c r="A185" t="s">
         <v>446</v>
       </c>
-      <c r="B185" s="24" t="s">
+      <c r="B185" s="3" t="s">
         <v>447</v>
       </c>
       <c r="C185" t="s">
@@ -6648,10 +6656,10 @@
       <c r="P185" s="6"/>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" s="23" t="s">
+      <c r="A186" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B186" s="23" t="s">
+      <c r="B186" s="11" t="s">
         <v>350</v>
       </c>
       <c r="C186" s="11" t="s">
@@ -7352,10 +7360,10 @@
       <c r="P217" s="6"/>
     </row>
     <row r="218" spans="1:16">
-      <c r="A218" s="23" t="s">
+      <c r="A218" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="B218" s="23" t="s">
+      <c r="B218" s="11" t="s">
         <v>406</v>
       </c>
       <c r="C218" s="11" t="s">
@@ -7496,10 +7504,10 @@
       <c r="P223" s="6"/>
     </row>
     <row r="224" spans="1:16">
-      <c r="A224" s="20" t="s">
+      <c r="A224" t="s">
         <v>460</v>
       </c>
-      <c r="B224" s="21" t="s">
+      <c r="B224" s="2" t="s">
         <v>461</v>
       </c>
       <c r="C224" t="s">
@@ -7518,10 +7526,10 @@
       <c r="P224" s="18"/>
     </row>
     <row r="225" spans="1:16">
-      <c r="A225" s="23" t="s">
+      <c r="A225" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="B225" s="23" t="s">
+      <c r="B225" s="11" t="s">
         <v>419</v>
       </c>
       <c r="C225" s="11" t="s">
@@ -7540,10 +7548,10 @@
       <c r="P225" s="6"/>
     </row>
     <row r="226" spans="1:16">
-      <c r="A226" s="23" t="s">
+      <c r="A226" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="B226" s="23" t="s">
+      <c r="B226" s="11" t="s">
         <v>422</v>
       </c>
       <c r="C226" s="11" t="s">
@@ -7581,7 +7589,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="I227" s="4"/>
-      <c r="P227" s="22"/>
+      <c r="P227" s="19"/>
     </row>
     <row r="228" spans="1:16">
       <c r="A228" t="s">
@@ -7603,7 +7611,6 @@
         <v>0.16</v>
       </c>
       <c r="I228" s="4"/>
-      <c r="P228" s="20"/>
     </row>
     <row r="229" spans="1:16">
       <c r="A229" t="s">
@@ -7625,7 +7632,6 @@
         <v>0.26</v>
       </c>
       <c r="I229" s="4"/>
-      <c r="P229" s="20"/>
     </row>
     <row r="230" spans="1:16">
       <c r="A230" s="11" t="s">
@@ -7647,7 +7653,7 @@
         <v>0.63</v>
       </c>
       <c r="I230" s="4"/>
-      <c r="P230" s="22"/>
+      <c r="P230" s="19"/>
     </row>
     <row r="231" spans="1:16">
       <c r="A231" s="11" t="s">
@@ -7669,7 +7675,7 @@
         <v>0.26</v>
       </c>
       <c r="I231" s="4"/>
-      <c r="P231" s="22"/>
+      <c r="P231" s="19"/>
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="11" t="s">
@@ -7691,7 +7697,7 @@
         <v>0.67</v>
       </c>
       <c r="I232" s="4"/>
-      <c r="P232" s="22"/>
+      <c r="P232" s="19"/>
     </row>
     <row r="233" spans="1:16">
       <c r="A233" s="11" t="s">
@@ -7713,7 +7719,7 @@
         <v>0.37</v>
       </c>
       <c r="I233" s="4"/>
-      <c r="P233" s="22"/>
+      <c r="P233" s="19"/>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" t="s">
@@ -7735,7 +7741,6 @@
         <v>0.35</v>
       </c>
       <c r="I234" s="4"/>
-      <c r="P234" s="20"/>
     </row>
     <row r="235" spans="1:16">
       <c r="A235" s="11" t="s">
@@ -7757,7 +7762,7 @@
         <v>0.44</v>
       </c>
       <c r="I235" s="4"/>
-      <c r="P235" s="22"/>
+      <c r="P235" s="19"/>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="11" t="s">
@@ -7779,7 +7784,7 @@
         <v>0.63</v>
       </c>
       <c r="I236" s="4"/>
-      <c r="P236" s="22"/>
+      <c r="P236" s="19"/>
     </row>
     <row r="237" spans="1:16">
       <c r="A237" t="s">
@@ -7801,7 +7806,6 @@
         <v>0.54</v>
       </c>
       <c r="I237" s="4"/>
-      <c r="P237" s="20"/>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" t="s">
@@ -7823,7 +7827,6 @@
         <v>0.42</v>
       </c>
       <c r="I238" s="4"/>
-      <c r="P238" s="20"/>
     </row>
     <row r="239" spans="1:16">
       <c r="A239" t="s">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C8A8F8-BC0D-D445-BA8D-D9E1F04B59F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACB0064-062B-D44B-90E5-67E10B3A5A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="35680" windowHeight="19280" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4567,7 +4567,9 @@
       <c r="H93">
         <v>0.47</v>
       </c>
-      <c r="I93" s="4"/>
+      <c r="I93" s="4">
+        <v>0.67</v>
+      </c>
       <c r="P93" s="6"/>
     </row>
     <row r="94" spans="1:16">
@@ -5058,7 +5060,9 @@
       <c r="H114">
         <v>0.42</v>
       </c>
-      <c r="I114" s="4"/>
+      <c r="I114" s="4">
+        <v>0.43</v>
+      </c>
       <c r="P114" s="6"/>
     </row>
     <row r="115" spans="1:16">
@@ -5218,7 +5222,9 @@
       <c r="H121">
         <v>0.26</v>
       </c>
-      <c r="I121" s="4"/>
+      <c r="I121" s="4">
+        <v>0.52</v>
+      </c>
       <c r="P121" s="6"/>
     </row>
     <row r="122" spans="1:16">
@@ -5430,7 +5436,9 @@
       <c r="H130">
         <v>0.65</v>
       </c>
-      <c r="I130" s="4"/>
+      <c r="I130" s="4">
+        <v>0.82</v>
+      </c>
       <c r="P130" s="6"/>
     </row>
     <row r="131" spans="1:16">
@@ -5500,7 +5508,9 @@
       <c r="H133">
         <v>0.35</v>
       </c>
-      <c r="I133" s="4"/>
+      <c r="I133" s="4">
+        <v>0.42</v>
+      </c>
       <c r="P133" s="6"/>
     </row>
     <row r="134" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACB0064-062B-D44B-90E5-67E10B3A5A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B401D8-0DB6-1B44-AF20-0BF06D074439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="35680" windowHeight="19280" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4545,7 +4545,9 @@
       <c r="H92">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I92" s="4"/>
+      <c r="I92" s="4">
+        <v>0.06</v>
+      </c>
       <c r="P92" s="18"/>
     </row>
     <row r="93" spans="1:16">
@@ -4706,7 +4708,9 @@
       <c r="H99">
         <v>0.72</v>
       </c>
-      <c r="I99" s="4"/>
+      <c r="I99" s="4">
+        <v>0.84</v>
+      </c>
       <c r="P99" s="6"/>
     </row>
     <row r="100" spans="1:16">
@@ -4728,7 +4732,9 @@
       <c r="H100">
         <v>0.28000000000000003</v>
       </c>
-      <c r="I100" s="4"/>
+      <c r="I100" s="4">
+        <v>0.76</v>
+      </c>
       <c r="P100" s="6"/>
     </row>
     <row r="101" spans="1:16">
@@ -4990,7 +4996,9 @@
       <c r="H111">
         <v>0.61</v>
       </c>
-      <c r="I111" s="4"/>
+      <c r="I111" s="4">
+        <v>0.66</v>
+      </c>
       <c r="P111" s="6"/>
     </row>
     <row r="112" spans="1:16">
@@ -5084,7 +5092,9 @@
       <c r="H115">
         <v>0.39</v>
       </c>
-      <c r="I115" s="4"/>
+      <c r="I115" s="4">
+        <v>0.63</v>
+      </c>
       <c r="P115" s="6"/>
     </row>
     <row r="116" spans="1:16">
@@ -5130,7 +5140,9 @@
       <c r="H117">
         <v>0.63</v>
       </c>
-      <c r="I117" s="4"/>
+      <c r="I117" s="4">
+        <v>0.48</v>
+      </c>
       <c r="P117" s="6"/>
     </row>
     <row r="118" spans="1:16">
@@ -5176,7 +5188,9 @@
       <c r="H119">
         <v>0.54</v>
       </c>
-      <c r="I119" s="4"/>
+      <c r="I119" s="4">
+        <v>0.51</v>
+      </c>
       <c r="P119" s="6"/>
     </row>
     <row r="120" spans="1:16">
@@ -5294,7 +5308,9 @@
       <c r="H124">
         <v>0.09</v>
       </c>
-      <c r="I124" s="4"/>
+      <c r="I124" s="4">
+        <v>0.42</v>
+      </c>
       <c r="P124" s="6"/>
     </row>
     <row r="125" spans="1:16">
@@ -5317,7 +5333,7 @@
         <v>0.49</v>
       </c>
       <c r="I125" s="4">
-        <v>0.42</v>
+        <v>0.18</v>
       </c>
       <c r="P125" s="6"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B401D8-0DB6-1B44-AF20-0BF06D074439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52505766-BE06-C142-B8A4-2C78D2352295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="960" windowWidth="35680" windowHeight="19280" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -5548,7 +5548,9 @@
       <c r="H134">
         <v>0.4</v>
       </c>
-      <c r="I134" s="4"/>
+      <c r="I134" s="4">
+        <v>0.25</v>
+      </c>
       <c r="P134" s="6"/>
     </row>
     <row r="135" spans="1:16">
@@ -5570,7 +5572,9 @@
       <c r="H135">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I135" s="4"/>
+      <c r="I135" s="4">
+        <v>0.61</v>
+      </c>
       <c r="P135" s="6"/>
     </row>
     <row r="136" spans="1:16">
@@ -5592,7 +5596,9 @@
       <c r="H136">
         <v>0.63</v>
       </c>
-      <c r="I136" s="4"/>
+      <c r="I136" s="4">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="P136" s="6"/>
     </row>
     <row r="137" spans="1:16">
@@ -5614,7 +5620,9 @@
       <c r="H137">
         <v>0.42</v>
       </c>
-      <c r="I137" s="4"/>
+      <c r="I137" s="4">
+        <v>0.27</v>
+      </c>
       <c r="P137" s="6"/>
     </row>
     <row r="138" spans="1:16">
@@ -5636,7 +5644,9 @@
       <c r="H138">
         <v>0.39</v>
       </c>
-      <c r="I138" s="4"/>
+      <c r="I138" s="4">
+        <v>0.22</v>
+      </c>
       <c r="P138" s="6"/>
     </row>
     <row r="139" spans="1:16">
@@ -5882,7 +5892,9 @@
       <c r="H149">
         <v>0.21</v>
       </c>
-      <c r="I149" s="4"/>
+      <c r="I149" s="4">
+        <v>0.66</v>
+      </c>
       <c r="P149" s="6"/>
     </row>
     <row r="150" spans="1:16">
@@ -5970,7 +5982,9 @@
       <c r="H153">
         <v>0.86</v>
       </c>
-      <c r="I153" s="4"/>
+      <c r="I153" s="4">
+        <v>0.81</v>
+      </c>
       <c r="P153" s="6"/>
     </row>
     <row r="154" spans="1:16">
@@ -6036,7 +6050,9 @@
       <c r="H156">
         <v>0.44</v>
       </c>
-      <c r="I156" s="4"/>
+      <c r="I156" s="4">
+        <v>0.27</v>
+      </c>
       <c r="P156" s="6"/>
     </row>
     <row r="157" spans="1:16">
@@ -6080,7 +6096,9 @@
       <c r="H158">
         <v>0.6</v>
       </c>
-      <c r="I158" s="4"/>
+      <c r="I158" s="4">
+        <v>0.31</v>
+      </c>
       <c r="P158" s="6"/>
     </row>
     <row r="159" spans="1:16">
@@ -6102,7 +6120,9 @@
       <c r="H159">
         <v>0.46</v>
       </c>
-      <c r="I159" s="4"/>
+      <c r="I159" s="4">
+        <v>0.18</v>
+      </c>
       <c r="P159" s="6"/>
     </row>
     <row r="160" spans="1:16">
@@ -6302,7 +6322,9 @@
       <c r="H168">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I168" s="4"/>
+      <c r="I168" s="4">
+        <v>0.78</v>
+      </c>
       <c r="P168" s="6"/>
     </row>
     <row r="169" spans="1:16">
@@ -6478,7 +6500,9 @@
       <c r="H176">
         <v>0.12</v>
       </c>
-      <c r="I176" s="4"/>
+      <c r="I176" s="4">
+        <v>0.24</v>
+      </c>
       <c r="P176" s="6"/>
     </row>
     <row r="177" spans="1:16">
@@ -6568,7 +6592,9 @@
       <c r="H180">
         <v>0.61</v>
       </c>
-      <c r="I180" s="4"/>
+      <c r="I180" s="4">
+        <v>0.48</v>
+      </c>
       <c r="P180" s="6"/>
     </row>
     <row r="181" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52505766-BE06-C142-B8A4-2C78D2352295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AAEFA5-A5A9-0A47-B1D1-F0C0D5CE9547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="960" windowWidth="35680" windowHeight="19280" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1663,13 +1663,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1680,7 +1678,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1690,16 +1687,66 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="14">
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1740,20 +1787,20 @@
   </sortState>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
-    <tableColumn id="2" xr3:uid="{F58DECFD-039A-A04B-8F5C-EAB87EBDF67E}" name="Reg" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{B367B5B8-26A8-004D-8405-A55D6B3FB2B6}" name="Dept"/>
-    <tableColumn id="4" xr3:uid="{248CFFC4-D566-4C47-A784-2D182108B777}" name="Q_1" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{4A2A2B68-EF30-7742-9921-AE9C8CB19994}" name="Q_2"/>
-    <tableColumn id="6" xr3:uid="{F4845CBF-1A2D-6F4D-8189-BDA9FF51FC40}" name="Q_3"/>
-    <tableColumn id="14" xr3:uid="{EB0128D0-EDEA-7E4E-BB55-3B322034409A}" name="Q_4"/>
-    <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="T_1"/>
-    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="T_2 " dataDxfId="0"/>
-    <tableColumn id="9" xr3:uid="{AF37A560-C5F8-4E49-A224-CE84A49E046A}" name="T_3 "/>
-    <tableColumn id="15" xr3:uid="{2B895D50-2C68-B148-81D6-7366E82004E7}" name="T_4"/>
-    <tableColumn id="10" xr3:uid="{E7DCE493-9761-F446-9017-EFE5CA173E6F}" name="AS_1"/>
-    <tableColumn id="11" xr3:uid="{22CC7E9A-51CA-274B-9C92-B1E8F88F4324}" name="AS_2 "/>
-    <tableColumn id="12" xr3:uid="{912F9A7A-D63B-9A42-91A4-38F3D4DCB1F9}" name="AS_3"/>
-    <tableColumn id="16" xr3:uid="{76DF5A99-15E2-F344-AF5E-3F2B5447E9FE}" name="AS_4"/>
+    <tableColumn id="2" xr3:uid="{F58DECFD-039A-A04B-8F5C-EAB87EBDF67E}" name="Reg" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B367B5B8-26A8-004D-8405-A55D6B3FB2B6}" name="Dept" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{248CFFC4-D566-4C47-A784-2D182108B777}" name="Q_1" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{4A2A2B68-EF30-7742-9921-AE9C8CB19994}" name="Q_2" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{F4845CBF-1A2D-6F4D-8189-BDA9FF51FC40}" name="Q_3" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{EB0128D0-EDEA-7E4E-BB55-3B322034409A}" name="Q_4" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="T_1" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="T_2 " dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{AF37A560-C5F8-4E49-A224-CE84A49E046A}" name="T_3 " dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{2B895D50-2C68-B148-81D6-7366E82004E7}" name="T_4" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{E7DCE493-9761-F446-9017-EFE5CA173E6F}" name="AS_1" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{22CC7E9A-51CA-274B-9C92-B1E8F88F4324}" name="AS_2 " dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{912F9A7A-D63B-9A42-91A4-38F3D4DCB1F9}" name="AS_3" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{76DF5A99-15E2-F344-AF5E-3F2B5447E9FE}" name="AS_4" dataDxfId="0"/>
     <tableColumn id="13" xr3:uid="{C1D2D2AB-5806-CA4E-9587-399F7BCCF779}" name="CW"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2082,7 +2129,9 @@
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="4"/>
+    <col min="3" max="7" width="10.7109375" style="17"/>
+    <col min="8" max="8" width="10.7109375" style="20"/>
+    <col min="9" max="15" width="10.7109375" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2092,43 +2141,43 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="17" t="s">
         <v>488</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="17" t="s">
         <v>489</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="17" t="s">
         <v>490</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="20" t="s">
         <v>491</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="17" t="s">
         <v>485</v>
       </c>
       <c r="P1" t="s">
@@ -2136,1105 +2185,1105 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="20">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="17">
         <v>0.99</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="17">
         <v>0.89</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="21">
         <v>0.76</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="17">
         <v>0.48</v>
       </c>
-      <c r="P2" s="6"/>
+      <c r="P2" s="4"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="20">
         <v>0.86</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="17">
         <v>0.94</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="17">
         <v>0.39</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="21">
         <v>0.22</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="17">
         <v>0.68</v>
       </c>
-      <c r="P3" s="6"/>
+      <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="20">
         <v>0.79</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="17">
         <v>0.94</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="17">
         <v>0.39</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="21">
         <v>0.31</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="17">
         <v>0.48</v>
       </c>
-      <c r="P4" s="6"/>
+      <c r="P4" s="4"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="20">
         <v>0.75</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="17">
         <v>0</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="17">
         <v>0.54</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="21">
         <v>0.16</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="17">
         <v>0.48</v>
       </c>
-      <c r="P5" s="6"/>
+      <c r="P5" s="4"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="20">
         <v>0.64</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="17">
         <v>0.91</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="17">
         <v>0.53</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="21">
         <v>0.25</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="17">
         <v>0.48</v>
       </c>
-      <c r="P6" s="6"/>
+      <c r="P6" s="4"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="20">
         <v>0.82</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="17">
         <v>0.94</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="17">
         <v>0.42</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="21">
         <v>0.25</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="17">
         <v>0.48</v>
       </c>
-      <c r="P7" s="6"/>
+      <c r="P7" s="4"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="20">
         <v>0</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="17">
         <v>0</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="17">
         <v>0.11</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="21">
         <v>0.21</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="17">
         <v>0.8</v>
       </c>
-      <c r="P8" s="6"/>
+      <c r="P8" s="4"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="20">
         <v>0.75</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="17">
         <v>0.93</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="17">
         <v>0.47</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="21">
         <v>0.18</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="17">
         <v>0.68</v>
       </c>
-      <c r="P9" s="6"/>
+      <c r="P9" s="4"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="20">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="17">
         <v>0.9</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="17">
         <v>0.54</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="21">
         <v>0.48</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="17">
         <v>0.48</v>
       </c>
-      <c r="P10" s="6"/>
+      <c r="P10" s="4"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="20">
         <v>0.76</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="17">
         <v>0.95</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="17">
         <v>0.16</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="21">
         <v>0.31</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="17">
         <v>0.48</v>
       </c>
-      <c r="P11" s="6"/>
+      <c r="P11" s="4"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="20">
         <v>0.79</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="17">
         <v>0.7</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="17">
         <v>0.44</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="21">
         <v>0.33</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="17">
         <v>0.48</v>
       </c>
-      <c r="P12" s="6"/>
+      <c r="P12" s="4"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="20">
         <v>0.75</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="17">
         <v>0.94</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="17">
         <v>0.44</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="21">
         <v>0.3</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="17">
         <v>0.48</v>
       </c>
-      <c r="P13" s="6"/>
+      <c r="P13" s="4"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="20">
         <v>0.74</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="17">
         <v>0.82</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="17">
         <v>0.4</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="21">
         <v>0.22</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="17">
         <v>0.48</v>
       </c>
-      <c r="P14" s="6"/>
+      <c r="P14" s="4"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="20">
         <v>0.75</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="17">
         <v>1</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="17">
         <v>0.67</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="21">
         <v>0.51</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="17">
         <v>0.68</v>
       </c>
-      <c r="P15" s="6"/>
+      <c r="P15" s="4"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="20">
         <v>0</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="17">
         <v>0.9</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="17">
         <v>0</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="21">
         <v>0.16</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="17">
         <v>0.48</v>
       </c>
-      <c r="P16" s="6"/>
+      <c r="P16" s="4"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="20">
         <v>0.72</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="17">
         <v>0.8</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="17">
         <v>0.37</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="21">
         <v>0</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="17">
         <v>0.48</v>
       </c>
-      <c r="P17" s="6"/>
+      <c r="P17" s="4"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="20">
         <v>0.68</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="17">
         <v>0.93</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="17">
         <v>0.44</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="21">
         <v>0.03</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="17">
         <v>0.48</v>
       </c>
-      <c r="P18" s="6"/>
+      <c r="P18" s="4"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="20">
         <v>0</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="17">
         <v>0</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="17">
         <v>0.53</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="20">
         <v>0</v>
       </c>
-      <c r="P19" s="18"/>
+      <c r="P19" s="15"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="20">
         <v>0.85</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="17">
         <v>0.92</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="17">
         <v>0.54</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="21">
         <v>0</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="17">
         <v>0.48</v>
       </c>
-      <c r="P20" s="6"/>
+      <c r="P20" s="4"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="20">
         <v>0.78</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="17">
         <v>0.92</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="17">
         <v>0.65</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="21">
         <v>0.3</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="17">
         <v>0.68</v>
       </c>
-      <c r="P21" s="6"/>
+      <c r="P21" s="4"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="20">
         <v>0.82</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="17">
         <v>0.92</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="17">
         <v>0.33</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="21">
         <v>0.16</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="17">
         <v>0.68</v>
       </c>
-      <c r="P22" s="6"/>
+      <c r="P22" s="4"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="20">
         <v>0.7</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="17">
         <v>0.93</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="17">
         <v>0.68</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="21">
         <v>0.22</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="17">
         <v>0.68</v>
       </c>
-      <c r="P23" s="6"/>
+      <c r="P23" s="4"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="20">
         <v>0.74</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="17">
         <v>0.93</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="17">
         <v>0.67</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="21">
         <v>0.1</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="17">
         <v>0.48</v>
       </c>
-      <c r="P24" s="6"/>
+      <c r="P24" s="4"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="20">
         <v>0.67</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="17">
         <v>0.9</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="17">
         <v>0.61</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="21">
         <v>0.37</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="17">
         <v>0.8</v>
       </c>
-      <c r="P25" s="6"/>
+      <c r="P25" s="4"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="20">
         <v>0.85</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="17">
         <v>0.95</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="17">
         <v>0.53</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="21">
         <v>0.46</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="17">
         <v>0.48</v>
       </c>
-      <c r="P26" s="6"/>
+      <c r="P26" s="4"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="20">
         <v>0.83</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="17">
         <v>0.94</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="17">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="21">
         <v>0.37</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="17">
         <v>0.8</v>
       </c>
-      <c r="P27" s="6"/>
+      <c r="P27" s="4"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="20">
         <v>0.77</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="17">
         <v>0.93</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="17">
         <v>0.63</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="21">
         <v>0.34</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="17">
         <v>0.48</v>
       </c>
-      <c r="P28" s="6"/>
+      <c r="P28" s="4"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="20">
         <v>0</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="17">
         <v>0.91</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="17">
         <v>0.75</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="21">
         <v>0.63</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="17">
         <v>0.8</v>
       </c>
-      <c r="P29" s="6"/>
+      <c r="P29" s="4"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="20">
         <v>0.86</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="17">
         <v>1</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="17">
         <v>0.35</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="21">
         <v>0</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="17">
         <v>0.48</v>
       </c>
-      <c r="P30" s="6"/>
+      <c r="P30" s="4"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="20">
         <v>0.79</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="17">
         <v>0.82</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="17">
         <v>0.6</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="21">
         <v>0.45</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="17">
         <v>0.24</v>
       </c>
-      <c r="P31" s="6"/>
+      <c r="P31" s="4"/>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="20">
         <v>0.84</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="17">
         <v>0.86</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="17">
         <v>0.47</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="21">
         <v>0.3</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="17">
         <v>0.8</v>
       </c>
-      <c r="P32" s="6"/>
+      <c r="P32" s="4"/>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="20">
         <v>0.81</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="17">
         <v>0.85</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="17">
         <v>0.54</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="21">
         <v>0.31</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="17">
         <v>0.8</v>
       </c>
-      <c r="P33" s="6"/>
+      <c r="P33" s="4"/>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="20">
         <v>0.65</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="17">
         <v>0.9</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="17">
         <v>0.16</v>
       </c>
-      <c r="I34" s="4">
+      <c r="I34" s="20">
         <v>0.12</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="17">
         <v>0</v>
       </c>
-      <c r="P34" s="6"/>
+      <c r="P34" s="4"/>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="20">
         <v>0.84</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="17">
         <v>0.99</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="17">
         <v>0.42</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="21">
         <v>0.61</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="17">
         <v>0.24</v>
       </c>
-      <c r="P35" s="6"/>
+      <c r="P35" s="4"/>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="20">
         <v>0.66</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="17">
         <v>0.74</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="17">
         <v>0.47</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I36" s="20">
         <v>0.25</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="17">
         <v>0</v>
       </c>
-      <c r="P36" s="6"/>
+      <c r="P36" s="4"/>
     </row>
     <row r="37" spans="1:16" ht="20">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="20">
         <v>0</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="17">
         <v>0</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="17">
         <v>0.77</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="21">
         <v>0.27</v>
       </c>
-      <c r="L37">
+      <c r="L37" s="17">
         <v>0</v>
       </c>
-      <c r="P37" s="6"/>
+      <c r="P37" s="4"/>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="20">
         <v>0</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="17">
         <v>0</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="17">
         <v>0.52</v>
       </c>
-      <c r="I38" s="4">
+      <c r="I38" s="20">
         <v>0.24</v>
       </c>
-      <c r="P38" s="18"/>
+      <c r="P38" s="15"/>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="20">
         <v>0.73</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="17">
         <v>0.95</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="17">
         <v>0.6</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="21">
         <v>0.49</v>
       </c>
-      <c r="L39">
+      <c r="L39" s="17">
         <v>0.8</v>
       </c>
-      <c r="P39" s="6"/>
+      <c r="P39" s="4"/>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="20">
         <v>0.75</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="17">
         <v>0.94</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="17">
         <v>0.47</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="21">
         <v>0.22</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="17">
         <v>0.8</v>
       </c>
-      <c r="P40" s="6"/>
+      <c r="P40" s="4"/>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="20">
         <v>0.77</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="17">
         <v>0.89</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="17">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="21">
         <v>0.31</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="17">
         <v>0.24</v>
       </c>
-      <c r="P41" s="6"/>
+      <c r="P41" s="4"/>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="20">
         <v>0.7</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="17">
         <v>0.93</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="17">
         <v>0.33</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="21">
         <v>0.19</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="17">
         <v>0.24</v>
       </c>
-      <c r="P42" s="6"/>
+      <c r="P42" s="4"/>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" t="s">
@@ -3243,22 +3292,22 @@
       <c r="B43" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="20">
         <v>0</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="17">
         <v>0</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="17">
         <v>0.54</v>
       </c>
-      <c r="I43" s="4">
+      <c r="I43" s="20">
         <v>0.51</v>
       </c>
-      <c r="P43" s="18"/>
+      <c r="P43" s="15"/>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" t="s">
@@ -3267,1033 +3316,1033 @@
       <c r="B44" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="20">
         <v>0</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="17">
         <v>0</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="17">
         <v>0.65</v>
       </c>
-      <c r="I44" s="4">
+      <c r="I44" s="20">
         <v>0.18</v>
       </c>
-      <c r="P44" s="18"/>
+      <c r="P44" s="15"/>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="20">
         <v>0.64</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="17">
         <v>0.82</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="17">
         <v>0.44</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="21">
         <v>0.39</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="17">
         <v>0.8</v>
       </c>
-      <c r="P45" s="6"/>
+      <c r="P45" s="4"/>
     </row>
     <row r="46" spans="1:16">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="20">
         <v>0.77</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="17">
         <v>0.89</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="17">
         <v>0.44</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="21">
         <v>0.27</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="17">
         <v>0.24</v>
       </c>
-      <c r="P46" s="6"/>
+      <c r="P46" s="4"/>
     </row>
     <row r="47" spans="1:16">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="20">
         <v>0.91</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="17">
         <v>1</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="17">
         <v>0.54</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="21">
         <v>0.15</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="17">
         <v>0.24</v>
       </c>
-      <c r="P47" s="6"/>
+      <c r="P47" s="4"/>
     </row>
     <row r="48" spans="1:16">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="20">
         <v>0.67</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="17">
         <v>0.97</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="21">
         <v>0.54</v>
       </c>
-      <c r="L48">
+      <c r="L48" s="17">
         <v>0.8</v>
       </c>
-      <c r="P48" s="6"/>
+      <c r="P48" s="4"/>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="19">
         <v>0.79</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="17">
         <v>0.98</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="17">
         <v>0.68</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I49" s="21">
         <v>0.79</v>
       </c>
-      <c r="P49" s="6"/>
+      <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="19">
         <v>0.89</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="17">
         <v>0.91</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="17">
         <v>0.75</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I50" s="21">
         <v>0.56999999999999995</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="17">
         <v>0.63</v>
       </c>
-      <c r="P50" s="6"/>
+      <c r="P50" s="4"/>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="19">
         <v>0.9</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="17">
         <v>0.94</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="17">
         <v>0.6</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I51" s="21">
         <v>0.46</v>
       </c>
-      <c r="L51">
+      <c r="L51" s="17">
         <v>0.92</v>
       </c>
-      <c r="P51" s="6"/>
+      <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="19">
         <v>0.85</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="17">
         <v>0.99</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="17">
         <v>0.54</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I52" s="21">
         <v>0.51</v>
       </c>
-      <c r="L52">
+      <c r="L52" s="17">
         <v>0.83</v>
       </c>
-      <c r="P52" s="6"/>
+      <c r="P52" s="4"/>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="19">
         <v>0.85</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="17">
         <v>0.98</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="17">
         <v>0.6</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I53" s="21">
         <v>0.51</v>
       </c>
-      <c r="L53">
+      <c r="L53" s="17">
         <v>0.79</v>
       </c>
-      <c r="P53" s="6"/>
+      <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="19">
         <v>0.77</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="17">
         <v>0.88</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="17">
         <v>0.33</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I54" s="21">
         <v>0.4</v>
       </c>
-      <c r="L54">
+      <c r="L54" s="17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P54" s="6"/>
+      <c r="P54" s="4"/>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="19">
         <v>0.86</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="17">
         <v>0.97</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I55" s="21">
         <v>0.52</v>
       </c>
-      <c r="L55">
+      <c r="L55" s="17">
         <v>0.83</v>
       </c>
-      <c r="P55" s="6"/>
+      <c r="P55" s="4"/>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="19">
         <v>0.75</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="17">
         <v>0.98</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="17">
         <v>0.32</v>
       </c>
-      <c r="I56" s="4">
+      <c r="I56" s="20">
         <v>0.64</v>
       </c>
-      <c r="L56">
+      <c r="L56" s="17">
         <v>0.92</v>
       </c>
-      <c r="P56" s="6"/>
+      <c r="P56" s="4"/>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="19">
         <v>0.69</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="17">
         <v>0.97</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="17">
         <v>0.51</v>
       </c>
-      <c r="I57" s="4">
+      <c r="I57" s="20">
         <v>0.25</v>
       </c>
-      <c r="L57">
+      <c r="L57" s="17">
         <v>0.37</v>
       </c>
-      <c r="P57" s="6"/>
+      <c r="P57" s="4"/>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="19">
         <v>0.71</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="17">
         <v>0.91</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="17">
         <v>0.32</v>
       </c>
-      <c r="I58" s="4">
+      <c r="I58" s="20">
         <v>0.34</v>
       </c>
-      <c r="P58" s="6"/>
+      <c r="P58" s="4"/>
     </row>
     <row r="59" spans="1:16">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="19">
         <v>0.9</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="17">
         <v>1</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="17">
         <v>0.81</v>
       </c>
-      <c r="I59" s="4">
+      <c r="I59" s="20">
         <v>0.66</v>
       </c>
-      <c r="L59">
+      <c r="L59" s="17">
         <v>0.92</v>
       </c>
-      <c r="P59" s="6"/>
+      <c r="P59" s="4"/>
     </row>
     <row r="60" spans="1:16">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="19">
         <v>0.91</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="17">
         <v>0.98</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="17">
         <v>0.46</v>
       </c>
-      <c r="I60" s="4">
+      <c r="I60" s="20">
         <v>0.39</v>
       </c>
-      <c r="L60">
+      <c r="L60" s="17">
         <v>0.83</v>
       </c>
-      <c r="P60" s="6"/>
+      <c r="P60" s="4"/>
     </row>
     <row r="61" spans="1:16">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="19">
         <v>0.82</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="17">
         <v>0.88</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="17">
         <v>0.46</v>
       </c>
-      <c r="I61" s="4">
+      <c r="I61" s="20">
         <v>0.45</v>
       </c>
-      <c r="L61">
+      <c r="L61" s="17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P61" s="6"/>
+      <c r="P61" s="4"/>
     </row>
     <row r="62" spans="1:16">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="19">
         <v>0.75</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="17">
         <v>0.91</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="17">
         <v>0.37</v>
       </c>
-      <c r="I62" s="4">
+      <c r="I62" s="20">
         <v>0.49</v>
       </c>
-      <c r="L62">
+      <c r="L62" s="17">
         <v>0.83</v>
       </c>
-      <c r="P62" s="6"/>
+      <c r="P62" s="4"/>
     </row>
     <row r="63" spans="1:16">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="19">
         <v>0.76</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="17">
         <v>0.92</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="17">
         <v>0.63</v>
       </c>
-      <c r="I63" s="4">
+      <c r="I63" s="20">
         <v>0.61</v>
       </c>
-      <c r="L63">
+      <c r="L63" s="17">
         <v>0.63</v>
       </c>
-      <c r="P63" s="6"/>
+      <c r="P63" s="4"/>
     </row>
     <row r="64" spans="1:16">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D64" s="11">
+      <c r="D64" s="19">
         <v>0.72</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="17">
         <v>0.99</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="17">
         <v>0.37</v>
       </c>
-      <c r="I64" s="4">
+      <c r="I64" s="20">
         <v>0.15</v>
       </c>
-      <c r="L64">
+      <c r="L64" s="17">
         <v>0.37</v>
       </c>
-      <c r="P64" s="6"/>
+      <c r="P64" s="4"/>
     </row>
     <row r="65" spans="1:16">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="19">
         <v>0.86</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="17">
         <v>1</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="17">
         <v>0.53</v>
       </c>
-      <c r="I65" s="4">
+      <c r="I65" s="20">
         <v>0.67</v>
       </c>
-      <c r="L65">
+      <c r="L65" s="17">
         <v>0.79</v>
       </c>
-      <c r="P65" s="6"/>
+      <c r="P65" s="4"/>
     </row>
     <row r="66" spans="1:16">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="19">
         <v>0.76</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="17">
         <v>0.78</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="17">
         <v>0.35</v>
       </c>
-      <c r="I66" s="4">
+      <c r="I66" s="20">
         <v>0.25</v>
       </c>
-      <c r="L66">
+      <c r="L66" s="17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P66" s="6"/>
+      <c r="P66" s="4"/>
     </row>
     <row r="67" spans="1:16">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="19">
         <v>0.88</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="17">
         <v>1</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="17">
         <v>0.77</v>
       </c>
-      <c r="I67" s="4">
+      <c r="I67" s="20">
         <v>0.7</v>
       </c>
-      <c r="L67">
+      <c r="L67" s="17">
         <v>0.83</v>
       </c>
-      <c r="P67" s="6"/>
+      <c r="P67" s="4"/>
     </row>
     <row r="68" spans="1:16">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="19">
         <v>0.85</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="17">
         <v>0.97</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="17">
         <v>0.6</v>
       </c>
-      <c r="I68" s="4">
+      <c r="I68" s="20">
         <v>0.39</v>
       </c>
-      <c r="L68">
+      <c r="L68" s="17">
         <v>0.79</v>
       </c>
-      <c r="P68" s="6"/>
+      <c r="P68" s="4"/>
     </row>
     <row r="69" spans="1:16">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="19">
         <v>0.82</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="17">
         <v>0.98</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I69" s="4">
+      <c r="I69" s="20">
         <v>0.6</v>
       </c>
-      <c r="L69">
+      <c r="L69" s="17">
         <v>0.92</v>
       </c>
-      <c r="P69" s="6"/>
+      <c r="P69" s="4"/>
     </row>
     <row r="70" spans="1:16">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D70" s="11">
+      <c r="D70" s="19">
         <v>0.78</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="17">
         <v>0.87</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="17">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I70" s="4">
+      <c r="I70" s="20">
         <v>0.24</v>
       </c>
-      <c r="L70">
+      <c r="L70" s="17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P70" s="6"/>
+      <c r="P70" s="4"/>
     </row>
     <row r="71" spans="1:16">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="19">
         <v>0.7</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="17">
         <v>0.91</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="17">
         <v>0.35</v>
       </c>
-      <c r="I71" s="4">
+      <c r="I71" s="20">
         <v>0.45</v>
       </c>
-      <c r="L71">
+      <c r="L71" s="17">
         <v>0.37</v>
       </c>
-      <c r="P71" s="6"/>
+      <c r="P71" s="4"/>
     </row>
     <row r="72" spans="1:16">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D72" s="11">
+      <c r="D72" s="19">
         <v>0.83</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="17">
         <v>0.89</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="17">
         <v>0.28000000000000003</v>
       </c>
-      <c r="I72" s="4">
+      <c r="I72" s="20">
         <v>0.36</v>
       </c>
-      <c r="L72">
+      <c r="L72" s="17">
         <v>0.79</v>
       </c>
-      <c r="P72" s="6"/>
+      <c r="P72" s="4"/>
     </row>
     <row r="73" spans="1:16">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="19">
         <v>0.84</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="17">
         <v>1</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="17">
         <v>0.77</v>
       </c>
-      <c r="I73" s="4">
+      <c r="I73" s="20">
         <v>0.66</v>
       </c>
-      <c r="L73">
+      <c r="L73" s="17">
         <v>0.83</v>
       </c>
-      <c r="P73" s="6"/>
+      <c r="P73" s="4"/>
     </row>
     <row r="74" spans="1:16">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D74" s="11">
+      <c r="D74" s="19">
         <v>0.84</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="17">
         <v>0.98</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="17">
         <v>0.51</v>
       </c>
-      <c r="I74" s="4">
+      <c r="I74" s="20">
         <v>0.34</v>
       </c>
-      <c r="P74" s="6"/>
+      <c r="P74" s="4"/>
     </row>
     <row r="75" spans="1:16">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="19">
         <v>0.75</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="17">
         <v>0.96</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="17">
         <v>0.05</v>
       </c>
-      <c r="I75" s="4">
+      <c r="I75" s="20">
         <v>0.18</v>
       </c>
-      <c r="P75" s="6"/>
+      <c r="P75" s="4"/>
     </row>
     <row r="76" spans="1:16">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D76" s="11">
+      <c r="D76" s="19">
         <v>0.89</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="17">
         <v>0.99</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="17">
         <v>0.61</v>
       </c>
-      <c r="I76" s="4">
+      <c r="I76" s="20">
         <v>0.63</v>
       </c>
-      <c r="L76">
+      <c r="L76" s="17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P76" s="6"/>
+      <c r="P76" s="4"/>
     </row>
     <row r="77" spans="1:16">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="19">
         <v>0.88</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="17">
         <v>1</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="17">
         <v>0.74</v>
       </c>
-      <c r="I77" s="4">
+      <c r="I77" s="20">
         <v>0.84</v>
       </c>
-      <c r="L77">
+      <c r="L77" s="17">
         <v>0.92</v>
       </c>
-      <c r="P77" s="6"/>
+      <c r="P77" s="4"/>
     </row>
     <row r="78" spans="1:16">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D78" s="11">
+      <c r="D78" s="19">
         <v>0.68</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="17">
         <v>0.92</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="17">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I78" s="4">
+      <c r="I78" s="20">
         <v>0.18</v>
       </c>
-      <c r="P78" s="6"/>
+      <c r="P78" s="4"/>
     </row>
     <row r="79" spans="1:16">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="19">
         <v>0.78</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="17">
         <v>0.93</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="17">
         <v>0.61</v>
       </c>
-      <c r="I79" s="4">
+      <c r="I79" s="20">
         <v>0.63</v>
       </c>
-      <c r="L79">
+      <c r="L79" s="17">
         <v>0.92</v>
       </c>
-      <c r="P79" s="6"/>
+      <c r="P79" s="4"/>
     </row>
     <row r="80" spans="1:16">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D80" s="11">
+      <c r="D80" s="19">
         <v>0.84</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="17">
         <v>0.94</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="17">
         <v>0.47</v>
       </c>
-      <c r="I80" s="4">
+      <c r="I80" s="20">
         <v>0.46</v>
       </c>
-      <c r="L80">
+      <c r="L80" s="17">
         <v>0.63</v>
       </c>
-      <c r="P80" s="6"/>
+      <c r="P80" s="4"/>
     </row>
     <row r="81" spans="1:16">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="19">
         <v>0.84</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="17">
         <v>0.87</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="17">
         <v>0.65</v>
       </c>
-      <c r="I81" s="4">
+      <c r="I81" s="20">
         <v>0.72</v>
       </c>
-      <c r="L81">
+      <c r="L81" s="17">
         <v>0.37</v>
       </c>
-      <c r="P81" s="6"/>
+      <c r="P81" s="4"/>
     </row>
     <row r="82" spans="1:16">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="19">
         <v>0.74</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="17">
         <v>0.98</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="17">
         <v>0.39</v>
       </c>
-      <c r="I82" s="4">
+      <c r="I82" s="20">
         <v>0.36</v>
       </c>
-      <c r="L82">
+      <c r="L82" s="17">
         <v>0.37</v>
       </c>
-      <c r="P82" s="6"/>
+      <c r="P82" s="4"/>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" t="s">
@@ -4302,229 +4351,229 @@
       <c r="B83" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83" s="20">
         <v>0</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="17">
         <v>0.97</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="17">
         <v>0.54</v>
       </c>
-      <c r="I83" s="4">
+      <c r="I83" s="20">
         <v>0.46</v>
       </c>
-      <c r="L83">
+      <c r="L83" s="17">
         <v>0.63</v>
       </c>
-      <c r="P83" s="6"/>
+      <c r="P83" s="4"/>
     </row>
     <row r="84" spans="1:16">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="11">
+      <c r="D84" s="19">
         <v>0.81</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="17">
         <v>0.93</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="17">
         <v>0.79</v>
       </c>
-      <c r="I84" s="4">
+      <c r="I84" s="20">
         <v>0.6</v>
       </c>
-      <c r="L84">
+      <c r="L84" s="17">
         <v>0.79</v>
       </c>
-      <c r="P84" s="6"/>
+      <c r="P84" s="4"/>
     </row>
     <row r="85" spans="1:16">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D85" s="11">
+      <c r="D85" s="19">
         <v>0.71</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="17">
         <v>1</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="17">
         <v>0.63</v>
       </c>
-      <c r="I85" s="4">
+      <c r="I85" s="20">
         <v>0.33</v>
       </c>
-      <c r="L85">
+      <c r="L85" s="17">
         <v>0.63</v>
       </c>
-      <c r="P85" s="6"/>
+      <c r="P85" s="4"/>
     </row>
     <row r="86" spans="1:16">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D86" s="11">
+      <c r="D86" s="19">
         <v>0.76</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="17">
         <v>0.89</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="17">
         <v>0.61</v>
       </c>
-      <c r="I86" s="4">
+      <c r="I86" s="20">
         <v>0.28000000000000003</v>
       </c>
-      <c r="L86">
+      <c r="L86" s="17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P86" s="6"/>
+      <c r="P86" s="4"/>
     </row>
     <row r="87" spans="1:16">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D87" s="19">
         <v>0.81</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="17">
         <v>0.82</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="17">
         <v>0.25</v>
       </c>
-      <c r="I87" s="4">
+      <c r="I87" s="20">
         <v>0.18</v>
       </c>
-      <c r="P87" s="6"/>
+      <c r="P87" s="4"/>
     </row>
     <row r="88" spans="1:16">
-      <c r="A88" s="11" t="s">
+      <c r="A88" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D88" s="11">
+      <c r="D88" s="19">
         <v>0.83</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="17">
         <v>0.98</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="17">
         <v>0.6</v>
       </c>
-      <c r="I88" s="4">
+      <c r="I88" s="20">
         <v>0.39</v>
       </c>
-      <c r="L88">
+      <c r="L88" s="17">
         <v>0.79</v>
       </c>
-      <c r="P88" s="6"/>
+      <c r="P88" s="4"/>
     </row>
     <row r="89" spans="1:16">
-      <c r="A89" s="11" t="s">
+      <c r="A89" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D89" s="11">
+      <c r="D89" s="19">
         <v>0.85</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="17">
         <v>0.96</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="17">
         <v>0.54</v>
       </c>
-      <c r="I89" s="4">
+      <c r="I89" s="20">
         <v>0.34</v>
       </c>
-      <c r="P89" s="6"/>
+      <c r="P89" s="4"/>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="C90" s="11" t="s">
+      <c r="C90" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D90" s="11">
+      <c r="D90" s="19">
         <v>0.75</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="17">
         <v>0.97</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="17">
         <v>0.68</v>
       </c>
-      <c r="I90" s="4">
+      <c r="I90" s="20">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P90" s="6"/>
+      <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="11" t="s">
+      <c r="A91" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D91" s="11">
+      <c r="D91" s="19">
         <v>0.75</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="17">
         <v>0.86</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="17">
         <v>0.6</v>
       </c>
-      <c r="I91" s="4">
+      <c r="I91" s="20">
         <v>0.76</v>
       </c>
-      <c r="P91" s="6"/>
+      <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" t="s">
@@ -4533,142 +4582,142 @@
       <c r="B92" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="D92" s="4">
+      <c r="D92" s="20">
         <v>0</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="17">
         <v>0.53</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I92" s="4">
+      <c r="I92" s="20">
         <v>0.06</v>
       </c>
-      <c r="P92" s="18"/>
+      <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="11" t="s">
+      <c r="A93" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="19">
         <v>0.82</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="17">
         <v>0.99</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="17">
         <v>0.47</v>
       </c>
-      <c r="I93" s="4">
+      <c r="I93" s="20">
         <v>0.67</v>
       </c>
-      <c r="P93" s="6"/>
+      <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="11" t="s">
+      <c r="A94" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D94" s="11">
+      <c r="D94" s="19">
         <v>0.75</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="17">
         <v>0.91</v>
       </c>
-      <c r="H94">
+      <c r="H94" s="17">
         <v>0.65</v>
       </c>
-      <c r="I94" s="4">
+      <c r="I94" s="20">
         <v>0.84</v>
       </c>
-      <c r="P94" s="6"/>
+      <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="11" t="s">
+      <c r="A95" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D95" s="11">
+      <c r="D95" s="19">
         <v>0.77</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="17">
         <v>1</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="17">
         <v>0.42</v>
       </c>
-      <c r="I95" s="4">
+      <c r="I95" s="20">
         <v>0.31</v>
       </c>
-      <c r="P95" s="6"/>
+      <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C96" s="11" t="s">
+      <c r="C96" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D96" s="11">
+      <c r="D96" s="19">
         <v>0.93</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="17">
         <v>0.9</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="17">
         <v>0.79</v>
       </c>
-      <c r="I96" s="4">
+      <c r="I96" s="20">
         <v>0.57999999999999996</v>
       </c>
-      <c r="P96" s="6"/>
+      <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="11" t="s">
+      <c r="A97" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C97" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D97" s="11">
+      <c r="D97" s="19">
         <v>0.79</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="17">
         <v>0.98</v>
       </c>
-      <c r="H97">
+      <c r="H97" s="17">
         <v>0.46</v>
       </c>
-      <c r="I97" s="4">
+      <c r="I97" s="20">
         <v>0.31</v>
       </c>
-      <c r="P97" s="6"/>
+      <c r="P97" s="4"/>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" t="s">
@@ -4677,185 +4726,185 @@
       <c r="B98" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="D98" s="4"/>
-      <c r="H98" s="4">
+      <c r="D98" s="20"/>
+      <c r="H98" s="20">
         <v>0</v>
       </c>
-      <c r="I98" s="4">
+      <c r="I98" s="20">
         <v>0.15</v>
       </c>
-      <c r="P98" s="18"/>
+      <c r="P98" s="15"/>
     </row>
     <row r="99" spans="1:16">
-      <c r="A99" s="11" t="s">
+      <c r="A99" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="C99" s="11" t="s">
+      <c r="C99" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D99" s="11">
+      <c r="D99" s="19">
         <v>0.93</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="17">
         <v>0.96</v>
       </c>
-      <c r="H99">
+      <c r="H99" s="17">
         <v>0.72</v>
       </c>
-      <c r="I99" s="4">
+      <c r="I99" s="20">
         <v>0.84</v>
       </c>
-      <c r="P99" s="6"/>
+      <c r="P99" s="4"/>
     </row>
     <row r="100" spans="1:16">
-      <c r="A100" s="11" t="s">
+      <c r="A100" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C100" s="11" t="s">
+      <c r="C100" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D100" s="11">
+      <c r="D100" s="19">
         <v>0.83</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="17">
         <v>0.96</v>
       </c>
-      <c r="H100">
+      <c r="H100" s="17">
         <v>0.28000000000000003</v>
       </c>
-      <c r="I100" s="4">
+      <c r="I100" s="20">
         <v>0.76</v>
       </c>
-      <c r="P100" s="6"/>
+      <c r="P100" s="4"/>
     </row>
     <row r="101" spans="1:16">
-      <c r="A101" s="11" t="s">
+      <c r="A101" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C101" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D101" s="11">
+      <c r="D101" s="19">
         <v>0.9</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="17">
         <v>1</v>
       </c>
-      <c r="H101">
+      <c r="H101" s="17">
         <v>0.4</v>
       </c>
-      <c r="I101" s="4">
+      <c r="I101" s="20">
         <v>0.48</v>
       </c>
-      <c r="P101" s="6"/>
+      <c r="P101" s="4"/>
     </row>
     <row r="102" spans="1:16">
-      <c r="A102" s="11" t="s">
+      <c r="A102" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="B102" s="11" t="s">
+      <c r="B102" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="C102" s="11" t="s">
+      <c r="C102" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D102" s="11">
+      <c r="D102" s="19">
         <v>0.83</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="17">
         <v>0.91</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="17">
         <v>0.44</v>
       </c>
-      <c r="I102" s="4">
+      <c r="I102" s="20">
         <v>0.37</v>
       </c>
-      <c r="P102" s="6"/>
+      <c r="P102" s="4"/>
     </row>
     <row r="103" spans="1:16">
-      <c r="A103" s="11" t="s">
+      <c r="A103" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B103" s="11" t="s">
+      <c r="B103" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C103" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="19">
         <v>0.85</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="17">
         <v>0.99</v>
       </c>
-      <c r="H103">
+      <c r="H103" s="17">
         <v>0.51</v>
       </c>
-      <c r="I103" s="4">
+      <c r="I103" s="20">
         <v>0.69</v>
       </c>
-      <c r="P103" s="6"/>
+      <c r="P103" s="4"/>
     </row>
     <row r="104" spans="1:16">
-      <c r="A104" s="11" t="s">
+      <c r="A104" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C104" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D104" s="11">
+      <c r="D104" s="19">
         <v>0.89</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="17">
         <v>0.8</v>
       </c>
-      <c r="H104">
+      <c r="H104" s="17">
         <v>0.49</v>
       </c>
-      <c r="I104" s="4">
+      <c r="I104" s="20">
         <v>0.27</v>
       </c>
-      <c r="P104" s="6"/>
+      <c r="P104" s="4"/>
     </row>
     <row r="105" spans="1:16">
-      <c r="A105" s="11" t="s">
+      <c r="A105" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="B105" s="11" t="s">
+      <c r="B105" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C105" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="19">
         <v>0.85</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="17">
         <v>1</v>
       </c>
-      <c r="H105">
+      <c r="H105" s="17">
         <v>0.54</v>
       </c>
-      <c r="I105" s="4">
+      <c r="I105" s="20">
         <v>0.3</v>
       </c>
-      <c r="P105" s="6"/>
+      <c r="P105" s="4"/>
     </row>
     <row r="106" spans="1:16">
       <c r="A106" t="s">
@@ -4864,334 +4913,334 @@
       <c r="B106" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="D106" s="4">
+      <c r="D106" s="20">
         <v>0</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="17">
         <v>1</v>
       </c>
-      <c r="H106">
+      <c r="H106" s="17">
         <v>0.51</v>
       </c>
-      <c r="I106" s="4">
+      <c r="I106" s="20">
         <v>0.45</v>
       </c>
-      <c r="P106" s="18"/>
+      <c r="P106" s="15"/>
     </row>
     <row r="107" spans="1:16">
-      <c r="A107" s="11" t="s">
+      <c r="A107" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="B107" s="11" t="s">
+      <c r="B107" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C107" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="19">
         <v>0.86</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="17">
         <v>0.94</v>
       </c>
-      <c r="H107">
+      <c r="H107" s="17">
         <v>0.4</v>
       </c>
-      <c r="I107" s="4">
+      <c r="I107" s="20">
         <v>0.37</v>
       </c>
-      <c r="P107" s="6"/>
+      <c r="P107" s="4"/>
     </row>
     <row r="108" spans="1:16">
-      <c r="A108" s="11" t="s">
+      <c r="A108" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C108" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D108" s="11">
+      <c r="D108" s="19">
         <v>0.79</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="17">
         <v>1</v>
       </c>
-      <c r="H108">
+      <c r="H108" s="17">
         <v>0.44</v>
       </c>
-      <c r="I108" s="4">
+      <c r="I108" s="20">
         <v>0.1</v>
       </c>
-      <c r="P108" s="6"/>
+      <c r="P108" s="4"/>
     </row>
     <row r="109" spans="1:16">
-      <c r="A109" s="11" t="s">
+      <c r="A109" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="B109" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C109" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D109" s="11">
+      <c r="D109" s="19">
         <v>0.76</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="17">
         <v>0.91</v>
       </c>
-      <c r="H109">
+      <c r="H109" s="17">
         <v>0.39</v>
       </c>
-      <c r="I109" s="4">
+      <c r="I109" s="20">
         <v>0.31</v>
       </c>
-      <c r="P109" s="6"/>
+      <c r="P109" s="4"/>
     </row>
     <row r="110" spans="1:16">
-      <c r="A110" s="11" t="s">
+      <c r="A110" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C110" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D110" s="11">
+      <c r="D110" s="19">
         <v>0.84</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="17">
         <v>0.89</v>
       </c>
-      <c r="H110">
+      <c r="H110" s="17">
         <v>0.75</v>
       </c>
-      <c r="I110" s="4">
+      <c r="I110" s="20">
         <v>0.66</v>
       </c>
-      <c r="P110" s="6"/>
+      <c r="P110" s="4"/>
     </row>
     <row r="111" spans="1:16">
-      <c r="A111" s="11" t="s">
+      <c r="A111" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B111" s="11" t="s">
+      <c r="B111" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C111" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D111" s="11">
+      <c r="D111" s="19">
         <v>0.82</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="17">
         <v>1</v>
       </c>
-      <c r="H111">
+      <c r="H111" s="17">
         <v>0.61</v>
       </c>
-      <c r="I111" s="4">
+      <c r="I111" s="20">
         <v>0.66</v>
       </c>
-      <c r="P111" s="6"/>
+      <c r="P111" s="4"/>
     </row>
     <row r="112" spans="1:16">
-      <c r="A112" s="11" t="s">
+      <c r="A112" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C112" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D112" s="11">
+      <c r="D112" s="19">
         <v>0.83</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="17">
         <v>0.94</v>
       </c>
-      <c r="H112">
+      <c r="H112" s="17">
         <v>0.26</v>
       </c>
-      <c r="I112" s="4">
+      <c r="I112" s="20">
         <v>0.67</v>
       </c>
-      <c r="P112" s="6"/>
+      <c r="P112" s="4"/>
     </row>
     <row r="113" spans="1:16">
-      <c r="A113" s="11" t="s">
+      <c r="A113" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B113" s="11" t="s">
+      <c r="B113" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="C113" s="11" t="s">
+      <c r="C113" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="19">
         <v>0.94</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="17">
         <v>1</v>
       </c>
-      <c r="H113">
+      <c r="H113" s="17">
         <v>0.46</v>
       </c>
-      <c r="I113" s="4">
+      <c r="I113" s="20">
         <v>0.46</v>
       </c>
-      <c r="P113" s="6"/>
+      <c r="P113" s="4"/>
     </row>
     <row r="114" spans="1:16">
-      <c r="A114" s="11" t="s">
+      <c r="A114" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B114" s="11" t="s">
+      <c r="B114" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C114" s="11" t="s">
+      <c r="C114" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D114" s="11">
+      <c r="D114" s="19">
         <v>0.9</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="17">
         <v>0.91</v>
       </c>
-      <c r="H114">
+      <c r="H114" s="17">
         <v>0.42</v>
       </c>
-      <c r="I114" s="4">
+      <c r="I114" s="20">
         <v>0.43</v>
       </c>
-      <c r="P114" s="6"/>
+      <c r="P114" s="4"/>
     </row>
     <row r="115" spans="1:16">
-      <c r="A115" s="11" t="s">
+      <c r="A115" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="B115" s="11" t="s">
+      <c r="B115" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C115" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D115" s="11">
+      <c r="D115" s="19">
         <v>0.75</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="17">
         <v>0.91</v>
       </c>
-      <c r="H115">
+      <c r="H115" s="17">
         <v>0.39</v>
       </c>
-      <c r="I115" s="4">
+      <c r="I115" s="20">
         <v>0.63</v>
       </c>
-      <c r="P115" s="6"/>
+      <c r="P115" s="4"/>
     </row>
     <row r="116" spans="1:16">
-      <c r="A116" s="11" t="s">
+      <c r="A116" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B116" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C116" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D116" s="11">
+      <c r="D116" s="19">
         <v>0.9</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="17">
         <v>0.87</v>
       </c>
-      <c r="H116">
+      <c r="H116" s="17">
         <v>0.46</v>
       </c>
-      <c r="I116" s="4">
+      <c r="I116" s="20">
         <v>0.4</v>
       </c>
-      <c r="P116" s="6"/>
+      <c r="P116" s="4"/>
     </row>
     <row r="117" spans="1:16">
-      <c r="A117" s="11" t="s">
+      <c r="A117" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="B117" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C117" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D117" s="11">
+      <c r="D117" s="19">
         <v>0.66</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="17">
         <v>0.84</v>
       </c>
-      <c r="H117">
+      <c r="H117" s="17">
         <v>0.63</v>
       </c>
-      <c r="I117" s="4">
+      <c r="I117" s="20">
         <v>0.48</v>
       </c>
-      <c r="P117" s="6"/>
+      <c r="P117" s="4"/>
     </row>
     <row r="118" spans="1:16">
-      <c r="A118" s="11" t="s">
+      <c r="A118" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C118" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D118" s="11">
+      <c r="D118" s="19">
         <v>0.92</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="17">
         <v>0.9</v>
       </c>
-      <c r="H118">
+      <c r="H118" s="17">
         <v>0.44</v>
       </c>
-      <c r="I118" s="4">
+      <c r="I118" s="20">
         <v>0.84</v>
       </c>
-      <c r="P118" s="6"/>
+      <c r="P118" s="4"/>
     </row>
     <row r="119" spans="1:16">
-      <c r="A119" s="11" t="s">
+      <c r="A119" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="B119" s="11" t="s">
+      <c r="B119" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="C119" s="11" t="s">
+      <c r="C119" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D119" s="11">
+      <c r="D119" s="19">
         <v>0.82</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="17">
         <v>0.9</v>
       </c>
-      <c r="H119">
+      <c r="H119" s="17">
         <v>0.54</v>
       </c>
-      <c r="I119" s="4">
+      <c r="I119" s="20">
         <v>0.51</v>
       </c>
-      <c r="P119" s="6"/>
+      <c r="P119" s="4"/>
     </row>
     <row r="120" spans="1:16">
       <c r="A120" t="s">
@@ -5200,1220 +5249,1220 @@
       <c r="B120" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="D120" s="4">
+      <c r="D120" s="20">
         <v>0</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="17">
         <v>0.9</v>
       </c>
-      <c r="H120">
+      <c r="H120" s="17">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I120" s="4">
+      <c r="I120" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P120" s="18"/>
+      <c r="P120" s="15"/>
     </row>
     <row r="121" spans="1:16">
-      <c r="A121" s="11" t="s">
+      <c r="A121" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B121" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="C121" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D121" s="11">
+      <c r="D121" s="19">
         <v>0.8</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="17">
         <v>0.97</v>
       </c>
-      <c r="H121">
+      <c r="H121" s="17">
         <v>0.26</v>
       </c>
-      <c r="I121" s="4">
+      <c r="I121" s="20">
         <v>0.52</v>
       </c>
-      <c r="P121" s="6"/>
+      <c r="P121" s="4"/>
     </row>
     <row r="122" spans="1:16">
-      <c r="A122" s="11" t="s">
+      <c r="A122" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="B122" s="11" t="s">
+      <c r="B122" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C122" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D122" s="11">
+      <c r="D122" s="19">
         <v>0.96</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="17">
         <v>0.96</v>
       </c>
-      <c r="H122">
+      <c r="H122" s="17">
         <v>0.26</v>
       </c>
-      <c r="I122" s="4">
+      <c r="I122" s="20">
         <v>0.75</v>
       </c>
-      <c r="P122" s="6"/>
+      <c r="P122" s="4"/>
     </row>
     <row r="123" spans="1:16">
-      <c r="A123" s="11" t="s">
+      <c r="A123" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B123" s="11" t="s">
+      <c r="B123" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C123" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D123" s="11">
+      <c r="D123" s="19">
         <v>0.69</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="17">
         <v>0.5</v>
       </c>
-      <c r="H123">
+      <c r="H123" s="17">
         <v>0.26</v>
       </c>
-      <c r="I123" s="4">
+      <c r="I123" s="20">
         <v>0.69</v>
       </c>
-      <c r="P123" s="6"/>
+      <c r="P123" s="4"/>
     </row>
     <row r="124" spans="1:16">
-      <c r="A124" s="11" t="s">
+      <c r="A124" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="B124" s="11" t="s">
+      <c r="B124" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C124" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D124" s="11">
+      <c r="D124" s="19">
         <v>0.78</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="17">
         <v>0.96</v>
       </c>
-      <c r="H124">
+      <c r="H124" s="17">
         <v>0.09</v>
       </c>
-      <c r="I124" s="4">
+      <c r="I124" s="20">
         <v>0.42</v>
       </c>
-      <c r="P124" s="6"/>
+      <c r="P124" s="4"/>
     </row>
     <row r="125" spans="1:16">
-      <c r="A125" s="11" t="s">
+      <c r="A125" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B125" s="11" t="s">
+      <c r="B125" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="C125" s="11" t="s">
+      <c r="C125" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D125" s="11">
+      <c r="D125" s="19">
         <v>0.75</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="17">
         <v>0.99</v>
       </c>
-      <c r="H125">
+      <c r="H125" s="17">
         <v>0.49</v>
       </c>
-      <c r="I125" s="4">
+      <c r="I125" s="20">
         <v>0.18</v>
       </c>
-      <c r="P125" s="6"/>
+      <c r="P125" s="4"/>
     </row>
     <row r="126" spans="1:16">
-      <c r="A126" s="11" t="s">
+      <c r="A126" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="B126" s="11" t="s">
+      <c r="B126" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="C126" s="11" t="s">
+      <c r="C126" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D126" s="11">
+      <c r="D126" s="19">
         <v>0.67</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="17">
         <v>0.98</v>
       </c>
-      <c r="H126">
+      <c r="H126" s="17">
         <v>0.74</v>
       </c>
-      <c r="I126" s="4">
+      <c r="I126" s="20">
         <v>0.78</v>
       </c>
-      <c r="P126" s="6"/>
+      <c r="P126" s="4"/>
     </row>
     <row r="127" spans="1:16">
-      <c r="A127" s="11" t="s">
+      <c r="A127" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B127" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C127" s="11" t="s">
+      <c r="C127" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D127" s="11">
+      <c r="D127" s="19">
         <v>0.84</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="17">
         <v>1</v>
       </c>
-      <c r="H127">
+      <c r="H127" s="17">
         <v>0.26</v>
       </c>
-      <c r="I127" s="4">
+      <c r="I127" s="20">
         <v>0.36</v>
       </c>
-      <c r="P127" s="6"/>
+      <c r="P127" s="4"/>
     </row>
     <row r="128" spans="1:16">
-      <c r="A128" s="11" t="s">
+      <c r="A128" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B128" s="11" t="s">
+      <c r="B128" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C128" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D128" s="11">
+      <c r="D128" s="19">
         <v>0.73</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="17">
         <v>0.99</v>
       </c>
-      <c r="H128">
+      <c r="H128" s="17">
         <v>0.32</v>
       </c>
-      <c r="I128" s="4">
+      <c r="I128" s="20">
         <v>0.24</v>
       </c>
-      <c r="P128" s="6"/>
+      <c r="P128" s="4"/>
     </row>
     <row r="129" spans="1:16">
-      <c r="A129" s="11" t="s">
+      <c r="A129" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="B129" s="11" t="s">
+      <c r="B129" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="C129" s="11" t="s">
+      <c r="C129" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D129" s="11">
+      <c r="D129" s="19">
         <v>0.83</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="17">
         <v>0.92</v>
       </c>
-      <c r="H129">
+      <c r="H129" s="17">
         <v>0.11</v>
       </c>
-      <c r="I129" s="4">
+      <c r="I129" s="20">
         <v>0.13</v>
       </c>
-      <c r="P129" s="6"/>
+      <c r="P129" s="4"/>
     </row>
     <row r="130" spans="1:16">
-      <c r="A130" s="11" t="s">
+      <c r="A130" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="B130" s="11" t="s">
+      <c r="B130" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="C130" s="11" t="s">
+      <c r="C130" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D130" s="11">
+      <c r="D130" s="19">
         <v>0.95</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="17">
         <v>0.96</v>
       </c>
-      <c r="H130">
+      <c r="H130" s="17">
         <v>0.65</v>
       </c>
-      <c r="I130" s="4">
+      <c r="I130" s="20">
         <v>0.82</v>
       </c>
-      <c r="P130" s="6"/>
+      <c r="P130" s="4"/>
     </row>
     <row r="131" spans="1:16">
-      <c r="A131" s="11" t="s">
+      <c r="A131" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B131" s="11" t="s">
+      <c r="B131" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="C131" s="11" t="s">
+      <c r="C131" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D131" s="11">
+      <c r="D131" s="19">
         <v>0.72</v>
       </c>
-      <c r="E131">
+      <c r="E131" s="17">
         <v>0.99</v>
       </c>
-      <c r="H131">
+      <c r="H131" s="17">
         <v>0.28000000000000003</v>
       </c>
-      <c r="I131" s="4">
+      <c r="I131" s="20">
         <v>0.64</v>
       </c>
-      <c r="P131" s="6"/>
+      <c r="P131" s="4"/>
     </row>
     <row r="132" spans="1:16">
-      <c r="A132" s="11" t="s">
+      <c r="A132" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B132" s="11" t="s">
+      <c r="B132" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="C132" s="11" t="s">
+      <c r="C132" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D132" s="11">
+      <c r="D132" s="19">
         <v>0.83</v>
       </c>
-      <c r="E132">
+      <c r="E132" s="17">
         <v>1</v>
       </c>
-      <c r="H132">
+      <c r="H132" s="17">
         <v>0.47</v>
       </c>
-      <c r="I132" s="4">
+      <c r="I132" s="20">
         <v>0.39</v>
       </c>
-      <c r="P132" s="6"/>
+      <c r="P132" s="4"/>
     </row>
     <row r="133" spans="1:16">
-      <c r="A133" s="11" t="s">
+      <c r="A133" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B133" s="11" t="s">
+      <c r="B133" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="C133" s="11" t="s">
+      <c r="C133" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D133" s="19">
         <v>0.75</v>
       </c>
-      <c r="E133">
+      <c r="E133" s="17">
         <v>0.86</v>
       </c>
-      <c r="H133">
+      <c r="H133" s="17">
         <v>0.35</v>
       </c>
-      <c r="I133" s="4">
+      <c r="I133" s="20">
         <v>0.42</v>
       </c>
-      <c r="P133" s="6"/>
+      <c r="P133" s="4"/>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="11" t="s">
+      <c r="A134" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="B134" s="11" t="s">
+      <c r="B134" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="C134" s="11" t="s">
+      <c r="C134" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D134" s="11">
+      <c r="D134" s="19">
         <v>0.78</v>
       </c>
-      <c r="E134">
+      <c r="E134" s="17">
         <v>0.98</v>
       </c>
-      <c r="H134">
+      <c r="H134" s="17">
         <v>0.4</v>
       </c>
-      <c r="I134" s="4">
+      <c r="I134" s="20">
         <v>0.25</v>
       </c>
-      <c r="P134" s="6"/>
+      <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" s="11" t="s">
+      <c r="A135" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="B135" s="11" t="s">
+      <c r="B135" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="C135" s="11" t="s">
+      <c r="C135" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D135" s="11">
+      <c r="D135" s="19">
         <v>0.81</v>
       </c>
-      <c r="E135">
+      <c r="E135" s="17">
         <v>0.97</v>
       </c>
-      <c r="H135">
+      <c r="H135" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I135" s="4">
+      <c r="I135" s="20">
         <v>0.61</v>
       </c>
-      <c r="P135" s="6"/>
+      <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="11" t="s">
+      <c r="A136" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="B136" s="11" t="s">
+      <c r="B136" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="C136" s="11" t="s">
+      <c r="C136" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D136" s="11">
+      <c r="D136" s="19">
         <v>0.93</v>
       </c>
-      <c r="E136">
+      <c r="E136" s="17">
         <v>0.99</v>
       </c>
-      <c r="H136">
+      <c r="H136" s="17">
         <v>0.63</v>
       </c>
-      <c r="I136" s="4">
+      <c r="I136" s="20">
         <v>0.56999999999999995</v>
       </c>
-      <c r="P136" s="6"/>
+      <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="11" t="s">
+      <c r="A137" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="B137" s="11" t="s">
+      <c r="B137" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C137" s="11" t="s">
+      <c r="C137" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D137" s="11">
+      <c r="D137" s="19">
         <v>0.77</v>
       </c>
-      <c r="E137">
+      <c r="E137" s="17">
         <v>0.93</v>
       </c>
-      <c r="H137">
+      <c r="H137" s="17">
         <v>0.42</v>
       </c>
-      <c r="I137" s="4">
+      <c r="I137" s="20">
         <v>0.27</v>
       </c>
-      <c r="P137" s="6"/>
+      <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="11" t="s">
+      <c r="A138" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="B138" s="11" t="s">
+      <c r="B138" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="C138" s="11" t="s">
+      <c r="C138" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D138" s="11">
+      <c r="D138" s="19">
         <v>0.9</v>
       </c>
-      <c r="E138">
+      <c r="E138" s="17">
         <v>1</v>
       </c>
-      <c r="H138">
+      <c r="H138" s="17">
         <v>0.39</v>
       </c>
-      <c r="I138" s="4">
+      <c r="I138" s="20">
         <v>0.22</v>
       </c>
-      <c r="P138" s="6"/>
+      <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="11" t="s">
+      <c r="A139" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="B139" s="11" t="s">
+      <c r="B139" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="C139" s="11" t="s">
+      <c r="C139" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D139" s="11">
+      <c r="D139" s="19">
         <v>0.87</v>
       </c>
-      <c r="E139">
+      <c r="E139" s="17">
         <v>0.98</v>
       </c>
-      <c r="H139">
+      <c r="H139" s="17">
         <v>0.74</v>
       </c>
-      <c r="I139" s="4"/>
-      <c r="P139" s="6"/>
+      <c r="I139" s="20"/>
+      <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" s="11" t="s">
+      <c r="A140" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="B140" s="11" t="s">
+      <c r="B140" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C140" s="11" t="s">
+      <c r="C140" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D140" s="11">
+      <c r="D140" s="19">
         <v>0.88</v>
       </c>
-      <c r="E140">
+      <c r="E140" s="17">
         <v>0.96</v>
       </c>
-      <c r="H140">
+      <c r="H140" s="17">
         <v>0.39</v>
       </c>
-      <c r="I140" s="4"/>
-      <c r="P140" s="6"/>
+      <c r="I140" s="20"/>
+      <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="11" t="s">
+      <c r="A141" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B141" s="11" t="s">
+      <c r="B141" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="C141" s="11" t="s">
+      <c r="C141" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D141" s="11">
+      <c r="D141" s="19">
         <v>0.77</v>
       </c>
-      <c r="E141">
+      <c r="E141" s="17">
         <v>0.92</v>
       </c>
-      <c r="H141">
+      <c r="H141" s="17">
         <v>0.51</v>
       </c>
-      <c r="I141" s="4"/>
-      <c r="P141" s="6"/>
+      <c r="I141" s="20"/>
+      <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="11" t="s">
+      <c r="A142" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="B142" s="11" t="s">
+      <c r="B142" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="C142" s="11" t="s">
+      <c r="C142" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D142" s="11">
+      <c r="D142" s="19">
         <v>0.86</v>
       </c>
-      <c r="E142">
+      <c r="E142" s="17">
         <v>0.82</v>
       </c>
-      <c r="H142">
+      <c r="H142" s="17">
         <v>0.42</v>
       </c>
-      <c r="I142" s="4"/>
-      <c r="P142" s="6"/>
+      <c r="I142" s="20"/>
+      <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="11" t="s">
+      <c r="A143" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="B143" s="11" t="s">
+      <c r="B143" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="C143" s="11" t="s">
+      <c r="C143" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="19">
         <v>0.68</v>
       </c>
-      <c r="E143">
+      <c r="E143" s="17">
         <v>0.93</v>
       </c>
-      <c r="H143">
+      <c r="H143" s="17">
         <v>0</v>
       </c>
-      <c r="I143" s="4"/>
-      <c r="P143" s="6"/>
+      <c r="I143" s="20"/>
+      <c r="P143" s="4"/>
     </row>
     <row r="144" spans="1:16">
-      <c r="A144" s="11" t="s">
+      <c r="A144" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B144" s="11" t="s">
+      <c r="B144" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="C144" s="11" t="s">
+      <c r="C144" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D144" s="11">
+      <c r="D144" s="19">
         <v>0.73</v>
       </c>
-      <c r="E144">
+      <c r="E144" s="17">
         <v>0.92</v>
       </c>
-      <c r="H144">
+      <c r="H144" s="17">
         <v>0.16</v>
       </c>
-      <c r="I144" s="4">
+      <c r="I144" s="20">
         <v>0</v>
       </c>
-      <c r="P144" s="6"/>
+      <c r="P144" s="4"/>
     </row>
     <row r="145" spans="1:16">
-      <c r="A145" s="11" t="s">
+      <c r="A145" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="B145" s="11" t="s">
+      <c r="B145" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="C145" s="11" t="s">
+      <c r="C145" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D145" s="11">
+      <c r="D145" s="19">
         <v>0.9</v>
       </c>
-      <c r="E145">
+      <c r="E145" s="17">
         <v>0.91</v>
       </c>
-      <c r="H145">
+      <c r="H145" s="17">
         <v>0.65</v>
       </c>
-      <c r="I145" s="4"/>
-      <c r="P145" s="6"/>
+      <c r="I145" s="20"/>
+      <c r="P145" s="4"/>
     </row>
     <row r="146" spans="1:16">
-      <c r="A146" s="11" t="s">
+      <c r="A146" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="B146" s="11" t="s">
+      <c r="B146" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C146" s="11" t="s">
+      <c r="C146" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D146" s="11">
+      <c r="D146" s="19">
         <v>0.87</v>
       </c>
-      <c r="E146">
+      <c r="E146" s="17">
         <v>1</v>
       </c>
-      <c r="H146">
+      <c r="H146" s="17">
         <v>0.4</v>
       </c>
-      <c r="I146" s="4">
+      <c r="I146" s="20">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P146" s="6"/>
+      <c r="P146" s="4"/>
     </row>
     <row r="147" spans="1:16">
-      <c r="A147" s="11" t="s">
+      <c r="A147" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="B147" s="11" t="s">
+      <c r="B147" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="C147" s="11" t="s">
+      <c r="C147" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D147" s="11">
+      <c r="D147" s="19">
         <v>0.94</v>
       </c>
-      <c r="E147">
+      <c r="E147" s="17">
         <v>0.99</v>
       </c>
-      <c r="H147">
+      <c r="H147" s="17">
         <v>0.75</v>
       </c>
-      <c r="I147" s="4"/>
-      <c r="P147" s="6"/>
+      <c r="I147" s="20"/>
+      <c r="P147" s="4"/>
     </row>
     <row r="148" spans="1:16">
-      <c r="A148" s="11" t="s">
+      <c r="A148" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="B148" s="11" t="s">
+      <c r="B148" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="C148" s="11" t="s">
+      <c r="C148" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D148" s="11">
+      <c r="D148" s="19">
         <v>0.91</v>
       </c>
-      <c r="E148">
+      <c r="E148" s="17">
         <v>1</v>
       </c>
-      <c r="H148">
+      <c r="H148" s="17">
         <v>0.63</v>
       </c>
-      <c r="I148" s="4"/>
-      <c r="P148" s="6"/>
+      <c r="I148" s="20"/>
+      <c r="P148" s="4"/>
     </row>
     <row r="149" spans="1:16">
-      <c r="A149" s="11" t="s">
+      <c r="A149" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="B149" s="11" t="s">
+      <c r="B149" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="C149" s="11" t="s">
+      <c r="C149" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D149" s="11">
+      <c r="D149" s="19">
         <v>0.82</v>
       </c>
-      <c r="E149">
+      <c r="E149" s="17">
         <v>0.93</v>
       </c>
-      <c r="H149">
+      <c r="H149" s="17">
         <v>0.21</v>
       </c>
-      <c r="I149" s="4">
+      <c r="I149" s="20">
         <v>0.66</v>
       </c>
-      <c r="P149" s="6"/>
+      <c r="P149" s="4"/>
     </row>
     <row r="150" spans="1:16">
-      <c r="A150" s="11" t="s">
+      <c r="A150" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="B150" s="11" t="s">
+      <c r="B150" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="C150" s="11" t="s">
+      <c r="C150" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D150" s="11">
+      <c r="D150" s="19">
         <v>0.79</v>
       </c>
-      <c r="E150">
+      <c r="E150" s="17">
         <v>0</v>
       </c>
-      <c r="H150">
+      <c r="H150" s="17">
         <v>0.25</v>
       </c>
-      <c r="I150" s="4"/>
-      <c r="P150" s="6"/>
+      <c r="I150" s="20"/>
+      <c r="P150" s="4"/>
     </row>
     <row r="151" spans="1:16">
-      <c r="A151" s="11" t="s">
+      <c r="A151" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="B151" s="11" t="s">
+      <c r="B151" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="C151" s="11" t="s">
+      <c r="C151" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D151" s="11">
+      <c r="D151" s="19">
         <v>0.8</v>
       </c>
-      <c r="E151">
+      <c r="E151" s="17">
         <v>0.94</v>
       </c>
-      <c r="H151">
+      <c r="H151" s="17">
         <v>0.3</v>
       </c>
-      <c r="I151" s="4"/>
-      <c r="P151" s="6"/>
+      <c r="I151" s="20"/>
+      <c r="P151" s="4"/>
     </row>
     <row r="152" spans="1:16">
-      <c r="A152" s="11" t="s">
+      <c r="A152" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="B152" s="11" t="s">
+      <c r="B152" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="C152" s="11" t="s">
+      <c r="C152" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D152" s="11">
+      <c r="D152" s="19">
         <v>0.83</v>
       </c>
-      <c r="E152">
+      <c r="E152" s="17">
         <v>0.91</v>
       </c>
-      <c r="H152">
+      <c r="H152" s="17">
         <v>0.63</v>
       </c>
-      <c r="I152" s="4"/>
-      <c r="P152" s="6"/>
+      <c r="I152" s="20"/>
+      <c r="P152" s="4"/>
     </row>
     <row r="153" spans="1:16">
-      <c r="A153" s="11" t="s">
+      <c r="A153" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="B153" s="11" t="s">
+      <c r="B153" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="C153" s="11" t="s">
+      <c r="C153" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D153" s="11">
+      <c r="D153" s="19">
         <v>0.77</v>
       </c>
-      <c r="E153">
+      <c r="E153" s="17">
         <v>0.97</v>
       </c>
-      <c r="H153">
+      <c r="H153" s="17">
         <v>0.86</v>
       </c>
-      <c r="I153" s="4">
+      <c r="I153" s="20">
         <v>0.81</v>
       </c>
-      <c r="P153" s="6"/>
+      <c r="P153" s="4"/>
     </row>
     <row r="154" spans="1:16">
-      <c r="A154" s="11" t="s">
+      <c r="A154" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="B154" s="11" t="s">
+      <c r="B154" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="C154" s="11" t="s">
+      <c r="C154" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D154" s="11">
+      <c r="D154" s="19">
         <v>0.88</v>
       </c>
-      <c r="E154">
+      <c r="E154" s="17">
         <v>0.81</v>
       </c>
-      <c r="H154">
+      <c r="H154" s="17">
         <v>0.47</v>
       </c>
-      <c r="I154" s="4"/>
-      <c r="P154" s="6"/>
+      <c r="I154" s="20"/>
+      <c r="P154" s="4"/>
     </row>
     <row r="155" spans="1:16">
-      <c r="A155" s="11" t="s">
+      <c r="A155" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="B155" s="11" t="s">
+      <c r="B155" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="C155" s="11" t="s">
+      <c r="C155" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D155" s="11">
+      <c r="D155" s="19">
         <v>0.9</v>
       </c>
-      <c r="E155">
+      <c r="E155" s="17">
         <v>0.94</v>
       </c>
-      <c r="H155">
+      <c r="H155" s="17">
         <v>0.49</v>
       </c>
-      <c r="I155" s="4"/>
-      <c r="P155" s="6"/>
+      <c r="I155" s="20"/>
+      <c r="P155" s="4"/>
     </row>
     <row r="156" spans="1:16">
-      <c r="A156" s="11" t="s">
+      <c r="A156" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="B156" s="11" t="s">
+      <c r="B156" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="C156" s="11" t="s">
+      <c r="C156" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D156" s="11">
+      <c r="D156" s="19">
         <v>0.77</v>
       </c>
-      <c r="E156">
+      <c r="E156" s="17">
         <v>0.97</v>
       </c>
-      <c r="H156">
+      <c r="H156" s="17">
         <v>0.44</v>
       </c>
-      <c r="I156" s="4">
+      <c r="I156" s="20">
         <v>0.27</v>
       </c>
-      <c r="P156" s="6"/>
+      <c r="P156" s="4"/>
     </row>
     <row r="157" spans="1:16">
-      <c r="A157" s="11" t="s">
+      <c r="A157" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="B157" s="11" t="s">
+      <c r="B157" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="C157" s="11" t="s">
+      <c r="C157" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D157" s="11">
+      <c r="D157" s="19">
         <v>0.79</v>
       </c>
-      <c r="E157">
+      <c r="E157" s="17">
         <v>0.89</v>
       </c>
-      <c r="H157">
+      <c r="H157" s="17">
         <v>0.65</v>
       </c>
-      <c r="I157" s="4"/>
-      <c r="P157" s="6"/>
+      <c r="I157" s="20"/>
+      <c r="P157" s="4"/>
     </row>
     <row r="158" spans="1:16">
-      <c r="A158" s="11" t="s">
+      <c r="A158" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="B158" s="11" t="s">
+      <c r="B158" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="C158" s="11" t="s">
+      <c r="C158" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D158" s="11">
+      <c r="D158" s="19">
         <v>0.84</v>
       </c>
-      <c r="E158">
+      <c r="E158" s="17">
         <v>0.99</v>
       </c>
-      <c r="H158">
+      <c r="H158" s="17">
         <v>0.6</v>
       </c>
-      <c r="I158" s="4">
+      <c r="I158" s="20">
         <v>0.31</v>
       </c>
-      <c r="P158" s="6"/>
+      <c r="P158" s="4"/>
     </row>
     <row r="159" spans="1:16">
-      <c r="A159" s="11" t="s">
+      <c r="A159" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="B159" s="11" t="s">
+      <c r="B159" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C159" s="11" t="s">
+      <c r="C159" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D159" s="11">
+      <c r="D159" s="19">
         <v>0.88</v>
       </c>
-      <c r="E159">
+      <c r="E159" s="17">
         <v>0.86</v>
       </c>
-      <c r="H159">
+      <c r="H159" s="17">
         <v>0.46</v>
       </c>
-      <c r="I159" s="4">
+      <c r="I159" s="20">
         <v>0.18</v>
       </c>
-      <c r="P159" s="6"/>
+      <c r="P159" s="4"/>
     </row>
     <row r="160" spans="1:16">
-      <c r="A160" s="11" t="s">
+      <c r="A160" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="B160" s="11" t="s">
+      <c r="B160" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="C160" s="11" t="s">
+      <c r="C160" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D160" s="11">
+      <c r="D160" s="19">
         <v>0.8</v>
       </c>
-      <c r="E160">
+      <c r="E160" s="17">
         <v>0.99</v>
       </c>
-      <c r="H160">
+      <c r="H160" s="17">
         <v>0.42</v>
       </c>
-      <c r="I160" s="4">
+      <c r="I160" s="20">
         <v>0.31</v>
       </c>
-      <c r="P160" s="6"/>
+      <c r="P160" s="4"/>
     </row>
     <row r="161" spans="1:16">
-      <c r="A161" s="11" t="s">
+      <c r="A161" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="B161" s="11" t="s">
+      <c r="B161" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="C161" s="11" t="s">
+      <c r="C161" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D161" s="11">
+      <c r="D161" s="19">
         <v>0.66</v>
       </c>
-      <c r="E161">
+      <c r="E161" s="17">
         <v>0.97</v>
       </c>
-      <c r="H161">
+      <c r="H161" s="17">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I161" s="4"/>
-      <c r="P161" s="6"/>
+      <c r="I161" s="20"/>
+      <c r="P161" s="4"/>
     </row>
     <row r="162" spans="1:16">
-      <c r="A162" s="11" t="s">
+      <c r="A162" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="B162" s="11" t="s">
+      <c r="B162" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="C162" s="11" t="s">
+      <c r="C162" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D162" s="11">
+      <c r="D162" s="19">
         <v>0.88</v>
       </c>
-      <c r="E162">
+      <c r="E162" s="17">
         <v>0.92</v>
       </c>
-      <c r="H162">
+      <c r="H162" s="17">
         <v>0.68</v>
       </c>
-      <c r="I162" s="4"/>
-      <c r="P162" s="6"/>
+      <c r="I162" s="20"/>
+      <c r="P162" s="4"/>
     </row>
     <row r="163" spans="1:16">
-      <c r="A163" s="11" t="s">
+      <c r="A163" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="B163" s="11" t="s">
+      <c r="B163" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="C163" s="11" t="s">
+      <c r="C163" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D163" s="11">
+      <c r="D163" s="19">
         <v>0.94</v>
       </c>
-      <c r="E163">
+      <c r="E163" s="17">
         <v>1</v>
       </c>
-      <c r="H163">
+      <c r="H163" s="17">
         <v>0.51</v>
       </c>
-      <c r="I163" s="4"/>
-      <c r="P163" s="6"/>
+      <c r="I163" s="20"/>
+      <c r="P163" s="4"/>
     </row>
     <row r="164" spans="1:16">
-      <c r="A164" s="11" t="s">
+      <c r="A164" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="B164" s="11" t="s">
+      <c r="B164" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="C164" s="11" t="s">
+      <c r="C164" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D164" s="11">
+      <c r="D164" s="19">
         <v>0.95</v>
       </c>
-      <c r="E164">
+      <c r="E164" s="17">
         <v>0.98</v>
       </c>
-      <c r="H164">
+      <c r="H164" s="17">
         <v>0.33</v>
       </c>
-      <c r="I164" s="4"/>
-      <c r="P164" s="6"/>
+      <c r="I164" s="20"/>
+      <c r="P164" s="4"/>
     </row>
     <row r="165" spans="1:16">
-      <c r="A165" s="11" t="s">
+      <c r="A165" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="B165" s="11" t="s">
+      <c r="B165" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="C165" s="11" t="s">
+      <c r="C165" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D165" s="11">
+      <c r="D165" s="19">
         <v>0.79</v>
       </c>
-      <c r="E165">
+      <c r="E165" s="17">
         <v>0.97</v>
       </c>
-      <c r="H165">
+      <c r="H165" s="17">
         <v>0.18</v>
       </c>
-      <c r="I165" s="4"/>
-      <c r="P165" s="6"/>
+      <c r="I165" s="20"/>
+      <c r="P165" s="4"/>
     </row>
     <row r="166" spans="1:16">
-      <c r="A166" s="11" t="s">
+      <c r="A166" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="B166" s="11" t="s">
+      <c r="B166" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="C166" s="11" t="s">
+      <c r="C166" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D166" s="11">
+      <c r="D166" s="19">
         <v>0.9</v>
       </c>
-      <c r="E166">
+      <c r="E166" s="17">
         <v>0.87</v>
       </c>
-      <c r="H166">
+      <c r="H166" s="17">
         <v>0.47</v>
       </c>
-      <c r="I166" s="4"/>
-      <c r="P166" s="6"/>
+      <c r="I166" s="20"/>
+      <c r="P166" s="4"/>
     </row>
     <row r="167" spans="1:16">
-      <c r="A167" s="11" t="s">
+      <c r="A167" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="B167" s="11" t="s">
+      <c r="B167" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="C167" s="11" t="s">
+      <c r="C167" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D167" s="11">
+      <c r="D167" s="19">
         <v>0.82</v>
       </c>
-      <c r="E167">
+      <c r="E167" s="17">
         <v>0.97</v>
       </c>
-      <c r="H167">
+      <c r="H167" s="17">
         <v>0.63</v>
       </c>
-      <c r="I167" s="4"/>
-      <c r="P167" s="6"/>
+      <c r="I167" s="20"/>
+      <c r="P167" s="4"/>
     </row>
     <row r="168" spans="1:16">
-      <c r="A168" s="11" t="s">
+      <c r="A168" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="B168" s="11" t="s">
+      <c r="B168" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="C168" s="11" t="s">
+      <c r="C168" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D168" s="11">
+      <c r="D168" s="19">
         <v>0.75</v>
       </c>
-      <c r="E168">
+      <c r="E168" s="17">
         <v>0.98</v>
       </c>
-      <c r="H168">
+      <c r="H168" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I168" s="4">
+      <c r="I168" s="20">
         <v>0.78</v>
       </c>
-      <c r="P168" s="6"/>
+      <c r="P168" s="4"/>
     </row>
     <row r="169" spans="1:16">
-      <c r="A169" s="11" t="s">
+      <c r="A169" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="B169" s="11" t="s">
+      <c r="B169" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="C169" s="11" t="s">
+      <c r="C169" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D169" s="11">
+      <c r="D169" s="19">
         <v>0.8</v>
       </c>
-      <c r="E169">
+      <c r="E169" s="17">
         <v>0.96</v>
       </c>
-      <c r="H169">
+      <c r="H169" s="17">
         <v>0.54</v>
       </c>
-      <c r="I169" s="4"/>
-      <c r="P169" s="6"/>
+      <c r="I169" s="20"/>
+      <c r="P169" s="4"/>
     </row>
     <row r="170" spans="1:16">
-      <c r="A170" s="11" t="s">
+      <c r="A170" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="B170" s="11" t="s">
+      <c r="B170" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="C170" s="11" t="s">
+      <c r="C170" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D170" s="11">
+      <c r="D170" s="19">
         <v>0.85</v>
       </c>
-      <c r="E170">
+      <c r="E170" s="17">
         <v>0.99</v>
       </c>
-      <c r="H170">
+      <c r="H170" s="17">
         <v>0.3</v>
       </c>
-      <c r="I170" s="4"/>
-      <c r="P170" s="6"/>
+      <c r="I170" s="20"/>
+      <c r="P170" s="4"/>
     </row>
     <row r="171" spans="1:16">
-      <c r="A171" s="11" t="s">
+      <c r="A171" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="B171" s="11" t="s">
+      <c r="B171" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="C171" s="11" t="s">
+      <c r="C171" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D171" s="11">
+      <c r="D171" s="19">
         <v>0.82</v>
       </c>
-      <c r="E171">
+      <c r="E171" s="17">
         <v>0.98</v>
       </c>
-      <c r="H171">
+      <c r="H171" s="17">
         <v>0.25</v>
       </c>
-      <c r="I171" s="4"/>
-      <c r="P171" s="6"/>
+      <c r="I171" s="20"/>
+      <c r="P171" s="4"/>
     </row>
     <row r="172" spans="1:16">
-      <c r="A172" s="11" t="s">
+      <c r="A172" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B172" s="11" t="s">
+      <c r="B172" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="C172" s="11" t="s">
+      <c r="C172" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D172" s="11">
+      <c r="D172" s="19">
         <v>0.9</v>
       </c>
-      <c r="E172">
+      <c r="E172" s="17">
         <v>1</v>
       </c>
-      <c r="H172">
+      <c r="H172" s="17">
         <v>0.39</v>
       </c>
-      <c r="I172" s="4"/>
-      <c r="P172" s="6"/>
+      <c r="I172" s="20"/>
+      <c r="P172" s="4"/>
     </row>
     <row r="173" spans="1:16">
       <c r="A173" t="s">
@@ -6422,42 +6471,42 @@
       <c r="B173" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C173" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="D173" s="4">
+      <c r="D173" s="20">
         <v>0</v>
       </c>
-      <c r="E173">
+      <c r="E173" s="17">
         <v>0.87</v>
       </c>
-      <c r="H173">
+      <c r="H173" s="17">
         <v>0.35</v>
       </c>
-      <c r="I173" s="4"/>
-      <c r="P173" s="6"/>
+      <c r="I173" s="20"/>
+      <c r="P173" s="4"/>
     </row>
     <row r="174" spans="1:16">
-      <c r="A174" s="11" t="s">
+      <c r="A174" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="B174" s="11" t="s">
+      <c r="B174" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="C174" s="11" t="s">
+      <c r="C174" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D174" s="11">
+      <c r="D174" s="19">
         <v>0.86</v>
       </c>
-      <c r="E174">
+      <c r="E174" s="17">
         <v>0.93</v>
       </c>
-      <c r="H174">
+      <c r="H174" s="17">
         <v>0.35</v>
       </c>
-      <c r="I174" s="4"/>
-      <c r="P174" s="6"/>
+      <c r="I174" s="20"/>
+      <c r="P174" s="4"/>
     </row>
     <row r="175" spans="1:16">
       <c r="A175" t="s">
@@ -6466,224 +6515,224 @@
       <c r="B175" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C175" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="D175" s="4">
+      <c r="D175" s="20">
         <v>0</v>
       </c>
-      <c r="E175">
+      <c r="E175" s="17">
         <v>1</v>
       </c>
-      <c r="H175">
+      <c r="H175" s="17">
         <v>0.33</v>
       </c>
-      <c r="I175" s="4"/>
-      <c r="P175" s="6"/>
+      <c r="I175" s="20"/>
+      <c r="P175" s="4"/>
     </row>
     <row r="176" spans="1:16">
-      <c r="A176" s="11" t="s">
+      <c r="A176" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="B176" s="11" t="s">
+      <c r="B176" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="C176" s="11" t="s">
+      <c r="C176" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D176" s="11">
+      <c r="D176" s="19">
         <v>0.69</v>
       </c>
-      <c r="E176">
+      <c r="E176" s="17">
         <v>0.89</v>
       </c>
-      <c r="H176">
+      <c r="H176" s="17">
         <v>0.12</v>
       </c>
-      <c r="I176" s="4">
+      <c r="I176" s="20">
         <v>0.24</v>
       </c>
-      <c r="P176" s="6"/>
+      <c r="P176" s="4"/>
     </row>
     <row r="177" spans="1:16">
-      <c r="A177" s="11" t="s">
+      <c r="A177" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="B177" s="11" t="s">
+      <c r="B177" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="C177" s="11" t="s">
+      <c r="C177" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D177" s="11">
+      <c r="D177" s="19">
         <v>0.77</v>
       </c>
-      <c r="E177">
+      <c r="E177" s="17">
         <v>0.97</v>
       </c>
-      <c r="H177">
+      <c r="H177" s="17">
         <v>0.46</v>
       </c>
-      <c r="I177" s="4"/>
-      <c r="P177" s="6"/>
+      <c r="I177" s="20"/>
+      <c r="P177" s="4"/>
     </row>
     <row r="178" spans="1:16">
-      <c r="A178" s="11" t="s">
+      <c r="A178" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="B178" s="11" t="s">
+      <c r="B178" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="C178" s="11" t="s">
+      <c r="C178" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D178" s="11">
+      <c r="D178" s="19">
         <v>0.73</v>
       </c>
-      <c r="E178">
+      <c r="E178" s="17">
         <v>0</v>
       </c>
-      <c r="H178">
+      <c r="H178" s="17">
         <v>0.19</v>
       </c>
-      <c r="I178" s="4">
+      <c r="I178" s="20">
         <v>0</v>
       </c>
-      <c r="P178" s="6"/>
+      <c r="P178" s="4"/>
     </row>
     <row r="179" spans="1:16">
-      <c r="A179" s="11" t="s">
+      <c r="A179" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="B179" s="11" t="s">
+      <c r="B179" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="C179" s="11" t="s">
+      <c r="C179" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D179" s="11">
+      <c r="D179" s="19">
         <v>0.86</v>
       </c>
-      <c r="E179">
+      <c r="E179" s="17">
         <v>0.99</v>
       </c>
-      <c r="H179">
+      <c r="H179" s="17">
         <v>0.42</v>
       </c>
-      <c r="I179" s="4"/>
-      <c r="P179" s="6"/>
+      <c r="I179" s="20"/>
+      <c r="P179" s="4"/>
     </row>
     <row r="180" spans="1:16">
-      <c r="A180" s="11" t="s">
+      <c r="A180" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="B180" s="11" t="s">
+      <c r="B180" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="C180" s="11" t="s">
+      <c r="C180" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D180" s="11">
+      <c r="D180" s="19">
         <v>0.68</v>
       </c>
-      <c r="E180">
+      <c r="E180" s="17">
         <v>1</v>
       </c>
-      <c r="H180">
+      <c r="H180" s="17">
         <v>0.61</v>
       </c>
-      <c r="I180" s="4">
+      <c r="I180" s="20">
         <v>0.48</v>
       </c>
-      <c r="P180" s="6"/>
+      <c r="P180" s="4"/>
     </row>
     <row r="181" spans="1:16">
-      <c r="A181" s="11" t="s">
+      <c r="A181" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="B181" s="11" t="s">
+      <c r="B181" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="C181" s="11" t="s">
+      <c r="C181" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D181" s="11">
+      <c r="D181" s="19">
         <v>0.82</v>
       </c>
-      <c r="E181">
+      <c r="E181" s="17">
         <v>0.91</v>
       </c>
-      <c r="H181">
+      <c r="H181" s="17">
         <v>0.53</v>
       </c>
-      <c r="I181" s="4"/>
-      <c r="P181" s="6"/>
+      <c r="I181" s="20"/>
+      <c r="P181" s="4"/>
     </row>
     <row r="182" spans="1:16">
-      <c r="A182" s="11" t="s">
+      <c r="A182" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="B182" s="11" t="s">
+      <c r="B182" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="C182" s="11" t="s">
+      <c r="C182" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D182" s="11">
+      <c r="D182" s="19">
         <v>0.61</v>
       </c>
-      <c r="E182">
+      <c r="E182" s="17">
         <v>0.98</v>
       </c>
-      <c r="H182">
+      <c r="H182" s="17">
         <v>0.35</v>
       </c>
-      <c r="I182" s="4"/>
-      <c r="P182" s="6"/>
+      <c r="I182" s="20"/>
+      <c r="P182" s="4"/>
     </row>
     <row r="183" spans="1:16">
-      <c r="A183" s="11" t="s">
+      <c r="A183" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="B183" s="11" t="s">
+      <c r="B183" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="C183" s="11" t="s">
+      <c r="C183" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D183" s="11">
+      <c r="D183" s="19">
         <v>0.75</v>
       </c>
-      <c r="E183">
+      <c r="E183" s="17">
         <v>0.89</v>
       </c>
-      <c r="H183">
+      <c r="H183" s="17">
         <v>0.32</v>
       </c>
-      <c r="I183" s="4"/>
-      <c r="P183" s="6"/>
+      <c r="I183" s="20"/>
+      <c r="P183" s="4"/>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" s="11" t="s">
+      <c r="A184" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="B184" s="11" t="s">
+      <c r="B184" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="C184" s="11" t="s">
+      <c r="C184" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D184" s="11">
+      <c r="D184" s="19">
         <v>0.87</v>
       </c>
-      <c r="E184">
+      <c r="E184" s="17">
         <v>0.97</v>
       </c>
-      <c r="H184">
+      <c r="H184" s="17">
         <v>0.26</v>
       </c>
-      <c r="I184" s="4"/>
-      <c r="P184" s="6"/>
+      <c r="I184" s="20"/>
+      <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
       <c r="A185" t="s">
@@ -6692,196 +6741,196 @@
       <c r="B185" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C185" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D185" s="4">
+      <c r="D185" s="20">
         <v>0</v>
       </c>
-      <c r="E185">
+      <c r="E185" s="17">
         <v>0.98</v>
       </c>
-      <c r="H185">
+      <c r="H185" s="17">
         <v>0.19</v>
       </c>
-      <c r="I185" s="4"/>
-      <c r="P185" s="6"/>
+      <c r="I185" s="20"/>
+      <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" s="11" t="s">
+      <c r="A186" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="B186" s="11" t="s">
+      <c r="B186" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="C186" s="11" t="s">
+      <c r="C186" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D186" s="11">
+      <c r="D186" s="19">
         <v>0.71</v>
       </c>
-      <c r="E186">
+      <c r="E186" s="17">
         <v>0.97</v>
       </c>
-      <c r="H186">
+      <c r="H186" s="17">
         <v>0.35</v>
       </c>
-      <c r="I186" s="4"/>
-      <c r="P186" s="6"/>
+      <c r="I186" s="20"/>
+      <c r="P186" s="4"/>
     </row>
     <row r="187" spans="1:16">
-      <c r="A187" s="11" t="s">
+      <c r="A187" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="B187" s="11" t="s">
+      <c r="B187" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="C187" s="11" t="s">
+      <c r="C187" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D187" s="11">
+      <c r="D187" s="19">
         <v>0.92</v>
       </c>
-      <c r="E187">
+      <c r="E187" s="17">
         <v>0.97</v>
       </c>
-      <c r="H187">
+      <c r="H187" s="17">
         <v>0.63</v>
       </c>
-      <c r="I187" s="4"/>
-      <c r="P187" s="6"/>
+      <c r="I187" s="20"/>
+      <c r="P187" s="4"/>
     </row>
     <row r="188" spans="1:16">
-      <c r="A188" s="11" t="s">
+      <c r="A188" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="B188" s="11" t="s">
+      <c r="B188" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="C188" s="11" t="s">
+      <c r="C188" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D188" s="11">
+      <c r="D188" s="19">
         <v>0.8</v>
       </c>
-      <c r="E188">
+      <c r="E188" s="17">
         <v>1</v>
       </c>
-      <c r="H188">
+      <c r="H188" s="17">
         <v>0.39</v>
       </c>
-      <c r="I188" s="4"/>
-      <c r="P188" s="6"/>
+      <c r="I188" s="20"/>
+      <c r="P188" s="4"/>
     </row>
     <row r="189" spans="1:16">
-      <c r="A189" s="11" t="s">
+      <c r="A189" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="B189" s="11" t="s">
+      <c r="B189" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="C189" s="11" t="s">
+      <c r="C189" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D189" s="11">
+      <c r="D189" s="19">
         <v>0.75</v>
       </c>
-      <c r="E189">
+      <c r="E189" s="17">
         <v>1</v>
       </c>
-      <c r="H189">
+      <c r="H189" s="17">
         <v>0.68</v>
       </c>
-      <c r="I189" s="4"/>
-      <c r="P189" s="6"/>
+      <c r="I189" s="20"/>
+      <c r="P189" s="4"/>
     </row>
     <row r="190" spans="1:16">
-      <c r="A190" s="11" t="s">
+      <c r="A190" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B190" s="11" t="s">
+      <c r="B190" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="C190" s="11" t="s">
+      <c r="C190" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D190" s="11">
+      <c r="D190" s="19">
         <v>0.87</v>
       </c>
-      <c r="E190">
+      <c r="E190" s="17">
         <v>0.96</v>
       </c>
-      <c r="H190">
+      <c r="H190" s="17">
         <v>0.42</v>
       </c>
-      <c r="I190" s="4"/>
-      <c r="P190" s="6"/>
+      <c r="I190" s="20"/>
+      <c r="P190" s="4"/>
     </row>
     <row r="191" spans="1:16">
-      <c r="A191" s="11" t="s">
+      <c r="A191" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B191" s="11" t="s">
+      <c r="B191" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="C191" s="11" t="s">
+      <c r="C191" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D191" s="11">
+      <c r="D191" s="19">
         <v>0.81</v>
       </c>
-      <c r="E191">
+      <c r="E191" s="17">
         <v>1</v>
       </c>
-      <c r="H191">
+      <c r="H191" s="17">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I191" s="4"/>
-      <c r="P191" s="6"/>
+      <c r="I191" s="20"/>
+      <c r="P191" s="4"/>
     </row>
     <row r="192" spans="1:16">
-      <c r="A192" s="11" t="s">
+      <c r="A192" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="B192" s="11" t="s">
+      <c r="B192" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="C192" s="11" t="s">
+      <c r="C192" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D192" s="11">
+      <c r="D192" s="19">
         <v>0.84</v>
       </c>
-      <c r="E192">
+      <c r="E192" s="17">
         <v>0.98</v>
       </c>
-      <c r="H192">
+      <c r="H192" s="17">
         <v>0.6</v>
       </c>
-      <c r="I192" s="4"/>
-      <c r="P192" s="6"/>
+      <c r="I192" s="20"/>
+      <c r="P192" s="4"/>
     </row>
     <row r="193" spans="1:16">
-      <c r="A193" s="11" t="s">
+      <c r="A193" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="B193" s="11" t="s">
+      <c r="B193" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="C193" s="11" t="s">
+      <c r="C193" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D193" s="11">
+      <c r="D193" s="19">
         <v>0.64</v>
       </c>
-      <c r="E193">
+      <c r="E193" s="17">
         <v>0.96</v>
       </c>
-      <c r="H193">
+      <c r="H193" s="17">
         <v>0.04</v>
       </c>
-      <c r="I193" s="4"/>
-      <c r="P193" s="6"/>
+      <c r="I193" s="20"/>
+      <c r="P193" s="4"/>
     </row>
     <row r="194" spans="1:16">
       <c r="A194" t="s">
@@ -6890,218 +6939,218 @@
       <c r="B194" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C194" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D194" s="4">
+      <c r="D194" s="20">
         <v>0</v>
       </c>
-      <c r="E194">
+      <c r="E194" s="17">
         <v>1</v>
       </c>
-      <c r="H194">
+      <c r="H194" s="17">
         <v>0.26</v>
       </c>
-      <c r="I194" s="4"/>
-      <c r="P194" s="6"/>
+      <c r="I194" s="20"/>
+      <c r="P194" s="4"/>
     </row>
     <row r="195" spans="1:16">
-      <c r="A195" s="11" t="s">
+      <c r="A195" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B195" s="11" t="s">
+      <c r="B195" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="C195" s="11" t="s">
+      <c r="C195" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D195" s="11">
+      <c r="D195" s="19">
         <v>0.78</v>
       </c>
-      <c r="E195">
+      <c r="E195" s="17">
         <v>0.97</v>
       </c>
-      <c r="H195">
+      <c r="H195" s="17">
         <v>0.54</v>
       </c>
-      <c r="I195" s="4"/>
-      <c r="P195" s="6"/>
+      <c r="I195" s="20"/>
+      <c r="P195" s="4"/>
     </row>
     <row r="196" spans="1:16">
-      <c r="A196" s="11" t="s">
+      <c r="A196" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="B196" s="11" t="s">
+      <c r="B196" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="C196" s="11" t="s">
+      <c r="C196" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D196" s="11">
+      <c r="D196" s="19">
         <v>0.91</v>
       </c>
-      <c r="E196">
+      <c r="E196" s="17">
         <v>0.94</v>
       </c>
-      <c r="H196">
+      <c r="H196" s="17">
         <v>0.51</v>
       </c>
-      <c r="I196" s="4"/>
-      <c r="P196" s="6"/>
+      <c r="I196" s="20"/>
+      <c r="P196" s="4"/>
     </row>
     <row r="197" spans="1:16">
-      <c r="A197" s="11" t="s">
+      <c r="A197" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="B197" s="11" t="s">
+      <c r="B197" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="C197" s="11" t="s">
+      <c r="C197" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D197" s="11">
+      <c r="D197" s="19">
         <v>0.81</v>
       </c>
-      <c r="E197">
+      <c r="E197" s="17">
         <v>0.98</v>
       </c>
-      <c r="H197">
+      <c r="H197" s="17">
         <v>0.46</v>
       </c>
-      <c r="I197" s="4"/>
-      <c r="P197" s="6"/>
+      <c r="I197" s="20"/>
+      <c r="P197" s="4"/>
     </row>
     <row r="198" spans="1:16">
-      <c r="A198" s="11" t="s">
+      <c r="A198" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="B198" s="11" t="s">
+      <c r="B198" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="C198" s="11" t="s">
+      <c r="C198" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D198" s="11">
+      <c r="D198" s="19">
         <v>0.84</v>
       </c>
-      <c r="E198">
+      <c r="E198" s="17">
         <v>0.99</v>
       </c>
-      <c r="H198">
+      <c r="H198" s="17">
         <v>0.67</v>
       </c>
-      <c r="I198" s="4"/>
-      <c r="P198" s="6"/>
+      <c r="I198" s="20"/>
+      <c r="P198" s="4"/>
     </row>
     <row r="199" spans="1:16">
-      <c r="A199" s="11" t="s">
+      <c r="A199" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="B199" s="11" t="s">
+      <c r="B199" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="C199" s="11" t="s">
+      <c r="C199" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D199" s="11">
+      <c r="D199" s="19">
         <v>0.84</v>
       </c>
-      <c r="E199">
+      <c r="E199" s="17">
         <v>1</v>
       </c>
-      <c r="H199">
+      <c r="H199" s="17">
         <v>0.67</v>
       </c>
-      <c r="I199" s="4"/>
-      <c r="P199" s="6"/>
+      <c r="I199" s="20"/>
+      <c r="P199" s="4"/>
     </row>
     <row r="200" spans="1:16">
-      <c r="A200" s="11" t="s">
+      <c r="A200" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="B200" s="11" t="s">
+      <c r="B200" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="C200" s="11" t="s">
+      <c r="C200" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D200" s="11">
+      <c r="D200" s="19">
         <v>0.91</v>
       </c>
-      <c r="E200">
+      <c r="E200" s="17">
         <v>0.93</v>
       </c>
-      <c r="H200">
+      <c r="H200" s="17">
         <v>0.37</v>
       </c>
-      <c r="I200" s="4"/>
-      <c r="P200" s="6"/>
+      <c r="I200" s="20"/>
+      <c r="P200" s="4"/>
     </row>
     <row r="201" spans="1:16">
-      <c r="A201" s="11" t="s">
+      <c r="A201" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="B201" s="11" t="s">
+      <c r="B201" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="C201" s="11" t="s">
+      <c r="C201" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D201" s="11">
+      <c r="D201" s="19">
         <v>0.83</v>
       </c>
-      <c r="E201">
+      <c r="E201" s="17">
         <v>0.98</v>
       </c>
-      <c r="H201">
+      <c r="H201" s="17">
         <v>0.6</v>
       </c>
-      <c r="I201" s="4"/>
-      <c r="P201" s="6"/>
+      <c r="I201" s="20"/>
+      <c r="P201" s="4"/>
     </row>
     <row r="202" spans="1:16">
-      <c r="A202" s="11" t="s">
+      <c r="A202" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="B202" s="11" t="s">
+      <c r="B202" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="C202" s="11" t="s">
+      <c r="C202" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D202" s="11">
+      <c r="D202" s="19">
         <v>0.84</v>
       </c>
-      <c r="E202">
+      <c r="E202" s="17">
         <v>1</v>
       </c>
-      <c r="H202">
+      <c r="H202" s="17">
         <v>0.32</v>
       </c>
-      <c r="I202" s="4"/>
-      <c r="P202" s="6"/>
+      <c r="I202" s="20"/>
+      <c r="P202" s="4"/>
     </row>
     <row r="203" spans="1:16">
-      <c r="A203" s="11" t="s">
+      <c r="A203" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="B203" s="11" t="s">
+      <c r="B203" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="C203" s="11" t="s">
+      <c r="C203" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D203" s="11">
+      <c r="D203" s="19">
         <v>0.85</v>
       </c>
-      <c r="E203">
+      <c r="E203" s="17">
         <v>0.99</v>
       </c>
-      <c r="H203">
+      <c r="H203" s="17">
         <v>0.37</v>
       </c>
-      <c r="I203" s="4"/>
-      <c r="P203" s="6"/>
+      <c r="I203" s="20"/>
+      <c r="P203" s="4"/>
     </row>
     <row r="204" spans="1:16">
       <c r="A204" t="s">
@@ -7110,152 +7159,152 @@
       <c r="B204" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C204" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D204" s="4">
+      <c r="D204" s="20">
         <v>0</v>
       </c>
-      <c r="E204">
+      <c r="E204" s="17">
         <v>1</v>
       </c>
-      <c r="H204">
+      <c r="H204" s="17">
         <v>0.46</v>
       </c>
-      <c r="I204" s="4"/>
-      <c r="P204" s="6"/>
+      <c r="I204" s="20"/>
+      <c r="P204" s="4"/>
     </row>
     <row r="205" spans="1:16">
-      <c r="A205" s="11" t="s">
+      <c r="A205" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="B205" s="11" t="s">
+      <c r="B205" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="C205" s="11" t="s">
+      <c r="C205" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D205" s="11">
+      <c r="D205" s="19">
         <v>0.88</v>
       </c>
-      <c r="E205">
+      <c r="E205" s="17">
         <v>0.82</v>
       </c>
-      <c r="H205">
+      <c r="H205" s="17">
         <v>0.3</v>
       </c>
-      <c r="I205" s="4"/>
-      <c r="P205" s="6"/>
+      <c r="I205" s="20"/>
+      <c r="P205" s="4"/>
     </row>
     <row r="206" spans="1:16">
-      <c r="A206" s="11" t="s">
+      <c r="A206" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="B206" s="11" t="s">
+      <c r="B206" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="C206" s="11" t="s">
+      <c r="C206" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D206" s="11">
+      <c r="D206" s="19">
         <v>0.82</v>
       </c>
-      <c r="E206">
+      <c r="E206" s="17">
         <v>0.97</v>
       </c>
-      <c r="H206">
+      <c r="H206" s="17">
         <v>0.42</v>
       </c>
-      <c r="I206" s="4"/>
-      <c r="P206" s="6"/>
+      <c r="I206" s="20"/>
+      <c r="P206" s="4"/>
     </row>
     <row r="207" spans="1:16">
-      <c r="A207" s="11" t="s">
+      <c r="A207" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="B207" s="11" t="s">
+      <c r="B207" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="C207" s="11" t="s">
+      <c r="C207" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D207" s="11">
+      <c r="D207" s="19">
         <v>0.76</v>
       </c>
-      <c r="E207">
+      <c r="E207" s="17">
         <v>0.93</v>
       </c>
-      <c r="H207">
+      <c r="H207" s="17">
         <v>0.39</v>
       </c>
-      <c r="I207" s="4"/>
-      <c r="P207" s="6"/>
+      <c r="I207" s="20"/>
+      <c r="P207" s="4"/>
     </row>
     <row r="208" spans="1:16">
-      <c r="A208" s="11" t="s">
+      <c r="A208" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="B208" s="11" t="s">
+      <c r="B208" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="C208" s="11" t="s">
+      <c r="C208" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D208" s="11">
+      <c r="D208" s="19">
         <v>0.59</v>
       </c>
-      <c r="E208">
+      <c r="E208" s="17">
         <v>0.93</v>
       </c>
-      <c r="H208">
+      <c r="H208" s="17">
         <v>0.65</v>
       </c>
-      <c r="I208" s="4"/>
-      <c r="P208" s="6"/>
+      <c r="I208" s="20"/>
+      <c r="P208" s="4"/>
     </row>
     <row r="209" spans="1:16">
-      <c r="A209" s="11" t="s">
+      <c r="A209" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="B209" s="11" t="s">
+      <c r="B209" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="C209" s="11" t="s">
+      <c r="C209" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D209" s="11">
+      <c r="D209" s="19">
         <v>0.79</v>
       </c>
-      <c r="E209">
+      <c r="E209" s="17">
         <v>0.93</v>
       </c>
-      <c r="H209">
+      <c r="H209" s="17">
         <v>0.44</v>
       </c>
-      <c r="I209" s="4"/>
-      <c r="P209" s="6"/>
+      <c r="I209" s="20"/>
+      <c r="P209" s="4"/>
     </row>
     <row r="210" spans="1:16">
-      <c r="A210" s="11" t="s">
+      <c r="A210" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B210" s="11" t="s">
+      <c r="B210" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="C210" s="11" t="s">
+      <c r="C210" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D210" s="11">
+      <c r="D210" s="19">
         <v>0.77</v>
       </c>
-      <c r="E210">
+      <c r="E210" s="17">
         <v>0.98</v>
       </c>
-      <c r="H210">
+      <c r="H210" s="17">
         <v>0.75</v>
       </c>
-      <c r="I210" s="4"/>
-      <c r="P210" s="6"/>
+      <c r="I210" s="20"/>
+      <c r="P210" s="4"/>
     </row>
     <row r="211" spans="1:16">
       <c r="A211" t="s">
@@ -7264,64 +7313,64 @@
       <c r="B211" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="C211" t="s">
+      <c r="C211" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D211" s="4">
+      <c r="D211" s="20">
         <v>0</v>
       </c>
-      <c r="E211">
+      <c r="E211" s="17">
         <v>0.8</v>
       </c>
-      <c r="H211">
+      <c r="H211" s="17">
         <v>0.05</v>
       </c>
-      <c r="I211" s="4"/>
-      <c r="P211" s="6"/>
+      <c r="I211" s="20"/>
+      <c r="P211" s="4"/>
     </row>
     <row r="212" spans="1:16">
-      <c r="A212" s="11" t="s">
+      <c r="A212" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="B212" s="11" t="s">
+      <c r="B212" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="C212" s="11" t="s">
+      <c r="C212" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D212" s="11">
+      <c r="D212" s="19">
         <v>0.75</v>
       </c>
-      <c r="E212">
+      <c r="E212" s="17">
         <v>0.98</v>
       </c>
-      <c r="H212">
+      <c r="H212" s="17">
         <v>0.53</v>
       </c>
-      <c r="I212" s="4"/>
-      <c r="P212" s="6"/>
+      <c r="I212" s="20"/>
+      <c r="P212" s="4"/>
     </row>
     <row r="213" spans="1:16">
-      <c r="A213" s="11" t="s">
+      <c r="A213" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="B213" s="11" t="s">
+      <c r="B213" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="C213" s="11" t="s">
+      <c r="C213" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D213" s="11">
+      <c r="D213" s="19">
         <v>0.79</v>
       </c>
-      <c r="E213">
+      <c r="E213" s="17">
         <v>0.92</v>
       </c>
-      <c r="H213">
+      <c r="H213" s="17">
         <v>0.32</v>
       </c>
-      <c r="I213" s="4"/>
-      <c r="P213" s="6"/>
+      <c r="I213" s="20"/>
+      <c r="P213" s="4"/>
     </row>
     <row r="214" spans="1:16">
       <c r="A214" t="s">
@@ -7330,230 +7379,230 @@
       <c r="B214" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="C214" t="s">
+      <c r="C214" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D214" s="4">
+      <c r="D214" s="20">
         <v>0</v>
       </c>
-      <c r="E214">
+      <c r="E214" s="17">
         <v>0.97</v>
       </c>
-      <c r="H214">
+      <c r="H214" s="17">
         <v>0.44</v>
       </c>
-      <c r="I214" s="4"/>
-      <c r="P214" s="6"/>
+      <c r="I214" s="20"/>
+      <c r="P214" s="4"/>
     </row>
     <row r="215" spans="1:16">
-      <c r="A215" s="11" t="s">
+      <c r="A215" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="B215" s="11" t="s">
+      <c r="B215" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="C215" s="11" t="s">
+      <c r="C215" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D215" s="11">
+      <c r="D215" s="19">
         <v>0.74</v>
       </c>
-      <c r="E215">
+      <c r="E215" s="17">
         <v>1</v>
       </c>
-      <c r="H215">
+      <c r="H215" s="17">
         <v>0.68</v>
       </c>
-      <c r="I215" s="4"/>
-      <c r="P215" s="6"/>
+      <c r="I215" s="20"/>
+      <c r="P215" s="4"/>
     </row>
     <row r="216" spans="1:16">
-      <c r="A216" s="11" t="s">
+      <c r="A216" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="B216" s="11" t="s">
+      <c r="B216" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="C216" s="11" t="s">
+      <c r="C216" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D216" s="11">
+      <c r="D216" s="19">
         <v>0.62</v>
       </c>
-      <c r="E216">
+      <c r="E216" s="17">
         <v>0.92</v>
       </c>
-      <c r="H216">
+      <c r="H216" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I216" s="4"/>
-      <c r="P216" s="6"/>
+      <c r="I216" s="20"/>
+      <c r="P216" s="4"/>
     </row>
     <row r="217" spans="1:16">
-      <c r="A217" s="11" t="s">
+      <c r="A217" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="B217" s="11" t="s">
+      <c r="B217" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="C217" s="11" t="s">
+      <c r="C217" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D217" s="11">
+      <c r="D217" s="19">
         <v>0.94</v>
       </c>
-      <c r="E217">
+      <c r="E217" s="17">
         <v>0.99</v>
       </c>
-      <c r="H217">
+      <c r="H217" s="17">
         <v>0.65</v>
       </c>
-      <c r="I217" s="4"/>
-      <c r="P217" s="6"/>
+      <c r="I217" s="20"/>
+      <c r="P217" s="4"/>
     </row>
     <row r="218" spans="1:16">
-      <c r="A218" s="11" t="s">
+      <c r="A218" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="B218" s="11" t="s">
+      <c r="B218" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="C218" s="11" t="s">
+      <c r="C218" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="D218" s="11">
+      <c r="D218" s="19">
         <v>0.75</v>
       </c>
-      <c r="E218">
+      <c r="E218" s="17">
         <v>0.9</v>
       </c>
-      <c r="H218">
+      <c r="H218" s="17">
         <v>0.79</v>
       </c>
-      <c r="I218" s="4">
+      <c r="I218" s="20">
         <v>0.57999999999999996</v>
       </c>
-      <c r="P218" s="6"/>
+      <c r="P218" s="4"/>
     </row>
     <row r="219" spans="1:16">
-      <c r="A219" s="11" t="s">
+      <c r="A219" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="B219" s="11" t="s">
+      <c r="B219" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="C219" s="11" t="s">
+      <c r="C219" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="D219" s="11">
+      <c r="D219" s="19">
         <v>0.61</v>
       </c>
-      <c r="E219">
+      <c r="E219" s="17">
         <v>0.91</v>
       </c>
-      <c r="H219">
+      <c r="H219" s="17">
         <v>0.32</v>
       </c>
-      <c r="I219" s="4">
+      <c r="I219" s="20">
         <v>0.1</v>
       </c>
-      <c r="P219" s="6"/>
+      <c r="P219" s="4"/>
     </row>
     <row r="220" spans="1:16">
-      <c r="A220" s="11" t="s">
+      <c r="A220" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="B220" s="11" t="s">
+      <c r="B220" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="C220" s="11" t="s">
+      <c r="C220" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="D220" s="11">
+      <c r="D220" s="19">
         <v>0.69</v>
       </c>
-      <c r="E220">
+      <c r="E220" s="17">
         <v>0.79</v>
       </c>
-      <c r="H220">
+      <c r="H220" s="17">
         <v>0.54</v>
       </c>
-      <c r="I220" s="4">
+      <c r="I220" s="20">
         <v>0.43</v>
       </c>
-      <c r="P220" s="6"/>
+      <c r="P220" s="4"/>
     </row>
     <row r="221" spans="1:16">
-      <c r="A221" s="11" t="s">
+      <c r="A221" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="B221" s="11" t="s">
+      <c r="B221" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="C221" s="11" t="s">
+      <c r="C221" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="D221" s="11">
+      <c r="D221" s="19">
         <v>0.67</v>
       </c>
-      <c r="E221">
+      <c r="E221" s="17">
         <v>0.97</v>
       </c>
-      <c r="H221">
+      <c r="H221" s="17">
         <v>0.11</v>
       </c>
-      <c r="I221" s="4">
+      <c r="I221" s="20">
         <v>0.21</v>
       </c>
-      <c r="P221" s="6"/>
+      <c r="P221" s="4"/>
     </row>
     <row r="222" spans="1:16">
-      <c r="A222" s="11" t="s">
+      <c r="A222" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="B222" s="11" t="s">
+      <c r="B222" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="C222" s="11" t="s">
+      <c r="C222" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="D222" s="11">
+      <c r="D222" s="19">
         <v>0.71</v>
       </c>
-      <c r="E222">
+      <c r="E222" s="17">
         <v>0.98</v>
       </c>
-      <c r="H222">
+      <c r="H222" s="17">
         <v>0.54</v>
       </c>
-      <c r="I222" s="4">
+      <c r="I222" s="20">
         <v>0.7</v>
       </c>
-      <c r="P222" s="6"/>
+      <c r="P222" s="4"/>
     </row>
     <row r="223" spans="1:16">
-      <c r="A223" s="11" t="s">
+      <c r="A223" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="B223" s="11" t="s">
+      <c r="B223" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="C223" s="11" t="s">
+      <c r="C223" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="D223" s="11">
+      <c r="D223" s="19">
         <v>0.89</v>
       </c>
-      <c r="E223">
+      <c r="E223" s="17">
         <v>0.97</v>
       </c>
-      <c r="H223">
+      <c r="H223" s="17">
         <v>0.61</v>
       </c>
-      <c r="I223" s="4">
+      <c r="I223" s="20">
         <v>0.34</v>
       </c>
-      <c r="P223" s="6"/>
+      <c r="P223" s="4"/>
     </row>
     <row r="224" spans="1:16">
       <c r="A224" t="s">
@@ -7562,86 +7611,86 @@
       <c r="B224" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="C224" t="s">
+      <c r="C224" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D224" s="4">
+      <c r="D224" s="20">
         <v>0</v>
       </c>
-      <c r="E224">
+      <c r="E224" s="17">
         <v>0.88</v>
       </c>
-      <c r="H224">
+      <c r="H224" s="17">
         <v>0.33</v>
       </c>
-      <c r="I224" s="4"/>
-      <c r="P224" s="18"/>
+      <c r="I224" s="20"/>
+      <c r="P224" s="15"/>
     </row>
     <row r="225" spans="1:16">
-      <c r="A225" s="11" t="s">
+      <c r="A225" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="B225" s="11" t="s">
+      <c r="B225" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="C225" s="11" t="s">
+      <c r="C225" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D225" s="11">
+      <c r="D225" s="19">
         <v>0.79</v>
       </c>
-      <c r="E225">
+      <c r="E225" s="17">
         <v>0.89</v>
       </c>
-      <c r="H225">
+      <c r="H225" s="17">
         <v>0.26</v>
       </c>
-      <c r="I225" s="4"/>
-      <c r="P225" s="6"/>
+      <c r="I225" s="20"/>
+      <c r="P225" s="4"/>
     </row>
     <row r="226" spans="1:16">
-      <c r="A226" s="11" t="s">
+      <c r="A226" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="B226" s="11" t="s">
+      <c r="B226" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="C226" s="11" t="s">
+      <c r="C226" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D226" s="11">
+      <c r="D226" s="19">
         <v>0.66</v>
       </c>
-      <c r="E226">
+      <c r="E226" s="17">
         <v>0.87</v>
       </c>
-      <c r="H226">
+      <c r="H226" s="17">
         <v>0.16</v>
       </c>
-      <c r="I226" s="4"/>
-      <c r="P226" s="6"/>
+      <c r="I226" s="20"/>
+      <c r="P226" s="4"/>
     </row>
     <row r="227" spans="1:16">
-      <c r="A227" s="11" t="s">
+      <c r="A227" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="B227" s="11" t="s">
+      <c r="B227" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="C227" s="11" t="s">
+      <c r="C227" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D227" s="11">
+      <c r="D227" s="19">
         <v>0.69</v>
       </c>
-      <c r="E227">
+      <c r="E227" s="17">
         <v>0.88</v>
       </c>
-      <c r="H227">
+      <c r="H227" s="17">
         <v>0.28000000000000003</v>
       </c>
-      <c r="I227" s="4"/>
-      <c r="P227" s="19"/>
+      <c r="I227" s="20"/>
+      <c r="P227" s="16"/>
     </row>
     <row r="228" spans="1:16">
       <c r="A228" t="s">
@@ -7650,19 +7699,19 @@
       <c r="B228" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C228" t="s">
+      <c r="C228" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D228" s="4">
+      <c r="D228" s="20">
         <v>0</v>
       </c>
-      <c r="E228">
+      <c r="E228" s="17">
         <v>0.98</v>
       </c>
-      <c r="H228">
+      <c r="H228" s="17">
         <v>0.16</v>
       </c>
-      <c r="I228" s="4"/>
+      <c r="I228" s="20"/>
     </row>
     <row r="229" spans="1:16">
       <c r="A229" t="s">
@@ -7671,107 +7720,107 @@
       <c r="B229" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C229" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D229" s="4">
+      <c r="D229" s="20">
         <v>0</v>
       </c>
-      <c r="E229">
+      <c r="E229" s="17">
         <v>0.94</v>
       </c>
-      <c r="H229">
+      <c r="H229" s="17">
         <v>0.26</v>
       </c>
-      <c r="I229" s="4"/>
+      <c r="I229" s="20"/>
     </row>
     <row r="230" spans="1:16">
-      <c r="A230" s="11" t="s">
+      <c r="A230" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="B230" s="11" t="s">
+      <c r="B230" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="C230" s="11" t="s">
+      <c r="C230" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D230" s="11">
+      <c r="D230" s="19">
         <v>0.83</v>
       </c>
-      <c r="E230">
+      <c r="E230" s="17">
         <v>0.9</v>
       </c>
-      <c r="H230">
+      <c r="H230" s="17">
         <v>0.63</v>
       </c>
-      <c r="I230" s="4"/>
-      <c r="P230" s="19"/>
+      <c r="I230" s="20"/>
+      <c r="P230" s="16"/>
     </row>
     <row r="231" spans="1:16">
-      <c r="A231" s="11" t="s">
+      <c r="A231" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="B231" s="11" t="s">
+      <c r="B231" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="C231" s="11" t="s">
+      <c r="C231" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D231" s="11">
+      <c r="D231" s="19">
         <v>0.79</v>
       </c>
-      <c r="E231">
+      <c r="E231" s="17">
         <v>0.99</v>
       </c>
-      <c r="H231">
+      <c r="H231" s="17">
         <v>0.26</v>
       </c>
-      <c r="I231" s="4"/>
-      <c r="P231" s="19"/>
+      <c r="I231" s="20"/>
+      <c r="P231" s="16"/>
     </row>
     <row r="232" spans="1:16">
-      <c r="A232" s="11" t="s">
+      <c r="A232" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="B232" s="11" t="s">
+      <c r="B232" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="C232" s="11" t="s">
+      <c r="C232" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D232" s="11">
+      <c r="D232" s="19">
         <v>0.81</v>
       </c>
-      <c r="E232">
+      <c r="E232" s="17">
         <v>0.92</v>
       </c>
-      <c r="H232">
+      <c r="H232" s="17">
         <v>0.67</v>
       </c>
-      <c r="I232" s="4"/>
-      <c r="P232" s="19"/>
+      <c r="I232" s="20"/>
+      <c r="P232" s="16"/>
     </row>
     <row r="233" spans="1:16">
-      <c r="A233" s="11" t="s">
+      <c r="A233" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="B233" s="11" t="s">
+      <c r="B233" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="C233" s="11" t="s">
+      <c r="C233" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D233" s="11">
+      <c r="D233" s="19">
         <v>0.74</v>
       </c>
-      <c r="E233">
+      <c r="E233" s="17">
         <v>0.94</v>
       </c>
-      <c r="H233">
+      <c r="H233" s="17">
         <v>0.37</v>
       </c>
-      <c r="I233" s="4"/>
-      <c r="P233" s="19"/>
+      <c r="I233" s="20"/>
+      <c r="P233" s="16"/>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" t="s">
@@ -7780,63 +7829,63 @@
       <c r="B234" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C234" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D234" s="4">
+      <c r="D234" s="20">
         <v>0</v>
       </c>
-      <c r="E234">
+      <c r="E234" s="17">
         <v>0.91</v>
       </c>
-      <c r="H234">
+      <c r="H234" s="17">
         <v>0.35</v>
       </c>
-      <c r="I234" s="4"/>
+      <c r="I234" s="20"/>
     </row>
     <row r="235" spans="1:16">
-      <c r="A235" s="11" t="s">
+      <c r="A235" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B235" s="11" t="s">
+      <c r="B235" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="C235" s="11" t="s">
+      <c r="C235" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D235" s="11">
+      <c r="D235" s="19">
         <v>0.75</v>
       </c>
-      <c r="E235">
+      <c r="E235" s="17">
         <v>1</v>
       </c>
-      <c r="H235">
+      <c r="H235" s="17">
         <v>0.44</v>
       </c>
-      <c r="I235" s="4"/>
-      <c r="P235" s="19"/>
+      <c r="I235" s="20"/>
+      <c r="P235" s="16"/>
     </row>
     <row r="236" spans="1:16">
-      <c r="A236" s="11" t="s">
+      <c r="A236" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B236" s="11" t="s">
+      <c r="B236" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="C236" s="11" t="s">
+      <c r="C236" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D236" s="11">
+      <c r="D236" s="19">
         <v>0.65</v>
       </c>
-      <c r="E236">
+      <c r="E236" s="17">
         <v>1</v>
       </c>
-      <c r="H236">
+      <c r="H236" s="17">
         <v>0.63</v>
       </c>
-      <c r="I236" s="4"/>
-      <c r="P236" s="19"/>
+      <c r="I236" s="20"/>
+      <c r="P236" s="16"/>
     </row>
     <row r="237" spans="1:16">
       <c r="A237" t="s">
@@ -7845,19 +7894,19 @@
       <c r="B237" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="C237" t="s">
+      <c r="C237" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D237" s="4">
+      <c r="D237" s="20">
         <v>0</v>
       </c>
-      <c r="E237">
+      <c r="E237" s="17">
         <v>0.9</v>
       </c>
-      <c r="H237">
+      <c r="H237" s="17">
         <v>0.54</v>
       </c>
-      <c r="I237" s="4"/>
+      <c r="I237" s="20"/>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" t="s">
@@ -7866,19 +7915,19 @@
       <c r="B238" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C238" t="s">
+      <c r="C238" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D238" s="4">
+      <c r="D238" s="20">
         <v>0</v>
       </c>
-      <c r="E238">
+      <c r="E238" s="17">
         <v>0.9</v>
       </c>
-      <c r="H238">
+      <c r="H238" s="17">
         <v>0.42</v>
       </c>
-      <c r="I238" s="4"/>
+      <c r="I238" s="20"/>
     </row>
     <row r="239" spans="1:16">
       <c r="A239" t="s">
@@ -7887,63 +7936,63 @@
       <c r="B239" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C239" t="s">
+      <c r="C239" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D239" s="4">
+      <c r="D239" s="20">
         <v>0</v>
       </c>
-      <c r="E239">
+      <c r="E239" s="17">
         <v>1</v>
       </c>
-      <c r="H239">
+      <c r="H239" s="17">
         <v>0.49</v>
       </c>
-      <c r="I239" s="4"/>
+      <c r="I239" s="20"/>
     </row>
     <row r="240" spans="1:16">
-      <c r="A240" s="11" t="s">
+      <c r="A240" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="B240" s="11" t="s">
+      <c r="B240" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="C240" s="11" t="s">
+      <c r="C240" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D240" s="11">
+      <c r="D240" s="19">
         <v>0.87</v>
       </c>
-      <c r="E240">
+      <c r="E240" s="17">
         <v>0.84</v>
       </c>
-      <c r="H240">
+      <c r="H240" s="17">
         <v>0.47</v>
       </c>
-      <c r="I240" s="4"/>
-      <c r="P240" s="19"/>
+      <c r="I240" s="20"/>
+      <c r="P240" s="16"/>
     </row>
     <row r="241" spans="1:16">
-      <c r="A241" s="11" t="s">
+      <c r="A241" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="B241" s="11" t="s">
+      <c r="B241" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="C241" s="11" t="s">
+      <c r="C241" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D241" s="11">
+      <c r="D241" s="19">
         <v>0.7</v>
       </c>
-      <c r="E241">
+      <c r="E241" s="17">
         <v>0.89</v>
       </c>
-      <c r="H241">
+      <c r="H241" s="17">
         <v>0.19</v>
       </c>
-      <c r="I241" s="4"/>
-      <c r="P241" s="19"/>
+      <c r="I241" s="20"/>
+      <c r="P241" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AAEFA5-A5A9-0A47-B1D1-F0C0D5CE9547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646B4EC8-BDD9-7C48-B07F-067EB77C4E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="499">
   <si>
     <t>Surname</t>
   </si>
@@ -1526,6 +1526,12 @@
   </si>
   <si>
     <t>H250784X</t>
+  </si>
+  <si>
+    <t>Chidamba</t>
+  </si>
+  <si>
+    <t>H250593R</t>
   </si>
 </sst>
 </file>
@@ -1663,7 +1669,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1702,6 +1708,13 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1780,10 +1793,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:P241" totalsRowShown="0">
-  <autoFilter ref="A1:P241" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P241">
-    <sortCondition ref="C1:C241"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:P242" totalsRowShown="0">
+  <autoFilter ref="A1:P242" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P242">
+    <sortCondition ref="C1:C242"/>
   </sortState>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -2124,7 +2137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:P241"/>
+  <dimension ref="A1:P242"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -3442,10 +3455,10 @@
       <c r="P48" s="4"/>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="25" t="s">
         <v>92</v>
       </c>
       <c r="C49" s="19" t="s">
@@ -3466,10 +3479,10 @@
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C50" s="19" t="s">
@@ -3493,10 +3506,10 @@
       <c r="P50" s="4"/>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="25" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="19" t="s">
@@ -3520,10 +3533,10 @@
       <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="25" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="19" t="s">
@@ -3547,10 +3560,10 @@
       <c r="P52" s="4"/>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="25" t="s">
         <v>101</v>
       </c>
       <c r="C53" s="19" t="s">
@@ -3574,10 +3587,10 @@
       <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -3601,10 +3614,10 @@
       <c r="P54" s="4"/>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="25" t="s">
         <v>476</v>
       </c>
       <c r="C55" s="19" t="s">
@@ -3628,10 +3641,10 @@
       <c r="P55" s="4"/>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="25" t="s">
         <v>106</v>
       </c>
       <c r="C56" s="19" t="s">
@@ -4528,10 +4541,10 @@
       <c r="P89" s="4"/>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="25" t="s">
         <v>172</v>
       </c>
       <c r="C90" s="19" t="s">
@@ -4552,10 +4565,10 @@
       <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="25" t="s">
         <v>175</v>
       </c>
       <c r="C91" s="19" t="s">
@@ -4576,10 +4589,10 @@
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" t="s">
+      <c r="A92" s="22" t="s">
         <v>474</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="23" t="s">
         <v>475</v>
       </c>
       <c r="C92" s="17" t="s">
@@ -4600,10 +4613,10 @@
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="B93" s="9" t="s">
+      <c r="B93" s="25" t="s">
         <v>177</v>
       </c>
       <c r="C93" s="19" t="s">
@@ -4624,10 +4637,10 @@
       <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="25" t="s">
         <v>179</v>
       </c>
       <c r="C94" s="19" t="s">
@@ -4648,10 +4661,10 @@
       <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="25" t="s">
         <v>181</v>
       </c>
       <c r="C95" s="19" t="s">
@@ -4672,10 +4685,10 @@
       <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="25" t="s">
         <v>183</v>
       </c>
       <c r="C96" s="19" t="s">
@@ -4696,10 +4709,10 @@
       <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="25" t="s">
         <v>185</v>
       </c>
       <c r="C97" s="19" t="s">
@@ -5579,10 +5592,10 @@
       <c r="P133" s="4"/>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="9" t="s">
+      <c r="A134" s="25" t="s">
         <v>250</v>
       </c>
-      <c r="B134" s="9" t="s">
+      <c r="B134" s="25" t="s">
         <v>251</v>
       </c>
       <c r="C134" s="19" t="s">
@@ -5603,10 +5616,10 @@
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" s="9" t="s">
+      <c r="A135" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="B135" s="9" t="s">
+      <c r="B135" s="25" t="s">
         <v>254</v>
       </c>
       <c r="C135" s="19" t="s">
@@ -5627,10 +5640,10 @@
       <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="9" t="s">
+      <c r="A136" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="B136" s="9" t="s">
+      <c r="B136" s="25" t="s">
         <v>256</v>
       </c>
       <c r="C136" s="19" t="s">
@@ -5651,10 +5664,10 @@
       <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="9" t="s">
+      <c r="A137" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="B137" s="9" t="s">
+      <c r="B137" s="25" t="s">
         <v>258</v>
       </c>
       <c r="C137" s="19" t="s">
@@ -5675,10 +5688,10 @@
       <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="9" t="s">
+      <c r="A138" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="B138" s="9" t="s">
+      <c r="B138" s="25" t="s">
         <v>260</v>
       </c>
       <c r="C138" s="19" t="s">
@@ -5699,10 +5712,10 @@
       <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="9" t="s">
+      <c r="A139" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="B139" s="9" t="s">
+      <c r="B139" s="25" t="s">
         <v>262</v>
       </c>
       <c r="C139" s="19" t="s">
@@ -5721,10 +5734,10 @@
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" s="9" t="s">
+      <c r="A140" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="B140" s="9" t="s">
+      <c r="B140" s="25" t="s">
         <v>264</v>
       </c>
       <c r="C140" s="19" t="s">
@@ -5743,10 +5756,10 @@
       <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="9" t="s">
+      <c r="A141" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="B141" s="9" t="s">
+      <c r="B141" s="25" t="s">
         <v>266</v>
       </c>
       <c r="C141" s="19" t="s">
@@ -5765,10 +5778,10 @@
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="9" t="s">
+      <c r="A142" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="B142" s="9" t="s">
+      <c r="B142" s="25" t="s">
         <v>268</v>
       </c>
       <c r="C142" s="19" t="s">
@@ -5787,10 +5800,10 @@
       <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="9" t="s">
+      <c r="A143" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="B143" s="9" t="s">
+      <c r="B143" s="25" t="s">
         <v>270</v>
       </c>
       <c r="C143" s="19" t="s">
@@ -5809,10 +5822,10 @@
       <c r="P143" s="4"/>
     </row>
     <row r="144" spans="1:16">
-      <c r="A144" s="9" t="s">
+      <c r="A144" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="B144" s="9" t="s">
+      <c r="B144" s="25" t="s">
         <v>271</v>
       </c>
       <c r="C144" s="19" t="s">
@@ -6713,10 +6726,10 @@
       <c r="P183" s="4"/>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" s="9" t="s">
+      <c r="A184" s="25" t="s">
         <v>346</v>
       </c>
-      <c r="B184" s="9" t="s">
+      <c r="B184" s="25" t="s">
         <v>347</v>
       </c>
       <c r="C184" s="19" t="s">
@@ -6735,10 +6748,10 @@
       <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
-      <c r="A185" t="s">
+      <c r="A185" s="22" t="s">
         <v>446</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="26" t="s">
         <v>447</v>
       </c>
       <c r="C185" s="17" t="s">
@@ -6757,10 +6770,10 @@
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" s="9" t="s">
+      <c r="A186" s="25" t="s">
         <v>349</v>
       </c>
-      <c r="B186" s="9" t="s">
+      <c r="B186" s="25" t="s">
         <v>350</v>
       </c>
       <c r="C186" s="19" t="s">
@@ -7461,10 +7474,10 @@
       <c r="P217" s="4"/>
     </row>
     <row r="218" spans="1:16">
-      <c r="A218" s="9" t="s">
+      <c r="A218" s="25" t="s">
         <v>405</v>
       </c>
-      <c r="B218" s="9" t="s">
+      <c r="B218" s="25" t="s">
         <v>406</v>
       </c>
       <c r="C218" s="19" t="s">
@@ -7605,10 +7618,10 @@
       <c r="P223" s="4"/>
     </row>
     <row r="224" spans="1:16">
-      <c r="A224" t="s">
+      <c r="A224" s="22" t="s">
         <v>460</v>
       </c>
-      <c r="B224" s="2" t="s">
+      <c r="B224" s="23" t="s">
         <v>461</v>
       </c>
       <c r="C224" s="17" t="s">
@@ -7623,14 +7636,16 @@
       <c r="H224" s="17">
         <v>0.33</v>
       </c>
-      <c r="I224" s="20"/>
+      <c r="I224" s="20">
+        <v>0.6</v>
+      </c>
       <c r="P224" s="15"/>
     </row>
     <row r="225" spans="1:16">
-      <c r="A225" s="9" t="s">
+      <c r="A225" s="25" t="s">
         <v>418</v>
       </c>
-      <c r="B225" s="9" t="s">
+      <c r="B225" s="25" t="s">
         <v>419</v>
       </c>
       <c r="C225" s="19" t="s">
@@ -7645,80 +7660,84 @@
       <c r="H225" s="17">
         <v>0.26</v>
       </c>
-      <c r="I225" s="20"/>
+      <c r="I225" s="20">
+        <v>0.19</v>
+      </c>
       <c r="P225" s="4"/>
     </row>
     <row r="226" spans="1:16">
-      <c r="A226" s="9" t="s">
+      <c r="A226" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="B226" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="C226" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="D226" s="20"/>
+      <c r="H226" s="20">
+        <v>0</v>
+      </c>
+      <c r="I226" s="20">
+        <v>0.08</v>
+      </c>
+      <c r="P226" s="15"/>
+    </row>
+    <row r="227" spans="1:16">
+      <c r="A227" s="25" t="s">
         <v>421</v>
       </c>
-      <c r="B226" s="9" t="s">
+      <c r="B227" s="25" t="s">
         <v>422</v>
-      </c>
-      <c r="C226" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D226" s="19">
-        <v>0.66</v>
-      </c>
-      <c r="E226" s="17">
-        <v>0.87</v>
-      </c>
-      <c r="H226" s="17">
-        <v>0.16</v>
-      </c>
-      <c r="I226" s="20"/>
-      <c r="P226" s="4"/>
-    </row>
-    <row r="227" spans="1:16">
-      <c r="A227" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="B227" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="C227" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D227" s="19">
+        <v>0.66</v>
+      </c>
+      <c r="E227" s="17">
+        <v>0.87</v>
+      </c>
+      <c r="H227" s="17">
+        <v>0.16</v>
+      </c>
+      <c r="I227" s="20">
+        <v>0.87</v>
+      </c>
+      <c r="P227" s="24"/>
+    </row>
+    <row r="228" spans="1:16">
+      <c r="A228" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C228" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="D228" s="19">
         <v>0.69</v>
       </c>
-      <c r="E227" s="17">
+      <c r="E228" s="17">
         <v>0.88</v>
       </c>
-      <c r="H227" s="17">
+      <c r="H228" s="17">
         <v>0.28000000000000003</v>
       </c>
-      <c r="I227" s="20"/>
-      <c r="P227" s="16"/>
-    </row>
-    <row r="228" spans="1:16">
-      <c r="A228" t="s">
-        <v>464</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="C228" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="D228" s="20">
-        <v>0</v>
-      </c>
-      <c r="E228" s="17">
-        <v>0.98</v>
-      </c>
-      <c r="H228" s="17">
-        <v>0.16</v>
-      </c>
-      <c r="I228" s="20"/>
+      <c r="I228" s="20">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="P228" s="24"/>
     </row>
     <row r="229" spans="1:16">
       <c r="A229" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C229" s="17" t="s">
         <v>420</v>
@@ -7727,193 +7746,214 @@
         <v>0</v>
       </c>
       <c r="E229" s="17">
+        <v>0.98</v>
+      </c>
+      <c r="H229" s="17">
+        <v>0.16</v>
+      </c>
+      <c r="I229" s="20">
+        <v>0.18</v>
+      </c>
+      <c r="P229" s="22"/>
+    </row>
+    <row r="230" spans="1:16">
+      <c r="A230" t="s">
+        <v>457</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C230" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="D230" s="20">
+        <v>0</v>
+      </c>
+      <c r="E230" s="17">
         <v>0.94</v>
       </c>
-      <c r="H229" s="17">
+      <c r="H230" s="17">
         <v>0.26</v>
       </c>
-      <c r="I229" s="20"/>
-    </row>
-    <row r="230" spans="1:16">
-      <c r="A230" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="B230" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="C230" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D230" s="19">
-        <v>0.83</v>
-      </c>
-      <c r="E230" s="17">
-        <v>0.9</v>
-      </c>
-      <c r="H230" s="17">
-        <v>0.63</v>
-      </c>
-      <c r="I230" s="20"/>
-      <c r="P230" s="16"/>
+      <c r="I230" s="20">
+        <v>0.21</v>
+      </c>
+      <c r="P230" s="22"/>
     </row>
     <row r="231" spans="1:16">
       <c r="A231" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C231" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D231" s="19">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="E231" s="17">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="H231" s="17">
-        <v>0.26</v>
-      </c>
-      <c r="I231" s="20"/>
-      <c r="P231" s="16"/>
+        <v>0.63</v>
+      </c>
+      <c r="I231" s="20">
+        <v>0.72</v>
+      </c>
+      <c r="P231" s="24"/>
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="9" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C232" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D232" s="19">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="E232" s="17">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="H232" s="17">
-        <v>0.67</v>
-      </c>
-      <c r="I232" s="20"/>
-      <c r="P232" s="16"/>
+        <v>0.26</v>
+      </c>
+      <c r="I232" s="20">
+        <v>0.43</v>
+      </c>
+      <c r="P232" s="24"/>
     </row>
     <row r="233" spans="1:16">
       <c r="A233" s="9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C233" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D233" s="19">
+        <v>0.81</v>
+      </c>
+      <c r="E233" s="17">
+        <v>0.92</v>
+      </c>
+      <c r="H233" s="17">
+        <v>0.67</v>
+      </c>
+      <c r="I233" s="20">
+        <v>0.66</v>
+      </c>
+      <c r="P233" s="24"/>
+    </row>
+    <row r="234" spans="1:16">
+      <c r="A234" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B234" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C234" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="D234" s="19">
         <v>0.74</v>
       </c>
-      <c r="E233" s="17">
+      <c r="E234" s="17">
         <v>0.94</v>
       </c>
-      <c r="H233" s="17">
+      <c r="H234" s="17">
         <v>0.37</v>
       </c>
-      <c r="I233" s="20"/>
-      <c r="P233" s="16"/>
-    </row>
-    <row r="234" spans="1:16">
-      <c r="A234" t="s">
+      <c r="I234" s="20">
+        <v>0.25</v>
+      </c>
+      <c r="P234" s="24"/>
+    </row>
+    <row r="235" spans="1:16">
+      <c r="A235" t="s">
         <v>468</v>
       </c>
-      <c r="B234" s="2" t="s">
+      <c r="B235" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="C234" s="17" t="s">
+      <c r="C235" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D234" s="20">
+      <c r="D235" s="20">
         <v>0</v>
       </c>
-      <c r="E234" s="17">
+      <c r="E235" s="17">
         <v>0.91</v>
       </c>
-      <c r="H234" s="17">
+      <c r="H235" s="17">
         <v>0.35</v>
       </c>
-      <c r="I234" s="20"/>
-    </row>
-    <row r="235" spans="1:16">
-      <c r="A235" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B235" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="C235" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D235" s="19">
-        <v>0.75</v>
-      </c>
-      <c r="E235" s="17">
-        <v>1</v>
-      </c>
-      <c r="H235" s="17">
-        <v>0.44</v>
-      </c>
-      <c r="I235" s="20"/>
-      <c r="P235" s="16"/>
+      <c r="I235" s="20">
+        <v>0</v>
+      </c>
+      <c r="P235" s="22"/>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C236" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D236" s="19">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="E236" s="17">
         <v>1</v>
       </c>
       <c r="H236" s="17">
+        <v>0.44</v>
+      </c>
+      <c r="I236" s="20">
+        <v>0.66</v>
+      </c>
+      <c r="P236" s="24"/>
+    </row>
+    <row r="237" spans="1:16">
+      <c r="A237" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="C237" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="D237" s="19">
+        <v>0.65</v>
+      </c>
+      <c r="E237" s="17">
+        <v>1</v>
+      </c>
+      <c r="H237" s="17">
         <v>0.63</v>
       </c>
-      <c r="I236" s="20"/>
-      <c r="P236" s="16"/>
-    </row>
-    <row r="237" spans="1:16">
-      <c r="A237" t="s">
-        <v>462</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C237" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="D237" s="20">
-        <v>0</v>
-      </c>
-      <c r="E237" s="17">
-        <v>0.9</v>
-      </c>
-      <c r="H237" s="17">
-        <v>0.54</v>
-      </c>
-      <c r="I237" s="20"/>
+      <c r="I237" s="20">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="P237" s="24"/>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C238" s="17" t="s">
         <v>420</v>
@@ -7925,16 +7965,19 @@
         <v>0.9</v>
       </c>
       <c r="H238" s="17">
-        <v>0.42</v>
-      </c>
-      <c r="I238" s="20"/>
+        <v>0.54</v>
+      </c>
+      <c r="I238" s="20">
+        <v>0.72</v>
+      </c>
+      <c r="P238" s="22"/>
     </row>
     <row r="239" spans="1:16">
       <c r="A239" t="s">
-        <v>165</v>
+        <v>466</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C239" s="17" t="s">
         <v>420</v>
@@ -7943,56 +7986,86 @@
         <v>0</v>
       </c>
       <c r="E239" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="H239" s="17">
+        <v>0.42</v>
+      </c>
+      <c r="I239" s="20">
+        <v>0</v>
+      </c>
+      <c r="P239" s="22"/>
+    </row>
+    <row r="240" spans="1:16">
+      <c r="A240" t="s">
+        <v>165</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C240" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="D240" s="20">
+        <v>0</v>
+      </c>
+      <c r="E240" s="17">
         <v>1</v>
       </c>
-      <c r="H239" s="17">
+      <c r="H240" s="17">
         <v>0.49</v>
       </c>
-      <c r="I239" s="20"/>
-    </row>
-    <row r="240" spans="1:16">
-      <c r="A240" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="C240" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D240" s="19">
-        <v>0.87</v>
-      </c>
-      <c r="E240" s="17">
-        <v>0.84</v>
-      </c>
-      <c r="H240" s="17">
-        <v>0.47</v>
-      </c>
-      <c r="I240" s="20"/>
-      <c r="P240" s="16"/>
+      <c r="I240" s="20">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="241" spans="1:16">
       <c r="A241" s="9" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C241" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D241" s="19">
+        <v>0.87</v>
+      </c>
+      <c r="E241" s="17">
+        <v>0.84</v>
+      </c>
+      <c r="H241" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="I241" s="20">
+        <v>0</v>
+      </c>
+      <c r="P241" s="16"/>
+    </row>
+    <row r="242" spans="1:16">
+      <c r="A242" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="B242" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="C242" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="D242" s="19">
         <v>0.7</v>
       </c>
-      <c r="E241" s="17">
+      <c r="E242" s="17">
         <v>0.89</v>
       </c>
-      <c r="H241" s="17">
+      <c r="H242" s="17">
         <v>0.19</v>
       </c>
-      <c r="I241" s="20"/>
-      <c r="P241" s="16"/>
+      <c r="I242" s="20">
+        <v>0.13</v>
+      </c>
+      <c r="P242" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646B4EC8-BDD9-7C48-B07F-067EB77C4E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3145FA58-82D7-464A-A1C3-E4DF0FDFCF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -5818,7 +5818,9 @@
       <c r="H143" s="17">
         <v>0</v>
       </c>
-      <c r="I143" s="20"/>
+      <c r="I143" s="20">
+        <v>0.24</v>
+      </c>
       <c r="P143" s="4"/>
     </row>
     <row r="144" spans="1:16">
@@ -5932,7 +5934,9 @@
       <c r="H148" s="17">
         <v>0.63</v>
       </c>
-      <c r="I148" s="20"/>
+      <c r="I148" s="20">
+        <v>0.51</v>
+      </c>
       <c r="P148" s="4"/>
     </row>
     <row r="149" spans="1:16">
@@ -6136,7 +6140,9 @@
       <c r="H157" s="17">
         <v>0.65</v>
       </c>
-      <c r="I157" s="20"/>
+      <c r="I157" s="20">
+        <v>0.42</v>
+      </c>
       <c r="P157" s="4"/>
     </row>
     <row r="158" spans="1:16">
@@ -6252,7 +6258,9 @@
       <c r="H162" s="17">
         <v>0.68</v>
       </c>
-      <c r="I162" s="20"/>
+      <c r="I162" s="20">
+        <v>0.52</v>
+      </c>
       <c r="P162" s="4"/>
     </row>
     <row r="163" spans="1:16">
@@ -6296,7 +6304,9 @@
       <c r="H164" s="17">
         <v>0.33</v>
       </c>
-      <c r="I164" s="20"/>
+      <c r="I164" s="20">
+        <v>0.09</v>
+      </c>
       <c r="P164" s="4"/>
     </row>
     <row r="165" spans="1:16">
@@ -6362,7 +6372,9 @@
       <c r="H167" s="17">
         <v>0.63</v>
       </c>
-      <c r="I167" s="20"/>
+      <c r="I167" s="20">
+        <v>0.45</v>
+      </c>
       <c r="P167" s="4"/>
     </row>
     <row r="168" spans="1:16">
@@ -6452,7 +6464,9 @@
       <c r="H171" s="17">
         <v>0.25</v>
       </c>
-      <c r="I171" s="20"/>
+      <c r="I171" s="20">
+        <v>0.15</v>
+      </c>
       <c r="P171" s="4"/>
     </row>
     <row r="172" spans="1:16">
@@ -6518,7 +6532,9 @@
       <c r="H174" s="17">
         <v>0.35</v>
       </c>
-      <c r="I174" s="20"/>
+      <c r="I174" s="20">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="P174" s="4"/>
     </row>
     <row r="175" spans="1:16">
@@ -6632,7 +6648,9 @@
       <c r="H179" s="17">
         <v>0.42</v>
       </c>
-      <c r="I179" s="20"/>
+      <c r="I179" s="20">
+        <v>0.37</v>
+      </c>
       <c r="P179" s="4"/>
     </row>
     <row r="180" spans="1:16">
@@ -6700,7 +6718,9 @@
       <c r="H182" s="17">
         <v>0.35</v>
       </c>
-      <c r="I182" s="20"/>
+      <c r="I182" s="20">
+        <v>0.24</v>
+      </c>
       <c r="P182" s="4"/>
     </row>
     <row r="183" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3145FA58-82D7-464A-A1C3-E4DF0FDFCF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4325F6-2E1B-DC4E-AE8C-B64479AAB18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4325F6-2E1B-DC4E-AE8C-B64479AAB18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24D53F6-D816-304D-8247-477A2E6E7A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1669,7 +1669,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1708,13 +1708,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3455,10 +3448,10 @@
       <c r="P48" s="4"/>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="9" t="s">
         <v>92</v>
       </c>
       <c r="C49" s="19" t="s">
@@ -3479,10 +3472,10 @@
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C50" s="19" t="s">
@@ -3506,10 +3499,10 @@
       <c r="P50" s="4"/>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="19" t="s">
@@ -3533,10 +3526,10 @@
       <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="19" t="s">
@@ -3560,10 +3553,10 @@
       <c r="P52" s="4"/>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="9" t="s">
         <v>101</v>
       </c>
       <c r="C53" s="19" t="s">
@@ -3587,10 +3580,10 @@
       <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="25" t="s">
+      <c r="B54" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -3614,10 +3607,10 @@
       <c r="P54" s="4"/>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="25" t="s">
+      <c r="B55" s="9" t="s">
         <v>476</v>
       </c>
       <c r="C55" s="19" t="s">
@@ -3641,10 +3634,10 @@
       <c r="P55" s="4"/>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="25" t="s">
+      <c r="B56" s="9" t="s">
         <v>106</v>
       </c>
       <c r="C56" s="19" t="s">
@@ -4541,10 +4534,10 @@
       <c r="P89" s="4"/>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="25" t="s">
+      <c r="A90" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B90" s="25" t="s">
+      <c r="B90" s="9" t="s">
         <v>172</v>
       </c>
       <c r="C90" s="19" t="s">
@@ -4565,10 +4558,10 @@
       <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="25" t="s">
+      <c r="A91" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B91" s="25" t="s">
+      <c r="B91" s="9" t="s">
         <v>175</v>
       </c>
       <c r="C91" s="19" t="s">
@@ -4589,10 +4582,10 @@
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" s="22" t="s">
+      <c r="A92" t="s">
         <v>474</v>
       </c>
-      <c r="B92" s="23" t="s">
+      <c r="B92" s="2" t="s">
         <v>475</v>
       </c>
       <c r="C92" s="17" t="s">
@@ -4613,10 +4606,10 @@
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="25" t="s">
+      <c r="A93" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B93" s="25" t="s">
+      <c r="B93" s="9" t="s">
         <v>177</v>
       </c>
       <c r="C93" s="19" t="s">
@@ -4637,10 +4630,10 @@
       <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="25" t="s">
+      <c r="A94" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B94" s="25" t="s">
+      <c r="B94" s="9" t="s">
         <v>179</v>
       </c>
       <c r="C94" s="19" t="s">
@@ -4661,10 +4654,10 @@
       <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="25" t="s">
+      <c r="A95" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B95" s="25" t="s">
+      <c r="B95" s="9" t="s">
         <v>181</v>
       </c>
       <c r="C95" s="19" t="s">
@@ -4685,10 +4678,10 @@
       <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="25" t="s">
+      <c r="A96" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B96" s="25" t="s">
+      <c r="B96" s="9" t="s">
         <v>183</v>
       </c>
       <c r="C96" s="19" t="s">
@@ -4709,10 +4702,10 @@
       <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="25" t="s">
+      <c r="A97" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B97" s="25" t="s">
+      <c r="B97" s="9" t="s">
         <v>185</v>
       </c>
       <c r="C97" s="19" t="s">
@@ -5592,10 +5585,10 @@
       <c r="P133" s="4"/>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="25" t="s">
+      <c r="A134" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="B134" s="25" t="s">
+      <c r="B134" s="9" t="s">
         <v>251</v>
       </c>
       <c r="C134" s="19" t="s">
@@ -5616,10 +5609,10 @@
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" s="25" t="s">
+      <c r="A135" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="B135" s="25" t="s">
+      <c r="B135" s="9" t="s">
         <v>254</v>
       </c>
       <c r="C135" s="19" t="s">
@@ -5640,10 +5633,10 @@
       <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="25" t="s">
+      <c r="A136" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="B136" s="25" t="s">
+      <c r="B136" s="9" t="s">
         <v>256</v>
       </c>
       <c r="C136" s="19" t="s">
@@ -5664,10 +5657,10 @@
       <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="25" t="s">
+      <c r="A137" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="B137" s="25" t="s">
+      <c r="B137" s="9" t="s">
         <v>258</v>
       </c>
       <c r="C137" s="19" t="s">
@@ -5688,10 +5681,10 @@
       <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="25" t="s">
+      <c r="A138" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="B138" s="25" t="s">
+      <c r="B138" s="9" t="s">
         <v>260</v>
       </c>
       <c r="C138" s="19" t="s">
@@ -5712,10 +5705,10 @@
       <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="25" t="s">
+      <c r="A139" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="B139" s="25" t="s">
+      <c r="B139" s="9" t="s">
         <v>262</v>
       </c>
       <c r="C139" s="19" t="s">
@@ -5730,14 +5723,16 @@
       <c r="H139" s="17">
         <v>0.74</v>
       </c>
-      <c r="I139" s="20"/>
+      <c r="I139" s="20">
+        <v>0.6</v>
+      </c>
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" s="25" t="s">
+      <c r="A140" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="B140" s="25" t="s">
+      <c r="B140" s="9" t="s">
         <v>264</v>
       </c>
       <c r="C140" s="19" t="s">
@@ -5752,14 +5747,16 @@
       <c r="H140" s="17">
         <v>0.39</v>
       </c>
-      <c r="I140" s="20"/>
+      <c r="I140" s="20">
+        <v>0.19</v>
+      </c>
       <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="25" t="s">
+      <c r="A141" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B141" s="25" t="s">
+      <c r="B141" s="9" t="s">
         <v>266</v>
       </c>
       <c r="C141" s="19" t="s">
@@ -5778,10 +5775,10 @@
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="25" t="s">
+      <c r="A142" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="B142" s="25" t="s">
+      <c r="B142" s="9" t="s">
         <v>268</v>
       </c>
       <c r="C142" s="19" t="s">
@@ -5796,14 +5793,16 @@
       <c r="H142" s="17">
         <v>0.42</v>
       </c>
-      <c r="I142" s="20"/>
+      <c r="I142" s="20">
+        <v>0.79</v>
+      </c>
       <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="25" t="s">
+      <c r="A143" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="B143" s="25" t="s">
+      <c r="B143" s="9" t="s">
         <v>270</v>
       </c>
       <c r="C143" s="19" t="s">
@@ -5824,10 +5823,10 @@
       <c r="P143" s="4"/>
     </row>
     <row r="144" spans="1:16">
-      <c r="A144" s="25" t="s">
+      <c r="A144" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B144" s="25" t="s">
+      <c r="B144" s="9" t="s">
         <v>271</v>
       </c>
       <c r="C144" s="19" t="s">
@@ -5866,7 +5865,9 @@
       <c r="H145" s="17">
         <v>0.65</v>
       </c>
-      <c r="I145" s="20"/>
+      <c r="I145" s="20">
+        <v>0.45</v>
+      </c>
       <c r="P145" s="4"/>
     </row>
     <row r="146" spans="1:16">
@@ -5982,7 +5983,9 @@
       <c r="H150" s="17">
         <v>0.25</v>
       </c>
-      <c r="I150" s="20"/>
+      <c r="I150" s="20">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="P150" s="4"/>
     </row>
     <row r="151" spans="1:16">
@@ -6236,7 +6239,9 @@
       <c r="H161" s="17">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I161" s="20"/>
+      <c r="I161" s="20">
+        <v>0.52</v>
+      </c>
       <c r="P161" s="4"/>
     </row>
     <row r="162" spans="1:16">
@@ -6259,7 +6264,7 @@
         <v>0.68</v>
       </c>
       <c r="I162" s="20">
-        <v>0.52</v>
+        <v>0.79</v>
       </c>
       <c r="P162" s="4"/>
     </row>
@@ -6282,7 +6287,9 @@
       <c r="H163" s="17">
         <v>0.51</v>
       </c>
-      <c r="I163" s="20"/>
+      <c r="I163" s="20">
+        <v>0.6</v>
+      </c>
       <c r="P163" s="4"/>
     </row>
     <row r="164" spans="1:16">
@@ -6328,7 +6335,9 @@
       <c r="H165" s="17">
         <v>0.18</v>
       </c>
-      <c r="I165" s="20"/>
+      <c r="I165" s="20">
+        <v>0.34</v>
+      </c>
       <c r="P165" s="4"/>
     </row>
     <row r="166" spans="1:16">
@@ -6350,7 +6359,9 @@
       <c r="H166" s="17">
         <v>0.47</v>
       </c>
-      <c r="I166" s="20"/>
+      <c r="I166" s="20">
+        <v>0.24</v>
+      </c>
       <c r="P166" s="4"/>
     </row>
     <row r="167" spans="1:16">
@@ -6442,7 +6453,9 @@
       <c r="H170" s="17">
         <v>0.3</v>
       </c>
-      <c r="I170" s="20"/>
+      <c r="I170" s="20">
+        <v>0.18</v>
+      </c>
       <c r="P170" s="4"/>
     </row>
     <row r="171" spans="1:16">
@@ -6602,7 +6615,9 @@
       <c r="H177" s="17">
         <v>0.46</v>
       </c>
-      <c r="I177" s="20"/>
+      <c r="I177" s="20">
+        <v>0.43</v>
+      </c>
       <c r="P177" s="4"/>
     </row>
     <row r="178" spans="1:16">
@@ -6696,7 +6711,9 @@
       <c r="H181" s="17">
         <v>0.53</v>
       </c>
-      <c r="I181" s="20"/>
+      <c r="I181" s="20">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="P181" s="4"/>
     </row>
     <row r="182" spans="1:16">
@@ -6746,10 +6763,10 @@
       <c r="P183" s="4"/>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" s="25" t="s">
+      <c r="A184" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="B184" s="25" t="s">
+      <c r="B184" s="9" t="s">
         <v>347</v>
       </c>
       <c r="C184" s="19" t="s">
@@ -6768,10 +6785,10 @@
       <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
-      <c r="A185" s="22" t="s">
+      <c r="A185" t="s">
         <v>446</v>
       </c>
-      <c r="B185" s="26" t="s">
+      <c r="B185" s="3" t="s">
         <v>447</v>
       </c>
       <c r="C185" s="17" t="s">
@@ -6790,10 +6807,10 @@
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" s="25" t="s">
+      <c r="A186" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="B186" s="25" t="s">
+      <c r="B186" s="9" t="s">
         <v>350</v>
       </c>
       <c r="C186" s="19" t="s">
@@ -7494,10 +7511,10 @@
       <c r="P217" s="4"/>
     </row>
     <row r="218" spans="1:16">
-      <c r="A218" s="25" t="s">
+      <c r="A218" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="B218" s="25" t="s">
+      <c r="B218" s="9" t="s">
         <v>406</v>
       </c>
       <c r="C218" s="19" t="s">
@@ -7638,10 +7655,10 @@
       <c r="P223" s="4"/>
     </row>
     <row r="224" spans="1:16">
-      <c r="A224" s="22" t="s">
+      <c r="A224" t="s">
         <v>460</v>
       </c>
-      <c r="B224" s="23" t="s">
+      <c r="B224" s="2" t="s">
         <v>461</v>
       </c>
       <c r="C224" s="17" t="s">
@@ -7662,10 +7679,10 @@
       <c r="P224" s="15"/>
     </row>
     <row r="225" spans="1:16">
-      <c r="A225" s="25" t="s">
+      <c r="A225" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="B225" s="25" t="s">
+      <c r="B225" s="9" t="s">
         <v>419</v>
       </c>
       <c r="C225" s="19" t="s">
@@ -7686,10 +7703,10 @@
       <c r="P225" s="4"/>
     </row>
     <row r="226" spans="1:16">
-      <c r="A226" s="22" t="s">
+      <c r="A226" t="s">
         <v>497</v>
       </c>
-      <c r="B226" s="23" t="s">
+      <c r="B226" s="2" t="s">
         <v>498</v>
       </c>
       <c r="C226" s="17" t="s">
@@ -7705,10 +7722,10 @@
       <c r="P226" s="15"/>
     </row>
     <row r="227" spans="1:16">
-      <c r="A227" s="25" t="s">
+      <c r="A227" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="B227" s="25" t="s">
+      <c r="B227" s="9" t="s">
         <v>422</v>
       </c>
       <c r="C227" s="19" t="s">
@@ -7726,7 +7743,7 @@
       <c r="I227" s="20">
         <v>0.87</v>
       </c>
-      <c r="P227" s="24"/>
+      <c r="P227" s="16"/>
     </row>
     <row r="228" spans="1:16">
       <c r="A228" s="9" t="s">
@@ -7750,7 +7767,7 @@
       <c r="I228" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P228" s="24"/>
+      <c r="P228" s="16"/>
     </row>
     <row r="229" spans="1:16">
       <c r="A229" t="s">
@@ -7774,7 +7791,6 @@
       <c r="I229" s="20">
         <v>0.18</v>
       </c>
-      <c r="P229" s="22"/>
     </row>
     <row r="230" spans="1:16">
       <c r="A230" t="s">
@@ -7798,7 +7814,6 @@
       <c r="I230" s="20">
         <v>0.21</v>
       </c>
-      <c r="P230" s="22"/>
     </row>
     <row r="231" spans="1:16">
       <c r="A231" s="9" t="s">
@@ -7822,7 +7837,7 @@
       <c r="I231" s="20">
         <v>0.72</v>
       </c>
-      <c r="P231" s="24"/>
+      <c r="P231" s="16"/>
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="9" t="s">
@@ -7846,7 +7861,7 @@
       <c r="I232" s="20">
         <v>0.43</v>
       </c>
-      <c r="P232" s="24"/>
+      <c r="P232" s="16"/>
     </row>
     <row r="233" spans="1:16">
       <c r="A233" s="9" t="s">
@@ -7870,7 +7885,7 @@
       <c r="I233" s="20">
         <v>0.66</v>
       </c>
-      <c r="P233" s="24"/>
+      <c r="P233" s="16"/>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" s="9" t="s">
@@ -7894,7 +7909,7 @@
       <c r="I234" s="20">
         <v>0.25</v>
       </c>
-      <c r="P234" s="24"/>
+      <c r="P234" s="16"/>
     </row>
     <row r="235" spans="1:16">
       <c r="A235" t="s">
@@ -7918,7 +7933,6 @@
       <c r="I235" s="20">
         <v>0</v>
       </c>
-      <c r="P235" s="22"/>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="9" t="s">
@@ -7942,7 +7956,7 @@
       <c r="I236" s="20">
         <v>0.66</v>
       </c>
-      <c r="P236" s="24"/>
+      <c r="P236" s="16"/>
     </row>
     <row r="237" spans="1:16">
       <c r="A237" s="9" t="s">
@@ -7966,7 +7980,7 @@
       <c r="I237" s="20">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P237" s="24"/>
+      <c r="P237" s="16"/>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" t="s">
@@ -7990,7 +8004,6 @@
       <c r="I238" s="20">
         <v>0.72</v>
       </c>
-      <c r="P238" s="22"/>
     </row>
     <row r="239" spans="1:16">
       <c r="A239" t="s">
@@ -8014,7 +8027,6 @@
       <c r="I239" s="20">
         <v>0</v>
       </c>
-      <c r="P239" s="22"/>
     </row>
     <row r="240" spans="1:16">
       <c r="A240" t="s">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24D53F6-D816-304D-8247-477A2E6E7A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A1A017-34C1-2E45-A0FB-FB47940DA6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -5771,7 +5771,9 @@
       <c r="H141" s="17">
         <v>0.51</v>
       </c>
-      <c r="I141" s="20"/>
+      <c r="I141" s="20">
+        <v>0.39</v>
+      </c>
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
@@ -5913,7 +5915,9 @@
       <c r="H147" s="17">
         <v>0.75</v>
       </c>
-      <c r="I147" s="20"/>
+      <c r="I147" s="20">
+        <v>0.96</v>
+      </c>
       <c r="P147" s="4"/>
     </row>
     <row r="148" spans="1:16">
@@ -6007,7 +6011,9 @@
       <c r="H151" s="17">
         <v>0.3</v>
       </c>
-      <c r="I151" s="20"/>
+      <c r="I151" s="20">
+        <v>0.34</v>
+      </c>
       <c r="P151" s="4"/>
     </row>
     <row r="152" spans="1:16">
@@ -6029,7 +6035,9 @@
       <c r="H152" s="17">
         <v>0.63</v>
       </c>
-      <c r="I152" s="20"/>
+      <c r="I152" s="20">
+        <v>0.48</v>
+      </c>
       <c r="P152" s="4"/>
     </row>
     <row r="153" spans="1:16">
@@ -6075,7 +6083,9 @@
       <c r="H154" s="17">
         <v>0.47</v>
       </c>
-      <c r="I154" s="20"/>
+      <c r="I154" s="20">
+        <v>0.51</v>
+      </c>
       <c r="P154" s="4"/>
     </row>
     <row r="155" spans="1:16">
@@ -6097,7 +6107,9 @@
       <c r="H155" s="17">
         <v>0.49</v>
       </c>
-      <c r="I155" s="20"/>
+      <c r="I155" s="20">
+        <v>0.25</v>
+      </c>
       <c r="P155" s="4"/>
     </row>
     <row r="156" spans="1:16">
@@ -6431,7 +6443,9 @@
       <c r="H169" s="17">
         <v>0.54</v>
       </c>
-      <c r="I169" s="20"/>
+      <c r="I169" s="20">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="P169" s="4"/>
     </row>
     <row r="170" spans="1:16">
@@ -6501,7 +6515,9 @@
       <c r="H172" s="17">
         <v>0.39</v>
       </c>
-      <c r="I172" s="20"/>
+      <c r="I172" s="20">
+        <v>0.48</v>
+      </c>
       <c r="P172" s="4"/>
     </row>
     <row r="173" spans="1:16">
@@ -6523,7 +6539,9 @@
       <c r="H173" s="17">
         <v>0.35</v>
       </c>
-      <c r="I173" s="20"/>
+      <c r="I173" s="20">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="P173" s="4"/>
     </row>
     <row r="174" spans="1:16">
@@ -6546,7 +6564,7 @@
         <v>0.35</v>
       </c>
       <c r="I174" s="20">
-        <v>7.0000000000000007E-2</v>
+        <v>0.21</v>
       </c>
       <c r="P174" s="4"/>
     </row>
@@ -6569,7 +6587,9 @@
       <c r="H175" s="17">
         <v>0.33</v>
       </c>
-      <c r="I175" s="20"/>
+      <c r="I175" s="20">
+        <v>0.63</v>
+      </c>
       <c r="P175" s="4"/>
     </row>
     <row r="176" spans="1:16">
@@ -6759,7 +6779,9 @@
       <c r="H183" s="17">
         <v>0.32</v>
       </c>
-      <c r="I183" s="20"/>
+      <c r="I183" s="20">
+        <v>0.43</v>
+      </c>
       <c r="P183" s="4"/>
     </row>
     <row r="184" spans="1:16">
@@ -7067,7 +7089,9 @@
       <c r="H197" s="17">
         <v>0.46</v>
       </c>
-      <c r="I197" s="20"/>
+      <c r="I197" s="20">
+        <v>0.06</v>
+      </c>
       <c r="P197" s="4"/>
     </row>
     <row r="198" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A1A017-34C1-2E45-A0FB-FB47940DA6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3FFBFF-E679-714B-A37D-34D513A3D5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="507">
   <si>
     <t>Surname</t>
   </si>
@@ -1532,6 +1532,30 @@
   </si>
   <si>
     <t>H250593R</t>
+  </si>
+  <si>
+    <t>Masube</t>
+  </si>
+  <si>
+    <t>H230342R</t>
+  </si>
+  <si>
+    <t>Chitonho</t>
+  </si>
+  <si>
+    <t>H220523Y</t>
+  </si>
+  <si>
+    <t>Dongo</t>
+  </si>
+  <si>
+    <t>H230801Q</t>
+  </si>
+  <si>
+    <t>Dzitiro</t>
+  </si>
+  <si>
+    <t>H230341Q</t>
   </si>
 </sst>
 </file>
@@ -1669,7 +1693,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1708,6 +1732,13 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1786,10 +1817,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:P242" totalsRowShown="0">
-  <autoFilter ref="A1:P242" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P242">
-    <sortCondition ref="C1:C242"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:P246" totalsRowShown="0">
+  <autoFilter ref="A1:P246" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P246">
+    <sortCondition ref="C1:C246"/>
   </sortState>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -2130,7 +2161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:P242"/>
+  <dimension ref="A1:P246"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -2206,6 +2237,9 @@
       <c r="E2" s="17">
         <v>0.99</v>
       </c>
+      <c r="F2" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H2" s="17">
         <v>0.89</v>
       </c>
@@ -2233,6 +2267,9 @@
       <c r="E3" s="17">
         <v>0.94</v>
       </c>
+      <c r="F3" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H3" s="17">
         <v>0.39</v>
       </c>
@@ -2260,6 +2297,9 @@
       <c r="E4" s="17">
         <v>0.94</v>
       </c>
+      <c r="F4" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H4" s="17">
         <v>0.39</v>
       </c>
@@ -2287,6 +2327,9 @@
       <c r="E5" s="17">
         <v>0</v>
       </c>
+      <c r="F5" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H5" s="17">
         <v>0.54</v>
       </c>
@@ -2314,6 +2357,9 @@
       <c r="E6" s="17">
         <v>0.91</v>
       </c>
+      <c r="F6" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H6" s="17">
         <v>0.53</v>
       </c>
@@ -2341,6 +2387,9 @@
       <c r="E7" s="17">
         <v>0.94</v>
       </c>
+      <c r="F7" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H7" s="17">
         <v>0.42</v>
       </c>
@@ -2368,6 +2417,9 @@
       <c r="E8" s="17">
         <v>0</v>
       </c>
+      <c r="F8" s="17">
+        <v>0.52</v>
+      </c>
       <c r="H8" s="17">
         <v>0.11</v>
       </c>
@@ -2395,6 +2447,9 @@
       <c r="E9" s="17">
         <v>0.93</v>
       </c>
+      <c r="F9" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H9" s="17">
         <v>0.47</v>
       </c>
@@ -2422,6 +2477,9 @@
       <c r="E10" s="17">
         <v>0.9</v>
       </c>
+      <c r="F10" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H10" s="17">
         <v>0.54</v>
       </c>
@@ -2449,6 +2507,9 @@
       <c r="E11" s="17">
         <v>0.95</v>
       </c>
+      <c r="F11" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H11" s="17">
         <v>0.16</v>
       </c>
@@ -2476,6 +2537,9 @@
       <c r="E12" s="17">
         <v>0.7</v>
       </c>
+      <c r="F12" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H12" s="17">
         <v>0.44</v>
       </c>
@@ -2503,6 +2567,9 @@
       <c r="E13" s="17">
         <v>0.94</v>
       </c>
+      <c r="F13" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H13" s="17">
         <v>0.44</v>
       </c>
@@ -2530,6 +2597,9 @@
       <c r="E14" s="17">
         <v>0.82</v>
       </c>
+      <c r="F14" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H14" s="17">
         <v>0.4</v>
       </c>
@@ -2557,6 +2627,9 @@
       <c r="E15" s="17">
         <v>1</v>
       </c>
+      <c r="F15" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H15" s="17">
         <v>0.67</v>
       </c>
@@ -2584,6 +2657,9 @@
       <c r="E16" s="17">
         <v>0.9</v>
       </c>
+      <c r="F16" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H16" s="17">
         <v>0</v>
       </c>
@@ -2611,6 +2687,9 @@
       <c r="E17" s="17">
         <v>0.8</v>
       </c>
+      <c r="F17" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H17" s="17">
         <v>0.37</v>
       </c>
@@ -2638,6 +2717,9 @@
       <c r="E18" s="17">
         <v>0.93</v>
       </c>
+      <c r="F18" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H18" s="17">
         <v>0.44</v>
       </c>
@@ -2665,6 +2747,9 @@
       <c r="E19" s="17">
         <v>0</v>
       </c>
+      <c r="F19" s="17">
+        <v>0</v>
+      </c>
       <c r="H19" s="17">
         <v>0.53</v>
       </c>
@@ -2689,6 +2774,9 @@
       <c r="E20" s="17">
         <v>0.92</v>
       </c>
+      <c r="F20" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H20" s="17">
         <v>0.54</v>
       </c>
@@ -2716,6 +2804,9 @@
       <c r="E21" s="17">
         <v>0.92</v>
       </c>
+      <c r="F21" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H21" s="17">
         <v>0.65</v>
       </c>
@@ -2743,6 +2834,9 @@
       <c r="E22" s="17">
         <v>0.92</v>
       </c>
+      <c r="F22" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H22" s="17">
         <v>0.33</v>
       </c>
@@ -2770,6 +2864,9 @@
       <c r="E23" s="17">
         <v>0.93</v>
       </c>
+      <c r="F23" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H23" s="17">
         <v>0.68</v>
       </c>
@@ -2797,6 +2894,9 @@
       <c r="E24" s="17">
         <v>0.93</v>
       </c>
+      <c r="F24" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H24" s="17">
         <v>0.67</v>
       </c>
@@ -2824,6 +2924,9 @@
       <c r="E25" s="17">
         <v>0.9</v>
       </c>
+      <c r="F25" s="17">
+        <v>0.61</v>
+      </c>
       <c r="H25" s="17">
         <v>0.61</v>
       </c>
@@ -2851,6 +2954,9 @@
       <c r="E26" s="17">
         <v>0.95</v>
       </c>
+      <c r="F26" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H26" s="17">
         <v>0.53</v>
       </c>
@@ -2878,6 +2984,9 @@
       <c r="E27" s="17">
         <v>0.94</v>
       </c>
+      <c r="F27" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H27" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -2905,6 +3014,9 @@
       <c r="E28" s="17">
         <v>0.93</v>
       </c>
+      <c r="F28" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H28" s="17">
         <v>0.63</v>
       </c>
@@ -2932,6 +3044,9 @@
       <c r="E29" s="17">
         <v>0.91</v>
       </c>
+      <c r="F29" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H29" s="17">
         <v>0.75</v>
       </c>
@@ -2959,6 +3074,9 @@
       <c r="E30" s="17">
         <v>1</v>
       </c>
+      <c r="F30" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H30" s="17">
         <v>0.35</v>
       </c>
@@ -2986,6 +3104,9 @@
       <c r="E31" s="17">
         <v>0.82</v>
       </c>
+      <c r="F31" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H31" s="17">
         <v>0.6</v>
       </c>
@@ -3013,6 +3134,9 @@
       <c r="E32" s="17">
         <v>0.86</v>
       </c>
+      <c r="F32" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H32" s="17">
         <v>0.47</v>
       </c>
@@ -3040,6 +3164,9 @@
       <c r="E33" s="17">
         <v>0.85</v>
       </c>
+      <c r="F33" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H33" s="17">
         <v>0.54</v>
       </c>
@@ -3067,6 +3194,9 @@
       <c r="E34" s="17">
         <v>0.9</v>
       </c>
+      <c r="F34" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H34" s="17">
         <v>0.16</v>
       </c>
@@ -3094,6 +3224,9 @@
       <c r="E35" s="17">
         <v>0.99</v>
       </c>
+      <c r="F35" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H35" s="17">
         <v>0.42</v>
       </c>
@@ -3121,6 +3254,9 @@
       <c r="E36" s="17">
         <v>0.74</v>
       </c>
+      <c r="F36" s="17">
+        <v>0.63</v>
+      </c>
       <c r="H36" s="17">
         <v>0.47</v>
       </c>
@@ -3148,6 +3284,9 @@
       <c r="E37" s="17">
         <v>0</v>
       </c>
+      <c r="F37" s="17">
+        <v>0</v>
+      </c>
       <c r="H37" s="17">
         <v>0.77</v>
       </c>
@@ -3175,6 +3314,9 @@
       <c r="E38" s="17">
         <v>0</v>
       </c>
+      <c r="F38" s="17">
+        <v>0</v>
+      </c>
       <c r="H38" s="17">
         <v>0.52</v>
       </c>
@@ -3199,6 +3341,9 @@
       <c r="E39" s="17">
         <v>0.95</v>
       </c>
+      <c r="F39" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H39" s="17">
         <v>0.6</v>
       </c>
@@ -3226,6 +3371,9 @@
       <c r="E40" s="17">
         <v>0.94</v>
       </c>
+      <c r="F40" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H40" s="17">
         <v>0.47</v>
       </c>
@@ -3253,6 +3401,9 @@
       <c r="E41" s="17">
         <v>0.89</v>
       </c>
+      <c r="F41" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H41" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -3280,6 +3431,9 @@
       <c r="E42" s="17">
         <v>0.93</v>
       </c>
+      <c r="F42" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H42" s="17">
         <v>0.33</v>
       </c>
@@ -3307,6 +3461,9 @@
       <c r="E43" s="17">
         <v>0</v>
       </c>
+      <c r="F43" s="17">
+        <v>0</v>
+      </c>
       <c r="H43" s="17">
         <v>0.54</v>
       </c>
@@ -3331,6 +3488,9 @@
       <c r="E44" s="17">
         <v>0</v>
       </c>
+      <c r="F44" s="17">
+        <v>0</v>
+      </c>
       <c r="H44" s="17">
         <v>0.65</v>
       </c>
@@ -3355,6 +3515,9 @@
       <c r="E45" s="17">
         <v>0.82</v>
       </c>
+      <c r="F45" s="17">
+        <v>0.61</v>
+      </c>
       <c r="H45" s="17">
         <v>0.44</v>
       </c>
@@ -3382,6 +3545,9 @@
       <c r="E46" s="17">
         <v>0.89</v>
       </c>
+      <c r="F46" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H46" s="17">
         <v>0.44</v>
       </c>
@@ -3409,6 +3575,9 @@
       <c r="E47" s="17">
         <v>1</v>
       </c>
+      <c r="F47" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H47" s="17">
         <v>0.54</v>
       </c>
@@ -3436,6 +3605,9 @@
       <c r="E48" s="17">
         <v>0.97</v>
       </c>
+      <c r="F48" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H48" s="17">
         <v>0.56000000000000005</v>
       </c>
@@ -3448,10 +3620,10 @@
       <c r="P48" s="4"/>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="25" t="s">
         <v>92</v>
       </c>
       <c r="C49" s="19" t="s">
@@ -3463,6 +3635,9 @@
       <c r="E49" s="17">
         <v>0.98</v>
       </c>
+      <c r="F49" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H49" s="17">
         <v>0.68</v>
       </c>
@@ -3472,10 +3647,10 @@
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C50" s="19" t="s">
@@ -3487,6 +3662,9 @@
       <c r="E50" s="17">
         <v>0.91</v>
       </c>
+      <c r="F50" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H50" s="17">
         <v>0.75</v>
       </c>
@@ -3499,10 +3677,10 @@
       <c r="P50" s="4"/>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="25" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="19" t="s">
@@ -3514,6 +3692,9 @@
       <c r="E51" s="17">
         <v>0.94</v>
       </c>
+      <c r="F51" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H51" s="17">
         <v>0.6</v>
       </c>
@@ -3526,10 +3707,10 @@
       <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="25" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="19" t="s">
@@ -3541,6 +3722,9 @@
       <c r="E52" s="17">
         <v>0.99</v>
       </c>
+      <c r="F52" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H52" s="17">
         <v>0.54</v>
       </c>
@@ -3553,10 +3737,10 @@
       <c r="P52" s="4"/>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="25" t="s">
         <v>101</v>
       </c>
       <c r="C53" s="19" t="s">
@@ -3568,6 +3752,9 @@
       <c r="E53" s="17">
         <v>0.98</v>
       </c>
+      <c r="F53" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H53" s="17">
         <v>0.6</v>
       </c>
@@ -3580,10 +3767,10 @@
       <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -3595,6 +3782,9 @@
       <c r="E54" s="17">
         <v>0.88</v>
       </c>
+      <c r="F54" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H54" s="17">
         <v>0.33</v>
       </c>
@@ -3607,10 +3797,10 @@
       <c r="P54" s="4"/>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="25" t="s">
         <v>476</v>
       </c>
       <c r="C55" s="19" t="s">
@@ -3622,6 +3812,9 @@
       <c r="E55" s="17">
         <v>0.97</v>
       </c>
+      <c r="F55" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H55" s="17">
         <v>0.56000000000000005</v>
       </c>
@@ -3634,10 +3827,10 @@
       <c r="P55" s="4"/>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="25" t="s">
         <v>106</v>
       </c>
       <c r="C56" s="19" t="s">
@@ -3648,6 +3841,9 @@
       </c>
       <c r="E56" s="17">
         <v>0.98</v>
+      </c>
+      <c r="F56" s="17">
+        <v>0.7</v>
       </c>
       <c r="H56" s="17">
         <v>0.32</v>
@@ -3676,6 +3872,9 @@
       <c r="E57" s="17">
         <v>0.97</v>
       </c>
+      <c r="F57" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H57" s="17">
         <v>0.51</v>
       </c>
@@ -3703,6 +3902,9 @@
       <c r="E58" s="17">
         <v>0.91</v>
       </c>
+      <c r="F58" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H58" s="17">
         <v>0.32</v>
       </c>
@@ -3727,6 +3929,9 @@
       <c r="E59" s="17">
         <v>1</v>
       </c>
+      <c r="F59" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H59" s="17">
         <v>0.81</v>
       </c>
@@ -3754,6 +3959,9 @@
       <c r="E60" s="17">
         <v>0.98</v>
       </c>
+      <c r="F60" s="17">
+        <v>0.61</v>
+      </c>
       <c r="H60" s="17">
         <v>0.46</v>
       </c>
@@ -3781,6 +3989,9 @@
       <c r="E61" s="17">
         <v>0.88</v>
       </c>
+      <c r="F61" s="17">
+        <v>0.59</v>
+      </c>
       <c r="H61" s="17">
         <v>0.46</v>
       </c>
@@ -3808,6 +4019,9 @@
       <c r="E62" s="17">
         <v>0.91</v>
       </c>
+      <c r="F62" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H62" s="17">
         <v>0.37</v>
       </c>
@@ -3835,6 +4049,9 @@
       <c r="E63" s="17">
         <v>0.92</v>
       </c>
+      <c r="F63" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H63" s="17">
         <v>0.63</v>
       </c>
@@ -3862,6 +4079,9 @@
       <c r="E64" s="17">
         <v>0.99</v>
       </c>
+      <c r="F64" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H64" s="17">
         <v>0.37</v>
       </c>
@@ -3889,6 +4109,9 @@
       <c r="E65" s="17">
         <v>1</v>
       </c>
+      <c r="F65" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H65" s="17">
         <v>0.53</v>
       </c>
@@ -3916,6 +4139,9 @@
       <c r="E66" s="17">
         <v>0.78</v>
       </c>
+      <c r="F66" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H66" s="17">
         <v>0.35</v>
       </c>
@@ -3943,6 +4169,9 @@
       <c r="E67" s="17">
         <v>1</v>
       </c>
+      <c r="F67" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H67" s="17">
         <v>0.77</v>
       </c>
@@ -3970,6 +4199,9 @@
       <c r="E68" s="17">
         <v>0.97</v>
       </c>
+      <c r="F68" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H68" s="17">
         <v>0.6</v>
       </c>
@@ -3997,6 +4229,9 @@
       <c r="E69" s="17">
         <v>0.98</v>
       </c>
+      <c r="F69" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H69" s="17">
         <v>0.56000000000000005</v>
       </c>
@@ -4024,6 +4259,9 @@
       <c r="E70" s="17">
         <v>0.87</v>
       </c>
+      <c r="F70" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H70" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -4051,6 +4289,9 @@
       <c r="E71" s="17">
         <v>0.91</v>
       </c>
+      <c r="F71" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H71" s="17">
         <v>0.35</v>
       </c>
@@ -4078,6 +4319,9 @@
       <c r="E72" s="17">
         <v>0.89</v>
       </c>
+      <c r="F72" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H72" s="17">
         <v>0.28000000000000003</v>
       </c>
@@ -4105,6 +4349,9 @@
       <c r="E73" s="17">
         <v>1</v>
       </c>
+      <c r="F73" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H73" s="17">
         <v>0.77</v>
       </c>
@@ -4132,6 +4379,9 @@
       <c r="E74" s="17">
         <v>0.98</v>
       </c>
+      <c r="F74" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H74" s="17">
         <v>0.51</v>
       </c>
@@ -4156,6 +4406,9 @@
       <c r="E75" s="17">
         <v>0.96</v>
       </c>
+      <c r="F75" s="17">
+        <v>0.72</v>
+      </c>
       <c r="H75" s="17">
         <v>0.05</v>
       </c>
@@ -4180,6 +4433,9 @@
       <c r="E76" s="17">
         <v>0.99</v>
       </c>
+      <c r="F76" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H76" s="17">
         <v>0.61</v>
       </c>
@@ -4207,6 +4463,9 @@
       <c r="E77" s="17">
         <v>1</v>
       </c>
+      <c r="F77" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H77" s="17">
         <v>0.74</v>
       </c>
@@ -4234,6 +4493,9 @@
       <c r="E78" s="17">
         <v>0.92</v>
       </c>
+      <c r="F78" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H78" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -4258,6 +4520,9 @@
       <c r="E79" s="17">
         <v>0.93</v>
       </c>
+      <c r="F79" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H79" s="17">
         <v>0.61</v>
       </c>
@@ -4285,6 +4550,9 @@
       <c r="E80" s="17">
         <v>0.94</v>
       </c>
+      <c r="F80" s="17">
+        <v>0.72</v>
+      </c>
       <c r="H80" s="17">
         <v>0.47</v>
       </c>
@@ -4312,6 +4580,9 @@
       <c r="E81" s="17">
         <v>0.87</v>
       </c>
+      <c r="F81" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="H81" s="17">
         <v>0.65</v>
       </c>
@@ -4339,6 +4610,9 @@
       <c r="E82" s="17">
         <v>0.98</v>
       </c>
+      <c r="F82" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H82" s="17">
         <v>0.39</v>
       </c>
@@ -4366,6 +4640,9 @@
       <c r="E83" s="17">
         <v>0.97</v>
       </c>
+      <c r="F83" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H83" s="17">
         <v>0.54</v>
       </c>
@@ -4393,6 +4670,9 @@
       <c r="E84" s="17">
         <v>0.93</v>
       </c>
+      <c r="F84" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H84" s="17">
         <v>0.79</v>
       </c>
@@ -4420,6 +4700,9 @@
       <c r="E85" s="17">
         <v>1</v>
       </c>
+      <c r="F85" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H85" s="17">
         <v>0.63</v>
       </c>
@@ -4447,6 +4730,9 @@
       <c r="E86" s="17">
         <v>0.89</v>
       </c>
+      <c r="F86" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H86" s="17">
         <v>0.61</v>
       </c>
@@ -4474,6 +4760,9 @@
       <c r="E87" s="17">
         <v>0.82</v>
       </c>
+      <c r="F87" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H87" s="17">
         <v>0.25</v>
       </c>
@@ -4498,6 +4787,9 @@
       <c r="E88" s="17">
         <v>0.98</v>
       </c>
+      <c r="F88" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H88" s="17">
         <v>0.6</v>
       </c>
@@ -4525,6 +4817,9 @@
       <c r="E89" s="17">
         <v>0.96</v>
       </c>
+      <c r="F89" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H89" s="17">
         <v>0.54</v>
       </c>
@@ -4534,10 +4829,10 @@
       <c r="P89" s="4"/>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="25" t="s">
         <v>172</v>
       </c>
       <c r="C90" s="19" t="s">
@@ -4549,6 +4844,9 @@
       <c r="E90" s="17">
         <v>0.97</v>
       </c>
+      <c r="F90" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H90" s="17">
         <v>0.68</v>
       </c>
@@ -4558,10 +4856,10 @@
       <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="25" t="s">
         <v>175</v>
       </c>
       <c r="C91" s="19" t="s">
@@ -4573,6 +4871,9 @@
       <c r="E91" s="17">
         <v>0.86</v>
       </c>
+      <c r="F91" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H91" s="17">
         <v>0.6</v>
       </c>
@@ -4582,10 +4883,10 @@
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" t="s">
+      <c r="A92" s="22" t="s">
         <v>474</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="23" t="s">
         <v>475</v>
       </c>
       <c r="C92" s="17" t="s">
@@ -4597,6 +4898,9 @@
       <c r="E92" s="17">
         <v>0.53</v>
       </c>
+      <c r="F92" s="17">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="H92" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -4606,10 +4910,10 @@
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="B93" s="9" t="s">
+      <c r="B93" s="25" t="s">
         <v>177</v>
       </c>
       <c r="C93" s="19" t="s">
@@ -4621,6 +4925,9 @@
       <c r="E93" s="17">
         <v>0.99</v>
       </c>
+      <c r="F93" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H93" s="17">
         <v>0.47</v>
       </c>
@@ -4630,10 +4937,10 @@
       <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="25" t="s">
         <v>179</v>
       </c>
       <c r="C94" s="19" t="s">
@@ -4645,6 +4952,9 @@
       <c r="E94" s="17">
         <v>0.91</v>
       </c>
+      <c r="F94" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H94" s="17">
         <v>0.65</v>
       </c>
@@ -4654,10 +4964,10 @@
       <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="25" t="s">
         <v>181</v>
       </c>
       <c r="C95" s="19" t="s">
@@ -4669,6 +4979,9 @@
       <c r="E95" s="17">
         <v>1</v>
       </c>
+      <c r="F95" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H95" s="17">
         <v>0.42</v>
       </c>
@@ -4678,10 +4991,10 @@
       <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="25" t="s">
         <v>183</v>
       </c>
       <c r="C96" s="19" t="s">
@@ -4693,6 +5006,9 @@
       <c r="E96" s="17">
         <v>0.9</v>
       </c>
+      <c r="F96" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H96" s="17">
         <v>0.79</v>
       </c>
@@ -4702,10 +5018,10 @@
       <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="25" t="s">
         <v>185</v>
       </c>
       <c r="C97" s="19" t="s">
@@ -4716,6 +5032,9 @@
       </c>
       <c r="E97" s="17">
         <v>0.98</v>
+      </c>
+      <c r="F97" s="17">
+        <v>0.7</v>
       </c>
       <c r="H97" s="17">
         <v>0.46</v>
@@ -4736,6 +5055,9 @@
         <v>173</v>
       </c>
       <c r="D98" s="20"/>
+      <c r="F98" s="17">
+        <v>0</v>
+      </c>
       <c r="H98" s="20">
         <v>0</v>
       </c>
@@ -4760,6 +5082,9 @@
       <c r="E99" s="17">
         <v>0.96</v>
       </c>
+      <c r="F99" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H99" s="17">
         <v>0.72</v>
       </c>
@@ -4784,6 +5109,9 @@
       <c r="E100" s="17">
         <v>0.96</v>
       </c>
+      <c r="F100" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H100" s="17">
         <v>0.28000000000000003</v>
       </c>
@@ -4808,6 +5136,9 @@
       <c r="E101" s="17">
         <v>1</v>
       </c>
+      <c r="F101" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H101" s="17">
         <v>0.4</v>
       </c>
@@ -4832,6 +5163,9 @@
       <c r="E102" s="17">
         <v>0.91</v>
       </c>
+      <c r="F102" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H102" s="17">
         <v>0.44</v>
       </c>
@@ -4856,6 +5190,9 @@
       <c r="E103" s="17">
         <v>0.99</v>
       </c>
+      <c r="F103" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H103" s="17">
         <v>0.51</v>
       </c>
@@ -4880,6 +5217,9 @@
       <c r="E104" s="17">
         <v>0.8</v>
       </c>
+      <c r="F104" s="17">
+        <v>0.53</v>
+      </c>
       <c r="H104" s="17">
         <v>0.49</v>
       </c>
@@ -4904,6 +5244,9 @@
       <c r="E105" s="17">
         <v>1</v>
       </c>
+      <c r="F105" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="H105" s="17">
         <v>0.54</v>
       </c>
@@ -4928,6 +5271,9 @@
       <c r="E106" s="17">
         <v>1</v>
       </c>
+      <c r="F106" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H106" s="17">
         <v>0.51</v>
       </c>
@@ -4952,6 +5298,9 @@
       <c r="E107" s="17">
         <v>0.94</v>
       </c>
+      <c r="F107" s="17">
+        <v>0.72</v>
+      </c>
       <c r="H107" s="17">
         <v>0.4</v>
       </c>
@@ -4976,6 +5325,9 @@
       <c r="E108" s="17">
         <v>1</v>
       </c>
+      <c r="F108" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H108" s="17">
         <v>0.44</v>
       </c>
@@ -5000,6 +5352,9 @@
       <c r="E109" s="17">
         <v>0.91</v>
       </c>
+      <c r="F109" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H109" s="17">
         <v>0.39</v>
       </c>
@@ -5024,6 +5379,9 @@
       <c r="E110" s="17">
         <v>0.89</v>
       </c>
+      <c r="F110" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H110" s="17">
         <v>0.75</v>
       </c>
@@ -5048,6 +5406,9 @@
       <c r="E111" s="17">
         <v>1</v>
       </c>
+      <c r="F111" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H111" s="17">
         <v>0.61</v>
       </c>
@@ -5072,6 +5433,9 @@
       <c r="E112" s="17">
         <v>0.94</v>
       </c>
+      <c r="F112" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H112" s="17">
         <v>0.26</v>
       </c>
@@ -5096,6 +5460,9 @@
       <c r="E113" s="17">
         <v>1</v>
       </c>
+      <c r="F113" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H113" s="17">
         <v>0.46</v>
       </c>
@@ -5120,6 +5487,9 @@
       <c r="E114" s="17">
         <v>0.91</v>
       </c>
+      <c r="F114" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H114" s="17">
         <v>0.42</v>
       </c>
@@ -5144,6 +5514,9 @@
       <c r="E115" s="17">
         <v>0.91</v>
       </c>
+      <c r="F115" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H115" s="17">
         <v>0.39</v>
       </c>
@@ -5168,6 +5541,9 @@
       <c r="E116" s="17">
         <v>0.87</v>
       </c>
+      <c r="F116" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H116" s="17">
         <v>0.46</v>
       </c>
@@ -5192,6 +5568,9 @@
       <c r="E117" s="17">
         <v>0.84</v>
       </c>
+      <c r="F117" s="17">
+        <v>0.69</v>
+      </c>
       <c r="H117" s="17">
         <v>0.63</v>
       </c>
@@ -5216,6 +5595,9 @@
       <c r="E118" s="17">
         <v>0.9</v>
       </c>
+      <c r="F118" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H118" s="17">
         <v>0.44</v>
       </c>
@@ -5240,6 +5622,9 @@
       <c r="E119" s="17">
         <v>0.9</v>
       </c>
+      <c r="F119" s="17">
+        <v>0.72</v>
+      </c>
       <c r="H119" s="17">
         <v>0.54</v>
       </c>
@@ -5264,6 +5649,9 @@
       <c r="E120" s="17">
         <v>0.9</v>
       </c>
+      <c r="F120" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H120" s="17">
         <v>0.14000000000000001</v>
       </c>
@@ -5288,6 +5676,9 @@
       <c r="E121" s="17">
         <v>0.97</v>
       </c>
+      <c r="F121" s="17">
+        <v>0.69</v>
+      </c>
       <c r="H121" s="17">
         <v>0.26</v>
       </c>
@@ -5312,6 +5703,9 @@
       <c r="E122" s="17">
         <v>0.96</v>
       </c>
+      <c r="F122" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H122" s="17">
         <v>0.26</v>
       </c>
@@ -5336,6 +5730,9 @@
       <c r="E123" s="17">
         <v>0.5</v>
       </c>
+      <c r="F123" s="17">
+        <v>0.63</v>
+      </c>
       <c r="H123" s="17">
         <v>0.26</v>
       </c>
@@ -5360,6 +5757,9 @@
       <c r="E124" s="17">
         <v>0.96</v>
       </c>
+      <c r="F124" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H124" s="17">
         <v>0.09</v>
       </c>
@@ -5384,6 +5784,9 @@
       <c r="E125" s="17">
         <v>0.99</v>
       </c>
+      <c r="F125" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H125" s="17">
         <v>0.49</v>
       </c>
@@ -5408,6 +5811,9 @@
       <c r="E126" s="17">
         <v>0.98</v>
       </c>
+      <c r="F126" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H126" s="17">
         <v>0.74</v>
       </c>
@@ -5432,6 +5838,9 @@
       <c r="E127" s="17">
         <v>1</v>
       </c>
+      <c r="F127" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H127" s="17">
         <v>0.26</v>
       </c>
@@ -5456,6 +5865,9 @@
       <c r="E128" s="17">
         <v>0.99</v>
       </c>
+      <c r="F128" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H128" s="17">
         <v>0.32</v>
       </c>
@@ -5480,6 +5892,9 @@
       <c r="E129" s="17">
         <v>0.92</v>
       </c>
+      <c r="F129" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H129" s="17">
         <v>0.11</v>
       </c>
@@ -5504,6 +5919,9 @@
       <c r="E130" s="17">
         <v>0.96</v>
       </c>
+      <c r="F130" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H130" s="17">
         <v>0.65</v>
       </c>
@@ -5528,6 +5946,9 @@
       <c r="E131" s="17">
         <v>0.99</v>
       </c>
+      <c r="F131" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="H131" s="17">
         <v>0.28000000000000003</v>
       </c>
@@ -5552,6 +5973,9 @@
       <c r="E132" s="17">
         <v>1</v>
       </c>
+      <c r="F132" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H132" s="17">
         <v>0.47</v>
       </c>
@@ -5576,6 +6000,9 @@
       <c r="E133" s="17">
         <v>0.86</v>
       </c>
+      <c r="F133" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H133" s="17">
         <v>0.35</v>
       </c>
@@ -5585,10 +6012,10 @@
       <c r="P133" s="4"/>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="9" t="s">
+      <c r="A134" s="25" t="s">
         <v>250</v>
       </c>
-      <c r="B134" s="9" t="s">
+      <c r="B134" s="25" t="s">
         <v>251</v>
       </c>
       <c r="C134" s="19" t="s">
@@ -5600,6 +6027,9 @@
       <c r="E134" s="17">
         <v>0.98</v>
       </c>
+      <c r="F134" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H134" s="17">
         <v>0.4</v>
       </c>
@@ -5609,10 +6039,10 @@
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" s="9" t="s">
+      <c r="A135" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="B135" s="9" t="s">
+      <c r="B135" s="25" t="s">
         <v>254</v>
       </c>
       <c r="C135" s="19" t="s">
@@ -5624,6 +6054,9 @@
       <c r="E135" s="17">
         <v>0.97</v>
       </c>
+      <c r="F135" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H135" s="17">
         <v>0.56000000000000005</v>
       </c>
@@ -5633,10 +6066,10 @@
       <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="9" t="s">
+      <c r="A136" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="B136" s="9" t="s">
+      <c r="B136" s="25" t="s">
         <v>256</v>
       </c>
       <c r="C136" s="19" t="s">
@@ -5648,6 +6081,9 @@
       <c r="E136" s="17">
         <v>0.99</v>
       </c>
+      <c r="F136" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H136" s="17">
         <v>0.63</v>
       </c>
@@ -5657,10 +6093,10 @@
       <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="9" t="s">
+      <c r="A137" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="B137" s="9" t="s">
+      <c r="B137" s="25" t="s">
         <v>258</v>
       </c>
       <c r="C137" s="19" t="s">
@@ -5672,6 +6108,9 @@
       <c r="E137" s="17">
         <v>0.93</v>
       </c>
+      <c r="F137" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H137" s="17">
         <v>0.42</v>
       </c>
@@ -5681,10 +6120,10 @@
       <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="9" t="s">
+      <c r="A138" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="B138" s="9" t="s">
+      <c r="B138" s="25" t="s">
         <v>260</v>
       </c>
       <c r="C138" s="19" t="s">
@@ -5696,6 +6135,9 @@
       <c r="E138" s="17">
         <v>1</v>
       </c>
+      <c r="F138" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H138" s="17">
         <v>0.39</v>
       </c>
@@ -5705,10 +6147,10 @@
       <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="9" t="s">
+      <c r="A139" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="B139" s="9" t="s">
+      <c r="B139" s="25" t="s">
         <v>262</v>
       </c>
       <c r="C139" s="19" t="s">
@@ -5720,6 +6162,9 @@
       <c r="E139" s="17">
         <v>0.98</v>
       </c>
+      <c r="F139" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H139" s="17">
         <v>0.74</v>
       </c>
@@ -5729,10 +6174,10 @@
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" s="9" t="s">
+      <c r="A140" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="B140" s="9" t="s">
+      <c r="B140" s="25" t="s">
         <v>264</v>
       </c>
       <c r="C140" s="19" t="s">
@@ -5744,6 +6189,9 @@
       <c r="E140" s="17">
         <v>0.96</v>
       </c>
+      <c r="F140" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H140" s="17">
         <v>0.39</v>
       </c>
@@ -5753,10 +6201,10 @@
       <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="9" t="s">
+      <c r="A141" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="B141" s="9" t="s">
+      <c r="B141" s="25" t="s">
         <v>266</v>
       </c>
       <c r="C141" s="19" t="s">
@@ -5768,6 +6216,9 @@
       <c r="E141" s="17">
         <v>0.92</v>
       </c>
+      <c r="F141" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H141" s="17">
         <v>0.51</v>
       </c>
@@ -5777,10 +6228,10 @@
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="9" t="s">
+      <c r="A142" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="B142" s="9" t="s">
+      <c r="B142" s="25" t="s">
         <v>268</v>
       </c>
       <c r="C142" s="19" t="s">
@@ -5792,6 +6243,9 @@
       <c r="E142" s="17">
         <v>0.82</v>
       </c>
+      <c r="F142" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H142" s="17">
         <v>0.42</v>
       </c>
@@ -5801,10 +6255,10 @@
       <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="9" t="s">
+      <c r="A143" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="B143" s="9" t="s">
+      <c r="B143" s="25" t="s">
         <v>270</v>
       </c>
       <c r="C143" s="19" t="s">
@@ -5815,6 +6269,9 @@
       </c>
       <c r="E143" s="17">
         <v>0.93</v>
+      </c>
+      <c r="F143" s="17">
+        <v>0.64</v>
       </c>
       <c r="H143" s="17">
         <v>0</v>
@@ -5840,6 +6297,9 @@
       <c r="E144" s="17">
         <v>0.92</v>
       </c>
+      <c r="F144" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H144" s="17">
         <v>0.16</v>
       </c>
@@ -5864,6 +6324,9 @@
       <c r="E145" s="17">
         <v>0.91</v>
       </c>
+      <c r="F145" s="17">
+        <v>0.47</v>
+      </c>
       <c r="H145" s="17">
         <v>0.65</v>
       </c>
@@ -5888,6 +6351,9 @@
       <c r="E146" s="17">
         <v>1</v>
       </c>
+      <c r="F146" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H146" s="17">
         <v>0.4</v>
       </c>
@@ -5912,6 +6378,9 @@
       <c r="E147" s="17">
         <v>0.99</v>
       </c>
+      <c r="F147" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H147" s="17">
         <v>0.75</v>
       </c>
@@ -5936,6 +6405,9 @@
       <c r="E148" s="17">
         <v>1</v>
       </c>
+      <c r="F148" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H148" s="17">
         <v>0.63</v>
       </c>
@@ -5960,6 +6432,9 @@
       <c r="E149" s="17">
         <v>0.93</v>
       </c>
+      <c r="F149" s="17">
+        <v>0.64</v>
+      </c>
       <c r="H149" s="17">
         <v>0.21</v>
       </c>
@@ -5984,6 +6459,9 @@
       <c r="E150" s="17">
         <v>0</v>
       </c>
+      <c r="F150" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H150" s="17">
         <v>0.25</v>
       </c>
@@ -6008,6 +6486,9 @@
       <c r="E151" s="17">
         <v>0.94</v>
       </c>
+      <c r="F151" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H151" s="17">
         <v>0.3</v>
       </c>
@@ -6032,6 +6513,9 @@
       <c r="E152" s="17">
         <v>0.91</v>
       </c>
+      <c r="F152" s="17">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="H152" s="17">
         <v>0.63</v>
       </c>
@@ -6056,6 +6540,9 @@
       <c r="E153" s="17">
         <v>0.97</v>
       </c>
+      <c r="F153" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H153" s="17">
         <v>0.86</v>
       </c>
@@ -6080,6 +6567,9 @@
       <c r="E154" s="17">
         <v>0.81</v>
       </c>
+      <c r="F154" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H154" s="17">
         <v>0.47</v>
       </c>
@@ -6104,6 +6594,9 @@
       <c r="E155" s="17">
         <v>0.94</v>
       </c>
+      <c r="F155" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H155" s="17">
         <v>0.49</v>
       </c>
@@ -6128,6 +6621,9 @@
       <c r="E156" s="17">
         <v>0.97</v>
       </c>
+      <c r="F156" s="17">
+        <v>0.64</v>
+      </c>
       <c r="H156" s="17">
         <v>0.44</v>
       </c>
@@ -6152,6 +6648,9 @@
       <c r="E157" s="17">
         <v>0.89</v>
       </c>
+      <c r="F157" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H157" s="17">
         <v>0.65</v>
       </c>
@@ -6176,6 +6675,9 @@
       <c r="E158" s="17">
         <v>0.99</v>
       </c>
+      <c r="F158" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H158" s="17">
         <v>0.6</v>
       </c>
@@ -6200,6 +6702,9 @@
       <c r="E159" s="17">
         <v>0.86</v>
       </c>
+      <c r="F159" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H159" s="17">
         <v>0.46</v>
       </c>
@@ -6224,6 +6729,9 @@
       <c r="E160" s="17">
         <v>0.99</v>
       </c>
+      <c r="F160" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H160" s="17">
         <v>0.42</v>
       </c>
@@ -6248,6 +6756,9 @@
       <c r="E161" s="17">
         <v>0.97</v>
       </c>
+      <c r="F161" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H161" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -6272,6 +6783,9 @@
       <c r="E162" s="17">
         <v>0.92</v>
       </c>
+      <c r="F162" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H162" s="17">
         <v>0.68</v>
       </c>
@@ -6296,6 +6810,9 @@
       <c r="E163" s="17">
         <v>1</v>
       </c>
+      <c r="F163" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H163" s="17">
         <v>0.51</v>
       </c>
@@ -6320,6 +6837,9 @@
       <c r="E164" s="17">
         <v>0.98</v>
       </c>
+      <c r="F164" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H164" s="17">
         <v>0.33</v>
       </c>
@@ -6344,6 +6864,9 @@
       <c r="E165" s="17">
         <v>0.97</v>
       </c>
+      <c r="F165" s="17">
+        <v>0.64</v>
+      </c>
       <c r="H165" s="17">
         <v>0.18</v>
       </c>
@@ -6368,6 +6891,9 @@
       <c r="E166" s="17">
         <v>0.87</v>
       </c>
+      <c r="F166" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H166" s="17">
         <v>0.47</v>
       </c>
@@ -6392,6 +6918,9 @@
       <c r="E167" s="17">
         <v>0.97</v>
       </c>
+      <c r="F167" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H167" s="17">
         <v>0.63</v>
       </c>
@@ -6416,6 +6945,9 @@
       <c r="E168" s="17">
         <v>0.98</v>
       </c>
+      <c r="F168" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H168" s="17">
         <v>0.56000000000000005</v>
       </c>
@@ -6440,6 +6972,9 @@
       <c r="E169" s="17">
         <v>0.96</v>
       </c>
+      <c r="F169" s="17">
+        <v>0.53</v>
+      </c>
       <c r="H169" s="17">
         <v>0.54</v>
       </c>
@@ -6464,6 +6999,9 @@
       <c r="E170" s="17">
         <v>0.99</v>
       </c>
+      <c r="F170" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H170" s="17">
         <v>0.3</v>
       </c>
@@ -6488,6 +7026,9 @@
       <c r="E171" s="17">
         <v>0.98</v>
       </c>
+      <c r="F171" s="17">
+        <v>0.64</v>
+      </c>
       <c r="H171" s="17">
         <v>0.25</v>
       </c>
@@ -6512,6 +7053,9 @@
       <c r="E172" s="17">
         <v>1</v>
       </c>
+      <c r="F172" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H172" s="17">
         <v>0.39</v>
       </c>
@@ -6536,6 +7080,9 @@
       <c r="E173" s="17">
         <v>0.87</v>
       </c>
+      <c r="F173" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H173" s="17">
         <v>0.35</v>
       </c>
@@ -6560,6 +7107,9 @@
       <c r="E174" s="17">
         <v>0.93</v>
       </c>
+      <c r="F174" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H174" s="17">
         <v>0.35</v>
       </c>
@@ -6584,6 +7134,9 @@
       <c r="E175" s="17">
         <v>1</v>
       </c>
+      <c r="F175" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H175" s="17">
         <v>0.33</v>
       </c>
@@ -6608,6 +7161,9 @@
       <c r="E176" s="17">
         <v>0.89</v>
       </c>
+      <c r="F176" s="17">
+        <v>0.64</v>
+      </c>
       <c r="H176" s="17">
         <v>0.12</v>
       </c>
@@ -6632,6 +7188,9 @@
       <c r="E177" s="17">
         <v>0.97</v>
       </c>
+      <c r="F177" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H177" s="17">
         <v>0.46</v>
       </c>
@@ -6656,6 +7215,9 @@
       <c r="E178" s="17">
         <v>0</v>
       </c>
+      <c r="F178" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H178" s="17">
         <v>0.19</v>
       </c>
@@ -6680,6 +7242,9 @@
       <c r="E179" s="17">
         <v>0.99</v>
       </c>
+      <c r="F179" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H179" s="17">
         <v>0.42</v>
       </c>
@@ -6704,6 +7269,9 @@
       <c r="E180" s="17">
         <v>1</v>
       </c>
+      <c r="F180" s="17">
+        <v>0.77</v>
+      </c>
       <c r="H180" s="17">
         <v>0.61</v>
       </c>
@@ -6728,6 +7296,9 @@
       <c r="E181" s="17">
         <v>0.91</v>
       </c>
+      <c r="F181" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H181" s="17">
         <v>0.53</v>
       </c>
@@ -6752,6 +7323,9 @@
       <c r="E182" s="17">
         <v>0.98</v>
       </c>
+      <c r="F182" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H182" s="17">
         <v>0.35</v>
       </c>
@@ -6776,6 +7350,9 @@
       <c r="E183" s="17">
         <v>0.89</v>
       </c>
+      <c r="F183" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H183" s="17">
         <v>0.32</v>
       </c>
@@ -6785,10 +7362,10 @@
       <c r="P183" s="4"/>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" s="9" t="s">
+      <c r="A184" s="25" t="s">
         <v>346</v>
       </c>
-      <c r="B184" s="9" t="s">
+      <c r="B184" s="25" t="s">
         <v>347</v>
       </c>
       <c r="C184" s="19" t="s">
@@ -6800,6 +7377,9 @@
       <c r="E184" s="17">
         <v>0.97</v>
       </c>
+      <c r="F184" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H184" s="17">
         <v>0.26</v>
       </c>
@@ -6807,10 +7387,10 @@
       <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
-      <c r="A185" t="s">
+      <c r="A185" s="22" t="s">
         <v>446</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="26" t="s">
         <v>447</v>
       </c>
       <c r="C185" s="17" t="s">
@@ -6822,6 +7402,9 @@
       <c r="E185" s="17">
         <v>0.98</v>
       </c>
+      <c r="F185" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H185" s="17">
         <v>0.19</v>
       </c>
@@ -6829,10 +7412,10 @@
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" s="9" t="s">
+      <c r="A186" s="25" t="s">
         <v>349</v>
       </c>
-      <c r="B186" s="9" t="s">
+      <c r="B186" s="25" t="s">
         <v>350</v>
       </c>
       <c r="C186" s="19" t="s">
@@ -6844,6 +7427,9 @@
       <c r="E186" s="17">
         <v>0.97</v>
       </c>
+      <c r="F186" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H186" s="17">
         <v>0.35</v>
       </c>
@@ -6851,343 +7437,394 @@
       <c r="P186" s="4"/>
     </row>
     <row r="187" spans="1:16">
-      <c r="A187" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="B187" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="C187" s="19" t="s">
+      <c r="A187" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="B187" s="23" t="s">
+        <v>502</v>
+      </c>
+      <c r="C187" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D187" s="19">
-        <v>0.92</v>
+      <c r="D187" s="20">
+        <v>0</v>
       </c>
       <c r="E187" s="17">
-        <v>0.97</v>
-      </c>
-      <c r="H187" s="17">
-        <v>0.63</v>
-      </c>
-      <c r="I187" s="20"/>
-      <c r="P187" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="F187" s="17">
+        <v>0</v>
+      </c>
+      <c r="H187" s="20">
+        <v>0</v>
+      </c>
+      <c r="I187" s="20">
+        <v>0.13</v>
+      </c>
+      <c r="P187" s="15"/>
     </row>
     <row r="188" spans="1:16">
-      <c r="A188" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="B188" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="C188" s="19" t="s">
+      <c r="A188" t="s">
+        <v>505</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C188" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D188" s="19">
-        <v>0.8</v>
+      <c r="D188" s="20">
+        <v>0</v>
       </c>
       <c r="E188" s="17">
-        <v>1</v>
-      </c>
-      <c r="H188" s="17">
-        <v>0.39</v>
+        <v>0</v>
+      </c>
+      <c r="F188" s="17">
+        <v>0.59</v>
+      </c>
+      <c r="H188" s="20">
+        <v>0</v>
       </c>
       <c r="I188" s="20"/>
-      <c r="P188" s="4"/>
+      <c r="P188" s="15"/>
     </row>
     <row r="189" spans="1:16">
       <c r="A189" s="9" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C189" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D189" s="19">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="E189" s="17">
-        <v>1</v>
+        <v>0.97</v>
+      </c>
+      <c r="F189" s="17">
+        <v>0.7</v>
       </c>
       <c r="H189" s="17">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="I189" s="20"/>
       <c r="P189" s="4"/>
     </row>
     <row r="190" spans="1:16">
       <c r="A190" s="9" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C190" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D190" s="19">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="E190" s="17">
-        <v>0.96</v>
+        <v>1</v>
+      </c>
+      <c r="F190" s="17">
+        <v>0.7</v>
       </c>
       <c r="H190" s="17">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="I190" s="20"/>
       <c r="P190" s="4"/>
     </row>
     <row r="191" spans="1:16">
       <c r="A191" s="9" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C191" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D191" s="19">
-        <v>0.81</v>
+        <v>0.75</v>
       </c>
       <c r="E191" s="17">
         <v>1</v>
       </c>
+      <c r="F191" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H191" s="17">
-        <v>0.57999999999999996</v>
+        <v>0.68</v>
       </c>
       <c r="I191" s="20"/>
       <c r="P191" s="4"/>
     </row>
     <row r="192" spans="1:16">
       <c r="A192" s="9" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C192" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D192" s="19">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="E192" s="17">
-        <v>0.98</v>
+        <v>0.96</v>
+      </c>
+      <c r="F192" s="17">
+        <v>0.7</v>
       </c>
       <c r="H192" s="17">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="I192" s="20"/>
       <c r="P192" s="4"/>
     </row>
     <row r="193" spans="1:16">
       <c r="A193" s="9" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C193" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D193" s="19">
-        <v>0.64</v>
+        <v>0.81</v>
       </c>
       <c r="E193" s="17">
-        <v>0.96</v>
+        <v>1</v>
+      </c>
+      <c r="F193" s="17">
+        <v>0.7</v>
       </c>
       <c r="H193" s="17">
-        <v>0.04</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I193" s="20"/>
       <c r="P193" s="4"/>
     </row>
     <row r="194" spans="1:16">
-      <c r="A194" t="s">
-        <v>442</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C194" s="17" t="s">
+      <c r="A194" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="C194" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D194" s="20">
-        <v>0</v>
+      <c r="D194" s="19">
+        <v>0.84</v>
       </c>
       <c r="E194" s="17">
-        <v>1</v>
+        <v>0.98</v>
+      </c>
+      <c r="F194" s="17">
+        <v>0.52</v>
       </c>
       <c r="H194" s="17">
-        <v>0.26</v>
-      </c>
-      <c r="I194" s="20"/>
+        <v>0.6</v>
+      </c>
+      <c r="I194" s="20">
+        <v>0.49</v>
+      </c>
       <c r="P194" s="4"/>
     </row>
     <row r="195" spans="1:16">
       <c r="A195" s="9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C195" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D195" s="19">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="E195" s="17">
-        <v>0.97</v>
+        <v>0.96</v>
+      </c>
+      <c r="F195" s="17">
+        <v>0.77</v>
       </c>
       <c r="H195" s="17">
-        <v>0.54</v>
+        <v>0.04</v>
       </c>
       <c r="I195" s="20"/>
       <c r="P195" s="4"/>
     </row>
     <row r="196" spans="1:16">
-      <c r="A196" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="B196" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="C196" s="19" t="s">
+      <c r="A196" t="s">
+        <v>442</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C196" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D196" s="19">
-        <v>0.91</v>
+      <c r="D196" s="20">
+        <v>0</v>
       </c>
       <c r="E196" s="17">
-        <v>0.94</v>
+        <v>1</v>
+      </c>
+      <c r="F196" s="17">
+        <v>0.7</v>
       </c>
       <c r="H196" s="17">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="I196" s="20"/>
       <c r="P196" s="4"/>
     </row>
     <row r="197" spans="1:16">
       <c r="A197" s="9" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C197" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D197" s="19">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="E197" s="17">
-        <v>0.98</v>
+        <v>0.97</v>
+      </c>
+      <c r="F197" s="17">
+        <v>0.7</v>
       </c>
       <c r="H197" s="17">
-        <v>0.46</v>
-      </c>
-      <c r="I197" s="20">
-        <v>0.06</v>
-      </c>
+        <v>0.54</v>
+      </c>
+      <c r="I197" s="20"/>
       <c r="P197" s="4"/>
     </row>
     <row r="198" spans="1:16">
       <c r="A198" s="9" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C198" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D198" s="19">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="E198" s="17">
-        <v>0.99</v>
+        <v>0.94</v>
+      </c>
+      <c r="F198" s="17">
+        <v>0.77</v>
       </c>
       <c r="H198" s="17">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="I198" s="20"/>
       <c r="P198" s="4"/>
     </row>
     <row r="199" spans="1:16">
-      <c r="A199" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="B199" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="C199" s="19" t="s">
+      <c r="A199" t="s">
+        <v>499</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C199" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D199" s="19">
-        <v>0.84</v>
+      <c r="D199" s="20">
+        <v>0</v>
       </c>
       <c r="E199" s="17">
-        <v>1</v>
-      </c>
-      <c r="H199" s="17">
-        <v>0.67</v>
-      </c>
-      <c r="I199" s="20"/>
-      <c r="P199" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="F199" s="17">
+        <v>0.64</v>
+      </c>
+      <c r="H199" s="20">
+        <v>0</v>
+      </c>
+      <c r="I199" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="P199" s="15"/>
     </row>
     <row r="200" spans="1:16">
       <c r="A200" s="9" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C200" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D200" s="19">
-        <v>0.91</v>
+        <v>0.81</v>
       </c>
       <c r="E200" s="17">
-        <v>0.93</v>
+        <v>0.98</v>
+      </c>
+      <c r="F200" s="17">
+        <v>0.73</v>
       </c>
       <c r="H200" s="17">
-        <v>0.37</v>
-      </c>
-      <c r="I200" s="20"/>
+        <v>0.46</v>
+      </c>
+      <c r="I200" s="20">
+        <v>0.06</v>
+      </c>
       <c r="P200" s="4"/>
     </row>
     <row r="201" spans="1:16">
       <c r="A201" s="9" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C201" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D201" s="19">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="E201" s="17">
-        <v>0.98</v>
+        <v>0.99</v>
+      </c>
+      <c r="F201" s="17">
+        <v>0.67</v>
       </c>
       <c r="H201" s="17">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="I201" s="20"/>
       <c r="P201" s="4"/>
     </row>
     <row r="202" spans="1:16">
       <c r="A202" s="9" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C202" s="19" t="s">
         <v>348</v>
@@ -7198,260 +7835,300 @@
       <c r="E202" s="17">
         <v>1</v>
       </c>
+      <c r="F202" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H202" s="17">
-        <v>0.32</v>
+        <v>0.67</v>
       </c>
       <c r="I202" s="20"/>
       <c r="P202" s="4"/>
     </row>
     <row r="203" spans="1:16">
       <c r="A203" s="9" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C203" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D203" s="19">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="E203" s="17">
-        <v>0.99</v>
+        <v>0.93</v>
+      </c>
+      <c r="F203" s="17">
+        <v>0.7</v>
       </c>
       <c r="H203" s="17">
         <v>0.37</v>
       </c>
-      <c r="I203" s="20"/>
+      <c r="I203" s="20">
+        <v>0.39</v>
+      </c>
       <c r="P203" s="4"/>
     </row>
     <row r="204" spans="1:16">
-      <c r="A204" t="s">
-        <v>450</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C204" s="17" t="s">
+      <c r="A204" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C204" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D204" s="20">
-        <v>0</v>
+      <c r="D204" s="19">
+        <v>0.83</v>
       </c>
       <c r="E204" s="17">
-        <v>1</v>
+        <v>0.98</v>
+      </c>
+      <c r="F204" s="17">
+        <v>0.7</v>
       </c>
       <c r="H204" s="17">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="I204" s="20"/>
       <c r="P204" s="4"/>
     </row>
     <row r="205" spans="1:16">
       <c r="A205" s="9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C205" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D205" s="19">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="E205" s="17">
-        <v>0.82</v>
+        <v>1</v>
+      </c>
+      <c r="F205" s="17">
+        <v>0.7</v>
       </c>
       <c r="H205" s="17">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="I205" s="20"/>
       <c r="P205" s="4"/>
     </row>
     <row r="206" spans="1:16">
       <c r="A206" s="9" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C206" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D206" s="19">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="E206" s="17">
-        <v>0.97</v>
+        <v>0.99</v>
+      </c>
+      <c r="F206" s="17">
+        <v>0.7</v>
       </c>
       <c r="H206" s="17">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="I206" s="20"/>
       <c r="P206" s="4"/>
     </row>
     <row r="207" spans="1:16">
-      <c r="A207" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="B207" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="C207" s="19" t="s">
+      <c r="A207" t="s">
+        <v>450</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C207" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D207" s="19">
-        <v>0.76</v>
+      <c r="D207" s="20">
+        <v>0</v>
       </c>
       <c r="E207" s="17">
-        <v>0.93</v>
+        <v>1</v>
+      </c>
+      <c r="F207" s="17">
+        <v>0.7</v>
       </c>
       <c r="H207" s="17">
-        <v>0.39</v>
-      </c>
-      <c r="I207" s="20"/>
+        <v>0.46</v>
+      </c>
+      <c r="I207" s="20">
+        <v>0.54</v>
+      </c>
       <c r="P207" s="4"/>
     </row>
     <row r="208" spans="1:16">
       <c r="A208" s="9" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C208" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D208" s="19">
-        <v>0.59</v>
+        <v>0.88</v>
       </c>
       <c r="E208" s="17">
-        <v>0.93</v>
+        <v>0.82</v>
+      </c>
+      <c r="F208" s="17">
+        <v>0.7</v>
       </c>
       <c r="H208" s="17">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="I208" s="20"/>
       <c r="P208" s="4"/>
     </row>
     <row r="209" spans="1:16">
       <c r="A209" s="9" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C209" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D209" s="19">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="E209" s="17">
-        <v>0.93</v>
+        <v>0.97</v>
+      </c>
+      <c r="F209" s="17">
+        <v>0.7</v>
       </c>
       <c r="H209" s="17">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="I209" s="20"/>
       <c r="P209" s="4"/>
     </row>
     <row r="210" spans="1:16">
       <c r="A210" s="9" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C210" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D210" s="19">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="E210" s="17">
-        <v>0.98</v>
+        <v>0.93</v>
+      </c>
+      <c r="F210" s="17">
+        <v>0.67</v>
       </c>
       <c r="H210" s="17">
-        <v>0.75</v>
+        <v>0.39</v>
       </c>
       <c r="I210" s="20"/>
       <c r="P210" s="4"/>
     </row>
     <row r="211" spans="1:16">
-      <c r="A211" t="s">
-        <v>444</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C211" s="17" t="s">
+      <c r="A211" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="C211" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="D211" s="20">
+      <c r="D211" s="19">
+        <v>0.59</v>
+      </c>
+      <c r="E211" s="17">
+        <v>0.93</v>
+      </c>
+      <c r="F211" s="17">
         <v>0</v>
       </c>
-      <c r="E211" s="17">
-        <v>0.8</v>
-      </c>
       <c r="H211" s="17">
-        <v>0.05</v>
+        <v>0.65</v>
       </c>
       <c r="I211" s="20"/>
       <c r="P211" s="4"/>
     </row>
     <row r="212" spans="1:16">
       <c r="A212" s="9" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C212" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D212" s="19">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="E212" s="17">
-        <v>0.98</v>
+        <v>0.93</v>
+      </c>
+      <c r="F212" s="17">
+        <v>0.77</v>
       </c>
       <c r="H212" s="17">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="I212" s="20"/>
       <c r="P212" s="4"/>
     </row>
     <row r="213" spans="1:16">
       <c r="A213" s="9" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C213" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D213" s="19">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="E213" s="17">
-        <v>0.92</v>
+        <v>0.98</v>
+      </c>
+      <c r="F213" s="17">
+        <v>0.64</v>
       </c>
       <c r="H213" s="17">
-        <v>0.32</v>
+        <v>0.75</v>
       </c>
       <c r="I213" s="20"/>
       <c r="P213" s="4"/>
     </row>
     <row r="214" spans="1:16">
       <c r="A214" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C214" s="17" t="s">
         <v>348</v>
@@ -7460,581 +8137,656 @@
         <v>0</v>
       </c>
       <c r="E214" s="17">
-        <v>0.97</v>
+        <v>0.8</v>
+      </c>
+      <c r="F214" s="17">
+        <v>0</v>
       </c>
       <c r="H214" s="17">
-        <v>0.44</v>
-      </c>
-      <c r="I214" s="20"/>
+        <v>0.05</v>
+      </c>
+      <c r="I214" s="20">
+        <v>0</v>
+      </c>
       <c r="P214" s="4"/>
     </row>
     <row r="215" spans="1:16">
       <c r="A215" s="9" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C215" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D215" s="19">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="E215" s="17">
-        <v>1</v>
+        <v>0.98</v>
+      </c>
+      <c r="F215" s="17">
+        <v>0.77</v>
       </c>
       <c r="H215" s="17">
-        <v>0.68</v>
+        <v>0.53</v>
       </c>
       <c r="I215" s="20"/>
       <c r="P215" s="4"/>
     </row>
     <row r="216" spans="1:16">
       <c r="A216" s="9" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C216" s="19" t="s">
         <v>348</v>
       </c>
       <c r="D216" s="19">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="E216" s="17">
         <v>0.92</v>
       </c>
+      <c r="F216" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H216" s="17">
-        <v>0.56000000000000005</v>
+        <v>0.32</v>
       </c>
       <c r="I216" s="20"/>
       <c r="P216" s="4"/>
     </row>
     <row r="217" spans="1:16">
-      <c r="A217" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="B217" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="C217" s="19" t="s">
+      <c r="A217" t="s">
+        <v>448</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C217" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D217" s="19">
-        <v>0.94</v>
+      <c r="D217" s="20">
+        <v>0</v>
       </c>
       <c r="E217" s="17">
-        <v>0.99</v>
+        <v>0.97</v>
+      </c>
+      <c r="F217" s="17">
+        <v>0.7</v>
       </c>
       <c r="H217" s="17">
-        <v>0.65</v>
+        <v>0.44</v>
       </c>
       <c r="I217" s="20"/>
       <c r="P217" s="4"/>
     </row>
     <row r="218" spans="1:16">
       <c r="A218" s="9" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C218" s="19" t="s">
-        <v>407</v>
+        <v>348</v>
       </c>
       <c r="D218" s="19">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="E218" s="17">
-        <v>0.9</v>
+        <v>1</v>
+      </c>
+      <c r="F218" s="17">
+        <v>0.77</v>
       </c>
       <c r="H218" s="17">
-        <v>0.79</v>
-      </c>
-      <c r="I218" s="20">
-        <v>0.57999999999999996</v>
-      </c>
+        <v>0.68</v>
+      </c>
+      <c r="I218" s="20"/>
       <c r="P218" s="4"/>
     </row>
     <row r="219" spans="1:16">
       <c r="A219" s="9" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="C219" s="19" t="s">
-        <v>407</v>
+        <v>348</v>
       </c>
       <c r="D219" s="19">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="E219" s="17">
-        <v>0.91</v>
+        <v>0.92</v>
+      </c>
+      <c r="F219" s="17">
+        <v>0.67</v>
       </c>
       <c r="H219" s="17">
-        <v>0.32</v>
-      </c>
-      <c r="I219" s="20">
-        <v>0.1</v>
-      </c>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I219" s="20"/>
       <c r="P219" s="4"/>
     </row>
     <row r="220" spans="1:16">
       <c r="A220" s="9" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C220" s="19" t="s">
-        <v>407</v>
+        <v>348</v>
       </c>
       <c r="D220" s="19">
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="E220" s="17">
-        <v>0.79</v>
+        <v>0.99</v>
+      </c>
+      <c r="F220" s="17">
+        <v>0.66</v>
       </c>
       <c r="H220" s="17">
-        <v>0.54</v>
-      </c>
-      <c r="I220" s="20">
-        <v>0.43</v>
-      </c>
+        <v>0.65</v>
+      </c>
+      <c r="I220" s="20"/>
       <c r="P220" s="4"/>
     </row>
     <row r="221" spans="1:16">
-      <c r="A221" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="B221" s="9" t="s">
-        <v>413</v>
+      <c r="A221" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="B221" s="25" t="s">
+        <v>406</v>
       </c>
       <c r="C221" s="19" t="s">
         <v>407</v>
       </c>
       <c r="D221" s="19">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="E221" s="17">
-        <v>0.97</v>
+        <v>0.9</v>
+      </c>
+      <c r="F221" s="17">
+        <v>0.7</v>
       </c>
       <c r="H221" s="17">
-        <v>0.11</v>
+        <v>0.79</v>
       </c>
       <c r="I221" s="20">
-        <v>0.21</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P221" s="4"/>
     </row>
     <row r="222" spans="1:16">
-      <c r="A222" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="B222" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="C222" s="19" t="s">
+      <c r="A222" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="B222" s="23" t="s">
+        <v>504</v>
+      </c>
+      <c r="C222" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="D222" s="19">
-        <v>0.71</v>
+      <c r="D222" s="20">
+        <v>0</v>
       </c>
       <c r="E222" s="17">
-        <v>0.98</v>
-      </c>
-      <c r="H222" s="17">
-        <v>0.54</v>
+        <v>0</v>
+      </c>
+      <c r="F222" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H222" s="20">
+        <v>0</v>
       </c>
       <c r="I222" s="20">
-        <v>0.7</v>
-      </c>
-      <c r="P222" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="P222" s="15"/>
     </row>
     <row r="223" spans="1:16">
       <c r="A223" s="9" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C223" s="19" t="s">
         <v>407</v>
       </c>
       <c r="D223" s="19">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="E223" s="17">
-        <v>0.97</v>
+        <v>0.91</v>
+      </c>
+      <c r="F223" s="17">
+        <v>0.67</v>
       </c>
       <c r="H223" s="17">
-        <v>0.61</v>
+        <v>0.32</v>
       </c>
       <c r="I223" s="20">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
       <c r="P223" s="4"/>
     </row>
     <row r="224" spans="1:16">
-      <c r="A224" t="s">
-        <v>460</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C224" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="D224" s="20">
-        <v>0</v>
+      <c r="A224" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="B224" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="C224" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="D224" s="19">
+        <v>0.69</v>
       </c>
       <c r="E224" s="17">
-        <v>0.88</v>
+        <v>0.79</v>
+      </c>
+      <c r="F224" s="17">
+        <v>0.7</v>
       </c>
       <c r="H224" s="17">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="I224" s="20">
-        <v>0.6</v>
-      </c>
-      <c r="P224" s="15"/>
+        <v>0.43</v>
+      </c>
+      <c r="P224" s="4"/>
     </row>
     <row r="225" spans="1:16">
       <c r="A225" s="9" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C225" s="19" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="D225" s="19">
-        <v>0.79</v>
+        <v>0.67</v>
       </c>
       <c r="E225" s="17">
-        <v>0.89</v>
+        <v>0.97</v>
+      </c>
+      <c r="F225" s="17">
+        <v>0.67</v>
       </c>
       <c r="H225" s="17">
-        <v>0.26</v>
+        <v>0.11</v>
       </c>
       <c r="I225" s="20">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="P225" s="4"/>
     </row>
     <row r="226" spans="1:16">
-      <c r="A226" t="s">
-        <v>497</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C226" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="D226" s="20"/>
-      <c r="H226" s="20">
-        <v>0</v>
+      <c r="A226" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="B226" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="C226" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="D226" s="19">
+        <v>0.71</v>
+      </c>
+      <c r="E226" s="17">
+        <v>0.98</v>
+      </c>
+      <c r="F226" s="17">
+        <v>0.66</v>
+      </c>
+      <c r="H226" s="17">
+        <v>0.54</v>
       </c>
       <c r="I226" s="20">
-        <v>0.08</v>
-      </c>
-      <c r="P226" s="15"/>
+        <v>0.7</v>
+      </c>
+      <c r="P226" s="4"/>
     </row>
     <row r="227" spans="1:16">
       <c r="A227" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C227" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="D227" s="19">
+        <v>0.89</v>
+      </c>
+      <c r="E227" s="17">
+        <v>0.97</v>
+      </c>
+      <c r="F227" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H227" s="17">
+        <v>0.61</v>
+      </c>
+      <c r="I227" s="20">
+        <v>0.34</v>
+      </c>
+      <c r="P227" s="24"/>
+    </row>
+    <row r="228" spans="1:16">
+      <c r="A228" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="B228" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="C228" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D227" s="19">
-        <v>0.66</v>
-      </c>
-      <c r="E227" s="17">
-        <v>0.87</v>
-      </c>
-      <c r="H227" s="17">
-        <v>0.16</v>
-      </c>
-      <c r="I227" s="20">
-        <v>0.87</v>
-      </c>
-      <c r="P227" s="16"/>
-    </row>
-    <row r="228" spans="1:16">
-      <c r="A228" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="B228" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="C228" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D228" s="19">
-        <v>0.69</v>
+      <c r="D228" s="20">
+        <v>0</v>
       </c>
       <c r="E228" s="17">
         <v>0.88</v>
       </c>
+      <c r="F228" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H228" s="17">
-        <v>0.28000000000000003</v>
+        <v>0.33</v>
       </c>
       <c r="I228" s="20">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="P228" s="16"/>
+        <v>0.6</v>
+      </c>
+      <c r="P228" s="22"/>
     </row>
     <row r="229" spans="1:16">
-      <c r="A229" t="s">
-        <v>464</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="C229" s="17" t="s">
+      <c r="A229" s="25" t="s">
+        <v>418</v>
+      </c>
+      <c r="B229" s="25" t="s">
+        <v>419</v>
+      </c>
+      <c r="C229" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D229" s="20">
-        <v>0</v>
+      <c r="D229" s="19">
+        <v>0.79</v>
       </c>
       <c r="E229" s="17">
-        <v>0.98</v>
+        <v>0.89</v>
+      </c>
+      <c r="F229" s="17">
+        <v>0.7</v>
       </c>
       <c r="H229" s="17">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="I229" s="20">
-        <v>0.18</v>
-      </c>
+        <v>0.19</v>
+      </c>
+      <c r="P229" s="24"/>
     </row>
     <row r="230" spans="1:16">
-      <c r="A230" t="s">
-        <v>457</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>458</v>
+      <c r="A230" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="B230" s="23" t="s">
+        <v>498</v>
       </c>
       <c r="C230" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D230" s="20">
+      <c r="D230" s="20"/>
+      <c r="F230" s="17">
+        <v>0.77</v>
+      </c>
+      <c r="H230" s="20">
         <v>0</v>
       </c>
-      <c r="E230" s="17">
-        <v>0.94</v>
-      </c>
-      <c r="H230" s="17">
-        <v>0.26</v>
-      </c>
       <c r="I230" s="20">
-        <v>0.21</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="P230" s="22"/>
     </row>
     <row r="231" spans="1:16">
-      <c r="A231" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="B231" s="9" t="s">
-        <v>426</v>
+      <c r="A231" s="25" t="s">
+        <v>421</v>
+      </c>
+      <c r="B231" s="25" t="s">
+        <v>422</v>
       </c>
       <c r="C231" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D231" s="19">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="E231" s="17">
-        <v>0.9</v>
+        <v>0.87</v>
+      </c>
+      <c r="F231" s="17">
+        <v>0.7</v>
       </c>
       <c r="H231" s="17">
-        <v>0.63</v>
+        <v>0.16</v>
       </c>
       <c r="I231" s="20">
-        <v>0.72</v>
-      </c>
-      <c r="P231" s="16"/>
+        <v>0.87</v>
+      </c>
+      <c r="P231" s="24"/>
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="9" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C232" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D232" s="19">
-        <v>0.79</v>
+        <v>0.69</v>
       </c>
       <c r="E232" s="17">
-        <v>0.99</v>
+        <v>0.88</v>
+      </c>
+      <c r="F232" s="17">
+        <v>0.7</v>
       </c>
       <c r="H232" s="17">
-        <v>0.26</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I232" s="20">
-        <v>0.43</v>
-      </c>
-      <c r="P232" s="16"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="P232" s="24"/>
     </row>
     <row r="233" spans="1:16">
-      <c r="A233" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="B233" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="C233" s="19" t="s">
+      <c r="A233" t="s">
+        <v>464</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C233" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D233" s="19">
-        <v>0.81</v>
+      <c r="D233" s="20">
+        <v>0</v>
       </c>
       <c r="E233" s="17">
-        <v>0.92</v>
+        <v>0.98</v>
+      </c>
+      <c r="F233" s="17">
+        <v>0.7</v>
       </c>
       <c r="H233" s="17">
-        <v>0.67</v>
+        <v>0.16</v>
       </c>
       <c r="I233" s="20">
-        <v>0.66</v>
-      </c>
-      <c r="P233" s="16"/>
+        <v>0.18</v>
+      </c>
+      <c r="P233" s="22"/>
     </row>
     <row r="234" spans="1:16">
-      <c r="A234" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="B234" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="C234" s="19" t="s">
+      <c r="A234" t="s">
+        <v>457</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C234" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D234" s="19">
-        <v>0.74</v>
+      <c r="D234" s="20">
+        <v>0</v>
       </c>
       <c r="E234" s="17">
         <v>0.94</v>
       </c>
+      <c r="F234" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H234" s="17">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="I234" s="20">
-        <v>0.25</v>
-      </c>
-      <c r="P234" s="16"/>
+        <v>0.21</v>
+      </c>
+      <c r="P234" s="22"/>
     </row>
     <row r="235" spans="1:16">
-      <c r="A235" t="s">
-        <v>468</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C235" s="17" t="s">
+      <c r="A235" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="C235" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D235" s="20">
-        <v>0</v>
+      <c r="D235" s="19">
+        <v>0.83</v>
       </c>
       <c r="E235" s="17">
-        <v>0.91</v>
+        <v>0.9</v>
+      </c>
+      <c r="F235" s="17">
+        <v>0.66</v>
       </c>
       <c r="H235" s="17">
-        <v>0.35</v>
+        <v>0.63</v>
       </c>
       <c r="I235" s="20">
-        <v>0</v>
-      </c>
+        <v>0.72</v>
+      </c>
+      <c r="P235" s="24"/>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="9" t="s">
-        <v>26</v>
+        <v>427</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C236" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D236" s="19">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="E236" s="17">
-        <v>1</v>
+        <v>0.99</v>
+      </c>
+      <c r="F236" s="17">
+        <v>0.7</v>
       </c>
       <c r="H236" s="17">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="I236" s="20">
-        <v>0.66</v>
-      </c>
-      <c r="P236" s="16"/>
+        <v>0.43</v>
+      </c>
+      <c r="P236" s="24"/>
     </row>
     <row r="237" spans="1:16">
       <c r="A237" s="9" t="s">
-        <v>26</v>
+        <v>429</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C237" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D237" s="19">
-        <v>0.65</v>
+        <v>0.81</v>
       </c>
       <c r="E237" s="17">
-        <v>1</v>
+        <v>0.92</v>
+      </c>
+      <c r="F237" s="17">
+        <v>0.66</v>
       </c>
       <c r="H237" s="17">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="I237" s="20">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="P237" s="16"/>
+        <v>0.66</v>
+      </c>
+      <c r="P237" s="24"/>
     </row>
     <row r="238" spans="1:16">
-      <c r="A238" t="s">
-        <v>462</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C238" s="17" t="s">
+      <c r="A238" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B238" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C238" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D238" s="20">
-        <v>0</v>
+      <c r="D238" s="19">
+        <v>0.74</v>
       </c>
       <c r="E238" s="17">
-        <v>0.9</v>
+        <v>0.94</v>
+      </c>
+      <c r="F238" s="17">
+        <v>0.7</v>
       </c>
       <c r="H238" s="17">
-        <v>0.54</v>
+        <v>0.37</v>
       </c>
       <c r="I238" s="20">
-        <v>0.72</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="P238" s="24"/>
     </row>
     <row r="239" spans="1:16">
       <c r="A239" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C239" s="17" t="s">
         <v>420</v>
@@ -8043,85 +8795,206 @@
         <v>0</v>
       </c>
       <c r="E239" s="17">
-        <v>0.9</v>
+        <v>0.91</v>
+      </c>
+      <c r="F239" s="17">
+        <v>0</v>
       </c>
       <c r="H239" s="17">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="I239" s="20">
         <v>0</v>
       </c>
+      <c r="P239" s="22"/>
     </row>
     <row r="240" spans="1:16">
-      <c r="A240" t="s">
-        <v>165</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C240" s="17" t="s">
+      <c r="A240" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C240" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D240" s="20">
-        <v>0</v>
+      <c r="D240" s="19">
+        <v>0.75</v>
       </c>
       <c r="E240" s="17">
         <v>1</v>
       </c>
+      <c r="F240" s="17">
+        <v>0.73</v>
+      </c>
       <c r="H240" s="17">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="I240" s="20">
-        <v>0.15</v>
-      </c>
+        <v>0.66</v>
+      </c>
+      <c r="P240" s="24"/>
     </row>
     <row r="241" spans="1:16">
       <c r="A241" s="9" t="s">
-        <v>435</v>
+        <v>26</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C241" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D241" s="19">
+        <v>0.65</v>
+      </c>
+      <c r="E241" s="17">
+        <v>1</v>
+      </c>
+      <c r="F241" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H241" s="17">
+        <v>0.63</v>
+      </c>
+      <c r="I241" s="20">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="P241" s="24"/>
+    </row>
+    <row r="242" spans="1:16">
+      <c r="A242" t="s">
+        <v>462</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C242" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="D242" s="20">
+        <v>0</v>
+      </c>
+      <c r="E242" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="F242" s="17">
+        <v>0.77</v>
+      </c>
+      <c r="H242" s="17">
+        <v>0.54</v>
+      </c>
+      <c r="I242" s="20">
+        <v>0.72</v>
+      </c>
+      <c r="P242" s="22"/>
+    </row>
+    <row r="243" spans="1:16">
+      <c r="A243" t="s">
+        <v>466</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C243" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="D243" s="20">
+        <v>0</v>
+      </c>
+      <c r="E243" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="F243" s="17">
+        <v>0</v>
+      </c>
+      <c r="H243" s="17">
+        <v>0.42</v>
+      </c>
+      <c r="I243" s="20">
+        <v>0</v>
+      </c>
+      <c r="P243" s="22"/>
+    </row>
+    <row r="244" spans="1:16">
+      <c r="A244" t="s">
+        <v>165</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C244" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="D244" s="20">
+        <v>0</v>
+      </c>
+      <c r="E244" s="17">
+        <v>1</v>
+      </c>
+      <c r="F244" s="17">
+        <v>0.73</v>
+      </c>
+      <c r="H244" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="I244" s="20">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16">
+      <c r="A245" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="C245" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="D245" s="19">
         <v>0.87</v>
       </c>
-      <c r="E241" s="17">
+      <c r="E245" s="17">
         <v>0.84</v>
       </c>
-      <c r="H241" s="17">
+      <c r="F245" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H245" s="17">
         <v>0.47</v>
       </c>
-      <c r="I241" s="20">
+      <c r="I245" s="20">
         <v>0</v>
       </c>
-      <c r="P241" s="16"/>
-    </row>
-    <row r="242" spans="1:16">
-      <c r="A242" s="9" t="s">
+      <c r="P245" s="16"/>
+    </row>
+    <row r="246" spans="1:16">
+      <c r="A246" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="B242" s="9" t="s">
+      <c r="B246" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="C242" s="19" t="s">
+      <c r="C246" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D242" s="19">
-        <v>0.7</v>
-      </c>
-      <c r="E242" s="17">
+      <c r="D246" s="19">
+        <v>0.7</v>
+      </c>
+      <c r="E246" s="17">
         <v>0.89</v>
       </c>
-      <c r="H242" s="17">
+      <c r="F246" s="17">
+        <v>0.66</v>
+      </c>
+      <c r="H246" s="17">
         <v>0.19</v>
       </c>
-      <c r="I242" s="20">
+      <c r="I246" s="20">
         <v>0.13</v>
       </c>
-      <c r="P242" s="16"/>
+      <c r="P246" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3FFBFF-E679-714B-A37D-34D513A3D5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1459FEA-22CB-524B-A426-31C00AB30D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1693,7 +1693,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1732,13 +1732,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3620,10 +3613,10 @@
       <c r="P48" s="4"/>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="9" t="s">
         <v>92</v>
       </c>
       <c r="C49" s="19" t="s">
@@ -3647,10 +3640,10 @@
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C50" s="19" t="s">
@@ -3677,10 +3670,10 @@
       <c r="P50" s="4"/>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="19" t="s">
@@ -3707,10 +3700,10 @@
       <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="19" t="s">
@@ -3737,10 +3730,10 @@
       <c r="P52" s="4"/>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="9" t="s">
         <v>101</v>
       </c>
       <c r="C53" s="19" t="s">
@@ -3767,10 +3760,10 @@
       <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="25" t="s">
+      <c r="B54" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -3797,10 +3790,10 @@
       <c r="P54" s="4"/>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="25" t="s">
+      <c r="B55" s="9" t="s">
         <v>476</v>
       </c>
       <c r="C55" s="19" t="s">
@@ -3827,10 +3820,10 @@
       <c r="P55" s="4"/>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="25" t="s">
+      <c r="B56" s="9" t="s">
         <v>106</v>
       </c>
       <c r="C56" s="19" t="s">
@@ -4829,10 +4822,10 @@
       <c r="P89" s="4"/>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="25" t="s">
+      <c r="A90" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B90" s="25" t="s">
+      <c r="B90" s="9" t="s">
         <v>172</v>
       </c>
       <c r="C90" s="19" t="s">
@@ -4856,10 +4849,10 @@
       <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="25" t="s">
+      <c r="A91" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B91" s="25" t="s">
+      <c r="B91" s="9" t="s">
         <v>175</v>
       </c>
       <c r="C91" s="19" t="s">
@@ -4883,10 +4876,10 @@
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" s="22" t="s">
+      <c r="A92" t="s">
         <v>474</v>
       </c>
-      <c r="B92" s="23" t="s">
+      <c r="B92" s="2" t="s">
         <v>475</v>
       </c>
       <c r="C92" s="17" t="s">
@@ -4910,10 +4903,10 @@
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="25" t="s">
+      <c r="A93" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B93" s="25" t="s">
+      <c r="B93" s="9" t="s">
         <v>177</v>
       </c>
       <c r="C93" s="19" t="s">
@@ -4937,10 +4930,10 @@
       <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="25" t="s">
+      <c r="A94" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B94" s="25" t="s">
+      <c r="B94" s="9" t="s">
         <v>179</v>
       </c>
       <c r="C94" s="19" t="s">
@@ -4964,10 +4957,10 @@
       <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="25" t="s">
+      <c r="A95" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B95" s="25" t="s">
+      <c r="B95" s="9" t="s">
         <v>181</v>
       </c>
       <c r="C95" s="19" t="s">
@@ -4991,10 +4984,10 @@
       <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="25" t="s">
+      <c r="A96" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B96" s="25" t="s">
+      <c r="B96" s="9" t="s">
         <v>183</v>
       </c>
       <c r="C96" s="19" t="s">
@@ -5018,10 +5011,10 @@
       <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="25" t="s">
+      <c r="A97" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B97" s="25" t="s">
+      <c r="B97" s="9" t="s">
         <v>185</v>
       </c>
       <c r="C97" s="19" t="s">
@@ -6012,10 +6005,10 @@
       <c r="P133" s="4"/>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="25" t="s">
+      <c r="A134" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="B134" s="25" t="s">
+      <c r="B134" s="9" t="s">
         <v>251</v>
       </c>
       <c r="C134" s="19" t="s">
@@ -6039,10 +6032,10 @@
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" s="25" t="s">
+      <c r="A135" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="B135" s="25" t="s">
+      <c r="B135" s="9" t="s">
         <v>254</v>
       </c>
       <c r="C135" s="19" t="s">
@@ -6066,10 +6059,10 @@
       <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="25" t="s">
+      <c r="A136" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="B136" s="25" t="s">
+      <c r="B136" s="9" t="s">
         <v>256</v>
       </c>
       <c r="C136" s="19" t="s">
@@ -6093,10 +6086,10 @@
       <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="25" t="s">
+      <c r="A137" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="B137" s="25" t="s">
+      <c r="B137" s="9" t="s">
         <v>258</v>
       </c>
       <c r="C137" s="19" t="s">
@@ -6120,10 +6113,10 @@
       <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="25" t="s">
+      <c r="A138" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="B138" s="25" t="s">
+      <c r="B138" s="9" t="s">
         <v>260</v>
       </c>
       <c r="C138" s="19" t="s">
@@ -6147,10 +6140,10 @@
       <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="25" t="s">
+      <c r="A139" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="B139" s="25" t="s">
+      <c r="B139" s="9" t="s">
         <v>262</v>
       </c>
       <c r="C139" s="19" t="s">
@@ -6174,10 +6167,10 @@
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" s="25" t="s">
+      <c r="A140" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="B140" s="25" t="s">
+      <c r="B140" s="9" t="s">
         <v>264</v>
       </c>
       <c r="C140" s="19" t="s">
@@ -6201,10 +6194,10 @@
       <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="25" t="s">
+      <c r="A141" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B141" s="25" t="s">
+      <c r="B141" s="9" t="s">
         <v>266</v>
       </c>
       <c r="C141" s="19" t="s">
@@ -6228,10 +6221,10 @@
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="25" t="s">
+      <c r="A142" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="B142" s="25" t="s">
+      <c r="B142" s="9" t="s">
         <v>268</v>
       </c>
       <c r="C142" s="19" t="s">
@@ -6255,10 +6248,10 @@
       <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="25" t="s">
+      <c r="A143" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="B143" s="25" t="s">
+      <c r="B143" s="9" t="s">
         <v>270</v>
       </c>
       <c r="C143" s="19" t="s">
@@ -6457,7 +6450,7 @@
         <v>0.79</v>
       </c>
       <c r="E150" s="17">
-        <v>0</v>
+        <v>0.94</v>
       </c>
       <c r="F150" s="17">
         <v>0.67</v>
@@ -7362,10 +7355,10 @@
       <c r="P183" s="4"/>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" s="25" t="s">
+      <c r="A184" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="B184" s="25" t="s">
+      <c r="B184" s="9" t="s">
         <v>347</v>
       </c>
       <c r="C184" s="19" t="s">
@@ -7387,10 +7380,10 @@
       <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
-      <c r="A185" s="22" t="s">
+      <c r="A185" t="s">
         <v>446</v>
       </c>
-      <c r="B185" s="26" t="s">
+      <c r="B185" s="3" t="s">
         <v>447</v>
       </c>
       <c r="C185" s="17" t="s">
@@ -7412,10 +7405,10 @@
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" s="25" t="s">
+      <c r="A186" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="B186" s="25" t="s">
+      <c r="B186" s="9" t="s">
         <v>350</v>
       </c>
       <c r="C186" s="19" t="s">
@@ -7437,10 +7430,10 @@
       <c r="P186" s="4"/>
     </row>
     <row r="187" spans="1:16">
-      <c r="A187" s="22" t="s">
+      <c r="A187" t="s">
         <v>501</v>
       </c>
-      <c r="B187" s="23" t="s">
+      <c r="B187" s="2" t="s">
         <v>502</v>
       </c>
       <c r="C187" s="17" t="s">
@@ -8301,10 +8294,10 @@
       <c r="P220" s="4"/>
     </row>
     <row r="221" spans="1:16">
-      <c r="A221" s="25" t="s">
+      <c r="A221" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="B221" s="25" t="s">
+      <c r="B221" s="9" t="s">
         <v>406</v>
       </c>
       <c r="C221" s="19" t="s">
@@ -8328,10 +8321,10 @@
       <c r="P221" s="4"/>
     </row>
     <row r="222" spans="1:16">
-      <c r="A222" s="22" t="s">
+      <c r="A222" t="s">
         <v>503</v>
       </c>
-      <c r="B222" s="23" t="s">
+      <c r="B222" s="2" t="s">
         <v>504</v>
       </c>
       <c r="C222" s="17" t="s">
@@ -8487,13 +8480,13 @@
       <c r="I227" s="20">
         <v>0.34</v>
       </c>
-      <c r="P227" s="24"/>
+      <c r="P227" s="16"/>
     </row>
     <row r="228" spans="1:16">
-      <c r="A228" s="22" t="s">
+      <c r="A228" t="s">
         <v>460</v>
       </c>
-      <c r="B228" s="23" t="s">
+      <c r="B228" s="2" t="s">
         <v>461</v>
       </c>
       <c r="C228" s="17" t="s">
@@ -8514,13 +8507,12 @@
       <c r="I228" s="20">
         <v>0.6</v>
       </c>
-      <c r="P228" s="22"/>
     </row>
     <row r="229" spans="1:16">
-      <c r="A229" s="25" t="s">
+      <c r="A229" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="B229" s="25" t="s">
+      <c r="B229" s="9" t="s">
         <v>419</v>
       </c>
       <c r="C229" s="19" t="s">
@@ -8541,13 +8533,13 @@
       <c r="I229" s="20">
         <v>0.19</v>
       </c>
-      <c r="P229" s="24"/>
+      <c r="P229" s="16"/>
     </row>
     <row r="230" spans="1:16">
-      <c r="A230" s="22" t="s">
+      <c r="A230" t="s">
         <v>497</v>
       </c>
-      <c r="B230" s="23" t="s">
+      <c r="B230" s="2" t="s">
         <v>498</v>
       </c>
       <c r="C230" s="17" t="s">
@@ -8563,13 +8555,12 @@
       <c r="I230" s="20">
         <v>0.08</v>
       </c>
-      <c r="P230" s="22"/>
     </row>
     <row r="231" spans="1:16">
-      <c r="A231" s="25" t="s">
+      <c r="A231" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="B231" s="25" t="s">
+      <c r="B231" s="9" t="s">
         <v>422</v>
       </c>
       <c r="C231" s="19" t="s">
@@ -8590,7 +8581,7 @@
       <c r="I231" s="20">
         <v>0.87</v>
       </c>
-      <c r="P231" s="24"/>
+      <c r="P231" s="16"/>
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="9" t="s">
@@ -8617,7 +8608,7 @@
       <c r="I232" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P232" s="24"/>
+      <c r="P232" s="16"/>
     </row>
     <row r="233" spans="1:16">
       <c r="A233" t="s">
@@ -8644,7 +8635,6 @@
       <c r="I233" s="20">
         <v>0.18</v>
       </c>
-      <c r="P233" s="22"/>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" t="s">
@@ -8671,7 +8661,6 @@
       <c r="I234" s="20">
         <v>0.21</v>
       </c>
-      <c r="P234" s="22"/>
     </row>
     <row r="235" spans="1:16">
       <c r="A235" s="9" t="s">
@@ -8698,7 +8687,7 @@
       <c r="I235" s="20">
         <v>0.72</v>
       </c>
-      <c r="P235" s="24"/>
+      <c r="P235" s="16"/>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="9" t="s">
@@ -8725,7 +8714,7 @@
       <c r="I236" s="20">
         <v>0.43</v>
       </c>
-      <c r="P236" s="24"/>
+      <c r="P236" s="16"/>
     </row>
     <row r="237" spans="1:16">
       <c r="A237" s="9" t="s">
@@ -8752,7 +8741,7 @@
       <c r="I237" s="20">
         <v>0.66</v>
       </c>
-      <c r="P237" s="24"/>
+      <c r="P237" s="16"/>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" s="9" t="s">
@@ -8779,7 +8768,7 @@
       <c r="I238" s="20">
         <v>0.25</v>
       </c>
-      <c r="P238" s="24"/>
+      <c r="P238" s="16"/>
     </row>
     <row r="239" spans="1:16">
       <c r="A239" t="s">
@@ -8806,7 +8795,6 @@
       <c r="I239" s="20">
         <v>0</v>
       </c>
-      <c r="P239" s="22"/>
     </row>
     <row r="240" spans="1:16">
       <c r="A240" s="9" t="s">
@@ -8833,7 +8821,7 @@
       <c r="I240" s="20">
         <v>0.66</v>
       </c>
-      <c r="P240" s="24"/>
+      <c r="P240" s="16"/>
     </row>
     <row r="241" spans="1:16">
       <c r="A241" s="9" t="s">
@@ -8860,7 +8848,7 @@
       <c r="I241" s="20">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P241" s="24"/>
+      <c r="P241" s="16"/>
     </row>
     <row r="242" spans="1:16">
       <c r="A242" t="s">
@@ -8887,7 +8875,6 @@
       <c r="I242" s="20">
         <v>0.72</v>
       </c>
-      <c r="P242" s="22"/>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" t="s">
@@ -8914,7 +8901,6 @@
       <c r="I243" s="20">
         <v>0</v>
       </c>
-      <c r="P243" s="22"/>
     </row>
     <row r="244" spans="1:16">
       <c r="A244" t="s">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1459FEA-22CB-524B-A426-31C00AB30D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF29CEB-43E7-7745-B461-D1CA6C192292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7401,7 +7401,9 @@
       <c r="H185" s="17">
         <v>0.19</v>
       </c>
-      <c r="I185" s="20"/>
+      <c r="I185" s="20">
+        <v>0.31</v>
+      </c>
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
@@ -7426,7 +7428,9 @@
       <c r="H186" s="17">
         <v>0.35</v>
       </c>
-      <c r="I186" s="20"/>
+      <c r="I186" s="20">
+        <v>0.48</v>
+      </c>
       <c r="P186" s="4"/>
     </row>
     <row r="187" spans="1:16">
@@ -7809,7 +7813,9 @@
       <c r="H201" s="17">
         <v>0.67</v>
       </c>
-      <c r="I201" s="20"/>
+      <c r="I201" s="20">
+        <v>0.54</v>
+      </c>
       <c r="P201" s="4"/>
     </row>
     <row r="202" spans="1:16">
@@ -7886,7 +7892,9 @@
       <c r="H204" s="17">
         <v>0.6</v>
       </c>
-      <c r="I204" s="20"/>
+      <c r="I204" s="20">
+        <v>0.64</v>
+      </c>
       <c r="P204" s="4"/>
     </row>
     <row r="205" spans="1:16">
@@ -7911,7 +7919,9 @@
       <c r="H205" s="17">
         <v>0.32</v>
       </c>
-      <c r="I205" s="20"/>
+      <c r="I205" s="20">
+        <v>0.42</v>
+      </c>
       <c r="P205" s="4"/>
     </row>
     <row r="206" spans="1:16">
@@ -7936,7 +7946,9 @@
       <c r="H206" s="17">
         <v>0.37</v>
       </c>
-      <c r="I206" s="20"/>
+      <c r="I206" s="20">
+        <v>0.64</v>
+      </c>
       <c r="P206" s="4"/>
     </row>
     <row r="207" spans="1:16">
@@ -8013,7 +8025,9 @@
       <c r="H209" s="17">
         <v>0.42</v>
       </c>
-      <c r="I209" s="20"/>
+      <c r="I209" s="20">
+        <v>0.33</v>
+      </c>
       <c r="P209" s="4"/>
     </row>
     <row r="210" spans="1:16">
@@ -8088,7 +8102,9 @@
       <c r="H212" s="17">
         <v>0.44</v>
       </c>
-      <c r="I212" s="20"/>
+      <c r="I212" s="20">
+        <v>0.52</v>
+      </c>
       <c r="P212" s="4"/>
     </row>
     <row r="213" spans="1:16">
@@ -8113,7 +8129,9 @@
       <c r="H213" s="17">
         <v>0.75</v>
       </c>
-      <c r="I213" s="20"/>
+      <c r="I213" s="20">
+        <v>0.36</v>
+      </c>
       <c r="P213" s="4"/>
     </row>
     <row r="214" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF29CEB-43E7-7745-B461-D1CA6C192292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6FF2D1-FFFF-7442-B1E8-675BD6DDD63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7376,7 +7376,9 @@
       <c r="H184" s="17">
         <v>0.26</v>
       </c>
-      <c r="I184" s="20"/>
+      <c r="I184" s="20">
+        <v>0.04</v>
+      </c>
       <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
@@ -7482,7 +7484,9 @@
       <c r="H188" s="20">
         <v>0</v>
       </c>
-      <c r="I188" s="20"/>
+      <c r="I188" s="20">
+        <v>0.48</v>
+      </c>
       <c r="P188" s="15"/>
     </row>
     <row r="189" spans="1:16">
@@ -7507,7 +7511,9 @@
       <c r="H189" s="17">
         <v>0.63</v>
       </c>
-      <c r="I189" s="20"/>
+      <c r="I189" s="20">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="P189" s="4"/>
     </row>
     <row r="190" spans="1:16">
@@ -7532,7 +7538,9 @@
       <c r="H190" s="17">
         <v>0.39</v>
       </c>
-      <c r="I190" s="20"/>
+      <c r="I190" s="20">
+        <v>0.13</v>
+      </c>
       <c r="P190" s="4"/>
     </row>
     <row r="191" spans="1:16">
@@ -7557,7 +7565,9 @@
       <c r="H191" s="17">
         <v>0.68</v>
       </c>
-      <c r="I191" s="20"/>
+      <c r="I191" s="20">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="P191" s="4"/>
     </row>
     <row r="192" spans="1:16">
@@ -7582,7 +7592,9 @@
       <c r="H192" s="17">
         <v>0.42</v>
       </c>
-      <c r="I192" s="20"/>
+      <c r="I192" s="20">
+        <v>0.36</v>
+      </c>
       <c r="P192" s="4"/>
     </row>
     <row r="193" spans="1:16">
@@ -7607,7 +7619,9 @@
       <c r="H193" s="17">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I193" s="20"/>
+      <c r="I193" s="20">
+        <v>0.24</v>
+      </c>
       <c r="P193" s="4"/>
     </row>
     <row r="194" spans="1:16">
@@ -7659,7 +7673,9 @@
       <c r="H195" s="17">
         <v>0.04</v>
       </c>
-      <c r="I195" s="20"/>
+      <c r="I195" s="20">
+        <v>0.46</v>
+      </c>
       <c r="P195" s="4"/>
     </row>
     <row r="196" spans="1:16">
@@ -7684,7 +7700,9 @@
       <c r="H196" s="17">
         <v>0.26</v>
       </c>
-      <c r="I196" s="20"/>
+      <c r="I196" s="20">
+        <v>0.51</v>
+      </c>
       <c r="P196" s="4"/>
     </row>
     <row r="197" spans="1:16">
@@ -7709,7 +7727,9 @@
       <c r="H197" s="17">
         <v>0.54</v>
       </c>
-      <c r="I197" s="20"/>
+      <c r="I197" s="20">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="P197" s="4"/>
     </row>
     <row r="198" spans="1:16">
@@ -7734,7 +7754,9 @@
       <c r="H198" s="17">
         <v>0.51</v>
       </c>
-      <c r="I198" s="20"/>
+      <c r="I198" s="20">
+        <v>0.43</v>
+      </c>
       <c r="P198" s="4"/>
     </row>
     <row r="199" spans="1:16">
@@ -7840,7 +7862,9 @@
       <c r="H202" s="17">
         <v>0.67</v>
       </c>
-      <c r="I202" s="20"/>
+      <c r="I202" s="20">
+        <v>0.49</v>
+      </c>
       <c r="P202" s="4"/>
     </row>
     <row r="203" spans="1:16">
@@ -8000,7 +8024,9 @@
       <c r="H208" s="17">
         <v>0.3</v>
       </c>
-      <c r="I208" s="20"/>
+      <c r="I208" s="20">
+        <v>0</v>
+      </c>
       <c r="P208" s="4"/>
     </row>
     <row r="209" spans="1:16">
@@ -8052,7 +8078,9 @@
       <c r="H210" s="17">
         <v>0.39</v>
       </c>
-      <c r="I210" s="20"/>
+      <c r="I210" s="20">
+        <v>0.78</v>
+      </c>
       <c r="P210" s="4"/>
     </row>
     <row r="211" spans="1:16">
@@ -8077,7 +8105,9 @@
       <c r="H211" s="17">
         <v>0.65</v>
       </c>
-      <c r="I211" s="20"/>
+      <c r="I211" s="20">
+        <v>0.42</v>
+      </c>
       <c r="P211" s="4"/>
     </row>
     <row r="212" spans="1:16">
@@ -8157,7 +8187,7 @@
         <v>0.05</v>
       </c>
       <c r="I214" s="20">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="P214" s="4"/>
     </row>
@@ -8183,7 +8213,9 @@
       <c r="H215" s="17">
         <v>0.53</v>
       </c>
-      <c r="I215" s="20"/>
+      <c r="I215" s="20">
+        <v>0.49</v>
+      </c>
       <c r="P215" s="4"/>
     </row>
     <row r="216" spans="1:16">
@@ -8208,7 +8240,9 @@
       <c r="H216" s="17">
         <v>0.32</v>
       </c>
-      <c r="I216" s="20"/>
+      <c r="I216" s="20">
+        <v>0.33</v>
+      </c>
       <c r="P216" s="4"/>
     </row>
     <row r="217" spans="1:16">
@@ -8233,7 +8267,9 @@
       <c r="H217" s="17">
         <v>0.44</v>
       </c>
-      <c r="I217" s="20"/>
+      <c r="I217" s="20">
+        <v>0.31</v>
+      </c>
       <c r="P217" s="4"/>
     </row>
     <row r="218" spans="1:16">
@@ -8258,7 +8294,9 @@
       <c r="H218" s="17">
         <v>0.68</v>
       </c>
-      <c r="I218" s="20"/>
+      <c r="I218" s="20">
+        <v>0.73</v>
+      </c>
       <c r="P218" s="4"/>
     </row>
     <row r="219" spans="1:16">
@@ -8283,7 +8321,9 @@
       <c r="H219" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I219" s="20"/>
+      <c r="I219" s="20">
+        <v>0.69</v>
+      </c>
       <c r="P219" s="4"/>
     </row>
     <row r="220" spans="1:16">
@@ -8308,7 +8348,9 @@
       <c r="H220" s="17">
         <v>0.65</v>
       </c>
-      <c r="I220" s="20"/>
+      <c r="I220" s="20">
+        <v>0.73</v>
+      </c>
       <c r="P220" s="4"/>
     </row>
     <row r="221" spans="1:16">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6FF2D1-FFFF-7442-B1E8-675BD6DDD63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FF9ED4-D169-9F44-8987-C5C3E57EF7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7487,6 +7487,9 @@
       <c r="I188" s="20">
         <v>0.48</v>
       </c>
+      <c r="J188" s="17">
+        <v>0.75</v>
+      </c>
       <c r="P188" s="15"/>
     </row>
     <row r="189" spans="1:16">
@@ -7676,6 +7679,9 @@
       <c r="I195" s="20">
         <v>0.46</v>
       </c>
+      <c r="J195" s="17">
+        <v>0.37</v>
+      </c>
       <c r="P195" s="4"/>
     </row>
     <row r="196" spans="1:16">
@@ -7945,6 +7951,9 @@
       </c>
       <c r="I205" s="20">
         <v>0.42</v>
+      </c>
+      <c r="J205" s="17">
+        <v>0.48</v>
       </c>
       <c r="P205" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FF9ED4-D169-9F44-8987-C5C3E57EF7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9C31ED-9C63-0F46-BB16-33070DB4D205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7544,6 +7544,9 @@
       <c r="I190" s="20">
         <v>0.13</v>
       </c>
+      <c r="J190" s="17">
+        <v>0.06</v>
+      </c>
       <c r="P190" s="4"/>
     </row>
     <row r="191" spans="1:16">
@@ -7625,6 +7628,9 @@
       <c r="I193" s="20">
         <v>0.24</v>
       </c>
+      <c r="J193" s="17">
+        <v>0.32</v>
+      </c>
       <c r="P193" s="4"/>
     </row>
     <row r="194" spans="1:16">
@@ -7763,6 +7769,9 @@
       <c r="I198" s="20">
         <v>0.43</v>
       </c>
+      <c r="J198" s="17">
+        <v>0.33</v>
+      </c>
       <c r="P198" s="4"/>
     </row>
     <row r="199" spans="1:16">
@@ -7817,6 +7826,9 @@
       <c r="I200" s="20">
         <v>0.06</v>
       </c>
+      <c r="J200" s="17">
+        <v>0.4</v>
+      </c>
       <c r="P200" s="4"/>
     </row>
     <row r="201" spans="1:16">
@@ -7871,6 +7883,9 @@
       <c r="I202" s="20">
         <v>0.49</v>
       </c>
+      <c r="J202" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P202" s="4"/>
     </row>
     <row r="203" spans="1:16">
@@ -7923,7 +7938,7 @@
         <v>0.6</v>
       </c>
       <c r="I204" s="20">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="P204" s="4"/>
     </row>
@@ -8090,6 +8105,9 @@
       <c r="I210" s="20">
         <v>0.78</v>
       </c>
+      <c r="J210" s="17">
+        <v>0.78</v>
+      </c>
       <c r="P210" s="4"/>
     </row>
     <row r="211" spans="1:16">
@@ -8115,7 +8133,7 @@
         <v>0.65</v>
       </c>
       <c r="I211" s="20">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="P211" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9C31ED-9C63-0F46-BB16-33070DB4D205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0219AD-227F-274C-B3A3-C31F8EA46C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7379,6 +7379,9 @@
       <c r="I184" s="20">
         <v>0.04</v>
       </c>
+      <c r="J184" s="17">
+        <v>0.19</v>
+      </c>
       <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
@@ -7406,6 +7409,9 @@
       <c r="I185" s="20">
         <v>0.31</v>
       </c>
+      <c r="J185" s="17">
+        <v>0.42</v>
+      </c>
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
@@ -7742,6 +7748,9 @@
       <c r="I197" s="20">
         <v>0.28000000000000003</v>
       </c>
+      <c r="J197" s="17">
+        <v>0.33</v>
+      </c>
       <c r="P197" s="4"/>
     </row>
     <row r="198" spans="1:16">
@@ -7770,7 +7779,7 @@
         <v>0.43</v>
       </c>
       <c r="J198" s="17">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="P198" s="4"/>
     </row>
@@ -7856,6 +7865,9 @@
       <c r="I201" s="20">
         <v>0.54</v>
       </c>
+      <c r="J201" s="17">
+        <v>0.73</v>
+      </c>
       <c r="P201" s="4"/>
     </row>
     <row r="202" spans="1:16">
@@ -7997,6 +8009,9 @@
       <c r="I206" s="20">
         <v>0.64</v>
       </c>
+      <c r="J206" s="17">
+        <v>0.33</v>
+      </c>
       <c r="P206" s="4"/>
     </row>
     <row r="207" spans="1:16">
@@ -8051,6 +8066,9 @@
       <c r="I208" s="20">
         <v>0</v>
       </c>
+      <c r="J208" s="17">
+        <v>0.33</v>
+      </c>
       <c r="P208" s="4"/>
     </row>
     <row r="209" spans="1:16">
@@ -8078,6 +8096,9 @@
       <c r="I209" s="20">
         <v>0.33</v>
       </c>
+      <c r="J209" s="17">
+        <v>0.35</v>
+      </c>
       <c r="P209" s="4"/>
     </row>
     <row r="210" spans="1:16">
@@ -8270,6 +8291,9 @@
       <c r="I216" s="20">
         <v>0.33</v>
       </c>
+      <c r="J216" s="17">
+        <v>0.14000000000000001</v>
+      </c>
       <c r="P216" s="4"/>
     </row>
     <row r="217" spans="1:16">
@@ -8297,6 +8321,9 @@
       <c r="I217" s="20">
         <v>0.31</v>
       </c>
+      <c r="J217" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P217" s="4"/>
     </row>
     <row r="218" spans="1:16">
@@ -8377,6 +8404,9 @@
       </c>
       <c r="I220" s="20">
         <v>0.73</v>
+      </c>
+      <c r="J220" s="17">
+        <v>0.67</v>
       </c>
       <c r="P220" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0219AD-227F-274C-B3A3-C31F8EA46C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D89599A-C694-3D4E-8A30-F8B702380E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7439,6 +7439,9 @@
       <c r="I186" s="20">
         <v>0.48</v>
       </c>
+      <c r="J186" s="17">
+        <v>0.27</v>
+      </c>
       <c r="P186" s="4"/>
     </row>
     <row r="187" spans="1:16">
@@ -7580,6 +7583,9 @@
       <c r="I191" s="20">
         <v>0.56999999999999995</v>
       </c>
+      <c r="J191" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P191" s="4"/>
     </row>
     <row r="192" spans="1:16">
@@ -7607,6 +7613,9 @@
       <c r="I192" s="20">
         <v>0.36</v>
       </c>
+      <c r="J192" s="17">
+        <v>0.27</v>
+      </c>
       <c r="P192" s="4"/>
     </row>
     <row r="193" spans="1:16">
@@ -7925,6 +7934,9 @@
       <c r="I203" s="20">
         <v>0.39</v>
       </c>
+      <c r="J203" s="17">
+        <v>0.49</v>
+      </c>
       <c r="P203" s="4"/>
     </row>
     <row r="204" spans="1:16">
@@ -7952,6 +7964,9 @@
       <c r="I204" s="20">
         <v>0.7</v>
       </c>
+      <c r="J204" s="17">
+        <v>0.81</v>
+      </c>
       <c r="P204" s="4"/>
     </row>
     <row r="205" spans="1:16">
@@ -8039,6 +8054,9 @@
       <c r="I207" s="20">
         <v>0.54</v>
       </c>
+      <c r="J207" s="17">
+        <v>0.4</v>
+      </c>
       <c r="P207" s="4"/>
     </row>
     <row r="208" spans="1:16">
@@ -8183,6 +8201,9 @@
       <c r="I212" s="20">
         <v>0.52</v>
       </c>
+      <c r="J212" s="17">
+        <v>0.49</v>
+      </c>
       <c r="P212" s="4"/>
     </row>
     <row r="213" spans="1:16">
@@ -8237,6 +8258,9 @@
       <c r="I214" s="20">
         <v>0.04</v>
       </c>
+      <c r="J214" s="17">
+        <v>0</v>
+      </c>
       <c r="P214" s="4"/>
     </row>
     <row r="215" spans="1:16">
@@ -8350,6 +8374,9 @@
       </c>
       <c r="I218" s="20">
         <v>0.73</v>
+      </c>
+      <c r="J218" s="17">
+        <v>0.67</v>
       </c>
       <c r="P218" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D89599A-C694-3D4E-8A30-F8B702380E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94522DD0-40C7-D347-9407-8AF1D94A8D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7526,6 +7526,9 @@
       <c r="I189" s="20">
         <v>0.57999999999999996</v>
       </c>
+      <c r="J189" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P189" s="4"/>
     </row>
     <row r="190" spans="1:16">
@@ -7673,6 +7676,9 @@
       <c r="I194" s="20">
         <v>0.49</v>
       </c>
+      <c r="J194" s="17">
+        <v>0.6</v>
+      </c>
       <c r="P194" s="4"/>
     </row>
     <row r="195" spans="1:16">
@@ -7730,6 +7736,9 @@
       <c r="I196" s="20">
         <v>0.51</v>
       </c>
+      <c r="J196" s="17">
+        <v>0.32</v>
+      </c>
       <c r="P196" s="4"/>
     </row>
     <row r="197" spans="1:16">
@@ -7817,6 +7826,9 @@
       <c r="I199" s="20">
         <v>0.4</v>
       </c>
+      <c r="J199" s="17">
+        <v>0.17</v>
+      </c>
       <c r="P199" s="15"/>
     </row>
     <row r="200" spans="1:16">
@@ -8174,6 +8186,9 @@
       <c r="I211" s="20">
         <v>0.45</v>
       </c>
+      <c r="J211" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P211" s="4"/>
     </row>
     <row r="212" spans="1:16">
@@ -8231,6 +8246,9 @@
       <c r="I213" s="20">
         <v>0.36</v>
       </c>
+      <c r="J213" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P213" s="4"/>
     </row>
     <row r="214" spans="1:16">
@@ -8288,6 +8306,9 @@
       <c r="I215" s="20">
         <v>0.49</v>
       </c>
+      <c r="J215" s="17">
+        <v>0.35</v>
+      </c>
       <c r="P215" s="4"/>
     </row>
     <row r="216" spans="1:16">
@@ -8404,6 +8425,9 @@
       </c>
       <c r="I219" s="20">
         <v>0.69</v>
+      </c>
+      <c r="J219" s="17">
+        <v>0.41</v>
       </c>
       <c r="P219" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94522DD0-40C7-D347-9407-8AF1D94A8D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4B579A-2414-4B4D-8BA8-9D6A23B0433C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3106,6 +3106,9 @@
       <c r="I31" s="21">
         <v>0.45</v>
       </c>
+      <c r="J31" s="17">
+        <v>0.62</v>
+      </c>
       <c r="L31" s="17">
         <v>0.24</v>
       </c>
@@ -3226,6 +3229,9 @@
       <c r="I35" s="21">
         <v>0.61</v>
       </c>
+      <c r="J35" s="17">
+        <v>0.62</v>
+      </c>
       <c r="L35" s="17">
         <v>0.24</v>
       </c>
@@ -3256,6 +3262,9 @@
       <c r="I36" s="20">
         <v>0.25</v>
       </c>
+      <c r="J36" s="17">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="L36" s="17">
         <v>0</v>
       </c>
@@ -3433,6 +3442,9 @@
       <c r="I42" s="21">
         <v>0.19</v>
       </c>
+      <c r="J42" s="17">
+        <v>0.33</v>
+      </c>
       <c r="L42" s="17">
         <v>0.24</v>
       </c>
@@ -3490,6 +3502,9 @@
       <c r="I44" s="20">
         <v>0.18</v>
       </c>
+      <c r="J44" s="17">
+        <v>0.25</v>
+      </c>
       <c r="P44" s="15"/>
     </row>
     <row r="45" spans="1:16">
@@ -3606,6 +3621,9 @@
       </c>
       <c r="I48" s="21">
         <v>0.54</v>
+      </c>
+      <c r="J48" s="17">
+        <v>0.56000000000000005</v>
       </c>
       <c r="L48" s="17">
         <v>0.8</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4B579A-2414-4B4D-8BA8-9D6A23B0433C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B95C7D-D2B8-094B-9D8D-821413453C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3139,6 +3139,9 @@
       <c r="I32" s="21">
         <v>0.3</v>
       </c>
+      <c r="J32" s="17">
+        <v>0.49</v>
+      </c>
       <c r="L32" s="17">
         <v>0.8</v>
       </c>
@@ -3169,6 +3172,9 @@
       <c r="I33" s="21">
         <v>0.31</v>
       </c>
+      <c r="J33" s="17">
+        <v>0.21</v>
+      </c>
       <c r="L33" s="17">
         <v>0.8</v>
       </c>
@@ -3199,6 +3205,9 @@
       <c r="I34" s="20">
         <v>0.12</v>
       </c>
+      <c r="J34" s="17">
+        <v>0.3</v>
+      </c>
       <c r="L34" s="17">
         <v>0</v>
       </c>
@@ -3295,6 +3304,9 @@
       <c r="I37" s="21">
         <v>0.27</v>
       </c>
+      <c r="J37" s="17">
+        <v>0.49</v>
+      </c>
       <c r="L37" s="17">
         <v>0</v>
       </c>
@@ -3325,6 +3337,9 @@
       <c r="I38" s="20">
         <v>0.24</v>
       </c>
+      <c r="J38" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P38" s="15"/>
     </row>
     <row r="39" spans="1:16">
@@ -3412,6 +3427,9 @@
       <c r="I41" s="21">
         <v>0.31</v>
       </c>
+      <c r="J41" s="17">
+        <v>0.52</v>
+      </c>
       <c r="L41" s="17">
         <v>0.24</v>
       </c>
@@ -3475,6 +3493,9 @@
       <c r="I43" s="20">
         <v>0.51</v>
       </c>
+      <c r="J43" s="17">
+        <v>0.4</v>
+      </c>
       <c r="P43" s="15"/>
     </row>
     <row r="44" spans="1:16">
@@ -3531,6 +3552,9 @@
       </c>
       <c r="I45" s="21">
         <v>0.39</v>
+      </c>
+      <c r="J45" s="17">
+        <v>0.4</v>
       </c>
       <c r="L45" s="17">
         <v>0.8</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B95C7D-D2B8-094B-9D8D-821413453C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E839DF0-C956-6B42-9563-AA0AC4C25B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3586,6 +3586,9 @@
       <c r="I46" s="21">
         <v>0.27</v>
       </c>
+      <c r="J46" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="L46" s="17">
         <v>0.24</v>
       </c>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E839DF0-C956-6B42-9563-AA0AC4C25B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FF4B02-D47F-AC41-9C94-38BB0991EB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3367,6 +3367,9 @@
       <c r="I39" s="21">
         <v>0.49</v>
       </c>
+      <c r="J39" s="17">
+        <v>0.59</v>
+      </c>
       <c r="L39" s="17">
         <v>0.8</v>
       </c>
@@ -3397,6 +3400,9 @@
       <c r="I40" s="21">
         <v>0.22</v>
       </c>
+      <c r="J40" s="17">
+        <v>0.32</v>
+      </c>
       <c r="L40" s="17">
         <v>0.8</v>
       </c>
@@ -3618,6 +3624,9 @@
       </c>
       <c r="I47" s="21">
         <v>0.15</v>
+      </c>
+      <c r="J47" s="17">
+        <v>0.41</v>
       </c>
       <c r="L47" s="17">
         <v>0.24</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FF4B02-D47F-AC41-9C94-38BB0991EB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F238EF7C-85CE-9443-8947-D250DE8C908A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1693,7 +1693,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1732,6 +1732,13 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3667,10 +3674,10 @@
       <c r="P48" s="4"/>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="25" t="s">
         <v>92</v>
       </c>
       <c r="C49" s="19" t="s">
@@ -3694,10 +3701,10 @@
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C50" s="19" t="s">
@@ -3724,10 +3731,10 @@
       <c r="P50" s="4"/>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="25" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="19" t="s">
@@ -3754,10 +3761,10 @@
       <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="25" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="19" t="s">
@@ -3784,10 +3791,10 @@
       <c r="P52" s="4"/>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="25" t="s">
         <v>101</v>
       </c>
       <c r="C53" s="19" t="s">
@@ -3814,10 +3821,10 @@
       <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -3844,10 +3851,10 @@
       <c r="P54" s="4"/>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="25" t="s">
         <v>476</v>
       </c>
       <c r="C55" s="19" t="s">
@@ -4876,10 +4883,10 @@
       <c r="P89" s="4"/>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="25" t="s">
         <v>172</v>
       </c>
       <c r="C90" s="19" t="s">
@@ -4903,10 +4910,10 @@
       <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="25" t="s">
         <v>175</v>
       </c>
       <c r="C91" s="19" t="s">
@@ -4930,10 +4937,10 @@
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" t="s">
+      <c r="A92" s="22" t="s">
         <v>474</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="23" t="s">
         <v>475</v>
       </c>
       <c r="C92" s="17" t="s">
@@ -4957,10 +4964,10 @@
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="B93" s="9" t="s">
+      <c r="B93" s="25" t="s">
         <v>177</v>
       </c>
       <c r="C93" s="19" t="s">
@@ -4984,10 +4991,10 @@
       <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="25" t="s">
         <v>179</v>
       </c>
       <c r="C94" s="19" t="s">
@@ -5011,10 +5018,10 @@
       <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="25" t="s">
         <v>181</v>
       </c>
       <c r="C95" s="19" t="s">
@@ -5038,10 +5045,10 @@
       <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="25" t="s">
         <v>183</v>
       </c>
       <c r="C96" s="19" t="s">
@@ -5065,10 +5072,10 @@
       <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="25" t="s">
         <v>185</v>
       </c>
       <c r="C97" s="19" t="s">
@@ -6059,10 +6066,10 @@
       <c r="P133" s="4"/>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="9" t="s">
+      <c r="A134" s="25" t="s">
         <v>250</v>
       </c>
-      <c r="B134" s="9" t="s">
+      <c r="B134" s="25" t="s">
         <v>251</v>
       </c>
       <c r="C134" s="19" t="s">
@@ -6086,10 +6093,10 @@
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" s="9" t="s">
+      <c r="A135" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="B135" s="9" t="s">
+      <c r="B135" s="25" t="s">
         <v>254</v>
       </c>
       <c r="C135" s="19" t="s">
@@ -6113,10 +6120,10 @@
       <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="9" t="s">
+      <c r="A136" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="B136" s="9" t="s">
+      <c r="B136" s="25" t="s">
         <v>256</v>
       </c>
       <c r="C136" s="19" t="s">
@@ -6140,10 +6147,10 @@
       <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="9" t="s">
+      <c r="A137" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="B137" s="9" t="s">
+      <c r="B137" s="25" t="s">
         <v>258</v>
       </c>
       <c r="C137" s="19" t="s">
@@ -6167,10 +6174,10 @@
       <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="9" t="s">
+      <c r="A138" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="B138" s="9" t="s">
+      <c r="B138" s="25" t="s">
         <v>260</v>
       </c>
       <c r="C138" s="19" t="s">
@@ -6194,10 +6201,10 @@
       <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="9" t="s">
+      <c r="A139" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="B139" s="9" t="s">
+      <c r="B139" s="25" t="s">
         <v>262</v>
       </c>
       <c r="C139" s="19" t="s">
@@ -6221,10 +6228,10 @@
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" s="9" t="s">
+      <c r="A140" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="B140" s="9" t="s">
+      <c r="B140" s="25" t="s">
         <v>264</v>
       </c>
       <c r="C140" s="19" t="s">
@@ -6248,10 +6255,10 @@
       <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="9" t="s">
+      <c r="A141" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="B141" s="9" t="s">
+      <c r="B141" s="25" t="s">
         <v>266</v>
       </c>
       <c r="C141" s="19" t="s">
@@ -6275,10 +6282,10 @@
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="9" t="s">
+      <c r="A142" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="B142" s="9" t="s">
+      <c r="B142" s="25" t="s">
         <v>268</v>
       </c>
       <c r="C142" s="19" t="s">
@@ -6302,10 +6309,10 @@
       <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="9" t="s">
+      <c r="A143" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="B143" s="9" t="s">
+      <c r="B143" s="25" t="s">
         <v>270</v>
       </c>
       <c r="C143" s="19" t="s">
@@ -7409,10 +7416,10 @@
       <c r="P183" s="4"/>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" s="9" t="s">
+      <c r="A184" s="25" t="s">
         <v>346</v>
       </c>
-      <c r="B184" s="9" t="s">
+      <c r="B184" s="25" t="s">
         <v>347</v>
       </c>
       <c r="C184" s="19" t="s">
@@ -7439,10 +7446,10 @@
       <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
-      <c r="A185" t="s">
+      <c r="A185" s="22" t="s">
         <v>446</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="26" t="s">
         <v>447</v>
       </c>
       <c r="C185" s="17" t="s">
@@ -7469,10 +7476,10 @@
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" s="9" t="s">
+      <c r="A186" s="25" t="s">
         <v>349</v>
       </c>
-      <c r="B186" s="9" t="s">
+      <c r="B186" s="25" t="s">
         <v>350</v>
       </c>
       <c r="C186" s="19" t="s">
@@ -7499,10 +7506,10 @@
       <c r="P186" s="4"/>
     </row>
     <row r="187" spans="1:16">
-      <c r="A187" t="s">
+      <c r="A187" s="22" t="s">
         <v>501</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="B187" s="23" t="s">
         <v>502</v>
       </c>
       <c r="C187" s="17" t="s">
@@ -8516,10 +8523,10 @@
       <c r="P220" s="4"/>
     </row>
     <row r="221" spans="1:16">
-      <c r="A221" s="9" t="s">
+      <c r="A221" s="25" t="s">
         <v>405</v>
       </c>
-      <c r="B221" s="9" t="s">
+      <c r="B221" s="25" t="s">
         <v>406</v>
       </c>
       <c r="C221" s="19" t="s">
@@ -8540,13 +8547,16 @@
       <c r="I221" s="20">
         <v>0.57999999999999996</v>
       </c>
+      <c r="J221" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P221" s="4"/>
     </row>
     <row r="222" spans="1:16">
-      <c r="A222" t="s">
+      <c r="A222" s="22" t="s">
         <v>503</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="B222" s="23" t="s">
         <v>504</v>
       </c>
       <c r="C222" s="17" t="s">
@@ -8565,6 +8575,9 @@
         <v>0</v>
       </c>
       <c r="I222" s="20">
+        <v>0</v>
+      </c>
+      <c r="J222" s="17">
         <v>0</v>
       </c>
       <c r="P222" s="15"/>
@@ -8594,6 +8607,9 @@
       <c r="I223" s="20">
         <v>0.1</v>
       </c>
+      <c r="J223" s="17">
+        <v>0.17</v>
+      </c>
       <c r="P223" s="4"/>
     </row>
     <row r="224" spans="1:16">
@@ -8621,249 +8637,267 @@
       <c r="I224" s="20">
         <v>0.43</v>
       </c>
+      <c r="J224" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P224" s="4"/>
     </row>
     <row r="225" spans="1:16">
-      <c r="A225" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="B225" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="C225" s="19" t="s">
+      <c r="A225" t="s">
+        <v>468</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C225" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="D225" s="19">
-        <v>0.67</v>
+      <c r="D225" s="20">
+        <v>0</v>
       </c>
       <c r="E225" s="17">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="F225" s="17">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H225" s="17">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="I225" s="20">
-        <v>0.21</v>
-      </c>
-      <c r="P225" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="J225" s="17">
+        <v>0.38</v>
+      </c>
+      <c r="P225" s="15"/>
     </row>
     <row r="226" spans="1:16">
       <c r="A226" s="9" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C226" s="19" t="s">
         <v>407</v>
       </c>
       <c r="D226" s="19">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="E226" s="17">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="F226" s="17">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H226" s="17">
-        <v>0.54</v>
+        <v>0.11</v>
       </c>
       <c r="I226" s="20">
-        <v>0.7</v>
+        <v>0.21</v>
+      </c>
+      <c r="J226" s="17">
+        <v>0.21</v>
       </c>
       <c r="P226" s="4"/>
     </row>
     <row r="227" spans="1:16">
       <c r="A227" s="9" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C227" s="19" t="s">
         <v>407</v>
       </c>
       <c r="D227" s="19">
+        <v>0.71</v>
+      </c>
+      <c r="E227" s="17">
+        <v>0.98</v>
+      </c>
+      <c r="F227" s="17">
+        <v>0.66</v>
+      </c>
+      <c r="H227" s="17">
+        <v>0.54</v>
+      </c>
+      <c r="I227" s="20">
+        <v>0.7</v>
+      </c>
+      <c r="J227" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="P227" s="24"/>
+    </row>
+    <row r="228" spans="1:16">
+      <c r="A228" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="C228" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="D228" s="19">
         <v>0.89</v>
       </c>
-      <c r="E227" s="17">
+      <c r="E228" s="17">
         <v>0.97</v>
       </c>
-      <c r="F227" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="H227" s="17">
+      <c r="F228" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H228" s="17">
         <v>0.61</v>
       </c>
-      <c r="I227" s="20">
+      <c r="I228" s="20">
         <v>0.34</v>
       </c>
-      <c r="P227" s="16"/>
-    </row>
-    <row r="228" spans="1:16">
-      <c r="A228" t="s">
+      <c r="J228" s="17">
+        <v>0.33</v>
+      </c>
+      <c r="P228" s="24"/>
+    </row>
+    <row r="229" spans="1:16">
+      <c r="A229" s="22" t="s">
         <v>460</v>
       </c>
-      <c r="B228" s="2" t="s">
+      <c r="B229" s="23" t="s">
         <v>461</v>
       </c>
-      <c r="C228" s="17" t="s">
+      <c r="C229" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D228" s="20">
+      <c r="D229" s="20">
         <v>0</v>
       </c>
-      <c r="E228" s="17">
+      <c r="E229" s="17">
         <v>0.88</v>
       </c>
-      <c r="F228" s="17">
+      <c r="F229" s="17">
         <v>0.66</v>
       </c>
-      <c r="H228" s="17">
+      <c r="H229" s="17">
         <v>0.33</v>
       </c>
-      <c r="I228" s="20">
+      <c r="I229" s="20">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="229" spans="1:16">
-      <c r="A229" s="9" t="s">
+      <c r="P229" s="22"/>
+    </row>
+    <row r="230" spans="1:16">
+      <c r="A230" s="25" t="s">
         <v>418</v>
       </c>
-      <c r="B229" s="9" t="s">
+      <c r="B230" s="25" t="s">
         <v>419</v>
       </c>
-      <c r="C229" s="19" t="s">
+      <c r="C230" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D229" s="19">
+      <c r="D230" s="19">
         <v>0.79</v>
       </c>
-      <c r="E229" s="17">
+      <c r="E230" s="17">
         <v>0.89</v>
       </c>
-      <c r="F229" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="H229" s="17">
+      <c r="F230" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H230" s="17">
         <v>0.26</v>
       </c>
-      <c r="I229" s="20">
+      <c r="I230" s="20">
         <v>0.19</v>
       </c>
-      <c r="P229" s="16"/>
-    </row>
-    <row r="230" spans="1:16">
-      <c r="A230" t="s">
+      <c r="P230" s="24"/>
+    </row>
+    <row r="231" spans="1:16">
+      <c r="A231" s="22" t="s">
         <v>497</v>
       </c>
-      <c r="B230" s="2" t="s">
+      <c r="B231" s="23" t="s">
         <v>498</v>
       </c>
-      <c r="C230" s="17" t="s">
+      <c r="C231" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D230" s="20"/>
-      <c r="F230" s="17">
+      <c r="D231" s="20"/>
+      <c r="F231" s="17">
         <v>0.77</v>
       </c>
-      <c r="H230" s="20">
+      <c r="H231" s="20">
         <v>0</v>
       </c>
-      <c r="I230" s="20">
+      <c r="I231" s="20">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="231" spans="1:16">
-      <c r="A231" s="9" t="s">
+      <c r="P231" s="22"/>
+    </row>
+    <row r="232" spans="1:16">
+      <c r="A232" s="25" t="s">
         <v>421</v>
       </c>
-      <c r="B231" s="9" t="s">
+      <c r="B232" s="25" t="s">
         <v>422</v>
-      </c>
-      <c r="C231" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D231" s="19">
-        <v>0.66</v>
-      </c>
-      <c r="E231" s="17">
-        <v>0.87</v>
-      </c>
-      <c r="F231" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="H231" s="17">
-        <v>0.16</v>
-      </c>
-      <c r="I231" s="20">
-        <v>0.87</v>
-      </c>
-      <c r="P231" s="16"/>
-    </row>
-    <row r="232" spans="1:16">
-      <c r="A232" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="B232" s="9" t="s">
-        <v>424</v>
       </c>
       <c r="C232" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D232" s="19">
+        <v>0.66</v>
+      </c>
+      <c r="E232" s="17">
+        <v>0.87</v>
+      </c>
+      <c r="F232" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H232" s="17">
+        <v>0.16</v>
+      </c>
+      <c r="I232" s="20">
+        <v>0.87</v>
+      </c>
+      <c r="P232" s="24"/>
+    </row>
+    <row r="233" spans="1:16">
+      <c r="A233" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C233" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="D233" s="19">
         <v>0.69</v>
       </c>
-      <c r="E232" s="17">
+      <c r="E233" s="17">
         <v>0.88</v>
       </c>
-      <c r="F232" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="H232" s="17">
+      <c r="F233" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H233" s="17">
         <v>0.28000000000000003</v>
       </c>
-      <c r="I232" s="20">
+      <c r="I233" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P232" s="16"/>
-    </row>
-    <row r="233" spans="1:16">
-      <c r="A233" t="s">
-        <v>464</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="C233" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="D233" s="20">
-        <v>0</v>
-      </c>
-      <c r="E233" s="17">
-        <v>0.98</v>
-      </c>
-      <c r="F233" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="H233" s="17">
-        <v>0.16</v>
-      </c>
-      <c r="I233" s="20">
-        <v>0.18</v>
-      </c>
+      <c r="P233" s="24"/>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C234" s="17" t="s">
         <v>420</v>
@@ -8872,151 +8906,153 @@
         <v>0</v>
       </c>
       <c r="E234" s="17">
+        <v>0.98</v>
+      </c>
+      <c r="F234" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H234" s="17">
+        <v>0.16</v>
+      </c>
+      <c r="I234" s="20">
+        <v>0.18</v>
+      </c>
+      <c r="P234" s="22"/>
+    </row>
+    <row r="235" spans="1:16">
+      <c r="A235" t="s">
+        <v>457</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C235" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="D235" s="20">
+        <v>0</v>
+      </c>
+      <c r="E235" s="17">
         <v>0.94</v>
       </c>
-      <c r="F234" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="H234" s="17">
+      <c r="F235" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H235" s="17">
         <v>0.26</v>
       </c>
-      <c r="I234" s="20">
+      <c r="I235" s="20">
         <v>0.21</v>
       </c>
-    </row>
-    <row r="235" spans="1:16">
-      <c r="A235" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="B235" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="C235" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D235" s="19">
-        <v>0.83</v>
-      </c>
-      <c r="E235" s="17">
-        <v>0.9</v>
-      </c>
-      <c r="F235" s="17">
-        <v>0.66</v>
-      </c>
-      <c r="H235" s="17">
-        <v>0.63</v>
-      </c>
-      <c r="I235" s="20">
-        <v>0.72</v>
-      </c>
-      <c r="P235" s="16"/>
+      <c r="P235" s="22"/>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C236" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D236" s="19">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="E236" s="17">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="F236" s="17">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="H236" s="17">
-        <v>0.26</v>
+        <v>0.63</v>
       </c>
       <c r="I236" s="20">
-        <v>0.43</v>
-      </c>
-      <c r="P236" s="16"/>
+        <v>0.72</v>
+      </c>
+      <c r="P236" s="24"/>
     </row>
     <row r="237" spans="1:16">
       <c r="A237" s="9" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C237" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D237" s="19">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="E237" s="17">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="F237" s="17">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H237" s="17">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="I237" s="20">
-        <v>0.66</v>
-      </c>
-      <c r="P237" s="16"/>
+        <v>0.43</v>
+      </c>
+      <c r="P237" s="24"/>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" s="9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C238" s="19" t="s">
         <v>420</v>
       </c>
       <c r="D238" s="19">
+        <v>0.81</v>
+      </c>
+      <c r="E238" s="17">
+        <v>0.92</v>
+      </c>
+      <c r="F238" s="17">
+        <v>0.66</v>
+      </c>
+      <c r="H238" s="17">
+        <v>0.67</v>
+      </c>
+      <c r="I238" s="20">
+        <v>0.66</v>
+      </c>
+      <c r="P238" s="24"/>
+    </row>
+    <row r="239" spans="1:16">
+      <c r="A239" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C239" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="D239" s="19">
         <v>0.74</v>
       </c>
-      <c r="E238" s="17">
+      <c r="E239" s="17">
         <v>0.94</v>
       </c>
-      <c r="F238" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="H238" s="17">
+      <c r="F239" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H239" s="17">
         <v>0.37</v>
       </c>
-      <c r="I238" s="20">
+      <c r="I239" s="20">
         <v>0.25</v>
       </c>
-      <c r="P238" s="16"/>
-    </row>
-    <row r="239" spans="1:16">
-      <c r="A239" t="s">
-        <v>468</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C239" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="D239" s="20">
-        <v>0</v>
-      </c>
-      <c r="E239" s="17">
-        <v>0.91</v>
-      </c>
-      <c r="F239" s="17">
-        <v>0</v>
-      </c>
-      <c r="H239" s="17">
-        <v>0.35</v>
-      </c>
-      <c r="I239" s="20">
-        <v>0</v>
-      </c>
+      <c r="P239" s="24"/>
     </row>
     <row r="240" spans="1:16">
       <c r="A240" s="9" t="s">
@@ -9043,7 +9079,7 @@
       <c r="I240" s="20">
         <v>0.66</v>
       </c>
-      <c r="P240" s="16"/>
+      <c r="P240" s="24"/>
     </row>
     <row r="241" spans="1:16">
       <c r="A241" s="9" t="s">
@@ -9070,7 +9106,7 @@
       <c r="I241" s="20">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P241" s="16"/>
+      <c r="P241" s="24"/>
     </row>
     <row r="242" spans="1:16">
       <c r="A242" t="s">
@@ -9097,6 +9133,7 @@
       <c r="I242" s="20">
         <v>0.72</v>
       </c>
+      <c r="P242" s="22"/>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" t="s">
@@ -9123,6 +9160,7 @@
       <c r="I243" s="20">
         <v>0</v>
       </c>
+      <c r="P243" s="22"/>
     </row>
     <row r="244" spans="1:16">
       <c r="A244" t="s">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F238EF7C-85CE-9443-8947-D250DE8C908A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E17031-7C25-A84F-825F-EEA83E7EEE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2276,6 +2276,9 @@
       <c r="I3" s="21">
         <v>0.22</v>
       </c>
+      <c r="J3" s="17">
+        <v>0.17</v>
+      </c>
       <c r="L3" s="17">
         <v>0.68</v>
       </c>
@@ -2306,6 +2309,9 @@
       <c r="I4" s="21">
         <v>0.31</v>
       </c>
+      <c r="J4" s="17">
+        <v>0.27</v>
+      </c>
       <c r="L4" s="17">
         <v>0.48</v>
       </c>
@@ -2396,6 +2402,9 @@
       <c r="I7" s="21">
         <v>0.25</v>
       </c>
+      <c r="J7" s="17">
+        <v>0.41</v>
+      </c>
       <c r="L7" s="17">
         <v>0.48</v>
       </c>
@@ -2726,6 +2735,9 @@
       <c r="I18" s="21">
         <v>0.03</v>
       </c>
+      <c r="J18" s="17">
+        <v>0.67</v>
+      </c>
       <c r="L18" s="17">
         <v>0.48</v>
       </c>
@@ -2992,6 +3004,9 @@
       </c>
       <c r="I27" s="21">
         <v>0.37</v>
+      </c>
+      <c r="J27" s="17">
+        <v>0.46</v>
       </c>
       <c r="L27" s="17">
         <v>0.8</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E17031-7C25-A84F-825F-EEA83E7EEE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F3A235-E69A-BA4C-AE66-FBDB2C0D5423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2342,6 +2342,9 @@
       <c r="I5" s="21">
         <v>0.16</v>
       </c>
+      <c r="J5" s="17">
+        <v>0.21</v>
+      </c>
       <c r="L5" s="17">
         <v>0.48</v>
       </c>
@@ -2435,6 +2438,9 @@
       <c r="I8" s="21">
         <v>0.21</v>
       </c>
+      <c r="J8" s="17">
+        <v>0.11</v>
+      </c>
       <c r="L8" s="17">
         <v>0.8</v>
       </c>
@@ -2525,6 +2531,9 @@
       <c r="I11" s="21">
         <v>0.31</v>
       </c>
+      <c r="J11" s="17">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="L11" s="17">
         <v>0.48</v>
       </c>
@@ -2795,6 +2804,9 @@
       <c r="I20" s="21">
         <v>0</v>
       </c>
+      <c r="J20" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L20" s="17">
         <v>0.48</v>
       </c>
@@ -2975,6 +2987,9 @@
       <c r="I26" s="21">
         <v>0.46</v>
       </c>
+      <c r="J26" s="17">
+        <v>0.46</v>
+      </c>
       <c r="L26" s="17">
         <v>0.48</v>
       </c>
@@ -3067,6 +3082,9 @@
       </c>
       <c r="I29" s="21">
         <v>0.63</v>
+      </c>
+      <c r="J29" s="17">
+        <v>0.7</v>
       </c>
       <c r="L29" s="17">
         <v>0.8</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F3A235-E69A-BA4C-AE66-FBDB2C0D5423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A168C93-54E4-4944-9081-C0DD8DC8F1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2246,6 +2246,9 @@
       <c r="I2" s="21">
         <v>0.76</v>
       </c>
+      <c r="J2" s="17">
+        <v>0.78</v>
+      </c>
       <c r="L2" s="17">
         <v>0.48</v>
       </c>
@@ -2471,6 +2474,9 @@
       <c r="I9" s="21">
         <v>0.18</v>
       </c>
+      <c r="J9" s="17">
+        <v>0.33</v>
+      </c>
       <c r="L9" s="17">
         <v>0.68</v>
       </c>
@@ -2501,6 +2507,9 @@
       <c r="I10" s="21">
         <v>0.48</v>
       </c>
+      <c r="J10" s="17">
+        <v>0.71</v>
+      </c>
       <c r="L10" s="17">
         <v>0.48</v>
       </c>
@@ -2624,6 +2633,9 @@
       <c r="I14" s="21">
         <v>0.22</v>
       </c>
+      <c r="J14" s="17">
+        <v>0.38</v>
+      </c>
       <c r="L14" s="17">
         <v>0.48</v>
       </c>
@@ -2654,6 +2666,9 @@
       <c r="I15" s="21">
         <v>0.51</v>
       </c>
+      <c r="J15" s="17">
+        <v>0.51</v>
+      </c>
       <c r="L15" s="17">
         <v>0.68</v>
       </c>
@@ -2867,6 +2882,9 @@
       <c r="I22" s="21">
         <v>0.16</v>
       </c>
+      <c r="J22" s="17">
+        <v>0.7</v>
+      </c>
       <c r="L22" s="17">
         <v>0.68</v>
       </c>
@@ -2926,6 +2944,9 @@
       </c>
       <c r="I24" s="21">
         <v>0.1</v>
+      </c>
+      <c r="J24" s="17">
+        <v>0.78</v>
       </c>
       <c r="L24" s="17">
         <v>0.48</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A168C93-54E4-4944-9081-C0DD8DC8F1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05B062E-332E-B841-96CA-358BDDF2C2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1693,7 +1693,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1732,13 +1732,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2792,6 +2785,9 @@
       <c r="I19" s="20">
         <v>0</v>
       </c>
+      <c r="J19" s="17">
+        <v>0</v>
+      </c>
       <c r="P19" s="15"/>
     </row>
     <row r="20" spans="1:16">
@@ -3074,6 +3070,9 @@
       <c r="I28" s="21">
         <v>0.34</v>
       </c>
+      <c r="J28" s="17">
+        <v>0.52</v>
+      </c>
       <c r="L28" s="17">
         <v>0.48</v>
       </c>
@@ -3137,6 +3136,9 @@
       <c r="I30" s="21">
         <v>0</v>
       </c>
+      <c r="J30" s="17">
+        <v>0</v>
+      </c>
       <c r="L30" s="17">
         <v>0.48</v>
       </c>
@@ -3728,10 +3730,10 @@
       <c r="P48" s="4"/>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="9" t="s">
         <v>92</v>
       </c>
       <c r="C49" s="19" t="s">
@@ -3755,10 +3757,10 @@
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C50" s="19" t="s">
@@ -3785,10 +3787,10 @@
       <c r="P50" s="4"/>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="19" t="s">
@@ -3815,10 +3817,10 @@
       <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="19" t="s">
@@ -3845,10 +3847,10 @@
       <c r="P52" s="4"/>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="9" t="s">
         <v>101</v>
       </c>
       <c r="C53" s="19" t="s">
@@ -3875,10 +3877,10 @@
       <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="25" t="s">
+      <c r="B54" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -3905,10 +3907,10 @@
       <c r="P54" s="4"/>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="25" t="s">
+      <c r="B55" s="9" t="s">
         <v>476</v>
       </c>
       <c r="C55" s="19" t="s">
@@ -4937,10 +4939,10 @@
       <c r="P89" s="4"/>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="25" t="s">
+      <c r="A90" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B90" s="25" t="s">
+      <c r="B90" s="9" t="s">
         <v>172</v>
       </c>
       <c r="C90" s="19" t="s">
@@ -4964,10 +4966,10 @@
       <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="25" t="s">
+      <c r="A91" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B91" s="25" t="s">
+      <c r="B91" s="9" t="s">
         <v>175</v>
       </c>
       <c r="C91" s="19" t="s">
@@ -4991,10 +4993,10 @@
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" s="22" t="s">
+      <c r="A92" t="s">
         <v>474</v>
       </c>
-      <c r="B92" s="23" t="s">
+      <c r="B92" s="2" t="s">
         <v>475</v>
       </c>
       <c r="C92" s="17" t="s">
@@ -5018,10 +5020,10 @@
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="25" t="s">
+      <c r="A93" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B93" s="25" t="s">
+      <c r="B93" s="9" t="s">
         <v>177</v>
       </c>
       <c r="C93" s="19" t="s">
@@ -5045,10 +5047,10 @@
       <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="25" t="s">
+      <c r="A94" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B94" s="25" t="s">
+      <c r="B94" s="9" t="s">
         <v>179</v>
       </c>
       <c r="C94" s="19" t="s">
@@ -5072,10 +5074,10 @@
       <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="25" t="s">
+      <c r="A95" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B95" s="25" t="s">
+      <c r="B95" s="9" t="s">
         <v>181</v>
       </c>
       <c r="C95" s="19" t="s">
@@ -5099,10 +5101,10 @@
       <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="25" t="s">
+      <c r="A96" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B96" s="25" t="s">
+      <c r="B96" s="9" t="s">
         <v>183</v>
       </c>
       <c r="C96" s="19" t="s">
@@ -5126,10 +5128,10 @@
       <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="25" t="s">
+      <c r="A97" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B97" s="25" t="s">
+      <c r="B97" s="9" t="s">
         <v>185</v>
       </c>
       <c r="C97" s="19" t="s">
@@ -6120,10 +6122,10 @@
       <c r="P133" s="4"/>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="25" t="s">
+      <c r="A134" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="B134" s="25" t="s">
+      <c r="B134" s="9" t="s">
         <v>251</v>
       </c>
       <c r="C134" s="19" t="s">
@@ -6147,10 +6149,10 @@
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" s="25" t="s">
+      <c r="A135" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="B135" s="25" t="s">
+      <c r="B135" s="9" t="s">
         <v>254</v>
       </c>
       <c r="C135" s="19" t="s">
@@ -6174,10 +6176,10 @@
       <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="25" t="s">
+      <c r="A136" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="B136" s="25" t="s">
+      <c r="B136" s="9" t="s">
         <v>256</v>
       </c>
       <c r="C136" s="19" t="s">
@@ -6201,10 +6203,10 @@
       <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="25" t="s">
+      <c r="A137" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="B137" s="25" t="s">
+      <c r="B137" s="9" t="s">
         <v>258</v>
       </c>
       <c r="C137" s="19" t="s">
@@ -6228,10 +6230,10 @@
       <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="25" t="s">
+      <c r="A138" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="B138" s="25" t="s">
+      <c r="B138" s="9" t="s">
         <v>260</v>
       </c>
       <c r="C138" s="19" t="s">
@@ -6255,10 +6257,10 @@
       <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="25" t="s">
+      <c r="A139" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="B139" s="25" t="s">
+      <c r="B139" s="9" t="s">
         <v>262</v>
       </c>
       <c r="C139" s="19" t="s">
@@ -6282,10 +6284,10 @@
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" s="25" t="s">
+      <c r="A140" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="B140" s="25" t="s">
+      <c r="B140" s="9" t="s">
         <v>264</v>
       </c>
       <c r="C140" s="19" t="s">
@@ -6309,10 +6311,10 @@
       <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="25" t="s">
+      <c r="A141" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B141" s="25" t="s">
+      <c r="B141" s="9" t="s">
         <v>266</v>
       </c>
       <c r="C141" s="19" t="s">
@@ -6336,10 +6338,10 @@
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="25" t="s">
+      <c r="A142" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="B142" s="25" t="s">
+      <c r="B142" s="9" t="s">
         <v>268</v>
       </c>
       <c r="C142" s="19" t="s">
@@ -6363,10 +6365,10 @@
       <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="25" t="s">
+      <c r="A143" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="B143" s="25" t="s">
+      <c r="B143" s="9" t="s">
         <v>270</v>
       </c>
       <c r="C143" s="19" t="s">
@@ -7470,10 +7472,10 @@
       <c r="P183" s="4"/>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" s="25" t="s">
+      <c r="A184" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="B184" s="25" t="s">
+      <c r="B184" s="9" t="s">
         <v>347</v>
       </c>
       <c r="C184" s="19" t="s">
@@ -7500,10 +7502,10 @@
       <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
-      <c r="A185" s="22" t="s">
+      <c r="A185" t="s">
         <v>446</v>
       </c>
-      <c r="B185" s="26" t="s">
+      <c r="B185" s="3" t="s">
         <v>447</v>
       </c>
       <c r="C185" s="17" t="s">
@@ -7530,10 +7532,10 @@
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" s="25" t="s">
+      <c r="A186" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="B186" s="25" t="s">
+      <c r="B186" s="9" t="s">
         <v>350</v>
       </c>
       <c r="C186" s="19" t="s">
@@ -7560,10 +7562,10 @@
       <c r="P186" s="4"/>
     </row>
     <row r="187" spans="1:16">
-      <c r="A187" s="22" t="s">
+      <c r="A187" t="s">
         <v>501</v>
       </c>
-      <c r="B187" s="23" t="s">
+      <c r="B187" s="2" t="s">
         <v>502</v>
       </c>
       <c r="C187" s="17" t="s">
@@ -8577,10 +8579,10 @@
       <c r="P220" s="4"/>
     </row>
     <row r="221" spans="1:16">
-      <c r="A221" s="25" t="s">
+      <c r="A221" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="B221" s="25" t="s">
+      <c r="B221" s="9" t="s">
         <v>406</v>
       </c>
       <c r="C221" s="19" t="s">
@@ -8607,10 +8609,10 @@
       <c r="P221" s="4"/>
     </row>
     <row r="222" spans="1:16">
-      <c r="A222" s="22" t="s">
+      <c r="A222" t="s">
         <v>503</v>
       </c>
-      <c r="B222" s="23" t="s">
+      <c r="B222" s="2" t="s">
         <v>504</v>
       </c>
       <c r="C222" s="17" t="s">
@@ -8784,7 +8786,7 @@
       <c r="J227" s="17">
         <v>0.6</v>
       </c>
-      <c r="P227" s="24"/>
+      <c r="P227" s="16"/>
     </row>
     <row r="228" spans="1:16">
       <c r="A228" s="9" t="s">
@@ -8814,13 +8816,13 @@
       <c r="J228" s="17">
         <v>0.33</v>
       </c>
-      <c r="P228" s="24"/>
+      <c r="P228" s="16"/>
     </row>
     <row r="229" spans="1:16">
-      <c r="A229" s="22" t="s">
+      <c r="A229" t="s">
         <v>460</v>
       </c>
-      <c r="B229" s="23" t="s">
+      <c r="B229" s="2" t="s">
         <v>461</v>
       </c>
       <c r="C229" s="17" t="s">
@@ -8841,13 +8843,12 @@
       <c r="I229" s="20">
         <v>0.6</v>
       </c>
-      <c r="P229" s="22"/>
     </row>
     <row r="230" spans="1:16">
-      <c r="A230" s="25" t="s">
+      <c r="A230" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="B230" s="25" t="s">
+      <c r="B230" s="9" t="s">
         <v>419</v>
       </c>
       <c r="C230" s="19" t="s">
@@ -8868,13 +8869,13 @@
       <c r="I230" s="20">
         <v>0.19</v>
       </c>
-      <c r="P230" s="24"/>
+      <c r="P230" s="16"/>
     </row>
     <row r="231" spans="1:16">
-      <c r="A231" s="22" t="s">
+      <c r="A231" t="s">
         <v>497</v>
       </c>
-      <c r="B231" s="23" t="s">
+      <c r="B231" s="2" t="s">
         <v>498</v>
       </c>
       <c r="C231" s="17" t="s">
@@ -8890,13 +8891,12 @@
       <c r="I231" s="20">
         <v>0.08</v>
       </c>
-      <c r="P231" s="22"/>
     </row>
     <row r="232" spans="1:16">
-      <c r="A232" s="25" t="s">
+      <c r="A232" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="B232" s="25" t="s">
+      <c r="B232" s="9" t="s">
         <v>422</v>
       </c>
       <c r="C232" s="19" t="s">
@@ -8917,7 +8917,7 @@
       <c r="I232" s="20">
         <v>0.87</v>
       </c>
-      <c r="P232" s="24"/>
+      <c r="P232" s="16"/>
     </row>
     <row r="233" spans="1:16">
       <c r="A233" s="9" t="s">
@@ -8944,7 +8944,7 @@
       <c r="I233" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P233" s="24"/>
+      <c r="P233" s="16"/>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" t="s">
@@ -8971,7 +8971,6 @@
       <c r="I234" s="20">
         <v>0.18</v>
       </c>
-      <c r="P234" s="22"/>
     </row>
     <row r="235" spans="1:16">
       <c r="A235" t="s">
@@ -8998,7 +8997,6 @@
       <c r="I235" s="20">
         <v>0.21</v>
       </c>
-      <c r="P235" s="22"/>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="9" t="s">
@@ -9025,7 +9023,7 @@
       <c r="I236" s="20">
         <v>0.72</v>
       </c>
-      <c r="P236" s="24"/>
+      <c r="P236" s="16"/>
     </row>
     <row r="237" spans="1:16">
       <c r="A237" s="9" t="s">
@@ -9052,7 +9050,7 @@
       <c r="I237" s="20">
         <v>0.43</v>
       </c>
-      <c r="P237" s="24"/>
+      <c r="P237" s="16"/>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" s="9" t="s">
@@ -9079,7 +9077,7 @@
       <c r="I238" s="20">
         <v>0.66</v>
       </c>
-      <c r="P238" s="24"/>
+      <c r="P238" s="16"/>
     </row>
     <row r="239" spans="1:16">
       <c r="A239" s="9" t="s">
@@ -9106,7 +9104,7 @@
       <c r="I239" s="20">
         <v>0.25</v>
       </c>
-      <c r="P239" s="24"/>
+      <c r="P239" s="16"/>
     </row>
     <row r="240" spans="1:16">
       <c r="A240" s="9" t="s">
@@ -9133,7 +9131,7 @@
       <c r="I240" s="20">
         <v>0.66</v>
       </c>
-      <c r="P240" s="24"/>
+      <c r="P240" s="16"/>
     </row>
     <row r="241" spans="1:16">
       <c r="A241" s="9" t="s">
@@ -9160,7 +9158,7 @@
       <c r="I241" s="20">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P241" s="24"/>
+      <c r="P241" s="16"/>
     </row>
     <row r="242" spans="1:16">
       <c r="A242" t="s">
@@ -9187,7 +9185,6 @@
       <c r="I242" s="20">
         <v>0.72</v>
       </c>
-      <c r="P242" s="22"/>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" t="s">
@@ -9214,7 +9211,6 @@
       <c r="I243" s="20">
         <v>0</v>
       </c>
-      <c r="P243" s="22"/>
     </row>
     <row r="244" spans="1:16">
       <c r="A244" t="s">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05B062E-332E-B841-96CA-358BDDF2C2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12629FEA-D479-6148-93DE-72E8E9F7F449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4963,6 +4963,9 @@
       <c r="I90" s="20">
         <v>0.55000000000000004</v>
       </c>
+      <c r="J90" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
@@ -4990,6 +4993,9 @@
       <c r="I91" s="20">
         <v>0.76</v>
       </c>
+      <c r="J91" s="17">
+        <v>0.54</v>
+      </c>
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
@@ -5017,6 +5023,9 @@
       <c r="I92" s="20">
         <v>0.06</v>
       </c>
+      <c r="J92" s="17">
+        <v>0.13</v>
+      </c>
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
@@ -5044,6 +5053,9 @@
       <c r="I93" s="20">
         <v>0.67</v>
       </c>
+      <c r="J93" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
@@ -5071,6 +5083,9 @@
       <c r="I94" s="20">
         <v>0.84</v>
       </c>
+      <c r="J94" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
@@ -5098,6 +5113,9 @@
       <c r="I95" s="20">
         <v>0.31</v>
       </c>
+      <c r="J95" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
@@ -5125,6 +5143,9 @@
       <c r="I96" s="20">
         <v>0.57999999999999996</v>
       </c>
+      <c r="J96" s="17">
+        <v>0.78</v>
+      </c>
       <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
@@ -5201,6 +5222,9 @@
       <c r="I99" s="20">
         <v>0.84</v>
       </c>
+      <c r="J99" s="17">
+        <v>0.63</v>
+      </c>
       <c r="P99" s="4"/>
     </row>
     <row r="100" spans="1:16">
@@ -5228,6 +5252,9 @@
       <c r="I100" s="20">
         <v>0.76</v>
       </c>
+      <c r="J100" s="17">
+        <v>0.4</v>
+      </c>
       <c r="P100" s="4"/>
     </row>
     <row r="101" spans="1:16">
@@ -5255,6 +5282,9 @@
       <c r="I101" s="20">
         <v>0.48</v>
       </c>
+      <c r="J101" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P101" s="4"/>
     </row>
     <row r="102" spans="1:16">
@@ -5282,6 +5312,9 @@
       <c r="I102" s="20">
         <v>0.37</v>
       </c>
+      <c r="J102" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P102" s="4"/>
     </row>
     <row r="103" spans="1:16">
@@ -5309,6 +5342,9 @@
       <c r="I103" s="20">
         <v>0.69</v>
       </c>
+      <c r="J103" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P103" s="4"/>
     </row>
     <row r="104" spans="1:16">
@@ -5336,6 +5372,9 @@
       <c r="I104" s="20">
         <v>0.27</v>
       </c>
+      <c r="J104" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P104" s="4"/>
     </row>
     <row r="105" spans="1:16">
@@ -5363,6 +5402,9 @@
       <c r="I105" s="20">
         <v>0.3</v>
       </c>
+      <c r="J105" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P105" s="4"/>
     </row>
     <row r="106" spans="1:16">
@@ -5390,6 +5432,9 @@
       <c r="I106" s="20">
         <v>0.45</v>
       </c>
+      <c r="J106" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P106" s="15"/>
     </row>
     <row r="107" spans="1:16">
@@ -5417,6 +5462,9 @@
       <c r="I107" s="20">
         <v>0.37</v>
       </c>
+      <c r="J107" s="17">
+        <v>0.3</v>
+      </c>
       <c r="P107" s="4"/>
     </row>
     <row r="108" spans="1:16">
@@ -5444,6 +5492,9 @@
       <c r="I108" s="20">
         <v>0.1</v>
       </c>
+      <c r="J108" s="17">
+        <v>0.32</v>
+      </c>
       <c r="P108" s="4"/>
     </row>
     <row r="109" spans="1:16">
@@ -5471,6 +5522,9 @@
       <c r="I109" s="20">
         <v>0.31</v>
       </c>
+      <c r="J109" s="17">
+        <v>0.35</v>
+      </c>
       <c r="P109" s="4"/>
     </row>
     <row r="110" spans="1:16">
@@ -5498,6 +5552,9 @@
       <c r="I110" s="20">
         <v>0.66</v>
       </c>
+      <c r="J110" s="17">
+        <v>0.7</v>
+      </c>
       <c r="P110" s="4"/>
     </row>
     <row r="111" spans="1:16">
@@ -5525,6 +5582,9 @@
       <c r="I111" s="20">
         <v>0.66</v>
       </c>
+      <c r="J111" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P111" s="4"/>
     </row>
     <row r="112" spans="1:16">
@@ -5552,6 +5612,9 @@
       <c r="I112" s="20">
         <v>0.67</v>
       </c>
+      <c r="J112" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P112" s="4"/>
     </row>
     <row r="113" spans="1:16">
@@ -5579,6 +5642,9 @@
       <c r="I113" s="20">
         <v>0.46</v>
       </c>
+      <c r="J113" s="17">
+        <v>0.32</v>
+      </c>
       <c r="P113" s="4"/>
     </row>
     <row r="114" spans="1:16">
@@ -5606,6 +5672,9 @@
       <c r="I114" s="20">
         <v>0.43</v>
       </c>
+      <c r="J114" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P114" s="4"/>
     </row>
     <row r="115" spans="1:16">
@@ -5633,6 +5702,9 @@
       <c r="I115" s="20">
         <v>0.63</v>
       </c>
+      <c r="J115" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P115" s="4"/>
     </row>
     <row r="116" spans="1:16">
@@ -5660,6 +5732,9 @@
       <c r="I116" s="20">
         <v>0.4</v>
       </c>
+      <c r="J116" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P116" s="4"/>
     </row>
     <row r="117" spans="1:16">
@@ -5687,6 +5762,9 @@
       <c r="I117" s="20">
         <v>0.48</v>
       </c>
+      <c r="J117" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P117" s="4"/>
     </row>
     <row r="118" spans="1:16">
@@ -5714,6 +5792,9 @@
       <c r="I118" s="20">
         <v>0.84</v>
       </c>
+      <c r="J118" s="17">
+        <v>0.7</v>
+      </c>
       <c r="P118" s="4"/>
     </row>
     <row r="119" spans="1:16">
@@ -5741,6 +5822,9 @@
       <c r="I119" s="20">
         <v>0.51</v>
       </c>
+      <c r="J119" s="17">
+        <v>0.6</v>
+      </c>
       <c r="P119" s="4"/>
     </row>
     <row r="120" spans="1:16">
@@ -5768,6 +5852,9 @@
       <c r="I120" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
+      <c r="J120" s="17">
+        <v>0.02</v>
+      </c>
       <c r="P120" s="15"/>
     </row>
     <row r="121" spans="1:16">
@@ -5795,6 +5882,9 @@
       <c r="I121" s="20">
         <v>0.52</v>
       </c>
+      <c r="J121" s="17">
+        <v>0.63</v>
+      </c>
       <c r="P121" s="4"/>
     </row>
     <row r="122" spans="1:16">
@@ -5822,6 +5912,9 @@
       <c r="I122" s="20">
         <v>0.75</v>
       </c>
+      <c r="J122" s="17">
+        <v>0.67</v>
+      </c>
       <c r="P122" s="4"/>
     </row>
     <row r="123" spans="1:16">
@@ -5849,6 +5942,9 @@
       <c r="I123" s="20">
         <v>0.69</v>
       </c>
+      <c r="J123" s="17">
+        <v>0.24</v>
+      </c>
       <c r="P123" s="4"/>
     </row>
     <row r="124" spans="1:16">
@@ -5876,6 +5972,9 @@
       <c r="I124" s="20">
         <v>0.42</v>
       </c>
+      <c r="J124" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P124" s="4"/>
     </row>
     <row r="125" spans="1:16">
@@ -5903,6 +6002,9 @@
       <c r="I125" s="20">
         <v>0.18</v>
       </c>
+      <c r="J125" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P125" s="4"/>
     </row>
     <row r="126" spans="1:16">
@@ -5930,6 +6032,9 @@
       <c r="I126" s="20">
         <v>0.78</v>
       </c>
+      <c r="J126" s="17">
+        <v>0.78</v>
+      </c>
       <c r="P126" s="4"/>
     </row>
     <row r="127" spans="1:16">
@@ -5957,6 +6062,9 @@
       <c r="I127" s="20">
         <v>0.36</v>
       </c>
+      <c r="J127" s="17">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="P127" s="4"/>
     </row>
     <row r="128" spans="1:16">
@@ -5984,6 +6092,9 @@
       <c r="I128" s="20">
         <v>0.24</v>
       </c>
+      <c r="J128" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P128" s="4"/>
     </row>
     <row r="129" spans="1:16">
@@ -6011,6 +6122,9 @@
       <c r="I129" s="20">
         <v>0.13</v>
       </c>
+      <c r="J129" s="17">
+        <v>0.32</v>
+      </c>
       <c r="P129" s="4"/>
     </row>
     <row r="130" spans="1:16">
@@ -6038,6 +6152,9 @@
       <c r="I130" s="20">
         <v>0.82</v>
       </c>
+      <c r="J130" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P130" s="4"/>
     </row>
     <row r="131" spans="1:16">
@@ -6065,6 +6182,9 @@
       <c r="I131" s="20">
         <v>0.64</v>
       </c>
+      <c r="J131" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P131" s="4"/>
     </row>
     <row r="132" spans="1:16">
@@ -6092,6 +6212,9 @@
       <c r="I132" s="20">
         <v>0.39</v>
       </c>
+      <c r="J132" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P132" s="4"/>
     </row>
     <row r="133" spans="1:16">
@@ -6119,6 +6242,9 @@
       <c r="I133" s="20">
         <v>0.42</v>
       </c>
+      <c r="J133" s="17">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="P133" s="4"/>
     </row>
     <row r="134" spans="1:16">
@@ -6551,6 +6677,9 @@
       <c r="I149" s="20">
         <v>0.66</v>
       </c>
+      <c r="J149" s="17">
+        <v>0.35</v>
+      </c>
       <c r="P149" s="4"/>
     </row>
     <row r="150" spans="1:16">
@@ -6712,6 +6841,9 @@
       </c>
       <c r="I155" s="20">
         <v>0.25</v>
+      </c>
+      <c r="J155" s="17">
+        <v>0.56999999999999995</v>
       </c>
       <c r="P155" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12629FEA-D479-6148-93DE-72E8E9F7F449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD44D079-908C-9C43-A648-8F45B8662AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3754,6 +3754,9 @@
       <c r="I49" s="21">
         <v>0.79</v>
       </c>
+      <c r="J49" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
@@ -3781,6 +3784,9 @@
       <c r="I50" s="21">
         <v>0.56999999999999995</v>
       </c>
+      <c r="J50" s="17">
+        <v>0.27</v>
+      </c>
       <c r="L50" s="17">
         <v>0.63</v>
       </c>
@@ -3811,6 +3817,9 @@
       <c r="I51" s="21">
         <v>0.46</v>
       </c>
+      <c r="J51" s="17">
+        <v>0.71</v>
+      </c>
       <c r="L51" s="17">
         <v>0.92</v>
       </c>
@@ -3841,6 +3850,9 @@
       <c r="I52" s="21">
         <v>0.51</v>
       </c>
+      <c r="J52" s="17">
+        <v>0.79</v>
+      </c>
       <c r="L52" s="17">
         <v>0.83</v>
       </c>
@@ -3871,6 +3883,9 @@
       <c r="I53" s="21">
         <v>0.51</v>
       </c>
+      <c r="J53" s="17">
+        <v>0.6</v>
+      </c>
       <c r="L53" s="17">
         <v>0.79</v>
       </c>
@@ -3901,6 +3916,9 @@
       <c r="I54" s="21">
         <v>0.4</v>
       </c>
+      <c r="J54" s="17">
+        <v>0.4</v>
+      </c>
       <c r="L54" s="17">
         <v>0.55000000000000004</v>
       </c>
@@ -3931,6 +3949,9 @@
       <c r="I55" s="21">
         <v>0.52</v>
       </c>
+      <c r="J55" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="L55" s="17">
         <v>0.83</v>
       </c>
@@ -3961,6 +3982,9 @@
       <c r="I56" s="20">
         <v>0.64</v>
       </c>
+      <c r="J56" s="17">
+        <v>0.59</v>
+      </c>
       <c r="L56" s="17">
         <v>0.92</v>
       </c>
@@ -3991,6 +4015,9 @@
       <c r="I57" s="20">
         <v>0.25</v>
       </c>
+      <c r="J57" s="17">
+        <v>0.32</v>
+      </c>
       <c r="L57" s="17">
         <v>0.37</v>
       </c>
@@ -4021,6 +4048,9 @@
       <c r="I58" s="20">
         <v>0.34</v>
       </c>
+      <c r="J58" s="17">
+        <v>0.37</v>
+      </c>
       <c r="P58" s="4"/>
     </row>
     <row r="59" spans="1:16">
@@ -4048,6 +4078,9 @@
       <c r="I59" s="20">
         <v>0.66</v>
       </c>
+      <c r="J59" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L59" s="17">
         <v>0.92</v>
       </c>
@@ -4078,6 +4111,9 @@
       <c r="I60" s="20">
         <v>0.39</v>
       </c>
+      <c r="J60" s="17">
+        <v>0.63</v>
+      </c>
       <c r="L60" s="17">
         <v>0.83</v>
       </c>
@@ -4108,6 +4144,9 @@
       <c r="I61" s="20">
         <v>0.45</v>
       </c>
+      <c r="J61" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="L61" s="17">
         <v>0.55000000000000004</v>
       </c>
@@ -4138,6 +4177,9 @@
       <c r="I62" s="20">
         <v>0.49</v>
       </c>
+      <c r="J62" s="17">
+        <v>0.51</v>
+      </c>
       <c r="L62" s="17">
         <v>0.83</v>
       </c>
@@ -4168,6 +4210,9 @@
       <c r="I63" s="20">
         <v>0.61</v>
       </c>
+      <c r="J63" s="17">
+        <v>0.68</v>
+      </c>
       <c r="L63" s="17">
         <v>0.63</v>
       </c>
@@ -4198,6 +4243,9 @@
       <c r="I64" s="20">
         <v>0.15</v>
       </c>
+      <c r="J64" s="17">
+        <v>0.37</v>
+      </c>
       <c r="L64" s="17">
         <v>0.37</v>
       </c>
@@ -4228,6 +4276,9 @@
       <c r="I65" s="20">
         <v>0.67</v>
       </c>
+      <c r="J65" s="17">
+        <v>0.7</v>
+      </c>
       <c r="L65" s="17">
         <v>0.79</v>
       </c>
@@ -4258,6 +4309,9 @@
       <c r="I66" s="20">
         <v>0.25</v>
       </c>
+      <c r="J66" s="17">
+        <v>0.63</v>
+      </c>
       <c r="L66" s="17">
         <v>0.55000000000000004</v>
       </c>
@@ -4288,6 +4342,9 @@
       <c r="I67" s="20">
         <v>0.7</v>
       </c>
+      <c r="J67" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L67" s="17">
         <v>0.83</v>
       </c>
@@ -4318,6 +4375,9 @@
       <c r="I68" s="20">
         <v>0.39</v>
       </c>
+      <c r="J68" s="17">
+        <v>0.59</v>
+      </c>
       <c r="L68" s="17">
         <v>0.79</v>
       </c>
@@ -4348,6 +4408,9 @@
       <c r="I69" s="20">
         <v>0.6</v>
       </c>
+      <c r="J69" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="L69" s="17">
         <v>0.92</v>
       </c>
@@ -4378,6 +4441,9 @@
       <c r="I70" s="20">
         <v>0.24</v>
       </c>
+      <c r="J70" s="17">
+        <v>0.52</v>
+      </c>
       <c r="L70" s="17">
         <v>0.55000000000000004</v>
       </c>
@@ -4408,6 +4474,9 @@
       <c r="I71" s="20">
         <v>0.45</v>
       </c>
+      <c r="J71" s="17">
+        <v>0.38</v>
+      </c>
       <c r="L71" s="17">
         <v>0.37</v>
       </c>
@@ -4438,6 +4507,9 @@
       <c r="I72" s="20">
         <v>0.36</v>
       </c>
+      <c r="J72" s="17">
+        <v>0.63</v>
+      </c>
       <c r="L72" s="17">
         <v>0.79</v>
       </c>
@@ -4468,6 +4540,9 @@
       <c r="I73" s="20">
         <v>0.66</v>
       </c>
+      <c r="J73" s="17">
+        <v>0.79</v>
+      </c>
       <c r="L73" s="17">
         <v>0.83</v>
       </c>
@@ -4498,6 +4573,9 @@
       <c r="I74" s="20">
         <v>0.34</v>
       </c>
+      <c r="J74" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P74" s="4"/>
     </row>
     <row r="75" spans="1:16">
@@ -4525,6 +4603,9 @@
       <c r="I75" s="20">
         <v>0.18</v>
       </c>
+      <c r="J75" s="17">
+        <v>0.17</v>
+      </c>
       <c r="P75" s="4"/>
     </row>
     <row r="76" spans="1:16">
@@ -4552,6 +4633,9 @@
       <c r="I76" s="20">
         <v>0.63</v>
       </c>
+      <c r="J76" s="17">
+        <v>0.7</v>
+      </c>
       <c r="L76" s="17">
         <v>0.55000000000000004</v>
       </c>
@@ -4582,6 +4666,9 @@
       <c r="I77" s="20">
         <v>0.84</v>
       </c>
+      <c r="J77" s="17">
+        <v>0.68</v>
+      </c>
       <c r="L77" s="17">
         <v>0.92</v>
       </c>
@@ -4612,6 +4699,9 @@
       <c r="I78" s="20">
         <v>0.18</v>
       </c>
+      <c r="J78" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P78" s="4"/>
     </row>
     <row r="79" spans="1:16">
@@ -4639,6 +4729,9 @@
       <c r="I79" s="20">
         <v>0.63</v>
       </c>
+      <c r="J79" s="17">
+        <v>0.63</v>
+      </c>
       <c r="L79" s="17">
         <v>0.92</v>
       </c>
@@ -4669,6 +4762,9 @@
       <c r="I80" s="20">
         <v>0.46</v>
       </c>
+      <c r="J80" s="17">
+        <v>0.51</v>
+      </c>
       <c r="L80" s="17">
         <v>0.63</v>
       </c>
@@ -4699,6 +4795,9 @@
       <c r="I81" s="20">
         <v>0.72</v>
       </c>
+      <c r="J81" s="17">
+        <v>0.78</v>
+      </c>
       <c r="L81" s="17">
         <v>0.37</v>
       </c>
@@ -4729,6 +4828,9 @@
       <c r="I82" s="20">
         <v>0.36</v>
       </c>
+      <c r="J82" s="17">
+        <v>0.48</v>
+      </c>
       <c r="L82" s="17">
         <v>0.37</v>
       </c>
@@ -4759,6 +4861,9 @@
       <c r="I83" s="20">
         <v>0.46</v>
       </c>
+      <c r="J83" s="17">
+        <v>0.84</v>
+      </c>
       <c r="L83" s="17">
         <v>0.63</v>
       </c>
@@ -4789,6 +4894,9 @@
       <c r="I84" s="20">
         <v>0.6</v>
       </c>
+      <c r="J84" s="17">
+        <v>0.68</v>
+      </c>
       <c r="L84" s="17">
         <v>0.79</v>
       </c>
@@ -4819,6 +4927,9 @@
       <c r="I85" s="20">
         <v>0.33</v>
       </c>
+      <c r="J85" s="17">
+        <v>0.49</v>
+      </c>
       <c r="L85" s="17">
         <v>0.63</v>
       </c>
@@ -4849,6 +4960,9 @@
       <c r="I86" s="20">
         <v>0.28000000000000003</v>
       </c>
+      <c r="J86" s="17">
+        <v>0.43</v>
+      </c>
       <c r="L86" s="17">
         <v>0.55000000000000004</v>
       </c>
@@ -4879,6 +4993,9 @@
       <c r="I87" s="20">
         <v>0.18</v>
       </c>
+      <c r="J87" s="17">
+        <v>0.25</v>
+      </c>
       <c r="P87" s="4"/>
     </row>
     <row r="88" spans="1:16">
@@ -4906,6 +5023,9 @@
       <c r="I88" s="20">
         <v>0.39</v>
       </c>
+      <c r="J88" s="17">
+        <v>0.37</v>
+      </c>
       <c r="L88" s="17">
         <v>0.79</v>
       </c>
@@ -4935,6 +5055,9 @@
       </c>
       <c r="I89" s="20">
         <v>0.34</v>
+      </c>
+      <c r="J89" s="17">
+        <v>0.46</v>
       </c>
       <c r="P89" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD44D079-908C-9C43-A648-8F45B8662AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2065488E-37BD-7641-BA2C-16E303568B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6422,6 +6422,9 @@
       <c r="I135" s="20">
         <v>0.61</v>
       </c>
+      <c r="J135" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
@@ -6476,6 +6479,9 @@
       <c r="I137" s="20">
         <v>0.27</v>
       </c>
+      <c r="J137" s="17">
+        <v>0.67</v>
+      </c>
       <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
@@ -6503,6 +6509,9 @@
       <c r="I138" s="20">
         <v>0.22</v>
       </c>
+      <c r="J138" s="17">
+        <v>0.46</v>
+      </c>
       <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
@@ -6611,6 +6620,9 @@
       <c r="I142" s="20">
         <v>0.79</v>
       </c>
+      <c r="J142" s="17">
+        <v>0.63</v>
+      </c>
       <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
@@ -6665,6 +6677,9 @@
       <c r="I144" s="20">
         <v>0</v>
       </c>
+      <c r="J144" s="17">
+        <v>0.43</v>
+      </c>
       <c r="P144" s="4"/>
     </row>
     <row r="145" spans="1:16">
@@ -6692,6 +6707,9 @@
       <c r="I145" s="20">
         <v>0.45</v>
       </c>
+      <c r="J145" s="17">
+        <v>0.54</v>
+      </c>
       <c r="P145" s="4"/>
     </row>
     <row r="146" spans="1:16">
@@ -6746,6 +6764,9 @@
       <c r="I147" s="20">
         <v>0.96</v>
       </c>
+      <c r="J147" s="17">
+        <v>0.86</v>
+      </c>
       <c r="P147" s="4"/>
     </row>
     <row r="148" spans="1:16">
@@ -6773,6 +6794,9 @@
       <c r="I148" s="20">
         <v>0.51</v>
       </c>
+      <c r="J148" s="17">
+        <v>0.67</v>
+      </c>
       <c r="P148" s="4"/>
     </row>
     <row r="149" spans="1:16">
@@ -6830,6 +6854,9 @@
       <c r="I150" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
+      <c r="J150" s="17">
+        <v>0.25</v>
+      </c>
       <c r="P150" s="4"/>
     </row>
     <row r="151" spans="1:16">
@@ -7049,6 +7076,9 @@
       <c r="I158" s="20">
         <v>0.31</v>
       </c>
+      <c r="J158" s="17">
+        <v>0.46</v>
+      </c>
       <c r="P158" s="4"/>
     </row>
     <row r="159" spans="1:16">
@@ -7076,6 +7106,9 @@
       <c r="I159" s="20">
         <v>0.18</v>
       </c>
+      <c r="J159" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P159" s="4"/>
     </row>
     <row r="160" spans="1:16">
@@ -7130,6 +7163,9 @@
       <c r="I161" s="20">
         <v>0.52</v>
       </c>
+      <c r="J161" s="17">
+        <v>0.63</v>
+      </c>
       <c r="P161" s="4"/>
     </row>
     <row r="162" spans="1:16">
@@ -7292,6 +7328,9 @@
       <c r="I167" s="20">
         <v>0.45</v>
       </c>
+      <c r="J167" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P167" s="4"/>
     </row>
     <row r="168" spans="1:16">
@@ -7346,6 +7385,9 @@
       <c r="I169" s="20">
         <v>0.57999999999999996</v>
       </c>
+      <c r="J169" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P169" s="4"/>
     </row>
     <row r="170" spans="1:16">
@@ -7400,6 +7442,9 @@
       <c r="I171" s="20">
         <v>0.15</v>
       </c>
+      <c r="J171" s="17">
+        <v>0.3</v>
+      </c>
       <c r="P171" s="4"/>
     </row>
     <row r="172" spans="1:16">
@@ -7427,6 +7472,9 @@
       <c r="I172" s="20">
         <v>0.48</v>
       </c>
+      <c r="J172" s="17">
+        <v>0.35</v>
+      </c>
       <c r="P172" s="4"/>
     </row>
     <row r="173" spans="1:16">
@@ -7481,6 +7529,9 @@
       <c r="I174" s="20">
         <v>0.21</v>
       </c>
+      <c r="J174" s="17">
+        <v>0.05</v>
+      </c>
       <c r="P174" s="4"/>
     </row>
     <row r="175" spans="1:16">
@@ -7643,6 +7694,9 @@
       <c r="I180" s="20">
         <v>0.48</v>
       </c>
+      <c r="J180" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P180" s="4"/>
     </row>
     <row r="181" spans="1:16">
@@ -7697,6 +7751,9 @@
       <c r="I182" s="20">
         <v>0.24</v>
       </c>
+      <c r="J182" s="17">
+        <v>0.43</v>
+      </c>
       <c r="P182" s="4"/>
     </row>
     <row r="183" spans="1:16">
@@ -7723,6 +7780,9 @@
       </c>
       <c r="I183" s="20">
         <v>0.43</v>
+      </c>
+      <c r="J183" s="17">
+        <v>0.4</v>
       </c>
       <c r="P183" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2065488E-37BD-7641-BA2C-16E303568B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2077121-D993-9D42-9FA4-8835A19F456B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2371,6 +2371,9 @@
       <c r="I6" s="21">
         <v>0.25</v>
       </c>
+      <c r="J6" s="17">
+        <v>0.51</v>
+      </c>
       <c r="L6" s="17">
         <v>0.48</v>
       </c>
@@ -2566,6 +2569,9 @@
       <c r="I12" s="21">
         <v>0.33</v>
       </c>
+      <c r="J12" s="17">
+        <v>0.54</v>
+      </c>
       <c r="L12" s="17">
         <v>0.48</v>
       </c>
@@ -2596,6 +2602,9 @@
       <c r="I13" s="21">
         <v>0.3</v>
       </c>
+      <c r="J13" s="17">
+        <v>0.46</v>
+      </c>
       <c r="L13" s="17">
         <v>0.48</v>
       </c>
@@ -2692,6 +2701,9 @@
       <c r="I16" s="21">
         <v>0.16</v>
       </c>
+      <c r="J16" s="17">
+        <v>0.33</v>
+      </c>
       <c r="L16" s="17">
         <v>0.48</v>
       </c>
@@ -2722,6 +2734,9 @@
       <c r="I17" s="21">
         <v>0</v>
       </c>
+      <c r="J17" s="17">
+        <v>0.25</v>
+      </c>
       <c r="L17" s="17">
         <v>0.48</v>
       </c>
@@ -2848,6 +2863,9 @@
       <c r="I21" s="21">
         <v>0.3</v>
       </c>
+      <c r="J21" s="17">
+        <v>0.41</v>
+      </c>
       <c r="L21" s="17">
         <v>0.68</v>
       </c>
@@ -2911,6 +2929,9 @@
       <c r="I23" s="21">
         <v>0.22</v>
       </c>
+      <c r="J23" s="17">
+        <v>0.62</v>
+      </c>
       <c r="L23" s="17">
         <v>0.68</v>
       </c>
@@ -2973,6 +2994,9 @@
       </c>
       <c r="I25" s="21">
         <v>0.37</v>
+      </c>
+      <c r="J25" s="17">
+        <v>0.59</v>
       </c>
       <c r="L25" s="17">
         <v>0.8</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2077121-D993-9D42-9FA4-8835A19F456B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D434DA0-43B4-CA42-ACF3-AF91C179472C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6419,6 +6419,9 @@
       <c r="I134" s="20">
         <v>0.25</v>
       </c>
+      <c r="J134" s="17">
+        <v>0.49</v>
+      </c>
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
@@ -6476,6 +6479,9 @@
       <c r="I136" s="20">
         <v>0.56999999999999995</v>
       </c>
+      <c r="J136" s="17">
+        <v>0.7</v>
+      </c>
       <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
@@ -6563,6 +6569,9 @@
       <c r="I139" s="20">
         <v>0.6</v>
       </c>
+      <c r="J139" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
@@ -6590,6 +6599,9 @@
       <c r="I140" s="20">
         <v>0.19</v>
       </c>
+      <c r="J140" s="17">
+        <v>0.3</v>
+      </c>
       <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
@@ -6617,6 +6629,9 @@
       <c r="I141" s="20">
         <v>0.39</v>
       </c>
+      <c r="J141" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
@@ -6674,6 +6689,9 @@
       <c r="I143" s="20">
         <v>0.24</v>
       </c>
+      <c r="J143" s="17">
+        <v>0.33</v>
+      </c>
       <c r="P143" s="4"/>
     </row>
     <row r="144" spans="1:16">
@@ -6761,6 +6779,9 @@
       <c r="I146" s="20">
         <v>0.55000000000000004</v>
       </c>
+      <c r="J146" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P146" s="4"/>
     </row>
     <row r="147" spans="1:16">
@@ -6908,6 +6929,9 @@
       <c r="I151" s="20">
         <v>0.34</v>
       </c>
+      <c r="J151" s="17">
+        <v>0.4</v>
+      </c>
       <c r="P151" s="4"/>
     </row>
     <row r="152" spans="1:16">
@@ -6935,6 +6959,9 @@
       <c r="I152" s="20">
         <v>0.48</v>
       </c>
+      <c r="J152" s="17">
+        <v>0.75</v>
+      </c>
       <c r="P152" s="4"/>
     </row>
     <row r="153" spans="1:16">
@@ -6962,6 +6989,9 @@
       <c r="I153" s="20">
         <v>0.81</v>
       </c>
+      <c r="J153" s="17">
+        <v>0.73</v>
+      </c>
       <c r="P153" s="4"/>
     </row>
     <row r="154" spans="1:16">
@@ -6989,6 +7019,9 @@
       <c r="I154" s="20">
         <v>0.51</v>
       </c>
+      <c r="J154" s="17">
+        <v>0.16</v>
+      </c>
       <c r="P154" s="4"/>
     </row>
     <row r="155" spans="1:16">
@@ -7046,6 +7079,9 @@
       <c r="I156" s="20">
         <v>0.27</v>
       </c>
+      <c r="J156" s="17">
+        <v>0.37</v>
+      </c>
       <c r="P156" s="4"/>
     </row>
     <row r="157" spans="1:16">
@@ -7073,6 +7109,9 @@
       <c r="I157" s="20">
         <v>0.42</v>
       </c>
+      <c r="J157" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P157" s="4"/>
     </row>
     <row r="158" spans="1:16">
@@ -7160,6 +7199,9 @@
       <c r="I160" s="20">
         <v>0.31</v>
       </c>
+      <c r="J160" s="17">
+        <v>0.49</v>
+      </c>
       <c r="P160" s="4"/>
     </row>
     <row r="161" spans="1:16">
@@ -7217,6 +7259,9 @@
       <c r="I162" s="20">
         <v>0.79</v>
       </c>
+      <c r="J162" s="17">
+        <v>0.63</v>
+      </c>
       <c r="P162" s="4"/>
     </row>
     <row r="163" spans="1:16">
@@ -7244,6 +7289,9 @@
       <c r="I163" s="20">
         <v>0.6</v>
       </c>
+      <c r="J163" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P163" s="4"/>
     </row>
     <row r="164" spans="1:16">
@@ -7271,6 +7319,9 @@
       <c r="I164" s="20">
         <v>0.09</v>
       </c>
+      <c r="J164" s="17">
+        <v>0.33</v>
+      </c>
       <c r="P164" s="4"/>
     </row>
     <row r="165" spans="1:16">
@@ -7298,6 +7349,9 @@
       <c r="I165" s="20">
         <v>0.34</v>
       </c>
+      <c r="J165" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P165" s="4"/>
     </row>
     <row r="166" spans="1:16">
@@ -7325,6 +7379,9 @@
       <c r="I166" s="20">
         <v>0.24</v>
       </c>
+      <c r="J166" s="17">
+        <v>0.32</v>
+      </c>
       <c r="P166" s="4"/>
     </row>
     <row r="167" spans="1:16">
@@ -7382,6 +7439,9 @@
       <c r="I168" s="20">
         <v>0.78</v>
       </c>
+      <c r="J168" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P168" s="4"/>
     </row>
     <row r="169" spans="1:16">
@@ -7439,6 +7499,9 @@
       <c r="I170" s="20">
         <v>0.18</v>
       </c>
+      <c r="J170" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P170" s="4"/>
     </row>
     <row r="171" spans="1:16">
@@ -7583,6 +7646,9 @@
       <c r="I175" s="20">
         <v>0.63</v>
       </c>
+      <c r="J175" s="17">
+        <v>0.33</v>
+      </c>
       <c r="P175" s="4"/>
     </row>
     <row r="176" spans="1:16">
@@ -7610,6 +7676,9 @@
       <c r="I176" s="20">
         <v>0.24</v>
       </c>
+      <c r="J176" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P176" s="4"/>
     </row>
     <row r="177" spans="1:16">
@@ -7637,6 +7706,9 @@
       <c r="I177" s="20">
         <v>0.43</v>
       </c>
+      <c r="J177" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P177" s="4"/>
     </row>
     <row r="178" spans="1:16">
@@ -7664,6 +7736,9 @@
       <c r="I178" s="20">
         <v>0</v>
       </c>
+      <c r="J178" s="17">
+        <v>0.27</v>
+      </c>
       <c r="P178" s="4"/>
     </row>
     <row r="179" spans="1:16">
@@ -7691,6 +7766,9 @@
       <c r="I179" s="20">
         <v>0.37</v>
       </c>
+      <c r="J179" s="17">
+        <v>0.49</v>
+      </c>
       <c r="P179" s="4"/>
     </row>
     <row r="180" spans="1:16">
@@ -7748,6 +7826,9 @@
       <c r="I181" s="20">
         <v>0.57999999999999996</v>
       </c>
+      <c r="J181" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="P181" s="4"/>
     </row>
     <row r="182" spans="1:16">
@@ -9230,6 +9311,9 @@
       <c r="I231" s="20">
         <v>0.08</v>
       </c>
+      <c r="J231" s="17">
+        <v>0.71</v>
+      </c>
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="9" t="s">
@@ -9256,6 +9340,9 @@
       <c r="I232" s="20">
         <v>0.87</v>
       </c>
+      <c r="J232" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P232" s="16"/>
     </row>
     <row r="233" spans="1:16">
@@ -9283,6 +9370,9 @@
       <c r="I233" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
+      <c r="J233" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P233" s="16"/>
     </row>
     <row r="234" spans="1:16">
@@ -9628,6 +9718,9 @@
       </c>
       <c r="I246" s="20">
         <v>0.13</v>
+      </c>
+      <c r="J246" s="17">
+        <v>0.37</v>
       </c>
       <c r="P246" s="16"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D434DA0-43B4-CA42-ACF3-AF91C179472C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D50184-B5E3-E642-92DD-2F78B2B671D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2930,7 +2930,7 @@
         <v>0.22</v>
       </c>
       <c r="J23" s="17">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="L23" s="17">
         <v>0.68</v>
@@ -9341,7 +9341,7 @@
         <v>0.87</v>
       </c>
       <c r="J232" s="17">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="P232" s="16"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D50184-B5E3-E642-92DD-2F78B2B671D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29470581-C5DF-D144-B7A9-93C3F29C9EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -9263,6 +9263,9 @@
       <c r="I229" s="20">
         <v>0.6</v>
       </c>
+      <c r="J229" s="17">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="230" spans="1:16">
       <c r="A230" s="9" t="s">
@@ -9289,6 +9292,9 @@
       <c r="I230" s="20">
         <v>0.19</v>
       </c>
+      <c r="J230" s="17">
+        <v>0.22</v>
+      </c>
       <c r="P230" s="16"/>
     </row>
     <row r="231" spans="1:16">
@@ -9400,6 +9406,9 @@
       <c r="I234" s="20">
         <v>0.18</v>
       </c>
+      <c r="J234" s="17">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="235" spans="1:16">
       <c r="A235" t="s">
@@ -9426,6 +9435,9 @@
       <c r="I235" s="20">
         <v>0.21</v>
       </c>
+      <c r="J235" s="17">
+        <v>0.43</v>
+      </c>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="9" t="s">
@@ -9452,6 +9464,9 @@
       <c r="I236" s="20">
         <v>0.72</v>
       </c>
+      <c r="J236" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P236" s="16"/>
     </row>
     <row r="237" spans="1:16">
@@ -9479,6 +9494,9 @@
       <c r="I237" s="20">
         <v>0.43</v>
       </c>
+      <c r="J237" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P237" s="16"/>
     </row>
     <row r="238" spans="1:16">
@@ -9506,6 +9524,9 @@
       <c r="I238" s="20">
         <v>0.66</v>
       </c>
+      <c r="J238" s="17">
+        <v>0.6</v>
+      </c>
       <c r="P238" s="16"/>
     </row>
     <row r="239" spans="1:16">
@@ -9533,6 +9554,9 @@
       <c r="I239" s="20">
         <v>0.25</v>
       </c>
+      <c r="J239" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P239" s="16"/>
     </row>
     <row r="240" spans="1:16">
@@ -9560,6 +9584,9 @@
       <c r="I240" s="20">
         <v>0.66</v>
       </c>
+      <c r="J240" s="17">
+        <v>0.49</v>
+      </c>
       <c r="P240" s="16"/>
     </row>
     <row r="241" spans="1:16">
@@ -9587,6 +9614,9 @@
       <c r="I241" s="20">
         <v>0.55000000000000004</v>
       </c>
+      <c r="J241" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P241" s="16"/>
     </row>
     <row r="242" spans="1:16">
@@ -9614,6 +9644,9 @@
       <c r="I242" s="20">
         <v>0.72</v>
       </c>
+      <c r="J242" s="17">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" t="s">
@@ -9640,6 +9673,9 @@
       <c r="I243" s="20">
         <v>0</v>
       </c>
+      <c r="J243" s="17">
+        <v>0.19</v>
+      </c>
     </row>
     <row r="244" spans="1:16">
       <c r="A244" t="s">
@@ -9666,6 +9702,9 @@
       <c r="I244" s="20">
         <v>0.15</v>
       </c>
+      <c r="J244" s="17">
+        <v>0.62</v>
+      </c>
     </row>
     <row r="245" spans="1:16">
       <c r="A245" s="9" t="s">
@@ -9691,6 +9730,9 @@
       </c>
       <c r="I245" s="20">
         <v>0</v>
+      </c>
+      <c r="J245" s="17">
+        <v>0.62</v>
       </c>
       <c r="P245" s="16"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29470581-C5DF-D144-B7A9-93C3F29C9EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA89EB1A-2395-644B-B2B0-0A5418A9A08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -1630,15 +1631,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="15"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1689,11 +1696,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1731,6 +1753,9 @@
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2245,7 +2270,10 @@
       <c r="L2" s="17">
         <v>0.48</v>
       </c>
-      <c r="P2" s="4"/>
+      <c r="P2" s="22" t="e">
+        <f>(((LARGE(D2:G2,1)+LARGE(D2:G2,2)+LARGE(D2:G2,3))*0.2/3+(LARGE(H2:K2,1)+LARGE(H2:K2,2)+LARGE(H2:K2,3))*0.5/3+(LARGE(L2:O2,1)+LARGE(L2:O2,2)+LARGE(L2:O2,3))*0.3/3))</f>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="5" t="s">
@@ -2803,6 +2831,9 @@
       <c r="J19" s="17">
         <v>0</v>
       </c>
+      <c r="L19" s="17">
+        <v>0</v>
+      </c>
       <c r="P19" s="15"/>
     </row>
     <row r="20" spans="1:16">
@@ -3427,6 +3458,9 @@
       <c r="J38" s="17">
         <v>0.48</v>
       </c>
+      <c r="L38" s="17">
+        <v>0</v>
+      </c>
       <c r="P38" s="15"/>
     </row>
     <row r="39" spans="1:16">
@@ -3589,6 +3623,9 @@
       <c r="J43" s="17">
         <v>0.4</v>
       </c>
+      <c r="L43" s="17">
+        <v>0</v>
+      </c>
       <c r="P43" s="15"/>
     </row>
     <row r="44" spans="1:16">
@@ -3619,6 +3656,9 @@
       <c r="J44" s="17">
         <v>0.25</v>
       </c>
+      <c r="L44" s="17">
+        <v>0</v>
+      </c>
       <c r="P44" s="15"/>
     </row>
     <row r="45" spans="1:16">
@@ -3781,6 +3821,9 @@
       <c r="J49" s="17">
         <v>0.59</v>
       </c>
+      <c r="L49" s="17">
+        <v>0</v>
+      </c>
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
@@ -3842,7 +3885,7 @@
         <v>0.46</v>
       </c>
       <c r="J51" s="17">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="L51" s="17">
         <v>0.92</v>
@@ -3875,7 +3918,7 @@
         <v>0.51</v>
       </c>
       <c r="J52" s="17">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="L52" s="17">
         <v>0.83</v>
@@ -4075,6 +4118,9 @@
       <c r="J58" s="17">
         <v>0.37</v>
       </c>
+      <c r="L58" s="17">
+        <v>0</v>
+      </c>
       <c r="P58" s="4"/>
     </row>
     <row r="59" spans="1:16">
@@ -4103,7 +4149,7 @@
         <v>0.66</v>
       </c>
       <c r="J59" s="17">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="L59" s="17">
         <v>0.92</v>
@@ -4433,7 +4479,7 @@
         <v>0.6</v>
       </c>
       <c r="J69" s="17">
-        <v>0.56000000000000005</v>
+        <v>0.62</v>
       </c>
       <c r="L69" s="17">
         <v>0.92</v>
@@ -4600,6 +4646,9 @@
       <c r="J74" s="17">
         <v>0.48</v>
       </c>
+      <c r="L74" s="17">
+        <v>0</v>
+      </c>
       <c r="P74" s="4"/>
     </row>
     <row r="75" spans="1:16">
@@ -4630,6 +4679,9 @@
       <c r="J75" s="17">
         <v>0.17</v>
       </c>
+      <c r="L75" s="17">
+        <v>0</v>
+      </c>
       <c r="P75" s="4"/>
     </row>
     <row r="76" spans="1:16">
@@ -4726,6 +4778,9 @@
       <c r="J78" s="17">
         <v>0.41</v>
       </c>
+      <c r="L78" s="17">
+        <v>0</v>
+      </c>
       <c r="P78" s="4"/>
     </row>
     <row r="79" spans="1:16">
@@ -5020,6 +5075,9 @@
       <c r="J87" s="17">
         <v>0.25</v>
       </c>
+      <c r="L87" s="17">
+        <v>0</v>
+      </c>
       <c r="P87" s="4"/>
     </row>
     <row r="88" spans="1:16">
@@ -5081,7 +5139,10 @@
         <v>0.34</v>
       </c>
       <c r="J89" s="17">
-        <v>0.46</v>
+        <v>0.51</v>
+      </c>
+      <c r="L89" s="17">
+        <v>0</v>
       </c>
       <c r="P89" s="4"/>
     </row>
@@ -5320,6 +5381,9 @@
       <c r="I97" s="20">
         <v>0.31</v>
       </c>
+      <c r="J97" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P97" s="4"/>
     </row>
     <row r="98" spans="1:16">
@@ -5332,7 +5396,12 @@
       <c r="C98" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="D98" s="20"/>
+      <c r="D98" s="20">
+        <v>0</v>
+      </c>
+      <c r="E98" s="17">
+        <v>0</v>
+      </c>
       <c r="F98" s="17">
         <v>0</v>
       </c>
@@ -5341,6 +5410,9 @@
       </c>
       <c r="I98" s="20">
         <v>0.15</v>
+      </c>
+      <c r="J98" s="17">
+        <v>0</v>
       </c>
       <c r="P98" s="15"/>
     </row>
@@ -7589,6 +7661,9 @@
       <c r="I173" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
+      <c r="J173" s="17">
+        <v>0</v>
+      </c>
       <c r="P173" s="4"/>
     </row>
     <row r="174" spans="1:16">
@@ -8006,6 +8081,12 @@
       <c r="I187" s="20">
         <v>0.13</v>
       </c>
+      <c r="J187" s="17">
+        <v>0</v>
+      </c>
+      <c r="L187" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P187" s="15"/>
     </row>
     <row r="188" spans="1:16">
@@ -8156,6 +8237,9 @@
       <c r="J192" s="17">
         <v>0.27</v>
       </c>
+      <c r="L192" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P192" s="4"/>
     </row>
     <row r="193" spans="1:16">
@@ -8816,6 +8900,9 @@
       <c r="J214" s="17">
         <v>0</v>
       </c>
+      <c r="L214" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P214" s="4"/>
     </row>
     <row r="215" spans="1:16">
@@ -9026,6 +9113,9 @@
       <c r="J221" s="17">
         <v>0.59</v>
       </c>
+      <c r="L221" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P221" s="4"/>
     </row>
     <row r="222" spans="1:16">
@@ -9086,6 +9176,9 @@
       <c r="J223" s="17">
         <v>0.17</v>
       </c>
+      <c r="L223" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P223" s="4"/>
     </row>
     <row r="224" spans="1:16">
@@ -9116,6 +9209,9 @@
       <c r="J224" s="17">
         <v>0.52</v>
       </c>
+      <c r="L224" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P224" s="4"/>
     </row>
     <row r="225" spans="1:16">
@@ -9176,6 +9272,9 @@
       <c r="J226" s="17">
         <v>0.21</v>
       </c>
+      <c r="L226" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P226" s="4"/>
     </row>
     <row r="227" spans="1:16">
@@ -9206,6 +9305,9 @@
       <c r="J227" s="17">
         <v>0.6</v>
       </c>
+      <c r="L227" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P227" s="16"/>
     </row>
     <row r="228" spans="1:16">
@@ -9236,6 +9338,9 @@
       <c r="J228" s="17">
         <v>0.33</v>
       </c>
+      <c r="L228" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P228" s="16"/>
     </row>
     <row r="229" spans="1:16">
@@ -9266,6 +9371,9 @@
       <c r="J229" s="17">
         <v>0.35</v>
       </c>
+      <c r="L229" s="17">
+        <v>0.57999999999999996</v>
+      </c>
     </row>
     <row r="230" spans="1:16">
       <c r="A230" s="9" t="s">
@@ -9295,6 +9403,9 @@
       <c r="J230" s="17">
         <v>0.22</v>
       </c>
+      <c r="L230" s="17">
+        <v>0.54</v>
+      </c>
       <c r="P230" s="16"/>
     </row>
     <row r="231" spans="1:16">
@@ -9307,7 +9418,12 @@
       <c r="C231" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="D231" s="20"/>
+      <c r="D231" s="20">
+        <v>0</v>
+      </c>
+      <c r="E231" s="17">
+        <v>0</v>
+      </c>
       <c r="F231" s="17">
         <v>0.77</v>
       </c>
@@ -9319,6 +9435,9 @@
       </c>
       <c r="J231" s="17">
         <v>0.71</v>
+      </c>
+      <c r="L231" s="17">
+        <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -9349,6 +9468,9 @@
       <c r="J232" s="17">
         <v>0.67</v>
       </c>
+      <c r="L232" s="17">
+        <v>0.69</v>
+      </c>
       <c r="P232" s="16"/>
     </row>
     <row r="233" spans="1:16">
@@ -9379,6 +9501,9 @@
       <c r="J233" s="17">
         <v>0.52</v>
       </c>
+      <c r="L233" s="17">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="P233" s="16"/>
     </row>
     <row r="234" spans="1:16">
@@ -9409,6 +9534,9 @@
       <c r="J234" s="17">
         <v>0.25</v>
       </c>
+      <c r="L234" s="17">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="235" spans="1:16">
       <c r="A235" t="s">
@@ -9438,6 +9566,9 @@
       <c r="J235" s="17">
         <v>0.43</v>
       </c>
+      <c r="L235" s="17">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="9" t="s">
@@ -9467,6 +9598,9 @@
       <c r="J236" s="17">
         <v>0.79</v>
       </c>
+      <c r="L236" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P236" s="16"/>
     </row>
     <row r="237" spans="1:16">
@@ -9497,6 +9631,9 @@
       <c r="J237" s="17">
         <v>0.62</v>
       </c>
+      <c r="L237" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P237" s="16"/>
     </row>
     <row r="238" spans="1:16">
@@ -9527,6 +9664,9 @@
       <c r="J238" s="17">
         <v>0.6</v>
       </c>
+      <c r="L238" s="17">
+        <v>0.69</v>
+      </c>
       <c r="P238" s="16"/>
     </row>
     <row r="239" spans="1:16">
@@ -9557,6 +9697,9 @@
       <c r="J239" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="L239" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P239" s="16"/>
     </row>
     <row r="240" spans="1:16">
@@ -9587,6 +9730,9 @@
       <c r="J240" s="17">
         <v>0.49</v>
       </c>
+      <c r="L240" s="17">
+        <v>0.54</v>
+      </c>
       <c r="P240" s="16"/>
     </row>
     <row r="241" spans="1:16">
@@ -9617,6 +9763,9 @@
       <c r="J241" s="17">
         <v>0.52</v>
       </c>
+      <c r="L241" s="17">
+        <v>0.69</v>
+      </c>
       <c r="P241" s="16"/>
     </row>
     <row r="242" spans="1:16">
@@ -9647,6 +9796,9 @@
       <c r="J242" s="17">
         <v>0.52</v>
       </c>
+      <c r="L242" s="17">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" t="s">
@@ -9676,6 +9828,9 @@
       <c r="J243" s="17">
         <v>0.19</v>
       </c>
+      <c r="L243" s="17">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="244" spans="1:16">
       <c r="A244" t="s">
@@ -9705,6 +9860,9 @@
       <c r="J244" s="17">
         <v>0.62</v>
       </c>
+      <c r="L244" s="17">
+        <v>0.69</v>
+      </c>
     </row>
     <row r="245" spans="1:16">
       <c r="A245" s="9" t="s">
@@ -9734,6 +9892,9 @@
       <c r="J245" s="17">
         <v>0.62</v>
       </c>
+      <c r="L245" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P245" s="16"/>
     </row>
     <row r="246" spans="1:16">
@@ -9763,6 +9924,9 @@
       </c>
       <c r="J246" s="17">
         <v>0.37</v>
+      </c>
+      <c r="L246" s="17">
+        <v>0.57999999999999996</v>
       </c>
       <c r="P246" s="16"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA89EB1A-2395-644B-B2B0-0A5418A9A08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A750D7-23CF-A74D-B594-DC95248ABDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7994,6 +7994,9 @@
       <c r="J184" s="17">
         <v>0.19</v>
       </c>
+      <c r="L184" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
@@ -8024,6 +8027,9 @@
       <c r="J185" s="17">
         <v>0.42</v>
       </c>
+      <c r="L185" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
@@ -8054,6 +8060,9 @@
       <c r="J186" s="17">
         <v>0.27</v>
       </c>
+      <c r="L186" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P186" s="4"/>
     </row>
     <row r="187" spans="1:16">
@@ -8117,6 +8126,9 @@
       <c r="J188" s="17">
         <v>0.75</v>
       </c>
+      <c r="L188" s="17">
+        <v>0</v>
+      </c>
       <c r="P188" s="15"/>
     </row>
     <row r="189" spans="1:16">
@@ -8147,6 +8159,9 @@
       <c r="J189" s="17">
         <v>0.52</v>
       </c>
+      <c r="L189" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P189" s="4"/>
     </row>
     <row r="190" spans="1:16">
@@ -8177,6 +8192,9 @@
       <c r="J190" s="17">
         <v>0.06</v>
       </c>
+      <c r="L190" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P190" s="4"/>
     </row>
     <row r="191" spans="1:16">
@@ -8207,6 +8225,9 @@
       <c r="J191" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="L191" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P191" s="4"/>
     </row>
     <row r="192" spans="1:16">
@@ -8270,6 +8291,9 @@
       <c r="J193" s="17">
         <v>0.32</v>
       </c>
+      <c r="L193" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P193" s="4"/>
     </row>
     <row r="194" spans="1:16">
@@ -8300,6 +8324,9 @@
       <c r="J194" s="17">
         <v>0.6</v>
       </c>
+      <c r="L194" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P194" s="4"/>
     </row>
     <row r="195" spans="1:16">
@@ -8330,6 +8357,9 @@
       <c r="J195" s="17">
         <v>0.37</v>
       </c>
+      <c r="L195" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P195" s="4"/>
     </row>
     <row r="196" spans="1:16">
@@ -8360,6 +8390,9 @@
       <c r="J196" s="17">
         <v>0.32</v>
       </c>
+      <c r="L196" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P196" s="4"/>
     </row>
     <row r="197" spans="1:16">
@@ -8390,6 +8423,9 @@
       <c r="J197" s="17">
         <v>0.33</v>
       </c>
+      <c r="L197" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P197" s="4"/>
     </row>
     <row r="198" spans="1:16">
@@ -8420,6 +8456,9 @@
       <c r="J198" s="17">
         <v>0.44</v>
       </c>
+      <c r="L198" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P198" s="4"/>
     </row>
     <row r="199" spans="1:16">
@@ -8450,6 +8489,9 @@
       <c r="J199" s="17">
         <v>0.17</v>
       </c>
+      <c r="L199" s="17">
+        <v>0</v>
+      </c>
       <c r="P199" s="15"/>
     </row>
     <row r="200" spans="1:16">
@@ -8480,6 +8522,9 @@
       <c r="J200" s="17">
         <v>0.4</v>
       </c>
+      <c r="L200" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P200" s="4"/>
     </row>
     <row r="201" spans="1:16">
@@ -8510,6 +8555,9 @@
       <c r="J201" s="17">
         <v>0.73</v>
       </c>
+      <c r="L201" s="17">
+        <v>0</v>
+      </c>
       <c r="P201" s="4"/>
     </row>
     <row r="202" spans="1:16">
@@ -8540,6 +8588,9 @@
       <c r="J202" s="17">
         <v>0.79</v>
       </c>
+      <c r="L202" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P202" s="4"/>
     </row>
     <row r="203" spans="1:16">
@@ -8570,6 +8621,9 @@
       <c r="J203" s="17">
         <v>0.49</v>
       </c>
+      <c r="L203" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P203" s="4"/>
     </row>
     <row r="204" spans="1:16">
@@ -8600,6 +8654,9 @@
       <c r="J204" s="17">
         <v>0.81</v>
       </c>
+      <c r="L204" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P204" s="4"/>
     </row>
     <row r="205" spans="1:16">
@@ -8630,6 +8687,9 @@
       <c r="J205" s="17">
         <v>0.48</v>
       </c>
+      <c r="L205" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P205" s="4"/>
     </row>
     <row r="206" spans="1:16">
@@ -8660,6 +8720,9 @@
       <c r="J206" s="17">
         <v>0.33</v>
       </c>
+      <c r="L206" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P206" s="4"/>
     </row>
     <row r="207" spans="1:16">
@@ -8690,6 +8753,9 @@
       <c r="J207" s="17">
         <v>0.4</v>
       </c>
+      <c r="L207" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P207" s="4"/>
     </row>
     <row r="208" spans="1:16">
@@ -8720,6 +8786,9 @@
       <c r="J208" s="17">
         <v>0.33</v>
       </c>
+      <c r="L208" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P208" s="4"/>
     </row>
     <row r="209" spans="1:16">
@@ -8750,6 +8819,9 @@
       <c r="J209" s="17">
         <v>0.35</v>
       </c>
+      <c r="L209" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P209" s="4"/>
     </row>
     <row r="210" spans="1:16">
@@ -8780,6 +8852,9 @@
       <c r="J210" s="17">
         <v>0.78</v>
       </c>
+      <c r="L210" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P210" s="4"/>
     </row>
     <row r="211" spans="1:16">
@@ -8810,6 +8885,9 @@
       <c r="J211" s="17">
         <v>0.41</v>
       </c>
+      <c r="L211" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P211" s="4"/>
     </row>
     <row r="212" spans="1:16">
@@ -8840,6 +8918,9 @@
       <c r="J212" s="17">
         <v>0.49</v>
       </c>
+      <c r="L212" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P212" s="4"/>
     </row>
     <row r="213" spans="1:16">
@@ -8870,6 +8951,9 @@
       <c r="J213" s="17">
         <v>0.52</v>
       </c>
+      <c r="L213" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P213" s="4"/>
     </row>
     <row r="214" spans="1:16">
@@ -8933,6 +9017,9 @@
       <c r="J215" s="17">
         <v>0.35</v>
       </c>
+      <c r="L215" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P215" s="4"/>
     </row>
     <row r="216" spans="1:16">
@@ -8963,6 +9050,9 @@
       <c r="J216" s="17">
         <v>0.14000000000000001</v>
       </c>
+      <c r="L216" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P216" s="4"/>
     </row>
     <row r="217" spans="1:16">
@@ -8993,6 +9083,9 @@
       <c r="J217" s="17">
         <v>0.41</v>
       </c>
+      <c r="L217" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P217" s="4"/>
     </row>
     <row r="218" spans="1:16">
@@ -9023,6 +9116,9 @@
       <c r="J218" s="17">
         <v>0.67</v>
       </c>
+      <c r="L218" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P218" s="4"/>
     </row>
     <row r="219" spans="1:16">
@@ -9053,6 +9149,9 @@
       <c r="J219" s="17">
         <v>0.41</v>
       </c>
+      <c r="L219" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P219" s="4"/>
     </row>
     <row r="220" spans="1:16">
@@ -9083,6 +9182,9 @@
       <c r="J220" s="17">
         <v>0.67</v>
       </c>
+      <c r="L220" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P220" s="4"/>
     </row>
     <row r="221" spans="1:16">
@@ -9146,6 +9248,9 @@
       <c r="J222" s="17">
         <v>0</v>
       </c>
+      <c r="L222" s="17">
+        <v>0</v>
+      </c>
       <c r="P222" s="15"/>
     </row>
     <row r="223" spans="1:16">
@@ -9241,6 +9346,9 @@
       </c>
       <c r="J225" s="17">
         <v>0.38</v>
+      </c>
+      <c r="L225" s="17">
+        <v>0</v>
       </c>
       <c r="P225" s="15"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A750D7-23CF-A74D-B594-DC95248ABDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA53E96F-E129-5848-BC5F-3B44F4380D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -5174,6 +5174,9 @@
       <c r="J90" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="L90" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
@@ -5204,6 +5207,9 @@
       <c r="J91" s="17">
         <v>0.54</v>
       </c>
+      <c r="L91" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
@@ -5234,6 +5240,9 @@
       <c r="J92" s="17">
         <v>0.13</v>
       </c>
+      <c r="L92" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
@@ -5264,6 +5273,9 @@
       <c r="J93" s="17">
         <v>0.44</v>
       </c>
+      <c r="L93" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
@@ -5294,6 +5306,9 @@
       <c r="J94" s="17">
         <v>0.65</v>
       </c>
+      <c r="L94" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
@@ -5324,6 +5339,9 @@
       <c r="J95" s="17">
         <v>0.62</v>
       </c>
+      <c r="L95" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
@@ -5354,6 +5372,9 @@
       <c r="J96" s="17">
         <v>0.78</v>
       </c>
+      <c r="L96" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
@@ -5384,6 +5405,9 @@
       <c r="J97" s="17">
         <v>0.71</v>
       </c>
+      <c r="L97" s="17">
+        <v>0.69</v>
+      </c>
       <c r="P97" s="4"/>
     </row>
     <row r="98" spans="1:16">
@@ -5414,6 +5438,9 @@
       <c r="J98" s="17">
         <v>0</v>
       </c>
+      <c r="L98" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P98" s="15"/>
     </row>
     <row r="99" spans="1:16">
@@ -5444,6 +5471,9 @@
       <c r="J99" s="17">
         <v>0.63</v>
       </c>
+      <c r="L99" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P99" s="4"/>
     </row>
     <row r="100" spans="1:16">
@@ -5474,6 +5504,9 @@
       <c r="J100" s="17">
         <v>0.4</v>
       </c>
+      <c r="L100" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P100" s="4"/>
     </row>
     <row r="101" spans="1:16">
@@ -5504,6 +5537,9 @@
       <c r="J101" s="17">
         <v>0.44</v>
       </c>
+      <c r="L101" s="17">
+        <v>0.69</v>
+      </c>
       <c r="P101" s="4"/>
     </row>
     <row r="102" spans="1:16">
@@ -5534,6 +5570,9 @@
       <c r="J102" s="17">
         <v>0.65</v>
       </c>
+      <c r="L102" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P102" s="4"/>
     </row>
     <row r="103" spans="1:16">
@@ -5564,6 +5603,9 @@
       <c r="J103" s="17">
         <v>0.71</v>
       </c>
+      <c r="L103" s="17">
+        <v>0.69</v>
+      </c>
       <c r="P103" s="4"/>
     </row>
     <row r="104" spans="1:16">
@@ -5594,6 +5636,9 @@
       <c r="J104" s="17">
         <v>0.38</v>
       </c>
+      <c r="L104" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P104" s="4"/>
     </row>
     <row r="105" spans="1:16">
@@ -5624,6 +5669,9 @@
       <c r="J105" s="17">
         <v>0.44</v>
       </c>
+      <c r="L105" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P105" s="4"/>
     </row>
     <row r="106" spans="1:16">
@@ -5654,6 +5702,9 @@
       <c r="J106" s="17">
         <v>0.62</v>
       </c>
+      <c r="L106" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P106" s="15"/>
     </row>
     <row r="107" spans="1:16">
@@ -5684,6 +5735,9 @@
       <c r="J107" s="17">
         <v>0.3</v>
       </c>
+      <c r="L107" s="17">
+        <v>0.69</v>
+      </c>
       <c r="P107" s="4"/>
     </row>
     <row r="108" spans="1:16">
@@ -5714,6 +5768,9 @@
       <c r="J108" s="17">
         <v>0.32</v>
       </c>
+      <c r="L108" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P108" s="4"/>
     </row>
     <row r="109" spans="1:16">
@@ -5744,6 +5801,9 @@
       <c r="J109" s="17">
         <v>0.35</v>
       </c>
+      <c r="L109" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P109" s="4"/>
     </row>
     <row r="110" spans="1:16">
@@ -5774,6 +5834,9 @@
       <c r="J110" s="17">
         <v>0.7</v>
       </c>
+      <c r="L110" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P110" s="4"/>
     </row>
     <row r="111" spans="1:16">
@@ -5804,6 +5867,9 @@
       <c r="J111" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="L111" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P111" s="4"/>
     </row>
     <row r="112" spans="1:16">
@@ -5834,6 +5900,9 @@
       <c r="J112" s="17">
         <v>0.65</v>
       </c>
+      <c r="L112" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P112" s="4"/>
     </row>
     <row r="113" spans="1:16">
@@ -5864,6 +5933,9 @@
       <c r="J113" s="17">
         <v>0.32</v>
       </c>
+      <c r="L113" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P113" s="4"/>
     </row>
     <row r="114" spans="1:16">
@@ -5894,6 +5966,9 @@
       <c r="J114" s="17">
         <v>0.48</v>
       </c>
+      <c r="L114" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P114" s="4"/>
     </row>
     <row r="115" spans="1:16">
@@ -5924,6 +5999,9 @@
       <c r="J115" s="17">
         <v>0.48</v>
       </c>
+      <c r="L115" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P115" s="4"/>
     </row>
     <row r="116" spans="1:16">
@@ -5954,6 +6032,9 @@
       <c r="J116" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="L116" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P116" s="4"/>
     </row>
     <row r="117" spans="1:16">
@@ -5984,6 +6065,9 @@
       <c r="J117" s="17">
         <v>0.38</v>
       </c>
+      <c r="L117" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P117" s="4"/>
     </row>
     <row r="118" spans="1:16">
@@ -6014,6 +6098,9 @@
       <c r="J118" s="17">
         <v>0.7</v>
       </c>
+      <c r="L118" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P118" s="4"/>
     </row>
     <row r="119" spans="1:16">
@@ -6044,6 +6131,9 @@
       <c r="J119" s="17">
         <v>0.6</v>
       </c>
+      <c r="L119" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P119" s="4"/>
     </row>
     <row r="120" spans="1:16">
@@ -6074,6 +6164,9 @@
       <c r="J120" s="17">
         <v>0.02</v>
       </c>
+      <c r="L120" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P120" s="15"/>
     </row>
     <row r="121" spans="1:16">
@@ -6104,6 +6197,9 @@
       <c r="J121" s="17">
         <v>0.63</v>
       </c>
+      <c r="L121" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P121" s="4"/>
     </row>
     <row r="122" spans="1:16">
@@ -6134,6 +6230,9 @@
       <c r="J122" s="17">
         <v>0.67</v>
       </c>
+      <c r="L122" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P122" s="4"/>
     </row>
     <row r="123" spans="1:16">
@@ -6164,6 +6263,9 @@
       <c r="J123" s="17">
         <v>0.24</v>
       </c>
+      <c r="L123" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P123" s="4"/>
     </row>
     <row r="124" spans="1:16">
@@ -6194,6 +6296,9 @@
       <c r="J124" s="17">
         <v>0.48</v>
       </c>
+      <c r="L124" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P124" s="4"/>
     </row>
     <row r="125" spans="1:16">
@@ -6224,6 +6329,9 @@
       <c r="J125" s="17">
         <v>0.51</v>
       </c>
+      <c r="L125" s="17">
+        <v>0.69</v>
+      </c>
       <c r="P125" s="4"/>
     </row>
     <row r="126" spans="1:16">
@@ -6254,6 +6362,9 @@
       <c r="J126" s="17">
         <v>0.78</v>
       </c>
+      <c r="L126" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P126" s="4"/>
     </row>
     <row r="127" spans="1:16">
@@ -6284,6 +6395,9 @@
       <c r="J127" s="17">
         <v>0.28999999999999998</v>
       </c>
+      <c r="L127" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P127" s="4"/>
     </row>
     <row r="128" spans="1:16">
@@ -6314,6 +6428,9 @@
       <c r="J128" s="17">
         <v>0.79</v>
       </c>
+      <c r="L128" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P128" s="4"/>
     </row>
     <row r="129" spans="1:16">
@@ -6344,6 +6461,9 @@
       <c r="J129" s="17">
         <v>0.32</v>
       </c>
+      <c r="L129" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P129" s="4"/>
     </row>
     <row r="130" spans="1:16">
@@ -6374,6 +6494,9 @@
       <c r="J130" s="17">
         <v>0.65</v>
       </c>
+      <c r="L130" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P130" s="4"/>
     </row>
     <row r="131" spans="1:16">
@@ -6404,6 +6527,9 @@
       <c r="J131" s="17">
         <v>0.52</v>
       </c>
+      <c r="L131" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P131" s="4"/>
     </row>
     <row r="132" spans="1:16">
@@ -6434,6 +6560,9 @@
       <c r="J132" s="17">
         <v>0.62</v>
       </c>
+      <c r="L132" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P132" s="4"/>
     </row>
     <row r="133" spans="1:16">
@@ -6463,6 +6592,9 @@
       </c>
       <c r="J133" s="17">
         <v>0.28999999999999998</v>
+      </c>
+      <c r="L133" s="17">
+        <v>0.69</v>
       </c>
       <c r="P133" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA53E96F-E129-5848-BC5F-3B44F4380D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA4FE6A-EFEE-A74F-A082-36E5F6654CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6626,6 +6626,9 @@
       <c r="J134" s="17">
         <v>0.49</v>
       </c>
+      <c r="L134" s="17">
+        <v>0.96</v>
+      </c>
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
@@ -6686,6 +6689,9 @@
       <c r="J136" s="17">
         <v>0.7</v>
       </c>
+      <c r="L136" s="17">
+        <v>0.96</v>
+      </c>
       <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
@@ -6746,6 +6752,9 @@
       <c r="J138" s="17">
         <v>0.46</v>
       </c>
+      <c r="L138" s="17">
+        <v>0.63</v>
+      </c>
       <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
@@ -6776,6 +6785,9 @@
       <c r="J139" s="17">
         <v>0.71</v>
       </c>
+      <c r="L139" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
@@ -6986,6 +6998,9 @@
       <c r="J146" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="L146" s="17">
+        <v>0.63</v>
+      </c>
       <c r="P146" s="4"/>
     </row>
     <row r="147" spans="1:16">
@@ -7016,6 +7031,9 @@
       <c r="J147" s="17">
         <v>0.86</v>
       </c>
+      <c r="L147" s="17">
+        <v>0.96</v>
+      </c>
       <c r="P147" s="4"/>
     </row>
     <row r="148" spans="1:16">
@@ -7136,6 +7154,9 @@
       <c r="J151" s="17">
         <v>0.4</v>
       </c>
+      <c r="L151" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P151" s="4"/>
     </row>
     <row r="152" spans="1:16">
@@ -7196,6 +7217,9 @@
       <c r="J153" s="17">
         <v>0.73</v>
       </c>
+      <c r="L153" s="17">
+        <v>0.63</v>
+      </c>
       <c r="P153" s="4"/>
     </row>
     <row r="154" spans="1:16">
@@ -7256,6 +7280,9 @@
       <c r="J155" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="L155" s="17">
+        <v>0.96</v>
+      </c>
       <c r="P155" s="4"/>
     </row>
     <row r="156" spans="1:16">
@@ -7286,6 +7313,9 @@
       <c r="J156" s="17">
         <v>0.37</v>
       </c>
+      <c r="L156" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P156" s="4"/>
     </row>
     <row r="157" spans="1:16">
@@ -7436,6 +7466,9 @@
       <c r="J161" s="17">
         <v>0.63</v>
       </c>
+      <c r="L161" s="17">
+        <v>0.63</v>
+      </c>
       <c r="P161" s="4"/>
     </row>
     <row r="162" spans="1:16">
@@ -7496,6 +7529,9 @@
       <c r="J163" s="17">
         <v>0.59</v>
       </c>
+      <c r="L163" s="17">
+        <v>0.96</v>
+      </c>
       <c r="P163" s="4"/>
     </row>
     <row r="164" spans="1:16">
@@ -7526,6 +7562,9 @@
       <c r="J164" s="17">
         <v>0.33</v>
       </c>
+      <c r="L164" s="17">
+        <v>0.96</v>
+      </c>
       <c r="P164" s="4"/>
     </row>
     <row r="165" spans="1:16">
@@ -7706,6 +7745,9 @@
       <c r="J170" s="17">
         <v>0.65</v>
       </c>
+      <c r="L170" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P170" s="4"/>
     </row>
     <row r="171" spans="1:16">
@@ -7766,6 +7808,9 @@
       <c r="J172" s="17">
         <v>0.35</v>
       </c>
+      <c r="L172" s="17">
+        <v>0.63</v>
+      </c>
       <c r="P172" s="4"/>
     </row>
     <row r="173" spans="1:16">
@@ -7976,6 +8021,9 @@
       <c r="J179" s="17">
         <v>0.49</v>
       </c>
+      <c r="L179" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P179" s="4"/>
     </row>
     <row r="180" spans="1:16">
@@ -8006,6 +8054,9 @@
       <c r="J180" s="17">
         <v>0.79</v>
       </c>
+      <c r="L180" s="17">
+        <v>0.63</v>
+      </c>
       <c r="P180" s="4"/>
     </row>
     <row r="181" spans="1:16">
@@ -8065,6 +8116,9 @@
       </c>
       <c r="J182" s="17">
         <v>0.43</v>
+      </c>
+      <c r="L182" s="17">
+        <v>0.8</v>
       </c>
       <c r="P182" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA4FE6A-EFEE-A74F-A082-36E5F6654CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCF7B5A-C85F-C142-B9B7-47DA04B42398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6659,6 +6659,9 @@
       <c r="J135" s="17">
         <v>0.41</v>
       </c>
+      <c r="L135" s="17">
+        <v>0.8</v>
+      </c>
       <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
@@ -6722,6 +6725,9 @@
       <c r="J137" s="17">
         <v>0.67</v>
       </c>
+      <c r="L137" s="17">
+        <v>0</v>
+      </c>
       <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
@@ -6818,6 +6824,9 @@
       <c r="J140" s="17">
         <v>0.3</v>
       </c>
+      <c r="L140" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
@@ -6848,6 +6857,9 @@
       <c r="J141" s="17">
         <v>0.59</v>
       </c>
+      <c r="L141" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
@@ -6878,6 +6890,9 @@
       <c r="J142" s="17">
         <v>0.63</v>
       </c>
+      <c r="L142" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
@@ -6908,6 +6923,9 @@
       <c r="J143" s="17">
         <v>0.33</v>
       </c>
+      <c r="L143" s="17">
+        <v>0</v>
+      </c>
       <c r="P143" s="4"/>
     </row>
     <row r="144" spans="1:16">
@@ -6938,6 +6956,9 @@
       <c r="J144" s="17">
         <v>0.43</v>
       </c>
+      <c r="L144" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P144" s="4"/>
     </row>
     <row r="145" spans="1:16">
@@ -6968,6 +6989,9 @@
       <c r="J145" s="17">
         <v>0.54</v>
       </c>
+      <c r="L145" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P145" s="4"/>
     </row>
     <row r="146" spans="1:16">
@@ -7064,6 +7088,9 @@
       <c r="J148" s="17">
         <v>0.67</v>
       </c>
+      <c r="L148" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P148" s="4"/>
     </row>
     <row r="149" spans="1:16">
@@ -7094,6 +7121,9 @@
       <c r="J149" s="17">
         <v>0.35</v>
       </c>
+      <c r="L149" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P149" s="4"/>
     </row>
     <row r="150" spans="1:16">
@@ -7124,6 +7154,9 @@
       <c r="J150" s="17">
         <v>0.25</v>
       </c>
+      <c r="L150" s="17">
+        <v>0</v>
+      </c>
       <c r="P150" s="4"/>
     </row>
     <row r="151" spans="1:16">
@@ -7187,6 +7220,9 @@
       <c r="J152" s="17">
         <v>0.75</v>
       </c>
+      <c r="L152" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P152" s="4"/>
     </row>
     <row r="153" spans="1:16">
@@ -7250,6 +7286,9 @@
       <c r="J154" s="17">
         <v>0.16</v>
       </c>
+      <c r="L154" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P154" s="4"/>
     </row>
     <row r="155" spans="1:16">
@@ -7346,6 +7385,9 @@
       <c r="J157" s="17">
         <v>0.52</v>
       </c>
+      <c r="L157" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P157" s="4"/>
     </row>
     <row r="158" spans="1:16">
@@ -7376,6 +7418,9 @@
       <c r="J158" s="17">
         <v>0.46</v>
       </c>
+      <c r="L158" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P158" s="4"/>
     </row>
     <row r="159" spans="1:16">
@@ -7406,6 +7451,9 @@
       <c r="J159" s="17">
         <v>0.48</v>
       </c>
+      <c r="L159" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P159" s="4"/>
     </row>
     <row r="160" spans="1:16">
@@ -7436,6 +7484,9 @@
       <c r="J160" s="17">
         <v>0.49</v>
       </c>
+      <c r="L160" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P160" s="4"/>
     </row>
     <row r="161" spans="1:16">
@@ -7499,6 +7550,9 @@
       <c r="J162" s="17">
         <v>0.63</v>
       </c>
+      <c r="L162" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P162" s="4"/>
     </row>
     <row r="163" spans="1:16">
@@ -7595,6 +7649,9 @@
       <c r="J165" s="17">
         <v>0.38</v>
       </c>
+      <c r="L165" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P165" s="4"/>
     </row>
     <row r="166" spans="1:16">
@@ -7625,6 +7682,9 @@
       <c r="J166" s="17">
         <v>0.32</v>
       </c>
+      <c r="L166" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P166" s="4"/>
     </row>
     <row r="167" spans="1:16">
@@ -7655,6 +7715,9 @@
       <c r="J167" s="17">
         <v>0.44</v>
       </c>
+      <c r="L167" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P167" s="4"/>
     </row>
     <row r="168" spans="1:16">
@@ -7685,6 +7748,9 @@
       <c r="J168" s="17">
         <v>0.62</v>
       </c>
+      <c r="L168" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P168" s="4"/>
     </row>
     <row r="169" spans="1:16">
@@ -7715,6 +7781,9 @@
       <c r="J169" s="17">
         <v>0.48</v>
       </c>
+      <c r="L169" s="17">
+        <v>0</v>
+      </c>
       <c r="P169" s="4"/>
     </row>
     <row r="170" spans="1:16">
@@ -7778,6 +7847,9 @@
       <c r="J171" s="17">
         <v>0.3</v>
       </c>
+      <c r="L171" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P171" s="4"/>
     </row>
     <row r="172" spans="1:16">
@@ -7841,6 +7913,9 @@
       <c r="J173" s="17">
         <v>0</v>
       </c>
+      <c r="L173" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P173" s="4"/>
     </row>
     <row r="174" spans="1:16">
@@ -7871,6 +7946,9 @@
       <c r="J174" s="17">
         <v>0.05</v>
       </c>
+      <c r="L174" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P174" s="4"/>
     </row>
     <row r="175" spans="1:16">
@@ -7901,6 +7979,9 @@
       <c r="J175" s="17">
         <v>0.33</v>
       </c>
+      <c r="L175" s="17">
+        <v>0.54</v>
+      </c>
       <c r="P175" s="4"/>
     </row>
     <row r="176" spans="1:16">
@@ -7931,6 +8012,9 @@
       <c r="J176" s="17">
         <v>0.41</v>
       </c>
+      <c r="L176" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P176" s="4"/>
     </row>
     <row r="177" spans="1:16">
@@ -7961,6 +8045,9 @@
       <c r="J177" s="17">
         <v>0.44</v>
       </c>
+      <c r="L177" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P177" s="4"/>
     </row>
     <row r="178" spans="1:16">
@@ -7991,6 +8078,9 @@
       <c r="J178" s="17">
         <v>0.27</v>
       </c>
+      <c r="L178" s="17">
+        <v>0</v>
+      </c>
       <c r="P178" s="4"/>
     </row>
     <row r="179" spans="1:16">
@@ -8087,6 +8177,9 @@
       <c r="J181" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="L181" s="17">
+        <v>0.61</v>
+      </c>
       <c r="P181" s="4"/>
     </row>
     <row r="182" spans="1:16">
@@ -8149,6 +8242,9 @@
       </c>
       <c r="J183" s="17">
         <v>0.4</v>
+      </c>
+      <c r="L183" s="17">
+        <v>0.51</v>
       </c>
       <c r="P183" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCF7B5A-C85F-C142-B9B7-47DA04B42398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F41265-9A1C-4A42-B9FD-40E966CAECDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6629,6 +6629,9 @@
       <c r="L134" s="17">
         <v>0.96</v>
       </c>
+      <c r="M134" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
@@ -6695,6 +6698,9 @@
       <c r="L136" s="17">
         <v>0.96</v>
       </c>
+      <c r="M136" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
@@ -6761,6 +6767,9 @@
       <c r="L138" s="17">
         <v>0.63</v>
       </c>
+      <c r="M138" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
@@ -6794,6 +6803,9 @@
       <c r="L139" s="17">
         <v>0.8</v>
       </c>
+      <c r="M139" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
@@ -7025,6 +7037,9 @@
       <c r="L146" s="17">
         <v>0.63</v>
       </c>
+      <c r="M146" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P146" s="4"/>
     </row>
     <row r="147" spans="1:16">
@@ -7058,6 +7073,9 @@
       <c r="L147" s="17">
         <v>0.96</v>
       </c>
+      <c r="M147" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P147" s="4"/>
     </row>
     <row r="148" spans="1:16">
@@ -7190,6 +7208,9 @@
       <c r="L151" s="17">
         <v>0.8</v>
       </c>
+      <c r="M151" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P151" s="4"/>
     </row>
     <row r="152" spans="1:16">
@@ -7256,6 +7277,9 @@
       <c r="L153" s="17">
         <v>0.63</v>
       </c>
+      <c r="M153" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P153" s="4"/>
     </row>
     <row r="154" spans="1:16">
@@ -7322,6 +7346,9 @@
       <c r="L155" s="17">
         <v>0.96</v>
       </c>
+      <c r="M155" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P155" s="4"/>
     </row>
     <row r="156" spans="1:16">
@@ -7355,6 +7382,9 @@
       <c r="L156" s="17">
         <v>0.8</v>
       </c>
+      <c r="M156" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P156" s="4"/>
     </row>
     <row r="157" spans="1:16">
@@ -7520,6 +7550,9 @@
       <c r="L161" s="17">
         <v>0.63</v>
       </c>
+      <c r="M161" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P161" s="4"/>
     </row>
     <row r="162" spans="1:16">
@@ -7586,6 +7619,9 @@
       <c r="L163" s="17">
         <v>0.96</v>
       </c>
+      <c r="M163" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P163" s="4"/>
     </row>
     <row r="164" spans="1:16">
@@ -7619,6 +7655,9 @@
       <c r="L164" s="17">
         <v>0.96</v>
       </c>
+      <c r="M164" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P164" s="4"/>
     </row>
     <row r="165" spans="1:16">
@@ -7817,6 +7856,9 @@
       <c r="L170" s="17">
         <v>0.8</v>
       </c>
+      <c r="M170" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P170" s="4"/>
     </row>
     <row r="171" spans="1:16">
@@ -7883,6 +7925,9 @@
       <c r="L172" s="17">
         <v>0.63</v>
       </c>
+      <c r="M172" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P172" s="4"/>
     </row>
     <row r="173" spans="1:16">
@@ -8114,6 +8159,9 @@
       <c r="L179" s="17">
         <v>0.8</v>
       </c>
+      <c r="M179" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P179" s="4"/>
     </row>
     <row r="180" spans="1:16">
@@ -8147,6 +8195,9 @@
       <c r="L180" s="17">
         <v>0.63</v>
       </c>
+      <c r="M180" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P180" s="4"/>
     </row>
     <row r="181" spans="1:16">
@@ -8212,6 +8263,9 @@
       </c>
       <c r="L182" s="17">
         <v>0.8</v>
+      </c>
+      <c r="M182" s="17">
+        <v>0.64</v>
       </c>
       <c r="P182" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F41265-9A1C-4A42-B9FD-40E966CAECDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC9D48C-C668-6C4A-AF08-B9EBEF188DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6905,6 +6905,9 @@
       <c r="L142" s="17">
         <v>0.61</v>
       </c>
+      <c r="M142" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
@@ -6971,6 +6974,9 @@
       <c r="L144" s="17">
         <v>0.83</v>
       </c>
+      <c r="M144" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P144" s="4"/>
     </row>
     <row r="145" spans="1:16">
@@ -7244,6 +7250,9 @@
       <c r="L152" s="17">
         <v>0.83</v>
       </c>
+      <c r="M152" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P152" s="4"/>
     </row>
     <row r="153" spans="1:16">
@@ -7418,6 +7427,9 @@
       <c r="L157" s="17">
         <v>0.61</v>
       </c>
+      <c r="M157" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P157" s="4"/>
     </row>
     <row r="158" spans="1:16">
@@ -7451,6 +7463,9 @@
       <c r="L158" s="17">
         <v>0.61</v>
       </c>
+      <c r="M158" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P158" s="4"/>
     </row>
     <row r="159" spans="1:16">
@@ -7484,6 +7499,9 @@
       <c r="L159" s="17">
         <v>0.83</v>
       </c>
+      <c r="M159" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P159" s="4"/>
     </row>
     <row r="160" spans="1:16">
@@ -7586,6 +7604,9 @@
       <c r="L162" s="17">
         <v>0.61</v>
       </c>
+      <c r="M162" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P162" s="4"/>
     </row>
     <row r="163" spans="1:16">
@@ -7724,6 +7745,9 @@
       <c r="L166" s="17">
         <v>0.83</v>
       </c>
+      <c r="M166" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P166" s="4"/>
     </row>
     <row r="167" spans="1:16">
@@ -7790,6 +7814,9 @@
       <c r="L168" s="17">
         <v>0.83</v>
       </c>
+      <c r="M168" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P168" s="4"/>
     </row>
     <row r="169" spans="1:16">
@@ -7892,6 +7919,9 @@
       <c r="L171" s="17">
         <v>0.61</v>
       </c>
+      <c r="M171" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P171" s="4"/>
     </row>
     <row r="172" spans="1:16">
@@ -8060,6 +8090,9 @@
       <c r="L176" s="17">
         <v>0.83</v>
       </c>
+      <c r="M176" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P176" s="4"/>
     </row>
     <row r="177" spans="1:16">
@@ -8230,6 +8263,9 @@
       </c>
       <c r="L181" s="17">
         <v>0.61</v>
+      </c>
+      <c r="M181" s="17">
+        <v>0.83</v>
       </c>
       <c r="P181" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC9D48C-C668-6C4A-AF08-B9EBEF188DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BA175C-5421-404B-8B34-95C91F9317C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4088,6 +4088,9 @@
       <c r="L57" s="17">
         <v>0.37</v>
       </c>
+      <c r="M57" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P57" s="4"/>
     </row>
     <row r="58" spans="1:16">
@@ -4319,6 +4322,9 @@
       <c r="L64" s="17">
         <v>0.37</v>
       </c>
+      <c r="M64" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P64" s="4"/>
     </row>
     <row r="65" spans="1:16">
@@ -4550,6 +4556,9 @@
       <c r="L71" s="17">
         <v>0.37</v>
       </c>
+      <c r="M71" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P71" s="4"/>
     </row>
     <row r="72" spans="1:16">
@@ -4880,6 +4889,9 @@
       <c r="L81" s="17">
         <v>0.37</v>
       </c>
+      <c r="M81" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P81" s="4"/>
     </row>
     <row r="82" spans="1:16">
@@ -4913,6 +4925,9 @@
       <c r="L82" s="17">
         <v>0.37</v>
       </c>
+      <c r="M82" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P82" s="4"/>
     </row>
     <row r="83" spans="1:16">
@@ -5078,6 +5093,9 @@
       <c r="L87" s="17">
         <v>0</v>
       </c>
+      <c r="M87" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P87" s="4"/>
     </row>
     <row r="88" spans="1:16">
@@ -6665,6 +6683,9 @@
       <c r="L135" s="17">
         <v>0.8</v>
       </c>
+      <c r="M135" s="17">
+        <v>0.9</v>
+      </c>
       <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
@@ -6734,6 +6755,9 @@
       <c r="L137" s="17">
         <v>0</v>
       </c>
+      <c r="M137" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
@@ -6839,6 +6863,9 @@
       <c r="L140" s="17">
         <v>0.61</v>
       </c>
+      <c r="M140" s="17">
+        <v>0</v>
+      </c>
       <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
@@ -6872,6 +6899,9 @@
       <c r="L141" s="17">
         <v>0.51</v>
       </c>
+      <c r="M141" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
@@ -6941,6 +6971,9 @@
       <c r="L143" s="17">
         <v>0</v>
       </c>
+      <c r="M143" s="17">
+        <v>0</v>
+      </c>
       <c r="P143" s="4"/>
     </row>
     <row r="144" spans="1:16">
@@ -7010,6 +7043,9 @@
       <c r="L145" s="17">
         <v>0.51</v>
       </c>
+      <c r="M145" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P145" s="4"/>
     </row>
     <row r="146" spans="1:16">
@@ -7115,6 +7151,9 @@
       <c r="L148" s="17">
         <v>0.51</v>
       </c>
+      <c r="M148" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P148" s="4"/>
     </row>
     <row r="149" spans="1:16">
@@ -7148,6 +7187,9 @@
       <c r="L149" s="17">
         <v>0.61</v>
       </c>
+      <c r="M149" s="17">
+        <v>0</v>
+      </c>
       <c r="P149" s="4"/>
     </row>
     <row r="150" spans="1:16">
@@ -7181,6 +7223,9 @@
       <c r="L150" s="17">
         <v>0</v>
       </c>
+      <c r="M150" s="17">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="P150" s="4"/>
     </row>
     <row r="151" spans="1:16">
@@ -7322,6 +7367,9 @@
       <c r="L154" s="17">
         <v>0.61</v>
       </c>
+      <c r="M154" s="17">
+        <v>0</v>
+      </c>
       <c r="P154" s="4"/>
     </row>
     <row r="155" spans="1:16">
@@ -7535,6 +7583,9 @@
       <c r="L160" s="17">
         <v>0.61</v>
       </c>
+      <c r="M160" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P160" s="4"/>
     </row>
     <row r="161" spans="1:16">
@@ -7712,6 +7763,9 @@
       <c r="L165" s="17">
         <v>0.51</v>
       </c>
+      <c r="M165" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P165" s="4"/>
     </row>
     <row r="166" spans="1:16">
@@ -7781,6 +7835,9 @@
       <c r="L167" s="17">
         <v>0.61</v>
       </c>
+      <c r="M167" s="17">
+        <v>0</v>
+      </c>
       <c r="P167" s="4"/>
     </row>
     <row r="168" spans="1:16">
@@ -7850,6 +7907,9 @@
       <c r="L169" s="17">
         <v>0</v>
       </c>
+      <c r="M169" s="17">
+        <v>0</v>
+      </c>
       <c r="P169" s="4"/>
     </row>
     <row r="170" spans="1:16">
@@ -7991,6 +8051,9 @@
       <c r="L173" s="17">
         <v>0.61</v>
       </c>
+      <c r="M173" s="17">
+        <v>0</v>
+      </c>
       <c r="P173" s="4"/>
     </row>
     <row r="174" spans="1:16">
@@ -8024,6 +8087,9 @@
       <c r="L174" s="17">
         <v>0.51</v>
       </c>
+      <c r="M174" s="17">
+        <v>0.6</v>
+      </c>
       <c r="P174" s="4"/>
     </row>
     <row r="175" spans="1:16">
@@ -8057,6 +8123,9 @@
       <c r="L175" s="17">
         <v>0.54</v>
       </c>
+      <c r="M175" s="17">
+        <v>0</v>
+      </c>
       <c r="P175" s="4"/>
     </row>
     <row r="176" spans="1:16">
@@ -8126,6 +8195,9 @@
       <c r="L177" s="17">
         <v>0.48</v>
       </c>
+      <c r="M177" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P177" s="4"/>
     </row>
     <row r="178" spans="1:16">
@@ -8159,6 +8231,9 @@
       <c r="L178" s="17">
         <v>0</v>
       </c>
+      <c r="M178" s="17">
+        <v>0</v>
+      </c>
       <c r="P178" s="4"/>
     </row>
     <row r="179" spans="1:16">
@@ -8335,6 +8410,9 @@
       </c>
       <c r="L183" s="17">
         <v>0.51</v>
+      </c>
+      <c r="M183" s="17">
+        <v>0.76</v>
       </c>
       <c r="P183" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BA175C-5421-404B-8B34-95C91F9317C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F153A16-7C12-EB46-8B61-CCBCED80AE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2258,6 +2258,9 @@
       <c r="F2" s="17">
         <v>0.77</v>
       </c>
+      <c r="G2" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H2" s="17">
         <v>0.89</v>
       </c>
@@ -2294,6 +2297,9 @@
       <c r="F3" s="17">
         <v>0.7</v>
       </c>
+      <c r="G3" s="17">
+        <v>0.86</v>
+      </c>
       <c r="H3" s="17">
         <v>0.39</v>
       </c>
@@ -2327,6 +2333,9 @@
       <c r="F4" s="17">
         <v>0.7</v>
       </c>
+      <c r="G4" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H4" s="17">
         <v>0.39</v>
       </c>
@@ -2360,6 +2369,9 @@
       <c r="F5" s="17">
         <v>0.7</v>
       </c>
+      <c r="G5" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H5" s="17">
         <v>0.54</v>
       </c>
@@ -2393,6 +2405,9 @@
       <c r="F6" s="17">
         <v>0.77</v>
       </c>
+      <c r="G6" s="17">
+        <v>0.8</v>
+      </c>
       <c r="H6" s="17">
         <v>0.53</v>
       </c>
@@ -2426,6 +2441,9 @@
       <c r="F7" s="17">
         <v>0.7</v>
       </c>
+      <c r="G7" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H7" s="17">
         <v>0.42</v>
       </c>
@@ -2459,6 +2477,9 @@
       <c r="F8" s="17">
         <v>0.52</v>
       </c>
+      <c r="G8" s="17">
+        <v>0.72</v>
+      </c>
       <c r="H8" s="17">
         <v>0.11</v>
       </c>
@@ -2492,6 +2513,9 @@
       <c r="F9" s="17">
         <v>0.77</v>
       </c>
+      <c r="G9" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H9" s="17">
         <v>0.47</v>
       </c>
@@ -2525,6 +2549,9 @@
       <c r="F10" s="17">
         <v>0.77</v>
       </c>
+      <c r="G10" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H10" s="17">
         <v>0.54</v>
       </c>
@@ -2558,6 +2585,9 @@
       <c r="F11" s="17">
         <v>0.66</v>
       </c>
+      <c r="G11" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H11" s="17">
         <v>0.16</v>
       </c>
@@ -2591,6 +2621,9 @@
       <c r="F12" s="17">
         <v>0.66</v>
       </c>
+      <c r="G12" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H12" s="17">
         <v>0.44</v>
       </c>
@@ -2624,6 +2657,9 @@
       <c r="F13" s="17">
         <v>0.7</v>
       </c>
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
       <c r="H13" s="17">
         <v>0.44</v>
       </c>
@@ -2657,6 +2693,9 @@
       <c r="F14" s="17">
         <v>0.66</v>
       </c>
+      <c r="G14" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H14" s="17">
         <v>0.4</v>
       </c>
@@ -2690,6 +2729,9 @@
       <c r="F15" s="17">
         <v>0.7</v>
       </c>
+      <c r="G15" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H15" s="17">
         <v>0.67</v>
       </c>
@@ -2723,6 +2765,9 @@
       <c r="F16" s="17">
         <v>0.7</v>
       </c>
+      <c r="G16" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H16" s="17">
         <v>0</v>
       </c>
@@ -2756,6 +2801,9 @@
       <c r="F17" s="17">
         <v>0.67</v>
       </c>
+      <c r="G17" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H17" s="17">
         <v>0.37</v>
       </c>
@@ -2789,6 +2837,9 @@
       <c r="F18" s="17">
         <v>0.67</v>
       </c>
+      <c r="G18" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H18" s="17">
         <v>0.44</v>
       </c>
@@ -2822,6 +2873,9 @@
       <c r="F19" s="17">
         <v>0</v>
       </c>
+      <c r="G19" s="17">
+        <v>0</v>
+      </c>
       <c r="H19" s="17">
         <v>0.53</v>
       </c>
@@ -2855,6 +2909,9 @@
       <c r="F20" s="17">
         <v>0.77</v>
       </c>
+      <c r="G20" s="17">
+        <v>0</v>
+      </c>
       <c r="H20" s="17">
         <v>0.54</v>
       </c>
@@ -2888,6 +2945,9 @@
       <c r="F21" s="17">
         <v>0.67</v>
       </c>
+      <c r="G21" s="17">
+        <v>0.75</v>
+      </c>
       <c r="H21" s="17">
         <v>0.65</v>
       </c>
@@ -2921,6 +2981,9 @@
       <c r="F22" s="17">
         <v>0.7</v>
       </c>
+      <c r="G22" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H22" s="17">
         <v>0.33</v>
       </c>
@@ -2954,6 +3017,9 @@
       <c r="F23" s="17">
         <v>0.67</v>
       </c>
+      <c r="G23" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H23" s="17">
         <v>0.68</v>
       </c>
@@ -2987,6 +3053,9 @@
       <c r="F24" s="17">
         <v>0.7</v>
       </c>
+      <c r="G24" s="17">
+        <v>0.75</v>
+      </c>
       <c r="H24" s="17">
         <v>0.67</v>
       </c>
@@ -3020,6 +3089,9 @@
       <c r="F25" s="17">
         <v>0.61</v>
       </c>
+      <c r="G25" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H25" s="17">
         <v>0.61</v>
       </c>
@@ -3053,6 +3125,9 @@
       <c r="F26" s="17">
         <v>0.67</v>
       </c>
+      <c r="G26" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H26" s="17">
         <v>0.53</v>
       </c>
@@ -3086,6 +3161,9 @@
       <c r="F27" s="17">
         <v>0.7</v>
       </c>
+      <c r="G27" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H27" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -3119,6 +3197,9 @@
       <c r="F28" s="17">
         <v>0.7</v>
       </c>
+      <c r="G28" s="17">
+        <v>0.8</v>
+      </c>
       <c r="H28" s="17">
         <v>0.63</v>
       </c>
@@ -3152,6 +3233,9 @@
       <c r="F29" s="17">
         <v>0.77</v>
       </c>
+      <c r="G29" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H29" s="17">
         <v>0.75</v>
       </c>
@@ -3185,6 +3269,9 @@
       <c r="F30" s="17">
         <v>0.7</v>
       </c>
+      <c r="G30" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H30" s="17">
         <v>0.35</v>
       </c>
@@ -3218,6 +3305,9 @@
       <c r="F31" s="17">
         <v>0.7</v>
       </c>
+      <c r="G31" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H31" s="17">
         <v>0.6</v>
       </c>
@@ -3251,6 +3341,9 @@
       <c r="F32" s="17">
         <v>0.7</v>
       </c>
+      <c r="G32" s="17">
+        <v>0.68</v>
+      </c>
       <c r="H32" s="17">
         <v>0.47</v>
       </c>
@@ -3284,6 +3377,9 @@
       <c r="F33" s="17">
         <v>0.7</v>
       </c>
+      <c r="G33" s="17">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="H33" s="17">
         <v>0.54</v>
       </c>
@@ -3317,6 +3413,9 @@
       <c r="F34" s="17">
         <v>0.77</v>
       </c>
+      <c r="G34" s="17">
+        <v>0</v>
+      </c>
       <c r="H34" s="17">
         <v>0.16</v>
       </c>
@@ -3350,6 +3449,9 @@
       <c r="F35" s="17">
         <v>0.7</v>
       </c>
+      <c r="G35" s="17">
+        <v>0.72</v>
+      </c>
       <c r="H35" s="17">
         <v>0.42</v>
       </c>
@@ -3383,6 +3485,9 @@
       <c r="F36" s="17">
         <v>0.63</v>
       </c>
+      <c r="G36" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H36" s="17">
         <v>0.47</v>
       </c>
@@ -3416,6 +3521,9 @@
       <c r="F37" s="17">
         <v>0</v>
       </c>
+      <c r="G37" s="17">
+        <v>0</v>
+      </c>
       <c r="H37" s="17">
         <v>0.77</v>
       </c>
@@ -3449,6 +3557,9 @@
       <c r="F38" s="17">
         <v>0</v>
       </c>
+      <c r="G38" s="17">
+        <v>0</v>
+      </c>
       <c r="H38" s="17">
         <v>0.52</v>
       </c>
@@ -3482,6 +3593,9 @@
       <c r="F39" s="17">
         <v>0.67</v>
       </c>
+      <c r="G39" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H39" s="17">
         <v>0.6</v>
       </c>
@@ -3515,6 +3629,9 @@
       <c r="F40" s="17">
         <v>0.7</v>
       </c>
+      <c r="G40" s="17">
+        <v>0.68</v>
+      </c>
       <c r="H40" s="17">
         <v>0.47</v>
       </c>
@@ -3548,6 +3665,9 @@
       <c r="F41" s="17">
         <v>0.7</v>
       </c>
+      <c r="G41" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H41" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -3581,6 +3701,9 @@
       <c r="F42" s="17">
         <v>0.77</v>
       </c>
+      <c r="G42" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H42" s="17">
         <v>0.33</v>
       </c>
@@ -3614,6 +3737,9 @@
       <c r="F43" s="17">
         <v>0</v>
       </c>
+      <c r="G43" s="17">
+        <v>0</v>
+      </c>
       <c r="H43" s="17">
         <v>0.54</v>
       </c>
@@ -3647,6 +3773,9 @@
       <c r="F44" s="17">
         <v>0</v>
       </c>
+      <c r="G44" s="17">
+        <v>0</v>
+      </c>
       <c r="H44" s="17">
         <v>0.65</v>
       </c>
@@ -3680,6 +3809,9 @@
       <c r="F45" s="17">
         <v>0.61</v>
       </c>
+      <c r="G45" s="17">
+        <v>0.72</v>
+      </c>
       <c r="H45" s="17">
         <v>0.44</v>
       </c>
@@ -3713,6 +3845,9 @@
       <c r="F46" s="17">
         <v>0.7</v>
       </c>
+      <c r="G46" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H46" s="17">
         <v>0.44</v>
       </c>
@@ -3746,6 +3881,9 @@
       <c r="F47" s="17">
         <v>0.67</v>
       </c>
+      <c r="G47" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H47" s="17">
         <v>0.54</v>
       </c>
@@ -3779,6 +3917,9 @@
       <c r="F48" s="17">
         <v>0.7</v>
       </c>
+      <c r="G48" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H48" s="17">
         <v>0.56000000000000005</v>
       </c>
@@ -3812,6 +3953,9 @@
       <c r="F49" s="17">
         <v>0.7</v>
       </c>
+      <c r="G49" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H49" s="17">
         <v>0.68</v>
       </c>
@@ -3845,6 +3989,9 @@
       <c r="F50" s="17">
         <v>0.7</v>
       </c>
+      <c r="G50" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H50" s="17">
         <v>0.75</v>
       </c>
@@ -3878,6 +4025,9 @@
       <c r="F51" s="17">
         <v>0.7</v>
       </c>
+      <c r="G51" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H51" s="17">
         <v>0.6</v>
       </c>
@@ -3911,6 +4061,9 @@
       <c r="F52" s="17">
         <v>0.77</v>
       </c>
+      <c r="G52" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H52" s="17">
         <v>0.54</v>
       </c>
@@ -3944,6 +4097,9 @@
       <c r="F53" s="17">
         <v>0.7</v>
       </c>
+      <c r="G53" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H53" s="17">
         <v>0.6</v>
       </c>
@@ -3977,6 +4133,9 @@
       <c r="F54" s="17">
         <v>0.67</v>
       </c>
+      <c r="G54" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H54" s="17">
         <v>0.33</v>
       </c>
@@ -4010,6 +4169,9 @@
       <c r="F55" s="17">
         <v>0.7</v>
       </c>
+      <c r="G55" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H55" s="17">
         <v>0.56000000000000005</v>
       </c>
@@ -4043,6 +4205,9 @@
       <c r="F56" s="17">
         <v>0.7</v>
       </c>
+      <c r="G56" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H56" s="17">
         <v>0.32</v>
       </c>
@@ -4076,6 +4241,9 @@
       <c r="F57" s="17">
         <v>0.7</v>
       </c>
+      <c r="G57" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H57" s="17">
         <v>0.51</v>
       </c>
@@ -4112,6 +4280,9 @@
       <c r="F58" s="17">
         <v>0.7</v>
       </c>
+      <c r="G58" s="17">
+        <v>0.61</v>
+      </c>
       <c r="H58" s="17">
         <v>0.32</v>
       </c>
@@ -4145,6 +4316,9 @@
       <c r="F59" s="17">
         <v>0.7</v>
       </c>
+      <c r="G59" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H59" s="17">
         <v>0.81</v>
       </c>
@@ -4178,6 +4352,9 @@
       <c r="F60" s="17">
         <v>0.61</v>
       </c>
+      <c r="G60" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H60" s="17">
         <v>0.46</v>
       </c>
@@ -4211,6 +4388,9 @@
       <c r="F61" s="17">
         <v>0.59</v>
       </c>
+      <c r="G61" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H61" s="17">
         <v>0.46</v>
       </c>
@@ -4244,6 +4424,9 @@
       <c r="F62" s="17">
         <v>0.77</v>
       </c>
+      <c r="G62" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H62" s="17">
         <v>0.37</v>
       </c>
@@ -4277,6 +4460,9 @@
       <c r="F63" s="17">
         <v>0.7</v>
       </c>
+      <c r="G63" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H63" s="17">
         <v>0.63</v>
       </c>
@@ -4310,6 +4496,9 @@
       <c r="F64" s="17">
         <v>0.7</v>
       </c>
+      <c r="G64" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H64" s="17">
         <v>0.37</v>
       </c>
@@ -4346,6 +4535,9 @@
       <c r="F65" s="17">
         <v>0.66</v>
       </c>
+      <c r="G65" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H65" s="17">
         <v>0.53</v>
       </c>
@@ -4379,6 +4571,9 @@
       <c r="F66" s="17">
         <v>0.67</v>
       </c>
+      <c r="G66" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H66" s="17">
         <v>0.35</v>
       </c>
@@ -4412,6 +4607,9 @@
       <c r="F67" s="17">
         <v>0.77</v>
       </c>
+      <c r="G67" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H67" s="17">
         <v>0.77</v>
       </c>
@@ -4445,6 +4643,9 @@
       <c r="F68" s="17">
         <v>0.7</v>
       </c>
+      <c r="G68" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H68" s="17">
         <v>0.6</v>
       </c>
@@ -4478,6 +4679,9 @@
       <c r="F69" s="17">
         <v>0.7</v>
       </c>
+      <c r="G69" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H69" s="17">
         <v>0.56000000000000005</v>
       </c>
@@ -4511,6 +4715,9 @@
       <c r="F70" s="17">
         <v>0.7</v>
       </c>
+      <c r="G70" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H70" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -4544,6 +4751,9 @@
       <c r="F71" s="17">
         <v>0.7</v>
       </c>
+      <c r="G71" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H71" s="17">
         <v>0.35</v>
       </c>
@@ -4580,6 +4790,9 @@
       <c r="F72" s="17">
         <v>0.7</v>
       </c>
+      <c r="G72" s="17">
+        <v>0.72</v>
+      </c>
       <c r="H72" s="17">
         <v>0.28000000000000003</v>
       </c>
@@ -4613,6 +4826,9 @@
       <c r="F73" s="17">
         <v>0.7</v>
       </c>
+      <c r="G73" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H73" s="17">
         <v>0.77</v>
       </c>
@@ -4646,6 +4862,9 @@
       <c r="F74" s="17">
         <v>0.66</v>
       </c>
+      <c r="G74" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H74" s="17">
         <v>0.51</v>
       </c>
@@ -4679,6 +4898,9 @@
       <c r="F75" s="17">
         <v>0.72</v>
       </c>
+      <c r="G75" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H75" s="17">
         <v>0.05</v>
       </c>
@@ -4712,6 +4934,9 @@
       <c r="F76" s="17">
         <v>0.77</v>
       </c>
+      <c r="G76" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H76" s="17">
         <v>0.61</v>
       </c>
@@ -4745,6 +4970,9 @@
       <c r="F77" s="17">
         <v>0.7</v>
       </c>
+      <c r="G77" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H77" s="17">
         <v>0.74</v>
       </c>
@@ -4778,6 +5006,9 @@
       <c r="F78" s="17">
         <v>0.7</v>
       </c>
+      <c r="G78" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H78" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -4811,6 +5042,9 @@
       <c r="F79" s="17">
         <v>0.7</v>
       </c>
+      <c r="G79" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H79" s="17">
         <v>0.61</v>
       </c>
@@ -4844,6 +5078,9 @@
       <c r="F80" s="17">
         <v>0.72</v>
       </c>
+      <c r="G80" s="17">
+        <v>0.79</v>
+      </c>
       <c r="H80" s="17">
         <v>0.47</v>
       </c>
@@ -4877,6 +5114,9 @@
       <c r="F81" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="G81" s="17">
+        <v>0</v>
+      </c>
       <c r="H81" s="17">
         <v>0.65</v>
       </c>
@@ -4913,6 +5153,9 @@
       <c r="F82" s="17">
         <v>0.7</v>
       </c>
+      <c r="G82" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H82" s="17">
         <v>0.39</v>
       </c>
@@ -4949,6 +5192,9 @@
       <c r="F83" s="17">
         <v>0.7</v>
       </c>
+      <c r="G83" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H83" s="17">
         <v>0.54</v>
       </c>
@@ -4982,6 +5228,9 @@
       <c r="F84" s="17">
         <v>0.67</v>
       </c>
+      <c r="G84" s="17">
+        <v>0</v>
+      </c>
       <c r="H84" s="17">
         <v>0.79</v>
       </c>
@@ -5015,6 +5264,9 @@
       <c r="F85" s="17">
         <v>0.7</v>
       </c>
+      <c r="G85" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H85" s="17">
         <v>0.63</v>
       </c>
@@ -5048,6 +5300,9 @@
       <c r="F86" s="17">
         <v>0.7</v>
       </c>
+      <c r="G86" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H86" s="17">
         <v>0.61</v>
       </c>
@@ -5081,6 +5336,9 @@
       <c r="F87" s="17">
         <v>0.7</v>
       </c>
+      <c r="G87" s="17">
+        <v>0.92</v>
+      </c>
       <c r="H87" s="17">
         <v>0.25</v>
       </c>
@@ -5117,6 +5375,9 @@
       <c r="F88" s="17">
         <v>0.67</v>
       </c>
+      <c r="G88" s="17">
+        <v>0.86</v>
+      </c>
       <c r="H88" s="17">
         <v>0.6</v>
       </c>
@@ -5150,6 +5411,9 @@
       <c r="F89" s="17">
         <v>0.77</v>
       </c>
+      <c r="G89" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H89" s="17">
         <v>0.54</v>
       </c>
@@ -5183,6 +5447,9 @@
       <c r="F90" s="17">
         <v>0.7</v>
       </c>
+      <c r="G90" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H90" s="17">
         <v>0.68</v>
       </c>
@@ -5216,6 +5483,9 @@
       <c r="F91" s="17">
         <v>0.7</v>
       </c>
+      <c r="G91" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H91" s="17">
         <v>0.6</v>
       </c>
@@ -5249,6 +5519,9 @@
       <c r="F92" s="17">
         <v>0.57999999999999996</v>
       </c>
+      <c r="G92" s="17">
+        <v>0.84</v>
+      </c>
       <c r="H92" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -5282,6 +5555,9 @@
       <c r="F93" s="17">
         <v>0.7</v>
       </c>
+      <c r="G93" s="17">
+        <v>0.79</v>
+      </c>
       <c r="H93" s="17">
         <v>0.47</v>
       </c>
@@ -5315,6 +5591,9 @@
       <c r="F94" s="17">
         <v>0.7</v>
       </c>
+      <c r="G94" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H94" s="17">
         <v>0.65</v>
       </c>
@@ -5348,6 +5627,9 @@
       <c r="F95" s="17">
         <v>0.7</v>
       </c>
+      <c r="G95" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H95" s="17">
         <v>0.42</v>
       </c>
@@ -5381,6 +5663,9 @@
       <c r="F96" s="17">
         <v>0.7</v>
       </c>
+      <c r="G96" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H96" s="17">
         <v>0.79</v>
       </c>
@@ -5414,6 +5699,9 @@
       <c r="F97" s="17">
         <v>0.7</v>
       </c>
+      <c r="G97" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H97" s="17">
         <v>0.46</v>
       </c>
@@ -5447,6 +5735,9 @@
       <c r="F98" s="17">
         <v>0</v>
       </c>
+      <c r="G98" s="17">
+        <v>0</v>
+      </c>
       <c r="H98" s="20">
         <v>0</v>
       </c>
@@ -5480,6 +5771,9 @@
       <c r="F99" s="17">
         <v>0.7</v>
       </c>
+      <c r="G99" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H99" s="17">
         <v>0.72</v>
       </c>
@@ -5513,6 +5807,9 @@
       <c r="F100" s="17">
         <v>0.77</v>
       </c>
+      <c r="G100" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H100" s="17">
         <v>0.28000000000000003</v>
       </c>
@@ -5546,6 +5843,9 @@
       <c r="F101" s="17">
         <v>0.7</v>
       </c>
+      <c r="G101" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H101" s="17">
         <v>0.4</v>
       </c>
@@ -5579,6 +5879,9 @@
       <c r="F102" s="17">
         <v>0.7</v>
       </c>
+      <c r="G102" s="17">
+        <v>0.72</v>
+      </c>
       <c r="H102" s="17">
         <v>0.44</v>
       </c>
@@ -5612,6 +5915,9 @@
       <c r="F103" s="17">
         <v>0.7</v>
       </c>
+      <c r="G103" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H103" s="17">
         <v>0.51</v>
       </c>
@@ -5645,6 +5951,9 @@
       <c r="F104" s="17">
         <v>0.53</v>
       </c>
+      <c r="G104" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H104" s="17">
         <v>0.49</v>
       </c>
@@ -5678,6 +5987,9 @@
       <c r="F105" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="G105" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H105" s="17">
         <v>0.54</v>
       </c>
@@ -5711,6 +6023,9 @@
       <c r="F106" s="17">
         <v>0.7</v>
       </c>
+      <c r="G106" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H106" s="17">
         <v>0.51</v>
       </c>
@@ -5744,6 +6059,9 @@
       <c r="F107" s="17">
         <v>0.72</v>
       </c>
+      <c r="G107" s="17">
+        <v>0.66</v>
+      </c>
       <c r="H107" s="17">
         <v>0.4</v>
       </c>
@@ -5777,6 +6095,9 @@
       <c r="F108" s="17">
         <v>0.66</v>
       </c>
+      <c r="G108" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H108" s="17">
         <v>0.44</v>
       </c>
@@ -5810,6 +6131,9 @@
       <c r="F109" s="17">
         <v>0.7</v>
       </c>
+      <c r="G109" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H109" s="17">
         <v>0.39</v>
       </c>
@@ -5843,6 +6167,9 @@
       <c r="F110" s="17">
         <v>0.66</v>
       </c>
+      <c r="G110" s="17">
+        <v>0.84</v>
+      </c>
       <c r="H110" s="17">
         <v>0.75</v>
       </c>
@@ -5876,6 +6203,9 @@
       <c r="F111" s="17">
         <v>0.7</v>
       </c>
+      <c r="G111" s="17">
+        <v>0</v>
+      </c>
       <c r="H111" s="17">
         <v>0.61</v>
       </c>
@@ -5909,6 +6239,9 @@
       <c r="F112" s="17">
         <v>0.7</v>
       </c>
+      <c r="G112" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H112" s="17">
         <v>0.26</v>
       </c>
@@ -5942,6 +6275,9 @@
       <c r="F113" s="17">
         <v>0.66</v>
       </c>
+      <c r="G113" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H113" s="17">
         <v>0.46</v>
       </c>
@@ -5975,6 +6311,9 @@
       <c r="F114" s="17">
         <v>0.7</v>
       </c>
+      <c r="G114" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H114" s="17">
         <v>0.42</v>
       </c>
@@ -6008,6 +6347,9 @@
       <c r="F115" s="17">
         <v>0.7</v>
       </c>
+      <c r="G115" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H115" s="17">
         <v>0.39</v>
       </c>
@@ -6041,6 +6383,9 @@
       <c r="F116" s="17">
         <v>0.7</v>
       </c>
+      <c r="G116" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H116" s="17">
         <v>0.46</v>
       </c>
@@ -6074,6 +6419,9 @@
       <c r="F117" s="17">
         <v>0.69</v>
       </c>
+      <c r="G117" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H117" s="17">
         <v>0.63</v>
       </c>
@@ -6107,6 +6455,9 @@
       <c r="F118" s="17">
         <v>0.7</v>
       </c>
+      <c r="G118" s="17">
+        <v>0</v>
+      </c>
       <c r="H118" s="17">
         <v>0.44</v>
       </c>
@@ -6140,6 +6491,9 @@
       <c r="F119" s="17">
         <v>0.72</v>
       </c>
+      <c r="G119" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H119" s="17">
         <v>0.54</v>
       </c>
@@ -6173,6 +6527,9 @@
       <c r="F120" s="17">
         <v>0.7</v>
       </c>
+      <c r="G120" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H120" s="17">
         <v>0.14000000000000001</v>
       </c>
@@ -6206,6 +6563,9 @@
       <c r="F121" s="17">
         <v>0.69</v>
       </c>
+      <c r="G121" s="17">
+        <v>0.75</v>
+      </c>
       <c r="H121" s="17">
         <v>0.26</v>
       </c>
@@ -6239,6 +6599,9 @@
       <c r="F122" s="17">
         <v>0.67</v>
       </c>
+      <c r="G122" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H122" s="17">
         <v>0.26</v>
       </c>
@@ -6272,6 +6635,9 @@
       <c r="F123" s="17">
         <v>0.63</v>
       </c>
+      <c r="G123" s="17">
+        <v>0.76</v>
+      </c>
       <c r="H123" s="17">
         <v>0.26</v>
       </c>
@@ -6305,6 +6671,9 @@
       <c r="F124" s="17">
         <v>0.66</v>
       </c>
+      <c r="G124" s="17">
+        <v>0.61</v>
+      </c>
       <c r="H124" s="17">
         <v>0.09</v>
       </c>
@@ -6338,6 +6707,9 @@
       <c r="F125" s="17">
         <v>0.7</v>
       </c>
+      <c r="G125" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H125" s="17">
         <v>0.49</v>
       </c>
@@ -6371,6 +6743,9 @@
       <c r="F126" s="17">
         <v>0.7</v>
       </c>
+      <c r="G126" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H126" s="17">
         <v>0.74</v>
       </c>
@@ -6404,6 +6779,9 @@
       <c r="F127" s="17">
         <v>0.77</v>
       </c>
+      <c r="G127" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H127" s="17">
         <v>0.26</v>
       </c>
@@ -6437,6 +6815,9 @@
       <c r="F128" s="17">
         <v>0.7</v>
       </c>
+      <c r="G128" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H128" s="17">
         <v>0.32</v>
       </c>
@@ -6470,6 +6851,9 @@
       <c r="F129" s="17">
         <v>0.7</v>
       </c>
+      <c r="G129" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H129" s="17">
         <v>0.11</v>
       </c>
@@ -6503,6 +6887,9 @@
       <c r="F130" s="17">
         <v>0.7</v>
       </c>
+      <c r="G130" s="17">
+        <v>0.84</v>
+      </c>
       <c r="H130" s="17">
         <v>0.65</v>
       </c>
@@ -6536,6 +6923,9 @@
       <c r="F131" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="G131" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H131" s="17">
         <v>0.28000000000000003</v>
       </c>
@@ -6569,6 +6959,9 @@
       <c r="F132" s="17">
         <v>0.7</v>
       </c>
+      <c r="G132" s="17">
+        <v>0.79</v>
+      </c>
       <c r="H132" s="17">
         <v>0.47</v>
       </c>
@@ -6602,6 +6995,9 @@
       <c r="F133" s="17">
         <v>0.67</v>
       </c>
+      <c r="G133" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H133" s="17">
         <v>0.35</v>
       </c>
@@ -6635,6 +7031,9 @@
       <c r="F134" s="17">
         <v>0.66</v>
       </c>
+      <c r="G134" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H134" s="17">
         <v>0.4</v>
       </c>
@@ -6671,6 +7070,9 @@
       <c r="F135" s="17">
         <v>0.77</v>
       </c>
+      <c r="G135" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H135" s="17">
         <v>0.56000000000000005</v>
       </c>
@@ -6707,6 +7109,9 @@
       <c r="F136" s="17">
         <v>0.7</v>
       </c>
+      <c r="G136" s="17">
+        <v>0.86</v>
+      </c>
       <c r="H136" s="17">
         <v>0.63</v>
       </c>
@@ -6743,6 +7148,9 @@
       <c r="F137" s="17">
         <v>0.73</v>
       </c>
+      <c r="G137" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H137" s="17">
         <v>0.42</v>
       </c>
@@ -6779,6 +7187,9 @@
       <c r="F138" s="17">
         <v>0.7</v>
       </c>
+      <c r="G138" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H138" s="17">
         <v>0.39</v>
       </c>
@@ -6815,6 +7226,9 @@
       <c r="F139" s="17">
         <v>0.73</v>
       </c>
+      <c r="G139" s="17">
+        <v>0</v>
+      </c>
       <c r="H139" s="17">
         <v>0.74</v>
       </c>
@@ -6851,6 +7265,9 @@
       <c r="F140" s="17">
         <v>0.7</v>
       </c>
+      <c r="G140" s="17">
+        <v>0.82</v>
+      </c>
       <c r="H140" s="17">
         <v>0.39</v>
       </c>
@@ -6887,6 +7304,9 @@
       <c r="F141" s="17">
         <v>0.7</v>
       </c>
+      <c r="G141" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H141" s="17">
         <v>0.51</v>
       </c>
@@ -6923,6 +7343,9 @@
       <c r="F142" s="17">
         <v>0.7</v>
       </c>
+      <c r="G142" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H142" s="17">
         <v>0.42</v>
       </c>
@@ -6959,6 +7382,9 @@
       <c r="F143" s="17">
         <v>0.64</v>
       </c>
+      <c r="G143" s="17">
+        <v>0.54</v>
+      </c>
       <c r="H143" s="17">
         <v>0</v>
       </c>
@@ -6995,6 +7421,9 @@
       <c r="F144" s="17">
         <v>0.73</v>
       </c>
+      <c r="G144" s="17">
+        <v>0.54</v>
+      </c>
       <c r="H144" s="17">
         <v>0.16</v>
       </c>
@@ -7031,6 +7460,9 @@
       <c r="F145" s="17">
         <v>0.47</v>
       </c>
+      <c r="G145" s="17">
+        <v>0.84</v>
+      </c>
       <c r="H145" s="17">
         <v>0.65</v>
       </c>
@@ -7067,6 +7499,9 @@
       <c r="F146" s="17">
         <v>0.7</v>
       </c>
+      <c r="G146" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H146" s="17">
         <v>0.4</v>
       </c>
@@ -7103,6 +7538,9 @@
       <c r="F147" s="17">
         <v>0.7</v>
       </c>
+      <c r="G147" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H147" s="17">
         <v>0.75</v>
       </c>
@@ -7139,6 +7577,9 @@
       <c r="F148" s="17">
         <v>0.7</v>
       </c>
+      <c r="G148" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H148" s="17">
         <v>0.63</v>
       </c>
@@ -7175,6 +7616,9 @@
       <c r="F149" s="17">
         <v>0.64</v>
       </c>
+      <c r="G149" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H149" s="17">
         <v>0.21</v>
       </c>
@@ -7211,6 +7655,9 @@
       <c r="F150" s="17">
         <v>0.67</v>
       </c>
+      <c r="G150" s="17">
+        <v>0</v>
+      </c>
       <c r="H150" s="17">
         <v>0.25</v>
       </c>
@@ -7247,6 +7694,9 @@
       <c r="F151" s="17">
         <v>0.67</v>
       </c>
+      <c r="G151" s="17">
+        <v>0.49</v>
+      </c>
       <c r="H151" s="17">
         <v>0.3</v>
       </c>
@@ -7283,6 +7733,9 @@
       <c r="F152" s="17">
         <v>0.57999999999999996</v>
       </c>
+      <c r="G152" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H152" s="17">
         <v>0.63</v>
       </c>
@@ -7319,6 +7772,9 @@
       <c r="F153" s="17">
         <v>0.73</v>
       </c>
+      <c r="G153" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H153" s="17">
         <v>0.86</v>
       </c>
@@ -7355,6 +7811,9 @@
       <c r="F154" s="17">
         <v>0.73</v>
       </c>
+      <c r="G154" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H154" s="17">
         <v>0.47</v>
       </c>
@@ -7391,6 +7850,9 @@
       <c r="F155" s="17">
         <v>0.7</v>
       </c>
+      <c r="G155" s="17">
+        <v>0.76</v>
+      </c>
       <c r="H155" s="17">
         <v>0.49</v>
       </c>
@@ -7427,6 +7889,9 @@
       <c r="F156" s="17">
         <v>0.64</v>
       </c>
+      <c r="G156" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H156" s="17">
         <v>0.44</v>
       </c>
@@ -7463,6 +7928,9 @@
       <c r="F157" s="17">
         <v>0.73</v>
       </c>
+      <c r="G157" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H157" s="17">
         <v>0.65</v>
       </c>
@@ -7499,6 +7967,9 @@
       <c r="F158" s="17">
         <v>0.67</v>
       </c>
+      <c r="G158" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H158" s="17">
         <v>0.6</v>
       </c>
@@ -7535,6 +8006,9 @@
       <c r="F159" s="17">
         <v>0.7</v>
       </c>
+      <c r="G159" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H159" s="17">
         <v>0.46</v>
       </c>
@@ -7571,6 +8045,9 @@
       <c r="F160" s="17">
         <v>0.67</v>
       </c>
+      <c r="G160" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H160" s="17">
         <v>0.42</v>
       </c>
@@ -7607,6 +8084,9 @@
       <c r="F161" s="17">
         <v>0.73</v>
       </c>
+      <c r="G161" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H161" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -7643,6 +8123,9 @@
       <c r="F162" s="17">
         <v>0.73</v>
       </c>
+      <c r="G162" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H162" s="17">
         <v>0.68</v>
       </c>
@@ -7679,6 +8162,9 @@
       <c r="F163" s="17">
         <v>0.7</v>
       </c>
+      <c r="G163" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H163" s="17">
         <v>0.51</v>
       </c>
@@ -7715,6 +8201,9 @@
       <c r="F164" s="17">
         <v>0.7</v>
       </c>
+      <c r="G164" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H164" s="17">
         <v>0.33</v>
       </c>
@@ -7751,6 +8240,9 @@
       <c r="F165" s="17">
         <v>0.64</v>
       </c>
+      <c r="G165" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H165" s="17">
         <v>0.18</v>
       </c>
@@ -7787,6 +8279,9 @@
       <c r="F166" s="17">
         <v>0.7</v>
       </c>
+      <c r="G166" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H166" s="17">
         <v>0.47</v>
       </c>
@@ -7823,6 +8318,9 @@
       <c r="F167" s="17">
         <v>0.67</v>
       </c>
+      <c r="G167" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H167" s="17">
         <v>0.63</v>
       </c>
@@ -7859,6 +8357,9 @@
       <c r="F168" s="17">
         <v>0.77</v>
       </c>
+      <c r="G168" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H168" s="17">
         <v>0.56000000000000005</v>
       </c>
@@ -7895,6 +8396,9 @@
       <c r="F169" s="17">
         <v>0.53</v>
       </c>
+      <c r="G169" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H169" s="17">
         <v>0.54</v>
       </c>
@@ -7931,6 +8435,9 @@
       <c r="F170" s="17">
         <v>0.66</v>
       </c>
+      <c r="G170" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H170" s="17">
         <v>0.3</v>
       </c>
@@ -7967,6 +8474,9 @@
       <c r="F171" s="17">
         <v>0.64</v>
       </c>
+      <c r="G171" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H171" s="17">
         <v>0.25</v>
       </c>
@@ -8003,6 +8513,9 @@
       <c r="F172" s="17">
         <v>0.77</v>
       </c>
+      <c r="G172" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H172" s="17">
         <v>0.39</v>
       </c>
@@ -8039,6 +8552,9 @@
       <c r="F173" s="17">
         <v>0.66</v>
       </c>
+      <c r="G173" s="17">
+        <v>0.64</v>
+      </c>
       <c r="H173" s="17">
         <v>0.35</v>
       </c>
@@ -8075,6 +8591,9 @@
       <c r="F174" s="17">
         <v>0.7</v>
       </c>
+      <c r="G174" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H174" s="17">
         <v>0.35</v>
       </c>
@@ -8111,6 +8630,9 @@
       <c r="F175" s="17">
         <v>0.7</v>
       </c>
+      <c r="G175" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H175" s="17">
         <v>0.33</v>
       </c>
@@ -8147,6 +8669,9 @@
       <c r="F176" s="17">
         <v>0.64</v>
       </c>
+      <c r="G176" s="17">
+        <v>0.59</v>
+      </c>
       <c r="H176" s="17">
         <v>0.12</v>
       </c>
@@ -8183,6 +8708,9 @@
       <c r="F177" s="17">
         <v>0.73</v>
       </c>
+      <c r="G177" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H177" s="17">
         <v>0.46</v>
       </c>
@@ -8219,6 +8747,9 @@
       <c r="F178" s="17">
         <v>0.67</v>
       </c>
+      <c r="G178" s="17">
+        <v>0.75</v>
+      </c>
       <c r="H178" s="17">
         <v>0.19</v>
       </c>
@@ -8255,6 +8786,9 @@
       <c r="F179" s="17">
         <v>0.7</v>
       </c>
+      <c r="G179" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H179" s="17">
         <v>0.42</v>
       </c>
@@ -8291,6 +8825,9 @@
       <c r="F180" s="17">
         <v>0.77</v>
       </c>
+      <c r="G180" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H180" s="17">
         <v>0.61</v>
       </c>
@@ -8327,6 +8864,9 @@
       <c r="F181" s="17">
         <v>0.73</v>
       </c>
+      <c r="G181" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H181" s="17">
         <v>0.53</v>
       </c>
@@ -8363,6 +8903,9 @@
       <c r="F182" s="17">
         <v>0.67</v>
       </c>
+      <c r="G182" s="17">
+        <v>0.79</v>
+      </c>
       <c r="H182" s="17">
         <v>0.35</v>
       </c>
@@ -8399,6 +8942,9 @@
       <c r="F183" s="17">
         <v>0.7</v>
       </c>
+      <c r="G183" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H183" s="17">
         <v>0.32</v>
       </c>
@@ -8435,6 +8981,9 @@
       <c r="F184" s="17">
         <v>0.7</v>
       </c>
+      <c r="G184" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H184" s="17">
         <v>0.26</v>
       </c>
@@ -8468,6 +9017,9 @@
       <c r="F185" s="17">
         <v>0.7</v>
       </c>
+      <c r="G185" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H185" s="17">
         <v>0.19</v>
       </c>
@@ -8501,6 +9053,9 @@
       <c r="F186" s="17">
         <v>0.7</v>
       </c>
+      <c r="G186" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H186" s="17">
         <v>0.35</v>
       </c>
@@ -8534,6 +9089,9 @@
       <c r="F187" s="17">
         <v>0</v>
       </c>
+      <c r="G187" s="17">
+        <v>0</v>
+      </c>
       <c r="H187" s="20">
         <v>0</v>
       </c>
@@ -8567,6 +9125,9 @@
       <c r="F188" s="17">
         <v>0.59</v>
       </c>
+      <c r="G188" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H188" s="20">
         <v>0</v>
       </c>
@@ -8600,6 +9161,9 @@
       <c r="F189" s="17">
         <v>0.7</v>
       </c>
+      <c r="G189" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H189" s="17">
         <v>0.63</v>
       </c>
@@ -8633,6 +9197,9 @@
       <c r="F190" s="17">
         <v>0.7</v>
       </c>
+      <c r="G190" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H190" s="17">
         <v>0.39</v>
       </c>
@@ -8666,6 +9233,9 @@
       <c r="F191" s="17">
         <v>0.7</v>
       </c>
+      <c r="G191" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H191" s="17">
         <v>0.68</v>
       </c>
@@ -8699,6 +9269,9 @@
       <c r="F192" s="17">
         <v>0.7</v>
       </c>
+      <c r="G192" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H192" s="17">
         <v>0.42</v>
       </c>
@@ -8732,6 +9305,9 @@
       <c r="F193" s="17">
         <v>0.7</v>
       </c>
+      <c r="G193" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H193" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -8765,6 +9341,9 @@
       <c r="F194" s="17">
         <v>0.52</v>
       </c>
+      <c r="G194" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H194" s="17">
         <v>0.6</v>
       </c>
@@ -8798,6 +9377,9 @@
       <c r="F195" s="17">
         <v>0.77</v>
       </c>
+      <c r="G195" s="17">
+        <v>0</v>
+      </c>
       <c r="H195" s="17">
         <v>0.04</v>
       </c>
@@ -8831,6 +9413,9 @@
       <c r="F196" s="17">
         <v>0.7</v>
       </c>
+      <c r="G196" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H196" s="17">
         <v>0.26</v>
       </c>
@@ -8864,6 +9449,9 @@
       <c r="F197" s="17">
         <v>0.7</v>
       </c>
+      <c r="G197" s="17">
+        <v>0.87</v>
+      </c>
       <c r="H197" s="17">
         <v>0.54</v>
       </c>
@@ -8897,6 +9485,9 @@
       <c r="F198" s="17">
         <v>0.77</v>
       </c>
+      <c r="G198" s="17">
+        <v>0.72</v>
+      </c>
       <c r="H198" s="17">
         <v>0.51</v>
       </c>
@@ -8930,6 +9521,9 @@
       <c r="F199" s="17">
         <v>0.64</v>
       </c>
+      <c r="G199" s="17">
+        <v>0.62</v>
+      </c>
       <c r="H199" s="20">
         <v>0</v>
       </c>
@@ -8963,6 +9557,9 @@
       <c r="F200" s="17">
         <v>0.73</v>
       </c>
+      <c r="G200" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H200" s="17">
         <v>0.46</v>
       </c>
@@ -8996,6 +9593,9 @@
       <c r="F201" s="17">
         <v>0.67</v>
       </c>
+      <c r="G201" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H201" s="17">
         <v>0.67</v>
       </c>
@@ -9029,6 +9629,9 @@
       <c r="F202" s="17">
         <v>0.73</v>
       </c>
+      <c r="G202" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H202" s="17">
         <v>0.67</v>
       </c>
@@ -9062,6 +9665,9 @@
       <c r="F203" s="17">
         <v>0.7</v>
       </c>
+      <c r="G203" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H203" s="17">
         <v>0.37</v>
       </c>
@@ -9095,6 +9701,9 @@
       <c r="F204" s="17">
         <v>0.7</v>
       </c>
+      <c r="G204" s="17">
+        <v>0</v>
+      </c>
       <c r="H204" s="17">
         <v>0.6</v>
       </c>
@@ -9128,6 +9737,9 @@
       <c r="F205" s="17">
         <v>0.7</v>
       </c>
+      <c r="G205" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H205" s="17">
         <v>0.32</v>
       </c>
@@ -9161,6 +9773,9 @@
       <c r="F206" s="17">
         <v>0.7</v>
       </c>
+      <c r="G206" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H206" s="17">
         <v>0.37</v>
       </c>
@@ -9194,6 +9809,9 @@
       <c r="F207" s="17">
         <v>0.7</v>
       </c>
+      <c r="G207" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H207" s="17">
         <v>0.46</v>
       </c>
@@ -9227,6 +9845,9 @@
       <c r="F208" s="17">
         <v>0.7</v>
       </c>
+      <c r="G208" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H208" s="17">
         <v>0.3</v>
       </c>
@@ -9260,6 +9881,9 @@
       <c r="F209" s="17">
         <v>0.7</v>
       </c>
+      <c r="G209" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H209" s="17">
         <v>0.42</v>
       </c>
@@ -9293,6 +9917,9 @@
       <c r="F210" s="17">
         <v>0.67</v>
       </c>
+      <c r="G210" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H210" s="17">
         <v>0.39</v>
       </c>
@@ -9326,6 +9953,9 @@
       <c r="F211" s="17">
         <v>0</v>
       </c>
+      <c r="G211" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H211" s="17">
         <v>0.65</v>
       </c>
@@ -9359,6 +9989,9 @@
       <c r="F212" s="17">
         <v>0.77</v>
       </c>
+      <c r="G212" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H212" s="17">
         <v>0.44</v>
       </c>
@@ -9392,6 +10025,9 @@
       <c r="F213" s="17">
         <v>0.64</v>
       </c>
+      <c r="G213" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H213" s="17">
         <v>0.75</v>
       </c>
@@ -9425,6 +10061,9 @@
       <c r="F214" s="17">
         <v>0</v>
       </c>
+      <c r="G214" s="17">
+        <v>0.68</v>
+      </c>
       <c r="H214" s="17">
         <v>0.05</v>
       </c>
@@ -9458,6 +10097,9 @@
       <c r="F215" s="17">
         <v>0.77</v>
       </c>
+      <c r="G215" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H215" s="17">
         <v>0.53</v>
       </c>
@@ -9491,6 +10133,9 @@
       <c r="F216" s="17">
         <v>0.7</v>
       </c>
+      <c r="G216" s="17">
+        <v>0.67</v>
+      </c>
       <c r="H216" s="17">
         <v>0.32</v>
       </c>
@@ -9524,6 +10169,9 @@
       <c r="F217" s="17">
         <v>0.7</v>
       </c>
+      <c r="G217" s="17">
+        <v>0.61</v>
+      </c>
       <c r="H217" s="17">
         <v>0.44</v>
       </c>
@@ -9557,6 +10205,9 @@
       <c r="F218" s="17">
         <v>0.77</v>
       </c>
+      <c r="G218" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H218" s="17">
         <v>0.68</v>
       </c>
@@ -9590,6 +10241,9 @@
       <c r="F219" s="17">
         <v>0.67</v>
       </c>
+      <c r="G219" s="17">
+        <v>0.87</v>
+      </c>
       <c r="H219" s="17">
         <v>0.56000000000000005</v>
       </c>
@@ -9623,6 +10277,9 @@
       <c r="F220" s="17">
         <v>0.66</v>
       </c>
+      <c r="G220" s="17">
+        <v>0.91</v>
+      </c>
       <c r="H220" s="17">
         <v>0.65</v>
       </c>
@@ -9656,6 +10313,9 @@
       <c r="F221" s="17">
         <v>0.7</v>
       </c>
+      <c r="G221" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H221" s="17">
         <v>0.79</v>
       </c>
@@ -9689,6 +10349,9 @@
       <c r="F222" s="17">
         <v>0.7</v>
       </c>
+      <c r="G222" s="17">
+        <v>0.8</v>
+      </c>
       <c r="H222" s="20">
         <v>0</v>
       </c>
@@ -9722,6 +10385,9 @@
       <c r="F223" s="17">
         <v>0.67</v>
       </c>
+      <c r="G223" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H223" s="17">
         <v>0.32</v>
       </c>
@@ -9755,6 +10421,9 @@
       <c r="F224" s="17">
         <v>0.7</v>
       </c>
+      <c r="G224" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H224" s="17">
         <v>0.54</v>
       </c>
@@ -9788,6 +10457,9 @@
       <c r="F225" s="17">
         <v>0</v>
       </c>
+      <c r="G225" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H225" s="17">
         <v>0.35</v>
       </c>
@@ -9821,6 +10493,9 @@
       <c r="F226" s="17">
         <v>0.67</v>
       </c>
+      <c r="G226" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H226" s="17">
         <v>0.11</v>
       </c>
@@ -9854,6 +10529,9 @@
       <c r="F227" s="17">
         <v>0.66</v>
       </c>
+      <c r="G227" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H227" s="17">
         <v>0.54</v>
       </c>
@@ -9887,6 +10565,9 @@
       <c r="F228" s="17">
         <v>0.7</v>
       </c>
+      <c r="G228" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H228" s="17">
         <v>0.61</v>
       </c>
@@ -9920,6 +10601,9 @@
       <c r="F229" s="17">
         <v>0.66</v>
       </c>
+      <c r="G229" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H229" s="17">
         <v>0.33</v>
       </c>
@@ -9952,6 +10636,9 @@
       <c r="F230" s="17">
         <v>0.7</v>
       </c>
+      <c r="G230" s="17">
+        <v>0.68</v>
+      </c>
       <c r="H230" s="17">
         <v>0.26</v>
       </c>
@@ -9985,6 +10672,9 @@
       <c r="F231" s="17">
         <v>0.77</v>
       </c>
+      <c r="G231" s="17">
+        <v>0.61</v>
+      </c>
       <c r="H231" s="20">
         <v>0</v>
       </c>
@@ -10017,6 +10707,9 @@
       <c r="F232" s="17">
         <v>0.7</v>
       </c>
+      <c r="G232" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H232" s="17">
         <v>0.16</v>
       </c>
@@ -10050,6 +10743,9 @@
       <c r="F233" s="17">
         <v>0.7</v>
       </c>
+      <c r="G233" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H233" s="17">
         <v>0.28000000000000003</v>
       </c>
@@ -10083,6 +10779,9 @@
       <c r="F234" s="17">
         <v>0.7</v>
       </c>
+      <c r="G234" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H234" s="17">
         <v>0.16</v>
       </c>
@@ -10115,6 +10814,9 @@
       <c r="F235" s="17">
         <v>0.7</v>
       </c>
+      <c r="G235" s="17">
+        <v>0.78</v>
+      </c>
       <c r="H235" s="17">
         <v>0.26</v>
       </c>
@@ -10147,6 +10849,9 @@
       <c r="F236" s="17">
         <v>0.66</v>
       </c>
+      <c r="G236" s="17">
+        <v>0</v>
+      </c>
       <c r="H236" s="17">
         <v>0.63</v>
       </c>
@@ -10180,6 +10885,9 @@
       <c r="F237" s="17">
         <v>0.7</v>
       </c>
+      <c r="G237" s="17">
+        <v>0.93</v>
+      </c>
       <c r="H237" s="17">
         <v>0.26</v>
       </c>
@@ -10213,6 +10921,9 @@
       <c r="F238" s="17">
         <v>0.66</v>
       </c>
+      <c r="G238" s="17">
+        <v>0.88</v>
+      </c>
       <c r="H238" s="17">
         <v>0.67</v>
       </c>
@@ -10246,6 +10957,9 @@
       <c r="F239" s="17">
         <v>0.7</v>
       </c>
+      <c r="G239" s="17">
+        <v>0.83</v>
+      </c>
       <c r="H239" s="17">
         <v>0.37</v>
       </c>
@@ -10279,6 +10993,9 @@
       <c r="F240" s="17">
         <v>0.73</v>
       </c>
+      <c r="G240" s="17">
+        <v>0</v>
+      </c>
       <c r="H240" s="17">
         <v>0.44</v>
       </c>
@@ -10312,6 +11029,9 @@
       <c r="F241" s="17">
         <v>0.7</v>
       </c>
+      <c r="G241" s="17">
+        <v>0</v>
+      </c>
       <c r="H241" s="17">
         <v>0.63</v>
       </c>
@@ -10345,6 +11065,9 @@
       <c r="F242" s="17">
         <v>0.77</v>
       </c>
+      <c r="G242" s="17">
+        <v>0.76</v>
+      </c>
       <c r="H242" s="17">
         <v>0.54</v>
       </c>
@@ -10377,6 +11100,9 @@
       <c r="F243" s="17">
         <v>0</v>
       </c>
+      <c r="G243" s="17">
+        <v>0.7</v>
+      </c>
       <c r="H243" s="17">
         <v>0.42</v>
       </c>
@@ -10409,6 +11135,9 @@
       <c r="F244" s="17">
         <v>0.73</v>
       </c>
+      <c r="G244" s="17">
+        <v>0.71</v>
+      </c>
       <c r="H244" s="17">
         <v>0.49</v>
       </c>
@@ -10441,6 +11170,9 @@
       <c r="F245" s="17">
         <v>0.7</v>
       </c>
+      <c r="G245" s="17">
+        <v>0.74</v>
+      </c>
       <c r="H245" s="17">
         <v>0.47</v>
       </c>
@@ -10473,6 +11205,9 @@
       </c>
       <c r="F246" s="17">
         <v>0.66</v>
+      </c>
+      <c r="G246" s="17">
+        <v>0.78</v>
       </c>
       <c r="H246" s="17">
         <v>0.19</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F153A16-7C12-EB46-8B61-CCBCED80AE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD7E76A-1090-F74F-B642-970BFE2E1498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4040,6 +4040,9 @@
       <c r="L51" s="17">
         <v>0.92</v>
       </c>
+      <c r="M51" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16">
@@ -4220,6 +4223,9 @@
       <c r="L56" s="17">
         <v>0.92</v>
       </c>
+      <c r="M56" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P56" s="4"/>
     </row>
     <row r="57" spans="1:16">
@@ -4259,7 +4265,7 @@
       <c r="M57" s="17">
         <v>0.76</v>
       </c>
-      <c r="P57" s="4"/>
+      <c r="P57" s="22"/>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="9" t="s">
@@ -4331,6 +4337,9 @@
       <c r="L59" s="17">
         <v>0.92</v>
       </c>
+      <c r="M59" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P59" s="4"/>
     </row>
     <row r="60" spans="1:16">
@@ -4694,6 +4703,9 @@
       <c r="L69" s="17">
         <v>0.92</v>
       </c>
+      <c r="M69" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P69" s="4"/>
     </row>
     <row r="70" spans="1:16">
@@ -4985,6 +4997,9 @@
       <c r="L77" s="17">
         <v>0.92</v>
       </c>
+      <c r="M77" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P77" s="4"/>
     </row>
     <row r="78" spans="1:16">
@@ -5056,6 +5071,9 @@
       </c>
       <c r="L79" s="17">
         <v>0.92</v>
+      </c>
+      <c r="M79" s="17">
+        <v>0.84</v>
       </c>
       <c r="P79" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD7E76A-1090-F74F-B642-970BFE2E1498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E30BABC-89C0-E04E-BDF2-A3418EABF410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -9624,7 +9624,7 @@
         <v>0.73</v>
       </c>
       <c r="L201" s="17">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="P201" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E30BABC-89C0-E04E-BDF2-A3418EABF410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB227637-32D3-A04C-B565-C524EF5E3B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2184,9 +2184,15 @@
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="7" width="10.7109375" style="17"/>
-    <col min="8" max="8" width="10.7109375" style="20"/>
-    <col min="9" max="15" width="10.7109375" style="17"/>
+    <col min="3" max="5" width="10.7109375" style="17"/>
+    <col min="6" max="6" width="6.140625" style="17" customWidth="1"/>
+    <col min="7" max="7" width="7" style="17" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" style="20" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" style="17" customWidth="1"/>
+    <col min="11" max="11" width="5.140625" style="17" customWidth="1"/>
+    <col min="12" max="12" width="7.7109375" style="17" customWidth="1"/>
+    <col min="13" max="15" width="10.7109375" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3968,6 +3974,9 @@
       <c r="L49" s="17">
         <v>0</v>
       </c>
+      <c r="M49" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
@@ -4004,6 +4013,9 @@
       <c r="L50" s="17">
         <v>0.63</v>
       </c>
+      <c r="M50" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P50" s="4"/>
     </row>
     <row r="51" spans="1:16">
@@ -4079,6 +4091,9 @@
       <c r="L52" s="17">
         <v>0.83</v>
       </c>
+      <c r="M52" s="17">
+        <v>0.97</v>
+      </c>
       <c r="P52" s="4"/>
     </row>
     <row r="53" spans="1:16">
@@ -4115,6 +4130,9 @@
       <c r="L53" s="17">
         <v>0.79</v>
       </c>
+      <c r="M53" s="17">
+        <v>0.9</v>
+      </c>
       <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16">
@@ -4151,6 +4169,9 @@
       <c r="L54" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="M54" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P54" s="4"/>
     </row>
     <row r="55" spans="1:16">
@@ -4187,6 +4208,9 @@
       <c r="L55" s="17">
         <v>0.83</v>
       </c>
+      <c r="M55" s="17">
+        <v>0.97</v>
+      </c>
       <c r="P55" s="4"/>
     </row>
     <row r="56" spans="1:16">
@@ -4301,6 +4325,9 @@
       <c r="L58" s="17">
         <v>0</v>
       </c>
+      <c r="M58" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P58" s="4"/>
     </row>
     <row r="59" spans="1:16">
@@ -4334,13 +4361,16 @@
       <c r="J59" s="17">
         <v>0.68</v>
       </c>
+      <c r="K59" s="17">
+        <v>0</v>
+      </c>
       <c r="L59" s="17">
         <v>0.92</v>
       </c>
       <c r="M59" s="17">
         <v>0.84</v>
       </c>
-      <c r="P59" s="4"/>
+      <c r="P59" s="22"/>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="9" t="s">
@@ -4376,6 +4406,9 @@
       <c r="L60" s="17">
         <v>0.83</v>
       </c>
+      <c r="M60" s="17">
+        <v>0.97</v>
+      </c>
       <c r="P60" s="4"/>
     </row>
     <row r="61" spans="1:16">
@@ -4412,6 +4445,9 @@
       <c r="L61" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="M61" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P61" s="4"/>
     </row>
     <row r="62" spans="1:16">
@@ -4448,6 +4484,9 @@
       <c r="L62" s="17">
         <v>0.83</v>
       </c>
+      <c r="M62" s="17">
+        <v>0.97</v>
+      </c>
       <c r="P62" s="4"/>
     </row>
     <row r="63" spans="1:16">
@@ -4484,6 +4523,9 @@
       <c r="L63" s="17">
         <v>0.63</v>
       </c>
+      <c r="M63" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P63" s="4"/>
     </row>
     <row r="64" spans="1:16">
@@ -4559,6 +4601,9 @@
       <c r="L65" s="17">
         <v>0.79</v>
       </c>
+      <c r="M65" s="17">
+        <v>0.9</v>
+      </c>
       <c r="P65" s="4"/>
     </row>
     <row r="66" spans="1:16">
@@ -4595,6 +4640,9 @@
       <c r="L66" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="M66" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P66" s="4"/>
     </row>
     <row r="67" spans="1:16">
@@ -4631,6 +4679,9 @@
       <c r="L67" s="17">
         <v>0.83</v>
       </c>
+      <c r="M67" s="17">
+        <v>0.97</v>
+      </c>
       <c r="P67" s="4"/>
     </row>
     <row r="68" spans="1:16">
@@ -4667,6 +4718,9 @@
       <c r="L68" s="17">
         <v>0.79</v>
       </c>
+      <c r="M68" s="17">
+        <v>0.9</v>
+      </c>
       <c r="P68" s="4"/>
     </row>
     <row r="69" spans="1:16">
@@ -4742,6 +4796,9 @@
       <c r="L70" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="M70" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P70" s="4"/>
     </row>
     <row r="71" spans="1:16">
@@ -4817,6 +4874,9 @@
       <c r="L72" s="17">
         <v>0.79</v>
       </c>
+      <c r="M72" s="17">
+        <v>0.9</v>
+      </c>
       <c r="P72" s="4"/>
     </row>
     <row r="73" spans="1:16">
@@ -4853,6 +4913,9 @@
       <c r="L73" s="17">
         <v>0.83</v>
       </c>
+      <c r="M73" s="17">
+        <v>0.97</v>
+      </c>
       <c r="P73" s="4"/>
     </row>
     <row r="74" spans="1:16">
@@ -4889,6 +4952,9 @@
       <c r="L74" s="17">
         <v>0</v>
       </c>
+      <c r="M74" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P74" s="4"/>
     </row>
     <row r="75" spans="1:16">
@@ -4925,6 +4991,9 @@
       <c r="L75" s="17">
         <v>0</v>
       </c>
+      <c r="M75" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P75" s="4"/>
     </row>
     <row r="76" spans="1:16">
@@ -4961,6 +5030,9 @@
       <c r="L76" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="M76" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P76" s="4"/>
     </row>
     <row r="77" spans="1:16">
@@ -5036,6 +5108,9 @@
       <c r="L78" s="17">
         <v>0</v>
       </c>
+      <c r="M78" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P78" s="4"/>
     </row>
     <row r="79" spans="1:16">
@@ -5111,6 +5186,9 @@
       <c r="L80" s="17">
         <v>0.63</v>
       </c>
+      <c r="M80" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P80" s="4"/>
     </row>
     <row r="81" spans="1:16">
@@ -5225,6 +5303,9 @@
       <c r="L83" s="17">
         <v>0.63</v>
       </c>
+      <c r="M83" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P83" s="4"/>
     </row>
     <row r="84" spans="1:16">
@@ -5261,6 +5342,9 @@
       <c r="L84" s="17">
         <v>0.79</v>
       </c>
+      <c r="M84" s="17">
+        <v>0.9</v>
+      </c>
       <c r="P84" s="4"/>
     </row>
     <row r="85" spans="1:16">
@@ -5297,6 +5381,9 @@
       <c r="L85" s="17">
         <v>0.63</v>
       </c>
+      <c r="M85" s="17">
+        <v>0.64</v>
+      </c>
       <c r="P85" s="4"/>
     </row>
     <row r="86" spans="1:16">
@@ -5333,6 +5420,9 @@
       <c r="L86" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="M86" s="17">
+        <v>0.72</v>
+      </c>
       <c r="P86" s="4"/>
     </row>
     <row r="87" spans="1:16">
@@ -5408,6 +5498,9 @@
       <c r="L88" s="17">
         <v>0.79</v>
       </c>
+      <c r="M88" s="17">
+        <v>0.9</v>
+      </c>
       <c r="P88" s="4"/>
     </row>
     <row r="89" spans="1:16">
@@ -5443,6 +5536,9 @@
       </c>
       <c r="L89" s="17">
         <v>0</v>
+      </c>
+      <c r="M89" s="17">
+        <v>0.72</v>
       </c>
       <c r="P89" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB227637-32D3-A04C-B565-C524EF5E3B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65C4763-CEFA-C844-82AF-5C7EBBB1CD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2675,6 +2675,9 @@
       <c r="J13" s="17">
         <v>0.46</v>
       </c>
+      <c r="K13" s="17">
+        <v>0.82</v>
+      </c>
       <c r="L13" s="17">
         <v>0.48</v>
       </c>
@@ -2711,6 +2714,9 @@
       <c r="J14" s="17">
         <v>0.38</v>
       </c>
+      <c r="K14" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L14" s="17">
         <v>0.48</v>
       </c>
@@ -2819,6 +2825,9 @@
       <c r="J17" s="17">
         <v>0.25</v>
       </c>
+      <c r="K17" s="17">
+        <v>0.45</v>
+      </c>
       <c r="L17" s="17">
         <v>0.48</v>
       </c>
@@ -2963,6 +2972,9 @@
       <c r="J21" s="17">
         <v>0.41</v>
       </c>
+      <c r="K21" s="17">
+        <v>0.76</v>
+      </c>
       <c r="L21" s="17">
         <v>0.68</v>
       </c>
@@ -3071,6 +3083,9 @@
       <c r="J24" s="17">
         <v>0.78</v>
       </c>
+      <c r="K24" s="17">
+        <v>0.86</v>
+      </c>
       <c r="L24" s="17">
         <v>0.48</v>
       </c>
@@ -3431,6 +3446,9 @@
       <c r="J34" s="17">
         <v>0.3</v>
       </c>
+      <c r="K34" s="17">
+        <v>0.18</v>
+      </c>
       <c r="L34" s="17">
         <v>0</v>
       </c>
@@ -3503,6 +3521,9 @@
       <c r="J36" s="17">
         <v>0.28999999999999998</v>
       </c>
+      <c r="K36" s="17">
+        <v>0.12</v>
+      </c>
       <c r="L36" s="17">
         <v>0</v>
       </c>
@@ -3647,6 +3668,9 @@
       <c r="J40" s="17">
         <v>0.32</v>
       </c>
+      <c r="K40" s="17">
+        <v>0.71</v>
+      </c>
       <c r="L40" s="17">
         <v>0.8</v>
       </c>
@@ -3827,6 +3851,9 @@
       <c r="J45" s="17">
         <v>0.4</v>
       </c>
+      <c r="K45" s="17">
+        <v>0.69</v>
+      </c>
       <c r="L45" s="17">
         <v>0.8</v>
       </c>
@@ -3934,6 +3961,9 @@
       </c>
       <c r="J48" s="17">
         <v>0.56000000000000005</v>
+      </c>
+      <c r="K48" s="17">
+        <v>0.67</v>
       </c>
       <c r="L48" s="17">
         <v>0.8</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65C4763-CEFA-C844-82AF-5C7EBBB1CD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A5817A-89C0-9940-B437-88248E8BC3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3338,6 +3338,9 @@
       <c r="J31" s="17">
         <v>0.62</v>
       </c>
+      <c r="K31" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L31" s="17">
         <v>0.24</v>
       </c>
@@ -3410,6 +3413,9 @@
       <c r="J33" s="17">
         <v>0.21</v>
       </c>
+      <c r="K33" s="17">
+        <v>0.53</v>
+      </c>
       <c r="L33" s="17">
         <v>0.8</v>
       </c>
@@ -3485,6 +3491,9 @@
       <c r="J35" s="17">
         <v>0.62</v>
       </c>
+      <c r="K35" s="17">
+        <v>0.96</v>
+      </c>
       <c r="L35" s="17">
         <v>0.24</v>
       </c>
@@ -3707,6 +3716,9 @@
       <c r="J41" s="17">
         <v>0.52</v>
       </c>
+      <c r="K41" s="17">
+        <v>0.63</v>
+      </c>
       <c r="L41" s="17">
         <v>0.24</v>
       </c>
@@ -3743,6 +3755,9 @@
       <c r="J42" s="17">
         <v>0.33</v>
       </c>
+      <c r="K42" s="17">
+        <v>0.69</v>
+      </c>
       <c r="L42" s="17">
         <v>0.24</v>
       </c>
@@ -3890,6 +3905,9 @@
       <c r="J46" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="K46" s="17">
+        <v>0.73</v>
+      </c>
       <c r="L46" s="17">
         <v>0.24</v>
       </c>
@@ -3926,6 +3944,9 @@
       <c r="J47" s="17">
         <v>0.41</v>
       </c>
+      <c r="K47" s="17">
+        <v>0.33</v>
+      </c>
       <c r="L47" s="17">
         <v>0.24</v>
       </c>
@@ -4390,9 +4411,6 @@
       </c>
       <c r="J59" s="17">
         <v>0.68</v>
-      </c>
-      <c r="K59" s="17">
-        <v>0</v>
       </c>
       <c r="L59" s="17">
         <v>0.92</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A5817A-89C0-9940-B437-88248E8BC3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E4AE31-2EB2-7F4F-86A0-96BB0F3DF21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2351,6 +2351,9 @@
       <c r="J4" s="17">
         <v>0.27</v>
       </c>
+      <c r="K4" s="17">
+        <v>0.53</v>
+      </c>
       <c r="L4" s="17">
         <v>0.48</v>
       </c>
@@ -2459,6 +2462,9 @@
       <c r="J7" s="17">
         <v>0.41</v>
       </c>
+      <c r="K7" s="17">
+        <v>0.43</v>
+      </c>
       <c r="L7" s="17">
         <v>0.48</v>
       </c>
@@ -2531,6 +2537,9 @@
       <c r="J9" s="17">
         <v>0.33</v>
       </c>
+      <c r="K9" s="17">
+        <v>0.53</v>
+      </c>
       <c r="L9" s="17">
         <v>0.68</v>
       </c>
@@ -2639,6 +2648,9 @@
       <c r="J12" s="17">
         <v>0.54</v>
       </c>
+      <c r="K12" s="17">
+        <v>0.76</v>
+      </c>
       <c r="L12" s="17">
         <v>0.48</v>
       </c>
@@ -3011,6 +3023,9 @@
       <c r="J22" s="17">
         <v>0.7</v>
       </c>
+      <c r="K22" s="17">
+        <v>0.41</v>
+      </c>
       <c r="L22" s="17">
         <v>0.68</v>
       </c>
@@ -3047,6 +3062,9 @@
       <c r="J23" s="17">
         <v>0.67</v>
       </c>
+      <c r="K23" s="17">
+        <v>0.53</v>
+      </c>
       <c r="L23" s="17">
         <v>0.68</v>
       </c>
@@ -3301,6 +3319,9 @@
       </c>
       <c r="J30" s="17">
         <v>0</v>
+      </c>
+      <c r="K30" s="17">
+        <v>0.56999999999999995</v>
       </c>
       <c r="L30" s="17">
         <v>0.48</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E4AE31-2EB2-7F4F-86A0-96BB0F3DF21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0425F050-DCE1-2F4D-B63F-0FA3B14E6B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2315,6 +2315,9 @@
       <c r="J3" s="17">
         <v>0.17</v>
       </c>
+      <c r="K3" s="17">
+        <v>0.39</v>
+      </c>
       <c r="L3" s="17">
         <v>0.68</v>
       </c>
@@ -2390,6 +2393,9 @@
       <c r="J5" s="17">
         <v>0.21</v>
       </c>
+      <c r="K5" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L5" s="17">
         <v>0.48</v>
       </c>
@@ -2501,6 +2507,9 @@
       <c r="J8" s="17">
         <v>0.11</v>
       </c>
+      <c r="K8" s="17">
+        <v>0.1</v>
+      </c>
       <c r="L8" s="17">
         <v>0.8</v>
       </c>
@@ -2612,6 +2621,9 @@
       <c r="J11" s="17">
         <v>0.28999999999999998</v>
       </c>
+      <c r="K11" s="17">
+        <v>0.43</v>
+      </c>
       <c r="L11" s="17">
         <v>0.48</v>
       </c>
@@ -2801,6 +2813,9 @@
       <c r="J16" s="17">
         <v>0.33</v>
       </c>
+      <c r="K16" s="17">
+        <v>0.22</v>
+      </c>
       <c r="L16" s="17">
         <v>0.48</v>
       </c>
@@ -2876,6 +2891,9 @@
       <c r="J18" s="17">
         <v>0.67</v>
       </c>
+      <c r="K18" s="17">
+        <v>0.59</v>
+      </c>
       <c r="L18" s="17">
         <v>0.48</v>
       </c>
@@ -2948,6 +2966,9 @@
       <c r="J20" s="17">
         <v>0.65</v>
       </c>
+      <c r="K20" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L20" s="17">
         <v>0.48</v>
       </c>
@@ -3176,6 +3197,9 @@
       <c r="J26" s="17">
         <v>0.46</v>
       </c>
+      <c r="K26" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L26" s="17">
         <v>0.48</v>
       </c>
@@ -3211,6 +3235,9 @@
       </c>
       <c r="J27" s="17">
         <v>0.46</v>
+      </c>
+      <c r="K27" s="17">
+        <v>0.56999999999999995</v>
       </c>
       <c r="L27" s="17">
         <v>0.8</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0425F050-DCE1-2F4D-B63F-0FA3B14E6B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD78A314-A9ED-9141-8DC9-047445E02F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -10571,6 +10571,9 @@
       <c r="J222" s="17">
         <v>0</v>
       </c>
+      <c r="K222" s="17">
+        <v>0.45</v>
+      </c>
       <c r="L222" s="17">
         <v>0</v>
       </c>
@@ -10607,6 +10610,9 @@
       <c r="J223" s="17">
         <v>0.17</v>
       </c>
+      <c r="K223" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="L223" s="17">
         <v>0.52</v>
       </c>
@@ -10643,6 +10649,9 @@
       <c r="J224" s="17">
         <v>0.52</v>
       </c>
+      <c r="K224" s="17">
+        <v>0.49</v>
+      </c>
       <c r="L224" s="17">
         <v>0.52</v>
       </c>
@@ -10679,6 +10688,9 @@
       <c r="J225" s="17">
         <v>0.38</v>
       </c>
+      <c r="K225" s="17">
+        <v>0.73</v>
+      </c>
       <c r="L225" s="17">
         <v>0</v>
       </c>
@@ -10715,6 +10727,9 @@
       <c r="J226" s="17">
         <v>0.21</v>
       </c>
+      <c r="K226" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="L226" s="17">
         <v>0.52</v>
       </c>
@@ -10786,6 +10801,9 @@
       </c>
       <c r="J228" s="17">
         <v>0.33</v>
+      </c>
+      <c r="K228" s="17">
+        <v>0.65</v>
       </c>
       <c r="L228" s="17">
         <v>0.52</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD78A314-A9ED-9141-8DC9-047445E02F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21588E24-A186-154B-A647-EA3861CA989E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4148,6 +4148,9 @@
       <c r="J51" s="17">
         <v>0.76</v>
       </c>
+      <c r="K51" s="17">
+        <v>0.88</v>
+      </c>
       <c r="L51" s="17">
         <v>0.92</v>
       </c>
@@ -4304,6 +4307,9 @@
       <c r="J55" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="K55" s="17">
+        <v>0.69</v>
+      </c>
       <c r="L55" s="17">
         <v>0.83</v>
       </c>
@@ -4421,6 +4427,9 @@
       <c r="J58" s="17">
         <v>0.37</v>
       </c>
+      <c r="K58" s="17">
+        <v>0.82</v>
+      </c>
       <c r="L58" s="17">
         <v>0</v>
       </c>
@@ -4655,6 +4664,9 @@
       <c r="J64" s="17">
         <v>0.37</v>
       </c>
+      <c r="K64" s="17">
+        <v>0.59</v>
+      </c>
       <c r="L64" s="17">
         <v>0.37</v>
       </c>
@@ -4733,6 +4745,9 @@
       <c r="J66" s="17">
         <v>0.63</v>
       </c>
+      <c r="K66" s="17">
+        <v>0.35</v>
+      </c>
       <c r="L66" s="17">
         <v>0.55000000000000004</v>
       </c>
@@ -5240,6 +5255,9 @@
       <c r="J79" s="17">
         <v>0.63</v>
       </c>
+      <c r="K79" s="17">
+        <v>0.49</v>
+      </c>
       <c r="L79" s="17">
         <v>0.92</v>
       </c>
@@ -5395,6 +5413,9 @@
       </c>
       <c r="J83" s="17">
         <v>0.84</v>
+      </c>
+      <c r="K83" s="17">
+        <v>0.86</v>
       </c>
       <c r="L83" s="17">
         <v>0.63</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21588E24-A186-154B-A647-EA3861CA989E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADCD1FC-8B0D-8243-8ADF-CF81F72E2999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4308,7 +4308,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="K55" s="17">
-        <v>0.69</v>
+        <v>0.71</v>
       </c>
       <c r="L55" s="17">
         <v>0.83</v>
@@ -4388,6 +4388,9 @@
       <c r="J57" s="17">
         <v>0.32</v>
       </c>
+      <c r="K57" s="17">
+        <v>0.63</v>
+      </c>
       <c r="L57" s="17">
         <v>0.37</v>
       </c>
@@ -4428,7 +4431,7 @@
         <v>0.37</v>
       </c>
       <c r="K58" s="17">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="L58" s="17">
         <v>0</v>
@@ -4865,6 +4868,9 @@
       <c r="J69" s="17">
         <v>0.62</v>
       </c>
+      <c r="K69" s="17">
+        <v>0.9</v>
+      </c>
       <c r="L69" s="17">
         <v>0.92</v>
       </c>
@@ -5060,6 +5066,9 @@
       <c r="J74" s="17">
         <v>0.48</v>
       </c>
+      <c r="K74" s="17">
+        <v>0.63</v>
+      </c>
       <c r="L74" s="17">
         <v>0</v>
       </c>
@@ -5099,6 +5108,9 @@
       <c r="J75" s="17">
         <v>0.17</v>
       </c>
+      <c r="K75" s="17">
+        <v>0.82</v>
+      </c>
       <c r="L75" s="17">
         <v>0</v>
       </c>
@@ -5256,7 +5268,7 @@
         <v>0.63</v>
       </c>
       <c r="K79" s="17">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="L79" s="17">
         <v>0.92</v>
@@ -5415,7 +5427,7 @@
         <v>0.84</v>
       </c>
       <c r="K83" s="17">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="L83" s="17">
         <v>0.63</v>
@@ -10632,7 +10644,7 @@
         <v>0.17</v>
       </c>
       <c r="K223" s="17">
-        <v>0.56999999999999995</v>
+        <v>0.61</v>
       </c>
       <c r="L223" s="17">
         <v>0.52</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADCD1FC-8B0D-8243-8ADF-CF81F72E2999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31425868-71C6-D04E-8460-897A96DAEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4070,6 +4070,9 @@
       <c r="J49" s="17">
         <v>0.59</v>
       </c>
+      <c r="K49" s="17">
+        <v>0.78</v>
+      </c>
       <c r="L49" s="17">
         <v>0</v>
       </c>
@@ -4229,6 +4232,9 @@
       <c r="J53" s="17">
         <v>0.6</v>
       </c>
+      <c r="K53" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="L53" s="17">
         <v>0.79</v>
       </c>
@@ -4829,6 +4835,9 @@
       <c r="J68" s="17">
         <v>0.59</v>
       </c>
+      <c r="K68" s="17">
+        <v>0.82</v>
+      </c>
       <c r="L68" s="17">
         <v>0.79</v>
       </c>
@@ -4988,6 +4997,9 @@
       <c r="J72" s="17">
         <v>0.63</v>
       </c>
+      <c r="K72" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L72" s="17">
         <v>0.79</v>
       </c>
@@ -5150,6 +5162,9 @@
       <c r="J76" s="17">
         <v>0.7</v>
       </c>
+      <c r="K76" s="17">
+        <v>0.84</v>
+      </c>
       <c r="L76" s="17">
         <v>0.55000000000000004</v>
       </c>
@@ -5506,6 +5521,9 @@
       </c>
       <c r="J85" s="17">
         <v>0.49</v>
+      </c>
+      <c r="K85" s="17">
+        <v>0.8</v>
       </c>
       <c r="L85" s="17">
         <v>0.63</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31425868-71C6-D04E-8460-897A96DAEC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC98CECD-AE4F-C246-B7B3-7DFBC223D72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4595,6 +4595,9 @@
       <c r="J62" s="17">
         <v>0.51</v>
       </c>
+      <c r="K62" s="17">
+        <v>0.49</v>
+      </c>
       <c r="L62" s="17">
         <v>0.83</v>
       </c>
@@ -4634,6 +4637,9 @@
       <c r="J63" s="17">
         <v>0.68</v>
       </c>
+      <c r="K63" s="17">
+        <v>0.76</v>
+      </c>
       <c r="L63" s="17">
         <v>0.63</v>
       </c>
@@ -5603,6 +5609,9 @@
       <c r="J87" s="17">
         <v>0.25</v>
       </c>
+      <c r="K87" s="17">
+        <v>0.51</v>
+      </c>
       <c r="L87" s="17">
         <v>0</v>
       </c>
@@ -5642,6 +5651,9 @@
       <c r="J88" s="17">
         <v>0.37</v>
       </c>
+      <c r="K88" s="17">
+        <v>0.33</v>
+      </c>
       <c r="L88" s="17">
         <v>0.79</v>
       </c>
@@ -5680,6 +5692,9 @@
       </c>
       <c r="J89" s="17">
         <v>0.51</v>
+      </c>
+      <c r="K89" s="17">
+        <v>0.55000000000000004</v>
       </c>
       <c r="L89" s="17">
         <v>0</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC98CECD-AE4F-C246-B7B3-7DFBC223D72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA34B5F-9525-7843-A80E-88BE2C9E43AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1563,7 +1563,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -1630,8 +1630,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1642,6 +1649,12 @@
       <patternFill patternType="solid">
         <fgColor indexed="15"/>
         <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1715,7 +1728,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1756,6 +1769,12 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2276,6 +2295,7 @@
       <c r="J2" s="17">
         <v>0.78</v>
       </c>
+      <c r="K2" s="24"/>
       <c r="L2" s="17">
         <v>0.48</v>
       </c>
@@ -2432,6 +2452,7 @@
       <c r="J6" s="17">
         <v>0.51</v>
       </c>
+      <c r="K6" s="24"/>
       <c r="L6" s="17">
         <v>0.48</v>
       </c>
@@ -2585,6 +2606,7 @@
       <c r="J10" s="17">
         <v>0.71</v>
       </c>
+      <c r="K10" s="24"/>
       <c r="L10" s="17">
         <v>0.48</v>
       </c>
@@ -2777,6 +2799,7 @@
       <c r="J15" s="17">
         <v>0.51</v>
       </c>
+      <c r="K15" s="24"/>
       <c r="L15" s="17">
         <v>0.68</v>
       </c>
@@ -2930,6 +2953,7 @@
       <c r="J19" s="17">
         <v>0</v>
       </c>
+      <c r="K19" s="24"/>
       <c r="L19" s="17">
         <v>0</v>
       </c>
@@ -3161,6 +3185,7 @@
       <c r="J25" s="17">
         <v>0.59</v>
       </c>
+      <c r="K25" s="24"/>
       <c r="L25" s="17">
         <v>0.8</v>
       </c>
@@ -3275,6 +3300,7 @@
       <c r="J28" s="17">
         <v>0.52</v>
       </c>
+      <c r="K28" s="24"/>
       <c r="L28" s="17">
         <v>0.48</v>
       </c>
@@ -3311,6 +3337,7 @@
       <c r="J29" s="17">
         <v>0.7</v>
       </c>
+      <c r="K29" s="24"/>
       <c r="L29" s="17">
         <v>0.8</v>
       </c>
@@ -3425,6 +3452,7 @@
       <c r="J32" s="17">
         <v>0.49</v>
       </c>
+      <c r="K32" s="24"/>
       <c r="L32" s="17">
         <v>0.8</v>
       </c>
@@ -3617,6 +3645,7 @@
       <c r="J37" s="17">
         <v>0.49</v>
       </c>
+      <c r="K37" s="24"/>
       <c r="L37" s="17">
         <v>0</v>
       </c>
@@ -3653,6 +3682,7 @@
       <c r="J38" s="17">
         <v>0.48</v>
       </c>
+      <c r="K38" s="24"/>
       <c r="L38" s="17">
         <v>0</v>
       </c>
@@ -3689,6 +3719,7 @@
       <c r="J39" s="17">
         <v>0.59</v>
       </c>
+      <c r="K39" s="24"/>
       <c r="L39" s="17">
         <v>0.8</v>
       </c>
@@ -3842,6 +3873,7 @@
       <c r="J43" s="17">
         <v>0.4</v>
       </c>
+      <c r="K43" s="24"/>
       <c r="L43" s="17">
         <v>0</v>
       </c>
@@ -3878,6 +3910,7 @@
       <c r="J44" s="17">
         <v>0.25</v>
       </c>
+      <c r="K44" s="24"/>
       <c r="L44" s="17">
         <v>0</v>
       </c>
@@ -4112,6 +4145,9 @@
       <c r="J50" s="17">
         <v>0.27</v>
       </c>
+      <c r="K50" s="17">
+        <v>0.59</v>
+      </c>
       <c r="L50" s="17">
         <v>0.63</v>
       </c>
@@ -4193,6 +4229,9 @@
       <c r="J52" s="17">
         <v>0.84</v>
       </c>
+      <c r="K52" s="17">
+        <v>0.96</v>
+      </c>
       <c r="L52" s="17">
         <v>0.83</v>
       </c>
@@ -4274,6 +4313,7 @@
       <c r="J54" s="17">
         <v>0.4</v>
       </c>
+      <c r="K54" s="24"/>
       <c r="L54" s="17">
         <v>0.55000000000000004</v>
       </c>
@@ -4355,6 +4395,9 @@
       <c r="J56" s="17">
         <v>0.59</v>
       </c>
+      <c r="K56" s="17">
+        <v>0.69</v>
+      </c>
       <c r="L56" s="17">
         <v>0.92</v>
       </c>
@@ -4478,6 +4521,9 @@
       <c r="J59" s="17">
         <v>0.68</v>
       </c>
+      <c r="K59" s="17">
+        <v>0.9</v>
+      </c>
       <c r="L59" s="17">
         <v>0.92</v>
       </c>
@@ -4517,6 +4563,9 @@
       <c r="J60" s="17">
         <v>0.63</v>
       </c>
+      <c r="K60" s="17">
+        <v>0.61</v>
+      </c>
       <c r="L60" s="17">
         <v>0.83</v>
       </c>
@@ -4556,6 +4605,9 @@
       <c r="J61" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="K61" s="17">
+        <v>0.59</v>
+      </c>
       <c r="L61" s="17">
         <v>0.55000000000000004</v>
       </c>
@@ -4721,6 +4773,9 @@
       <c r="J65" s="17">
         <v>0.7</v>
       </c>
+      <c r="K65" s="17">
+        <v>0.86</v>
+      </c>
       <c r="L65" s="17">
         <v>0.79</v>
       </c>
@@ -4802,6 +4857,9 @@
       <c r="J67" s="17">
         <v>0.65</v>
       </c>
+      <c r="K67" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="L67" s="17">
         <v>0.83</v>
       </c>
@@ -4925,6 +4983,9 @@
       <c r="J70" s="17">
         <v>0.52</v>
       </c>
+      <c r="K70" s="17">
+        <v>0.71</v>
+      </c>
       <c r="L70" s="17">
         <v>0.55000000000000004</v>
       </c>
@@ -4964,6 +5025,9 @@
       <c r="J71" s="17">
         <v>0.38</v>
       </c>
+      <c r="K71" s="17">
+        <v>0.69</v>
+      </c>
       <c r="L71" s="17">
         <v>0.37</v>
       </c>
@@ -5045,6 +5109,9 @@
       <c r="J73" s="17">
         <v>0.79</v>
       </c>
+      <c r="K73" s="17">
+        <v>0.96</v>
+      </c>
       <c r="L73" s="17">
         <v>0.83</v>
       </c>
@@ -5210,6 +5277,9 @@
       <c r="J77" s="17">
         <v>0.68</v>
       </c>
+      <c r="K77" s="17">
+        <v>0.86</v>
+      </c>
       <c r="L77" s="17">
         <v>0.92</v>
       </c>
@@ -5249,6 +5319,9 @@
       <c r="J78" s="17">
         <v>0.41</v>
       </c>
+      <c r="K78" s="17">
+        <v>0.86</v>
+      </c>
       <c r="L78" s="17">
         <v>0</v>
       </c>
@@ -5330,6 +5403,7 @@
       <c r="J80" s="17">
         <v>0.51</v>
       </c>
+      <c r="K80" s="23"/>
       <c r="L80" s="17">
         <v>0.63</v>
       </c>
@@ -5569,6 +5643,9 @@
       </c>
       <c r="J86" s="17">
         <v>0.43</v>
+      </c>
+      <c r="K86" s="17">
+        <v>0.53</v>
       </c>
       <c r="L86" s="17">
         <v>0.55000000000000004</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA34B5F-9525-7843-A80E-88BE2C9E43AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCDAF34-94F0-D249-BDD2-A1C981DA6306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6064,6 +6064,9 @@
       <c r="J97" s="17">
         <v>0.71</v>
       </c>
+      <c r="K97" s="17">
+        <v>0.51</v>
+      </c>
       <c r="L97" s="17">
         <v>0.69</v>
       </c>
@@ -6172,6 +6175,9 @@
       <c r="J100" s="17">
         <v>0.4</v>
       </c>
+      <c r="K100" s="17">
+        <v>0.76</v>
+      </c>
       <c r="L100" s="17">
         <v>0.82</v>
       </c>
@@ -6208,6 +6214,9 @@
       <c r="J101" s="17">
         <v>0.44</v>
       </c>
+      <c r="K101" s="17">
+        <v>0.39</v>
+      </c>
       <c r="L101" s="17">
         <v>0.69</v>
       </c>
@@ -6244,6 +6253,9 @@
       <c r="J102" s="17">
         <v>0.65</v>
       </c>
+      <c r="K102" s="17">
+        <v>0.94</v>
+      </c>
       <c r="L102" s="17">
         <v>0.82</v>
       </c>
@@ -6280,6 +6292,9 @@
       <c r="J103" s="17">
         <v>0.71</v>
       </c>
+      <c r="K103" s="17">
+        <v>0.82</v>
+      </c>
       <c r="L103" s="17">
         <v>0.69</v>
       </c>
@@ -6352,6 +6367,9 @@
       <c r="J105" s="17">
         <v>0.44</v>
       </c>
+      <c r="K105" s="17">
+        <v>0.33</v>
+      </c>
       <c r="L105" s="17">
         <v>0.83</v>
       </c>
@@ -6712,6 +6730,9 @@
       <c r="J115" s="17">
         <v>0.48</v>
       </c>
+      <c r="K115" s="17">
+        <v>0.84</v>
+      </c>
       <c r="L115" s="17">
         <v>0.61</v>
       </c>
@@ -7251,6 +7272,9 @@
       </c>
       <c r="J130" s="17">
         <v>0.65</v>
+      </c>
+      <c r="K130" s="17">
+        <v>0.96</v>
       </c>
       <c r="L130" s="17">
         <v>0.82</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCDAF34-94F0-D249-BDD2-A1C981DA6306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE92C5EB-F5B9-5E45-90D3-0D5B7A811022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1451,9 +1451,6 @@
     <t>Kanyama</t>
   </si>
   <si>
-    <t>Munzvangi</t>
-  </si>
-  <si>
     <t>H250319B</t>
   </si>
   <si>
@@ -1557,6 +1554,9 @@
   </si>
   <si>
     <t>H230341Q</t>
+  </si>
+  <si>
+    <t>Munzvengi</t>
   </si>
 </sst>
 </file>
@@ -2225,28 +2225,28 @@
         <v>3</v>
       </c>
       <c r="D1" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>488</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="17" t="s">
         <v>489</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="I1" s="20" t="s">
         <v>490</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="J1" s="17" t="s">
         <v>491</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="K1" s="17" t="s">
         <v>492</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>493</v>
       </c>
       <c r="L1" s="17" t="s">
         <v>4</v>
@@ -2258,7 +2258,7 @@
         <v>6</v>
       </c>
       <c r="O1" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="P1" t="s">
         <v>2</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>482</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>483</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>63</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>84</v>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>478</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>479</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>90</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" t="s">
+        <v>479</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>90</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>90</v>
@@ -4327,7 +4327,7 @@
         <v>104</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C55" s="19" t="s">
         <v>93</v>
@@ -5848,6 +5848,9 @@
       <c r="J91" s="17">
         <v>0.54</v>
       </c>
+      <c r="K91" s="17">
+        <v>0.73</v>
+      </c>
       <c r="L91" s="17">
         <v>0.62</v>
       </c>
@@ -5855,10 +5858,10 @@
     </row>
     <row r="92" spans="1:16">
       <c r="A92" t="s">
+        <v>473</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="C92" s="17" t="s">
         <v>173</v>
@@ -5920,6 +5923,9 @@
       <c r="J93" s="17">
         <v>0.44</v>
       </c>
+      <c r="K93" s="17">
+        <v>0.82</v>
+      </c>
       <c r="L93" s="17">
         <v>0.62</v>
       </c>
@@ -6074,10 +6080,10 @@
     </row>
     <row r="98" spans="1:16">
       <c r="A98" t="s">
+        <v>494</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="C98" s="17" t="s">
         <v>173</v>
@@ -6380,7 +6386,7 @@
         <v>470</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C106" s="17" t="s">
         <v>173</v>
@@ -6478,6 +6484,9 @@
       <c r="J108" s="17">
         <v>0.32</v>
       </c>
+      <c r="K108" s="17">
+        <v>0.47</v>
+      </c>
       <c r="L108" s="17">
         <v>0.62</v>
       </c>
@@ -6658,6 +6667,9 @@
       <c r="J113" s="17">
         <v>0.32</v>
       </c>
+      <c r="K113" s="17">
+        <v>0.8</v>
+      </c>
       <c r="L113" s="17">
         <v>0.82</v>
       </c>
@@ -6805,6 +6817,9 @@
       <c r="J117" s="17">
         <v>0.38</v>
       </c>
+      <c r="K117" s="17">
+        <v>0.43</v>
+      </c>
       <c r="L117" s="17">
         <v>0.72</v>
       </c>
@@ -6884,10 +6899,10 @@
     </row>
     <row r="120" spans="1:16">
       <c r="A120" t="s">
-        <v>471</v>
+        <v>506</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C120" s="17" t="s">
         <v>173</v>
@@ -6912,6 +6927,9 @@
       </c>
       <c r="J120" s="17">
         <v>0.02</v>
+      </c>
+      <c r="K120" s="17">
+        <v>0.27</v>
       </c>
       <c r="L120" s="17">
         <v>0.72</v>
@@ -6949,6 +6967,9 @@
       <c r="J121" s="17">
         <v>0.63</v>
       </c>
+      <c r="K121" s="17">
+        <v>0.69</v>
+      </c>
       <c r="L121" s="17">
         <v>0.72</v>
       </c>
@@ -9449,10 +9470,10 @@
     </row>
     <row r="187" spans="1:16">
       <c r="A187" t="s">
+        <v>500</v>
+      </c>
+      <c r="B187" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="C187" s="17" t="s">
         <v>348</v>
@@ -9485,10 +9506,10 @@
     </row>
     <row r="188" spans="1:16">
       <c r="A188" t="s">
+        <v>504</v>
+      </c>
+      <c r="B188" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="C188" s="17" t="s">
         <v>348</v>
@@ -9881,10 +9902,10 @@
     </row>
     <row r="199" spans="1:16">
       <c r="A199" t="s">
+        <v>498</v>
+      </c>
+      <c r="B199" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="C199" s="17" t="s">
         <v>348</v>
@@ -10709,10 +10730,10 @@
     </row>
     <row r="222" spans="1:16">
       <c r="A222" t="s">
+        <v>502</v>
+      </c>
+      <c r="B222" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="C222" s="17" t="s">
         <v>407</v>
@@ -11050,10 +11071,10 @@
     </row>
     <row r="231" spans="1:16">
       <c r="A231" t="s">
+        <v>496</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="C231" s="17" t="s">
         <v>420</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE92C5EB-F5B9-5E45-90D3-0D5B7A811022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED716D1-E1E0-7C4E-8B30-6B95B6954B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -5443,6 +5443,7 @@
       <c r="J81" s="17">
         <v>0.78</v>
       </c>
+      <c r="K81" s="24"/>
       <c r="L81" s="17">
         <v>0.37</v>
       </c>
@@ -5482,6 +5483,7 @@
       <c r="J82" s="17">
         <v>0.48</v>
       </c>
+      <c r="K82" s="24"/>
       <c r="L82" s="17">
         <v>0.37</v>
       </c>
@@ -5563,6 +5565,7 @@
       <c r="J84" s="17">
         <v>0.68</v>
       </c>
+      <c r="K84" s="24"/>
       <c r="L84" s="17">
         <v>0.79</v>
       </c>
@@ -6523,6 +6526,9 @@
       <c r="J109" s="17">
         <v>0.35</v>
       </c>
+      <c r="K109" s="17">
+        <v>0.73</v>
+      </c>
       <c r="L109" s="17">
         <v>0.82</v>
       </c>
@@ -6631,6 +6637,9 @@
       <c r="J112" s="17">
         <v>0.65</v>
       </c>
+      <c r="K112" s="17">
+        <v>0.73</v>
+      </c>
       <c r="L112" s="17">
         <v>0.72</v>
       </c>
@@ -7006,6 +7015,9 @@
       <c r="J122" s="17">
         <v>0.67</v>
       </c>
+      <c r="K122" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L122" s="17">
         <v>0.83</v>
       </c>
@@ -7042,6 +7054,9 @@
       <c r="J123" s="17">
         <v>0.24</v>
       </c>
+      <c r="K123" s="17">
+        <v>0.27</v>
+      </c>
       <c r="L123" s="17">
         <v>0.62</v>
       </c>
@@ -7077,6 +7092,9 @@
       </c>
       <c r="J124" s="17">
         <v>0.48</v>
+      </c>
+      <c r="K124" s="17">
+        <v>0.63</v>
       </c>
       <c r="L124" s="17">
         <v>0.83</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED716D1-E1E0-7C4E-8B30-6B95B6954B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4FFE16-A18D-B04D-9FA2-14CCB398E8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -5815,6 +5815,9 @@
       <c r="J90" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="K90" s="17">
+        <v>0.76</v>
+      </c>
       <c r="L90" s="17">
         <v>0.82</v>
       </c>
@@ -5890,6 +5893,9 @@
       <c r="J92" s="17">
         <v>0.13</v>
       </c>
+      <c r="K92" s="17">
+        <v>0.22</v>
+      </c>
       <c r="L92" s="17">
         <v>0.72</v>
       </c>
@@ -6037,6 +6043,9 @@
       <c r="J96" s="17">
         <v>0.78</v>
       </c>
+      <c r="K96" s="17">
+        <v>0.8</v>
+      </c>
       <c r="L96" s="17">
         <v>0.61</v>
       </c>
@@ -6148,6 +6157,9 @@
       <c r="J99" s="17">
         <v>0.63</v>
       </c>
+      <c r="K99" s="17">
+        <v>0.67</v>
+      </c>
       <c r="L99" s="17">
         <v>0.82</v>
       </c>
@@ -6340,6 +6352,9 @@
       <c r="J104" s="17">
         <v>0.38</v>
       </c>
+      <c r="K104" s="17">
+        <v>0.86</v>
+      </c>
       <c r="L104" s="17">
         <v>0.72</v>
       </c>
@@ -6451,6 +6466,9 @@
       <c r="J107" s="17">
         <v>0.3</v>
       </c>
+      <c r="K107" s="17">
+        <v>0.47</v>
+      </c>
       <c r="L107" s="17">
         <v>0.69</v>
       </c>
@@ -6565,6 +6583,9 @@
       <c r="J110" s="17">
         <v>0.7</v>
       </c>
+      <c r="K110" s="17">
+        <v>0.84</v>
+      </c>
       <c r="L110" s="17">
         <v>0.72</v>
       </c>
@@ -6715,6 +6736,9 @@
       <c r="J114" s="17">
         <v>0.48</v>
       </c>
+      <c r="K114" s="17">
+        <v>0.69</v>
+      </c>
       <c r="L114" s="17">
         <v>0.83</v>
       </c>
@@ -6790,6 +6814,9 @@
       <c r="J116" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="K116" s="17">
+        <v>0.61</v>
+      </c>
       <c r="L116" s="17">
         <v>0.62</v>
       </c>
@@ -7132,6 +7159,9 @@
       <c r="J125" s="17">
         <v>0.51</v>
       </c>
+      <c r="K125" s="17">
+        <v>0.47</v>
+      </c>
       <c r="L125" s="17">
         <v>0.69</v>
       </c>
@@ -7240,6 +7270,9 @@
       <c r="J128" s="17">
         <v>0.79</v>
       </c>
+      <c r="K128" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L128" s="17">
         <v>0.83</v>
       </c>
@@ -7276,6 +7309,9 @@
       <c r="J129" s="17">
         <v>0.32</v>
       </c>
+      <c r="K129" s="17">
+        <v>0.73</v>
+      </c>
       <c r="L129" s="17">
         <v>0.61</v>
       </c>
@@ -7350,6 +7386,9 @@
       </c>
       <c r="J131" s="17">
         <v>0.52</v>
+      </c>
+      <c r="K131" s="17">
+        <v>0.69</v>
       </c>
       <c r="L131" s="17">
         <v>0.82</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4FFE16-A18D-B04D-9FA2-14CCB398E8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B43C888-8709-1847-B536-3A18DBC7808B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -11086,6 +11086,9 @@
       <c r="J229" s="17">
         <v>0.35</v>
       </c>
+      <c r="K229" s="17">
+        <v>0.73</v>
+      </c>
       <c r="L229" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -11121,6 +11124,9 @@
       <c r="J230" s="17">
         <v>0.22</v>
       </c>
+      <c r="K230" s="17">
+        <v>0.8</v>
+      </c>
       <c r="L230" s="17">
         <v>0.54</v>
       </c>
@@ -11157,6 +11163,9 @@
       <c r="J231" s="17">
         <v>0.71</v>
       </c>
+      <c r="K231" s="17">
+        <v>0.88</v>
+      </c>
       <c r="L231" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -11192,6 +11201,9 @@
       <c r="J232" s="17">
         <v>0.67</v>
       </c>
+      <c r="K232" s="17">
+        <v>0.94</v>
+      </c>
       <c r="L232" s="17">
         <v>0.69</v>
       </c>
@@ -11228,6 +11240,9 @@
       <c r="J233" s="17">
         <v>0.52</v>
       </c>
+      <c r="K233" s="17">
+        <v>0.69</v>
+      </c>
       <c r="L233" s="17">
         <v>0.57999999999999996</v>
       </c>
@@ -11264,6 +11279,9 @@
       <c r="J234" s="17">
         <v>0.25</v>
       </c>
+      <c r="K234" s="17">
+        <v>0.12</v>
+      </c>
       <c r="L234" s="17">
         <v>0.85</v>
       </c>
@@ -11299,6 +11317,9 @@
       <c r="J235" s="17">
         <v>0.43</v>
       </c>
+      <c r="K235" s="17">
+        <v>0.78</v>
+      </c>
       <c r="L235" s="17">
         <v>0.54</v>
       </c>
@@ -11334,6 +11355,7 @@
       <c r="J236" s="17">
         <v>0.79</v>
       </c>
+      <c r="K236" s="24"/>
       <c r="L236" s="17">
         <v>0.72</v>
       </c>
@@ -11370,6 +11392,9 @@
       <c r="J237" s="17">
         <v>0.62</v>
       </c>
+      <c r="K237" s="17">
+        <v>0.92</v>
+      </c>
       <c r="L237" s="17">
         <v>0.72</v>
       </c>
@@ -11406,6 +11431,7 @@
       <c r="J238" s="17">
         <v>0.6</v>
       </c>
+      <c r="K238" s="24"/>
       <c r="L238" s="17">
         <v>0.69</v>
       </c>
@@ -11442,6 +11468,9 @@
       <c r="J239" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="K239" s="17">
+        <v>0.47</v>
+      </c>
       <c r="L239" s="17">
         <v>0.72</v>
       </c>
@@ -11478,6 +11507,7 @@
       <c r="J240" s="17">
         <v>0.49</v>
       </c>
+      <c r="K240" s="24"/>
       <c r="L240" s="17">
         <v>0.54</v>
       </c>
@@ -11514,6 +11544,7 @@
       <c r="J241" s="17">
         <v>0.52</v>
       </c>
+      <c r="K241" s="24"/>
       <c r="L241" s="17">
         <v>0.69</v>
       </c>
@@ -11550,6 +11581,9 @@
       <c r="J242" s="17">
         <v>0.52</v>
       </c>
+      <c r="K242" s="17">
+        <v>0.76</v>
+      </c>
       <c r="L242" s="17">
         <v>0.54</v>
       </c>
@@ -11585,6 +11619,9 @@
       <c r="J243" s="17">
         <v>0.19</v>
       </c>
+      <c r="K243" s="17">
+        <v>0.71</v>
+      </c>
       <c r="L243" s="17">
         <v>0.85</v>
       </c>
@@ -11620,6 +11657,9 @@
       <c r="J244" s="17">
         <v>0.62</v>
       </c>
+      <c r="K244" s="17">
+        <v>0.63</v>
+      </c>
       <c r="L244" s="17">
         <v>0.69</v>
       </c>
@@ -11655,6 +11695,9 @@
       <c r="J245" s="17">
         <v>0.62</v>
       </c>
+      <c r="K245" s="17">
+        <v>0.88</v>
+      </c>
       <c r="L245" s="17">
         <v>0.72</v>
       </c>
@@ -11690,6 +11733,9 @@
       </c>
       <c r="J246" s="17">
         <v>0.37</v>
+      </c>
+      <c r="K246" s="17">
+        <v>0.86</v>
       </c>
       <c r="L246" s="17">
         <v>0.57999999999999996</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B43C888-8709-1847-B536-3A18DBC7808B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5E4E3B-C83C-7A45-8739-BD86818B4758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7732,6 +7732,9 @@
       <c r="J140" s="17">
         <v>0.3</v>
       </c>
+      <c r="K140" s="17">
+        <v>0.31</v>
+      </c>
       <c r="L140" s="17">
         <v>0.61</v>
       </c>
@@ -7849,6 +7852,9 @@
       <c r="J143" s="17">
         <v>0.33</v>
       </c>
+      <c r="K143" s="17">
+        <v>0.71</v>
+      </c>
       <c r="L143" s="17">
         <v>0</v>
       </c>
@@ -7927,6 +7933,9 @@
       <c r="J145" s="17">
         <v>0.54</v>
       </c>
+      <c r="K145" s="17">
+        <v>0.49</v>
+      </c>
       <c r="L145" s="17">
         <v>0.51</v>
       </c>
@@ -8122,6 +8131,9 @@
       <c r="J150" s="17">
         <v>0.25</v>
       </c>
+      <c r="K150" s="17">
+        <v>0.39</v>
+      </c>
       <c r="L150" s="17">
         <v>0</v>
       </c>
@@ -8200,6 +8212,9 @@
       <c r="J152" s="17">
         <v>0.75</v>
       </c>
+      <c r="K152" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L152" s="17">
         <v>0.83</v>
       </c>
@@ -8278,6 +8293,9 @@
       <c r="J154" s="17">
         <v>0.16</v>
       </c>
+      <c r="K154" s="17">
+        <v>0.8</v>
+      </c>
       <c r="L154" s="17">
         <v>0.61</v>
       </c>
@@ -8668,6 +8686,9 @@
       <c r="J164" s="17">
         <v>0.33</v>
       </c>
+      <c r="K164" s="17">
+        <v>0.41</v>
+      </c>
       <c r="L164" s="17">
         <v>0.96</v>
       </c>
@@ -8707,6 +8728,9 @@
       <c r="J165" s="17">
         <v>0.38</v>
       </c>
+      <c r="K165" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="L165" s="17">
         <v>0.51</v>
       </c>
@@ -8980,6 +9004,9 @@
       <c r="J172" s="17">
         <v>0.35</v>
       </c>
+      <c r="K172" s="17">
+        <v>0.16</v>
+      </c>
       <c r="L172" s="17">
         <v>0.63</v>
       </c>
@@ -9018,6 +9045,9 @@
       </c>
       <c r="J173" s="17">
         <v>0</v>
+      </c>
+      <c r="K173" s="17">
+        <v>0.2</v>
       </c>
       <c r="L173" s="17">
         <v>0.61</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5E4E3B-C83C-7A45-8739-BD86818B4758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2570997A-794B-5B4D-8D59-73560DF76CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -8254,6 +8254,9 @@
       <c r="J153" s="17">
         <v>0.73</v>
       </c>
+      <c r="K153" s="17">
+        <v>0.91</v>
+      </c>
       <c r="L153" s="17">
         <v>0.63</v>
       </c>
@@ -8452,6 +8455,9 @@
       <c r="J158" s="17">
         <v>0.46</v>
       </c>
+      <c r="K158" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="L158" s="17">
         <v>0.61</v>
       </c>
@@ -8530,6 +8536,9 @@
       <c r="J160" s="17">
         <v>0.49</v>
       </c>
+      <c r="K160" s="17">
+        <v>0.35</v>
+      </c>
       <c r="L160" s="17">
         <v>0.61</v>
       </c>
@@ -8770,6 +8779,9 @@
       <c r="J166" s="17">
         <v>0.32</v>
       </c>
+      <c r="K166" s="17">
+        <v>0.59</v>
+      </c>
       <c r="L166" s="17">
         <v>0.83</v>
       </c>
@@ -9127,6 +9139,9 @@
       <c r="J175" s="17">
         <v>0.33</v>
       </c>
+      <c r="K175" s="17">
+        <v>0.86</v>
+      </c>
       <c r="L175" s="17">
         <v>0.54</v>
       </c>
@@ -9399,6 +9414,9 @@
       </c>
       <c r="J182" s="17">
         <v>0.43</v>
+      </c>
+      <c r="K182" s="17">
+        <v>0.2</v>
       </c>
       <c r="L182" s="17">
         <v>0.8</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2570997A-794B-5B4D-8D59-73560DF76CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2050E75F-E96B-164F-B141-65FD34EFF99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7654,6 +7654,9 @@
       <c r="J138" s="17">
         <v>0.46</v>
       </c>
+      <c r="K138" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="L138" s="17">
         <v>0.63</v>
       </c>
@@ -8977,6 +8980,9 @@
       <c r="J171" s="17">
         <v>0.3</v>
       </c>
+      <c r="K171" s="17">
+        <v>0.14000000000000001</v>
+      </c>
       <c r="L171" s="17">
         <v>0.61</v>
       </c>
@@ -9100,6 +9106,9 @@
       <c r="J174" s="17">
         <v>0.05</v>
       </c>
+      <c r="K174" s="17">
+        <v>0.37</v>
+      </c>
       <c r="L174" s="17">
         <v>0.51</v>
       </c>
@@ -9181,6 +9190,9 @@
       <c r="J176" s="17">
         <v>0.41</v>
       </c>
+      <c r="K176" s="17">
+        <v>0.67</v>
+      </c>
       <c r="L176" s="17">
         <v>0.83</v>
       </c>
@@ -9219,6 +9231,9 @@
       </c>
       <c r="J177" s="17">
         <v>0.44</v>
+      </c>
+      <c r="K177" s="17">
+        <v>0.69</v>
       </c>
       <c r="L177" s="17">
         <v>0.48</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2050E75F-E96B-164F-B141-65FD34EFF99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F004B82-AD6A-7543-828C-8B399D5BA517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7897,6 +7897,9 @@
       <c r="J144" s="17">
         <v>0.43</v>
       </c>
+      <c r="K144" s="17">
+        <v>0.76</v>
+      </c>
       <c r="L144" s="17">
         <v>0.83</v>
       </c>
@@ -7978,6 +7981,9 @@
       <c r="J146" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="K146" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L146" s="17">
         <v>0.63</v>
       </c>
@@ -8176,6 +8182,9 @@
       <c r="J151" s="17">
         <v>0.4</v>
       </c>
+      <c r="K151" s="17">
+        <v>0.53</v>
+      </c>
       <c r="L151" s="17">
         <v>0.8</v>
       </c>
@@ -8341,6 +8350,9 @@
       <c r="J155" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="K155" s="17">
+        <v>0.59</v>
+      </c>
       <c r="L155" s="17">
         <v>0.96</v>
       </c>
@@ -8380,6 +8392,9 @@
       <c r="J156" s="17">
         <v>0.37</v>
       </c>
+      <c r="K156" s="17">
+        <v>0.35</v>
+      </c>
       <c r="L156" s="17">
         <v>0.8</v>
       </c>
@@ -8500,6 +8515,9 @@
       <c r="J159" s="17">
         <v>0.48</v>
       </c>
+      <c r="K159" s="17">
+        <v>0.2</v>
+      </c>
       <c r="L159" s="17">
         <v>0.83</v>
       </c>
@@ -9274,6 +9292,9 @@
       <c r="J178" s="17">
         <v>0.27</v>
       </c>
+      <c r="K178" s="17">
+        <v>0.27</v>
+      </c>
       <c r="L178" s="17">
         <v>0</v>
       </c>
@@ -9351,6 +9372,9 @@
       </c>
       <c r="J180" s="17">
         <v>0.79</v>
+      </c>
+      <c r="K180" s="17">
+        <v>0.22</v>
       </c>
       <c r="L180" s="17">
         <v>0.63</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F004B82-AD6A-7543-828C-8B399D5BA517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C00331D-9BF5-214C-9514-69F00A64FC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7498,6 +7498,9 @@
       <c r="J134" s="17">
         <v>0.49</v>
       </c>
+      <c r="K134" s="17">
+        <v>0.35</v>
+      </c>
       <c r="L134" s="17">
         <v>0.96</v>
       </c>
@@ -7615,6 +7618,9 @@
       <c r="J137" s="17">
         <v>0.67</v>
       </c>
+      <c r="K137" s="17">
+        <v>0.71</v>
+      </c>
       <c r="L137" s="17">
         <v>0</v>
       </c>
@@ -8062,6 +8068,9 @@
       <c r="J148" s="17">
         <v>0.67</v>
       </c>
+      <c r="K148" s="17">
+        <v>0.49</v>
+      </c>
       <c r="L148" s="17">
         <v>0.51</v>
       </c>
@@ -8101,6 +8110,9 @@
       <c r="J149" s="17">
         <v>0.35</v>
       </c>
+      <c r="K149" s="17">
+        <v>0.86</v>
+      </c>
       <c r="L149" s="17">
         <v>0.61</v>
       </c>
@@ -8434,6 +8446,9 @@
       <c r="J157" s="17">
         <v>0.52</v>
       </c>
+      <c r="K157" s="17">
+        <v>0.53</v>
+      </c>
       <c r="L157" s="17">
         <v>0.61</v>
       </c>
@@ -8677,6 +8692,9 @@
       <c r="J163" s="17">
         <v>0.59</v>
       </c>
+      <c r="K163" s="17">
+        <v>0.78</v>
+      </c>
       <c r="L163" s="17">
         <v>0.96</v>
       </c>
@@ -8920,6 +8938,9 @@
       <c r="J169" s="17">
         <v>0.48</v>
       </c>
+      <c r="K169" s="17">
+        <v>0.84</v>
+      </c>
       <c r="L169" s="17">
         <v>0</v>
       </c>
@@ -8959,6 +8980,9 @@
       <c r="J170" s="17">
         <v>0.65</v>
       </c>
+      <c r="K170" s="17">
+        <v>0.86</v>
+      </c>
       <c r="L170" s="17">
         <v>0.8</v>
       </c>
@@ -9496,6 +9520,9 @@
       <c r="J183" s="17">
         <v>0.4</v>
       </c>
+      <c r="K183" s="17">
+        <v>0.45</v>
+      </c>
       <c r="L183" s="17">
         <v>0.51</v>
       </c>
@@ -10650,6 +10677,9 @@
       </c>
       <c r="J215" s="17">
         <v>0.35</v>
+      </c>
+      <c r="K215" s="17">
+        <v>0.71</v>
       </c>
       <c r="L215" s="17">
         <v>0.65</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C00331D-9BF5-214C-9514-69F00A64FC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887620DA-1BF0-AB40-BC53-A5C700F885A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -9922,6 +9922,9 @@
       <c r="J194" s="17">
         <v>0.6</v>
       </c>
+      <c r="K194" s="17">
+        <v>0.9</v>
+      </c>
       <c r="L194" s="17">
         <v>0.83</v>
       </c>
@@ -10066,6 +10069,9 @@
       <c r="J198" s="17">
         <v>0.44</v>
       </c>
+      <c r="K198" s="17">
+        <v>0.71</v>
+      </c>
       <c r="L198" s="17">
         <v>0.65</v>
       </c>
@@ -10210,6 +10216,9 @@
       <c r="J202" s="17">
         <v>0.79</v>
       </c>
+      <c r="K202" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="L202" s="17">
         <v>0.38</v>
       </c>
@@ -10246,6 +10255,9 @@
       <c r="J203" s="17">
         <v>0.49</v>
       </c>
+      <c r="K203" s="17">
+        <v>0.35</v>
+      </c>
       <c r="L203" s="17">
         <v>0.8</v>
       </c>
@@ -10716,6 +10728,9 @@
       </c>
       <c r="J216" s="17">
         <v>0.14000000000000001</v>
+      </c>
+      <c r="K216" s="17">
+        <v>0.56999999999999995</v>
       </c>
       <c r="L216" s="17">
         <v>0.83</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887620DA-1BF0-AB40-BC53-A5C700F885A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9586DE19-19B2-7C48-BF4F-5F871BEE726F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -9778,6 +9778,9 @@
       <c r="J190" s="17">
         <v>0.06</v>
       </c>
+      <c r="K190" s="17">
+        <v>0.47</v>
+      </c>
       <c r="L190" s="17">
         <v>0.83</v>
       </c>
@@ -10839,6 +10842,9 @@
       </c>
       <c r="J219" s="17">
         <v>0.41</v>
+      </c>
+      <c r="K219" s="17">
+        <v>0.73</v>
       </c>
       <c r="L219" s="17">
         <v>0.8</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9586DE19-19B2-7C48-BF4F-5F871BEE726F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F62E0B2-E64E-4B4C-9BCF-756C6E3408D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -9598,6 +9598,9 @@
       <c r="J185" s="17">
         <v>0.42</v>
       </c>
+      <c r="K185" s="17">
+        <v>0.9</v>
+      </c>
       <c r="L185" s="17">
         <v>0.83</v>
       </c>
@@ -9845,13 +9848,16 @@
         <v>0.93</v>
       </c>
       <c r="H192" s="17">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="I192" s="20">
         <v>0.36</v>
       </c>
       <c r="J192" s="17">
         <v>0.27</v>
+      </c>
+      <c r="K192" s="17">
+        <v>0.88</v>
       </c>
       <c r="L192" s="17">
         <v>0.79</v>
@@ -9889,6 +9895,9 @@
       <c r="J193" s="17">
         <v>0.32</v>
       </c>
+      <c r="K193" s="17">
+        <v>0.51</v>
+      </c>
       <c r="L193" s="17">
         <v>0.65</v>
       </c>
@@ -10000,6 +10009,9 @@
       <c r="J196" s="17">
         <v>0.32</v>
       </c>
+      <c r="K196" s="17">
+        <v>0.82</v>
+      </c>
       <c r="L196" s="17">
         <v>0.38</v>
       </c>
@@ -10111,6 +10123,9 @@
       <c r="J199" s="17">
         <v>0.17</v>
       </c>
+      <c r="K199" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L199" s="17">
         <v>0</v>
       </c>
@@ -10147,6 +10162,9 @@
       <c r="J200" s="17">
         <v>0.4</v>
       </c>
+      <c r="K200" s="17">
+        <v>0.63</v>
+      </c>
       <c r="L200" s="17">
         <v>0.38</v>
       </c>
@@ -10183,6 +10201,9 @@
       <c r="J201" s="17">
         <v>0.73</v>
       </c>
+      <c r="K201" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="L201" s="17">
         <v>0.51</v>
       </c>
@@ -10477,6 +10498,9 @@
       <c r="J209" s="17">
         <v>0.35</v>
       </c>
+      <c r="K209" s="17">
+        <v>0.67</v>
+      </c>
       <c r="L209" s="17">
         <v>0.51</v>
       </c>
@@ -10513,6 +10537,9 @@
       <c r="J210" s="17">
         <v>0.78</v>
       </c>
+      <c r="K210" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="L210" s="17">
         <v>0.83</v>
       </c>
@@ -10549,6 +10576,9 @@
       <c r="J211" s="17">
         <v>0.41</v>
       </c>
+      <c r="K211" s="17">
+        <v>0.69</v>
+      </c>
       <c r="L211" s="17">
         <v>0.51</v>
       </c>
@@ -10585,6 +10615,9 @@
       <c r="J212" s="17">
         <v>0.49</v>
       </c>
+      <c r="K212" s="17">
+        <v>0.65</v>
+      </c>
       <c r="L212" s="17">
         <v>0.8</v>
       </c>
@@ -10621,6 +10654,9 @@
       <c r="J213" s="17">
         <v>0.52</v>
       </c>
+      <c r="K213" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="L213" s="17">
         <v>0.8</v>
       </c>
@@ -10657,6 +10693,9 @@
       <c r="J214" s="17">
         <v>0</v>
       </c>
+      <c r="K214" s="17">
+        <v>0.31</v>
+      </c>
       <c r="L214" s="17">
         <v>0.83</v>
       </c>
@@ -10770,6 +10809,9 @@
       </c>
       <c r="J217" s="17">
         <v>0.41</v>
+      </c>
+      <c r="K217" s="17">
+        <v>0.55000000000000004</v>
       </c>
       <c r="L217" s="17">
         <v>0.65</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F62E0B2-E64E-4B4C-9BCF-756C6E3408D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71DF0DF-B100-754E-B5A9-C52518745603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -9637,6 +9637,9 @@
       <c r="J186" s="17">
         <v>0.27</v>
       </c>
+      <c r="K186" s="17">
+        <v>0.86</v>
+      </c>
       <c r="L186" s="17">
         <v>0.51</v>
       </c>
@@ -9709,6 +9712,9 @@
       <c r="J188" s="17">
         <v>0.75</v>
       </c>
+      <c r="K188" s="17">
+        <v>0.94</v>
+      </c>
       <c r="L188" s="17">
         <v>0</v>
       </c>
@@ -9820,6 +9826,9 @@
       <c r="J191" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="K191" s="17">
+        <v>0.67</v>
+      </c>
       <c r="L191" s="17">
         <v>0.8</v>
       </c>
@@ -10048,6 +10057,9 @@
       <c r="J197" s="17">
         <v>0.33</v>
       </c>
+      <c r="K197" s="17">
+        <v>0.49</v>
+      </c>
       <c r="L197" s="17">
         <v>0.83</v>
       </c>
@@ -10354,6 +10366,9 @@
       <c r="J205" s="17">
         <v>0.48</v>
       </c>
+      <c r="K205" s="17">
+        <v>0.53</v>
+      </c>
       <c r="L205" s="17">
         <v>0.38</v>
       </c>
@@ -10390,6 +10405,9 @@
       <c r="J206" s="17">
         <v>0.33</v>
       </c>
+      <c r="K206" s="17">
+        <v>0.84</v>
+      </c>
       <c r="L206" s="17">
         <v>0.65</v>
       </c>
@@ -10462,6 +10480,9 @@
       <c r="J208" s="17">
         <v>0.33</v>
       </c>
+      <c r="K208" s="17">
+        <v>0.31</v>
+      </c>
       <c r="L208" s="17">
         <v>0.51</v>
       </c>
@@ -10923,6 +10944,9 @@
       </c>
       <c r="J220" s="17">
         <v>0.67</v>
+      </c>
+      <c r="K220" s="17">
+        <v>0.73</v>
       </c>
       <c r="L220" s="17">
         <v>0.83</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71DF0DF-B100-754E-B5A9-C52518745603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5626C8-1AA2-434C-95CC-66CEE9FE3919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -11296,6 +11296,9 @@
       <c r="L229" s="17">
         <v>0.57999999999999996</v>
       </c>
+      <c r="M229" s="17">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="230" spans="1:16">
       <c r="A230" s="9" t="s">
@@ -11334,6 +11337,9 @@
       <c r="L230" s="17">
         <v>0.54</v>
       </c>
+      <c r="M230" s="17">
+        <v>0.5</v>
+      </c>
       <c r="P230" s="16"/>
     </row>
     <row r="231" spans="1:16">
@@ -11373,6 +11379,9 @@
       <c r="L231" s="17">
         <v>0.57999999999999996</v>
       </c>
+      <c r="M231" s="17">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="9" t="s">
@@ -11411,6 +11420,9 @@
       <c r="L232" s="17">
         <v>0.69</v>
       </c>
+      <c r="M232" s="17">
+        <v>0.78</v>
+      </c>
       <c r="P232" s="16"/>
     </row>
     <row r="233" spans="1:16">
@@ -11450,6 +11462,9 @@
       <c r="L233" s="17">
         <v>0.57999999999999996</v>
       </c>
+      <c r="M233" s="17">
+        <v>0.6</v>
+      </c>
       <c r="P233" s="16"/>
     </row>
     <row r="234" spans="1:16">
@@ -11489,6 +11504,9 @@
       <c r="L234" s="17">
         <v>0.85</v>
       </c>
+      <c r="M234" s="17">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="235" spans="1:16">
       <c r="A235" t="s">
@@ -11527,6 +11545,9 @@
       <c r="L235" s="17">
         <v>0.54</v>
       </c>
+      <c r="M235" s="17">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="9" t="s">
@@ -11563,6 +11584,9 @@
       <c r="L236" s="17">
         <v>0.72</v>
       </c>
+      <c r="M236" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P236" s="16"/>
     </row>
     <row r="237" spans="1:16">
@@ -11602,6 +11626,9 @@
       <c r="L237" s="17">
         <v>0.72</v>
       </c>
+      <c r="M237" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P237" s="16"/>
     </row>
     <row r="238" spans="1:16">
@@ -11639,6 +11666,9 @@
       <c r="L238" s="17">
         <v>0.69</v>
       </c>
+      <c r="M238" s="17">
+        <v>0.78</v>
+      </c>
       <c r="P238" s="16"/>
     </row>
     <row r="239" spans="1:16">
@@ -11678,6 +11708,9 @@
       <c r="L239" s="17">
         <v>0.72</v>
       </c>
+      <c r="M239" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P239" s="16"/>
     </row>
     <row r="240" spans="1:16">
@@ -11715,6 +11748,9 @@
       <c r="L240" s="17">
         <v>0.54</v>
       </c>
+      <c r="M240" s="17">
+        <v>0.5</v>
+      </c>
       <c r="P240" s="16"/>
     </row>
     <row r="241" spans="1:16">
@@ -11752,6 +11788,9 @@
       <c r="L241" s="17">
         <v>0.69</v>
       </c>
+      <c r="M241" s="17">
+        <v>0.78</v>
+      </c>
       <c r="P241" s="16"/>
     </row>
     <row r="242" spans="1:16">
@@ -11791,6 +11830,9 @@
       <c r="L242" s="17">
         <v>0.54</v>
       </c>
+      <c r="M242" s="17">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" t="s">
@@ -11829,6 +11871,9 @@
       <c r="L243" s="17">
         <v>0.85</v>
       </c>
+      <c r="M243" s="17">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="244" spans="1:16">
       <c r="A244" t="s">
@@ -11867,6 +11912,9 @@
       <c r="L244" s="17">
         <v>0.69</v>
       </c>
+      <c r="M244" s="17">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="245" spans="1:16">
       <c r="A245" s="9" t="s">
@@ -11905,6 +11953,9 @@
       <c r="L245" s="17">
         <v>0.72</v>
       </c>
+      <c r="M245" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P245" s="16"/>
     </row>
     <row r="246" spans="1:16">
@@ -11943,6 +11994,9 @@
       </c>
       <c r="L246" s="17">
         <v>0.57999999999999996</v>
+      </c>
+      <c r="M246" s="17">
+        <v>0.6</v>
       </c>
       <c r="P246" s="16"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5626C8-1AA2-434C-95CC-66CEE9FE3919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883A572C-0FF2-4F4E-ADC6-C09A92A3C8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -9604,6 +9604,9 @@
       <c r="L185" s="17">
         <v>0.83</v>
       </c>
+      <c r="M185" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
@@ -9643,6 +9646,9 @@
       <c r="L186" s="17">
         <v>0.51</v>
       </c>
+      <c r="M186" s="17">
+        <v>0.5</v>
+      </c>
       <c r="P186" s="4"/>
     </row>
     <row r="187" spans="1:16">
@@ -9793,6 +9799,9 @@
       <c r="L190" s="17">
         <v>0.83</v>
       </c>
+      <c r="M190" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P190" s="4"/>
     </row>
     <row r="191" spans="1:16">
@@ -9871,6 +9880,9 @@
       <c r="L192" s="17">
         <v>0.79</v>
       </c>
+      <c r="M192" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="P192" s="4"/>
     </row>
     <row r="193" spans="1:16">
@@ -10219,6 +10231,9 @@
       <c r="L201" s="17">
         <v>0.51</v>
       </c>
+      <c r="M201" s="17">
+        <v>0.5</v>
+      </c>
       <c r="P201" s="4"/>
     </row>
     <row r="202" spans="1:16">
@@ -10486,6 +10501,9 @@
       <c r="L208" s="17">
         <v>0.51</v>
       </c>
+      <c r="M208" s="17">
+        <v>0.5</v>
+      </c>
       <c r="P208" s="4"/>
     </row>
     <row r="209" spans="1:16">
@@ -10525,6 +10543,9 @@
       <c r="L209" s="17">
         <v>0.51</v>
       </c>
+      <c r="M209" s="17">
+        <v>0.5</v>
+      </c>
       <c r="P209" s="4"/>
     </row>
     <row r="210" spans="1:16">
@@ -10564,6 +10585,9 @@
       <c r="L210" s="17">
         <v>0.83</v>
       </c>
+      <c r="M210" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P210" s="4"/>
     </row>
     <row r="211" spans="1:16">
@@ -10603,6 +10627,9 @@
       <c r="L211" s="17">
         <v>0.51</v>
       </c>
+      <c r="M211" s="17">
+        <v>0.5</v>
+      </c>
       <c r="P211" s="4"/>
     </row>
     <row r="212" spans="1:16">
@@ -10950,6 +10977,9 @@
       </c>
       <c r="L220" s="17">
         <v>0.83</v>
+      </c>
+      <c r="M220" s="17">
+        <v>0.55000000000000004</v>
       </c>
       <c r="P220" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883A572C-0FF2-4F4E-ADC6-C09A92A3C8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FDA3E4-3662-194F-AB77-E2CF5C31E913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -9565,6 +9565,9 @@
       <c r="L184" s="17">
         <v>0.38</v>
       </c>
+      <c r="M184" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
@@ -9760,6 +9763,9 @@
       <c r="L189" s="17">
         <v>0.8</v>
       </c>
+      <c r="M189" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P189" s="4"/>
     </row>
     <row r="190" spans="1:16">
@@ -9841,6 +9847,9 @@
       <c r="L191" s="17">
         <v>0.8</v>
       </c>
+      <c r="M191" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P191" s="4"/>
     </row>
     <row r="192" spans="1:16">
@@ -9922,6 +9931,9 @@
       <c r="L193" s="17">
         <v>0.65</v>
       </c>
+      <c r="M193" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P193" s="4"/>
     </row>
     <row r="194" spans="1:16">
@@ -9961,6 +9973,9 @@
       <c r="L194" s="17">
         <v>0.83</v>
       </c>
+      <c r="M194" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P194" s="4"/>
     </row>
     <row r="195" spans="1:16">
@@ -9997,6 +10012,9 @@
       <c r="L195" s="17">
         <v>0.83</v>
       </c>
+      <c r="M195" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P195" s="4"/>
     </row>
     <row r="196" spans="1:16">
@@ -10036,6 +10054,9 @@
       <c r="L196" s="17">
         <v>0.38</v>
       </c>
+      <c r="M196" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P196" s="4"/>
     </row>
     <row r="197" spans="1:16">
@@ -10075,6 +10096,9 @@
       <c r="L197" s="17">
         <v>0.83</v>
       </c>
+      <c r="M197" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P197" s="4"/>
     </row>
     <row r="198" spans="1:16">
@@ -10114,6 +10138,9 @@
       <c r="L198" s="17">
         <v>0.65</v>
       </c>
+      <c r="M198" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P198" s="4"/>
     </row>
     <row r="199" spans="1:16">
@@ -10192,6 +10219,9 @@
       <c r="L200" s="17">
         <v>0.38</v>
       </c>
+      <c r="M200" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P200" s="4"/>
     </row>
     <row r="201" spans="1:16">
@@ -10273,6 +10303,9 @@
       <c r="L202" s="17">
         <v>0.38</v>
       </c>
+      <c r="M202" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P202" s="4"/>
     </row>
     <row r="203" spans="1:16">
@@ -10312,6 +10345,9 @@
       <c r="L203" s="17">
         <v>0.8</v>
       </c>
+      <c r="M203" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P203" s="4"/>
     </row>
     <row r="204" spans="1:16">
@@ -10348,6 +10384,9 @@
       <c r="L204" s="17">
         <v>0.38</v>
       </c>
+      <c r="M204" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P204" s="4"/>
     </row>
     <row r="205" spans="1:16">
@@ -10387,6 +10426,9 @@
       <c r="L205" s="17">
         <v>0.38</v>
       </c>
+      <c r="M205" s="17">
+        <v>0.51</v>
+      </c>
       <c r="P205" s="4"/>
     </row>
     <row r="206" spans="1:16">
@@ -10426,6 +10468,9 @@
       <c r="L206" s="17">
         <v>0.65</v>
       </c>
+      <c r="M206" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P206" s="4"/>
     </row>
     <row r="207" spans="1:16">
@@ -10462,6 +10507,9 @@
       <c r="L207" s="17">
         <v>0.65</v>
       </c>
+      <c r="M207" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P207" s="4"/>
     </row>
     <row r="208" spans="1:16">
@@ -10669,6 +10717,9 @@
       <c r="L212" s="17">
         <v>0.8</v>
       </c>
+      <c r="M212" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P212" s="4"/>
     </row>
     <row r="213" spans="1:16">
@@ -10708,6 +10759,9 @@
       <c r="L213" s="17">
         <v>0.8</v>
       </c>
+      <c r="M213" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P213" s="4"/>
     </row>
     <row r="214" spans="1:16">
@@ -10786,6 +10840,9 @@
       <c r="L215" s="17">
         <v>0.65</v>
       </c>
+      <c r="M215" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P215" s="4"/>
     </row>
     <row r="216" spans="1:16">
@@ -10825,6 +10882,9 @@
       <c r="L216" s="17">
         <v>0.83</v>
       </c>
+      <c r="M216" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P216" s="4"/>
     </row>
     <row r="217" spans="1:16">
@@ -10864,6 +10924,9 @@
       <c r="L217" s="17">
         <v>0.65</v>
       </c>
+      <c r="M217" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P217" s="4"/>
     </row>
     <row r="218" spans="1:16">
@@ -10900,6 +10963,9 @@
       <c r="L218" s="17">
         <v>0.83</v>
       </c>
+      <c r="M218" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P218" s="4"/>
     </row>
     <row r="219" spans="1:16">
@@ -10939,6 +11005,9 @@
       <c r="L219" s="17">
         <v>0.8</v>
       </c>
+      <c r="M219" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P219" s="4"/>
     </row>
     <row r="220" spans="1:16">
@@ -11017,6 +11086,9 @@
       <c r="L221" s="17">
         <v>0.52</v>
       </c>
+      <c r="M221" s="17">
+        <v>0</v>
+      </c>
       <c r="P221" s="4"/>
     </row>
     <row r="222" spans="1:16">
@@ -11056,6 +11128,9 @@
       <c r="L222" s="17">
         <v>0</v>
       </c>
+      <c r="M222" s="17">
+        <v>0</v>
+      </c>
       <c r="P222" s="15"/>
     </row>
     <row r="223" spans="1:16">
@@ -11095,6 +11170,9 @@
       <c r="L223" s="17">
         <v>0.52</v>
       </c>
+      <c r="M223" s="17">
+        <v>0</v>
+      </c>
       <c r="P223" s="4"/>
     </row>
     <row r="224" spans="1:16">
@@ -11134,6 +11212,9 @@
       <c r="L224" s="17">
         <v>0.52</v>
       </c>
+      <c r="M224" s="17">
+        <v>0</v>
+      </c>
       <c r="P224" s="4"/>
     </row>
     <row r="225" spans="1:16">
@@ -11173,6 +11254,9 @@
       <c r="L225" s="17">
         <v>0</v>
       </c>
+      <c r="M225" s="17">
+        <v>0</v>
+      </c>
       <c r="P225" s="15"/>
     </row>
     <row r="226" spans="1:16">
@@ -11212,6 +11296,9 @@
       <c r="L226" s="17">
         <v>0.52</v>
       </c>
+      <c r="M226" s="17">
+        <v>0</v>
+      </c>
       <c r="P226" s="4"/>
     </row>
     <row r="227" spans="1:16">
@@ -11248,6 +11335,9 @@
       <c r="L227" s="17">
         <v>0.52</v>
       </c>
+      <c r="M227" s="17">
+        <v>0</v>
+      </c>
       <c r="P227" s="16"/>
     </row>
     <row r="228" spans="1:16">
@@ -11286,6 +11376,9 @@
       </c>
       <c r="L228" s="17">
         <v>0.52</v>
+      </c>
+      <c r="M228" s="17">
+        <v>0</v>
       </c>
       <c r="P228" s="16"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FDA3E4-3662-194F-AB77-E2CF5C31E913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46280B0-54ED-EF4B-A40B-2E054A36983C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -5821,6 +5821,9 @@
       <c r="L90" s="17">
         <v>0.82</v>
       </c>
+      <c r="M90" s="17">
+        <v>0</v>
+      </c>
       <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
@@ -5860,6 +5863,9 @@
       <c r="L91" s="17">
         <v>0.62</v>
       </c>
+      <c r="M91" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
@@ -5899,6 +5905,9 @@
       <c r="L92" s="17">
         <v>0.72</v>
       </c>
+      <c r="M92" s="17">
+        <v>0.43</v>
+      </c>
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
@@ -5938,6 +5947,9 @@
       <c r="L93" s="17">
         <v>0.62</v>
       </c>
+      <c r="M93" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
@@ -5974,6 +5986,9 @@
       <c r="L94" s="17">
         <v>0.62</v>
       </c>
+      <c r="M94" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
@@ -6010,6 +6025,9 @@
       <c r="L95" s="17">
         <v>0.72</v>
       </c>
+      <c r="M95" s="17">
+        <v>0.43</v>
+      </c>
       <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
@@ -6049,6 +6067,9 @@
       <c r="L96" s="17">
         <v>0.61</v>
       </c>
+      <c r="M96" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
@@ -6088,6 +6109,9 @@
       <c r="L97" s="17">
         <v>0.69</v>
       </c>
+      <c r="M97" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P97" s="4"/>
     </row>
     <row r="98" spans="1:16">
@@ -6124,6 +6148,9 @@
       <c r="L98" s="17">
         <v>0.62</v>
       </c>
+      <c r="M98" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P98" s="15"/>
     </row>
     <row r="99" spans="1:16">
@@ -6163,6 +6190,9 @@
       <c r="L99" s="17">
         <v>0.82</v>
       </c>
+      <c r="M99" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P99" s="4"/>
     </row>
     <row r="100" spans="1:16">
@@ -6202,6 +6232,9 @@
       <c r="L100" s="17">
         <v>0.82</v>
       </c>
+      <c r="M100" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P100" s="4"/>
     </row>
     <row r="101" spans="1:16">
@@ -6241,6 +6274,9 @@
       <c r="L101" s="17">
         <v>0.69</v>
       </c>
+      <c r="M101" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P101" s="4"/>
     </row>
     <row r="102" spans="1:16">
@@ -6280,6 +6316,9 @@
       <c r="L102" s="17">
         <v>0.82</v>
       </c>
+      <c r="M102" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P102" s="4"/>
     </row>
     <row r="103" spans="1:16">
@@ -6319,6 +6358,9 @@
       <c r="L103" s="17">
         <v>0.69</v>
       </c>
+      <c r="M103" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P103" s="4"/>
     </row>
     <row r="104" spans="1:16">
@@ -6358,6 +6400,9 @@
       <c r="L104" s="17">
         <v>0.72</v>
       </c>
+      <c r="M104" s="17">
+        <v>0</v>
+      </c>
       <c r="P104" s="4"/>
     </row>
     <row r="105" spans="1:16">
@@ -6397,6 +6442,9 @@
       <c r="L105" s="17">
         <v>0.83</v>
       </c>
+      <c r="M105" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P105" s="4"/>
     </row>
     <row r="106" spans="1:16">
@@ -6433,6 +6481,9 @@
       <c r="L106" s="17">
         <v>0.82</v>
       </c>
+      <c r="M106" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P106" s="15"/>
     </row>
     <row r="107" spans="1:16">
@@ -6472,6 +6523,9 @@
       <c r="L107" s="17">
         <v>0.69</v>
       </c>
+      <c r="M107" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P107" s="4"/>
     </row>
     <row r="108" spans="1:16">
@@ -6511,6 +6565,9 @@
       <c r="L108" s="17">
         <v>0.62</v>
       </c>
+      <c r="M108" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="P108" s="4"/>
     </row>
     <row r="109" spans="1:16">
@@ -6550,6 +6607,9 @@
       <c r="L109" s="17">
         <v>0.82</v>
       </c>
+      <c r="M109" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P109" s="4"/>
     </row>
     <row r="110" spans="1:16">
@@ -6589,6 +6649,9 @@
       <c r="L110" s="17">
         <v>0.72</v>
       </c>
+      <c r="M110" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P110" s="4"/>
     </row>
     <row r="111" spans="1:16">
@@ -6625,6 +6688,9 @@
       <c r="L111" s="17">
         <v>0.72</v>
       </c>
+      <c r="M111" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P111" s="4"/>
     </row>
     <row r="112" spans="1:16">
@@ -6664,6 +6730,9 @@
       <c r="L112" s="17">
         <v>0.72</v>
       </c>
+      <c r="M112" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P112" s="4"/>
     </row>
     <row r="113" spans="1:16">
@@ -6703,6 +6772,9 @@
       <c r="L113" s="17">
         <v>0.82</v>
       </c>
+      <c r="M113" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P113" s="4"/>
     </row>
     <row r="114" spans="1:16">
@@ -6742,6 +6814,9 @@
       <c r="L114" s="17">
         <v>0.83</v>
       </c>
+      <c r="M114" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P114" s="4"/>
     </row>
     <row r="115" spans="1:16">
@@ -6781,6 +6856,9 @@
       <c r="L115" s="17">
         <v>0.61</v>
       </c>
+      <c r="M115" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="P115" s="4"/>
     </row>
     <row r="116" spans="1:16">
@@ -6820,6 +6898,9 @@
       <c r="L116" s="17">
         <v>0.62</v>
       </c>
+      <c r="M116" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P116" s="4"/>
     </row>
     <row r="117" spans="1:16">
@@ -6859,6 +6940,9 @@
       <c r="L117" s="17">
         <v>0.72</v>
       </c>
+      <c r="M117" s="17">
+        <v>0.43</v>
+      </c>
       <c r="P117" s="4"/>
     </row>
     <row r="118" spans="1:16">
@@ -6895,6 +6979,9 @@
       <c r="L118" s="17">
         <v>0.72</v>
       </c>
+      <c r="M118" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P118" s="4"/>
     </row>
     <row r="119" spans="1:16">
@@ -6931,6 +7018,9 @@
       <c r="L119" s="17">
         <v>0.82</v>
       </c>
+      <c r="M119" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P119" s="4"/>
     </row>
     <row r="120" spans="1:16">
@@ -6970,6 +7060,9 @@
       <c r="L120" s="17">
         <v>0.72</v>
       </c>
+      <c r="M120" s="17">
+        <v>0.43</v>
+      </c>
       <c r="P120" s="15"/>
     </row>
     <row r="121" spans="1:16">
@@ -7009,6 +7102,9 @@
       <c r="L121" s="17">
         <v>0.72</v>
       </c>
+      <c r="M121" s="17">
+        <v>0.83</v>
+      </c>
       <c r="P121" s="4"/>
     </row>
     <row r="122" spans="1:16">
@@ -7048,6 +7144,9 @@
       <c r="L122" s="17">
         <v>0.83</v>
       </c>
+      <c r="M122" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P122" s="4"/>
     </row>
     <row r="123" spans="1:16">
@@ -7087,6 +7186,9 @@
       <c r="L123" s="17">
         <v>0.62</v>
       </c>
+      <c r="M123" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P123" s="4"/>
     </row>
     <row r="124" spans="1:16">
@@ -7126,6 +7228,9 @@
       <c r="L124" s="17">
         <v>0.83</v>
       </c>
+      <c r="M124" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P124" s="4"/>
     </row>
     <row r="125" spans="1:16">
@@ -7165,6 +7270,9 @@
       <c r="L125" s="17">
         <v>0.69</v>
       </c>
+      <c r="M125" s="17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="P125" s="4"/>
     </row>
     <row r="126" spans="1:16">
@@ -7201,6 +7309,9 @@
       <c r="L126" s="17">
         <v>0.61</v>
       </c>
+      <c r="M126" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="P126" s="4"/>
     </row>
     <row r="127" spans="1:16">
@@ -7237,6 +7348,9 @@
       <c r="L127" s="17">
         <v>0.83</v>
       </c>
+      <c r="M127" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P127" s="4"/>
     </row>
     <row r="128" spans="1:16">
@@ -7276,6 +7390,9 @@
       <c r="L128" s="17">
         <v>0.83</v>
       </c>
+      <c r="M128" s="17">
+        <v>0.84</v>
+      </c>
       <c r="P128" s="4"/>
     </row>
     <row r="129" spans="1:16">
@@ -7315,6 +7432,9 @@
       <c r="L129" s="17">
         <v>0.61</v>
       </c>
+      <c r="M129" s="17">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="P129" s="4"/>
     </row>
     <row r="130" spans="1:16">
@@ -7354,6 +7474,9 @@
       <c r="L130" s="17">
         <v>0.82</v>
       </c>
+      <c r="M130" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P130" s="4"/>
     </row>
     <row r="131" spans="1:16">
@@ -7393,6 +7516,9 @@
       <c r="L131" s="17">
         <v>0.82</v>
       </c>
+      <c r="M131" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P131" s="4"/>
     </row>
     <row r="132" spans="1:16">
@@ -7429,6 +7555,9 @@
       <c r="L132" s="17">
         <v>0.72</v>
       </c>
+      <c r="M132" s="17">
+        <v>0.43</v>
+      </c>
       <c r="P132" s="4"/>
     </row>
     <row r="133" spans="1:16">
@@ -7464,6 +7593,9 @@
       </c>
       <c r="L133" s="17">
         <v>0.69</v>
+      </c>
+      <c r="M133" s="17">
+        <v>0.55000000000000004</v>
       </c>
       <c r="P133" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46280B0-54ED-EF4B-A40B-2E054A36983C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5844C1-26EB-BE45-847D-A9A841F6E708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2299,6 +2299,9 @@
       <c r="L2" s="17">
         <v>0.48</v>
       </c>
+      <c r="M2" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P2" s="22" t="e">
         <f>(((LARGE(D2:G2,1)+LARGE(D2:G2,2)+LARGE(D2:G2,3))*0.2/3+(LARGE(H2:K2,1)+LARGE(H2:K2,2)+LARGE(H2:K2,3))*0.5/3+(LARGE(L2:O2,1)+LARGE(L2:O2,2)+LARGE(L2:O2,3))*0.3/3))</f>
         <v>#NUM!</v>
@@ -2341,6 +2344,9 @@
       <c r="L3" s="17">
         <v>0.68</v>
       </c>
+      <c r="M3" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16">
@@ -2380,6 +2386,9 @@
       <c r="L4" s="17">
         <v>0.48</v>
       </c>
+      <c r="M4" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P4" s="4"/>
     </row>
     <row r="5" spans="1:16">
@@ -2419,6 +2428,9 @@
       <c r="L5" s="17">
         <v>0.48</v>
       </c>
+      <c r="M5" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P5" s="4"/>
     </row>
     <row r="6" spans="1:16">
@@ -2456,6 +2468,9 @@
       <c r="L6" s="17">
         <v>0.48</v>
       </c>
+      <c r="M6" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P6" s="4"/>
     </row>
     <row r="7" spans="1:16">
@@ -2495,6 +2510,9 @@
       <c r="L7" s="17">
         <v>0.48</v>
       </c>
+      <c r="M7" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P7" s="4"/>
     </row>
     <row r="8" spans="1:16">
@@ -2534,6 +2552,9 @@
       <c r="L8" s="17">
         <v>0.8</v>
       </c>
+      <c r="M8" s="17">
+        <v>0.6</v>
+      </c>
       <c r="P8" s="4"/>
     </row>
     <row r="9" spans="1:16">
@@ -2573,6 +2594,9 @@
       <c r="L9" s="17">
         <v>0.68</v>
       </c>
+      <c r="M9" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P9" s="4"/>
     </row>
     <row r="10" spans="1:16">
@@ -2610,6 +2634,9 @@
       <c r="L10" s="17">
         <v>0.48</v>
       </c>
+      <c r="M10" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P10" s="4"/>
     </row>
     <row r="11" spans="1:16">
@@ -2649,6 +2676,9 @@
       <c r="L11" s="17">
         <v>0.48</v>
       </c>
+      <c r="M11" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P11" s="4"/>
     </row>
     <row r="12" spans="1:16">
@@ -2688,6 +2718,9 @@
       <c r="L12" s="17">
         <v>0.48</v>
       </c>
+      <c r="M12" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P12" s="4"/>
     </row>
     <row r="13" spans="1:16">
@@ -2727,6 +2760,9 @@
       <c r="L13" s="17">
         <v>0.48</v>
       </c>
+      <c r="M13" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P13" s="4"/>
     </row>
     <row r="14" spans="1:16">
@@ -2766,6 +2802,9 @@
       <c r="L14" s="17">
         <v>0.48</v>
       </c>
+      <c r="M14" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P14" s="4"/>
     </row>
     <row r="15" spans="1:16">
@@ -2803,6 +2842,9 @@
       <c r="L15" s="17">
         <v>0.68</v>
       </c>
+      <c r="M15" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P15" s="4"/>
     </row>
     <row r="16" spans="1:16">
@@ -2842,6 +2884,9 @@
       <c r="L16" s="17">
         <v>0.48</v>
       </c>
+      <c r="M16" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P16" s="4"/>
     </row>
     <row r="17" spans="1:16">
@@ -2881,6 +2926,9 @@
       <c r="L17" s="17">
         <v>0.48</v>
       </c>
+      <c r="M17" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P17" s="4"/>
     </row>
     <row r="18" spans="1:16">
@@ -2920,6 +2968,9 @@
       <c r="L18" s="17">
         <v>0.48</v>
       </c>
+      <c r="M18" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P18" s="4"/>
     </row>
     <row r="19" spans="1:16">
@@ -2957,6 +3008,9 @@
       <c r="L19" s="17">
         <v>0</v>
       </c>
+      <c r="M19" s="17">
+        <v>0</v>
+      </c>
       <c r="P19" s="15"/>
     </row>
     <row r="20" spans="1:16">
@@ -2991,10 +3045,13 @@
         <v>0.65</v>
       </c>
       <c r="K20" s="17">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="L20" s="17">
         <v>0.48</v>
+      </c>
+      <c r="M20" s="17">
+        <v>0.76</v>
       </c>
       <c r="P20" s="4"/>
     </row>
@@ -3035,6 +3092,9 @@
       <c r="L21" s="17">
         <v>0.68</v>
       </c>
+      <c r="M21" s="17">
+        <v>0.6</v>
+      </c>
       <c r="P21" s="4"/>
     </row>
     <row r="22" spans="1:16">
@@ -3074,6 +3134,9 @@
       <c r="L22" s="17">
         <v>0.68</v>
       </c>
+      <c r="M22" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P22" s="4"/>
     </row>
     <row r="23" spans="1:16">
@@ -3113,6 +3176,9 @@
       <c r="L23" s="17">
         <v>0.68</v>
       </c>
+      <c r="M23" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P23" s="4"/>
     </row>
     <row r="24" spans="1:16">
@@ -3152,6 +3218,9 @@
       <c r="L24" s="17">
         <v>0.48</v>
       </c>
+      <c r="M24" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P24" s="4"/>
     </row>
     <row r="25" spans="1:16">
@@ -3189,6 +3258,9 @@
       <c r="L25" s="17">
         <v>0.8</v>
       </c>
+      <c r="M25" s="17">
+        <v>0.6</v>
+      </c>
       <c r="P25" s="4"/>
     </row>
     <row r="26" spans="1:16">
@@ -3228,6 +3300,9 @@
       <c r="L26" s="17">
         <v>0.48</v>
       </c>
+      <c r="M26" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P26" s="4"/>
     </row>
     <row r="27" spans="1:16">
@@ -3267,6 +3342,9 @@
       <c r="L27" s="17">
         <v>0.8</v>
       </c>
+      <c r="M27" s="17">
+        <v>0.6</v>
+      </c>
       <c r="P27" s="4"/>
     </row>
     <row r="28" spans="1:16">
@@ -3304,6 +3382,9 @@
       <c r="L28" s="17">
         <v>0.48</v>
       </c>
+      <c r="M28" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P28" s="4"/>
     </row>
     <row r="29" spans="1:16">
@@ -3341,6 +3422,9 @@
       <c r="L29" s="17">
         <v>0.8</v>
       </c>
+      <c r="M29" s="17">
+        <v>0.6</v>
+      </c>
       <c r="P29" s="4"/>
     </row>
     <row r="30" spans="1:16">
@@ -3380,6 +3464,9 @@
       <c r="L30" s="17">
         <v>0.48</v>
       </c>
+      <c r="M30" s="17">
+        <v>0.48</v>
+      </c>
       <c r="P30" s="4"/>
     </row>
     <row r="31" spans="1:16">
@@ -3419,6 +3506,9 @@
       <c r="L31" s="17">
         <v>0.24</v>
       </c>
+      <c r="M31" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P31" s="4"/>
     </row>
     <row r="32" spans="1:16">
@@ -3456,6 +3546,9 @@
       <c r="L32" s="17">
         <v>0.8</v>
       </c>
+      <c r="M32" s="17">
+        <v>0.67</v>
+      </c>
       <c r="P32" s="4"/>
     </row>
     <row r="33" spans="1:16">
@@ -3495,6 +3588,9 @@
       <c r="L33" s="17">
         <v>0.8</v>
       </c>
+      <c r="M33" s="17">
+        <v>0.67</v>
+      </c>
       <c r="P33" s="4"/>
     </row>
     <row r="34" spans="1:16">
@@ -3534,6 +3630,9 @@
       <c r="L34" s="17">
         <v>0</v>
       </c>
+      <c r="M34" s="17">
+        <v>0</v>
+      </c>
       <c r="P34" s="4"/>
     </row>
     <row r="35" spans="1:16">
@@ -3573,6 +3672,9 @@
       <c r="L35" s="17">
         <v>0.24</v>
       </c>
+      <c r="M35" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P35" s="4"/>
     </row>
     <row r="36" spans="1:16">
@@ -3612,6 +3714,9 @@
       <c r="L36" s="17">
         <v>0</v>
       </c>
+      <c r="M36" s="17">
+        <v>0</v>
+      </c>
       <c r="P36" s="4"/>
     </row>
     <row r="37" spans="1:16" ht="20">
@@ -3649,6 +3754,9 @@
       <c r="L37" s="17">
         <v>0</v>
       </c>
+      <c r="M37" s="17">
+        <v>0</v>
+      </c>
       <c r="P37" s="4"/>
     </row>
     <row r="38" spans="1:16">
@@ -3686,6 +3794,9 @@
       <c r="L38" s="17">
         <v>0</v>
       </c>
+      <c r="M38" s="17">
+        <v>0</v>
+      </c>
       <c r="P38" s="15"/>
     </row>
     <row r="39" spans="1:16">
@@ -3723,6 +3834,9 @@
       <c r="L39" s="17">
         <v>0.8</v>
       </c>
+      <c r="M39" s="17">
+        <v>0.67</v>
+      </c>
       <c r="P39" s="4"/>
     </row>
     <row r="40" spans="1:16">
@@ -3762,6 +3876,9 @@
       <c r="L40" s="17">
         <v>0.8</v>
       </c>
+      <c r="M40" s="17">
+        <v>0.67</v>
+      </c>
       <c r="P40" s="4"/>
     </row>
     <row r="41" spans="1:16">
@@ -3801,6 +3918,9 @@
       <c r="L41" s="17">
         <v>0.24</v>
       </c>
+      <c r="M41" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P41" s="4"/>
     </row>
     <row r="42" spans="1:16">
@@ -3840,6 +3960,9 @@
       <c r="L42" s="17">
         <v>0.24</v>
       </c>
+      <c r="M42" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P42" s="4"/>
     </row>
     <row r="43" spans="1:16">
@@ -3877,6 +4000,9 @@
       <c r="L43" s="17">
         <v>0</v>
       </c>
+      <c r="M43" s="17">
+        <v>0</v>
+      </c>
       <c r="P43" s="15"/>
     </row>
     <row r="44" spans="1:16">
@@ -3914,6 +4040,9 @@
       <c r="L44" s="17">
         <v>0</v>
       </c>
+      <c r="M44" s="17">
+        <v>0</v>
+      </c>
       <c r="P44" s="15"/>
     </row>
     <row r="45" spans="1:16">
@@ -3953,6 +4082,9 @@
       <c r="L45" s="17">
         <v>0.8</v>
       </c>
+      <c r="M45" s="17">
+        <v>0.67</v>
+      </c>
       <c r="P45" s="4"/>
     </row>
     <row r="46" spans="1:16">
@@ -3992,6 +4124,9 @@
       <c r="L46" s="17">
         <v>0.24</v>
       </c>
+      <c r="M46" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P46" s="4"/>
     </row>
     <row r="47" spans="1:16">
@@ -4031,6 +4166,9 @@
       <c r="L47" s="17">
         <v>0.24</v>
       </c>
+      <c r="M47" s="17">
+        <v>0.66</v>
+      </c>
       <c r="P47" s="4"/>
     </row>
     <row r="48" spans="1:16">
@@ -4069,6 +4207,9 @@
       </c>
       <c r="L48" s="17">
         <v>0.8</v>
+      </c>
+      <c r="M48" s="17">
+        <v>0.67</v>
       </c>
       <c r="P48" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5844C1-26EB-BE45-847D-A9A841F6E708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BDE2A1-0E9E-F84D-AA98-AB155D443BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2302,9 +2302,12 @@
       <c r="M2" s="17">
         <v>0.71</v>
       </c>
-      <c r="P2" s="22" t="e">
+      <c r="O2" s="17">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="P2" s="22">
         <f>(((LARGE(D2:G2,1)+LARGE(D2:G2,2)+LARGE(D2:G2,3))*0.2/3+(LARGE(H2:K2,1)+LARGE(H2:K2,2)+LARGE(H2:K2,3))*0.5/3+(LARGE(L2:O2,1)+LARGE(L2:O2,2)+LARGE(L2:O2,3))*0.3/3))</f>
-        <v>#NUM!</v>
+        <v>0.7466666666666667</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2347,6 +2350,9 @@
       <c r="M3" s="17">
         <v>0.71</v>
       </c>
+      <c r="O3" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16">
@@ -2389,6 +2395,9 @@
       <c r="M4" s="17">
         <v>0.76</v>
       </c>
+      <c r="O4" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P4" s="4"/>
     </row>
     <row r="5" spans="1:16">
@@ -2431,6 +2440,9 @@
       <c r="M5" s="17">
         <v>0.76</v>
       </c>
+      <c r="O5" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P5" s="4"/>
     </row>
     <row r="6" spans="1:16">
@@ -2471,6 +2483,9 @@
       <c r="M6" s="17">
         <v>0.71</v>
       </c>
+      <c r="O6" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P6" s="4"/>
     </row>
     <row r="7" spans="1:16">
@@ -2513,6 +2528,9 @@
       <c r="M7" s="17">
         <v>0.48</v>
       </c>
+      <c r="O7" s="17">
+        <v>0</v>
+      </c>
       <c r="P7" s="4"/>
     </row>
     <row r="8" spans="1:16">
@@ -2555,6 +2573,9 @@
       <c r="M8" s="17">
         <v>0.6</v>
       </c>
+      <c r="O8" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P8" s="4"/>
     </row>
     <row r="9" spans="1:16">
@@ -2597,6 +2618,9 @@
       <c r="M9" s="17">
         <v>0.71</v>
       </c>
+      <c r="O9" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P9" s="4"/>
     </row>
     <row r="10" spans="1:16">
@@ -2637,6 +2661,9 @@
       <c r="M10" s="17">
         <v>0.71</v>
       </c>
+      <c r="O10" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P10" s="4"/>
     </row>
     <row r="11" spans="1:16">
@@ -2679,6 +2706,9 @@
       <c r="M11" s="17">
         <v>0.48</v>
       </c>
+      <c r="O11" s="17">
+        <v>0</v>
+      </c>
       <c r="P11" s="4"/>
     </row>
     <row r="12" spans="1:16">
@@ -2721,6 +2751,9 @@
       <c r="M12" s="17">
         <v>0.76</v>
       </c>
+      <c r="O12" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P12" s="4"/>
     </row>
     <row r="13" spans="1:16">
@@ -2763,6 +2796,9 @@
       <c r="M13" s="17">
         <v>0.48</v>
       </c>
+      <c r="O13" s="17">
+        <v>0</v>
+      </c>
       <c r="P13" s="4"/>
     </row>
     <row r="14" spans="1:16">
@@ -2805,6 +2841,9 @@
       <c r="M14" s="17">
         <v>0.76</v>
       </c>
+      <c r="O14" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P14" s="4"/>
     </row>
     <row r="15" spans="1:16">
@@ -2845,6 +2884,9 @@
       <c r="M15" s="17">
         <v>0.71</v>
       </c>
+      <c r="O15" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P15" s="4"/>
     </row>
     <row r="16" spans="1:16">
@@ -2887,6 +2929,9 @@
       <c r="M16" s="17">
         <v>0.48</v>
       </c>
+      <c r="O16" s="17">
+        <v>0</v>
+      </c>
       <c r="P16" s="4"/>
     </row>
     <row r="17" spans="1:16">
@@ -2929,6 +2974,9 @@
       <c r="M17" s="17">
         <v>0.71</v>
       </c>
+      <c r="O17" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P17" s="4"/>
     </row>
     <row r="18" spans="1:16">
@@ -2971,6 +3019,9 @@
       <c r="M18" s="17">
         <v>0.48</v>
       </c>
+      <c r="O18" s="17">
+        <v>0</v>
+      </c>
       <c r="P18" s="4"/>
     </row>
     <row r="19" spans="1:16">
@@ -3011,6 +3062,9 @@
       <c r="M19" s="17">
         <v>0</v>
       </c>
+      <c r="O19" s="17">
+        <v>0</v>
+      </c>
       <c r="P19" s="15"/>
     </row>
     <row r="20" spans="1:16">
@@ -3053,6 +3107,9 @@
       <c r="M20" s="17">
         <v>0.76</v>
       </c>
+      <c r="O20" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P20" s="4"/>
     </row>
     <row r="21" spans="1:16">
@@ -3095,6 +3152,9 @@
       <c r="M21" s="17">
         <v>0.6</v>
       </c>
+      <c r="O21" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P21" s="4"/>
     </row>
     <row r="22" spans="1:16">
@@ -3137,6 +3197,9 @@
       <c r="M22" s="17">
         <v>0.71</v>
       </c>
+      <c r="O22" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P22" s="4"/>
     </row>
     <row r="23" spans="1:16">
@@ -3179,6 +3242,9 @@
       <c r="M23" s="17">
         <v>0.71</v>
       </c>
+      <c r="O23" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P23" s="4"/>
     </row>
     <row r="24" spans="1:16">
@@ -3221,6 +3287,9 @@
       <c r="M24" s="17">
         <v>0.76</v>
       </c>
+      <c r="O24" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P24" s="4"/>
     </row>
     <row r="25" spans="1:16">
@@ -3261,6 +3330,9 @@
       <c r="M25" s="17">
         <v>0.6</v>
       </c>
+      <c r="O25" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P25" s="4"/>
     </row>
     <row r="26" spans="1:16">
@@ -3303,6 +3375,9 @@
       <c r="M26" s="17">
         <v>0.71</v>
       </c>
+      <c r="O26" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P26" s="4"/>
     </row>
     <row r="27" spans="1:16">
@@ -3345,6 +3420,9 @@
       <c r="M27" s="17">
         <v>0.6</v>
       </c>
+      <c r="O27" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P27" s="4"/>
     </row>
     <row r="28" spans="1:16">
@@ -3385,6 +3463,9 @@
       <c r="M28" s="17">
         <v>0.71</v>
       </c>
+      <c r="O28" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P28" s="4"/>
     </row>
     <row r="29" spans="1:16">
@@ -3425,6 +3506,9 @@
       <c r="M29" s="17">
         <v>0.6</v>
       </c>
+      <c r="O29" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P29" s="4"/>
     </row>
     <row r="30" spans="1:16">
@@ -3467,6 +3551,9 @@
       <c r="M30" s="17">
         <v>0.48</v>
       </c>
+      <c r="O30" s="17">
+        <v>0</v>
+      </c>
       <c r="P30" s="4"/>
     </row>
     <row r="31" spans="1:16">
@@ -3509,6 +3596,9 @@
       <c r="M31" s="17">
         <v>0.66</v>
       </c>
+      <c r="O31" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P31" s="4"/>
     </row>
     <row r="32" spans="1:16">
@@ -3549,6 +3639,9 @@
       <c r="M32" s="17">
         <v>0.67</v>
       </c>
+      <c r="O32" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P32" s="4"/>
     </row>
     <row r="33" spans="1:16">
@@ -3591,6 +3684,9 @@
       <c r="M33" s="17">
         <v>0.67</v>
       </c>
+      <c r="O33" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P33" s="4"/>
     </row>
     <row r="34" spans="1:16">
@@ -3633,6 +3729,9 @@
       <c r="M34" s="17">
         <v>0</v>
       </c>
+      <c r="O34" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P34" s="4"/>
     </row>
     <row r="35" spans="1:16">
@@ -3675,6 +3774,9 @@
       <c r="M35" s="17">
         <v>0.66</v>
       </c>
+      <c r="O35" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P35" s="4"/>
     </row>
     <row r="36" spans="1:16">
@@ -3717,6 +3819,9 @@
       <c r="M36" s="17">
         <v>0</v>
       </c>
+      <c r="O36" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P36" s="4"/>
     </row>
     <row r="37" spans="1:16" ht="20">
@@ -3757,6 +3862,9 @@
       <c r="M37" s="17">
         <v>0</v>
       </c>
+      <c r="O37" s="17">
+        <v>0</v>
+      </c>
       <c r="P37" s="4"/>
     </row>
     <row r="38" spans="1:16">
@@ -3797,6 +3905,9 @@
       <c r="M38" s="17">
         <v>0</v>
       </c>
+      <c r="O38" s="17">
+        <v>0</v>
+      </c>
       <c r="P38" s="15"/>
     </row>
     <row r="39" spans="1:16">
@@ -3837,6 +3948,9 @@
       <c r="M39" s="17">
         <v>0.67</v>
       </c>
+      <c r="O39" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P39" s="4"/>
     </row>
     <row r="40" spans="1:16">
@@ -3879,6 +3993,9 @@
       <c r="M40" s="17">
         <v>0.67</v>
       </c>
+      <c r="O40" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P40" s="4"/>
     </row>
     <row r="41" spans="1:16">
@@ -3921,6 +4038,9 @@
       <c r="M41" s="17">
         <v>0.66</v>
       </c>
+      <c r="O41" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P41" s="4"/>
     </row>
     <row r="42" spans="1:16">
@@ -3963,6 +4083,9 @@
       <c r="M42" s="17">
         <v>0.66</v>
       </c>
+      <c r="O42" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P42" s="4"/>
     </row>
     <row r="43" spans="1:16">
@@ -4003,6 +4126,9 @@
       <c r="M43" s="17">
         <v>0</v>
       </c>
+      <c r="O43" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P43" s="15"/>
     </row>
     <row r="44" spans="1:16">
@@ -4043,6 +4169,9 @@
       <c r="M44" s="17">
         <v>0</v>
       </c>
+      <c r="O44" s="17">
+        <v>0</v>
+      </c>
       <c r="P44" s="15"/>
     </row>
     <row r="45" spans="1:16">
@@ -4085,6 +4214,9 @@
       <c r="M45" s="17">
         <v>0.67</v>
       </c>
+      <c r="O45" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P45" s="4"/>
     </row>
     <row r="46" spans="1:16">
@@ -4127,6 +4259,9 @@
       <c r="M46" s="17">
         <v>0.66</v>
       </c>
+      <c r="O46" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P46" s="4"/>
     </row>
     <row r="47" spans="1:16">
@@ -4169,6 +4304,9 @@
       <c r="M47" s="17">
         <v>0.66</v>
       </c>
+      <c r="O47" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P47" s="4"/>
     </row>
     <row r="48" spans="1:16">
@@ -4211,6 +4349,9 @@
       <c r="M48" s="17">
         <v>0.67</v>
       </c>
+      <c r="O48" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P48" s="4"/>
     </row>
     <row r="49" spans="1:16">
@@ -6586,6 +6727,9 @@
       <c r="M105" s="17">
         <v>0.84</v>
       </c>
+      <c r="O105" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P105" s="4"/>
     </row>
     <row r="106" spans="1:16">
@@ -6709,6 +6853,9 @@
       <c r="M108" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="O108" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P108" s="4"/>
     </row>
     <row r="109" spans="1:16">
@@ -6958,6 +7105,9 @@
       <c r="M114" s="17">
         <v>0.84</v>
       </c>
+      <c r="O114" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P114" s="4"/>
     </row>
     <row r="115" spans="1:16">
@@ -7288,6 +7438,9 @@
       <c r="M122" s="17">
         <v>0.84</v>
       </c>
+      <c r="O122" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P122" s="4"/>
     </row>
     <row r="123" spans="1:16">
@@ -7372,6 +7525,9 @@
       <c r="M124" s="17">
         <v>0.84</v>
       </c>
+      <c r="O124" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P124" s="4"/>
     </row>
     <row r="125" spans="1:16">
@@ -7492,6 +7648,9 @@
       <c r="M127" s="17">
         <v>0.84</v>
       </c>
+      <c r="O127" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P127" s="4"/>
     </row>
     <row r="128" spans="1:16">
@@ -7534,6 +7693,9 @@
       <c r="M128" s="17">
         <v>0.84</v>
       </c>
+      <c r="O128" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P128" s="4"/>
     </row>
     <row r="129" spans="1:16">
@@ -7575,6 +7737,9 @@
       </c>
       <c r="M129" s="17">
         <v>0.56999999999999995</v>
+      </c>
+      <c r="O129" s="17">
+        <v>0.44</v>
       </c>
       <c r="P129" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BDE2A1-0E9E-F84D-AA98-AB155D443BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D07351-1620-9F49-B7E2-49D06219776C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2302,12 +2302,15 @@
       <c r="M2" s="17">
         <v>0.71</v>
       </c>
+      <c r="N2" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O2" s="17">
         <v>0.56000000000000005</v>
       </c>
       <c r="P2" s="22">
         <f>(((LARGE(D2:G2,1)+LARGE(D2:G2,2)+LARGE(D2:G2,3))*0.2/3+(LARGE(H2:K2,1)+LARGE(H2:K2,2)+LARGE(H2:K2,3))*0.5/3+(LARGE(L2:O2,1)+LARGE(L2:O2,2)+LARGE(L2:O2,3))*0.3/3))</f>
-        <v>0.7466666666666667</v>
+        <v>0.78066666666666662</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2350,10 +2353,16 @@
       <c r="M3" s="17">
         <v>0.71</v>
       </c>
+      <c r="N3" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O3" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P3" s="4"/>
+      <c r="P3" s="22">
+        <f t="shared" ref="P3:P48" si="0">(((LARGE(D3:G3,1)+LARGE(D3:G3,2)+LARGE(D3:G3,3))*0.2/3+(LARGE(H3:K3,1)+LARGE(H3:K3,2)+LARGE(H3:K3,3))*0.5/3+(LARGE(L3:O3,1)+LARGE(L3:O3,2)+LARGE(L3:O3,3))*0.3/3))</f>
+        <v>0.56499999999999995</v>
+      </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="5" t="s">
@@ -2395,10 +2404,16 @@
       <c r="M4" s="17">
         <v>0.76</v>
       </c>
+      <c r="N4" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O4" s="17">
         <v>0.41</v>
       </c>
-      <c r="P4" s="4"/>
+      <c r="P4" s="22">
+        <f t="shared" si="0"/>
+        <v>0.58833333333333326</v>
+      </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="5" t="s">
@@ -2440,10 +2455,16 @@
       <c r="M5" s="17">
         <v>0.76</v>
       </c>
+      <c r="N5" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O5" s="17">
         <v>0.41</v>
       </c>
-      <c r="P5" s="4"/>
+      <c r="P5" s="22">
+        <f t="shared" si="0"/>
+        <v>0.58799999999999997</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="6" t="s">
@@ -2483,10 +2504,16 @@
       <c r="M6" s="17">
         <v>0.71</v>
       </c>
+      <c r="N6" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O6" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P6" s="4"/>
+      <c r="P6" s="22">
+        <f t="shared" si="0"/>
+        <v>0.58933333333333326</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="5" t="s">
@@ -2528,10 +2555,16 @@
       <c r="M7" s="17">
         <v>0.48</v>
       </c>
+      <c r="N7" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O7" s="17">
         <v>0</v>
       </c>
-      <c r="P7" s="4"/>
+      <c r="P7" s="22">
+        <f t="shared" si="0"/>
+        <v>0.55466666666666664</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="6" t="s">
@@ -2573,10 +2606,16 @@
       <c r="M8" s="17">
         <v>0.6</v>
       </c>
+      <c r="N8" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O8" s="17">
         <v>0.59</v>
       </c>
-      <c r="P8" s="4"/>
+      <c r="P8" s="22">
+        <f t="shared" si="0"/>
+        <v>0.3763333333333333</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="6" t="s">
@@ -2618,10 +2657,16 @@
       <c r="M9" s="17">
         <v>0.71</v>
       </c>
+      <c r="N9" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O9" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P9" s="4"/>
+      <c r="P9" s="22">
+        <f t="shared" si="0"/>
+        <v>0.6113333333333334</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="5" t="s">
@@ -2661,10 +2706,16 @@
       <c r="M10" s="17">
         <v>0.71</v>
       </c>
+      <c r="N10" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O10" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P10" s="4"/>
+      <c r="P10" s="22">
+        <f t="shared" si="0"/>
+        <v>0.65266666666666662</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="6" t="s">
@@ -2706,10 +2757,16 @@
       <c r="M11" s="17">
         <v>0.48</v>
       </c>
+      <c r="N11" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O11" s="17">
         <v>0</v>
       </c>
-      <c r="P11" s="4"/>
+      <c r="P11" s="22">
+        <f t="shared" si="0"/>
+        <v>0.51566666666666661</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="5" t="s">
@@ -2751,10 +2808,16 @@
       <c r="M12" s="17">
         <v>0.76</v>
       </c>
+      <c r="N12" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O12" s="17">
         <v>0.41</v>
       </c>
-      <c r="P12" s="4"/>
+      <c r="P12" s="22">
+        <f t="shared" si="0"/>
+        <v>0.64733333333333332</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="6" t="s">
@@ -2796,10 +2859,16 @@
       <c r="M13" s="17">
         <v>0.48</v>
       </c>
+      <c r="N13" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O13" s="17">
         <v>0</v>
       </c>
-      <c r="P13" s="4"/>
+      <c r="P13" s="22">
+        <f t="shared" si="0"/>
+        <v>0.624</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="5" t="s">
@@ -2841,10 +2910,16 @@
       <c r="M14" s="17">
         <v>0.76</v>
       </c>
+      <c r="N14" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O14" s="17">
         <v>0.41</v>
       </c>
-      <c r="P14" s="4"/>
+      <c r="P14" s="22">
+        <f t="shared" si="0"/>
+        <v>0.60033333333333339</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="6" t="s">
@@ -2884,10 +2959,16 @@
       <c r="M15" s="17">
         <v>0.71</v>
       </c>
+      <c r="N15" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O15" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P15" s="4"/>
+      <c r="P15" s="22">
+        <f t="shared" si="0"/>
+        <v>0.68133333333333335</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="6" t="s">
@@ -2929,10 +3010,16 @@
       <c r="M16" s="17">
         <v>0.48</v>
       </c>
+      <c r="N16" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O16" s="17">
         <v>0</v>
       </c>
-      <c r="P16" s="4"/>
+      <c r="P16" s="22">
+        <f t="shared" si="0"/>
+        <v>0.45233333333333325</v>
+      </c>
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="6" t="s">
@@ -2974,10 +3061,16 @@
       <c r="M17" s="17">
         <v>0.71</v>
       </c>
+      <c r="N17" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O17" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P17" s="4"/>
+      <c r="P17" s="22">
+        <f t="shared" si="0"/>
+        <v>0.55066666666666664</v>
+      </c>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="5" t="s">
@@ -3019,10 +3112,16 @@
       <c r="M18" s="17">
         <v>0.48</v>
       </c>
+      <c r="N18" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O18" s="17">
         <v>0</v>
       </c>
-      <c r="P18" s="4"/>
+      <c r="P18" s="22">
+        <f t="shared" si="0"/>
+        <v>0.62066666666666659</v>
+      </c>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="12" t="s">
@@ -3062,10 +3161,16 @@
       <c r="M19" s="17">
         <v>0</v>
       </c>
+      <c r="N19" s="17">
+        <v>0</v>
+      </c>
       <c r="O19" s="17">
         <v>0</v>
       </c>
-      <c r="P19" s="15"/>
+      <c r="P19" s="22">
+        <f t="shared" si="0"/>
+        <v>8.8333333333333333E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="6" t="s">
@@ -3107,10 +3212,16 @@
       <c r="M20" s="17">
         <v>0.76</v>
       </c>
+      <c r="N20" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O20" s="17">
         <v>0.41</v>
       </c>
-      <c r="P20" s="4"/>
+      <c r="P20" s="22">
+        <f t="shared" si="0"/>
+        <v>0.69866666666666666</v>
+      </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="5" t="s">
@@ -3152,10 +3263,16 @@
       <c r="M21" s="17">
         <v>0.6</v>
       </c>
+      <c r="N21" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O21" s="17">
         <v>0.59</v>
       </c>
-      <c r="P21" s="4"/>
+      <c r="P21" s="22">
+        <f t="shared" si="0"/>
+        <v>0.67666666666666664</v>
+      </c>
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="5" t="s">
@@ -3197,10 +3314,16 @@
       <c r="M22" s="17">
         <v>0.71</v>
       </c>
+      <c r="N22" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O22" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P22" s="4"/>
+      <c r="P22" s="22">
+        <f t="shared" si="0"/>
+        <v>0.6356666666666666</v>
+      </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="6" t="s">
@@ -3242,10 +3365,16 @@
       <c r="M23" s="17">
         <v>0.71</v>
       </c>
+      <c r="N23" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O23" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P23" s="4"/>
+      <c r="P23" s="22">
+        <f t="shared" si="0"/>
+        <v>0.69233333333333336</v>
+      </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="5" t="s">
@@ -3287,10 +3416,16 @@
       <c r="M24" s="17">
         <v>0.76</v>
       </c>
+      <c r="N24" s="17">
+        <v>0.79</v>
+      </c>
       <c r="O24" s="17">
         <v>0.41</v>
       </c>
-      <c r="P24" s="4"/>
+      <c r="P24" s="22">
+        <f t="shared" si="0"/>
+        <v>0.74933333333333341</v>
+      </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="5" t="s">
@@ -3330,10 +3465,16 @@
       <c r="M25" s="17">
         <v>0.6</v>
       </c>
+      <c r="N25" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O25" s="17">
         <v>0.59</v>
       </c>
-      <c r="P25" s="4"/>
+      <c r="P25" s="22">
+        <f t="shared" si="0"/>
+        <v>0.64366666666666661</v>
+      </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="6" t="s">
@@ -3375,10 +3516,16 @@
       <c r="M26" s="17">
         <v>0.71</v>
       </c>
+      <c r="N26" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O26" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P26" s="4"/>
+      <c r="P26" s="22">
+        <f t="shared" si="0"/>
+        <v>0.64966666666666661</v>
+      </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="5" t="s">
@@ -3420,10 +3567,16 @@
       <c r="M27" s="17">
         <v>0.6</v>
       </c>
+      <c r="N27" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O27" s="17">
         <v>0.59</v>
       </c>
-      <c r="P27" s="4"/>
+      <c r="P27" s="22">
+        <f t="shared" si="0"/>
+        <v>0.65566666666666662</v>
+      </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="5" t="s">
@@ -3463,10 +3616,16 @@
       <c r="M28" s="17">
         <v>0.71</v>
       </c>
+      <c r="N28" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O28" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P28" s="4"/>
+      <c r="P28" s="22">
+        <f t="shared" si="0"/>
+        <v>0.62399999999999989</v>
+      </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="6" t="s">
@@ -3506,10 +3665,16 @@
       <c r="M29" s="17">
         <v>0.6</v>
       </c>
+      <c r="N29" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O29" s="17">
         <v>0.59</v>
       </c>
-      <c r="P29" s="4"/>
+      <c r="P29" s="22">
+        <f t="shared" si="0"/>
+        <v>0.73266666666666669</v>
+      </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" s="5" t="s">
@@ -3551,10 +3716,16 @@
       <c r="M30" s="17">
         <v>0.48</v>
       </c>
+      <c r="N30" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O30" s="17">
         <v>0</v>
       </c>
-      <c r="P30" s="4"/>
+      <c r="P30" s="22">
+        <f t="shared" si="0"/>
+        <v>0.50733333333333319</v>
+      </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="6" t="s">
@@ -3596,10 +3767,16 @@
       <c r="M31" s="17">
         <v>0.66</v>
       </c>
+      <c r="N31" s="17">
+        <v>0.88</v>
+      </c>
       <c r="O31" s="17">
         <v>0.91</v>
       </c>
-      <c r="P31" s="4"/>
+      <c r="P31" s="22">
+        <f t="shared" si="0"/>
+        <v>0.72599999999999998</v>
+      </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="5" t="s">
@@ -3639,10 +3816,16 @@
       <c r="M32" s="17">
         <v>0.67</v>
       </c>
+      <c r="N32" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O32" s="17">
         <v>0.59</v>
       </c>
-      <c r="P32" s="4"/>
+      <c r="P32" s="22">
+        <f t="shared" si="0"/>
+        <v>0.59899999999999998</v>
+      </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="5" t="s">
@@ -3684,10 +3867,16 @@
       <c r="M33" s="17">
         <v>0.67</v>
       </c>
+      <c r="N33" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O33" s="17">
         <v>0.59</v>
       </c>
-      <c r="P33" s="4"/>
+      <c r="P33" s="22">
+        <f t="shared" si="0"/>
+        <v>0.6163333333333334</v>
+      </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="10" t="s">
@@ -3729,10 +3918,16 @@
       <c r="M34" s="17">
         <v>0</v>
       </c>
+      <c r="N34" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O34" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P34" s="4"/>
+      <c r="P34" s="22">
+        <f t="shared" si="0"/>
+        <v>0.39933333333333332</v>
+      </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="6" t="s">
@@ -3774,10 +3969,16 @@
       <c r="M35" s="17">
         <v>0.66</v>
       </c>
+      <c r="N35" s="17">
+        <v>0.88</v>
+      </c>
       <c r="O35" s="17">
         <v>0.91</v>
       </c>
-      <c r="P35" s="4"/>
+      <c r="P35" s="22">
+        <f t="shared" si="0"/>
+        <v>0.78</v>
+      </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="10" t="s">
@@ -3819,10 +4020,16 @@
       <c r="M36" s="17">
         <v>0</v>
       </c>
+      <c r="N36" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O36" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P36" s="4"/>
+      <c r="P36" s="22">
+        <f t="shared" si="0"/>
+        <v>0.44699999999999995</v>
+      </c>
     </row>
     <row r="37" spans="1:16" ht="20">
       <c r="A37" s="7" t="s">
@@ -3862,10 +4069,16 @@
       <c r="M37" s="17">
         <v>0</v>
       </c>
+      <c r="N37" s="17">
+        <v>0</v>
+      </c>
       <c r="O37" s="17">
         <v>0</v>
       </c>
-      <c r="P37" s="4"/>
+      <c r="P37" s="22">
+        <f t="shared" si="0"/>
+        <v>0.255</v>
+      </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="12" t="s">
@@ -3905,10 +4118,16 @@
       <c r="M38" s="17">
         <v>0</v>
       </c>
+      <c r="N38" s="17">
+        <v>0</v>
+      </c>
       <c r="O38" s="17">
         <v>0</v>
       </c>
-      <c r="P38" s="15"/>
+      <c r="P38" s="22">
+        <f t="shared" si="0"/>
+        <v>0.20666666666666667</v>
+      </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="6" t="s">
@@ -3948,10 +4167,16 @@
       <c r="M39" s="17">
         <v>0.67</v>
       </c>
+      <c r="N39" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O39" s="17">
         <v>0.59</v>
       </c>
-      <c r="P39" s="4"/>
+      <c r="P39" s="22">
+        <f t="shared" si="0"/>
+        <v>0.67966666666666664</v>
+      </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="5" t="s">
@@ -3993,10 +4218,16 @@
       <c r="M40" s="17">
         <v>0.67</v>
       </c>
+      <c r="N40" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O40" s="17">
         <v>0.59</v>
       </c>
-      <c r="P40" s="4"/>
+      <c r="P40" s="22">
+        <f t="shared" si="0"/>
+        <v>0.63833333333333331</v>
+      </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="6" t="s">
@@ -4038,10 +4269,16 @@
       <c r="M41" s="17">
         <v>0.66</v>
       </c>
+      <c r="N41" s="17">
+        <v>0.88</v>
+      </c>
       <c r="O41" s="17">
         <v>0.91</v>
       </c>
-      <c r="P41" s="4"/>
+      <c r="P41" s="22">
+        <f t="shared" si="0"/>
+        <v>0.70599999999999996</v>
+      </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="6" t="s">
@@ -4083,10 +4320,16 @@
       <c r="M42" s="17">
         <v>0.66</v>
       </c>
+      <c r="N42" s="17">
+        <v>0.88</v>
+      </c>
       <c r="O42" s="17">
         <v>0.91</v>
       </c>
-      <c r="P42" s="4"/>
+      <c r="P42" s="22">
+        <f t="shared" si="0"/>
+        <v>0.63266666666666671</v>
+      </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" t="s">
@@ -4126,10 +4369,16 @@
       <c r="M43" s="17">
         <v>0</v>
       </c>
+      <c r="N43" s="17">
+        <v>0.88</v>
+      </c>
       <c r="O43" s="17">
         <v>0.91</v>
       </c>
-      <c r="P43" s="15"/>
+      <c r="P43" s="22">
+        <f t="shared" si="0"/>
+        <v>0.42066666666666674</v>
+      </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" t="s">
@@ -4169,10 +4418,16 @@
       <c r="M44" s="17">
         <v>0</v>
       </c>
+      <c r="N44" s="17">
+        <v>0</v>
+      </c>
       <c r="O44" s="17">
         <v>0</v>
       </c>
-      <c r="P44" s="15"/>
+      <c r="P44" s="22">
+        <f t="shared" si="0"/>
+        <v>0.18000000000000002</v>
+      </c>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="13" t="s">
@@ -4214,10 +4469,16 @@
       <c r="M45" s="17">
         <v>0.67</v>
       </c>
+      <c r="N45" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O45" s="17">
         <v>0.59</v>
       </c>
-      <c r="P45" s="4"/>
+      <c r="P45" s="22">
+        <f t="shared" si="0"/>
+        <v>0.6293333333333333</v>
+      </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="13" t="s">
@@ -4259,10 +4520,16 @@
       <c r="M46" s="17">
         <v>0.66</v>
       </c>
+      <c r="N46" s="17">
+        <v>0.88</v>
+      </c>
       <c r="O46" s="17">
         <v>0.91</v>
       </c>
-      <c r="P46" s="4"/>
+      <c r="P46" s="22">
+        <f t="shared" si="0"/>
+        <v>0.69766666666666666</v>
+      </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="11" t="s">
@@ -4304,10 +4571,16 @@
       <c r="M47" s="17">
         <v>0.66</v>
       </c>
+      <c r="N47" s="17">
+        <v>0.88</v>
+      </c>
       <c r="O47" s="17">
         <v>0.91</v>
       </c>
-      <c r="P47" s="4"/>
+      <c r="P47" s="22">
+        <f t="shared" si="0"/>
+        <v>0.64633333333333343</v>
+      </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="11" t="s">
@@ -4349,10 +4622,16 @@
       <c r="M48" s="17">
         <v>0.67</v>
       </c>
+      <c r="N48" s="17">
+        <v>0.82</v>
+      </c>
       <c r="O48" s="17">
         <v>0.59</v>
       </c>
-      <c r="P48" s="4"/>
+      <c r="P48" s="22">
+        <f t="shared" si="0"/>
+        <v>0.69066666666666665</v>
+      </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="9" t="s">

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D07351-1620-9F49-B7E2-49D06219776C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCDBEDD-55EC-7C4B-8264-584178327B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4673,6 +4673,9 @@
       <c r="M49" s="17">
         <v>0.72</v>
       </c>
+      <c r="N49" s="17">
+        <v>0.52</v>
+      </c>
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
@@ -4715,6 +4718,9 @@
       <c r="M50" s="17">
         <v>0.64</v>
       </c>
+      <c r="N50" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P50" s="4"/>
     </row>
     <row r="51" spans="1:16">
@@ -4757,6 +4763,9 @@
       <c r="M51" s="17">
         <v>0.84</v>
       </c>
+      <c r="N51" s="17">
+        <v>0.94</v>
+      </c>
       <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16">
@@ -4799,6 +4808,9 @@
       <c r="M52" s="17">
         <v>0.97</v>
       </c>
+      <c r="N52" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P52" s="4"/>
     </row>
     <row r="53" spans="1:16">
@@ -4841,6 +4853,9 @@
       <c r="M53" s="17">
         <v>0.9</v>
       </c>
+      <c r="N53" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16">
@@ -4881,6 +4896,9 @@
       <c r="M54" s="17">
         <v>0.72</v>
       </c>
+      <c r="N54" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P54" s="4"/>
     </row>
     <row r="55" spans="1:16">
@@ -4923,6 +4941,9 @@
       <c r="M55" s="17">
         <v>0.97</v>
       </c>
+      <c r="N55" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P55" s="4"/>
     </row>
     <row r="56" spans="1:16">
@@ -4965,6 +4986,9 @@
       <c r="M56" s="17">
         <v>0.84</v>
       </c>
+      <c r="N56" s="17">
+        <v>0.94</v>
+      </c>
       <c r="P56" s="4"/>
     </row>
     <row r="57" spans="1:16">
@@ -5007,6 +5031,9 @@
       <c r="M57" s="17">
         <v>0.76</v>
       </c>
+      <c r="N57" s="17">
+        <v>0.53</v>
+      </c>
       <c r="P57" s="22"/>
     </row>
     <row r="58" spans="1:16">
@@ -5049,6 +5076,9 @@
       <c r="M58" s="17">
         <v>0.72</v>
       </c>
+      <c r="N58" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P58" s="4"/>
     </row>
     <row r="59" spans="1:16">
@@ -5091,6 +5121,9 @@
       <c r="M59" s="17">
         <v>0.84</v>
       </c>
+      <c r="N59" s="17">
+        <v>0.94</v>
+      </c>
       <c r="P59" s="22"/>
     </row>
     <row r="60" spans="1:16">
@@ -5133,6 +5166,9 @@
       <c r="M60" s="17">
         <v>0.97</v>
       </c>
+      <c r="N60" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P60" s="4"/>
     </row>
     <row r="61" spans="1:16">
@@ -5175,6 +5211,9 @@
       <c r="M61" s="17">
         <v>0.72</v>
       </c>
+      <c r="N61" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P61" s="4"/>
     </row>
     <row r="62" spans="1:16">
@@ -5217,6 +5256,9 @@
       <c r="M62" s="17">
         <v>0.97</v>
       </c>
+      <c r="N62" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P62" s="4"/>
     </row>
     <row r="63" spans="1:16">
@@ -5259,6 +5301,9 @@
       <c r="M63" s="17">
         <v>0.64</v>
       </c>
+      <c r="N63" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P63" s="4"/>
     </row>
     <row r="64" spans="1:16">
@@ -5301,6 +5346,9 @@
       <c r="M64" s="17">
         <v>0.76</v>
       </c>
+      <c r="N64" s="17">
+        <v>0.53</v>
+      </c>
       <c r="P64" s="4"/>
     </row>
     <row r="65" spans="1:16">
@@ -5343,6 +5391,9 @@
       <c r="M65" s="17">
         <v>0.9</v>
       </c>
+      <c r="N65" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P65" s="4"/>
     </row>
     <row r="66" spans="1:16">
@@ -5385,6 +5436,9 @@
       <c r="M66" s="17">
         <v>0.72</v>
       </c>
+      <c r="N66" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P66" s="4"/>
     </row>
     <row r="67" spans="1:16">
@@ -5427,6 +5481,9 @@
       <c r="M67" s="17">
         <v>0.97</v>
       </c>
+      <c r="N67" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P67" s="4"/>
     </row>
     <row r="68" spans="1:16">
@@ -5469,6 +5526,9 @@
       <c r="M68" s="17">
         <v>0.9</v>
       </c>
+      <c r="N68" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P68" s="4"/>
     </row>
     <row r="69" spans="1:16">
@@ -5511,6 +5571,9 @@
       <c r="M69" s="17">
         <v>0.84</v>
       </c>
+      <c r="N69" s="17">
+        <v>0.94</v>
+      </c>
       <c r="P69" s="4"/>
     </row>
     <row r="70" spans="1:16">
@@ -5553,6 +5616,9 @@
       <c r="M70" s="17">
         <v>0.72</v>
       </c>
+      <c r="N70" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P70" s="4"/>
     </row>
     <row r="71" spans="1:16">
@@ -5595,6 +5661,9 @@
       <c r="M71" s="17">
         <v>0.76</v>
       </c>
+      <c r="N71" s="17">
+        <v>0.53</v>
+      </c>
       <c r="P71" s="4"/>
     </row>
     <row r="72" spans="1:16">
@@ -5637,6 +5706,9 @@
       <c r="M72" s="17">
         <v>0.9</v>
       </c>
+      <c r="N72" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P72" s="4"/>
     </row>
     <row r="73" spans="1:16">
@@ -5679,6 +5751,9 @@
       <c r="M73" s="17">
         <v>0.97</v>
       </c>
+      <c r="N73" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P73" s="4"/>
     </row>
     <row r="74" spans="1:16">
@@ -5721,6 +5796,9 @@
       <c r="M74" s="17">
         <v>0.72</v>
       </c>
+      <c r="N74" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P74" s="4"/>
     </row>
     <row r="75" spans="1:16">
@@ -5763,6 +5841,9 @@
       <c r="M75" s="17">
         <v>0.72</v>
       </c>
+      <c r="N75" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P75" s="4"/>
     </row>
     <row r="76" spans="1:16">
@@ -5805,6 +5886,9 @@
       <c r="M76" s="17">
         <v>0.72</v>
       </c>
+      <c r="N76" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P76" s="4"/>
     </row>
     <row r="77" spans="1:16">
@@ -5847,6 +5931,9 @@
       <c r="M77" s="17">
         <v>0.84</v>
       </c>
+      <c r="N77" s="17">
+        <v>0.94</v>
+      </c>
       <c r="P77" s="4"/>
     </row>
     <row r="78" spans="1:16">
@@ -5889,6 +5976,9 @@
       <c r="M78" s="17">
         <v>0.72</v>
       </c>
+      <c r="N78" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P78" s="4"/>
     </row>
     <row r="79" spans="1:16">
@@ -5931,6 +6021,9 @@
       <c r="M79" s="17">
         <v>0.84</v>
       </c>
+      <c r="N79" s="17">
+        <v>0.94</v>
+      </c>
       <c r="P79" s="4"/>
     </row>
     <row r="80" spans="1:16">
@@ -5971,6 +6064,9 @@
       <c r="M80" s="17">
         <v>0.64</v>
       </c>
+      <c r="N80" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P80" s="4"/>
     </row>
     <row r="81" spans="1:16">
@@ -6011,6 +6107,9 @@
       <c r="M81" s="17">
         <v>0.76</v>
       </c>
+      <c r="N81" s="17">
+        <v>0.53</v>
+      </c>
       <c r="P81" s="4"/>
     </row>
     <row r="82" spans="1:16">
@@ -6051,6 +6150,9 @@
       <c r="M82" s="17">
         <v>0.76</v>
       </c>
+      <c r="N82" s="17">
+        <v>0.53</v>
+      </c>
       <c r="P82" s="4"/>
     </row>
     <row r="83" spans="1:16">
@@ -6093,6 +6195,9 @@
       <c r="M83" s="17">
         <v>0.64</v>
       </c>
+      <c r="N83" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P83" s="4"/>
     </row>
     <row r="84" spans="1:16">
@@ -6133,6 +6238,9 @@
       <c r="M84" s="17">
         <v>0.9</v>
       </c>
+      <c r="N84" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P84" s="4"/>
     </row>
     <row r="85" spans="1:16">
@@ -6175,6 +6283,9 @@
       <c r="M85" s="17">
         <v>0.64</v>
       </c>
+      <c r="N85" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P85" s="4"/>
     </row>
     <row r="86" spans="1:16">
@@ -6217,6 +6328,9 @@
       <c r="M86" s="17">
         <v>0.72</v>
       </c>
+      <c r="N86" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P86" s="4"/>
     </row>
     <row r="87" spans="1:16">
@@ -6259,6 +6373,9 @@
       <c r="M87" s="17">
         <v>0.76</v>
       </c>
+      <c r="N87" s="17">
+        <v>0.53</v>
+      </c>
       <c r="P87" s="4"/>
     </row>
     <row r="88" spans="1:16">
@@ -6301,6 +6418,9 @@
       <c r="M88" s="17">
         <v>0.9</v>
       </c>
+      <c r="N88" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P88" s="4"/>
     </row>
     <row r="89" spans="1:16">
@@ -6342,6 +6462,9 @@
       </c>
       <c r="M89" s="17">
         <v>0.72</v>
+      </c>
+      <c r="N89" s="17">
+        <v>0.62</v>
       </c>
       <c r="P89" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCDBEDD-55EC-7C4B-8264-584178327B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE51D26-504F-484D-93CF-590611842181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6508,6 +6508,9 @@
       <c r="M90" s="17">
         <v>0</v>
       </c>
+      <c r="N90" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
@@ -6550,6 +6553,9 @@
       <c r="M91" s="17">
         <v>0.38</v>
       </c>
+      <c r="N91" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
@@ -6592,6 +6598,9 @@
       <c r="M92" s="17">
         <v>0.43</v>
       </c>
+      <c r="N92" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
@@ -6634,6 +6643,9 @@
       <c r="M93" s="17">
         <v>0.38</v>
       </c>
+      <c r="N93" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
@@ -6673,6 +6685,9 @@
       <c r="M94" s="17">
         <v>0.38</v>
       </c>
+      <c r="N94" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
@@ -6712,6 +6727,9 @@
       <c r="M95" s="17">
         <v>0.43</v>
       </c>
+      <c r="N95" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
@@ -6754,6 +6772,9 @@
       <c r="M96" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="N96" s="17">
+        <v>0</v>
+      </c>
       <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
@@ -6796,6 +6817,9 @@
       <c r="M97" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="N97" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P97" s="4"/>
     </row>
     <row r="98" spans="1:16">
@@ -6835,6 +6859,9 @@
       <c r="M98" s="17">
         <v>0.38</v>
       </c>
+      <c r="N98" s="17">
+        <v>0</v>
+      </c>
       <c r="P98" s="15"/>
     </row>
     <row r="99" spans="1:16">
@@ -6877,6 +6904,9 @@
       <c r="M99" s="17">
         <v>0.66</v>
       </c>
+      <c r="N99" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P99" s="4"/>
     </row>
     <row r="100" spans="1:16">
@@ -6919,6 +6949,9 @@
       <c r="M100" s="17">
         <v>0.66</v>
       </c>
+      <c r="N100" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P100" s="4"/>
     </row>
     <row r="101" spans="1:16">
@@ -6961,6 +6994,9 @@
       <c r="M101" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="N101" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P101" s="4"/>
     </row>
     <row r="102" spans="1:16">
@@ -7003,6 +7039,9 @@
       <c r="M102" s="17">
         <v>0.88</v>
       </c>
+      <c r="N102" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P102" s="4"/>
     </row>
     <row r="103" spans="1:16">
@@ -7045,6 +7084,9 @@
       <c r="M103" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="N103" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P103" s="4"/>
     </row>
     <row r="104" spans="1:16">
@@ -7087,6 +7129,9 @@
       <c r="M104" s="17">
         <v>0</v>
       </c>
+      <c r="N104" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P104" s="4"/>
     </row>
     <row r="105" spans="1:16">
@@ -7129,6 +7174,9 @@
       <c r="M105" s="17">
         <v>0.84</v>
       </c>
+      <c r="N105" s="17">
+        <v>0</v>
+      </c>
       <c r="O105" s="17">
         <v>0.85</v>
       </c>
@@ -7171,6 +7219,9 @@
       <c r="M106" s="17">
         <v>0.88</v>
       </c>
+      <c r="N106" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P106" s="15"/>
     </row>
     <row r="107" spans="1:16">
@@ -7213,6 +7264,9 @@
       <c r="M107" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="N107" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P107" s="4"/>
     </row>
     <row r="108" spans="1:16">
@@ -7255,6 +7309,9 @@
       <c r="M108" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="N108" s="17">
+        <v>0</v>
+      </c>
       <c r="O108" s="17">
         <v>0.44</v>
       </c>
@@ -7300,6 +7357,9 @@
       <c r="M109" s="17">
         <v>0.88</v>
       </c>
+      <c r="N109" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P109" s="4"/>
     </row>
     <row r="110" spans="1:16">
@@ -7342,6 +7402,9 @@
       <c r="M110" s="17">
         <v>0.83</v>
       </c>
+      <c r="N110" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P110" s="4"/>
     </row>
     <row r="111" spans="1:16">
@@ -7381,6 +7444,9 @@
       <c r="M111" s="17">
         <v>0.83</v>
       </c>
+      <c r="N111" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P111" s="4"/>
     </row>
     <row r="112" spans="1:16">
@@ -7423,6 +7489,9 @@
       <c r="M112" s="17">
         <v>0.83</v>
       </c>
+      <c r="N112" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P112" s="4"/>
     </row>
     <row r="113" spans="1:16">
@@ -7465,6 +7534,9 @@
       <c r="M113" s="17">
         <v>0.88</v>
       </c>
+      <c r="N113" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P113" s="4"/>
     </row>
     <row r="114" spans="1:16">
@@ -7507,6 +7579,9 @@
       <c r="M114" s="17">
         <v>0.84</v>
       </c>
+      <c r="N114" s="17">
+        <v>0</v>
+      </c>
       <c r="O114" s="17">
         <v>0.85</v>
       </c>
@@ -7552,6 +7627,9 @@
       <c r="M115" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="N115" s="17">
+        <v>0</v>
+      </c>
       <c r="P115" s="4"/>
     </row>
     <row r="116" spans="1:16">
@@ -7594,6 +7672,9 @@
       <c r="M116" s="17">
         <v>0.38</v>
       </c>
+      <c r="N116" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P116" s="4"/>
     </row>
     <row r="117" spans="1:16">
@@ -7636,6 +7717,9 @@
       <c r="M117" s="17">
         <v>0.43</v>
       </c>
+      <c r="N117" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P117" s="4"/>
     </row>
     <row r="118" spans="1:16">
@@ -7675,6 +7759,9 @@
       <c r="M118" s="17">
         <v>0.83</v>
       </c>
+      <c r="N118" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P118" s="4"/>
     </row>
     <row r="119" spans="1:16">
@@ -7714,6 +7801,9 @@
       <c r="M119" s="17">
         <v>0.88</v>
       </c>
+      <c r="N119" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P119" s="4"/>
     </row>
     <row r="120" spans="1:16">
@@ -7756,6 +7846,9 @@
       <c r="M120" s="17">
         <v>0.43</v>
       </c>
+      <c r="N120" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P120" s="15"/>
     </row>
     <row r="121" spans="1:16">
@@ -7798,6 +7891,9 @@
       <c r="M121" s="17">
         <v>0.83</v>
       </c>
+      <c r="N121" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P121" s="4"/>
     </row>
     <row r="122" spans="1:16">
@@ -7840,6 +7936,9 @@
       <c r="M122" s="17">
         <v>0.84</v>
       </c>
+      <c r="N122" s="17">
+        <v>0</v>
+      </c>
       <c r="O122" s="17">
         <v>0.85</v>
       </c>
@@ -7885,6 +7984,9 @@
       <c r="M123" s="17">
         <v>0.38</v>
       </c>
+      <c r="N123" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P123" s="4"/>
     </row>
     <row r="124" spans="1:16">
@@ -7927,6 +8029,9 @@
       <c r="M124" s="17">
         <v>0.84</v>
       </c>
+      <c r="N124" s="17">
+        <v>0</v>
+      </c>
       <c r="O124" s="17">
         <v>0.85</v>
       </c>
@@ -7972,6 +8077,9 @@
       <c r="M125" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="N125" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P125" s="4"/>
     </row>
     <row r="126" spans="1:16">
@@ -8011,6 +8119,9 @@
       <c r="M126" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="N126" s="17">
+        <v>0</v>
+      </c>
       <c r="P126" s="4"/>
     </row>
     <row r="127" spans="1:16">
@@ -8050,6 +8161,9 @@
       <c r="M127" s="17">
         <v>0.84</v>
       </c>
+      <c r="N127" s="17">
+        <v>0</v>
+      </c>
       <c r="O127" s="17">
         <v>0.85</v>
       </c>
@@ -8095,6 +8209,9 @@
       <c r="M128" s="17">
         <v>0.84</v>
       </c>
+      <c r="N128" s="17">
+        <v>0</v>
+      </c>
       <c r="O128" s="17">
         <v>0.85</v>
       </c>
@@ -8140,6 +8257,9 @@
       <c r="M129" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="N129" s="17">
+        <v>0</v>
+      </c>
       <c r="O129" s="17">
         <v>0.44</v>
       </c>
@@ -8185,6 +8305,9 @@
       <c r="M130" s="17">
         <v>0.66</v>
       </c>
+      <c r="N130" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P130" s="4"/>
     </row>
     <row r="131" spans="1:16">
@@ -8227,6 +8350,9 @@
       <c r="M131" s="17">
         <v>0.66</v>
       </c>
+      <c r="N131" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P131" s="4"/>
     </row>
     <row r="132" spans="1:16">
@@ -8266,6 +8392,9 @@
       <c r="M132" s="17">
         <v>0.43</v>
       </c>
+      <c r="N132" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P132" s="4"/>
     </row>
     <row r="133" spans="1:16">
@@ -8304,6 +8433,9 @@
       </c>
       <c r="M133" s="17">
         <v>0.55000000000000004</v>
+      </c>
+      <c r="N133" s="17">
+        <v>0.44</v>
       </c>
       <c r="P133" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE51D26-504F-484D-93CF-590611842181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ED9F8D-28D6-BB47-A5B9-280ED65DD089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -8479,6 +8479,9 @@
       <c r="M134" s="17">
         <v>0.84</v>
       </c>
+      <c r="N134" s="17">
+        <v>0</v>
+      </c>
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
@@ -8518,6 +8521,9 @@
       <c r="M135" s="17">
         <v>0.9</v>
       </c>
+      <c r="N135" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
@@ -8557,6 +8563,9 @@
       <c r="M136" s="17">
         <v>0.84</v>
       </c>
+      <c r="N136" s="17">
+        <v>0</v>
+      </c>
       <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
@@ -8599,6 +8608,9 @@
       <c r="M137" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="N137" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
@@ -8641,6 +8653,9 @@
       <c r="M138" s="17">
         <v>0.64</v>
       </c>
+      <c r="N138" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
@@ -8680,6 +8695,9 @@
       <c r="M139" s="17">
         <v>0.64</v>
       </c>
+      <c r="N139" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
@@ -8722,6 +8740,9 @@
       <c r="M140" s="17">
         <v>0</v>
       </c>
+      <c r="N140" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
@@ -8761,6 +8782,9 @@
       <c r="M141" s="17">
         <v>0.76</v>
       </c>
+      <c r="N141" s="17">
+        <v>0.47</v>
+      </c>
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
@@ -8800,6 +8824,9 @@
       <c r="M142" s="17">
         <v>0.83</v>
       </c>
+      <c r="N142" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
@@ -8842,6 +8869,9 @@
       <c r="M143" s="17">
         <v>0</v>
       </c>
+      <c r="N143" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P143" s="4"/>
     </row>
     <row r="144" spans="1:16">
@@ -8884,6 +8914,9 @@
       <c r="M144" s="17">
         <v>0.88</v>
       </c>
+      <c r="N144" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P144" s="4"/>
     </row>
     <row r="145" spans="1:16">
@@ -8926,6 +8959,9 @@
       <c r="M145" s="17">
         <v>0.76</v>
       </c>
+      <c r="N145" s="17">
+        <v>0.47</v>
+      </c>
       <c r="P145" s="4"/>
     </row>
     <row r="146" spans="1:16">
@@ -8968,6 +9004,9 @@
       <c r="M146" s="17">
         <v>0.64</v>
       </c>
+      <c r="N146" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P146" s="4"/>
     </row>
     <row r="147" spans="1:16">
@@ -9007,6 +9046,9 @@
       <c r="M147" s="17">
         <v>0.84</v>
       </c>
+      <c r="N147" s="17">
+        <v>0</v>
+      </c>
       <c r="P147" s="4"/>
     </row>
     <row r="148" spans="1:16">
@@ -9049,6 +9091,9 @@
       <c r="M148" s="17">
         <v>0.76</v>
       </c>
+      <c r="N148" s="17">
+        <v>0.47</v>
+      </c>
       <c r="P148" s="4"/>
     </row>
     <row r="149" spans="1:16">
@@ -9091,6 +9136,9 @@
       <c r="M149" s="17">
         <v>0</v>
       </c>
+      <c r="N149" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P149" s="4"/>
     </row>
     <row r="150" spans="1:16">
@@ -9133,6 +9181,9 @@
       <c r="M150" s="17">
         <v>0.28000000000000003</v>
       </c>
+      <c r="N150" s="17">
+        <v>0.38</v>
+      </c>
       <c r="P150" s="4"/>
     </row>
     <row r="151" spans="1:16">
@@ -9175,6 +9226,9 @@
       <c r="M151" s="17">
         <v>0.64</v>
       </c>
+      <c r="N151" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P151" s="4"/>
     </row>
     <row r="152" spans="1:16">
@@ -9217,6 +9271,9 @@
       <c r="M152" s="17">
         <v>0.88</v>
       </c>
+      <c r="N152" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P152" s="4"/>
     </row>
     <row r="153" spans="1:16">
@@ -9259,6 +9316,9 @@
       <c r="M153" s="17">
         <v>0.64</v>
       </c>
+      <c r="N153" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P153" s="4"/>
     </row>
     <row r="154" spans="1:16">
@@ -9301,6 +9361,9 @@
       <c r="M154" s="17">
         <v>0</v>
       </c>
+      <c r="N154" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P154" s="4"/>
     </row>
     <row r="155" spans="1:16">
@@ -9343,6 +9406,9 @@
       <c r="M155" s="17">
         <v>0.84</v>
       </c>
+      <c r="N155" s="17">
+        <v>0</v>
+      </c>
       <c r="P155" s="4"/>
     </row>
     <row r="156" spans="1:16">
@@ -9385,6 +9451,9 @@
       <c r="M156" s="17">
         <v>0.64</v>
       </c>
+      <c r="N156" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P156" s="4"/>
     </row>
     <row r="157" spans="1:16">
@@ -9427,6 +9496,9 @@
       <c r="M157" s="17">
         <v>0.83</v>
       </c>
+      <c r="N157" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P157" s="4"/>
     </row>
     <row r="158" spans="1:16">
@@ -9469,6 +9541,9 @@
       <c r="M158" s="17">
         <v>0.83</v>
       </c>
+      <c r="N158" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P158" s="4"/>
     </row>
     <row r="159" spans="1:16">
@@ -9511,6 +9586,9 @@
       <c r="M159" s="17">
         <v>0.88</v>
       </c>
+      <c r="N159" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P159" s="4"/>
     </row>
     <row r="160" spans="1:16">
@@ -9553,6 +9631,9 @@
       <c r="M160" s="17">
         <v>0.64</v>
       </c>
+      <c r="N160" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P160" s="4"/>
     </row>
     <row r="161" spans="1:16">
@@ -9592,6 +9673,9 @@
       <c r="M161" s="17">
         <v>0.64</v>
       </c>
+      <c r="N161" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P161" s="4"/>
     </row>
     <row r="162" spans="1:16">
@@ -9631,6 +9715,9 @@
       <c r="M162" s="17">
         <v>0.83</v>
       </c>
+      <c r="N162" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P162" s="4"/>
     </row>
     <row r="163" spans="1:16">
@@ -9673,6 +9760,9 @@
       <c r="M163" s="17">
         <v>0.84</v>
       </c>
+      <c r="N163" s="17">
+        <v>0</v>
+      </c>
       <c r="P163" s="4"/>
     </row>
     <row r="164" spans="1:16">
@@ -9715,6 +9805,9 @@
       <c r="M164" s="17">
         <v>0.84</v>
       </c>
+      <c r="N164" s="17">
+        <v>0</v>
+      </c>
       <c r="P164" s="4"/>
     </row>
     <row r="165" spans="1:16">
@@ -9757,6 +9850,9 @@
       <c r="M165" s="17">
         <v>0.76</v>
       </c>
+      <c r="N165" s="17">
+        <v>0.47</v>
+      </c>
       <c r="P165" s="4"/>
     </row>
     <row r="166" spans="1:16">
@@ -9799,6 +9895,9 @@
       <c r="M166" s="17">
         <v>0.88</v>
       </c>
+      <c r="N166" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P166" s="4"/>
     </row>
     <row r="167" spans="1:16">
@@ -9838,6 +9937,9 @@
       <c r="M167" s="17">
         <v>0</v>
       </c>
+      <c r="N167" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P167" s="4"/>
     </row>
     <row r="168" spans="1:16">
@@ -9877,6 +9979,9 @@
       <c r="M168" s="17">
         <v>0.88</v>
       </c>
+      <c r="N168" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P168" s="4"/>
     </row>
     <row r="169" spans="1:16">
@@ -9919,6 +10024,9 @@
       <c r="M169" s="17">
         <v>0</v>
       </c>
+      <c r="N169" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P169" s="4"/>
     </row>
     <row r="170" spans="1:16">
@@ -9961,6 +10069,9 @@
       <c r="M170" s="17">
         <v>0.64</v>
       </c>
+      <c r="N170" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P170" s="4"/>
     </row>
     <row r="171" spans="1:16">
@@ -10003,6 +10114,9 @@
       <c r="M171" s="17">
         <v>0.83</v>
       </c>
+      <c r="N171" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P171" s="4"/>
     </row>
     <row r="172" spans="1:16">
@@ -10045,6 +10159,9 @@
       <c r="M172" s="17">
         <v>0.64</v>
       </c>
+      <c r="N172" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P172" s="4"/>
     </row>
     <row r="173" spans="1:16">
@@ -10087,6 +10204,9 @@
       <c r="M173" s="17">
         <v>0</v>
       </c>
+      <c r="N173" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P173" s="4"/>
     </row>
     <row r="174" spans="1:16">
@@ -10129,6 +10249,9 @@
       <c r="M174" s="17">
         <v>0.6</v>
       </c>
+      <c r="N174" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P174" s="4"/>
     </row>
     <row r="175" spans="1:16">
@@ -10171,6 +10294,9 @@
       <c r="M175" s="17">
         <v>0</v>
       </c>
+      <c r="N175" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P175" s="4"/>
     </row>
     <row r="176" spans="1:16">
@@ -10213,6 +10339,9 @@
       <c r="M176" s="17">
         <v>0.88</v>
       </c>
+      <c r="N176" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P176" s="4"/>
     </row>
     <row r="177" spans="1:16">
@@ -10255,6 +10384,9 @@
       <c r="M177" s="17">
         <v>0.76</v>
       </c>
+      <c r="N177" s="17">
+        <v>0</v>
+      </c>
       <c r="P177" s="4"/>
     </row>
     <row r="178" spans="1:16">
@@ -10297,6 +10429,9 @@
       <c r="M178" s="17">
         <v>0</v>
       </c>
+      <c r="N178" s="17">
+        <v>0</v>
+      </c>
       <c r="P178" s="4"/>
     </row>
     <row r="179" spans="1:16">
@@ -10336,6 +10471,9 @@
       <c r="M179" s="17">
         <v>0.64</v>
       </c>
+      <c r="N179" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P179" s="4"/>
     </row>
     <row r="180" spans="1:16">
@@ -10378,6 +10516,9 @@
       <c r="M180" s="17">
         <v>0.64</v>
       </c>
+      <c r="N180" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P180" s="4"/>
     </row>
     <row r="181" spans="1:16">
@@ -10417,6 +10558,9 @@
       <c r="M181" s="17">
         <v>0.83</v>
       </c>
+      <c r="N181" s="17">
+        <v>0.59</v>
+      </c>
       <c r="P181" s="4"/>
     </row>
     <row r="182" spans="1:16">
@@ -10459,6 +10603,9 @@
       <c r="M182" s="17">
         <v>0.64</v>
       </c>
+      <c r="N182" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P182" s="4"/>
     </row>
     <row r="183" spans="1:16">
@@ -10501,6 +10648,9 @@
       <c r="M183" s="17">
         <v>0.76</v>
       </c>
+      <c r="N183" s="17">
+        <v>0.47</v>
+      </c>
       <c r="P183" s="4"/>
     </row>
     <row r="184" spans="1:16">
@@ -10660,6 +10810,9 @@
       <c r="L187" s="17">
         <v>0.83</v>
       </c>
+      <c r="M187" s="17">
+        <v>0</v>
+      </c>
       <c r="P187" s="15"/>
     </row>
     <row r="188" spans="1:16">
@@ -10699,6 +10852,9 @@
       <c r="L188" s="17">
         <v>0</v>
       </c>
+      <c r="M188" s="17">
+        <v>0</v>
+      </c>
       <c r="P188" s="15"/>
     </row>
     <row r="189" spans="1:16">
@@ -11152,6 +11308,9 @@
       <c r="L199" s="17">
         <v>0</v>
       </c>
+      <c r="M199" s="17">
+        <v>0</v>
+      </c>
       <c r="P199" s="15"/>
     </row>
     <row r="200" spans="1:16">
@@ -11772,6 +11931,9 @@
       </c>
       <c r="L214" s="17">
         <v>0.83</v>
+      </c>
+      <c r="M214" s="17">
+        <v>0</v>
       </c>
       <c r="P214" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ED9F8D-28D6-BB47-A5B9-280ED65DD089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D10A76B-18B8-3A42-965D-8D15804AA8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -10690,6 +10690,9 @@
       <c r="M184" s="17">
         <v>0.51</v>
       </c>
+      <c r="N184" s="17">
+        <v>0.24</v>
+      </c>
       <c r="P184" s="4"/>
     </row>
     <row r="185" spans="1:16">
@@ -10732,6 +10735,9 @@
       <c r="M185" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="N185" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
@@ -10774,6 +10780,9 @@
       <c r="M186" s="17">
         <v>0.5</v>
       </c>
+      <c r="N186" s="17">
+        <v>0.15</v>
+      </c>
       <c r="P186" s="4"/>
     </row>
     <row r="187" spans="1:16">
@@ -10813,6 +10822,9 @@
       <c r="M187" s="17">
         <v>0</v>
       </c>
+      <c r="N187" s="17">
+        <v>0</v>
+      </c>
       <c r="P187" s="15"/>
     </row>
     <row r="188" spans="1:16">
@@ -10855,6 +10867,9 @@
       <c r="M188" s="17">
         <v>0</v>
       </c>
+      <c r="N188" s="17">
+        <v>0</v>
+      </c>
       <c r="P188" s="15"/>
     </row>
     <row r="189" spans="1:16">
@@ -10894,6 +10909,9 @@
       <c r="M189" s="17">
         <v>0.74</v>
       </c>
+      <c r="N189" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P189" s="4"/>
     </row>
     <row r="190" spans="1:16">
@@ -10936,6 +10954,9 @@
       <c r="M190" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="N190" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P190" s="4"/>
     </row>
     <row r="191" spans="1:16">
@@ -10978,6 +10999,9 @@
       <c r="M191" s="17">
         <v>0.74</v>
       </c>
+      <c r="N191" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P191" s="4"/>
     </row>
     <row r="192" spans="1:16">
@@ -11020,6 +11044,9 @@
       <c r="M192" s="17">
         <v>0.56999999999999995</v>
       </c>
+      <c r="N192" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P192" s="4"/>
     </row>
     <row r="193" spans="1:16">
@@ -11062,6 +11089,9 @@
       <c r="M193" s="17">
         <v>0.41</v>
       </c>
+      <c r="N193" s="17">
+        <v>0</v>
+      </c>
       <c r="P193" s="4"/>
     </row>
     <row r="194" spans="1:16">
@@ -11104,6 +11134,9 @@
       <c r="M194" s="17">
         <v>0.84</v>
       </c>
+      <c r="N194" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P194" s="4"/>
     </row>
     <row r="195" spans="1:16">
@@ -11143,6 +11176,9 @@
       <c r="M195" s="17">
         <v>0.84</v>
       </c>
+      <c r="N195" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P195" s="4"/>
     </row>
     <row r="196" spans="1:16">
@@ -11185,6 +11221,9 @@
       <c r="M196" s="17">
         <v>0.51</v>
       </c>
+      <c r="N196" s="17">
+        <v>0.24</v>
+      </c>
       <c r="P196" s="4"/>
     </row>
     <row r="197" spans="1:16">
@@ -11227,6 +11266,9 @@
       <c r="M197" s="17">
         <v>0.84</v>
       </c>
+      <c r="N197" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P197" s="4"/>
     </row>
     <row r="198" spans="1:16">
@@ -11269,6 +11311,9 @@
       <c r="M198" s="17">
         <v>0.41</v>
       </c>
+      <c r="N198" s="17">
+        <v>0</v>
+      </c>
       <c r="P198" s="4"/>
     </row>
     <row r="199" spans="1:16">
@@ -11311,6 +11356,9 @@
       <c r="M199" s="17">
         <v>0</v>
       </c>
+      <c r="N199" s="17">
+        <v>0</v>
+      </c>
       <c r="P199" s="15"/>
     </row>
     <row r="200" spans="1:16">
@@ -11353,6 +11401,9 @@
       <c r="M200" s="17">
         <v>0.51</v>
       </c>
+      <c r="N200" s="17">
+        <v>0.24</v>
+      </c>
       <c r="P200" s="4"/>
     </row>
     <row r="201" spans="1:16">
@@ -11395,6 +11446,9 @@
       <c r="M201" s="17">
         <v>0.5</v>
       </c>
+      <c r="N201" s="17">
+        <v>0.15</v>
+      </c>
       <c r="P201" s="4"/>
     </row>
     <row r="202" spans="1:16">
@@ -11437,6 +11491,9 @@
       <c r="M202" s="17">
         <v>0.51</v>
       </c>
+      <c r="N202" s="17">
+        <v>0.24</v>
+      </c>
       <c r="P202" s="4"/>
     </row>
     <row r="203" spans="1:16">
@@ -11479,6 +11536,9 @@
       <c r="M203" s="17">
         <v>0.74</v>
       </c>
+      <c r="N203" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P203" s="4"/>
     </row>
     <row r="204" spans="1:16">
@@ -11518,6 +11578,9 @@
       <c r="M204" s="17">
         <v>0.51</v>
       </c>
+      <c r="N204" s="17">
+        <v>0.24</v>
+      </c>
       <c r="P204" s="4"/>
     </row>
     <row r="205" spans="1:16">
@@ -11560,6 +11623,9 @@
       <c r="M205" s="17">
         <v>0.51</v>
       </c>
+      <c r="N205" s="17">
+        <v>0.24</v>
+      </c>
       <c r="P205" s="4"/>
     </row>
     <row r="206" spans="1:16">
@@ -11602,6 +11668,9 @@
       <c r="M206" s="17">
         <v>0.41</v>
       </c>
+      <c r="N206" s="17">
+        <v>0</v>
+      </c>
       <c r="P206" s="4"/>
     </row>
     <row r="207" spans="1:16">
@@ -11641,6 +11710,9 @@
       <c r="M207" s="17">
         <v>0.41</v>
       </c>
+      <c r="N207" s="17">
+        <v>0</v>
+      </c>
       <c r="P207" s="4"/>
     </row>
     <row r="208" spans="1:16">
@@ -11683,6 +11755,9 @@
       <c r="M208" s="17">
         <v>0.5</v>
       </c>
+      <c r="N208" s="17">
+        <v>0.15</v>
+      </c>
       <c r="P208" s="4"/>
     </row>
     <row r="209" spans="1:16">
@@ -11725,6 +11800,9 @@
       <c r="M209" s="17">
         <v>0.5</v>
       </c>
+      <c r="N209" s="17">
+        <v>0.15</v>
+      </c>
       <c r="P209" s="4"/>
     </row>
     <row r="210" spans="1:16">
@@ -11767,6 +11845,9 @@
       <c r="M210" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="N210" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P210" s="4"/>
     </row>
     <row r="211" spans="1:16">
@@ -11809,6 +11890,9 @@
       <c r="M211" s="17">
         <v>0.5</v>
       </c>
+      <c r="N211" s="17">
+        <v>0.15</v>
+      </c>
       <c r="P211" s="4"/>
     </row>
     <row r="212" spans="1:16">
@@ -11851,6 +11935,9 @@
       <c r="M212" s="17">
         <v>0.74</v>
       </c>
+      <c r="N212" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P212" s="4"/>
     </row>
     <row r="213" spans="1:16">
@@ -11893,6 +11980,9 @@
       <c r="M213" s="17">
         <v>0.74</v>
       </c>
+      <c r="N213" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P213" s="4"/>
     </row>
     <row r="214" spans="1:16">
@@ -11935,6 +12025,9 @@
       <c r="M214" s="17">
         <v>0</v>
       </c>
+      <c r="N214" s="17">
+        <v>0</v>
+      </c>
       <c r="P214" s="4"/>
     </row>
     <row r="215" spans="1:16">
@@ -11977,6 +12070,9 @@
       <c r="M215" s="17">
         <v>0.41</v>
       </c>
+      <c r="N215" s="17">
+        <v>0</v>
+      </c>
       <c r="P215" s="4"/>
     </row>
     <row r="216" spans="1:16">
@@ -12019,6 +12115,9 @@
       <c r="M216" s="17">
         <v>0.84</v>
       </c>
+      <c r="N216" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P216" s="4"/>
     </row>
     <row r="217" spans="1:16">
@@ -12061,6 +12160,9 @@
       <c r="M217" s="17">
         <v>0.41</v>
       </c>
+      <c r="N217" s="17">
+        <v>0</v>
+      </c>
       <c r="P217" s="4"/>
     </row>
     <row r="218" spans="1:16">
@@ -12100,6 +12202,9 @@
       <c r="M218" s="17">
         <v>0.84</v>
       </c>
+      <c r="N218" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P218" s="4"/>
     </row>
     <row r="219" spans="1:16">
@@ -12142,6 +12247,9 @@
       <c r="M219" s="17">
         <v>0.74</v>
       </c>
+      <c r="N219" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P219" s="4"/>
     </row>
     <row r="220" spans="1:16">
@@ -12184,6 +12292,9 @@
       <c r="M220" s="17">
         <v>0.55000000000000004</v>
       </c>
+      <c r="N220" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P220" s="4"/>
     </row>
     <row r="221" spans="1:16">
@@ -12223,6 +12334,9 @@
       <c r="M221" s="17">
         <v>0</v>
       </c>
+      <c r="N221" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P221" s="4"/>
     </row>
     <row r="222" spans="1:16">
@@ -12265,6 +12379,9 @@
       <c r="M222" s="17">
         <v>0</v>
       </c>
+      <c r="N222" s="17">
+        <v>0</v>
+      </c>
       <c r="P222" s="15"/>
     </row>
     <row r="223" spans="1:16">
@@ -12307,6 +12424,9 @@
       <c r="M223" s="17">
         <v>0</v>
       </c>
+      <c r="N223" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P223" s="4"/>
     </row>
     <row r="224" spans="1:16">
@@ -12349,6 +12469,9 @@
       <c r="M224" s="17">
         <v>0</v>
       </c>
+      <c r="N224" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P224" s="4"/>
     </row>
     <row r="225" spans="1:16">
@@ -12391,6 +12514,9 @@
       <c r="M225" s="17">
         <v>0</v>
       </c>
+      <c r="N225" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P225" s="15"/>
     </row>
     <row r="226" spans="1:16">
@@ -12433,6 +12559,9 @@
       <c r="M226" s="17">
         <v>0</v>
       </c>
+      <c r="N226" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P226" s="4"/>
     </row>
     <row r="227" spans="1:16">
@@ -12472,6 +12601,9 @@
       <c r="M227" s="17">
         <v>0</v>
       </c>
+      <c r="N227" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P227" s="16"/>
     </row>
     <row r="228" spans="1:16">
@@ -12513,6 +12645,9 @@
       </c>
       <c r="M228" s="17">
         <v>0</v>
+      </c>
+      <c r="N228" s="17">
+        <v>0.71</v>
       </c>
       <c r="P228" s="16"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D10A76B-18B8-3A42-965D-8D15804AA8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75CCCA0-6AE2-C14F-9228-4C1F303C6B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -12691,6 +12691,9 @@
       <c r="M229" s="17">
         <v>0.6</v>
       </c>
+      <c r="N229" s="17">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="230" spans="1:16">
       <c r="A230" s="9" t="s">
@@ -12732,6 +12735,9 @@
       <c r="M230" s="17">
         <v>0.5</v>
       </c>
+      <c r="N230" s="17">
+        <v>0.5</v>
+      </c>
       <c r="P230" s="16"/>
     </row>
     <row r="231" spans="1:16">
@@ -12774,6 +12780,9 @@
       <c r="M231" s="17">
         <v>0.6</v>
       </c>
+      <c r="N231" s="17">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="9" t="s">
@@ -12815,6 +12824,9 @@
       <c r="M232" s="17">
         <v>0.78</v>
       </c>
+      <c r="N232" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P232" s="16"/>
     </row>
     <row r="233" spans="1:16">
@@ -12857,6 +12869,9 @@
       <c r="M233" s="17">
         <v>0.6</v>
       </c>
+      <c r="N233" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P233" s="16"/>
     </row>
     <row r="234" spans="1:16">
@@ -12899,6 +12914,9 @@
       <c r="M234" s="17">
         <v>0.52</v>
       </c>
+      <c r="N234" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="235" spans="1:16">
       <c r="A235" t="s">
@@ -12940,6 +12958,9 @@
       <c r="M235" s="17">
         <v>0.5</v>
       </c>
+      <c r="N235" s="17">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="9" t="s">
@@ -12979,6 +13000,9 @@
       <c r="M236" s="17">
         <v>0.66</v>
       </c>
+      <c r="N236" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P236" s="16"/>
     </row>
     <row r="237" spans="1:16">
@@ -13021,6 +13045,9 @@
       <c r="M237" s="17">
         <v>0.66</v>
       </c>
+      <c r="N237" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P237" s="16"/>
     </row>
     <row r="238" spans="1:16">
@@ -13061,6 +13088,9 @@
       <c r="M238" s="17">
         <v>0.78</v>
       </c>
+      <c r="N238" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P238" s="16"/>
     </row>
     <row r="239" spans="1:16">
@@ -13103,6 +13133,9 @@
       <c r="M239" s="17">
         <v>0.66</v>
       </c>
+      <c r="N239" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P239" s="16"/>
     </row>
     <row r="240" spans="1:16">
@@ -13143,6 +13176,9 @@
       <c r="M240" s="17">
         <v>0.5</v>
       </c>
+      <c r="N240" s="17">
+        <v>0.5</v>
+      </c>
       <c r="P240" s="16"/>
     </row>
     <row r="241" spans="1:16">
@@ -13183,6 +13219,9 @@
       <c r="M241" s="17">
         <v>0.78</v>
       </c>
+      <c r="N241" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P241" s="16"/>
     </row>
     <row r="242" spans="1:16">
@@ -13225,6 +13264,9 @@
       <c r="M242" s="17">
         <v>0.5</v>
       </c>
+      <c r="N242" s="17">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" t="s">
@@ -13266,6 +13308,9 @@
       <c r="M243" s="17">
         <v>0.52</v>
       </c>
+      <c r="N243" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="244" spans="1:16">
       <c r="A244" t="s">
@@ -13307,6 +13352,9 @@
       <c r="M244" s="17">
         <v>0.78</v>
       </c>
+      <c r="N244" s="17">
+        <v>0.71</v>
+      </c>
     </row>
     <row r="245" spans="1:16">
       <c r="A245" s="9" t="s">
@@ -13348,6 +13396,9 @@
       <c r="M245" s="17">
         <v>0.66</v>
       </c>
+      <c r="N245" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P245" s="16"/>
     </row>
     <row r="246" spans="1:16">
@@ -13389,6 +13440,9 @@
       </c>
       <c r="M246" s="17">
         <v>0.6</v>
+      </c>
+      <c r="N246" s="17">
+        <v>0.44</v>
       </c>
       <c r="P246" s="16"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75CCCA0-6AE2-C14F-9228-4C1F303C6B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03DB440-142E-1043-BA07-F424FDBA1E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -5923,7 +5923,7 @@
         <v>0.68</v>
       </c>
       <c r="K77" s="17">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="L77" s="17">
         <v>0.92</v>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03DB440-142E-1043-BA07-F424FDBA1E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CEC5FE-E89E-394B-B13D-13193E46604D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4676,6 +4676,9 @@
       <c r="N49" s="17">
         <v>0.52</v>
       </c>
+      <c r="O49" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16">
@@ -4721,6 +4724,9 @@
       <c r="N50" s="17">
         <v>0.79</v>
       </c>
+      <c r="O50" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P50" s="4"/>
     </row>
     <row r="51" spans="1:16">
@@ -4766,6 +4772,9 @@
       <c r="N51" s="17">
         <v>0.94</v>
       </c>
+      <c r="O51" s="17">
+        <v>1</v>
+      </c>
       <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16">
@@ -4811,6 +4820,9 @@
       <c r="N52" s="17">
         <v>0.74</v>
       </c>
+      <c r="O52" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P52" s="4"/>
     </row>
     <row r="53" spans="1:16">
@@ -4899,6 +4911,9 @@
       <c r="N54" s="17">
         <v>0.76</v>
       </c>
+      <c r="O54" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P54" s="4"/>
     </row>
     <row r="55" spans="1:16">
@@ -4944,6 +4959,9 @@
       <c r="N55" s="17">
         <v>0.74</v>
       </c>
+      <c r="O55" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P55" s="4"/>
     </row>
     <row r="56" spans="1:16">
@@ -4989,6 +5007,9 @@
       <c r="N56" s="17">
         <v>0.94</v>
       </c>
+      <c r="O56" s="17">
+        <v>1</v>
+      </c>
       <c r="P56" s="4"/>
     </row>
     <row r="57" spans="1:16">
@@ -5034,6 +5055,9 @@
       <c r="N57" s="17">
         <v>0.53</v>
       </c>
+      <c r="O57" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P57" s="22"/>
     </row>
     <row r="58" spans="1:16">
@@ -5079,6 +5103,9 @@
       <c r="N58" s="17">
         <v>0.62</v>
       </c>
+      <c r="O58" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P58" s="4"/>
     </row>
     <row r="59" spans="1:16">
@@ -5124,6 +5151,9 @@
       <c r="N59" s="17">
         <v>0.94</v>
       </c>
+      <c r="O59" s="17">
+        <v>1</v>
+      </c>
       <c r="P59" s="22"/>
     </row>
     <row r="60" spans="1:16">
@@ -5169,6 +5199,9 @@
       <c r="N60" s="17">
         <v>0.74</v>
       </c>
+      <c r="O60" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P60" s="4"/>
     </row>
     <row r="61" spans="1:16">
@@ -5214,6 +5247,9 @@
       <c r="N61" s="17">
         <v>0.76</v>
       </c>
+      <c r="O61" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P61" s="4"/>
     </row>
     <row r="62" spans="1:16">
@@ -5259,6 +5295,9 @@
       <c r="N62" s="17">
         <v>0.74</v>
       </c>
+      <c r="O62" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P62" s="4"/>
     </row>
     <row r="63" spans="1:16">
@@ -5304,6 +5343,9 @@
       <c r="N63" s="17">
         <v>0.79</v>
       </c>
+      <c r="O63" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P63" s="4"/>
     </row>
     <row r="64" spans="1:16">
@@ -5349,6 +5391,9 @@
       <c r="N64" s="17">
         <v>0.53</v>
       </c>
+      <c r="O64" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P64" s="4"/>
     </row>
     <row r="65" spans="1:16">
@@ -5439,6 +5484,9 @@
       <c r="N66" s="17">
         <v>0.76</v>
       </c>
+      <c r="O66" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P66" s="4"/>
     </row>
     <row r="67" spans="1:16">
@@ -5484,6 +5532,9 @@
       <c r="N67" s="17">
         <v>0.74</v>
       </c>
+      <c r="O67" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P67" s="4"/>
     </row>
     <row r="68" spans="1:16">
@@ -5574,6 +5625,9 @@
       <c r="N69" s="17">
         <v>0.94</v>
       </c>
+      <c r="O69" s="17">
+        <v>1</v>
+      </c>
       <c r="P69" s="4"/>
     </row>
     <row r="70" spans="1:16">
@@ -5619,6 +5673,9 @@
       <c r="N70" s="17">
         <v>0.76</v>
       </c>
+      <c r="O70" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P70" s="4"/>
     </row>
     <row r="71" spans="1:16">
@@ -5664,6 +5721,9 @@
       <c r="N71" s="17">
         <v>0.53</v>
       </c>
+      <c r="O71" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P71" s="4"/>
     </row>
     <row r="72" spans="1:16">
@@ -5754,6 +5814,9 @@
       <c r="N73" s="17">
         <v>0.74</v>
       </c>
+      <c r="O73" s="17">
+        <v>0.91</v>
+      </c>
       <c r="P73" s="4"/>
     </row>
     <row r="74" spans="1:16">
@@ -5799,6 +5862,9 @@
       <c r="N74" s="17">
         <v>0.62</v>
       </c>
+      <c r="O74" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P74" s="4"/>
     </row>
     <row r="75" spans="1:16">
@@ -5844,6 +5910,9 @@
       <c r="N75" s="17">
         <v>0.62</v>
       </c>
+      <c r="O75" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P75" s="4"/>
     </row>
     <row r="76" spans="1:16">
@@ -5889,6 +5958,9 @@
       <c r="N76" s="17">
         <v>0.76</v>
       </c>
+      <c r="O76" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P76" s="4"/>
     </row>
     <row r="77" spans="1:16">
@@ -5934,6 +6006,9 @@
       <c r="N77" s="17">
         <v>0.94</v>
       </c>
+      <c r="O77" s="17">
+        <v>1</v>
+      </c>
       <c r="P77" s="4"/>
     </row>
     <row r="78" spans="1:16">
@@ -5979,6 +6054,9 @@
       <c r="N78" s="17">
         <v>0.62</v>
       </c>
+      <c r="O78" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P78" s="4"/>
     </row>
     <row r="79" spans="1:16">
@@ -6024,6 +6102,9 @@
       <c r="N79" s="17">
         <v>0.94</v>
       </c>
+      <c r="O79" s="17">
+        <v>1</v>
+      </c>
       <c r="P79" s="4"/>
     </row>
     <row r="80" spans="1:16">
@@ -6067,6 +6148,9 @@
       <c r="N80" s="17">
         <v>0.79</v>
       </c>
+      <c r="O80" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P80" s="4"/>
     </row>
     <row r="81" spans="1:16">
@@ -6110,6 +6194,9 @@
       <c r="N81" s="17">
         <v>0.53</v>
       </c>
+      <c r="O81" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P81" s="4"/>
     </row>
     <row r="82" spans="1:16">
@@ -6153,6 +6240,9 @@
       <c r="N82" s="17">
         <v>0.53</v>
       </c>
+      <c r="O82" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P82" s="4"/>
     </row>
     <row r="83" spans="1:16">
@@ -6198,6 +6288,9 @@
       <c r="N83" s="17">
         <v>0.79</v>
       </c>
+      <c r="O83" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P83" s="4"/>
     </row>
     <row r="84" spans="1:16">
@@ -6286,6 +6379,9 @@
       <c r="N85" s="17">
         <v>0.79</v>
       </c>
+      <c r="O85" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P85" s="4"/>
     </row>
     <row r="86" spans="1:16">
@@ -6331,6 +6427,9 @@
       <c r="N86" s="17">
         <v>0.76</v>
       </c>
+      <c r="O86" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P86" s="4"/>
     </row>
     <row r="87" spans="1:16">
@@ -6376,6 +6475,9 @@
       <c r="N87" s="17">
         <v>0.53</v>
       </c>
+      <c r="O87" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P87" s="4"/>
     </row>
     <row r="88" spans="1:16">
@@ -6465,6 +6567,9 @@
       </c>
       <c r="N89" s="17">
         <v>0.62</v>
+      </c>
+      <c r="O89" s="17">
+        <v>0.56000000000000005</v>
       </c>
       <c r="P89" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CEC5FE-E89E-394B-B13D-13193E46604D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7966F9A1-9B5A-B94F-B94D-231644178FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -5439,6 +5439,9 @@
       <c r="N65" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O65" s="17">
+        <v>0</v>
+      </c>
       <c r="P65" s="4"/>
     </row>
     <row r="66" spans="1:16">
@@ -5580,6 +5583,9 @@
       <c r="N68" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O68" s="17">
+        <v>0</v>
+      </c>
       <c r="P68" s="4"/>
     </row>
     <row r="69" spans="1:16">
@@ -5769,6 +5775,9 @@
       <c r="N72" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O72" s="17">
+        <v>0</v>
+      </c>
       <c r="P72" s="4"/>
     </row>
     <row r="73" spans="1:16">
@@ -6334,6 +6343,9 @@
       <c r="N84" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O84" s="17">
+        <v>0</v>
+      </c>
       <c r="P84" s="4"/>
     </row>
     <row r="85" spans="1:16">
@@ -6523,6 +6535,9 @@
       <c r="N88" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O88" s="17">
+        <v>0</v>
+      </c>
       <c r="P88" s="4"/>
     </row>
     <row r="89" spans="1:16">
@@ -6616,6 +6631,9 @@
       <c r="N90" s="17">
         <v>0.68</v>
       </c>
+      <c r="O90" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P90" s="4"/>
     </row>
     <row r="91" spans="1:16">
@@ -6706,6 +6724,9 @@
       <c r="N92" s="17">
         <v>0.74</v>
       </c>
+      <c r="O92" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16">
@@ -6835,6 +6856,9 @@
       <c r="N95" s="17">
         <v>0.74</v>
       </c>
+      <c r="O95" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P95" s="4"/>
     </row>
     <row r="96" spans="1:16">
@@ -6880,6 +6904,9 @@
       <c r="N96" s="17">
         <v>0</v>
       </c>
+      <c r="O96" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P96" s="4"/>
     </row>
     <row r="97" spans="1:16">
@@ -6925,6 +6952,9 @@
       <c r="N97" s="17">
         <v>0.44</v>
       </c>
+      <c r="O97" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P97" s="4"/>
     </row>
     <row r="98" spans="1:16">
@@ -7012,6 +7042,9 @@
       <c r="N99" s="17">
         <v>0.68</v>
       </c>
+      <c r="O99" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P99" s="4"/>
     </row>
     <row r="100" spans="1:16">
@@ -7057,6 +7090,9 @@
       <c r="N100" s="17">
         <v>0.68</v>
       </c>
+      <c r="O100" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P100" s="4"/>
     </row>
     <row r="101" spans="1:16">
@@ -7102,6 +7138,9 @@
       <c r="N101" s="17">
         <v>0.44</v>
       </c>
+      <c r="O101" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P101" s="4"/>
     </row>
     <row r="102" spans="1:16">
@@ -7192,6 +7231,9 @@
       <c r="N103" s="17">
         <v>0.44</v>
       </c>
+      <c r="O103" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P103" s="4"/>
     </row>
     <row r="104" spans="1:16">
@@ -7237,6 +7279,9 @@
       <c r="N104" s="17">
         <v>0.79</v>
       </c>
+      <c r="O104" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P104" s="4"/>
     </row>
     <row r="105" spans="1:16">
@@ -7372,6 +7417,9 @@
       <c r="N107" s="17">
         <v>0.44</v>
       </c>
+      <c r="O107" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P107" s="4"/>
     </row>
     <row r="108" spans="1:16">
@@ -7510,6 +7558,9 @@
       <c r="N110" s="17">
         <v>0.79</v>
       </c>
+      <c r="O110" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P110" s="4"/>
     </row>
     <row r="111" spans="1:16">
@@ -7552,6 +7603,9 @@
       <c r="N111" s="17">
         <v>0.79</v>
       </c>
+      <c r="O111" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P111" s="4"/>
     </row>
     <row r="112" spans="1:16">
@@ -7597,6 +7651,9 @@
       <c r="N112" s="17">
         <v>0.79</v>
       </c>
+      <c r="O112" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P112" s="4"/>
     </row>
     <row r="113" spans="1:16">
@@ -7688,7 +7745,7 @@
         <v>0</v>
       </c>
       <c r="O114" s="17">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="P114" s="4"/>
     </row>
@@ -7825,6 +7882,9 @@
       <c r="N117" s="17">
         <v>0.74</v>
       </c>
+      <c r="O117" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P117" s="4"/>
     </row>
     <row r="118" spans="1:16">
@@ -7867,6 +7927,9 @@
       <c r="N118" s="17">
         <v>0.79</v>
       </c>
+      <c r="O118" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P118" s="4"/>
     </row>
     <row r="119" spans="1:16">
@@ -7954,6 +8017,9 @@
       <c r="N120" s="17">
         <v>0.74</v>
       </c>
+      <c r="O120" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P120" s="15"/>
     </row>
     <row r="121" spans="1:16">
@@ -7999,6 +8065,9 @@
       <c r="N121" s="17">
         <v>0.79</v>
       </c>
+      <c r="O121" s="17">
+        <v>0.88</v>
+      </c>
       <c r="P121" s="4"/>
     </row>
     <row r="122" spans="1:16">
@@ -8045,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="O122" s="17">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="P122" s="4"/>
     </row>
@@ -8092,6 +8161,9 @@
       <c r="N123" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O123" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P123" s="4"/>
     </row>
     <row r="124" spans="1:16">
@@ -8138,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="O124" s="17">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="P124" s="4"/>
     </row>
@@ -8185,6 +8257,9 @@
       <c r="N125" s="17">
         <v>0.44</v>
       </c>
+      <c r="O125" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P125" s="4"/>
     </row>
     <row r="126" spans="1:16">
@@ -8227,6 +8302,9 @@
       <c r="N126" s="17">
         <v>0</v>
       </c>
+      <c r="O126" s="17">
+        <v>0.85</v>
+      </c>
       <c r="P126" s="4"/>
     </row>
     <row r="127" spans="1:16">
@@ -8270,7 +8348,7 @@
         <v>0</v>
       </c>
       <c r="O127" s="17">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="P127" s="4"/>
     </row>
@@ -8318,7 +8396,7 @@
         <v>0</v>
       </c>
       <c r="O128" s="17">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="P128" s="4"/>
     </row>
@@ -8413,6 +8491,9 @@
       <c r="N130" s="17">
         <v>0.68</v>
       </c>
+      <c r="O130" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P130" s="4"/>
     </row>
     <row r="131" spans="1:16">
@@ -8458,6 +8539,9 @@
       <c r="N131" s="17">
         <v>0.68</v>
       </c>
+      <c r="O131" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P131" s="4"/>
     </row>
     <row r="132" spans="1:16">
@@ -8500,6 +8584,9 @@
       <c r="N132" s="17">
         <v>0.74</v>
       </c>
+      <c r="O132" s="17">
+        <v>0.76</v>
+      </c>
       <c r="P132" s="4"/>
     </row>
     <row r="133" spans="1:16">
@@ -8541,6 +8628,9 @@
       </c>
       <c r="N133" s="17">
         <v>0.44</v>
+      </c>
+      <c r="O133" s="17">
+        <v>0.62</v>
       </c>
       <c r="P133" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7966F9A1-9B5A-B94F-B94D-231644178FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72331BE1-AB06-024F-A800-BD8D8C0C314E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6679,6 +6679,9 @@
       <c r="N91" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O91" s="17">
+        <v>0</v>
+      </c>
       <c r="P91" s="4"/>
     </row>
     <row r="92" spans="1:16">
@@ -6772,6 +6775,9 @@
       <c r="N93" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O93" s="17">
+        <v>0</v>
+      </c>
       <c r="P93" s="4"/>
     </row>
     <row r="94" spans="1:16">
@@ -6814,6 +6820,9 @@
       <c r="N94" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O94" s="17">
+        <v>0</v>
+      </c>
       <c r="P94" s="4"/>
     </row>
     <row r="95" spans="1:16">
@@ -6997,6 +7006,9 @@
       <c r="N98" s="17">
         <v>0</v>
       </c>
+      <c r="O98" s="17">
+        <v>0</v>
+      </c>
       <c r="P98" s="15"/>
     </row>
     <row r="99" spans="1:16">
@@ -7186,6 +7198,9 @@
       <c r="N102" s="17">
         <v>0.65</v>
       </c>
+      <c r="O102" s="17">
+        <v>0</v>
+      </c>
       <c r="P102" s="4"/>
     </row>
     <row r="103" spans="1:16">
@@ -7372,6 +7387,9 @@
       <c r="N106" s="17">
         <v>0.65</v>
       </c>
+      <c r="O106" s="17">
+        <v>0</v>
+      </c>
       <c r="P106" s="15"/>
     </row>
     <row r="107" spans="1:16">
@@ -7513,6 +7531,9 @@
       <c r="N109" s="17">
         <v>0.65</v>
       </c>
+      <c r="O109" s="17">
+        <v>0</v>
+      </c>
       <c r="P109" s="4"/>
     </row>
     <row r="110" spans="1:16">
@@ -7699,6 +7720,9 @@
       <c r="N113" s="17">
         <v>0.65</v>
       </c>
+      <c r="O113" s="17">
+        <v>0</v>
+      </c>
       <c r="P113" s="4"/>
     </row>
     <row r="114" spans="1:16">
@@ -7792,6 +7816,9 @@
       <c r="N115" s="17">
         <v>0</v>
       </c>
+      <c r="O115" s="17">
+        <v>0</v>
+      </c>
       <c r="P115" s="4"/>
     </row>
     <row r="116" spans="1:16">
@@ -7837,6 +7864,9 @@
       <c r="N116" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O116" s="17">
+        <v>0</v>
+      </c>
       <c r="P116" s="4"/>
     </row>
     <row r="117" spans="1:16">
@@ -7972,6 +8002,9 @@
       <c r="N119" s="17">
         <v>0.65</v>
       </c>
+      <c r="O119" s="17">
+        <v>0</v>
+      </c>
       <c r="P119" s="4"/>
     </row>
     <row r="120" spans="1:16">
@@ -8677,6 +8710,9 @@
       <c r="N134" s="17">
         <v>0</v>
       </c>
+      <c r="O134" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P134" s="4"/>
     </row>
     <row r="135" spans="1:16">
@@ -8719,6 +8755,9 @@
       <c r="N135" s="17">
         <v>0.88</v>
       </c>
+      <c r="O135" s="17">
+        <v>0.74</v>
+      </c>
       <c r="P135" s="4"/>
     </row>
     <row r="136" spans="1:16">
@@ -8761,6 +8800,9 @@
       <c r="N136" s="17">
         <v>0</v>
       </c>
+      <c r="O136" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P136" s="4"/>
     </row>
     <row r="137" spans="1:16">
@@ -8806,6 +8848,9 @@
       <c r="N137" s="17">
         <v>0.76</v>
       </c>
+      <c r="O137" s="17">
+        <v>0.97</v>
+      </c>
       <c r="P137" s="4"/>
     </row>
     <row r="138" spans="1:16">
@@ -8851,6 +8896,9 @@
       <c r="N138" s="17">
         <v>0.65</v>
       </c>
+      <c r="O138" s="17">
+        <v>0</v>
+      </c>
       <c r="P138" s="4"/>
     </row>
     <row r="139" spans="1:16">
@@ -8893,6 +8941,9 @@
       <c r="N139" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O139" s="17">
+        <v>0.35</v>
+      </c>
       <c r="P139" s="4"/>
     </row>
     <row r="140" spans="1:16">
@@ -8938,6 +8989,9 @@
       <c r="N140" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O140" s="17">
+        <v>0.47</v>
+      </c>
       <c r="P140" s="4"/>
     </row>
     <row r="141" spans="1:16">
@@ -8980,6 +9034,9 @@
       <c r="N141" s="17">
         <v>0.47</v>
       </c>
+      <c r="O141" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P141" s="4"/>
     </row>
     <row r="142" spans="1:16">
@@ -9022,6 +9079,9 @@
       <c r="N142" s="17">
         <v>0.59</v>
       </c>
+      <c r="O142" s="17">
+        <v>0</v>
+      </c>
       <c r="P142" s="4"/>
     </row>
     <row r="143" spans="1:16">
@@ -9067,6 +9127,9 @@
       <c r="N143" s="17">
         <v>0.38</v>
       </c>
+      <c r="O143" s="17">
+        <v>0</v>
+      </c>
       <c r="P143" s="4"/>
     </row>
     <row r="144" spans="1:16">
@@ -9112,6 +9175,9 @@
       <c r="N144" s="17">
         <v>0.85</v>
       </c>
+      <c r="O144" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P144" s="4"/>
     </row>
     <row r="145" spans="1:16">
@@ -9157,6 +9223,9 @@
       <c r="N145" s="17">
         <v>0.47</v>
       </c>
+      <c r="O145" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P145" s="4"/>
     </row>
     <row r="146" spans="1:16">
@@ -9202,6 +9271,9 @@
       <c r="N146" s="17">
         <v>0.65</v>
       </c>
+      <c r="O146" s="17">
+        <v>0</v>
+      </c>
       <c r="P146" s="4"/>
     </row>
     <row r="147" spans="1:16">
@@ -9244,6 +9316,9 @@
       <c r="N147" s="17">
         <v>0</v>
       </c>
+      <c r="O147" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P147" s="4"/>
     </row>
     <row r="148" spans="1:16">
@@ -9289,6 +9364,9 @@
       <c r="N148" s="17">
         <v>0.47</v>
       </c>
+      <c r="O148" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P148" s="4"/>
     </row>
     <row r="149" spans="1:16">
@@ -9334,6 +9412,9 @@
       <c r="N149" s="17">
         <v>0.59</v>
       </c>
+      <c r="O149" s="17">
+        <v>0</v>
+      </c>
       <c r="P149" s="4"/>
     </row>
     <row r="150" spans="1:16">
@@ -9379,6 +9460,9 @@
       <c r="N150" s="17">
         <v>0.38</v>
       </c>
+      <c r="O150" s="17">
+        <v>0.44</v>
+      </c>
       <c r="P150" s="4"/>
     </row>
     <row r="151" spans="1:16">
@@ -9424,6 +9508,9 @@
       <c r="N151" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O151" s="17">
+        <v>0.35</v>
+      </c>
       <c r="P151" s="4"/>
     </row>
     <row r="152" spans="1:16">
@@ -9469,6 +9556,9 @@
       <c r="N152" s="17">
         <v>0.85</v>
       </c>
+      <c r="O152" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P152" s="4"/>
     </row>
     <row r="153" spans="1:16">
@@ -9514,6 +9604,9 @@
       <c r="N153" s="17">
         <v>0.65</v>
       </c>
+      <c r="O153" s="17">
+        <v>0</v>
+      </c>
       <c r="P153" s="4"/>
     </row>
     <row r="154" spans="1:16">
@@ -9559,6 +9652,9 @@
       <c r="N154" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O154" s="17">
+        <v>0.47</v>
+      </c>
       <c r="P154" s="4"/>
     </row>
     <row r="155" spans="1:16">
@@ -9604,6 +9700,9 @@
       <c r="N155" s="17">
         <v>0</v>
       </c>
+      <c r="O155" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P155" s="4"/>
     </row>
     <row r="156" spans="1:16">
@@ -9649,6 +9748,9 @@
       <c r="N156" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O156" s="17">
+        <v>0.35</v>
+      </c>
       <c r="P156" s="4"/>
     </row>
     <row r="157" spans="1:16">
@@ -9694,6 +9796,9 @@
       <c r="N157" s="17">
         <v>0.59</v>
       </c>
+      <c r="O157" s="17">
+        <v>0</v>
+      </c>
       <c r="P157" s="4"/>
     </row>
     <row r="158" spans="1:16">
@@ -9739,6 +9844,9 @@
       <c r="N158" s="17">
         <v>0.59</v>
       </c>
+      <c r="O158" s="17">
+        <v>0</v>
+      </c>
       <c r="P158" s="4"/>
     </row>
     <row r="159" spans="1:16">
@@ -9784,6 +9892,9 @@
       <c r="N159" s="17">
         <v>0.85</v>
       </c>
+      <c r="O159" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P159" s="4"/>
     </row>
     <row r="160" spans="1:16">
@@ -9829,6 +9940,9 @@
       <c r="N160" s="17">
         <v>0.59</v>
       </c>
+      <c r="O160" s="17">
+        <v>0.53</v>
+      </c>
       <c r="P160" s="4"/>
     </row>
     <row r="161" spans="1:16">
@@ -9871,6 +9985,9 @@
       <c r="N161" s="17">
         <v>0.65</v>
       </c>
+      <c r="O161" s="17">
+        <v>0</v>
+      </c>
       <c r="P161" s="4"/>
     </row>
     <row r="162" spans="1:16">
@@ -9913,6 +10030,9 @@
       <c r="N162" s="17">
         <v>0.59</v>
       </c>
+      <c r="O162" s="17">
+        <v>0</v>
+      </c>
       <c r="P162" s="4"/>
     </row>
     <row r="163" spans="1:16">
@@ -9958,6 +10078,9 @@
       <c r="N163" s="17">
         <v>0</v>
       </c>
+      <c r="O163" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P163" s="4"/>
     </row>
     <row r="164" spans="1:16">
@@ -10003,6 +10126,9 @@
       <c r="N164" s="17">
         <v>0</v>
       </c>
+      <c r="O164" s="17">
+        <v>0.79</v>
+      </c>
       <c r="P164" s="4"/>
     </row>
     <row r="165" spans="1:16">
@@ -10048,6 +10174,9 @@
       <c r="N165" s="17">
         <v>0.47</v>
       </c>
+      <c r="O165" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P165" s="4"/>
     </row>
     <row r="166" spans="1:16">
@@ -10093,6 +10222,9 @@
       <c r="N166" s="17">
         <v>0.85</v>
       </c>
+      <c r="O166" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P166" s="4"/>
     </row>
     <row r="167" spans="1:16">
@@ -10135,6 +10267,9 @@
       <c r="N167" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O167" s="17">
+        <v>0.47</v>
+      </c>
       <c r="P167" s="4"/>
     </row>
     <row r="168" spans="1:16">
@@ -10177,6 +10312,9 @@
       <c r="N168" s="17">
         <v>0.85</v>
       </c>
+      <c r="O168" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P168" s="4"/>
     </row>
     <row r="169" spans="1:16">
@@ -10222,6 +10360,9 @@
       <c r="N169" s="17">
         <v>0.59</v>
       </c>
+      <c r="O169" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P169" s="4"/>
     </row>
     <row r="170" spans="1:16">
@@ -10267,6 +10408,9 @@
       <c r="N170" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O170" s="17">
+        <v>0.35</v>
+      </c>
       <c r="P170" s="4"/>
     </row>
     <row r="171" spans="1:16">
@@ -10312,6 +10456,9 @@
       <c r="N171" s="17">
         <v>0.59</v>
       </c>
+      <c r="O171" s="17">
+        <v>0</v>
+      </c>
       <c r="P171" s="4"/>
     </row>
     <row r="172" spans="1:16">
@@ -10357,6 +10504,9 @@
       <c r="N172" s="17">
         <v>0.65</v>
       </c>
+      <c r="O172" s="17">
+        <v>0</v>
+      </c>
       <c r="P172" s="4"/>
     </row>
     <row r="173" spans="1:16">
@@ -10402,6 +10552,9 @@
       <c r="N173" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O173" s="17">
+        <v>0.47</v>
+      </c>
       <c r="P173" s="4"/>
     </row>
     <row r="174" spans="1:16">
@@ -10447,6 +10600,9 @@
       <c r="N174" s="17">
         <v>0.59</v>
       </c>
+      <c r="O174" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P174" s="4"/>
     </row>
     <row r="175" spans="1:16">
@@ -10492,6 +10648,9 @@
       <c r="N175" s="17">
         <v>0.59</v>
       </c>
+      <c r="O175" s="17">
+        <v>0.41</v>
+      </c>
       <c r="P175" s="4"/>
     </row>
     <row r="176" spans="1:16">
@@ -10537,6 +10696,9 @@
       <c r="N176" s="17">
         <v>0.85</v>
       </c>
+      <c r="O176" s="17">
+        <v>0.82</v>
+      </c>
       <c r="P176" s="4"/>
     </row>
     <row r="177" spans="1:16">
@@ -10582,6 +10744,9 @@
       <c r="N177" s="17">
         <v>0</v>
       </c>
+      <c r="O177" s="17">
+        <v>0.71</v>
+      </c>
       <c r="P177" s="4"/>
     </row>
     <row r="178" spans="1:16">
@@ -10627,6 +10792,9 @@
       <c r="N178" s="17">
         <v>0</v>
       </c>
+      <c r="O178" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P178" s="4"/>
     </row>
     <row r="179" spans="1:16">
@@ -10669,6 +10837,9 @@
       <c r="N179" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O179" s="17">
+        <v>0.35</v>
+      </c>
       <c r="P179" s="4"/>
     </row>
     <row r="180" spans="1:16">
@@ -10714,6 +10885,9 @@
       <c r="N180" s="17">
         <v>0.65</v>
       </c>
+      <c r="O180" s="17">
+        <v>0</v>
+      </c>
       <c r="P180" s="4"/>
     </row>
     <row r="181" spans="1:16">
@@ -10756,6 +10930,9 @@
       <c r="N181" s="17">
         <v>0.59</v>
       </c>
+      <c r="O181" s="17">
+        <v>0</v>
+      </c>
       <c r="P181" s="4"/>
     </row>
     <row r="182" spans="1:16">
@@ -10801,6 +10978,9 @@
       <c r="N182" s="17">
         <v>0.56000000000000005</v>
       </c>
+      <c r="O182" s="17">
+        <v>0.35</v>
+      </c>
       <c r="P182" s="4"/>
     </row>
     <row r="183" spans="1:16">
@@ -10845,6 +11025,9 @@
       </c>
       <c r="N183" s="17">
         <v>0.47</v>
+      </c>
+      <c r="O183" s="17">
+        <v>0.71</v>
       </c>
       <c r="P183" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72331BE1-AB06-024F-A800-BD8D8C0C314E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DDCD89-F942-FA4D-A48C-AFC3AC025935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -11116,6 +11116,9 @@
       <c r="N185" s="17">
         <v>0.79</v>
       </c>
+      <c r="O185" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P185" s="4"/>
     </row>
     <row r="186" spans="1:16">
@@ -11161,6 +11164,9 @@
       <c r="N186" s="17">
         <v>0.15</v>
       </c>
+      <c r="O186" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P186" s="4"/>
     </row>
     <row r="187" spans="1:16">
@@ -11290,6 +11296,9 @@
       <c r="N189" s="17">
         <v>0.62</v>
       </c>
+      <c r="O189" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P189" s="4"/>
     </row>
     <row r="190" spans="1:16">
@@ -11335,6 +11344,9 @@
       <c r="N190" s="17">
         <v>0.79</v>
       </c>
+      <c r="O190" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P190" s="4"/>
     </row>
     <row r="191" spans="1:16">
@@ -11380,6 +11392,9 @@
       <c r="N191" s="17">
         <v>0.62</v>
       </c>
+      <c r="O191" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P191" s="4"/>
     </row>
     <row r="192" spans="1:16">
@@ -11425,6 +11440,9 @@
       <c r="N192" s="17">
         <v>0.65</v>
       </c>
+      <c r="O192" s="17">
+        <v>0.53</v>
+      </c>
       <c r="P192" s="4"/>
     </row>
     <row r="193" spans="1:16">
@@ -11470,6 +11488,9 @@
       <c r="N193" s="17">
         <v>0</v>
       </c>
+      <c r="O193" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P193" s="4"/>
     </row>
     <row r="194" spans="1:16">
@@ -11692,6 +11713,9 @@
       <c r="N198" s="17">
         <v>0</v>
       </c>
+      <c r="O198" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P198" s="4"/>
     </row>
     <row r="199" spans="1:16">
@@ -11827,6 +11851,9 @@
       <c r="N201" s="17">
         <v>0.15</v>
       </c>
+      <c r="O201" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P201" s="4"/>
     </row>
     <row r="202" spans="1:16">
@@ -11917,6 +11944,9 @@
       <c r="N203" s="17">
         <v>0.62</v>
       </c>
+      <c r="O203" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P203" s="4"/>
     </row>
     <row r="204" spans="1:16">
@@ -12049,6 +12079,9 @@
       <c r="N206" s="17">
         <v>0</v>
       </c>
+      <c r="O206" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P206" s="4"/>
     </row>
     <row r="207" spans="1:16">
@@ -12091,6 +12124,9 @@
       <c r="N207" s="17">
         <v>0</v>
       </c>
+      <c r="O207" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P207" s="4"/>
     </row>
     <row r="208" spans="1:16">
@@ -12136,6 +12172,9 @@
       <c r="N208" s="17">
         <v>0.15</v>
       </c>
+      <c r="O208" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P208" s="4"/>
     </row>
     <row r="209" spans="1:16">
@@ -12181,6 +12220,9 @@
       <c r="N209" s="17">
         <v>0.15</v>
       </c>
+      <c r="O209" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P209" s="4"/>
     </row>
     <row r="210" spans="1:16">
@@ -12226,6 +12268,9 @@
       <c r="N210" s="17">
         <v>0.79</v>
       </c>
+      <c r="O210" s="17">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="P210" s="4"/>
     </row>
     <row r="211" spans="1:16">
@@ -12271,6 +12316,9 @@
       <c r="N211" s="17">
         <v>0.15</v>
       </c>
+      <c r="O211" s="17">
+        <v>0.68</v>
+      </c>
       <c r="P211" s="4"/>
     </row>
     <row r="212" spans="1:16">
@@ -12316,6 +12364,9 @@
       <c r="N212" s="17">
         <v>0.62</v>
       </c>
+      <c r="O212" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P212" s="4"/>
     </row>
     <row r="213" spans="1:16">
@@ -12361,6 +12412,9 @@
       <c r="N213" s="17">
         <v>0.62</v>
       </c>
+      <c r="O213" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P213" s="4"/>
     </row>
     <row r="214" spans="1:16">
@@ -12451,6 +12505,9 @@
       <c r="N215" s="17">
         <v>0</v>
       </c>
+      <c r="O215" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P215" s="4"/>
     </row>
     <row r="216" spans="1:16">
@@ -12541,6 +12598,9 @@
       <c r="N217" s="17">
         <v>0</v>
       </c>
+      <c r="O217" s="17">
+        <v>0.62</v>
+      </c>
       <c r="P217" s="4"/>
     </row>
     <row r="218" spans="1:16">
@@ -12628,6 +12688,9 @@
       <c r="N219" s="17">
         <v>0.62</v>
       </c>
+      <c r="O219" s="17">
+        <v>0.65</v>
+      </c>
       <c r="P219" s="4"/>
     </row>
     <row r="220" spans="1:16">
@@ -12672,6 +12735,9 @@
       </c>
       <c r="N220" s="17">
         <v>0.79</v>
+      </c>
+      <c r="O220" s="17">
+        <v>0.56000000000000005</v>
       </c>
       <c r="P220" s="4"/>
     </row>

--- a/cw12022026.xlsx
+++ b/cw12022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFDBCA8-0D7F-0745-9102-B72B625F8232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A997C1-8349-3141-923D-AB1280AD07B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="32000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="531">
   <si>
     <t>Surname</t>
   </si>
@@ -1617,6 +1617,18 @@
   </si>
   <si>
     <t>H240491N</t>
+  </si>
+  <si>
+    <t>Madanhire</t>
+  </si>
+  <si>
+    <t>H230182N</t>
+  </si>
+  <si>
+    <t>Jayaguru</t>
+  </si>
+  <si>
+    <t>H210960R</t>
   </si>
 </sst>
 </file>
@@ -1766,7 +1778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1807,11 +1819,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1895,10 +1906,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:P256" totalsRowShown="0">
-  <autoFilter ref="A1:P256" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P256">
-    <sortCondition ref="C1:C256"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:P258" totalsRowShown="0">
+  <autoFilter ref="A1:P258" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P258">
+    <sortCondition ref="C1:C258"/>
   </sortState>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -2239,7 +2250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:P256"/>
+  <dimension ref="A1:P258"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -2366,7 +2377,7 @@
       </c>
       <c r="D3" s="17"/>
       <c r="I3" s="17"/>
-      <c r="P3" s="26">
+      <c r="P3" s="22">
         <v>0.63</v>
       </c>
     </row>
@@ -2433,7 +2444,7 @@
       </c>
       <c r="D5" s="17"/>
       <c r="I5" s="17"/>
-      <c r="P5" s="26">
+      <c r="P5" s="22">
         <v>0.53</v>
       </c>
     </row>
@@ -2500,7 +2511,7 @@
       </c>
       <c r="D7" s="17"/>
       <c r="I7" s="17"/>
-      <c r="P7" s="26">
+      <c r="P7" s="22">
         <v>0.52</v>
       </c>
     </row>
@@ -2769,7 +2780,7 @@
       </c>
       <c r="D13" s="17"/>
       <c r="I13" s="17"/>
-      <c r="P13" s="26">
+      <c r="P13" s="22">
         <v>0.67</v>
       </c>
     </row>
@@ -3309,7 +3320,7 @@
       </c>
       <c r="D25" s="17"/>
       <c r="I25" s="17"/>
-      <c r="P25" s="26">
+      <c r="P25" s="22">
         <v>0.62</v>
       </c>
     </row>
@@ -3795,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="14">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K35" s="14">
         <v>0.56999999999999995</v>
@@ -3814,7 +3825,7 @@
       </c>
       <c r="P35" s="19">
         <f>(((LARGE(D35:G35,1)+LARGE(D35:G35,2)+LARGE(D35:G35,3))*0.2/3+(LARGE(H35:K35,1)+LARGE(H35:K35,2)+LARGE(H35:K35,3))*0.5/3+(LARGE(L35:O35,1)+LARGE(L35:O35,2)+LARGE(L35:O35,3))*0.3/3))</f>
-        <v>0.50733333333333319</v>
+        <v>0.57399999999999984</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4220,10 +4231,10 @@
       </c>
     </row>
     <row r="44" spans="1:16">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="10" t="s">
         <v>79</v>
       </c>
       <c r="C44" s="14" t="s">
@@ -4269,10 +4280,10 @@
       </c>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="12" t="s">
         <v>89</v>
       </c>
       <c r="C45" s="14" t="s">
@@ -4320,10 +4331,10 @@
       </c>
     </row>
     <row r="46" spans="1:16">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="10" t="s">
         <v>83</v>
       </c>
       <c r="C46" s="14" t="s">
@@ -4371,10 +4382,10 @@
       </c>
     </row>
     <row r="47" spans="1:16">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="B47" s="10" t="s">
         <v>86</v>
       </c>
       <c r="C47" s="14" t="s">
@@ -4422,10 +4433,10 @@
       </c>
     </row>
     <row r="48" spans="1:16">
-      <c r="A48" t="s">
+      <c r="A48" s="24" t="s">
         <v>479</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="25" t="s">
         <v>480</v>
       </c>
       <c r="C48" s="14" t="s">
@@ -4471,10 +4482,10 @@
       </c>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" t="s">
+      <c r="A49" s="24" t="s">
         <v>483</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="25" t="s">
         <v>493</v>
       </c>
       <c r="C49" s="14" t="s">
@@ -4591,10 +4602,10 @@
       </c>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="23" t="s">
         <v>80</v>
       </c>
       <c r="C52" s="14" t="s">
@@ -4693,10 +4704,10 @@
       </c>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="28" t="s">
+      <c r="A54" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B54" s="28" t="s">
+      <c r="B54" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C54" s="16" t="s">
@@ -4744,10 +4755,10 @@
       </c>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="28" t="s">
+      <c r="A55" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="27" t="s">
         <v>95</v>
       </c>
       <c r="C55" s="16" t="s">
@@ -4795,10 +4806,10 @@
       </c>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="28" t="s">
+      <c r="B56" s="27" t="s">
         <v>97</v>
       </c>
       <c r="C56" s="16" t="s">
@@ -4846,10 +4857,10 @@
       </c>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="28" t="s">
+      <c r="A57" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="B57" s="28" t="s">
+      <c r="B57" s="27" t="s">
         <v>99</v>
       </c>
       <c r="C57" s="16" t="s">
@@ -4897,10 +4908,10 @@
       </c>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" s="28" t="s">
+      <c r="A58" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B58" s="28" t="s">
+      <c r="B58" s="27" t="s">
         <v>101</v>
       </c>
       <c r="C58" s="16" t="s">
@@ -4945,10 +4956,10 @@
       </c>
     </row>
     <row r="59" spans="1:16">
-      <c r="A59" s="28" t="s">
+      <c r="A59" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="27" t="s">
         <v>103</v>
       </c>
       <c r="C59" s="16" t="s">
@@ -5657,10 +5668,10 @@
       </c>
     </row>
     <row r="73" spans="1:16">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="27" t="s">
         <v>130</v>
       </c>
       <c r="C73" s="16" t="s">
@@ -6618,10 +6629,10 @@
       </c>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="27" t="s">
         <v>166</v>
       </c>
       <c r="C92" s="16" t="s">
@@ -6771,10 +6782,10 @@
       </c>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" t="s">
+      <c r="A95" s="24" t="s">
         <v>517</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="25" t="s">
         <v>518</v>
       </c>
       <c r="C95" s="14" t="s">
@@ -6782,15 +6793,15 @@
       </c>
       <c r="D95" s="17"/>
       <c r="I95" s="17"/>
-      <c r="P95" s="26">
+      <c r="P95" s="22">
         <v>0.51</v>
       </c>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="28" t="s">
+      <c r="A96" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="B96" s="28" t="s">
+      <c r="B96" s="27" t="s">
         <v>172</v>
       </c>
       <c r="C96" s="16" t="s">
@@ -6838,10 +6849,10 @@
       </c>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="28" t="s">
+      <c r="A97" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="B97" s="28" t="s">
+      <c r="B97" s="27" t="s">
         <v>175</v>
       </c>
       <c r="C97" s="16" t="s">
@@ -6940,10 +6951,10 @@
       </c>
     </row>
     <row r="99" spans="1:16">
-      <c r="A99" s="28" t="s">
+      <c r="A99" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="B99" s="28" t="s">
+      <c r="B99" s="27" t="s">
         <v>177</v>
       </c>
       <c r="C99" s="16" t="s">
@@ -6991,10 +7002,10 @@
       </c>
     </row>
     <row r="100" spans="1:16">
-      <c r="A100" s="28" t="s">
+      <c r="A100" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="B100" s="28" t="s">
+      <c r="B100" s="27" t="s">
         <v>179</v>
       </c>
       <c r="C100" s="16" t="s">
@@ -7039,10 +7050,10 @@
       </c>
     </row>
     <row r="101" spans="1:16">
-      <c r="A101" s="28" t="s">
+      <c r="A101" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="B101" s="28" t="s">
+      <c r="B101" s="27" t="s">
         <v>181</v>
       </c>
       <c r="C101" s="16" t="s">
@@ -7087,10 +7098,10 @@
       </c>
     </row>
     <row r="102" spans="1:16">
-      <c r="A102" s="28" t="s">
+      <c r="A102" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="B102" s="28" t="s">
+      <c r="B102" s="27" t="s">
         <v>183</v>
       </c>
       <c r="C102" s="16" t="s">
@@ -7138,10 +7149,10 @@
       </c>
     </row>
     <row r="103" spans="1:16">
-      <c r="A103" s="28" t="s">
+      <c r="A103" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="B103" s="28" t="s">
+      <c r="B103" s="27" t="s">
         <v>185</v>
       </c>
       <c r="C103" s="16" t="s">
@@ -7288,10 +7299,10 @@
       </c>
     </row>
     <row r="106" spans="1:16">
-      <c r="A106" s="8" t="s">
+      <c r="A106" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B106" s="27" t="s">
         <v>189</v>
       </c>
       <c r="C106" s="16" t="s">
@@ -7441,10 +7452,10 @@
       </c>
     </row>
     <row r="109" spans="1:16">
-      <c r="A109" s="8" t="s">
+      <c r="A109" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="B109" s="8" t="s">
+      <c r="B109" s="27" t="s">
         <v>195</v>
       </c>
       <c r="C109" s="16" t="s">
@@ -7492,10 +7503,10 @@
       </c>
     </row>
     <row r="110" spans="1:16">
-      <c r="A110" s="8" t="s">
+      <c r="A110" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="B110" s="8" t="s">
+      <c r="B110" s="27" t="s">
         <v>197</v>
       </c>
       <c r="C110" s="16" t="s">
@@ -7996,10 +8007,10 @@
       </c>
     </row>
     <row r="120" spans="1:16">
-      <c r="A120" t="s">
+      <c r="A120" s="24" t="s">
         <v>525</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="25" t="s">
         <v>526</v>
       </c>
       <c r="C120" s="14" t="s">
@@ -8007,7 +8018,7 @@
       </c>
       <c r="D120" s="17"/>
       <c r="I120" s="17"/>
-      <c r="P120" s="26">
+      <c r="P120" s="22">
         <v>0.57999999999999996</v>
       </c>
     </row>
@@ -8165,10 +8176,10 @@
       </c>
     </row>
     <row r="124" spans="1:16">
-      <c r="A124" t="s">
+      <c r="A124" s="24" t="s">
         <v>519</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="25" t="s">
         <v>520</v>
       </c>
       <c r="C124" s="14" t="s">
@@ -8176,7 +8187,7 @@
       </c>
       <c r="D124" s="17"/>
       <c r="I124" s="17"/>
-      <c r="P124" s="26">
+      <c r="P124" s="22">
         <v>0.59</v>
       </c>
     </row>
@@ -8280,10 +8291,10 @@
       </c>
     </row>
     <row r="127" spans="1:16">
-      <c r="A127" s="8" t="s">
+      <c r="A127" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="B127" s="8" t="s">
+      <c r="B127" s="27" t="s">
         <v>224</v>
       </c>
       <c r="C127" s="16" t="s">
@@ -8982,10 +8993,10 @@
       </c>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" s="8" t="s">
+      <c r="A141" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="B141" s="8" t="s">
+      <c r="B141" s="27" t="s">
         <v>249</v>
       </c>
       <c r="C141" s="16" t="s">
@@ -9030,10 +9041,10 @@
       </c>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="28" t="s">
+      <c r="A142" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="B142" s="28" t="s">
+      <c r="B142" s="27" t="s">
         <v>251</v>
       </c>
       <c r="C142" s="16" t="s">
@@ -9081,10 +9092,10 @@
       </c>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" s="28" t="s">
+      <c r="A143" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="B143" s="28" t="s">
+      <c r="B143" s="27" t="s">
         <v>254</v>
       </c>
       <c r="C143" s="16" t="s">
@@ -9129,10 +9140,10 @@
       </c>
     </row>
     <row r="144" spans="1:16">
-      <c r="A144" s="28" t="s">
+      <c r="A144" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="B144" s="28" t="s">
+      <c r="B144" s="27" t="s">
         <v>256</v>
       </c>
       <c r="C144" s="16" t="s">
@@ -9177,10 +9188,10 @@
       </c>
     </row>
     <row r="145" spans="1:16">
-      <c r="A145" s="28" t="s">
+      <c r="A145" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="B145" s="28" t="s">
+      <c r="B145" s="27" t="s">
         <v>258</v>
       </c>
       <c r="C145" s="16" t="s">
@@ -9228,10 +9239,10 @@
       </c>
     </row>
     <row r="146" spans="1:16">
-      <c r="A146" s="28" t="s">
+      <c r="A146" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="B146" s="28" t="s">
+      <c r="B146" s="27" t="s">
         <v>260</v>
       </c>
       <c r="C146" s="16" t="s">
@@ -9279,10 +9290,10 @@
       </c>
     </row>
     <row r="147" spans="1:16">
-      <c r="A147" s="28" t="s">
+      <c r="A147" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="B147" s="28" t="s">
+      <c r="B147" s="27" t="s">
         <v>262</v>
       </c>
       <c r="C147" s="16" t="s">
@@ -9327,10 +9338,10 @@
       </c>
     </row>
     <row r="148" spans="1:16">
-      <c r="A148" s="28" t="s">
+      <c r="A148" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="B148" s="28" t="s">
+      <c r="B148" s="27" t="s">
         <v>264</v>
       </c>
       <c r="C148" s="16" t="s">
@@ -9378,10 +9389,10 @@
       </c>
     </row>
     <row r="149" spans="1:16">
-      <c r="A149" s="28" t="s">
+      <c r="A149" s="27" t="s">
         <v>265</v>
       </c>
-      <c r="B149" s="28" t="s">
+      <c r="B149" s="27" t="s">
         <v>266</v>
       </c>
       <c r="C149" s="16" t="s">
@@ -9426,10 +9437,10 @@
       </c>
     </row>
     <row r="150" spans="1:16">
-      <c r="A150" s="28" t="s">
+      <c r="A150" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="B150" s="28" t="s">
+      <c r="B150" s="27" t="s">
         <v>268</v>
       </c>
       <c r="C150" s="16" t="s">
@@ -9474,10 +9485,10 @@
       </c>
     </row>
     <row r="151" spans="1:16">
-      <c r="A151" s="28" t="s">
+      <c r="A151" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="B151" s="28" t="s">
+      <c r="B151" s="27" t="s">
         <v>270</v>
       </c>
       <c r="C151" s="16" t="s">
@@ -11243,10 +11254,10 @@
       </c>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" s="8" t="s">
+      <c r="A186" s="27" t="s">
         <v>334</v>
       </c>
-      <c r="B186" s="8" t="s">
+      <c r="B186" s="27" t="s">
         <v>335</v>
       </c>
       <c r="C186" s="16" t="s">
@@ -11554,15 +11565,15 @@
       </c>
       <c r="D192" s="17"/>
       <c r="I192" s="17"/>
-      <c r="P192" s="26">
+      <c r="P192" s="22">
         <v>0.5</v>
       </c>
     </row>
     <row r="193" spans="1:16">
-      <c r="A193" s="28" t="s">
+      <c r="A193" s="27" t="s">
         <v>346</v>
       </c>
-      <c r="B193" s="28" t="s">
+      <c r="B193" s="27" t="s">
         <v>347</v>
       </c>
       <c r="C193" s="16" t="s">
@@ -11607,7 +11618,7 @@
       <c r="A194" s="24" t="s">
         <v>446</v>
       </c>
-      <c r="B194" s="29" t="s">
+      <c r="B194" s="28" t="s">
         <v>447</v>
       </c>
       <c r="C194" s="14" t="s">
@@ -11655,10 +11666,10 @@
       </c>
     </row>
     <row r="195" spans="1:16">
-      <c r="A195" s="28" t="s">
+      <c r="A195" s="27" t="s">
         <v>349</v>
       </c>
-      <c r="B195" s="28" t="s">
+      <c r="B195" s="27" t="s">
         <v>350</v>
       </c>
       <c r="C195" s="16" t="s">
@@ -11717,7 +11728,7 @@
       </c>
       <c r="D196" s="17"/>
       <c r="I196" s="17"/>
-      <c r="P196" s="26">
+      <c r="P196" s="22">
         <v>0.57999999999999996</v>
       </c>
     </row>
@@ -11770,51 +11781,19 @@
       </c>
     </row>
     <row r="198" spans="1:16">
-      <c r="A198" t="s">
+      <c r="A198" s="24" t="s">
         <v>504</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="B198" s="25" t="s">
         <v>505</v>
       </c>
       <c r="C198" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="D198" s="17">
-        <v>0</v>
-      </c>
-      <c r="E198" s="14">
-        <v>0</v>
-      </c>
-      <c r="F198" s="14">
-        <v>0.59</v>
-      </c>
-      <c r="G198" s="14">
-        <v>0.78</v>
-      </c>
-      <c r="H198" s="17">
-        <v>0</v>
-      </c>
-      <c r="I198" s="17">
-        <v>0.48</v>
-      </c>
-      <c r="J198" s="14">
-        <v>0.75</v>
-      </c>
-      <c r="K198" s="14">
-        <v>0.94</v>
-      </c>
-      <c r="L198" s="14">
-        <v>0</v>
-      </c>
-      <c r="M198" s="14">
-        <v>0</v>
-      </c>
-      <c r="N198" s="14">
-        <v>0</v>
-      </c>
+      <c r="D198" s="17"/>
+      <c r="I198" s="17"/>
       <c r="P198" s="19">
-        <f>(((LARGE(D198:G198,1)+LARGE(D198:G198,2)+LARGE(D198:G198,3))*0.2/3+(LARGE(H198:K198,1)+LARGE(H198:K198,2)+LARGE(H198:K198,3))*0.5/3+(LARGE(L198:O198,1)+LARGE(L198:O198,2)+LARGE(L198:O198,3))*0.3/3))</f>
-        <v>0.45299999999999996</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11968,10 +11947,10 @@
       </c>
     </row>
     <row r="202" spans="1:16">
-      <c r="A202" s="8" t="s">
+      <c r="A202" s="27" t="s">
         <v>357</v>
       </c>
-      <c r="B202" s="8" t="s">
+      <c r="B202" s="27" t="s">
         <v>358</v>
       </c>
       <c r="C202" s="16" t="s">
@@ -12322,10 +12301,10 @@
       </c>
     </row>
     <row r="209" spans="1:16">
-      <c r="A209" t="s">
+      <c r="A209" s="24" t="s">
         <v>498</v>
       </c>
-      <c r="B209" s="2" t="s">
+      <c r="B209" s="25" t="s">
         <v>499</v>
       </c>
       <c r="C209" s="14" t="s">
@@ -13080,10 +13059,10 @@
       </c>
     </row>
     <row r="224" spans="1:16">
-      <c r="A224" t="s">
+      <c r="A224" s="24" t="s">
         <v>444</v>
       </c>
-      <c r="B224" s="2" t="s">
+      <c r="B224" s="25" t="s">
         <v>445</v>
       </c>
       <c r="C224" s="14" t="s">
@@ -13383,10 +13362,10 @@
       </c>
     </row>
     <row r="230" spans="1:16">
-      <c r="A230" s="8" t="s">
+      <c r="A230" s="27" t="s">
         <v>403</v>
       </c>
-      <c r="B230" s="8" t="s">
+      <c r="B230" s="27" t="s">
         <v>404</v>
       </c>
       <c r="C230" s="16" t="s">
@@ -13434,10 +13413,10 @@
       </c>
     </row>
     <row r="231" spans="1:16">
-      <c r="A231" s="28" t="s">
+      <c r="A231" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="B231" s="28" t="s">
+      <c r="B231" s="27" t="s">
         <v>406</v>
       </c>
       <c r="C231" s="16" t="s">
@@ -13482,10 +13461,10 @@
       </c>
     </row>
     <row r="232" spans="1:16">
-      <c r="A232" t="s">
+      <c r="A232" s="24" t="s">
         <v>502</v>
       </c>
-      <c r="B232" s="2" t="s">
+      <c r="B232" s="25" t="s">
         <v>503</v>
       </c>
       <c r="C232" s="14" t="s">
@@ -13584,92 +13563,57 @@
       </c>
     </row>
     <row r="234" spans="1:16">
-      <c r="A234" s="8" t="s">
+      <c r="A234" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="B234" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="C234" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="D234" s="17"/>
+      <c r="I234" s="17"/>
+      <c r="P234" s="22">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16">
+      <c r="A235" s="27" t="s">
         <v>410</v>
       </c>
-      <c r="B234" s="8" t="s">
+      <c r="B235" s="27" t="s">
         <v>411</v>
       </c>
-      <c r="C234" s="16" t="s">
+      <c r="C235" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="D234" s="16">
+      <c r="D235" s="16">
         <v>0.69</v>
       </c>
-      <c r="E234" s="14">
+      <c r="E235" s="14">
         <v>0.79</v>
       </c>
-      <c r="F234" s="14">
+      <c r="F235" s="14">
         <v>0.7</v>
-      </c>
-      <c r="G234" s="14">
-        <v>0.74</v>
-      </c>
-      <c r="H234" s="14">
-        <v>0.54</v>
-      </c>
-      <c r="I234" s="17">
-        <v>0.43</v>
-      </c>
-      <c r="J234" s="14">
-        <v>0.52</v>
-      </c>
-      <c r="K234" s="14">
-        <v>0.49</v>
-      </c>
-      <c r="L234" s="14">
-        <v>0.52</v>
-      </c>
-      <c r="M234" s="14">
-        <v>0</v>
-      </c>
-      <c r="N234" s="14">
-        <v>0.71</v>
-      </c>
-      <c r="O234" s="14">
-        <v>0.65</v>
-      </c>
-      <c r="P234" s="19">
-        <f>(((LARGE(D234:G234,1)+LARGE(D234:G234,2)+LARGE(D234:G234,3))*0.2/3+(LARGE(H234:K234,1)+LARGE(H234:K234,2)+LARGE(H234:K234,3))*0.5/3+(LARGE(L234:O234,1)+LARGE(L234:O234,2)+LARGE(L234:O234,3))*0.3/3))</f>
-        <v>0.59499999999999997</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16">
-      <c r="A235" t="s">
-        <v>468</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C235" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="D235" s="17">
-        <v>0</v>
-      </c>
-      <c r="E235" s="14">
-        <v>0.91</v>
-      </c>
-      <c r="F235" s="14">
-        <v>0</v>
       </c>
       <c r="G235" s="14">
         <v>0.74</v>
       </c>
       <c r="H235" s="14">
-        <v>0.35</v>
+        <v>0.54</v>
       </c>
       <c r="I235" s="17">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="J235" s="14">
-        <v>0.38</v>
+        <v>0.52</v>
       </c>
       <c r="K235" s="14">
-        <v>0.73</v>
+        <v>0.49</v>
       </c>
       <c r="L235" s="14">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="M235" s="14">
         <v>0</v>
@@ -13681,45 +13625,46 @@
         <v>0.65</v>
       </c>
       <c r="P235" s="19">
-        <v>0.5</v>
+        <f>(((LARGE(D235:G235,1)+LARGE(D235:G235,2)+LARGE(D235:G235,3))*0.2/3+(LARGE(H235:K235,1)+LARGE(H235:K235,2)+LARGE(H235:K235,3))*0.5/3+(LARGE(L235:O235,1)+LARGE(L235:O235,2)+LARGE(L235:O235,3))*0.3/3))</f>
+        <v>0.59499999999999997</v>
       </c>
     </row>
     <row r="236" spans="1:16">
-      <c r="A236" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="B236" s="8" t="s">
-        <v>413</v>
-      </c>
-      <c r="C236" s="16" t="s">
+      <c r="A236" s="24" t="s">
+        <v>468</v>
+      </c>
+      <c r="B236" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="C236" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="D236" s="16">
-        <v>0.67</v>
+      <c r="D236" s="17">
+        <v>0</v>
       </c>
       <c r="E236" s="14">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="F236" s="14">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="G236" s="14">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="H236" s="14">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="I236" s="17">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="J236" s="14">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="K236" s="14">
-        <v>0.56999999999999995</v>
+        <v>0.73</v>
       </c>
       <c r="L236" s="14">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="M236" s="14">
         <v>0</v>
@@ -13731,40 +13676,42 @@
         <v>0.65</v>
       </c>
       <c r="P236" s="19">
-        <f>(((LARGE(D236:G236,1)+LARGE(D236:G236,2)+LARGE(D236:G236,3))*0.2/3+(LARGE(H236:K236,1)+LARGE(H236:K236,2)+LARGE(H236:K236,3))*0.5/3+(LARGE(L236:O236,1)+LARGE(L236:O236,2)+LARGE(L236:O236,3))*0.3/3))</f>
-        <v>0.5096666666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="237" spans="1:16">
       <c r="A237" s="8" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C237" s="16" t="s">
         <v>407</v>
       </c>
       <c r="D237" s="16">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="E237" s="14">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="F237" s="14">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="G237" s="14">
         <v>0.71</v>
       </c>
       <c r="H237" s="14">
-        <v>0.54</v>
+        <v>0.11</v>
       </c>
       <c r="I237" s="17">
-        <v>0.7</v>
+        <v>0.21</v>
       </c>
       <c r="J237" s="14">
-        <v>0.6</v>
+        <v>0.21</v>
+      </c>
+      <c r="K237" s="14">
+        <v>0.56999999999999995</v>
       </c>
       <c r="L237" s="14">
         <v>0.52</v>
@@ -13780,42 +13727,39 @@
       </c>
       <c r="P237" s="19">
         <f>(((LARGE(D237:G237,1)+LARGE(D237:G237,2)+LARGE(D237:G237,3))*0.2/3+(LARGE(H237:K237,1)+LARGE(H237:K237,2)+LARGE(H237:K237,3))*0.5/3+(LARGE(L237:O237,1)+LARGE(L237:O237,2)+LARGE(L237:O237,3))*0.3/3))</f>
-        <v>0.65466666666666662</v>
+        <v>0.5096666666666666</v>
       </c>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" s="8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B238" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C238" s="16" t="s">
         <v>407</v>
       </c>
       <c r="D238" s="16">
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
       <c r="E238" s="14">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="F238" s="14">
+        <v>0.66</v>
+      </c>
+      <c r="G238" s="14">
+        <v>0.71</v>
+      </c>
+      <c r="H238" s="14">
+        <v>0.54</v>
+      </c>
+      <c r="I238" s="17">
         <v>0.7</v>
       </c>
-      <c r="G238" s="14">
-        <v>0.78</v>
-      </c>
-      <c r="H238" s="14">
-        <v>0.61</v>
-      </c>
-      <c r="I238" s="17">
-        <v>0.34</v>
-      </c>
       <c r="J238" s="14">
-        <v>0.33</v>
-      </c>
-      <c r="K238" s="14">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="L238" s="14">
         <v>0.52</v>
@@ -13831,321 +13775,321 @@
       </c>
       <c r="P238" s="19">
         <f>(((LARGE(D238:G238,1)+LARGE(D238:G238,2)+LARGE(D238:G238,3))*0.2/3+(LARGE(H238:K238,1)+LARGE(H238:K238,2)+LARGE(H238:K238,3))*0.5/3+(LARGE(L238:O238,1)+LARGE(L238:O238,2)+LARGE(L238:O238,3))*0.3/3))</f>
-        <v>0.6306666666666666</v>
+        <v>0.65466666666666662</v>
       </c>
     </row>
     <row r="239" spans="1:16">
-      <c r="A239" s="24" t="s">
-        <v>460</v>
-      </c>
-      <c r="B239" s="25" t="s">
-        <v>461</v>
-      </c>
-      <c r="C239" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="D239" s="17">
-        <v>0</v>
+      <c r="A239" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="B239" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="C239" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="D239" s="16">
+        <v>0.89</v>
       </c>
       <c r="E239" s="14">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="F239" s="14">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="G239" s="14">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="H239" s="14">
+        <v>0.61</v>
+      </c>
+      <c r="I239" s="17">
+        <v>0.34</v>
+      </c>
+      <c r="J239" s="14">
         <v>0.33</v>
       </c>
-      <c r="I239" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="J239" s="14">
-        <v>0.35</v>
-      </c>
       <c r="K239" s="14">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="L239" s="14">
-        <v>0.57999999999999996</v>
+        <v>0.52</v>
       </c>
       <c r="M239" s="14">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N239" s="14">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="O239" s="14">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="P239" s="19">
         <f>(((LARGE(D239:G239,1)+LARGE(D239:G239,2)+LARGE(D239:G239,3))*0.2/3+(LARGE(H239:K239,1)+LARGE(H239:K239,2)+LARGE(H239:K239,3))*0.5/3+(LARGE(L239:O239,1)+LARGE(L239:O239,2)+LARGE(L239:O239,3))*0.3/3))</f>
-        <v>0.60666666666666669</v>
+        <v>0.6306666666666666</v>
       </c>
     </row>
     <row r="240" spans="1:16">
-      <c r="A240" s="28" t="s">
-        <v>418</v>
-      </c>
-      <c r="B240" s="28" t="s">
-        <v>419</v>
-      </c>
-      <c r="C240" s="16" t="s">
+      <c r="A240" s="24" t="s">
+        <v>460</v>
+      </c>
+      <c r="B240" s="25" t="s">
+        <v>461</v>
+      </c>
+      <c r="C240" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="D240" s="16">
-        <v>0.79</v>
+      <c r="D240" s="17">
+        <v>0</v>
       </c>
       <c r="E240" s="14">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="F240" s="14">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="G240" s="14">
-        <v>0.68</v>
+        <v>0.93</v>
       </c>
       <c r="H240" s="14">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="I240" s="17">
-        <v>0.19</v>
+        <v>0.6</v>
       </c>
       <c r="J240" s="14">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="K240" s="14">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="L240" s="14">
-        <v>0.54</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M240" s="14">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="N240" s="14">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O240" s="14">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="P240" s="19">
         <f>(((LARGE(D240:G240,1)+LARGE(D240:G240,2)+LARGE(D240:G240,3))*0.2/3+(LARGE(H240:K240,1)+LARGE(H240:K240,2)+LARGE(H240:K240,3))*0.5/3+(LARGE(L240:O240,1)+LARGE(L240:O240,2)+LARGE(L240:O240,3))*0.3/3))</f>
-        <v>0.52600000000000002</v>
+        <v>0.60666666666666669</v>
       </c>
     </row>
     <row r="241" spans="1:16">
-      <c r="A241" s="24" t="s">
-        <v>496</v>
-      </c>
-      <c r="B241" s="25" t="s">
-        <v>497</v>
-      </c>
-      <c r="C241" s="14" t="s">
+      <c r="A241" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="B241" s="27" t="s">
+        <v>419</v>
+      </c>
+      <c r="C241" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="D241" s="17">
-        <v>0</v>
+      <c r="D241" s="16">
+        <v>0.79</v>
       </c>
       <c r="E241" s="14">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="F241" s="14">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="G241" s="14">
-        <v>0.61</v>
-      </c>
-      <c r="H241" s="17">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="H241" s="14">
+        <v>0.26</v>
       </c>
       <c r="I241" s="17">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="J241" s="14">
-        <v>0.71</v>
+        <v>0.22</v>
       </c>
       <c r="K241" s="14">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="L241" s="14">
-        <v>0.57999999999999996</v>
+        <v>0.54</v>
       </c>
       <c r="M241" s="14">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="N241" s="14">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O241" s="14">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="P241" s="19">
         <f>(((LARGE(D241:G241,1)+LARGE(D241:G241,2)+LARGE(D241:G241,3))*0.2/3+(LARGE(H241:K241,1)+LARGE(H241:K241,2)+LARGE(H241:K241,3))*0.5/3+(LARGE(L241:O241,1)+LARGE(L241:O241,2)+LARGE(L241:O241,3))*0.3/3))</f>
-        <v>0.53233333333333333</v>
+        <v>0.52600000000000002</v>
       </c>
     </row>
     <row r="242" spans="1:16">
-      <c r="A242" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="B242" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="C242" s="16" t="s">
+      <c r="A242" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="B242" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="C242" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="D242" s="16">
-        <v>0.66</v>
+      <c r="D242" s="17">
+        <v>0</v>
       </c>
       <c r="E242" s="14">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="F242" s="14">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="G242" s="14">
-        <v>0.78</v>
-      </c>
-      <c r="H242" s="14">
-        <v>0.16</v>
+        <v>0.61</v>
+      </c>
+      <c r="H242" s="17">
+        <v>0</v>
       </c>
       <c r="I242" s="17">
-        <v>0.87</v>
+        <v>0.08</v>
       </c>
       <c r="J242" s="14">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="K242" s="14">
-        <v>0.94</v>
+        <v>0.88</v>
       </c>
       <c r="L242" s="14">
-        <v>0.69</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M242" s="14">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="N242" s="14">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="O242" s="14">
         <v>0</v>
       </c>
       <c r="P242" s="19">
         <f>(((LARGE(D242:G242,1)+LARGE(D242:G242,2)+LARGE(D242:G242,3))*0.2/3+(LARGE(H242:K242,1)+LARGE(H242:K242,2)+LARGE(H242:K242,3))*0.5/3+(LARGE(L242:O242,1)+LARGE(L242:O242,2)+LARGE(L242:O242,3))*0.3/3))</f>
-        <v>0.78799999999999992</v>
+        <v>0.53233333333333333</v>
       </c>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" s="8" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B243" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C243" s="16" t="s">
         <v>420</v>
       </c>
       <c r="D243" s="16">
-        <v>0.69</v>
+        <v>0.66</v>
       </c>
       <c r="E243" s="14">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="F243" s="14">
         <v>0.7</v>
       </c>
       <c r="G243" s="14">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="H243" s="14">
-        <v>0.28000000000000003</v>
+        <v>0.16</v>
       </c>
       <c r="I243" s="17">
-        <v>7.0000000000000007E-2</v>
+        <v>0.87</v>
       </c>
       <c r="J243" s="14">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="K243" s="14">
+        <v>0.94</v>
+      </c>
+      <c r="L243" s="14">
         <v>0.69</v>
       </c>
-      <c r="L243" s="14">
-        <v>0.57999999999999996</v>
-      </c>
       <c r="M243" s="14">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="N243" s="14">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="O243" s="14">
         <v>0</v>
       </c>
       <c r="P243" s="19">
         <f>(((LARGE(D243:G243,1)+LARGE(D243:G243,2)+LARGE(D243:G243,3))*0.2/3+(LARGE(H243:K243,1)+LARGE(H243:K243,2)+LARGE(H243:K243,3))*0.5/3+(LARGE(L243:O243,1)+LARGE(L243:O243,2)+LARGE(L243:O243,3))*0.3/3))</f>
-        <v>0.56499999999999995</v>
+        <v>0.78799999999999992</v>
       </c>
     </row>
     <row r="244" spans="1:16">
-      <c r="A244" t="s">
-        <v>464</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="C244" s="14" t="s">
+      <c r="A244" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="B244" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="C244" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="D244" s="17">
-        <v>0</v>
+      <c r="D244" s="16">
+        <v>0.69</v>
       </c>
       <c r="E244" s="14">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="F244" s="14">
         <v>0.7</v>
       </c>
       <c r="G244" s="14">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="H244" s="14">
-        <v>0.16</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I244" s="17">
-        <v>0.18</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J244" s="14">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="K244" s="14">
-        <v>0.12</v>
+        <v>0.69</v>
       </c>
       <c r="L244" s="14">
-        <v>0.85</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M244" s="14">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="N244" s="14">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="O244" s="14">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="P244" s="19">
         <f>(((LARGE(D244:G244,1)+LARGE(D244:G244,2)+LARGE(D244:G244,3))*0.2/3+(LARGE(H244:K244,1)+LARGE(H244:K244,2)+LARGE(H244:K244,3))*0.5/3+(LARGE(L244:O244,1)+LARGE(L244:O244,2)+LARGE(L244:O244,3))*0.3/3))</f>
-        <v>0.46199999999999997</v>
+        <v>0.56499999999999995</v>
       </c>
     </row>
     <row r="245" spans="1:16">
-      <c r="A245" t="s">
-        <v>457</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>458</v>
+      <c r="A245" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="B245" s="25" t="s">
+        <v>465</v>
       </c>
       <c r="C245" s="14" t="s">
         <v>420</v>
@@ -14154,126 +14098,126 @@
         <v>0</v>
       </c>
       <c r="E245" s="14">
-        <v>0.94</v>
+        <v>0.98</v>
       </c>
       <c r="F245" s="14">
         <v>0.7</v>
       </c>
       <c r="G245" s="14">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="H245" s="14">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I245" s="17">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="J245" s="14">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="K245" s="14">
-        <v>0.78</v>
+        <v>0.12</v>
       </c>
       <c r="L245" s="14">
-        <v>0.54</v>
+        <v>0.85</v>
       </c>
       <c r="M245" s="14">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="N245" s="14">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O245" s="14">
-        <v>0.47</v>
+        <v>0.68</v>
       </c>
       <c r="P245" s="19">
         <f>(((LARGE(D245:G245,1)+LARGE(D245:G245,2)+LARGE(D245:G245,3))*0.2/3+(LARGE(H245:K245,1)+LARGE(H245:K245,2)+LARGE(H245:K245,3))*0.5/3+(LARGE(L245:O245,1)+LARGE(L245:O245,2)+LARGE(L245:O245,3))*0.3/3))</f>
-        <v>0.56033333333333335</v>
+        <v>0.46199999999999997</v>
       </c>
     </row>
     <row r="246" spans="1:16">
-      <c r="A246" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="B246" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="C246" s="16" t="s">
+      <c r="A246" t="s">
+        <v>457</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C246" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="D246" s="16">
-        <v>0.83</v>
+      <c r="D246" s="17">
+        <v>0</v>
       </c>
       <c r="E246" s="14">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="F246" s="14">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="G246" s="14">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="H246" s="14">
-        <v>0.63</v>
+        <v>0.26</v>
       </c>
       <c r="I246" s="17">
-        <v>0.72</v>
+        <v>0.21</v>
       </c>
       <c r="J246" s="14">
-        <v>0.79</v>
-      </c>
-      <c r="K246" s="21"/>
+        <v>0.43</v>
+      </c>
+      <c r="K246" s="14">
+        <v>0.78</v>
+      </c>
       <c r="L246" s="14">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="M246" s="14">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="N246" s="14">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="O246" s="14">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="P246" s="19">
         <f>(((LARGE(D246:G246,1)+LARGE(D246:G246,2)+LARGE(D246:G246,3))*0.2/3+(LARGE(H246:K246,1)+LARGE(H246:K246,2)+LARGE(H246:K246,3))*0.5/3+(LARGE(L246:O246,1)+LARGE(L246:O246,2)+LARGE(L246:O246,3))*0.3/3))</f>
-        <v>0.72799999999999998</v>
+        <v>0.56033333333333335</v>
       </c>
     </row>
     <row r="247" spans="1:16">
       <c r="A247" s="8" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B247" s="8" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C247" s="16" t="s">
         <v>420</v>
       </c>
       <c r="D247" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="E247" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="F247" s="14">
+        <v>0.66</v>
+      </c>
+      <c r="G247" s="14">
+        <v>0</v>
+      </c>
+      <c r="H247" s="14">
+        <v>0.63</v>
+      </c>
+      <c r="I247" s="17">
+        <v>0.72</v>
+      </c>
+      <c r="J247" s="14">
         <v>0.79</v>
       </c>
-      <c r="E247" s="14">
-        <v>0.99</v>
-      </c>
-      <c r="F247" s="14">
-        <v>0.7</v>
-      </c>
-      <c r="G247" s="14">
-        <v>0.93</v>
-      </c>
-      <c r="H247" s="14">
-        <v>0.26</v>
-      </c>
-      <c r="I247" s="17">
-        <v>0.43</v>
-      </c>
-      <c r="J247" s="14">
-        <v>0.62</v>
-      </c>
-      <c r="K247" s="14">
-        <v>0.92</v>
-      </c>
+      <c r="K247" s="21"/>
       <c r="L247" s="14">
         <v>0.72</v>
       </c>
@@ -14286,158 +14230,160 @@
       <c r="O247" s="14">
         <v>0.62</v>
       </c>
-      <c r="P247" s="27">
+      <c r="P247" s="26">
         <f>(((LARGE(D247:G247,1)+LARGE(D247:G247,2)+LARGE(D247:G247,3))*0.2/3+(LARGE(H247:K247,1)+LARGE(H247:K247,2)+LARGE(H247:K247,3))*0.5/3+(LARGE(L247:O247,1)+LARGE(L247:O247,2)+LARGE(L247:O247,3))*0.3/3))</f>
-        <v>0.72099999999999997</v>
+        <v>0.72799999999999998</v>
       </c>
     </row>
     <row r="248" spans="1:16">
       <c r="A248" s="8" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C248" s="16" t="s">
         <v>420</v>
       </c>
       <c r="D248" s="16">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="E248" s="14">
+        <v>0.99</v>
+      </c>
+      <c r="F248" s="14">
+        <v>0.7</v>
+      </c>
+      <c r="G248" s="14">
+        <v>0.93</v>
+      </c>
+      <c r="H248" s="14">
+        <v>0.26</v>
+      </c>
+      <c r="I248" s="17">
+        <v>0.43</v>
+      </c>
+      <c r="J248" s="14">
+        <v>0.62</v>
+      </c>
+      <c r="K248" s="14">
         <v>0.92</v>
       </c>
-      <c r="F248" s="14">
+      <c r="L248" s="14">
+        <v>0.72</v>
+      </c>
+      <c r="M248" s="14">
         <v>0.66</v>
       </c>
-      <c r="G248" s="14">
-        <v>0.88</v>
-      </c>
-      <c r="H248" s="14">
-        <v>0.67</v>
-      </c>
-      <c r="I248" s="17">
-        <v>0.66</v>
-      </c>
-      <c r="J248" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="K248" s="21"/>
-      <c r="L248" s="14">
-        <v>0.69</v>
-      </c>
-      <c r="M248" s="14">
-        <v>0.78</v>
-      </c>
       <c r="N248" s="14">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="O248" s="14">
-        <v>0</v>
-      </c>
-      <c r="P248" s="27">
+        <v>0.62</v>
+      </c>
+      <c r="P248" s="26">
         <f>(((LARGE(D248:G248,1)+LARGE(D248:G248,2)+LARGE(D248:G248,3))*0.2/3+(LARGE(H248:K248,1)+LARGE(H248:K248,2)+LARGE(H248:K248,3))*0.5/3+(LARGE(L248:O248,1)+LARGE(L248:O248,2)+LARGE(L248:O248,3))*0.3/3))</f>
-        <v>0.71366666666666667</v>
+        <v>0.72099999999999997</v>
       </c>
     </row>
     <row r="249" spans="1:16">
       <c r="A249" s="8" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B249" s="8" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C249" s="16" t="s">
         <v>420</v>
       </c>
       <c r="D249" s="16">
-        <v>0.74</v>
+        <v>0.81</v>
       </c>
       <c r="E249" s="14">
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
       <c r="F249" s="14">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="G249" s="14">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="H249" s="14">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="I249" s="17">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="J249" s="14">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="K249" s="14">
-        <v>0.47</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="K249" s="21"/>
       <c r="L249" s="14">
-        <v>0.72</v>
+        <v>0.69</v>
       </c>
       <c r="M249" s="14">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="N249" s="14">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="O249" s="14">
-        <v>0.62</v>
-      </c>
-      <c r="P249" s="27">
+        <v>0</v>
+      </c>
+      <c r="P249" s="26">
         <f>(((LARGE(D249:G249,1)+LARGE(D249:G249,2)+LARGE(D249:G249,3))*0.2/3+(LARGE(H249:K249,1)+LARGE(H249:K249,2)+LARGE(H249:K249,3))*0.5/3+(LARGE(L249:O249,1)+LARGE(L249:O249,2)+LARGE(L249:O249,3))*0.3/3))</f>
-        <v>0.61266666666666658</v>
+        <v>0.71366666666666667</v>
       </c>
     </row>
     <row r="250" spans="1:16">
       <c r="A250" s="8" t="s">
-        <v>26</v>
+        <v>431</v>
       </c>
       <c r="B250" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C250" s="16" t="s">
         <v>420</v>
       </c>
       <c r="D250" s="16">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="E250" s="14">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="F250" s="14">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="G250" s="14">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="H250" s="14">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="I250" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="J250" s="14">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="K250" s="14">
+        <v>0.47</v>
+      </c>
+      <c r="L250" s="14">
+        <v>0.72</v>
+      </c>
+      <c r="M250" s="14">
         <v>0.66</v>
       </c>
-      <c r="J250" s="14">
-        <v>0.49</v>
-      </c>
-      <c r="K250" s="21"/>
-      <c r="L250" s="14">
-        <v>0.54</v>
-      </c>
-      <c r="M250" s="14">
-        <v>0.5</v>
-      </c>
       <c r="N250" s="14">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="O250" s="14">
-        <v>0.47</v>
-      </c>
-      <c r="P250" s="27">
+        <v>0.62</v>
+      </c>
+      <c r="P250" s="26">
         <f>(((LARGE(D250:G250,1)+LARGE(D250:G250,2)+LARGE(D250:G250,3))*0.2/3+(LARGE(H250:K250,1)+LARGE(H250:K250,2)+LARGE(H250:K250,3))*0.5/3+(LARGE(L250:O250,1)+LARGE(L250:O250,2)+LARGE(L250:O250,3))*0.3/3))</f>
-        <v>0.58433333333333326</v>
+        <v>0.61266666666666658</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14445,107 +14391,105 @@
         <v>26</v>
       </c>
       <c r="B251" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C251" s="16" t="s">
         <v>420</v>
       </c>
       <c r="D251" s="16">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="E251" s="14">
         <v>1</v>
       </c>
       <c r="F251" s="14">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="G251" s="14">
         <v>0</v>
       </c>
       <c r="H251" s="14">
-        <v>0.63</v>
+        <v>0.44</v>
       </c>
       <c r="I251" s="17">
-        <v>0.55000000000000004</v>
+        <v>0.66</v>
       </c>
       <c r="J251" s="14">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="K251" s="21"/>
       <c r="L251" s="14">
-        <v>0.69</v>
+        <v>0.54</v>
       </c>
       <c r="M251" s="14">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="N251" s="14">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="O251" s="14">
-        <v>0</v>
-      </c>
-      <c r="P251" s="27">
+        <v>0.47</v>
+      </c>
+      <c r="P251" s="26">
         <f>(((LARGE(D251:G251,1)+LARGE(D251:G251,2)+LARGE(D251:G251,3))*0.2/3+(LARGE(H251:K251,1)+LARGE(H251:K251,2)+LARGE(H251:K251,3))*0.5/3+(LARGE(L251:O251,1)+LARGE(L251:O251,2)+LARGE(L251:O251,3))*0.3/3))</f>
-        <v>0.65800000000000003</v>
+        <v>0.58433333333333326</v>
       </c>
     </row>
     <row r="252" spans="1:16">
-      <c r="A252" t="s">
-        <v>462</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>463</v>
-      </c>
-